--- a/playoffs-example-large.xlsx
+++ b/playoffs-example-large.xlsx
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="301">
   <si>
     <t>Elimination Round 1</t>
   </si>
@@ -94,13 +94,16 @@
     <t>Display Name</t>
   </si>
   <si>
+    <t>Metadata</t>
+  </si>
+  <si>
     <t>Kevin Clark</t>
   </si>
   <si>
     <t>Team Alpha</t>
   </si>
   <si>
-    <t>K. CLARK</t>
+    <t>CLARK</t>
   </si>
   <si>
     <t>Luke Rodriguez</t>
@@ -109,7 +112,7 @@
     <t>Team Beta</t>
   </si>
   <si>
-    <t>L. RODRIGUEZ</t>
+    <t>RODRIGUEZ</t>
   </si>
   <si>
     <t>Michael Lewis</t>
@@ -118,7 +121,7 @@
     <t>Team Gamma</t>
   </si>
   <si>
-    <t>M. LEWIS</t>
+    <t>LEWIS</t>
   </si>
   <si>
     <t>Nathan Lee</t>
@@ -127,7 +130,7 @@
     <t>Team Delta</t>
   </si>
   <si>
-    <t>N. LEE</t>
+    <t>LEE</t>
   </si>
   <si>
     <t>Oliver Walker</t>
@@ -136,103 +139,103 @@
     <t>Team Epsilon</t>
   </si>
   <si>
-    <t>O. WALKER</t>
+    <t>WALKER</t>
   </si>
   <si>
     <t>Paul Hall</t>
   </si>
   <si>
-    <t>P. HALL</t>
+    <t>HALL</t>
   </si>
   <si>
     <t>Quentin Allen</t>
   </si>
   <si>
-    <t>Q. ALLEN</t>
+    <t>ALLEN</t>
   </si>
   <si>
     <t>Robert Young</t>
   </si>
   <si>
-    <t>R. YOUNG</t>
+    <t>YOUNG</t>
   </si>
   <si>
     <t>Steven Hernandez</t>
   </si>
   <si>
-    <t>S. HERNANDEZ</t>
+    <t>HERNANDEZ</t>
   </si>
   <si>
     <t>Thomas King</t>
   </si>
   <si>
-    <t>T. KING</t>
+    <t>KING</t>
   </si>
   <si>
     <t>Uriel Wright</t>
   </si>
   <si>
-    <t>U. WRIGHT</t>
+    <t>WRIGHT</t>
   </si>
   <si>
     <t>Victor Lopez</t>
   </si>
   <si>
-    <t>V. LOPEZ</t>
+    <t>LOPEZ</t>
   </si>
   <si>
     <t>William Hill</t>
   </si>
   <si>
-    <t>W. HILL</t>
+    <t>HILL</t>
   </si>
   <si>
     <t>Xavier Scott</t>
   </si>
   <si>
-    <t>X. SCOTT</t>
+    <t>SCOTT</t>
   </si>
   <si>
     <t>Yosef Green</t>
   </si>
   <si>
-    <t>Y. GREEN</t>
+    <t>GREEN</t>
   </si>
   <si>
     <t>Zachary Adams</t>
   </si>
   <si>
-    <t>Z. ADAMS</t>
+    <t>ADAMS</t>
   </si>
   <si>
     <t>Aaron Thompson</t>
   </si>
   <si>
-    <t>A. THOMPSON</t>
+    <t>THOMPSON</t>
   </si>
   <si>
     <t>Benjamin Evans</t>
   </si>
   <si>
-    <t>B. EVANS</t>
+    <t>EVANS</t>
   </si>
   <si>
     <t>Caleb Wilson</t>
   </si>
   <si>
-    <t>C. WILSON</t>
+    <t>WILSON</t>
   </si>
   <si>
     <t>Dylan Moore</t>
   </si>
   <si>
-    <t>D. MOORE</t>
+    <t>MOORE</t>
   </si>
   <si>
     <t>Elijah Taylor</t>
   </si>
   <si>
-    <t>E. TAYLOR</t>
+    <t>TAYLOR</t>
   </si>
   <si>
     <t>Finn Anderson</t>
@@ -241,7 +244,7 @@
     <t>Team Zeta</t>
   </si>
   <si>
-    <t>F. ANDERSON</t>
+    <t>ANDERSON</t>
   </si>
   <si>
     <t>Gabriel Thomas</t>
@@ -250,7 +253,7 @@
     <t>Team Eta</t>
   </si>
   <si>
-    <t>G. THOMAS</t>
+    <t>THOMAS</t>
   </si>
   <si>
     <t>Hudson Jackson</t>
@@ -259,7 +262,7 @@
     <t>Team Theta</t>
   </si>
   <si>
-    <t>H. JACKSON</t>
+    <t>JACKSON</t>
   </si>
   <si>
     <t>Isaac White</t>
@@ -268,7 +271,7 @@
     <t>Team Iota</t>
   </si>
   <si>
-    <t>I. WHITE</t>
+    <t>WHITE</t>
   </si>
   <si>
     <t>Jackson Harris</t>
@@ -277,157 +280,118 @@
     <t>Team Kappa</t>
   </si>
   <si>
-    <t>J. HARRIS</t>
+    <t>HARRIS</t>
   </si>
   <si>
     <t>Kaden Martin</t>
   </si>
   <si>
-    <t>K. MARTIN</t>
+    <t>MARTIN</t>
   </si>
   <si>
     <t>Liam Thompson</t>
   </si>
   <si>
-    <t>L. THOMPSON</t>
-  </si>
-  <si>
     <t>Mason Martinez</t>
   </si>
   <si>
-    <t>M. MARTINEZ</t>
+    <t>MARTINEZ</t>
   </si>
   <si>
     <t>Nolan Clark</t>
   </si>
   <si>
-    <t>N. CLARK</t>
-  </si>
-  <si>
     <t>Owen Rodriguez</t>
   </si>
   <si>
-    <t>O. RODRIGUEZ</t>
-  </si>
-  <si>
     <t>Parker Lewis</t>
   </si>
   <si>
-    <t>P. LEWIS</t>
-  </si>
-  <si>
     <t>Quinn Walker</t>
   </si>
   <si>
-    <t>Q. WALKER</t>
-  </si>
-  <si>
     <t>Ryan Hall</t>
   </si>
   <si>
-    <t>R. HALL</t>
-  </si>
-  <si>
     <t>Sebastian Allen</t>
   </si>
   <si>
-    <t>S. ALLEN</t>
-  </si>
-  <si>
     <t>Tristan Young</t>
   </si>
   <si>
-    <t>T. YOUNG</t>
-  </si>
-  <si>
     <t>Ulysses Hernandez</t>
   </si>
   <si>
-    <t>U. HERNANDEZ</t>
-  </si>
-  <si>
     <t>Vincent King</t>
   </si>
   <si>
-    <t>V. KING</t>
-  </si>
-  <si>
     <t>William Wright</t>
   </si>
   <si>
-    <t>W. WRIGHT</t>
-  </si>
-  <si>
     <t>Xavier Lopez</t>
   </si>
   <si>
-    <t>X. LOPEZ</t>
-  </si>
-  <si>
     <t>Yosef Hill</t>
   </si>
   <si>
-    <t>Y. HILL</t>
-  </si>
-  <si>
     <t>Arthur Conan</t>
   </si>
   <si>
-    <t>A. CONAN</t>
+    <t>CONAN</t>
   </si>
   <si>
     <t>Bram Stoker</t>
   </si>
   <si>
-    <t>B. STOKER</t>
+    <t>STOKER</t>
   </si>
   <si>
     <t>Charles Dickens</t>
   </si>
   <si>
-    <t>C. DICKENS</t>
+    <t>DICKENS</t>
   </si>
   <si>
     <t>Daniel Defoe</t>
   </si>
   <si>
-    <t>D. DEFOE</t>
+    <t>DEFOE</t>
   </si>
   <si>
     <t>Emily Bronte</t>
   </si>
   <si>
-    <t>E. BRONTE</t>
+    <t>BRONTE</t>
   </si>
   <si>
     <t>Fyodor Dostoevsky</t>
   </si>
   <si>
-    <t>F. DOSTOEVSKY</t>
+    <t>DOSTOEVSKY</t>
   </si>
   <si>
     <t>George Orwell</t>
   </si>
   <si>
-    <t>G. ORWELL</t>
+    <t>ORWELL</t>
   </si>
   <si>
     <t>Herman Melville</t>
   </si>
   <si>
-    <t>H. MELVILLE</t>
+    <t>MELVILLE</t>
   </si>
   <si>
     <t>Isaac Asimov</t>
   </si>
   <si>
-    <t>I. ASIMOV</t>
+    <t>ASIMOV</t>
   </si>
   <si>
     <t>Jane Austen</t>
   </si>
   <si>
-    <t>J. AUSTEN</t>
+    <t>AUSTEN</t>
   </si>
   <si>
     <t>Kurt Vonnegut</t>
@@ -436,7 +400,7 @@
     <t>Team Lambda</t>
   </si>
   <si>
-    <t>K. VONNEGUT</t>
+    <t>VONNEGUT</t>
   </si>
   <si>
     <t>Lewis Carroll</t>
@@ -445,7 +409,7 @@
     <t>Team Mu</t>
   </si>
   <si>
-    <t>L. CARROLL</t>
+    <t>CARROLL</t>
   </si>
   <si>
     <t>Mary Shelley</t>
@@ -454,7 +418,7 @@
     <t>Team Nu</t>
   </si>
   <si>
-    <t>M. SHELLEY</t>
+    <t>SHELLEY</t>
   </si>
   <si>
     <t>Nathaniel Hawthorne</t>
@@ -463,7 +427,7 @@
     <t>Team Xi</t>
   </si>
   <si>
-    <t>N. HAWTHORNE</t>
+    <t>HAWTHORNE</t>
   </si>
   <si>
     <t>Oscar Wilde</t>
@@ -472,7 +436,7 @@
     <t>Team Omicron</t>
   </si>
   <si>
-    <t>O. WILDE</t>
+    <t>WILDE</t>
   </si>
   <si>
     <t>Philip K Dick</t>
@@ -481,7 +445,7 @@
     <t>Team Pi</t>
   </si>
   <si>
-    <t>P. DICK</t>
+    <t>DICK</t>
   </si>
   <si>
     <t>Quentin Blake</t>
@@ -490,7 +454,7 @@
     <t>Team Rho</t>
   </si>
   <si>
-    <t>Q. BLAKE</t>
+    <t>BLAKE</t>
   </si>
   <si>
     <t>Ray Bradbury</t>
@@ -499,7 +463,7 @@
     <t>Team Sigma</t>
   </si>
   <si>
-    <t>R. BRADBURY</t>
+    <t>BRADBURY</t>
   </si>
   <si>
     <t>Sylvia Plath</t>
@@ -508,7 +472,7 @@
     <t>Team Tau</t>
   </si>
   <si>
-    <t>S. PLATH</t>
+    <t>PLATH</t>
   </si>
   <si>
     <t>Thomas Hardy</t>
@@ -517,7 +481,7 @@
     <t>Team Upsilon</t>
   </si>
   <si>
-    <t>T. HARDY</t>
+    <t>HARDY</t>
   </si>
   <si>
     <t>Ursula K Le Guin</t>
@@ -526,7 +490,7 @@
     <t>Team Phi</t>
   </si>
   <si>
-    <t>U. GUIN</t>
+    <t>LE GUIN</t>
   </si>
   <si>
     <t>Virginia Woolf</t>
@@ -535,7 +499,7 @@
     <t>Team Chi</t>
   </si>
   <si>
-    <t>V. WOOLF</t>
+    <t>WOOLF</t>
   </si>
   <si>
     <t>William Shakespeare</t>
@@ -544,7 +508,7 @@
     <t>Team Psi</t>
   </si>
   <si>
-    <t>W. SHAKESPEARE</t>
+    <t>SHAKESPEARE</t>
   </si>
   <si>
     <t>Xavier Herbert</t>
@@ -553,97 +517,91 @@
     <t>Team Omega</t>
   </si>
   <si>
-    <t>X. HERBERT</t>
+    <t>HERBERT</t>
   </si>
   <si>
     <t>Yann Martel</t>
   </si>
   <si>
-    <t>Y. MARTEL</t>
+    <t>MARTEL</t>
   </si>
   <si>
     <t>Albus Dumbledore</t>
   </si>
   <si>
-    <t>A. DUMBLEDORE</t>
+    <t>DUMBLEDORE</t>
   </si>
   <si>
     <t>Bilbo Baggins</t>
   </si>
   <si>
-    <t>B. BAGGINS</t>
+    <t>BAGGINS</t>
   </si>
   <si>
     <t>Cersei Lannister</t>
   </si>
   <si>
-    <t>C. LANNISTER</t>
+    <t>LANNISTER</t>
   </si>
   <si>
     <t>Daenerys Targaryen</t>
   </si>
   <si>
-    <t>D. TARGARYEN</t>
+    <t>TARGARYEN</t>
   </si>
   <si>
     <t>Eddard Stark</t>
   </si>
   <si>
-    <t>E. STARK</t>
+    <t>STARK</t>
   </si>
   <si>
     <t>Frodo Baggins</t>
   </si>
   <si>
-    <t>F. BAGGINS</t>
-  </si>
-  <si>
     <t>Gandalf The Grey</t>
   </si>
   <si>
-    <t>G. GREY</t>
+    <t>GANDALF</t>
   </si>
   <si>
     <t>Hermione Granger</t>
   </si>
   <si>
-    <t>H. GRANGER</t>
+    <t>GRANGER</t>
   </si>
   <si>
     <t>Inigo Montoya</t>
   </si>
   <si>
-    <t>I. MONTOYA</t>
+    <t>MONTOYA</t>
   </si>
   <si>
     <t>Jon Snow</t>
   </si>
   <si>
-    <t>J. SNOW</t>
+    <t>SNOW</t>
   </si>
   <si>
     <t>Katniss Everdeen</t>
   </si>
   <si>
-    <t>K. EVERDEEN</t>
+    <t>EVERDEEN</t>
   </si>
   <si>
     <t>Legolas Greenleaf</t>
   </si>
   <si>
-    <t>L. GREENLEAF</t>
+    <t>GREENLEAF</t>
   </si>
   <si>
     <t>Moby Dick</t>
   </si>
   <si>
-    <t>M. DICK</t>
-  </si>
-  <si>
     <t>Neville Longbottom</t>
   </si>
   <si>
-    <t>N. LONGBOTTOM</t>
+    <t>LONGBOTTOM</t>
   </si>
   <si>
     <t>Othello</t>
@@ -655,33 +613,30 @@
     <t>Petyr Baelish</t>
   </si>
   <si>
-    <t>P. BAELISH</t>
+    <t>BAELISH</t>
   </si>
   <si>
     <t>Quirinus Quirrell</t>
   </si>
   <si>
-    <t>Q. QUIRRELL</t>
+    <t>QUIRRELL</t>
   </si>
   <si>
     <t>Ron Weasley</t>
   </si>
   <si>
-    <t>R. WEASLEY</t>
+    <t>WEASLEY</t>
   </si>
   <si>
     <t>Samwise Gamgee</t>
   </si>
   <si>
-    <t>S. GAMGEE</t>
+    <t>GAMGEE</t>
   </si>
   <si>
     <t>Tyrion Lannister</t>
   </si>
   <si>
-    <t>T. LANNISTER</t>
-  </si>
-  <si>
     <t>Ulysses</t>
   </si>
   <si>
@@ -697,13 +652,13 @@
     <t>Willy Wonka</t>
   </si>
   <si>
-    <t>W. WONKA</t>
+    <t>WONKA</t>
   </si>
   <si>
     <t>Xaro Xhoan Daxos</t>
   </si>
   <si>
-    <t>X. DAXOS</t>
+    <t>DAXOS</t>
   </si>
   <si>
     <t>Ygritte</t>
@@ -1247,7 +1202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="120">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true"/>
@@ -1322,276 +1277,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1813,8 +1498,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="true"/>
   <cols>
     <col customWidth="true" max="1" min="1" width="15"/>
-    <col customWidth="true" max="4" min="2" width="30"/>
-    <col customWidth="true" max="26" min="5" width="10.6640625"/>
+    <col customWidth="true" max="26" min="2" width="30"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="12.75" customHeight="true">
@@ -1830,19 +1514,22 @@
       <c r="D1" t="s">
         <v>14</v>
       </c>
+      <c r="E1" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="2" spans="1:2" ht="12.75" customHeight="true">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="12.75" customHeight="true">
@@ -1850,13 +1537,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="12.75" customHeight="true">
@@ -1864,13 +1551,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="12.75" customHeight="true">
@@ -1878,13 +1565,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="12.75" customHeight="true">
@@ -1892,13 +1579,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="12.75" customHeight="true">
@@ -1906,13 +1593,13 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="12.75" customHeight="true">
@@ -1920,13 +1607,13 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="12.75" customHeight="true">
@@ -1934,13 +1621,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="12.75" customHeight="true">
@@ -1948,13 +1635,13 @@
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="12.75" customHeight="true">
@@ -1962,13 +1649,13 @@
         <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="12.75" customHeight="true">
@@ -1976,13 +1663,13 @@
         <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="12.75" customHeight="true">
@@ -1990,13 +1677,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="12.75" customHeight="true">
@@ -2004,13 +1691,13 @@
         <v>12</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="12.75" customHeight="true">
@@ -2018,13 +1705,13 @@
         <v>13</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D15" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="12.75" customHeight="true">
@@ -2032,13 +1719,13 @@
         <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C16" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="12.75" customHeight="true">
@@ -2046,13 +1733,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C17" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="12.75" customHeight="true">
@@ -2060,13 +1747,13 @@
         <v>16</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D18" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="12.75" customHeight="true">
@@ -2074,13 +1761,13 @@
         <v>17</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="12.75" customHeight="true">
@@ -2088,13 +1775,13 @@
         <v>18</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C20" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D20" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="12.75" customHeight="true">
@@ -2102,13 +1789,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C21" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D21" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="12.75" customHeight="true">
@@ -2116,13 +1803,13 @@
         <v>20</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C22" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D22" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="12.75" customHeight="true">
@@ -2130,13 +1817,13 @@
         <v>21</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C23" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D23" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="12.75" customHeight="true">
@@ -2144,13 +1831,13 @@
         <v>22</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C24" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D24" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="12.75" customHeight="true">
@@ -2158,13 +1845,13 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C25" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D25" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="12.75" customHeight="true">
@@ -2172,13 +1859,13 @@
         <v>24</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C26" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D26" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="12.75" customHeight="true">
@@ -2186,13 +1873,13 @@
         <v>25</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C27" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D27" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="12.75" customHeight="true">
@@ -2200,13 +1887,13 @@
         <v>26</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D28" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="12.75" customHeight="true">
@@ -2214,13 +1901,13 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C29" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D29" t="s">
-        <v>80</v>
+        <v>54</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="12.75" customHeight="true">
@@ -2231,7 +1918,7 @@
         <v>81</v>
       </c>
       <c r="C30" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D30" t="s">
         <v>82</v>
@@ -2245,10 +1932,10 @@
         <v>83</v>
       </c>
       <c r="C31" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D31" t="s">
-        <v>84</v>
+        <v>18</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="12.75" customHeight="true">
@@ -2256,13 +1943,13 @@
         <v>30</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C32" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D32" t="s">
-        <v>86</v>
+        <v>21</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="12.75" customHeight="true">
@@ -2270,13 +1957,13 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C33" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D33" t="s">
-        <v>88</v>
+        <v>24</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="12.75" customHeight="true">
@@ -2284,13 +1971,13 @@
         <v>32</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C34" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D34" t="s">
-        <v>90</v>
+        <v>30</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="12.75" customHeight="true">
@@ -2298,13 +1985,13 @@
         <v>33</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C35" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D35" t="s">
-        <v>92</v>
+        <v>32</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="12.75" customHeight="true">
@@ -2312,13 +1999,13 @@
         <v>34</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C36" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D36" t="s">
-        <v>94</v>
+        <v>34</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="12.75" customHeight="true">
@@ -2326,13 +2013,13 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C37" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D37" t="s">
-        <v>96</v>
+        <v>36</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="12.75" customHeight="true">
@@ -2340,13 +2027,13 @@
         <v>36</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C38" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D38" t="s">
-        <v>98</v>
+        <v>38</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="12.75" customHeight="true">
@@ -2354,13 +2041,13 @@
         <v>37</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="C39" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D39" t="s">
-        <v>100</v>
+        <v>40</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="12.75" customHeight="true">
@@ -2368,13 +2055,13 @@
         <v>38</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="C40" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D40" t="s">
-        <v>102</v>
+        <v>42</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="12.75" customHeight="true">
@@ -2382,13 +2069,13 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="C41" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D41" t="s">
-        <v>104</v>
+        <v>44</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="12.75" customHeight="true">
@@ -2396,13 +2083,13 @@
         <v>40</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="C42" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D42" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="12.75" customHeight="true">
@@ -2410,13 +2097,13 @@
         <v>41</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="C43" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D43" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="12.75" customHeight="true">
@@ -2424,13 +2111,13 @@
         <v>42</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="C44" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D44" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="12.75" customHeight="true">
@@ -2438,13 +2125,13 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="C45" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D45" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="12.75" customHeight="true">
@@ -2452,13 +2139,13 @@
         <v>44</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="C46" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D46" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="12.75" customHeight="true">
@@ -2466,13 +2153,13 @@
         <v>45</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="C47" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D47" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="12.75" customHeight="true">
@@ -2480,13 +2167,13 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="C48" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D48" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
     </row>
     <row r="49" ht="12.75" customHeight="true">
@@ -2494,13 +2181,13 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="C49" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D49" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
     </row>
     <row r="50" ht="12.75" customHeight="true">
@@ -2508,13 +2195,13 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="C50" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D50" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
     </row>
     <row r="51" ht="12.75" customHeight="true">
@@ -2522,13 +2209,13 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="C51" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D51" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
     </row>
     <row r="52" ht="12.75" customHeight="true">
@@ -2536,13 +2223,13 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="C52" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D52" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
     </row>
     <row r="53" ht="12.75" customHeight="true">
@@ -2550,13 +2237,13 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="C53" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="D53" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
     </row>
     <row r="54" ht="12.75" customHeight="true">
@@ -2564,13 +2251,13 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="C54" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="D54" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
     </row>
     <row r="55" ht="12.75" customHeight="true">
@@ -2578,13 +2265,13 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="C55" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="D55" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
     </row>
     <row r="56" ht="12.75" customHeight="true">
@@ -2592,13 +2279,13 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="C56" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="D56" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
     </row>
     <row r="57" ht="12.75" customHeight="true">
@@ -2606,13 +2293,13 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="C57" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="D57" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="58" ht="12.75" customHeight="true">
@@ -2620,13 +2307,13 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="C58" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="D58" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
     </row>
     <row r="59" ht="12.75" customHeight="true">
@@ -2634,13 +2321,13 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="C59" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="D59" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="60" ht="12.75" customHeight="true">
@@ -2648,13 +2335,13 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="C60" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="D60" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
     </row>
     <row r="61" ht="12.75" customHeight="true">
@@ -2662,13 +2349,13 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="C61" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="D61" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
     </row>
     <row r="62" ht="12.75" customHeight="true">
@@ -2676,13 +2363,13 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="C62" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="D62" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
     </row>
     <row r="63" ht="12.75" customHeight="true">
@@ -2690,13 +2377,13 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="C63" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="D63" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
     </row>
     <row r="64" ht="12.75" customHeight="true">
@@ -2704,13 +2391,13 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="C64" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="D64" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
     </row>
     <row r="65" ht="12.75" customHeight="true">
@@ -2718,13 +2405,13 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="C65" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="D65" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="66" ht="12.75" customHeight="true">
@@ -2732,13 +2419,13 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="C66" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D66" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
     </row>
     <row r="67" ht="12.75" customHeight="true">
@@ -2746,13 +2433,13 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="C67" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D67" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
     </row>
     <row r="68" ht="12.75" customHeight="true">
@@ -2760,13 +2447,13 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="C68" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D68" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
     </row>
     <row r="69" ht="12.75" customHeight="true">
@@ -2774,13 +2461,13 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="C69" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D69" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
     </row>
     <row r="70" ht="12.75" customHeight="true">
@@ -2788,13 +2475,13 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="C70" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D70" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
     </row>
     <row r="71" ht="12.75" customHeight="true">
@@ -2802,13 +2489,13 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="C71" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D71" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
     </row>
     <row r="72" ht="12.75" customHeight="true">
@@ -2816,13 +2503,13 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="C72" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D72" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
     </row>
     <row r="73" ht="12.75" customHeight="true">
@@ -2830,13 +2517,13 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="C73" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D73" t="s">
-        <v>182</v>
+        <v>162</v>
       </c>
     </row>
     <row r="74" ht="12.75" customHeight="true">
@@ -2844,13 +2531,13 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="C74" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D74" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
     </row>
     <row r="75" ht="12.75" customHeight="true">
@@ -2858,13 +2545,13 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="C75" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D75" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
     </row>
     <row r="76" ht="12.75" customHeight="true">
@@ -2872,13 +2559,13 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="C76" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D76" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
     </row>
     <row r="77" ht="12.75" customHeight="true">
@@ -2886,13 +2573,13 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="C77" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D77" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
     </row>
     <row r="78" ht="12.75" customHeight="true">
@@ -2900,13 +2587,13 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="C78" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="D78" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
     </row>
     <row r="79" ht="12.75" customHeight="true">
@@ -2914,13 +2601,13 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="C79" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="D79" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
     </row>
     <row r="80" ht="12.75" customHeight="true">
@@ -2928,13 +2615,13 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="C80" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="D80" t="s">
-        <v>196</v>
+        <v>132</v>
       </c>
     </row>
     <row r="81" ht="12.75" customHeight="true">
@@ -2942,13 +2629,13 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
       <c r="C81" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="D81" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
     </row>
     <row r="82" ht="12.75" customHeight="true">
@@ -2956,13 +2643,13 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="C82" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="D82" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
     </row>
     <row r="83" ht="12.75" customHeight="true">
@@ -2970,13 +2657,13 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>201</v>
+        <v>187</v>
       </c>
       <c r="C83" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="D83" t="s">
-        <v>202</v>
+        <v>188</v>
       </c>
     </row>
     <row r="84" ht="12.75" customHeight="true">
@@ -2984,13 +2671,13 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="C84" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="D84" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
     </row>
     <row r="85" ht="12.75" customHeight="true">
@@ -2998,13 +2685,13 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="C85" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="D85" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="86" ht="12.75" customHeight="true">
@@ -3012,13 +2699,13 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="C86" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="D86" t="s">
-        <v>208</v>
+        <v>194</v>
       </c>
     </row>
     <row r="87" ht="12.75" customHeight="true">
@@ -3026,13 +2713,13 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="C87" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="D87" t="s">
-        <v>210</v>
+        <v>164</v>
       </c>
     </row>
     <row r="88" ht="12.75" customHeight="true">
@@ -3040,13 +2727,13 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>211</v>
+        <v>196</v>
       </c>
       <c r="C88" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="D88" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
     </row>
     <row r="89" ht="12.75" customHeight="true">
@@ -3054,13 +2741,13 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="C89" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="D89" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
     </row>
     <row r="90" ht="12.75" customHeight="true">
@@ -3068,13 +2755,13 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="C90" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="D90" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
     </row>
     <row r="91" ht="12.75" customHeight="true">
@@ -3082,13 +2769,13 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="C91" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D91" t="s">
-        <v>218</v>
+        <v>203</v>
       </c>
     </row>
     <row r="92" ht="12.75" customHeight="true">
@@ -3096,13 +2783,13 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="C92" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D92" t="s">
-        <v>220</v>
+        <v>205</v>
       </c>
     </row>
     <row r="93" ht="12.75" customHeight="true"/>
@@ -4031,11 +3718,9 @@
     <col customWidth="true" max="2" min="2" width="10"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2"/>
     <row r="3">
       <c r="E3" s="24" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
@@ -4054,7 +3739,7 @@
     </row>
     <row r="7">
       <c r="E7" s="24" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F7" s="23"/>
       <c r="G7" s="20"/>
@@ -4075,7 +3760,7 @@
     </row>
     <row r="11">
       <c r="E11" s="24" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I11" s="20"/>
       <c r="K11" s="20"/>
@@ -4096,7 +3781,7 @@
     </row>
     <row r="14">
       <c r="C14" s="24" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G14" s="20"/>
       <c r="K14" s="20"/>
@@ -4112,7 +3797,7 @@
     </row>
     <row r="16">
       <c r="C16" s="24" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D16" s="23"/>
       <c r="E16" s="20"/>
@@ -4128,7 +3813,7 @@
     </row>
     <row r="19">
       <c r="E19" s="24" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K19" s="20"/>
     </row>
@@ -4145,7 +3830,7 @@
     </row>
     <row r="22">
       <c r="C22" s="24" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G22" s="20"/>
       <c r="H22" s="22"/>
@@ -4164,7 +3849,7 @@
     </row>
     <row r="24">
       <c r="C24" s="24" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D24" s="23"/>
       <c r="E24" s="20"/>
@@ -4183,7 +3868,7 @@
     </row>
     <row r="27">
       <c r="E27" s="24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I27" s="20"/>
     </row>
@@ -4201,7 +3886,7 @@
     </row>
     <row r="30">
       <c r="C30" s="24" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G30" s="20"/>
     </row>
@@ -4215,7 +3900,7 @@
     </row>
     <row r="32">
       <c r="C32" s="24" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D32" s="23"/>
       <c r="E32" s="20"/>
@@ -4238,11 +3923,9 @@
     <col customWidth="true" max="2" min="2" width="10"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2"/>
     <row r="3">
       <c r="E3" s="24" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4">
@@ -4261,7 +3944,7 @@
     </row>
     <row r="7">
       <c r="E7" s="24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F7" s="23"/>
       <c r="G7" s="20"/>
@@ -4282,7 +3965,7 @@
     </row>
     <row r="11">
       <c r="E11" s="24" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I11" s="20"/>
       <c r="K11" s="20"/>
@@ -4303,7 +3986,7 @@
     </row>
     <row r="14">
       <c r="C14" s="24" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G14" s="20"/>
       <c r="K14" s="20"/>
@@ -4319,7 +4002,7 @@
     </row>
     <row r="16">
       <c r="C16" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D16" s="23"/>
       <c r="E16" s="20"/>
@@ -4335,7 +4018,7 @@
     </row>
     <row r="19">
       <c r="E19" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K19" s="20"/>
     </row>
@@ -4352,7 +4035,7 @@
     </row>
     <row r="22">
       <c r="C22" s="24" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G22" s="20"/>
       <c r="H22" s="22"/>
@@ -4371,7 +4054,7 @@
     </row>
     <row r="24">
       <c r="C24" s="24" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D24" s="23"/>
       <c r="E24" s="20"/>
@@ -4390,7 +4073,7 @@
     </row>
     <row r="27">
       <c r="E27" s="24" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I27" s="20"/>
     </row>
@@ -4408,7 +4091,7 @@
     </row>
     <row r="30">
       <c r="C30" s="24" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G30" s="20"/>
     </row>
@@ -4422,7 +4105,7 @@
     </row>
     <row r="32">
       <c r="C32" s="24" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D32" s="23"/>
       <c r="E32" s="20"/>
@@ -4445,11 +4128,9 @@
     <col customWidth="true" max="2" min="2" width="10"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2"/>
     <row r="3">
       <c r="E3" s="24" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4">
@@ -4468,7 +4149,7 @@
     </row>
     <row r="7">
       <c r="E7" s="24" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F7" s="23"/>
       <c r="G7" s="20"/>
@@ -4489,7 +4170,7 @@
     </row>
     <row r="11">
       <c r="E11" s="24" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I11" s="20"/>
       <c r="K11" s="20"/>
@@ -4510,7 +4191,7 @@
     </row>
     <row r="14">
       <c r="C14" s="24" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G14" s="20"/>
       <c r="K14" s="20"/>
@@ -4526,7 +4207,7 @@
     </row>
     <row r="16">
       <c r="C16" s="24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D16" s="23"/>
       <c r="E16" s="20"/>
@@ -4542,7 +4223,7 @@
     </row>
     <row r="19">
       <c r="E19" s="24" t="s">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="K19" s="20"/>
     </row>
@@ -4578,7 +4259,7 @@
     </row>
     <row r="24">
       <c r="C24" s="24" t="s">
-        <v>84</v>
+        <v>18</v>
       </c>
       <c r="D24" s="23"/>
       <c r="E24" s="20"/>
@@ -4597,7 +4278,7 @@
     </row>
     <row r="27">
       <c r="E27" s="24" t="s">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="I27" s="20"/>
     </row>
@@ -4615,7 +4296,7 @@
     </row>
     <row r="30">
       <c r="C30" s="24" t="s">
-        <v>88</v>
+        <v>24</v>
       </c>
       <c r="G30" s="20"/>
     </row>
@@ -4629,7 +4310,7 @@
     </row>
     <row r="32">
       <c r="C32" s="24" t="s">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="D32" s="23"/>
       <c r="E32" s="20"/>
@@ -4652,11 +4333,9 @@
     <col customWidth="true" max="2" min="2" width="10"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2"/>
     <row r="3">
       <c r="E3" s="24" t="s">
-        <v>92</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
@@ -4670,7 +4349,7 @@
     </row>
     <row r="6">
       <c r="C6" s="24" t="s">
-        <v>94</v>
+        <v>34</v>
       </c>
       <c r="G6" s="20"/>
       <c r="H6" s="22"/>
@@ -4687,7 +4366,7 @@
     </row>
     <row r="8">
       <c r="C8" s="24" t="s">
-        <v>96</v>
+        <v>36</v>
       </c>
       <c r="D8" s="23"/>
       <c r="E8" s="20"/>
@@ -4705,7 +4384,7 @@
     </row>
     <row r="11">
       <c r="E11" s="24" t="s">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="I11" s="20"/>
       <c r="K11" s="20"/>
@@ -4726,7 +4405,7 @@
     </row>
     <row r="14">
       <c r="C14" s="24" t="s">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="G14" s="20"/>
       <c r="K14" s="20"/>
@@ -4742,7 +4421,7 @@
     </row>
     <row r="16">
       <c r="C16" s="24" t="s">
-        <v>102</v>
+        <v>42</v>
       </c>
       <c r="D16" s="23"/>
       <c r="E16" s="20"/>
@@ -4758,7 +4437,7 @@
     </row>
     <row r="19">
       <c r="E19" s="24" t="s">
-        <v>104</v>
+        <v>44</v>
       </c>
       <c r="K19" s="20"/>
     </row>
@@ -4775,7 +4454,7 @@
     </row>
     <row r="22">
       <c r="C22" s="24" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="G22" s="20"/>
       <c r="H22" s="22"/>
@@ -4794,7 +4473,7 @@
     </row>
     <row r="24">
       <c r="C24" s="24" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="D24" s="23"/>
       <c r="E24" s="20"/>
@@ -4813,7 +4492,7 @@
     </row>
     <row r="27">
       <c r="E27" s="24" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="I27" s="20"/>
     </row>
@@ -4831,7 +4510,7 @@
     </row>
     <row r="30">
       <c r="C30" s="24" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="G30" s="20"/>
     </row>
@@ -4845,7 +4524,7 @@
     </row>
     <row r="32">
       <c r="C32" s="24" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="D32" s="23"/>
       <c r="E32" s="20"/>
@@ -4868,11 +4547,9 @@
     <col customWidth="true" max="2" min="2" width="10"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2"/>
     <row r="3">
       <c r="E3" s="24" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4">
@@ -4891,7 +4568,7 @@
     </row>
     <row r="7">
       <c r="E7" s="24" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="F7" s="23"/>
       <c r="G7" s="20"/>
@@ -4912,7 +4589,7 @@
     </row>
     <row r="11">
       <c r="E11" s="24" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="I11" s="20"/>
       <c r="K11" s="20"/>
@@ -4933,7 +4610,7 @@
     </row>
     <row r="14">
       <c r="C14" s="24" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="G14" s="20"/>
       <c r="K14" s="20"/>
@@ -4949,7 +4626,7 @@
     </row>
     <row r="16">
       <c r="C16" s="24" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="D16" s="23"/>
       <c r="E16" s="20"/>
@@ -4965,7 +4642,7 @@
     </row>
     <row r="19">
       <c r="E19" s="24" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="K19" s="20"/>
     </row>
@@ -4982,7 +4659,7 @@
     </row>
     <row r="22">
       <c r="C22" s="24" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="G22" s="20"/>
       <c r="H22" s="22"/>
@@ -5001,7 +4678,7 @@
     </row>
     <row r="24">
       <c r="C24" s="24" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="D24" s="23"/>
       <c r="E24" s="20"/>
@@ -5020,7 +4697,7 @@
     </row>
     <row r="27">
       <c r="E27" s="24" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="I27" s="20"/>
     </row>
@@ -5038,7 +4715,7 @@
     </row>
     <row r="30">
       <c r="C30" s="24" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="G30" s="20"/>
     </row>
@@ -5052,7 +4729,7 @@
     </row>
     <row r="32">
       <c r="C32" s="24" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="D32" s="23"/>
       <c r="E32" s="20"/>
@@ -5075,11 +4752,9 @@
     <col customWidth="true" max="2" min="2" width="10"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2"/>
     <row r="3">
       <c r="E3" s="24" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4">
@@ -5093,7 +4768,7 @@
     </row>
     <row r="6">
       <c r="C6" s="24" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="G6" s="20"/>
       <c r="H6" s="22"/>
@@ -5110,7 +4785,7 @@
     </row>
     <row r="8">
       <c r="C8" s="24" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="D8" s="23"/>
       <c r="E8" s="20"/>
@@ -5128,7 +4803,7 @@
     </row>
     <row r="11">
       <c r="E11" s="24" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="I11" s="20"/>
       <c r="K11" s="20"/>
@@ -5149,7 +4824,7 @@
     </row>
     <row r="14">
       <c r="C14" s="24" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="G14" s="20"/>
       <c r="K14" s="20"/>
@@ -5165,7 +4840,7 @@
     </row>
     <row r="16">
       <c r="C16" s="24" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="D16" s="23"/>
       <c r="E16" s="20"/>
@@ -5181,7 +4856,7 @@
     </row>
     <row r="19">
       <c r="E19" s="24" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="K19" s="20"/>
     </row>
@@ -5198,7 +4873,7 @@
     </row>
     <row r="22">
       <c r="C22" s="24" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="G22" s="20"/>
       <c r="H22" s="22"/>
@@ -5217,7 +4892,7 @@
     </row>
     <row r="24">
       <c r="C24" s="24" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="D24" s="23"/>
       <c r="E24" s="20"/>
@@ -5236,7 +4911,7 @@
     </row>
     <row r="27">
       <c r="E27" s="24" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="I27" s="20"/>
     </row>
@@ -5254,7 +4929,7 @@
     </row>
     <row r="30">
       <c r="C30" s="24" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="G30" s="20"/>
     </row>
@@ -5268,7 +4943,7 @@
     </row>
     <row r="32">
       <c r="C32" s="24" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="D32" s="23"/>
       <c r="E32" s="20"/>
@@ -5291,11 +4966,9 @@
     <col customWidth="true" max="2" min="2" width="10"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2"/>
     <row r="3">
       <c r="E3" s="24" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
     </row>
     <row r="4">
@@ -5314,7 +4987,7 @@
     </row>
     <row r="7">
       <c r="E7" s="24" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="F7" s="23"/>
       <c r="G7" s="20"/>
@@ -5335,7 +5008,7 @@
     </row>
     <row r="11">
       <c r="E11" s="24" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="I11" s="20"/>
       <c r="K11" s="20"/>
@@ -5356,7 +5029,7 @@
     </row>
     <row r="14">
       <c r="C14" s="24" t="s">
-        <v>182</v>
+        <v>162</v>
       </c>
       <c r="G14" s="20"/>
       <c r="K14" s="20"/>
@@ -5372,7 +5045,7 @@
     </row>
     <row r="16">
       <c r="C16" s="24" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="D16" s="23"/>
       <c r="E16" s="20"/>
@@ -5388,7 +5061,7 @@
     </row>
     <row r="19">
       <c r="E19" s="24" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="K19" s="20"/>
     </row>
@@ -5405,7 +5078,7 @@
     </row>
     <row r="22">
       <c r="C22" s="24" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="G22" s="20"/>
       <c r="H22" s="22"/>
@@ -5424,7 +5097,7 @@
     </row>
     <row r="24">
       <c r="C24" s="24" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="D24" s="23"/>
       <c r="E24" s="20"/>
@@ -5443,7 +5116,7 @@
     </row>
     <row r="27">
       <c r="E27" s="24" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="I27" s="20"/>
     </row>
@@ -5461,7 +5134,7 @@
     </row>
     <row r="30">
       <c r="C30" s="24" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="G30" s="20"/>
     </row>
@@ -5475,7 +5148,7 @@
     </row>
     <row r="32">
       <c r="C32" s="24" t="s">
-        <v>196</v>
+        <v>132</v>
       </c>
       <c r="D32" s="23"/>
       <c r="E32" s="20"/>
@@ -5498,11 +5171,9 @@
     <col customWidth="true" max="2" min="2" width="10"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2"/>
     <row r="3">
       <c r="E3" s="24" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
     </row>
     <row r="4">
@@ -5516,7 +5187,7 @@
     </row>
     <row r="6">
       <c r="C6" s="24" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="G6" s="20"/>
       <c r="H6" s="22"/>
@@ -5533,7 +5204,7 @@
     </row>
     <row r="8">
       <c r="C8" s="24" t="s">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="D8" s="23"/>
       <c r="E8" s="20"/>
@@ -5551,7 +5222,7 @@
     </row>
     <row r="11">
       <c r="E11" s="24" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="I11" s="20"/>
       <c r="K11" s="20"/>
@@ -5572,7 +5243,7 @@
     </row>
     <row r="14">
       <c r="C14" s="24" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="G14" s="20"/>
       <c r="K14" s="20"/>
@@ -5588,7 +5259,7 @@
     </row>
     <row r="16">
       <c r="C16" s="24" t="s">
-        <v>208</v>
+        <v>194</v>
       </c>
       <c r="D16" s="23"/>
       <c r="E16" s="20"/>
@@ -5604,7 +5275,7 @@
     </row>
     <row r="19">
       <c r="E19" s="24" t="s">
-        <v>210</v>
+        <v>164</v>
       </c>
       <c r="K19" s="20"/>
     </row>
@@ -5621,7 +5292,7 @@
     </row>
     <row r="22">
       <c r="C22" s="24" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="G22" s="20"/>
       <c r="H22" s="22"/>
@@ -5640,7 +5311,7 @@
     </row>
     <row r="24">
       <c r="C24" s="24" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="D24" s="23"/>
       <c r="E24" s="20"/>
@@ -5659,7 +5330,7 @@
     </row>
     <row r="27">
       <c r="E27" s="24" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="I27" s="20"/>
     </row>
@@ -5677,7 +5348,7 @@
     </row>
     <row r="30">
       <c r="C30" s="24" t="s">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="G30" s="20"/>
     </row>
@@ -5691,7 +5362,7 @@
     </row>
     <row r="32">
       <c r="C32" s="24" t="s">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="D32" s="23"/>
       <c r="E32" s="20"/>
@@ -5947,10 +5618,9 @@
       <c r="N1" s="27"/>
       <c r="O1" s="27"/>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="27" t="s">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="B3" s="27"/>
       <c r="C3" s="27"/>
@@ -5959,7 +5629,7 @@
       <c r="F3" s="27"/>
       <c r="G3" s="27"/>
       <c r="I3" s="27" t="s">
-        <v>227</v>
+        <v>212</v>
       </c>
       <c r="J3" s="27"/>
       <c r="K3" s="27"/>
@@ -5970,22 +5640,22 @@
     </row>
     <row r="4">
       <c r="A4" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="D4" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="G4" s="30" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="G4" t="s">
+        <v>209</v>
       </c>
       <c r="I4" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="L4" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="O4" s="31" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="O4" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="5">
@@ -5998,10 +5668,10 @@
       <c r="E5" s="29"/>
       <c r="F5" s="29"/>
       <c r="G5" s="29" t="str">
-        <f>'data'!$B$6</f>
+        <f>'data'!$B$34</f>
       </c>
       <c r="I5" s="29" t="str">
-        <f>'data'!$B$8</f>
+        <f>'data'!$B$36</f>
       </c>
       <c r="J5" s="29"/>
       <c r="K5" s="29"/>
@@ -6009,35 +5679,32 @@
       <c r="M5" s="29"/>
       <c r="N5" s="29"/>
       <c r="O5" s="29" t="str">
-        <f>'data'!$B$9</f>
-      </c>
-    </row>
-    <row r="6"/>
+        <f>'data'!$B$37</f>
+      </c>
+    </row>
     <row r="7">
       <c r="F7" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="G7" s="23"/>
       <c r="N7" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="O7" s="23"/>
     </row>
     <row r="8">
       <c r="F8" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="G8" s="23"/>
       <c r="N8" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="O8" s="23"/>
     </row>
-    <row r="9"/>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="27" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="B11" s="27"/>
       <c r="C11" s="27"/>
@@ -6046,7 +5713,7 @@
       <c r="F11" s="27"/>
       <c r="G11" s="27"/>
       <c r="I11" s="27" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="J11" s="27"/>
       <c r="K11" s="27"/>
@@ -6057,27 +5724,27 @@
     </row>
     <row r="12">
       <c r="A12" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="D12" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="G12" s="32" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="G12" t="s">
+        <v>209</v>
       </c>
       <c r="I12" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="L12" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="O12" s="33" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="O12" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="29" t="str">
-        <f>'data'!$B$11</f>
+        <f>'data'!$B$39</f>
       </c>
       <c r="B13" s="29"/>
       <c r="C13" s="29"/>
@@ -6085,7 +5752,7 @@
       <c r="E13" s="29"/>
       <c r="F13" s="29"/>
       <c r="G13" s="29" t="str">
-        <f>'data'!$B$12</f>
+        <f>'data'!$B$40</f>
       </c>
       <c r="I13" s="29" t="str">
         <f>'data'!$B$16</f>
@@ -6099,32 +5766,29 @@
         <f>'data'!$B$17</f>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="F15" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="G15" s="23"/>
       <c r="N15" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="O15" s="23"/>
     </row>
     <row r="16">
       <c r="F16" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="G16" s="23"/>
       <c r="N16" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="O16" s="23"/>
     </row>
-    <row r="17"/>
-    <row r="18"/>
     <row r="19">
       <c r="A19" s="27" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="B19" s="27"/>
       <c r="C19" s="27"/>
@@ -6133,7 +5797,7 @@
       <c r="F19" s="27"/>
       <c r="G19" s="27"/>
       <c r="I19" s="27" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="J19" s="27"/>
       <c r="K19" s="27"/>
@@ -6144,22 +5808,22 @@
     </row>
     <row r="20">
       <c r="A20" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="D20" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="G20" s="34" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="G20" t="s">
+        <v>209</v>
       </c>
       <c r="I20" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="L20" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="O20" s="35" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="O20" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="21">
@@ -6186,32 +5850,29 @@
         <f>'data'!$B$23</f>
       </c>
     </row>
-    <row r="22"/>
     <row r="23">
       <c r="F23" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="G23" s="23"/>
       <c r="N23" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="O23" s="23"/>
     </row>
     <row r="24">
       <c r="F24" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="G24" s="23"/>
       <c r="N24" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="O24" s="23"/>
     </row>
-    <row r="25"/>
-    <row r="26"/>
     <row r="27">
       <c r="A27" s="27" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="B27" s="27"/>
       <c r="C27" s="27"/>
@@ -6220,7 +5881,7 @@
       <c r="F27" s="27"/>
       <c r="G27" s="27"/>
       <c r="I27" s="27" t="s">
-        <v>233</v>
+        <v>218</v>
       </c>
       <c r="J27" s="27"/>
       <c r="K27" s="27"/>
@@ -6231,22 +5892,22 @@
     </row>
     <row r="28">
       <c r="A28" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="D28" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="G28" s="36" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="G28" t="s">
+        <v>209</v>
       </c>
       <c r="I28" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="L28" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="O28" s="37" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="O28" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="29">
@@ -6273,32 +5934,29 @@
         <f>'data'!$B$31</f>
       </c>
     </row>
-    <row r="30"/>
     <row r="31">
       <c r="F31" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="G31" s="23"/>
       <c r="N31" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="O31" s="23"/>
     </row>
     <row r="32">
       <c r="F32" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="G32" s="23"/>
       <c r="N32" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="O32" s="23"/>
     </row>
-    <row r="33"/>
-    <row r="34"/>
     <row r="35">
       <c r="A35" s="27" t="s">
-        <v>234</v>
+        <v>219</v>
       </c>
       <c r="B35" s="27"/>
       <c r="C35" s="27"/>
@@ -6307,7 +5965,7 @@
       <c r="F35" s="27"/>
       <c r="G35" s="27"/>
       <c r="I35" s="27" t="s">
-        <v>235</v>
+        <v>220</v>
       </c>
       <c r="J35" s="27"/>
       <c r="K35" s="27"/>
@@ -6318,22 +5976,22 @@
     </row>
     <row r="36">
       <c r="A36" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="D36" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="G36" s="38" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="G36" t="s">
+        <v>209</v>
       </c>
       <c r="I36" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="L36" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="O36" s="39" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="O36" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="37">
@@ -6360,32 +6018,29 @@
         <f>'data'!$B$37</f>
       </c>
     </row>
-    <row r="38"/>
     <row r="39">
       <c r="F39" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="G39" s="23"/>
       <c r="N39" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="O39" s="23"/>
     </row>
     <row r="40">
       <c r="F40" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="G40" s="23"/>
       <c r="N40" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="O40" s="23"/>
     </row>
-    <row r="41"/>
-    <row r="42"/>
     <row r="43">
       <c r="A43" s="27" t="s">
-        <v>236</v>
+        <v>221</v>
       </c>
       <c r="B43" s="27"/>
       <c r="C43" s="27"/>
@@ -6394,7 +6049,7 @@
       <c r="F43" s="27"/>
       <c r="G43" s="27"/>
       <c r="I43" s="27" t="s">
-        <v>237</v>
+        <v>222</v>
       </c>
       <c r="J43" s="27"/>
       <c r="K43" s="27"/>
@@ -6405,22 +6060,22 @@
     </row>
     <row r="44">
       <c r="A44" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="D44" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="G44" s="40" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="G44" t="s">
+        <v>209</v>
       </c>
       <c r="I44" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="L44" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="O44" s="41" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="O44" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="45">
@@ -6447,32 +6102,29 @@
         <f>'data'!$B$43</f>
       </c>
     </row>
-    <row r="46"/>
     <row r="47">
       <c r="F47" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="G47" s="23"/>
       <c r="N47" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="O47" s="23"/>
     </row>
     <row r="48">
       <c r="F48" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="G48" s="23"/>
       <c r="N48" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="O48" s="23"/>
     </row>
-    <row r="49"/>
-    <row r="50"/>
     <row r="51">
       <c r="A51" s="27" t="s">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="B51" s="27"/>
       <c r="C51" s="27"/>
@@ -6481,7 +6133,7 @@
       <c r="F51" s="27"/>
       <c r="G51" s="27"/>
       <c r="I51" s="27" t="s">
-        <v>239</v>
+        <v>224</v>
       </c>
       <c r="J51" s="27"/>
       <c r="K51" s="27"/>
@@ -6492,22 +6144,22 @@
     </row>
     <row r="52">
       <c r="A52" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="D52" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="G52" s="42" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="G52" t="s">
+        <v>209</v>
       </c>
       <c r="I52" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="L52" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="O52" s="43" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="O52" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="53">
@@ -6534,32 +6186,29 @@
         <f>'data'!$B$51</f>
       </c>
     </row>
-    <row r="54"/>
     <row r="55">
       <c r="F55" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="G55" s="23"/>
       <c r="N55" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="O55" s="23"/>
     </row>
     <row r="56">
       <c r="F56" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="G56" s="23"/>
       <c r="N56" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="O56" s="23"/>
     </row>
-    <row r="57"/>
-    <row r="58"/>
     <row r="59">
       <c r="A59" s="27" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="B59" s="27"/>
       <c r="C59" s="27"/>
@@ -6568,7 +6217,7 @@
       <c r="F59" s="27"/>
       <c r="G59" s="27"/>
       <c r="I59" s="27" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="J59" s="27"/>
       <c r="K59" s="27"/>
@@ -6579,22 +6228,22 @@
     </row>
     <row r="60">
       <c r="A60" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="D60" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="G60" s="44" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="G60" t="s">
+        <v>209</v>
       </c>
       <c r="I60" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="L60" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="O60" s="45" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="O60" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="61">
@@ -6621,32 +6270,29 @@
         <f>'data'!$B$57</f>
       </c>
     </row>
-    <row r="62"/>
     <row r="63">
       <c r="F63" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="G63" s="23"/>
       <c r="N63" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="O63" s="23"/>
     </row>
     <row r="64">
       <c r="F64" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="G64" s="23"/>
       <c r="N64" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="O64" s="23"/>
     </row>
-    <row r="65"/>
-    <row r="66"/>
     <row r="67">
       <c r="A67" s="27" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="B67" s="27"/>
       <c r="C67" s="27"/>
@@ -6655,7 +6301,7 @@
       <c r="F67" s="27"/>
       <c r="G67" s="27"/>
       <c r="I67" s="27" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="J67" s="27"/>
       <c r="K67" s="27"/>
@@ -6666,22 +6312,22 @@
     </row>
     <row r="68">
       <c r="A68" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="D68" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="G68" s="46" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="G68" t="s">
+        <v>209</v>
       </c>
       <c r="I68" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="L68" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="O68" s="47" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="O68" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="69">
@@ -6708,32 +6354,29 @@
         <f>'data'!$B$63</f>
       </c>
     </row>
-    <row r="70"/>
     <row r="71">
       <c r="F71" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="G71" s="23"/>
       <c r="N71" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="O71" s="23"/>
     </row>
     <row r="72">
       <c r="F72" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="G72" s="23"/>
       <c r="N72" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="O72" s="23"/>
     </row>
-    <row r="73"/>
-    <row r="74"/>
     <row r="75">
       <c r="A75" s="27" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="B75" s="27"/>
       <c r="C75" s="27"/>
@@ -6742,7 +6385,7 @@
       <c r="F75" s="27"/>
       <c r="G75" s="27"/>
       <c r="I75" s="27" t="s">
-        <v>245</v>
+        <v>230</v>
       </c>
       <c r="J75" s="27"/>
       <c r="K75" s="27"/>
@@ -6753,22 +6396,22 @@
     </row>
     <row r="76">
       <c r="A76" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="D76" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="G76" s="48" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="G76" t="s">
+        <v>209</v>
       </c>
       <c r="I76" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="L76" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="O76" s="49" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="O76" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="77">
@@ -6792,35 +6435,32 @@
       <c r="M77" s="29"/>
       <c r="N77" s="29"/>
       <c r="O77" s="29" t="str">
-        <f>'data'!$B$69</f>
-      </c>
-    </row>
-    <row r="78"/>
+        <f>'data'!$B$73</f>
+      </c>
+    </row>
     <row r="79">
       <c r="F79" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="G79" s="23"/>
       <c r="N79" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="O79" s="23"/>
     </row>
     <row r="80">
       <c r="F80" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="G80" s="23"/>
       <c r="N80" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="O80" s="23"/>
     </row>
-    <row r="81"/>
-    <row r="82"/>
     <row r="83">
       <c r="A83" s="27" t="s">
-        <v>246</v>
+        <v>231</v>
       </c>
       <c r="B83" s="27"/>
       <c r="C83" s="27"/>
@@ -6829,7 +6469,7 @@
       <c r="F83" s="27"/>
       <c r="G83" s="27"/>
       <c r="I83" s="27" t="s">
-        <v>247</v>
+        <v>232</v>
       </c>
       <c r="J83" s="27"/>
       <c r="K83" s="27"/>
@@ -6840,22 +6480,22 @@
     </row>
     <row r="84">
       <c r="A84" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="D84" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="G84" s="50" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="G84" t="s">
+        <v>209</v>
       </c>
       <c r="I84" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="L84" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="O84" s="51" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="O84" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="85">
@@ -6882,32 +6522,29 @@
         <f>'data'!$B$77</f>
       </c>
     </row>
-    <row r="86"/>
     <row r="87">
       <c r="F87" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="G87" s="23"/>
       <c r="N87" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="O87" s="23"/>
     </row>
     <row r="88">
       <c r="F88" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="G88" s="23"/>
       <c r="N88" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="O88" s="23"/>
     </row>
-    <row r="89"/>
-    <row r="90"/>
     <row r="91">
       <c r="A91" s="27" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="B91" s="27"/>
       <c r="C91" s="27"/>
@@ -6916,7 +6553,7 @@
       <c r="F91" s="27"/>
       <c r="G91" s="27"/>
       <c r="I91" s="27" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
       <c r="J91" s="27"/>
       <c r="K91" s="27"/>
@@ -6927,22 +6564,22 @@
     </row>
     <row r="92">
       <c r="A92" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="D92" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="G92" s="52" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="G92" t="s">
+        <v>209</v>
       </c>
       <c r="I92" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="L92" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="O92" s="53" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="O92" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="93">
@@ -6969,32 +6606,29 @@
         <f>'data'!$B$83</f>
       </c>
     </row>
-    <row r="94"/>
     <row r="95">
       <c r="F95" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="G95" s="23"/>
       <c r="N95" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="O95" s="23"/>
     </row>
     <row r="96">
       <c r="F96" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="G96" s="23"/>
       <c r="N96" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="O96" s="23"/>
     </row>
-    <row r="97"/>
-    <row r="98"/>
     <row r="99">
       <c r="A99" s="27" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="B99" s="27"/>
       <c r="C99" s="27"/>
@@ -7003,7 +6637,7 @@
       <c r="F99" s="27"/>
       <c r="G99" s="27"/>
       <c r="I99" s="27" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="J99" s="27"/>
       <c r="K99" s="27"/>
@@ -7014,22 +6648,22 @@
     </row>
     <row r="100">
       <c r="A100" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="D100" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="G100" s="54" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="G100" t="s">
+        <v>209</v>
       </c>
       <c r="I100" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="L100" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="O100" s="55" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="O100" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="101">
@@ -7056,32 +6690,29 @@
         <f>'data'!$B$89</f>
       </c>
     </row>
-    <row r="102"/>
     <row r="103">
       <c r="F103" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="G103" s="23"/>
       <c r="N103" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="O103" s="23"/>
     </row>
     <row r="104">
       <c r="F104" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="G104" s="23"/>
       <c r="N104" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="O104" s="23"/>
     </row>
-    <row r="105"/>
-    <row r="106"/>
     <row r="107">
       <c r="A107" s="27" t="s">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="B107" s="27"/>
       <c r="C107" s="27"/>
@@ -7092,13 +6723,13 @@
     </row>
     <row r="108">
       <c r="A108" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="D108" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="G108" s="56" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="G108" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="109">
@@ -7114,29 +6745,21 @@
         <f>'data'!$B$92</f>
       </c>
     </row>
-    <row r="110"/>
     <row r="111">
       <c r="F111" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="G111" s="23"/>
     </row>
     <row r="112">
       <c r="F112" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="G112" s="23"/>
     </row>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
     <row r="120">
       <c r="A120" s="27" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
       <c r="B120" s="27"/>
       <c r="C120" s="27"/>
@@ -7153,10 +6776,9 @@
       <c r="N120" s="27"/>
       <c r="O120" s="27"/>
     </row>
-    <row r="121"/>
     <row r="122">
       <c r="A122" s="27" t="s">
-        <v>254</v>
+        <v>239</v>
       </c>
       <c r="B122" s="27"/>
       <c r="C122" s="27"/>
@@ -7165,7 +6787,7 @@
       <c r="F122" s="27"/>
       <c r="G122" s="27"/>
       <c r="I122" s="27" t="s">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="J122" s="27"/>
       <c r="K122" s="27"/>
@@ -7176,27 +6798,27 @@
     </row>
     <row r="123">
       <c r="A123" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="D123" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="G123" s="57" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="G123" t="s">
+        <v>209</v>
       </c>
       <c r="I123" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="L123" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="O123" s="58" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="O123" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="29" t="str">
-        <f>'data'!$B$2</f>
+        <f>'data'!$B$31</f>
       </c>
       <c r="B124" s="29"/>
       <c r="C124" s="29"/>
@@ -7204,10 +6826,10 @@
       <c r="E124" s="29"/>
       <c r="F124" s="29"/>
       <c r="G124" s="29" t="str">
-        <f>'data'!$B$3</f>
+        <f>'data'!$B$32</f>
       </c>
       <c r="I124" s="29" t="str">
-        <f>'data'!$B$4</f>
+        <f>'data'!$B$33</f>
       </c>
       <c r="J124" s="29"/>
       <c r="K124" s="29"/>
@@ -7218,32 +6840,29 @@
         <f>CONCATENATE("M 1 ",'Elimination Matches'!G7)</f>
       </c>
     </row>
-    <row r="125"/>
     <row r="126">
       <c r="F126" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="G126" s="23"/>
       <c r="N126" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="O126" s="23"/>
     </row>
     <row r="127">
       <c r="F127" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="G127" s="23"/>
       <c r="N127" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="O127" s="23"/>
     </row>
-    <row r="128"/>
-    <row r="129"/>
     <row r="130">
       <c r="A130" s="27" t="s">
-        <v>256</v>
+        <v>241</v>
       </c>
       <c r="B130" s="27"/>
       <c r="C130" s="27"/>
@@ -7252,7 +6871,7 @@
       <c r="F130" s="27"/>
       <c r="G130" s="27"/>
       <c r="I130" s="27" t="s">
-        <v>257</v>
+        <v>242</v>
       </c>
       <c r="J130" s="27"/>
       <c r="K130" s="27"/>
@@ -7263,27 +6882,27 @@
     </row>
     <row r="131">
       <c r="A131" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="D131" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="G131" s="59" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="G131" t="s">
+        <v>209</v>
       </c>
       <c r="I131" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="L131" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="O131" s="60" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="O131" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="29" t="str">
-        <f>'data'!$B$7</f>
+        <f>'data'!$B$35</f>
       </c>
       <c r="B132" s="29"/>
       <c r="C132" s="29"/>
@@ -7294,7 +6913,7 @@
         <f>CONCATENATE("M 2 ",'Elimination Matches'!O7)</f>
       </c>
       <c r="I132" s="29" t="str">
-        <f>'data'!$B$10</f>
+        <f>'data'!$B$38</f>
       </c>
       <c r="J132" s="29"/>
       <c r="K132" s="29"/>
@@ -7305,32 +6924,29 @@
         <f>CONCATENATE("M 3 ",'Elimination Matches'!G15)</f>
       </c>
     </row>
-    <row r="133"/>
     <row r="134">
       <c r="F134" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="G134" s="23"/>
       <c r="N134" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="O134" s="23"/>
     </row>
     <row r="135">
       <c r="F135" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="G135" s="23"/>
       <c r="N135" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="O135" s="23"/>
     </row>
-    <row r="136"/>
-    <row r="137"/>
     <row r="138">
       <c r="A138" s="27" t="s">
-        <v>258</v>
+        <v>243</v>
       </c>
       <c r="B138" s="27"/>
       <c r="C138" s="27"/>
@@ -7339,7 +6955,7 @@
       <c r="F138" s="27"/>
       <c r="G138" s="27"/>
       <c r="I138" s="27" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
       <c r="J138" s="27"/>
       <c r="K138" s="27"/>
@@ -7350,27 +6966,27 @@
     </row>
     <row r="139">
       <c r="A139" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="D139" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="G139" s="61" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="G139" t="s">
+        <v>209</v>
       </c>
       <c r="I139" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="L139" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="O139" s="62" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="O139" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="29" t="str">
-        <f>'data'!$B$13</f>
+        <f>'data'!$B$41</f>
       </c>
       <c r="B140" s="29"/>
       <c r="C140" s="29"/>
@@ -7378,7 +6994,7 @@
       <c r="E140" s="29"/>
       <c r="F140" s="29"/>
       <c r="G140" s="29" t="str">
-        <f>'data'!$B$14</f>
+        <f>'data'!$B$42</f>
       </c>
       <c r="I140" s="29" t="str">
         <f>'data'!$B$15</f>
@@ -7392,32 +7008,29 @@
         <f>CONCATENATE("M 4 ",'Elimination Matches'!O15)</f>
       </c>
     </row>
-    <row r="141"/>
     <row r="142">
       <c r="F142" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="G142" s="23"/>
       <c r="N142" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="O142" s="23"/>
     </row>
     <row r="143">
       <c r="F143" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="G143" s="23"/>
       <c r="N143" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="O143" s="23"/>
     </row>
-    <row r="144"/>
-    <row r="145"/>
     <row r="146">
       <c r="A146" s="27" t="s">
-        <v>260</v>
+        <v>245</v>
       </c>
       <c r="B146" s="27"/>
       <c r="C146" s="27"/>
@@ -7426,7 +7039,7 @@
       <c r="F146" s="27"/>
       <c r="G146" s="27"/>
       <c r="I146" s="27" t="s">
-        <v>261</v>
+        <v>246</v>
       </c>
       <c r="J146" s="27"/>
       <c r="K146" s="27"/>
@@ -7437,27 +7050,27 @@
     </row>
     <row r="147">
       <c r="A147" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="D147" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="G147" s="63" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="G147" t="s">
+        <v>209</v>
       </c>
       <c r="I147" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="L147" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="O147" s="64" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="O147" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="29" t="str">
-        <f>'data'!$B$18</f>
+        <f>'data'!$B$29</f>
       </c>
       <c r="B148" s="29"/>
       <c r="C148" s="29"/>
@@ -7479,32 +7092,29 @@
         <f>CONCATENATE("M 6 ",'Elimination Matches'!O23)</f>
       </c>
     </row>
-    <row r="149"/>
     <row r="150">
       <c r="F150" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="G150" s="23"/>
       <c r="N150" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="O150" s="23"/>
     </row>
     <row r="151">
       <c r="F151" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="G151" s="23"/>
       <c r="N151" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="O151" s="23"/>
     </row>
-    <row r="152"/>
-    <row r="153"/>
     <row r="154">
       <c r="A154" s="27" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="B154" s="27"/>
       <c r="C154" s="27"/>
@@ -7513,7 +7123,7 @@
       <c r="F154" s="27"/>
       <c r="G154" s="27"/>
       <c r="I154" s="27" t="s">
-        <v>263</v>
+        <v>248</v>
       </c>
       <c r="J154" s="27"/>
       <c r="K154" s="27"/>
@@ -7524,22 +7134,22 @@
     </row>
     <row r="155">
       <c r="A155" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="D155" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="G155" s="65" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="G155" t="s">
+        <v>209</v>
       </c>
       <c r="I155" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="L155" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="O155" s="66" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="O155" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="156">
@@ -7566,32 +7176,29 @@
         <f>CONCATENATE("M 7 ",'Elimination Matches'!G31)</f>
       </c>
     </row>
-    <row r="157"/>
     <row r="158">
       <c r="F158" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="G158" s="23"/>
       <c r="N158" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="O158" s="23"/>
     </row>
     <row r="159">
       <c r="F159" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="G159" s="23"/>
       <c r="N159" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="O159" s="23"/>
     </row>
-    <row r="160"/>
-    <row r="161"/>
     <row r="162">
       <c r="A162" s="27" t="s">
-        <v>264</v>
+        <v>249</v>
       </c>
       <c r="B162" s="27"/>
       <c r="C162" s="27"/>
@@ -7600,7 +7207,7 @@
       <c r="F162" s="27"/>
       <c r="G162" s="27"/>
       <c r="I162" s="27" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
       <c r="J162" s="27"/>
       <c r="K162" s="27"/>
@@ -7611,22 +7218,22 @@
     </row>
     <row r="163">
       <c r="A163" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="D163" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="G163" s="67" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="G163" t="s">
+        <v>209</v>
       </c>
       <c r="I163" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="L163" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="O163" s="68" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="O163" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="164">
@@ -7653,32 +7260,29 @@
         <f>CONCATENATE("M 9 ",'Elimination Matches'!G39)</f>
       </c>
     </row>
-    <row r="165"/>
     <row r="166">
       <c r="F166" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="G166" s="23"/>
       <c r="N166" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="O166" s="23"/>
     </row>
     <row r="167">
       <c r="F167" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="G167" s="23"/>
       <c r="N167" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="O167" s="23"/>
     </row>
-    <row r="168"/>
-    <row r="169"/>
     <row r="170">
       <c r="A170" s="27" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
       <c r="B170" s="27"/>
       <c r="C170" s="27"/>
@@ -7687,7 +7291,7 @@
       <c r="F170" s="27"/>
       <c r="G170" s="27"/>
       <c r="I170" s="27" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
       <c r="J170" s="27"/>
       <c r="K170" s="27"/>
@@ -7698,22 +7302,22 @@
     </row>
     <row r="171">
       <c r="A171" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="D171" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="G171" s="69" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="G171" t="s">
+        <v>209</v>
       </c>
       <c r="I171" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="L171" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="O171" s="70" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="O171" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="172">
@@ -7740,32 +7344,29 @@
         <f>CONCATENATE("M 11 ",'Elimination Matches'!G47)</f>
       </c>
     </row>
-    <row r="173"/>
     <row r="174">
       <c r="F174" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="G174" s="23"/>
       <c r="N174" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="O174" s="23"/>
     </row>
     <row r="175">
       <c r="F175" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="G175" s="23"/>
       <c r="N175" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="O175" s="23"/>
     </row>
-    <row r="176"/>
-    <row r="177"/>
     <row r="178">
       <c r="A178" s="27" t="s">
-        <v>268</v>
+        <v>253</v>
       </c>
       <c r="B178" s="27"/>
       <c r="C178" s="27"/>
@@ -7774,7 +7375,7 @@
       <c r="F178" s="27"/>
       <c r="G178" s="27"/>
       <c r="I178" s="27" t="s">
-        <v>269</v>
+        <v>254</v>
       </c>
       <c r="J178" s="27"/>
       <c r="K178" s="27"/>
@@ -7785,22 +7386,22 @@
     </row>
     <row r="179">
       <c r="A179" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="D179" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="G179" s="71" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="G179" t="s">
+        <v>209</v>
       </c>
       <c r="I179" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="L179" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="O179" s="72" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="O179" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="180">
@@ -7827,32 +7428,29 @@
         <f>CONCATENATE("M 13 ",'Elimination Matches'!G55)</f>
       </c>
     </row>
-    <row r="181"/>
     <row r="182">
       <c r="F182" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="G182" s="23"/>
       <c r="N182" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="O182" s="23"/>
     </row>
     <row r="183">
       <c r="F183" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="G183" s="23"/>
       <c r="N183" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="O183" s="23"/>
     </row>
-    <row r="184"/>
-    <row r="185"/>
     <row r="186">
       <c r="A186" s="27" t="s">
-        <v>270</v>
+        <v>255</v>
       </c>
       <c r="B186" s="27"/>
       <c r="C186" s="27"/>
@@ -7861,7 +7459,7 @@
       <c r="F186" s="27"/>
       <c r="G186" s="27"/>
       <c r="I186" s="27" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
       <c r="J186" s="27"/>
       <c r="K186" s="27"/>
@@ -7872,22 +7470,22 @@
     </row>
     <row r="187">
       <c r="A187" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="D187" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="G187" s="73" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="G187" t="s">
+        <v>209</v>
       </c>
       <c r="I187" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="L187" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="O187" s="74" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="O187" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="188">
@@ -7914,32 +7512,29 @@
         <f>CONCATENATE("M 14 ",'Elimination Matches'!O55)</f>
       </c>
     </row>
-    <row r="189"/>
     <row r="190">
       <c r="F190" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="G190" s="23"/>
       <c r="N190" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="O190" s="23"/>
     </row>
     <row r="191">
       <c r="F191" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="G191" s="23"/>
       <c r="N191" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="O191" s="23"/>
     </row>
-    <row r="192"/>
-    <row r="193"/>
     <row r="194">
       <c r="A194" s="27" t="s">
-        <v>272</v>
+        <v>257</v>
       </c>
       <c r="B194" s="27"/>
       <c r="C194" s="27"/>
@@ -7948,7 +7543,7 @@
       <c r="F194" s="27"/>
       <c r="G194" s="27"/>
       <c r="I194" s="27" t="s">
-        <v>273</v>
+        <v>258</v>
       </c>
       <c r="J194" s="27"/>
       <c r="K194" s="27"/>
@@ -7959,22 +7554,22 @@
     </row>
     <row r="195">
       <c r="A195" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="D195" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="G195" s="75" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="G195" t="s">
+        <v>209</v>
       </c>
       <c r="I195" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="L195" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="O195" s="76" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="O195" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="196">
@@ -8001,32 +7596,29 @@
         <f>CONCATENATE("M 16 ",'Elimination Matches'!O63)</f>
       </c>
     </row>
-    <row r="197"/>
     <row r="198">
       <c r="F198" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="G198" s="23"/>
       <c r="N198" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="O198" s="23"/>
     </row>
     <row r="199">
       <c r="F199" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="G199" s="23"/>
       <c r="N199" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="O199" s="23"/>
     </row>
-    <row r="200"/>
-    <row r="201"/>
     <row r="202">
       <c r="A202" s="27" t="s">
-        <v>274</v>
+        <v>259</v>
       </c>
       <c r="B202" s="27"/>
       <c r="C202" s="27"/>
@@ -8035,7 +7627,7 @@
       <c r="F202" s="27"/>
       <c r="G202" s="27"/>
       <c r="I202" s="27" t="s">
-        <v>275</v>
+        <v>260</v>
       </c>
       <c r="J202" s="27"/>
       <c r="K202" s="27"/>
@@ -8046,27 +7638,27 @@
     </row>
     <row r="203">
       <c r="A203" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="D203" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="G203" s="77" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="G203" t="s">
+        <v>209</v>
       </c>
       <c r="I203" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="L203" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="O203" s="78" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="O203" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="29" t="str">
-        <f>'data'!$B$58</f>
+        <f>'data'!$B$80</f>
       </c>
       <c r="B204" s="29"/>
       <c r="C204" s="29"/>
@@ -8088,32 +7680,29 @@
         <f>CONCATENATE("M 18 ",'Elimination Matches'!O71)</f>
       </c>
     </row>
-    <row r="205"/>
     <row r="206">
       <c r="F206" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="G206" s="23"/>
       <c r="N206" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="O206" s="23"/>
     </row>
     <row r="207">
       <c r="F207" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="G207" s="23"/>
       <c r="N207" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="O207" s="23"/>
     </row>
-    <row r="208"/>
-    <row r="209"/>
     <row r="210">
       <c r="A210" s="27" t="s">
-        <v>276</v>
+        <v>261</v>
       </c>
       <c r="B210" s="27"/>
       <c r="C210" s="27"/>
@@ -8122,7 +7711,7 @@
       <c r="F210" s="27"/>
       <c r="G210" s="27"/>
       <c r="I210" s="27" t="s">
-        <v>277</v>
+        <v>262</v>
       </c>
       <c r="J210" s="27"/>
       <c r="K210" s="27"/>
@@ -8133,22 +7722,22 @@
     </row>
     <row r="211">
       <c r="A211" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="D211" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="G211" s="79" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="G211" t="s">
+        <v>209</v>
       </c>
       <c r="I211" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="L211" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="O211" s="80" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="O211" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="212">
@@ -8175,32 +7764,29 @@
         <f>CONCATENATE("M 20 ",'Elimination Matches'!O79)</f>
       </c>
     </row>
-    <row r="213"/>
     <row r="214">
       <c r="F214" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="G214" s="23"/>
       <c r="N214" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="O214" s="23"/>
     </row>
     <row r="215">
       <c r="F215" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="G215" s="23"/>
       <c r="N215" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="O215" s="23"/>
     </row>
-    <row r="216"/>
-    <row r="217"/>
     <row r="218">
       <c r="A218" s="27" t="s">
-        <v>278</v>
+        <v>263</v>
       </c>
       <c r="B218" s="27"/>
       <c r="C218" s="27"/>
@@ -8209,7 +7795,7 @@
       <c r="F218" s="27"/>
       <c r="G218" s="27"/>
       <c r="I218" s="27" t="s">
-        <v>279</v>
+        <v>264</v>
       </c>
       <c r="J218" s="27"/>
       <c r="K218" s="27"/>
@@ -8220,27 +7806,27 @@
     </row>
     <row r="219">
       <c r="A219" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="D219" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="G219" s="81" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="G219" t="s">
+        <v>209</v>
       </c>
       <c r="I219" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="L219" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="O219" s="82" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="O219" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="29" t="str">
-        <f>'data'!$B$70</f>
+        <f>'data'!$B$87</f>
       </c>
       <c r="B220" s="29"/>
       <c r="C220" s="29"/>
@@ -8262,32 +7848,29 @@
         <f>CONCATENATE("M 21 ",'Elimination Matches'!G87)</f>
       </c>
     </row>
-    <row r="221"/>
     <row r="222">
       <c r="F222" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="G222" s="23"/>
       <c r="N222" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="O222" s="23"/>
     </row>
     <row r="223">
       <c r="F223" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="G223" s="23"/>
       <c r="N223" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="O223" s="23"/>
     </row>
-    <row r="224"/>
-    <row r="225"/>
     <row r="226">
       <c r="A226" s="27" t="s">
-        <v>280</v>
+        <v>265</v>
       </c>
       <c r="B226" s="27"/>
       <c r="C226" s="27"/>
@@ -8296,7 +7879,7 @@
       <c r="F226" s="27"/>
       <c r="G226" s="27"/>
       <c r="I226" s="27" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
       <c r="J226" s="27"/>
       <c r="K226" s="27"/>
@@ -8307,22 +7890,22 @@
     </row>
     <row r="227">
       <c r="A227" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="D227" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="G227" s="83" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="G227" t="s">
+        <v>209</v>
       </c>
       <c r="I227" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="L227" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="O227" s="84" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="O227" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="228">
@@ -8349,32 +7932,29 @@
         <f>CONCATENATE("M 23 ",'Elimination Matches'!G95)</f>
       </c>
     </row>
-    <row r="229"/>
     <row r="230">
       <c r="F230" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="G230" s="23"/>
       <c r="N230" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="O230" s="23"/>
     </row>
     <row r="231">
       <c r="F231" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="G231" s="23"/>
       <c r="N231" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="O231" s="23"/>
     </row>
-    <row r="232"/>
-    <row r="233"/>
     <row r="234">
       <c r="A234" s="27" t="s">
-        <v>282</v>
+        <v>267</v>
       </c>
       <c r="B234" s="27"/>
       <c r="C234" s="27"/>
@@ -8383,7 +7963,7 @@
       <c r="F234" s="27"/>
       <c r="G234" s="27"/>
       <c r="I234" s="27" t="s">
-        <v>283</v>
+        <v>268</v>
       </c>
       <c r="J234" s="27"/>
       <c r="K234" s="27"/>
@@ -8394,22 +7974,22 @@
     </row>
     <row r="235">
       <c r="A235" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="D235" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="G235" s="85" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="G235" t="s">
+        <v>209</v>
       </c>
       <c r="I235" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="L235" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="O235" s="86" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="O235" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="236">
@@ -8436,32 +8016,29 @@
         <f>CONCATENATE("M 25 ",'Elimination Matches'!G103)</f>
       </c>
     </row>
-    <row r="237"/>
     <row r="238">
       <c r="F238" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="G238" s="23"/>
       <c r="N238" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="O238" s="23"/>
     </row>
     <row r="239">
       <c r="F239" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="G239" s="23"/>
       <c r="N239" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="O239" s="23"/>
     </row>
-    <row r="240"/>
-    <row r="241"/>
     <row r="242">
       <c r="A242" s="27" t="s">
-        <v>284</v>
+        <v>269</v>
       </c>
       <c r="B242" s="27"/>
       <c r="C242" s="27"/>
@@ -8470,7 +8047,7 @@
       <c r="F242" s="27"/>
       <c r="G242" s="27"/>
       <c r="I242" s="27" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="J242" s="27"/>
       <c r="K242" s="27"/>
@@ -8481,22 +8058,22 @@
     </row>
     <row r="243">
       <c r="A243" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="D243" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="G243" s="87" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="G243" t="s">
+        <v>209</v>
       </c>
       <c r="I243" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="L243" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="O243" s="88" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="O243" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="244">
@@ -8523,37 +8100,29 @@
         <f>CONCATENATE("M 27 ",'Elimination Matches'!G111)</f>
       </c>
     </row>
-    <row r="245"/>
     <row r="246">
       <c r="F246" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="G246" s="23"/>
       <c r="N246" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="O246" s="23"/>
     </row>
     <row r="247">
       <c r="F247" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="G247" s="23"/>
       <c r="N247" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="O247" s="23"/>
     </row>
-    <row r="248"/>
-    <row r="249"/>
-    <row r="250"/>
-    <row r="251"/>
-    <row r="252"/>
-    <row r="253"/>
-    <row r="254"/>
     <row r="255">
       <c r="A255" s="27" t="s">
-        <v>286</v>
+        <v>271</v>
       </c>
       <c r="B255" s="27"/>
       <c r="C255" s="27"/>
@@ -8570,10 +8139,9 @@
       <c r="N255" s="27"/>
       <c r="O255" s="27"/>
     </row>
-    <row r="256"/>
     <row r="257">
       <c r="A257" s="27" t="s">
-        <v>287</v>
+        <v>272</v>
       </c>
       <c r="B257" s="27"/>
       <c r="C257" s="27"/>
@@ -8582,7 +8150,7 @@
       <c r="F257" s="27"/>
       <c r="G257" s="27"/>
       <c r="I257" s="27" t="s">
-        <v>288</v>
+        <v>273</v>
       </c>
       <c r="J257" s="27"/>
       <c r="K257" s="27"/>
@@ -8593,22 +8161,22 @@
     </row>
     <row r="258">
       <c r="A258" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="D258" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="G258" s="89" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="G258" t="s">
+        <v>209</v>
       </c>
       <c r="I258" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="L258" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="O258" s="90" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="O258" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="259">
@@ -8635,32 +8203,29 @@
         <f>CONCATENATE("M 31 ",'Elimination Matches'!O134)</f>
       </c>
     </row>
-    <row r="260"/>
     <row r="261">
       <c r="F261" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="G261" s="23"/>
       <c r="N261" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="O261" s="23"/>
     </row>
     <row r="262">
       <c r="F262" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="G262" s="23"/>
       <c r="N262" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="O262" s="23"/>
     </row>
-    <row r="263"/>
-    <row r="264"/>
     <row r="265">
       <c r="A265" s="27" t="s">
-        <v>289</v>
+        <v>274</v>
       </c>
       <c r="B265" s="27"/>
       <c r="C265" s="27"/>
@@ -8669,7 +8234,7 @@
       <c r="F265" s="27"/>
       <c r="G265" s="27"/>
       <c r="I265" s="27" t="s">
-        <v>290</v>
+        <v>275</v>
       </c>
       <c r="J265" s="27"/>
       <c r="K265" s="27"/>
@@ -8680,22 +8245,22 @@
     </row>
     <row r="266">
       <c r="A266" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="D266" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="G266" s="91" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="G266" t="s">
+        <v>209</v>
       </c>
       <c r="I266" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="L266" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="O266" s="92" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="O266" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="267">
@@ -8722,32 +8287,29 @@
         <f>CONCATENATE("M 35 ",'Elimination Matches'!O150)</f>
       </c>
     </row>
-    <row r="268"/>
     <row r="269">
       <c r="F269" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="G269" s="23"/>
       <c r="N269" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="O269" s="23"/>
     </row>
     <row r="270">
       <c r="F270" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="G270" s="23"/>
       <c r="N270" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="O270" s="23"/>
     </row>
-    <row r="271"/>
-    <row r="272"/>
     <row r="273">
       <c r="A273" s="27" t="s">
-        <v>291</v>
+        <v>276</v>
       </c>
       <c r="B273" s="27"/>
       <c r="C273" s="27"/>
@@ -8756,7 +8318,7 @@
       <c r="F273" s="27"/>
       <c r="G273" s="27"/>
       <c r="I273" s="27" t="s">
-        <v>292</v>
+        <v>277</v>
       </c>
       <c r="J273" s="27"/>
       <c r="K273" s="27"/>
@@ -8767,22 +8329,22 @@
     </row>
     <row r="274">
       <c r="A274" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="D274" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="G274" s="93" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="G274" t="s">
+        <v>209</v>
       </c>
       <c r="I274" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="L274" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="O274" s="94" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="O274" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="275">
@@ -8809,32 +8371,29 @@
         <f>CONCATENATE("M 39 ",'Elimination Matches'!O166)</f>
       </c>
     </row>
-    <row r="276"/>
     <row r="277">
       <c r="F277" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="G277" s="23"/>
       <c r="N277" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="O277" s="23"/>
     </row>
     <row r="278">
       <c r="F278" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="G278" s="23"/>
       <c r="N278" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="O278" s="23"/>
     </row>
-    <row r="279"/>
-    <row r="280"/>
     <row r="281">
       <c r="A281" s="27" t="s">
-        <v>293</v>
+        <v>278</v>
       </c>
       <c r="B281" s="27"/>
       <c r="C281" s="27"/>
@@ -8843,7 +8402,7 @@
       <c r="F281" s="27"/>
       <c r="G281" s="27"/>
       <c r="I281" s="27" t="s">
-        <v>294</v>
+        <v>279</v>
       </c>
       <c r="J281" s="27"/>
       <c r="K281" s="27"/>
@@ -8854,22 +8413,22 @@
     </row>
     <row r="282">
       <c r="A282" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="D282" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="G282" s="95" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="G282" t="s">
+        <v>209</v>
       </c>
       <c r="I282" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="L282" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="O282" s="96" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="O282" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="283">
@@ -8896,32 +8455,29 @@
         <f>CONCATENATE("M 43 ",'Elimination Matches'!O182)</f>
       </c>
     </row>
-    <row r="284"/>
     <row r="285">
       <c r="F285" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="G285" s="23"/>
       <c r="N285" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="O285" s="23"/>
     </row>
     <row r="286">
       <c r="F286" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="G286" s="23"/>
       <c r="N286" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="O286" s="23"/>
     </row>
-    <row r="287"/>
-    <row r="288"/>
     <row r="289">
       <c r="A289" s="27" t="s">
-        <v>295</v>
+        <v>280</v>
       </c>
       <c r="B289" s="27"/>
       <c r="C289" s="27"/>
@@ -8930,7 +8486,7 @@
       <c r="F289" s="27"/>
       <c r="G289" s="27"/>
       <c r="I289" s="27" t="s">
-        <v>296</v>
+        <v>281</v>
       </c>
       <c r="J289" s="27"/>
       <c r="K289" s="27"/>
@@ -8941,22 +8497,22 @@
     </row>
     <row r="290">
       <c r="A290" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="D290" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="G290" s="97" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="G290" t="s">
+        <v>209</v>
       </c>
       <c r="I290" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="L290" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="O290" s="98" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="O290" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="291">
@@ -8983,32 +8539,29 @@
         <f>CONCATENATE("M 47 ",'Elimination Matches'!O198)</f>
       </c>
     </row>
-    <row r="292"/>
     <row r="293">
       <c r="F293" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="G293" s="23"/>
       <c r="N293" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="O293" s="23"/>
     </row>
     <row r="294">
       <c r="F294" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="G294" s="23"/>
       <c r="N294" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="O294" s="23"/>
     </row>
-    <row r="295"/>
-    <row r="296"/>
     <row r="297">
       <c r="A297" s="27" t="s">
-        <v>297</v>
+        <v>282</v>
       </c>
       <c r="B297" s="27"/>
       <c r="C297" s="27"/>
@@ -9017,7 +8570,7 @@
       <c r="F297" s="27"/>
       <c r="G297" s="27"/>
       <c r="I297" s="27" t="s">
-        <v>298</v>
+        <v>283</v>
       </c>
       <c r="J297" s="27"/>
       <c r="K297" s="27"/>
@@ -9028,22 +8581,22 @@
     </row>
     <row r="298">
       <c r="A298" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="D298" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="G298" s="99" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="G298" t="s">
+        <v>209</v>
       </c>
       <c r="I298" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="L298" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="O298" s="100" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="O298" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="299">
@@ -9070,32 +8623,29 @@
         <f>CONCATENATE("M 51 ",'Elimination Matches'!O214)</f>
       </c>
     </row>
-    <row r="300"/>
     <row r="301">
       <c r="F301" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="G301" s="23"/>
       <c r="N301" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="O301" s="23"/>
     </row>
     <row r="302">
       <c r="F302" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="G302" s="23"/>
       <c r="N302" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="O302" s="23"/>
     </row>
-    <row r="303"/>
-    <row r="304"/>
     <row r="305">
       <c r="A305" s="27" t="s">
-        <v>299</v>
+        <v>284</v>
       </c>
       <c r="B305" s="27"/>
       <c r="C305" s="27"/>
@@ -9104,7 +8654,7 @@
       <c r="F305" s="27"/>
       <c r="G305" s="27"/>
       <c r="I305" s="27" t="s">
-        <v>300</v>
+        <v>285</v>
       </c>
       <c r="J305" s="27"/>
       <c r="K305" s="27"/>
@@ -9115,22 +8665,22 @@
     </row>
     <row r="306">
       <c r="A306" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="D306" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="G306" s="101" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="G306" t="s">
+        <v>209</v>
       </c>
       <c r="I306" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="L306" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="O306" s="102" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="O306" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="307">
@@ -9157,32 +8707,29 @@
         <f>CONCATENATE("M 55 ",'Elimination Matches'!O230)</f>
       </c>
     </row>
-    <row r="308"/>
     <row r="309">
       <c r="F309" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="G309" s="23"/>
       <c r="N309" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="O309" s="23"/>
     </row>
     <row r="310">
       <c r="F310" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="G310" s="23"/>
       <c r="N310" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="O310" s="23"/>
     </row>
-    <row r="311"/>
-    <row r="312"/>
     <row r="313">
       <c r="A313" s="27" t="s">
-        <v>301</v>
+        <v>286</v>
       </c>
       <c r="B313" s="27"/>
       <c r="C313" s="27"/>
@@ -9191,7 +8738,7 @@
       <c r="F313" s="27"/>
       <c r="G313" s="27"/>
       <c r="I313" s="27" t="s">
-        <v>302</v>
+        <v>287</v>
       </c>
       <c r="J313" s="27"/>
       <c r="K313" s="27"/>
@@ -9202,22 +8749,22 @@
     </row>
     <row r="314">
       <c r="A314" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="D314" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="G314" s="103" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="G314" t="s">
+        <v>209</v>
       </c>
       <c r="I314" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="L314" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="O314" s="104" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="O314" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="315">
@@ -9244,37 +8791,29 @@
         <f>CONCATENATE("M 59 ",'Elimination Matches'!O246)</f>
       </c>
     </row>
-    <row r="316"/>
     <row r="317">
       <c r="F317" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="G317" s="23"/>
       <c r="N317" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="O317" s="23"/>
     </row>
     <row r="318">
       <c r="F318" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="G318" s="23"/>
       <c r="N318" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="O318" s="23"/>
     </row>
-    <row r="319"/>
-    <row r="320"/>
-    <row r="321"/>
-    <row r="322"/>
-    <row r="323"/>
-    <row r="324"/>
-    <row r="325"/>
     <row r="326">
       <c r="A326" s="27" t="s">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="B326" s="27"/>
       <c r="C326" s="27"/>
@@ -9291,10 +8830,9 @@
       <c r="N326" s="27"/>
       <c r="O326" s="27"/>
     </row>
-    <row r="327"/>
     <row r="328">
       <c r="A328" s="27" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="B328" s="27"/>
       <c r="C328" s="27"/>
@@ -9303,7 +8841,7 @@
       <c r="F328" s="27"/>
       <c r="G328" s="27"/>
       <c r="I328" s="27" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="J328" s="27"/>
       <c r="K328" s="27"/>
@@ -9314,22 +8852,22 @@
     </row>
     <row r="329">
       <c r="A329" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="D329" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="G329" s="105" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="G329" t="s">
+        <v>209</v>
       </c>
       <c r="I329" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="L329" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="O329" s="106" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="O329" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="330">
@@ -9356,32 +8894,29 @@
         <f>CONCATENATE("M 63 ",'Elimination Matches'!O269)</f>
       </c>
     </row>
-    <row r="331"/>
     <row r="332">
       <c r="F332" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="G332" s="23"/>
       <c r="N332" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="O332" s="23"/>
     </row>
     <row r="333">
       <c r="F333" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="G333" s="23"/>
       <c r="N333" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="O333" s="23"/>
     </row>
-    <row r="334"/>
-    <row r="335"/>
     <row r="336">
       <c r="A336" s="27" t="s">
-        <v>306</v>
+        <v>291</v>
       </c>
       <c r="B336" s="27"/>
       <c r="C336" s="27"/>
@@ -9390,7 +8925,7 @@
       <c r="F336" s="27"/>
       <c r="G336" s="27"/>
       <c r="I336" s="27" t="s">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="J336" s="27"/>
       <c r="K336" s="27"/>
@@ -9401,22 +8936,22 @@
     </row>
     <row r="337">
       <c r="A337" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="D337" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="G337" s="107" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="G337" t="s">
+        <v>209</v>
       </c>
       <c r="I337" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="L337" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="O337" s="108" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="O337" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="338">
@@ -9443,32 +8978,29 @@
         <f>CONCATENATE("M 67 ",'Elimination Matches'!O285)</f>
       </c>
     </row>
-    <row r="339"/>
     <row r="340">
       <c r="F340" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="G340" s="23"/>
       <c r="N340" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="O340" s="23"/>
     </row>
     <row r="341">
       <c r="F341" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="G341" s="23"/>
       <c r="N341" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="O341" s="23"/>
     </row>
-    <row r="342"/>
-    <row r="343"/>
     <row r="344">
       <c r="A344" s="27" t="s">
-        <v>308</v>
+        <v>293</v>
       </c>
       <c r="B344" s="27"/>
       <c r="C344" s="27"/>
@@ -9477,7 +9009,7 @@
       <c r="F344" s="27"/>
       <c r="G344" s="27"/>
       <c r="I344" s="27" t="s">
-        <v>309</v>
+        <v>294</v>
       </c>
       <c r="J344" s="27"/>
       <c r="K344" s="27"/>
@@ -9488,22 +9020,22 @@
     </row>
     <row r="345">
       <c r="A345" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="D345" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="G345" s="109" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="G345" t="s">
+        <v>209</v>
       </c>
       <c r="I345" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="L345" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="O345" s="110" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="O345" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="346">
@@ -9530,32 +9062,29 @@
         <f>CONCATENATE("M 71 ",'Elimination Matches'!O301)</f>
       </c>
     </row>
-    <row r="347"/>
     <row r="348">
       <c r="F348" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="G348" s="23"/>
       <c r="N348" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="O348" s="23"/>
     </row>
     <row r="349">
       <c r="F349" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="G349" s="23"/>
       <c r="N349" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="O349" s="23"/>
     </row>
-    <row r="350"/>
-    <row r="351"/>
     <row r="352">
       <c r="A352" s="27" t="s">
-        <v>310</v>
+        <v>295</v>
       </c>
       <c r="B352" s="27"/>
       <c r="C352" s="27"/>
@@ -9564,7 +9093,7 @@
       <c r="F352" s="27"/>
       <c r="G352" s="27"/>
       <c r="I352" s="27" t="s">
-        <v>311</v>
+        <v>296</v>
       </c>
       <c r="J352" s="27"/>
       <c r="K352" s="27"/>
@@ -9575,22 +9104,22 @@
     </row>
     <row r="353">
       <c r="A353" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="D353" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="G353" s="111" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="G353" t="s">
+        <v>209</v>
       </c>
       <c r="I353" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="L353" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="O353" s="112" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="O353" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="354">
@@ -9617,37 +9146,29 @@
         <f>CONCATENATE("M 75 ",'Elimination Matches'!O317)</f>
       </c>
     </row>
-    <row r="355"/>
     <row r="356">
       <c r="F356" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="G356" s="23"/>
       <c r="N356" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="O356" s="23"/>
     </row>
     <row r="357">
       <c r="F357" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="G357" s="23"/>
       <c r="N357" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="O357" s="23"/>
     </row>
-    <row r="358"/>
-    <row r="359"/>
-    <row r="360"/>
-    <row r="361"/>
-    <row r="362"/>
-    <row r="363"/>
-    <row r="364"/>
     <row r="365">
       <c r="A365" s="27" t="s">
-        <v>312</v>
+        <v>297</v>
       </c>
       <c r="B365" s="27"/>
       <c r="C365" s="27"/>
@@ -9664,10 +9185,9 @@
       <c r="N365" s="27"/>
       <c r="O365" s="27"/>
     </row>
-    <row r="366"/>
     <row r="367">
       <c r="A367" s="27" t="s">
-        <v>313</v>
+        <v>298</v>
       </c>
       <c r="B367" s="27"/>
       <c r="C367" s="27"/>
@@ -9676,7 +9196,7 @@
       <c r="F367" s="27"/>
       <c r="G367" s="27"/>
       <c r="I367" s="27" t="s">
-        <v>313</v>
+        <v>298</v>
       </c>
       <c r="J367" s="27"/>
       <c r="K367" s="27"/>
@@ -9687,22 +9207,22 @@
     </row>
     <row r="368">
       <c r="A368" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="D368" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="G368" s="113" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="G368" t="s">
+        <v>209</v>
       </c>
       <c r="I368" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="L368" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="O368" s="114" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="O368" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="369">
@@ -9729,32 +9249,29 @@
         <f>CONCATENATE("M 79 ",'Elimination Matches'!O340)</f>
       </c>
     </row>
-    <row r="370"/>
     <row r="371">
       <c r="F371" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="G371" s="23"/>
       <c r="N371" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="O371" s="23"/>
     </row>
     <row r="372">
       <c r="F372" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="G372" s="23"/>
       <c r="N372" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="O372" s="23"/>
     </row>
-    <row r="373"/>
-    <row r="374"/>
     <row r="375">
       <c r="A375" s="27" t="s">
-        <v>313</v>
+        <v>298</v>
       </c>
       <c r="B375" s="27"/>
       <c r="C375" s="27"/>
@@ -9763,7 +9280,7 @@
       <c r="F375" s="27"/>
       <c r="G375" s="27"/>
       <c r="I375" s="27" t="s">
-        <v>313</v>
+        <v>298</v>
       </c>
       <c r="J375" s="27"/>
       <c r="K375" s="27"/>
@@ -9774,22 +9291,22 @@
     </row>
     <row r="376">
       <c r="A376" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="D376" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="G376" s="115" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="G376" t="s">
+        <v>209</v>
       </c>
       <c r="I376" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="L376" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="O376" s="116" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="O376" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="377">
@@ -9816,37 +9333,29 @@
         <f>CONCATENATE("M 83 ",'Elimination Matches'!O356)</f>
       </c>
     </row>
-    <row r="378"/>
     <row r="379">
       <c r="F379" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="G379" s="23"/>
       <c r="N379" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="O379" s="23"/>
     </row>
     <row r="380">
       <c r="F380" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="G380" s="23"/>
       <c r="N380" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="O380" s="23"/>
     </row>
-    <row r="381"/>
-    <row r="382"/>
-    <row r="383"/>
-    <row r="384"/>
-    <row r="385"/>
-    <row r="386"/>
-    <row r="387"/>
     <row r="388">
       <c r="A388" s="27" t="s">
-        <v>314</v>
+        <v>299</v>
       </c>
       <c r="B388" s="27"/>
       <c r="C388" s="27"/>
@@ -9863,10 +9372,9 @@
       <c r="N388" s="27"/>
       <c r="O388" s="27"/>
     </row>
-    <row r="389"/>
     <row r="390">
       <c r="A390" s="27" t="s">
-        <v>313</v>
+        <v>298</v>
       </c>
       <c r="B390" s="27"/>
       <c r="C390" s="27"/>
@@ -9875,7 +9383,7 @@
       <c r="F390" s="27"/>
       <c r="G390" s="27"/>
       <c r="I390" s="27" t="s">
-        <v>313</v>
+        <v>298</v>
       </c>
       <c r="J390" s="27"/>
       <c r="K390" s="27"/>
@@ -9886,22 +9394,22 @@
     </row>
     <row r="391">
       <c r="A391" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="D391" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="G391" s="117" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="G391" t="s">
+        <v>209</v>
       </c>
       <c r="I391" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="L391" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="O391" s="118" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="O391" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="392">
@@ -9928,37 +9436,29 @@
         <f>CONCATENATE("M 0 ",'Elimination Matches'!G394)</f>
       </c>
     </row>
-    <row r="393"/>
     <row r="394">
       <c r="F394" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="G394" s="23"/>
       <c r="N394" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="O394" s="23"/>
     </row>
     <row r="395">
       <c r="F395" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="G395" s="23"/>
       <c r="N395" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="O395" s="23"/>
     </row>
-    <row r="396"/>
-    <row r="397"/>
-    <row r="398"/>
-    <row r="399"/>
-    <row r="400"/>
-    <row r="401"/>
-    <row r="402"/>
     <row r="403">
       <c r="A403" s="27" t="s">
-        <v>315</v>
+        <v>300</v>
       </c>
       <c r="B403" s="27"/>
       <c r="C403" s="27"/>
@@ -9975,10 +9475,9 @@
       <c r="N403" s="27"/>
       <c r="O403" s="27"/>
     </row>
-    <row r="404"/>
     <row r="405">
       <c r="A405" s="27" t="s">
-        <v>313</v>
+        <v>298</v>
       </c>
       <c r="B405" s="27"/>
       <c r="C405" s="27"/>
@@ -9989,13 +9488,13 @@
     </row>
     <row r="406">
       <c r="A406" s="28" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="D406" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="G406" s="119" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="G406" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="407">
@@ -10011,16 +9510,15 @@
         <f>CONCATENATE("M 0 ",'Elimination Matches'!O394)</f>
       </c>
     </row>
-    <row r="408"/>
     <row r="409">
       <c r="F409" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="G409" s="23"/>
     </row>
     <row r="410">
       <c r="F410" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="G410" s="23"/>
     </row>

--- a/playoffs-example-large.xlsx
+++ b/playoffs-example-large.xlsx
@@ -25,7 +25,9 @@
     <sheet name="Tree 7" sheetId="16" r:id="rId19"/>
     <sheet name="Tree 8" sheetId="17" r:id="rId20"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName localSheetId="3" name="_xlnm.Print_Area">'Names to Print'!$A$1:$B$182</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -1068,7 +1070,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1084,6 +1086,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -1202,7 +1209,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true"/>
@@ -1273,10 +1280,13 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="10" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="10" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -3718,192 +3728,192 @@
     <col customWidth="true" max="2" min="2" width="10"/>
   </cols>
   <sheetData>
-    <row r="3">
-      <c r="E3" s="24" t="s">
+    <row r="6">
+      <c r="E6" s="24" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4">
-      <c r="F4" s="22"/>
-      <c r="G4" s="20"/>
-    </row>
-    <row r="5">
-      <c r="G5" s="21">
+    <row r="7">
+      <c r="F7" s="22"/>
+      <c r="G7" s="20"/>
+    </row>
+    <row r="8">
+      <c r="G8" s="21">
         <v>28</v>
       </c>
     </row>
-    <row r="6">
-      <c r="G6" s="20"/>
-      <c r="H6" s="22"/>
-      <c r="I6" s="20"/>
-    </row>
-    <row r="7">
-      <c r="E7" s="24" t="s">
+    <row r="9">
+      <c r="G9" s="20"/>
+      <c r="H9" s="22"/>
+      <c r="I9" s="20"/>
+    </row>
+    <row r="10">
+      <c r="E10" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="F7" s="23"/>
-      <c r="G7" s="20"/>
-      <c r="I7" s="20"/>
-    </row>
-    <row r="8">
-      <c r="I8" s="20"/>
-    </row>
-    <row r="9">
-      <c r="I9" s="21">
+      <c r="F10" s="23"/>
+      <c r="G10" s="20"/>
+      <c r="I10" s="20"/>
+    </row>
+    <row r="11">
+      <c r="I11" s="20"/>
+    </row>
+    <row r="12">
+      <c r="I12" s="21">
         <v>60</v>
       </c>
     </row>
-    <row r="10">
-      <c r="I10" s="20"/>
-      <c r="J10" s="22"/>
-      <c r="K10" s="20"/>
-    </row>
-    <row r="11">
-      <c r="E11" s="24" t="s">
+    <row r="13">
+      <c r="I13" s="20"/>
+      <c r="J13" s="22"/>
+      <c r="K13" s="20"/>
+    </row>
+    <row r="14">
+      <c r="E14" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="I11" s="20"/>
-      <c r="K11" s="20"/>
-    </row>
-    <row r="12">
-      <c r="F12" s="22"/>
-      <c r="G12" s="20"/>
-      <c r="I12" s="20"/>
-      <c r="K12" s="20"/>
-    </row>
-    <row r="13">
-      <c r="G13" s="21">
+      <c r="I14" s="20"/>
+      <c r="K14" s="20"/>
+    </row>
+    <row r="15">
+      <c r="F15" s="22"/>
+      <c r="G15" s="20"/>
+      <c r="I15" s="20"/>
+      <c r="K15" s="20"/>
+    </row>
+    <row r="16">
+      <c r="G16" s="21">
         <v>29</v>
       </c>
-      <c r="H13" s="23"/>
-      <c r="I13" s="20"/>
-      <c r="K13" s="20"/>
-    </row>
-    <row r="14">
-      <c r="C14" s="24" t="s">
+      <c r="H16" s="23"/>
+      <c r="I16" s="20"/>
+      <c r="K16" s="20"/>
+    </row>
+    <row r="17">
+      <c r="C17" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="G14" s="20"/>
-      <c r="K14" s="20"/>
-    </row>
-    <row r="15">
-      <c r="D15" s="22"/>
-      <c r="E15" s="21">
+      <c r="G17" s="20"/>
+      <c r="K17" s="20"/>
+    </row>
+    <row r="18">
+      <c r="D18" s="22"/>
+      <c r="E18" s="21">
         <v>1</v>
       </c>
-      <c r="F15" s="23"/>
-      <c r="G15" s="20"/>
-      <c r="K15" s="20"/>
-    </row>
-    <row r="16">
-      <c r="C16" s="24" t="s">
+      <c r="F18" s="23"/>
+      <c r="G18" s="20"/>
+      <c r="K18" s="20"/>
+    </row>
+    <row r="19">
+      <c r="C19" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="23"/>
-      <c r="E16" s="20"/>
-      <c r="K16" s="20"/>
-    </row>
-    <row r="17">
-      <c r="K17" s="21">
+      <c r="D19" s="23"/>
+      <c r="E19" s="20"/>
+      <c r="K19" s="20"/>
+    </row>
+    <row r="20">
+      <c r="K20" s="21">
         <v>76</v>
       </c>
     </row>
-    <row r="18">
-      <c r="K18" s="20"/>
-    </row>
-    <row r="19">
-      <c r="E19" s="24" t="s">
+    <row r="21">
+      <c r="K21" s="20"/>
+    </row>
+    <row r="22">
+      <c r="E22" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="K19" s="20"/>
-    </row>
-    <row r="20">
-      <c r="F20" s="22"/>
-      <c r="G20" s="20"/>
-      <c r="K20" s="20"/>
-    </row>
-    <row r="21">
-      <c r="G21" s="21">
+      <c r="K22" s="20"/>
+    </row>
+    <row r="23">
+      <c r="F23" s="22"/>
+      <c r="G23" s="20"/>
+      <c r="K23" s="20"/>
+    </row>
+    <row r="24">
+      <c r="G24" s="21">
         <v>30</v>
       </c>
-      <c r="K21" s="20"/>
-    </row>
-    <row r="22">
-      <c r="C22" s="24" t="s">
+      <c r="K24" s="20"/>
+    </row>
+    <row r="25">
+      <c r="C25" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="G22" s="20"/>
-      <c r="H22" s="22"/>
-      <c r="I22" s="20"/>
-      <c r="K22" s="20"/>
-    </row>
-    <row r="23">
-      <c r="D23" s="22"/>
-      <c r="E23" s="21">
+      <c r="G25" s="20"/>
+      <c r="H25" s="22"/>
+      <c r="I25" s="20"/>
+      <c r="K25" s="20"/>
+    </row>
+    <row r="26">
+      <c r="D26" s="22"/>
+      <c r="E26" s="21">
         <v>2</v>
       </c>
-      <c r="F23" s="23"/>
-      <c r="G23" s="20"/>
-      <c r="I23" s="20"/>
-      <c r="K23" s="20"/>
-    </row>
-    <row r="24">
-      <c r="C24" s="24" t="s">
+      <c r="F26" s="23"/>
+      <c r="G26" s="20"/>
+      <c r="I26" s="20"/>
+      <c r="K26" s="20"/>
+    </row>
+    <row r="27">
+      <c r="C27" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="D24" s="23"/>
-      <c r="E24" s="20"/>
-      <c r="I24" s="20"/>
-      <c r="K24" s="20"/>
-    </row>
-    <row r="25">
-      <c r="I25" s="21">
+      <c r="D27" s="23"/>
+      <c r="E27" s="20"/>
+      <c r="I27" s="20"/>
+      <c r="K27" s="20"/>
+    </row>
+    <row r="28">
+      <c r="I28" s="21">
         <v>61</v>
       </c>
-      <c r="J25" s="23"/>
-      <c r="K25" s="20"/>
-    </row>
-    <row r="26">
-      <c r="I26" s="20"/>
-    </row>
-    <row r="27">
-      <c r="E27" s="24" t="s">
+      <c r="J28" s="23"/>
+      <c r="K28" s="20"/>
+    </row>
+    <row r="29">
+      <c r="I29" s="20"/>
+    </row>
+    <row r="30">
+      <c r="E30" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="I27" s="20"/>
-    </row>
-    <row r="28">
-      <c r="F28" s="22"/>
-      <c r="G28" s="20"/>
-      <c r="I28" s="20"/>
-    </row>
-    <row r="29">
-      <c r="G29" s="21">
+      <c r="I30" s="20"/>
+    </row>
+    <row r="31">
+      <c r="F31" s="22"/>
+      <c r="G31" s="20"/>
+      <c r="I31" s="20"/>
+    </row>
+    <row r="32">
+      <c r="G32" s="21">
         <v>31</v>
       </c>
-      <c r="H29" s="23"/>
-      <c r="I29" s="20"/>
-    </row>
-    <row r="30">
-      <c r="C30" s="24" t="s">
+      <c r="H32" s="23"/>
+      <c r="I32" s="20"/>
+    </row>
+    <row r="33">
+      <c r="C33" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="G30" s="20"/>
-    </row>
-    <row r="31">
-      <c r="D31" s="22"/>
-      <c r="E31" s="21">
+      <c r="G33" s="20"/>
+    </row>
+    <row r="34">
+      <c r="D34" s="22"/>
+      <c r="E34" s="21">
         <v>3</v>
       </c>
-      <c r="F31" s="23"/>
-      <c r="G31" s="20"/>
-    </row>
-    <row r="32">
-      <c r="C32" s="24" t="s">
+      <c r="F34" s="23"/>
+      <c r="G34" s="20"/>
+    </row>
+    <row r="35">
+      <c r="C35" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="D32" s="23"/>
-      <c r="E32" s="20"/>
+      <c r="D35" s="23"/>
+      <c r="E35" s="20"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="true" verticalCentered="true"/>
@@ -3923,192 +3933,192 @@
     <col customWidth="true" max="2" min="2" width="10"/>
   </cols>
   <sheetData>
-    <row r="3">
-      <c r="E3" s="24" t="s">
+    <row r="6">
+      <c r="E6" s="24" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="4">
-      <c r="F4" s="22"/>
-      <c r="G4" s="20"/>
-    </row>
-    <row r="5">
-      <c r="G5" s="21">
+    <row r="7">
+      <c r="F7" s="22"/>
+      <c r="G7" s="20"/>
+    </row>
+    <row r="8">
+      <c r="G8" s="21">
         <v>32</v>
       </c>
     </row>
-    <row r="6">
-      <c r="G6" s="20"/>
-      <c r="H6" s="22"/>
-      <c r="I6" s="20"/>
-    </row>
-    <row r="7">
-      <c r="E7" s="24" t="s">
+    <row r="9">
+      <c r="G9" s="20"/>
+      <c r="H9" s="22"/>
+      <c r="I9" s="20"/>
+    </row>
+    <row r="10">
+      <c r="E10" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="F7" s="23"/>
-      <c r="G7" s="20"/>
-      <c r="I7" s="20"/>
-    </row>
-    <row r="8">
-      <c r="I8" s="20"/>
-    </row>
-    <row r="9">
-      <c r="I9" s="21">
+      <c r="F10" s="23"/>
+      <c r="G10" s="20"/>
+      <c r="I10" s="20"/>
+    </row>
+    <row r="11">
+      <c r="I11" s="20"/>
+    </row>
+    <row r="12">
+      <c r="I12" s="21">
         <v>62</v>
       </c>
     </row>
-    <row r="10">
-      <c r="I10" s="20"/>
-      <c r="J10" s="22"/>
-      <c r="K10" s="20"/>
-    </row>
-    <row r="11">
-      <c r="E11" s="24" t="s">
+    <row r="13">
+      <c r="I13" s="20"/>
+      <c r="J13" s="22"/>
+      <c r="K13" s="20"/>
+    </row>
+    <row r="14">
+      <c r="E14" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="I11" s="20"/>
-      <c r="K11" s="20"/>
-    </row>
-    <row r="12">
-      <c r="F12" s="22"/>
-      <c r="G12" s="20"/>
-      <c r="I12" s="20"/>
-      <c r="K12" s="20"/>
-    </row>
-    <row r="13">
-      <c r="G13" s="21">
+      <c r="I14" s="20"/>
+      <c r="K14" s="20"/>
+    </row>
+    <row r="15">
+      <c r="F15" s="22"/>
+      <c r="G15" s="20"/>
+      <c r="I15" s="20"/>
+      <c r="K15" s="20"/>
+    </row>
+    <row r="16">
+      <c r="G16" s="21">
         <v>33</v>
       </c>
-      <c r="H13" s="23"/>
-      <c r="I13" s="20"/>
-      <c r="K13" s="20"/>
-    </row>
-    <row r="14">
-      <c r="C14" s="24" t="s">
+      <c r="H16" s="23"/>
+      <c r="I16" s="20"/>
+      <c r="K16" s="20"/>
+    </row>
+    <row r="17">
+      <c r="C17" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="G14" s="20"/>
-      <c r="K14" s="20"/>
-    </row>
-    <row r="15">
-      <c r="D15" s="22"/>
-      <c r="E15" s="21">
+      <c r="G17" s="20"/>
+      <c r="K17" s="20"/>
+    </row>
+    <row r="18">
+      <c r="D18" s="22"/>
+      <c r="E18" s="21">
         <v>4</v>
       </c>
-      <c r="F15" s="23"/>
-      <c r="G15" s="20"/>
-      <c r="K15" s="20"/>
-    </row>
-    <row r="16">
-      <c r="C16" s="24" t="s">
+      <c r="F18" s="23"/>
+      <c r="G18" s="20"/>
+      <c r="K18" s="20"/>
+    </row>
+    <row r="19">
+      <c r="C19" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="D16" s="23"/>
-      <c r="E16" s="20"/>
-      <c r="K16" s="20"/>
-    </row>
-    <row r="17">
-      <c r="K17" s="21">
+      <c r="D19" s="23"/>
+      <c r="E19" s="20"/>
+      <c r="K19" s="20"/>
+    </row>
+    <row r="20">
+      <c r="K20" s="21">
         <v>77</v>
       </c>
     </row>
-    <row r="18">
-      <c r="K18" s="20"/>
-    </row>
-    <row r="19">
-      <c r="E19" s="24" t="s">
+    <row r="21">
+      <c r="K21" s="20"/>
+    </row>
+    <row r="22">
+      <c r="E22" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="K19" s="20"/>
-    </row>
-    <row r="20">
-      <c r="F20" s="22"/>
-      <c r="G20" s="20"/>
-      <c r="K20" s="20"/>
-    </row>
-    <row r="21">
-      <c r="G21" s="21">
+      <c r="K22" s="20"/>
+    </row>
+    <row r="23">
+      <c r="F23" s="22"/>
+      <c r="G23" s="20"/>
+      <c r="K23" s="20"/>
+    </row>
+    <row r="24">
+      <c r="G24" s="21">
         <v>34</v>
       </c>
-      <c r="K21" s="20"/>
-    </row>
-    <row r="22">
-      <c r="C22" s="24" t="s">
+      <c r="K24" s="20"/>
+    </row>
+    <row r="25">
+      <c r="C25" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="G22" s="20"/>
-      <c r="H22" s="22"/>
-      <c r="I22" s="20"/>
-      <c r="K22" s="20"/>
-    </row>
-    <row r="23">
-      <c r="D23" s="22"/>
-      <c r="E23" s="21">
+      <c r="G25" s="20"/>
+      <c r="H25" s="22"/>
+      <c r="I25" s="20"/>
+      <c r="K25" s="20"/>
+    </row>
+    <row r="26">
+      <c r="D26" s="22"/>
+      <c r="E26" s="21">
         <v>5</v>
       </c>
-      <c r="F23" s="23"/>
-      <c r="G23" s="20"/>
-      <c r="I23" s="20"/>
-      <c r="K23" s="20"/>
-    </row>
-    <row r="24">
-      <c r="C24" s="24" t="s">
+      <c r="F26" s="23"/>
+      <c r="G26" s="20"/>
+      <c r="I26" s="20"/>
+      <c r="K26" s="20"/>
+    </row>
+    <row r="27">
+      <c r="C27" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="D24" s="23"/>
-      <c r="E24" s="20"/>
-      <c r="I24" s="20"/>
-      <c r="K24" s="20"/>
-    </row>
-    <row r="25">
-      <c r="I25" s="21">
+      <c r="D27" s="23"/>
+      <c r="E27" s="20"/>
+      <c r="I27" s="20"/>
+      <c r="K27" s="20"/>
+    </row>
+    <row r="28">
+      <c r="I28" s="21">
         <v>63</v>
       </c>
-      <c r="J25" s="23"/>
-      <c r="K25" s="20"/>
-    </row>
-    <row r="26">
-      <c r="I26" s="20"/>
-    </row>
-    <row r="27">
-      <c r="E27" s="24" t="s">
+      <c r="J28" s="23"/>
+      <c r="K28" s="20"/>
+    </row>
+    <row r="29">
+      <c r="I29" s="20"/>
+    </row>
+    <row r="30">
+      <c r="E30" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="I27" s="20"/>
-    </row>
-    <row r="28">
-      <c r="F28" s="22"/>
-      <c r="G28" s="20"/>
-      <c r="I28" s="20"/>
-    </row>
-    <row r="29">
-      <c r="G29" s="21">
+      <c r="I30" s="20"/>
+    </row>
+    <row r="31">
+      <c r="F31" s="22"/>
+      <c r="G31" s="20"/>
+      <c r="I31" s="20"/>
+    </row>
+    <row r="32">
+      <c r="G32" s="21">
         <v>35</v>
       </c>
-      <c r="H29" s="23"/>
-      <c r="I29" s="20"/>
-    </row>
-    <row r="30">
-      <c r="C30" s="24" t="s">
+      <c r="H32" s="23"/>
+      <c r="I32" s="20"/>
+    </row>
+    <row r="33">
+      <c r="C33" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="G30" s="20"/>
-    </row>
-    <row r="31">
-      <c r="D31" s="22"/>
-      <c r="E31" s="21">
+      <c r="G33" s="20"/>
+    </row>
+    <row r="34">
+      <c r="D34" s="22"/>
+      <c r="E34" s="21">
         <v>6</v>
       </c>
-      <c r="F31" s="23"/>
-      <c r="G31" s="20"/>
-    </row>
-    <row r="32">
-      <c r="C32" s="24" t="s">
+      <c r="F34" s="23"/>
+      <c r="G34" s="20"/>
+    </row>
+    <row r="35">
+      <c r="C35" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="D32" s="23"/>
-      <c r="E32" s="20"/>
+      <c r="D35" s="23"/>
+      <c r="E35" s="20"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="true" verticalCentered="true"/>
@@ -4128,192 +4138,192 @@
     <col customWidth="true" max="2" min="2" width="10"/>
   </cols>
   <sheetData>
-    <row r="3">
-      <c r="E3" s="24" t="s">
+    <row r="6">
+      <c r="E6" s="24" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="4">
-      <c r="F4" s="22"/>
-      <c r="G4" s="20"/>
-    </row>
-    <row r="5">
-      <c r="G5" s="21">
+    <row r="7">
+      <c r="F7" s="22"/>
+      <c r="G7" s="20"/>
+    </row>
+    <row r="8">
+      <c r="G8" s="21">
         <v>36</v>
       </c>
     </row>
-    <row r="6">
-      <c r="G6" s="20"/>
-      <c r="H6" s="22"/>
-      <c r="I6" s="20"/>
-    </row>
-    <row r="7">
-      <c r="E7" s="24" t="s">
+    <row r="9">
+      <c r="G9" s="20"/>
+      <c r="H9" s="22"/>
+      <c r="I9" s="20"/>
+    </row>
+    <row r="10">
+      <c r="E10" s="24" t="s">
         <v>71</v>
       </c>
-      <c r="F7" s="23"/>
-      <c r="G7" s="20"/>
-      <c r="I7" s="20"/>
-    </row>
-    <row r="8">
-      <c r="I8" s="20"/>
-    </row>
-    <row r="9">
-      <c r="I9" s="21">
+      <c r="F10" s="23"/>
+      <c r="G10" s="20"/>
+      <c r="I10" s="20"/>
+    </row>
+    <row r="11">
+      <c r="I11" s="20"/>
+    </row>
+    <row r="12">
+      <c r="I12" s="21">
         <v>64</v>
       </c>
     </row>
-    <row r="10">
-      <c r="I10" s="20"/>
-      <c r="J10" s="22"/>
-      <c r="K10" s="20"/>
-    </row>
-    <row r="11">
-      <c r="E11" s="24" t="s">
+    <row r="13">
+      <c r="I13" s="20"/>
+      <c r="J13" s="22"/>
+      <c r="K13" s="20"/>
+    </row>
+    <row r="14">
+      <c r="E14" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="I11" s="20"/>
-      <c r="K11" s="20"/>
-    </row>
-    <row r="12">
-      <c r="F12" s="22"/>
-      <c r="G12" s="20"/>
-      <c r="I12" s="20"/>
-      <c r="K12" s="20"/>
-    </row>
-    <row r="13">
-      <c r="G13" s="21">
+      <c r="I14" s="20"/>
+      <c r="K14" s="20"/>
+    </row>
+    <row r="15">
+      <c r="F15" s="22"/>
+      <c r="G15" s="20"/>
+      <c r="I15" s="20"/>
+      <c r="K15" s="20"/>
+    </row>
+    <row r="16">
+      <c r="G16" s="21">
         <v>37</v>
       </c>
-      <c r="H13" s="23"/>
-      <c r="I13" s="20"/>
-      <c r="K13" s="20"/>
-    </row>
-    <row r="14">
-      <c r="C14" s="24" t="s">
+      <c r="H16" s="23"/>
+      <c r="I16" s="20"/>
+      <c r="K16" s="20"/>
+    </row>
+    <row r="17">
+      <c r="C17" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="G14" s="20"/>
-      <c r="K14" s="20"/>
-    </row>
-    <row r="15">
-      <c r="D15" s="22"/>
-      <c r="E15" s="21">
+      <c r="G17" s="20"/>
+      <c r="K17" s="20"/>
+    </row>
+    <row r="18">
+      <c r="D18" s="22"/>
+      <c r="E18" s="21">
         <v>7</v>
       </c>
-      <c r="F15" s="23"/>
-      <c r="G15" s="20"/>
-      <c r="K15" s="20"/>
-    </row>
-    <row r="16">
-      <c r="C16" s="24" t="s">
+      <c r="F18" s="23"/>
+      <c r="G18" s="20"/>
+      <c r="K18" s="20"/>
+    </row>
+    <row r="19">
+      <c r="C19" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="D16" s="23"/>
-      <c r="E16" s="20"/>
-      <c r="K16" s="20"/>
-    </row>
-    <row r="17">
-      <c r="K17" s="21">
+      <c r="D19" s="23"/>
+      <c r="E19" s="20"/>
+      <c r="K19" s="20"/>
+    </row>
+    <row r="20">
+      <c r="K20" s="21">
         <v>78</v>
       </c>
     </row>
-    <row r="18">
-      <c r="K18" s="20"/>
-    </row>
-    <row r="19">
-      <c r="E19" s="24" t="s">
+    <row r="21">
+      <c r="K21" s="20"/>
+    </row>
+    <row r="22">
+      <c r="E22" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="K19" s="20"/>
-    </row>
-    <row r="20">
-      <c r="F20" s="22"/>
-      <c r="G20" s="20"/>
-      <c r="K20" s="20"/>
-    </row>
-    <row r="21">
-      <c r="G21" s="21">
+      <c r="K22" s="20"/>
+    </row>
+    <row r="23">
+      <c r="F23" s="22"/>
+      <c r="G23" s="20"/>
+      <c r="K23" s="20"/>
+    </row>
+    <row r="24">
+      <c r="G24" s="21">
         <v>38</v>
       </c>
-      <c r="K21" s="20"/>
-    </row>
-    <row r="22">
-      <c r="C22" s="24" t="s">
+      <c r="K24" s="20"/>
+    </row>
+    <row r="25">
+      <c r="C25" s="24" t="s">
         <v>82</v>
       </c>
-      <c r="G22" s="20"/>
-      <c r="H22" s="22"/>
-      <c r="I22" s="20"/>
-      <c r="K22" s="20"/>
-    </row>
-    <row r="23">
-      <c r="D23" s="22"/>
-      <c r="E23" s="21">
+      <c r="G25" s="20"/>
+      <c r="H25" s="22"/>
+      <c r="I25" s="20"/>
+      <c r="K25" s="20"/>
+    </row>
+    <row r="26">
+      <c r="D26" s="22"/>
+      <c r="E26" s="21">
         <v>8</v>
       </c>
-      <c r="F23" s="23"/>
-      <c r="G23" s="20"/>
-      <c r="I23" s="20"/>
-      <c r="K23" s="20"/>
-    </row>
-    <row r="24">
-      <c r="C24" s="24" t="s">
+      <c r="F26" s="23"/>
+      <c r="G26" s="20"/>
+      <c r="I26" s="20"/>
+      <c r="K26" s="20"/>
+    </row>
+    <row r="27">
+      <c r="C27" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="D24" s="23"/>
-      <c r="E24" s="20"/>
-      <c r="I24" s="20"/>
-      <c r="K24" s="20"/>
-    </row>
-    <row r="25">
-      <c r="I25" s="21">
+      <c r="D27" s="23"/>
+      <c r="E27" s="20"/>
+      <c r="I27" s="20"/>
+      <c r="K27" s="20"/>
+    </row>
+    <row r="28">
+      <c r="I28" s="21">
         <v>65</v>
       </c>
-      <c r="J25" s="23"/>
-      <c r="K25" s="20"/>
-    </row>
-    <row r="26">
-      <c r="I26" s="20"/>
-    </row>
-    <row r="27">
-      <c r="E27" s="24" t="s">
+      <c r="J28" s="23"/>
+      <c r="K28" s="20"/>
+    </row>
+    <row r="29">
+      <c r="I29" s="20"/>
+    </row>
+    <row r="30">
+      <c r="E30" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="I27" s="20"/>
-    </row>
-    <row r="28">
-      <c r="F28" s="22"/>
-      <c r="G28" s="20"/>
-      <c r="I28" s="20"/>
-    </row>
-    <row r="29">
-      <c r="G29" s="21">
+      <c r="I30" s="20"/>
+    </row>
+    <row r="31">
+      <c r="F31" s="22"/>
+      <c r="G31" s="20"/>
+      <c r="I31" s="20"/>
+    </row>
+    <row r="32">
+      <c r="G32" s="21">
         <v>39</v>
       </c>
-      <c r="H29" s="23"/>
-      <c r="I29" s="20"/>
-    </row>
-    <row r="30">
-      <c r="C30" s="24" t="s">
+      <c r="H32" s="23"/>
+      <c r="I32" s="20"/>
+    </row>
+    <row r="33">
+      <c r="C33" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="G30" s="20"/>
-    </row>
-    <row r="31">
-      <c r="D31" s="22"/>
-      <c r="E31" s="21">
+      <c r="G33" s="20"/>
+    </row>
+    <row r="34">
+      <c r="D34" s="22"/>
+      <c r="E34" s="21">
         <v>9</v>
       </c>
-      <c r="F31" s="23"/>
-      <c r="G31" s="20"/>
-    </row>
-    <row r="32">
-      <c r="C32" s="24" t="s">
+      <c r="F34" s="23"/>
+      <c r="G34" s="20"/>
+    </row>
+    <row r="35">
+      <c r="C35" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="D32" s="23"/>
-      <c r="E32" s="20"/>
+      <c r="D35" s="23"/>
+      <c r="E35" s="20"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="true" verticalCentered="true"/>
@@ -4333,201 +4343,201 @@
     <col customWidth="true" max="2" min="2" width="10"/>
   </cols>
   <sheetData>
-    <row r="3">
-      <c r="E3" s="24" t="s">
+    <row r="6">
+      <c r="E6" s="24" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="4">
-      <c r="F4" s="22"/>
-      <c r="G4" s="20"/>
-    </row>
-    <row r="5">
-      <c r="G5" s="21">
+    <row r="7">
+      <c r="F7" s="22"/>
+      <c r="G7" s="20"/>
+    </row>
+    <row r="8">
+      <c r="G8" s="21">
         <v>40</v>
       </c>
     </row>
-    <row r="6">
-      <c r="C6" s="24" t="s">
+    <row r="9">
+      <c r="C9" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="G6" s="20"/>
-      <c r="H6" s="22"/>
-      <c r="I6" s="20"/>
-    </row>
-    <row r="7">
-      <c r="D7" s="22"/>
-      <c r="E7" s="21">
+      <c r="G9" s="20"/>
+      <c r="H9" s="22"/>
+      <c r="I9" s="20"/>
+    </row>
+    <row r="10">
+      <c r="D10" s="22"/>
+      <c r="E10" s="21">
         <v>10</v>
       </c>
-      <c r="F7" s="23"/>
-      <c r="G7" s="20"/>
-      <c r="I7" s="20"/>
-    </row>
-    <row r="8">
-      <c r="C8" s="24" t="s">
+      <c r="F10" s="23"/>
+      <c r="G10" s="20"/>
+      <c r="I10" s="20"/>
+    </row>
+    <row r="11">
+      <c r="C11" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="23"/>
-      <c r="E8" s="20"/>
-      <c r="I8" s="20"/>
-    </row>
-    <row r="9">
-      <c r="I9" s="21">
+      <c r="D11" s="23"/>
+      <c r="E11" s="20"/>
+      <c r="I11" s="20"/>
+    </row>
+    <row r="12">
+      <c r="I12" s="21">
         <v>66</v>
       </c>
     </row>
-    <row r="10">
-      <c r="I10" s="20"/>
-      <c r="J10" s="22"/>
-      <c r="K10" s="20"/>
-    </row>
-    <row r="11">
-      <c r="E11" s="24" t="s">
+    <row r="13">
+      <c r="I13" s="20"/>
+      <c r="J13" s="22"/>
+      <c r="K13" s="20"/>
+    </row>
+    <row r="14">
+      <c r="E14" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="I11" s="20"/>
-      <c r="K11" s="20"/>
-    </row>
-    <row r="12">
-      <c r="F12" s="22"/>
-      <c r="G12" s="20"/>
-      <c r="I12" s="20"/>
-      <c r="K12" s="20"/>
-    </row>
-    <row r="13">
-      <c r="G13" s="21">
+      <c r="I14" s="20"/>
+      <c r="K14" s="20"/>
+    </row>
+    <row r="15">
+      <c r="F15" s="22"/>
+      <c r="G15" s="20"/>
+      <c r="I15" s="20"/>
+      <c r="K15" s="20"/>
+    </row>
+    <row r="16">
+      <c r="G16" s="21">
         <v>41</v>
       </c>
-      <c r="H13" s="23"/>
-      <c r="I13" s="20"/>
-      <c r="K13" s="20"/>
-    </row>
-    <row r="14">
-      <c r="C14" s="24" t="s">
+      <c r="H16" s="23"/>
+      <c r="I16" s="20"/>
+      <c r="K16" s="20"/>
+    </row>
+    <row r="17">
+      <c r="C17" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="G14" s="20"/>
-      <c r="K14" s="20"/>
-    </row>
-    <row r="15">
-      <c r="D15" s="22"/>
-      <c r="E15" s="21">
+      <c r="G17" s="20"/>
+      <c r="K17" s="20"/>
+    </row>
+    <row r="18">
+      <c r="D18" s="22"/>
+      <c r="E18" s="21">
         <v>11</v>
       </c>
-      <c r="F15" s="23"/>
-      <c r="G15" s="20"/>
-      <c r="K15" s="20"/>
-    </row>
-    <row r="16">
-      <c r="C16" s="24" t="s">
+      <c r="F18" s="23"/>
+      <c r="G18" s="20"/>
+      <c r="K18" s="20"/>
+    </row>
+    <row r="19">
+      <c r="C19" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="D16" s="23"/>
-      <c r="E16" s="20"/>
-      <c r="K16" s="20"/>
-    </row>
-    <row r="17">
-      <c r="K17" s="21">
+      <c r="D19" s="23"/>
+      <c r="E19" s="20"/>
+      <c r="K19" s="20"/>
+    </row>
+    <row r="20">
+      <c r="K20" s="21">
         <v>79</v>
       </c>
     </row>
-    <row r="18">
-      <c r="K18" s="20"/>
-    </row>
-    <row r="19">
-      <c r="E19" s="24" t="s">
+    <row r="21">
+      <c r="K21" s="20"/>
+    </row>
+    <row r="22">
+      <c r="E22" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="K19" s="20"/>
-    </row>
-    <row r="20">
-      <c r="F20" s="22"/>
-      <c r="G20" s="20"/>
-      <c r="K20" s="20"/>
-    </row>
-    <row r="21">
-      <c r="G21" s="21">
+      <c r="K22" s="20"/>
+    </row>
+    <row r="23">
+      <c r="F23" s="22"/>
+      <c r="G23" s="20"/>
+      <c r="K23" s="20"/>
+    </row>
+    <row r="24">
+      <c r="G24" s="21">
         <v>42</v>
       </c>
-      <c r="K21" s="20"/>
-    </row>
-    <row r="22">
-      <c r="C22" s="24" t="s">
+      <c r="K24" s="20"/>
+    </row>
+    <row r="25">
+      <c r="C25" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="G22" s="20"/>
-      <c r="H22" s="22"/>
-      <c r="I22" s="20"/>
-      <c r="K22" s="20"/>
-    </row>
-    <row r="23">
-      <c r="D23" s="22"/>
-      <c r="E23" s="21">
+      <c r="G25" s="20"/>
+      <c r="H25" s="22"/>
+      <c r="I25" s="20"/>
+      <c r="K25" s="20"/>
+    </row>
+    <row r="26">
+      <c r="D26" s="22"/>
+      <c r="E26" s="21">
         <v>12</v>
       </c>
-      <c r="F23" s="23"/>
-      <c r="G23" s="20"/>
-      <c r="I23" s="20"/>
-      <c r="K23" s="20"/>
-    </row>
-    <row r="24">
-      <c r="C24" s="24" t="s">
+      <c r="F26" s="23"/>
+      <c r="G26" s="20"/>
+      <c r="I26" s="20"/>
+      <c r="K26" s="20"/>
+    </row>
+    <row r="27">
+      <c r="C27" s="24" t="s">
         <v>96</v>
       </c>
-      <c r="D24" s="23"/>
-      <c r="E24" s="20"/>
-      <c r="I24" s="20"/>
-      <c r="K24" s="20"/>
-    </row>
-    <row r="25">
-      <c r="I25" s="21">
+      <c r="D27" s="23"/>
+      <c r="E27" s="20"/>
+      <c r="I27" s="20"/>
+      <c r="K27" s="20"/>
+    </row>
+    <row r="28">
+      <c r="I28" s="21">
         <v>67</v>
       </c>
-      <c r="J25" s="23"/>
-      <c r="K25" s="20"/>
-    </row>
-    <row r="26">
-      <c r="I26" s="20"/>
-    </row>
-    <row r="27">
-      <c r="E27" s="24" t="s">
+      <c r="J28" s="23"/>
+      <c r="K28" s="20"/>
+    </row>
+    <row r="29">
+      <c r="I29" s="20"/>
+    </row>
+    <row r="30">
+      <c r="E30" s="24" t="s">
         <v>98</v>
       </c>
-      <c r="I27" s="20"/>
-    </row>
-    <row r="28">
-      <c r="F28" s="22"/>
-      <c r="G28" s="20"/>
-      <c r="I28" s="20"/>
-    </row>
-    <row r="29">
-      <c r="G29" s="21">
+      <c r="I30" s="20"/>
+    </row>
+    <row r="31">
+      <c r="F31" s="22"/>
+      <c r="G31" s="20"/>
+      <c r="I31" s="20"/>
+    </row>
+    <row r="32">
+      <c r="G32" s="21">
         <v>43</v>
       </c>
-      <c r="H29" s="23"/>
-      <c r="I29" s="20"/>
-    </row>
-    <row r="30">
-      <c r="C30" s="24" t="s">
+      <c r="H32" s="23"/>
+      <c r="I32" s="20"/>
+    </row>
+    <row r="33">
+      <c r="C33" s="24" t="s">
         <v>100</v>
       </c>
-      <c r="G30" s="20"/>
-    </row>
-    <row r="31">
-      <c r="D31" s="22"/>
-      <c r="E31" s="21">
+      <c r="G33" s="20"/>
+    </row>
+    <row r="34">
+      <c r="D34" s="22"/>
+      <c r="E34" s="21">
         <v>13</v>
       </c>
-      <c r="F31" s="23"/>
-      <c r="G31" s="20"/>
-    </row>
-    <row r="32">
-      <c r="C32" s="24" t="s">
+      <c r="F34" s="23"/>
+      <c r="G34" s="20"/>
+    </row>
+    <row r="35">
+      <c r="C35" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="D32" s="23"/>
-      <c r="E32" s="20"/>
+      <c r="D35" s="23"/>
+      <c r="E35" s="20"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="true" verticalCentered="true"/>
@@ -4547,192 +4557,192 @@
     <col customWidth="true" max="2" min="2" width="10"/>
   </cols>
   <sheetData>
-    <row r="3">
-      <c r="E3" s="24" t="s">
+    <row r="6">
+      <c r="E6" s="24" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="4">
-      <c r="F4" s="22"/>
-      <c r="G4" s="20"/>
-    </row>
-    <row r="5">
-      <c r="G5" s="21">
+    <row r="7">
+      <c r="F7" s="22"/>
+      <c r="G7" s="20"/>
+    </row>
+    <row r="8">
+      <c r="G8" s="21">
         <v>44</v>
       </c>
     </row>
-    <row r="6">
-      <c r="G6" s="20"/>
-      <c r="H6" s="22"/>
-      <c r="I6" s="20"/>
-    </row>
-    <row r="7">
-      <c r="E7" s="24" t="s">
+    <row r="9">
+      <c r="G9" s="20"/>
+      <c r="H9" s="22"/>
+      <c r="I9" s="20"/>
+    </row>
+    <row r="10">
+      <c r="E10" s="24" t="s">
         <v>106</v>
       </c>
-      <c r="F7" s="23"/>
-      <c r="G7" s="20"/>
-      <c r="I7" s="20"/>
-    </row>
-    <row r="8">
-      <c r="I8" s="20"/>
-    </row>
-    <row r="9">
-      <c r="I9" s="21">
+      <c r="F10" s="23"/>
+      <c r="G10" s="20"/>
+      <c r="I10" s="20"/>
+    </row>
+    <row r="11">
+      <c r="I11" s="20"/>
+    </row>
+    <row r="12">
+      <c r="I12" s="21">
         <v>68</v>
       </c>
     </row>
-    <row r="10">
-      <c r="I10" s="20"/>
-      <c r="J10" s="22"/>
-      <c r="K10" s="20"/>
-    </row>
-    <row r="11">
-      <c r="E11" s="24" t="s">
+    <row r="13">
+      <c r="I13" s="20"/>
+      <c r="J13" s="22"/>
+      <c r="K13" s="20"/>
+    </row>
+    <row r="14">
+      <c r="E14" s="24" t="s">
         <v>108</v>
       </c>
-      <c r="I11" s="20"/>
-      <c r="K11" s="20"/>
-    </row>
-    <row r="12">
-      <c r="F12" s="22"/>
-      <c r="G12" s="20"/>
-      <c r="I12" s="20"/>
-      <c r="K12" s="20"/>
-    </row>
-    <row r="13">
-      <c r="G13" s="21">
+      <c r="I14" s="20"/>
+      <c r="K14" s="20"/>
+    </row>
+    <row r="15">
+      <c r="F15" s="22"/>
+      <c r="G15" s="20"/>
+      <c r="I15" s="20"/>
+      <c r="K15" s="20"/>
+    </row>
+    <row r="16">
+      <c r="G16" s="21">
         <v>45</v>
       </c>
-      <c r="H13" s="23"/>
-      <c r="I13" s="20"/>
-      <c r="K13" s="20"/>
-    </row>
-    <row r="14">
-      <c r="C14" s="24" t="s">
+      <c r="H16" s="23"/>
+      <c r="I16" s="20"/>
+      <c r="K16" s="20"/>
+    </row>
+    <row r="17">
+      <c r="C17" s="24" t="s">
         <v>110</v>
       </c>
-      <c r="G14" s="20"/>
-      <c r="K14" s="20"/>
-    </row>
-    <row r="15">
-      <c r="D15" s="22"/>
-      <c r="E15" s="21">
+      <c r="G17" s="20"/>
+      <c r="K17" s="20"/>
+    </row>
+    <row r="18">
+      <c r="D18" s="22"/>
+      <c r="E18" s="21">
         <v>14</v>
       </c>
-      <c r="F15" s="23"/>
-      <c r="G15" s="20"/>
-      <c r="K15" s="20"/>
-    </row>
-    <row r="16">
-      <c r="C16" s="24" t="s">
+      <c r="F18" s="23"/>
+      <c r="G18" s="20"/>
+      <c r="K18" s="20"/>
+    </row>
+    <row r="19">
+      <c r="C19" s="24" t="s">
         <v>112</v>
       </c>
-      <c r="D16" s="23"/>
-      <c r="E16" s="20"/>
-      <c r="K16" s="20"/>
-    </row>
-    <row r="17">
-      <c r="K17" s="21">
+      <c r="D19" s="23"/>
+      <c r="E19" s="20"/>
+      <c r="K19" s="20"/>
+    </row>
+    <row r="20">
+      <c r="K20" s="21">
         <v>80</v>
       </c>
     </row>
-    <row r="18">
-      <c r="K18" s="20"/>
-    </row>
-    <row r="19">
-      <c r="E19" s="24" t="s">
+    <row r="21">
+      <c r="K21" s="20"/>
+    </row>
+    <row r="22">
+      <c r="E22" s="24" t="s">
         <v>114</v>
       </c>
-      <c r="K19" s="20"/>
-    </row>
-    <row r="20">
-      <c r="F20" s="22"/>
-      <c r="G20" s="20"/>
-      <c r="K20" s="20"/>
-    </row>
-    <row r="21">
-      <c r="G21" s="21">
+      <c r="K22" s="20"/>
+    </row>
+    <row r="23">
+      <c r="F23" s="22"/>
+      <c r="G23" s="20"/>
+      <c r="K23" s="20"/>
+    </row>
+    <row r="24">
+      <c r="G24" s="21">
         <v>46</v>
       </c>
-      <c r="K21" s="20"/>
-    </row>
-    <row r="22">
-      <c r="C22" s="24" t="s">
+      <c r="K24" s="20"/>
+    </row>
+    <row r="25">
+      <c r="C25" s="24" t="s">
         <v>117</v>
       </c>
-      <c r="G22" s="20"/>
-      <c r="H22" s="22"/>
-      <c r="I22" s="20"/>
-      <c r="K22" s="20"/>
-    </row>
-    <row r="23">
-      <c r="D23" s="22"/>
-      <c r="E23" s="21">
+      <c r="G25" s="20"/>
+      <c r="H25" s="22"/>
+      <c r="I25" s="20"/>
+      <c r="K25" s="20"/>
+    </row>
+    <row r="26">
+      <c r="D26" s="22"/>
+      <c r="E26" s="21">
         <v>15</v>
       </c>
-      <c r="F23" s="23"/>
-      <c r="G23" s="20"/>
-      <c r="I23" s="20"/>
-      <c r="K23" s="20"/>
-    </row>
-    <row r="24">
-      <c r="C24" s="24" t="s">
+      <c r="F26" s="23"/>
+      <c r="G26" s="20"/>
+      <c r="I26" s="20"/>
+      <c r="K26" s="20"/>
+    </row>
+    <row r="27">
+      <c r="C27" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="D24" s="23"/>
-      <c r="E24" s="20"/>
-      <c r="I24" s="20"/>
-      <c r="K24" s="20"/>
-    </row>
-    <row r="25">
-      <c r="I25" s="21">
+      <c r="D27" s="23"/>
+      <c r="E27" s="20"/>
+      <c r="I27" s="20"/>
+      <c r="K27" s="20"/>
+    </row>
+    <row r="28">
+      <c r="I28" s="21">
         <v>69</v>
       </c>
-      <c r="J25" s="23"/>
-      <c r="K25" s="20"/>
-    </row>
-    <row r="26">
-      <c r="I26" s="20"/>
-    </row>
-    <row r="27">
-      <c r="E27" s="24" t="s">
+      <c r="J28" s="23"/>
+      <c r="K28" s="20"/>
+    </row>
+    <row r="29">
+      <c r="I29" s="20"/>
+    </row>
+    <row r="30">
+      <c r="E30" s="24" t="s">
         <v>123</v>
       </c>
-      <c r="I27" s="20"/>
-    </row>
-    <row r="28">
-      <c r="F28" s="22"/>
-      <c r="G28" s="20"/>
-      <c r="I28" s="20"/>
-    </row>
-    <row r="29">
-      <c r="G29" s="21">
+      <c r="I30" s="20"/>
+    </row>
+    <row r="31">
+      <c r="F31" s="22"/>
+      <c r="G31" s="20"/>
+      <c r="I31" s="20"/>
+    </row>
+    <row r="32">
+      <c r="G32" s="21">
         <v>47</v>
       </c>
-      <c r="H29" s="23"/>
-      <c r="I29" s="20"/>
-    </row>
-    <row r="30">
-      <c r="C30" s="24" t="s">
+      <c r="H32" s="23"/>
+      <c r="I32" s="20"/>
+    </row>
+    <row r="33">
+      <c r="C33" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="G30" s="20"/>
-    </row>
-    <row r="31">
-      <c r="D31" s="22"/>
-      <c r="E31" s="21">
+      <c r="G33" s="20"/>
+    </row>
+    <row r="34">
+      <c r="D34" s="22"/>
+      <c r="E34" s="21">
         <v>16</v>
       </c>
-      <c r="F31" s="23"/>
-      <c r="G31" s="20"/>
-    </row>
-    <row r="32">
-      <c r="C32" s="24" t="s">
+      <c r="F34" s="23"/>
+      <c r="G34" s="20"/>
+    </row>
+    <row r="35">
+      <c r="C35" s="24" t="s">
         <v>129</v>
       </c>
-      <c r="D32" s="23"/>
-      <c r="E32" s="20"/>
+      <c r="D35" s="23"/>
+      <c r="E35" s="20"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="true" verticalCentered="true"/>
@@ -4752,201 +4762,201 @@
     <col customWidth="true" max="2" min="2" width="10"/>
   </cols>
   <sheetData>
-    <row r="3">
-      <c r="E3" s="24" t="s">
+    <row r="6">
+      <c r="E6" s="24" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="4">
-      <c r="F4" s="22"/>
-      <c r="G4" s="20"/>
-    </row>
-    <row r="5">
-      <c r="G5" s="21">
+    <row r="7">
+      <c r="F7" s="22"/>
+      <c r="G7" s="20"/>
+    </row>
+    <row r="8">
+      <c r="G8" s="21">
         <v>48</v>
       </c>
     </row>
-    <row r="6">
-      <c r="C6" s="24" t="s">
+    <row r="9">
+      <c r="C9" s="24" t="s">
         <v>135</v>
       </c>
-      <c r="G6" s="20"/>
-      <c r="H6" s="22"/>
-      <c r="I6" s="20"/>
-    </row>
-    <row r="7">
-      <c r="D7" s="22"/>
-      <c r="E7" s="21">
+      <c r="G9" s="20"/>
+      <c r="H9" s="22"/>
+      <c r="I9" s="20"/>
+    </row>
+    <row r="10">
+      <c r="D10" s="22"/>
+      <c r="E10" s="21">
         <v>17</v>
       </c>
-      <c r="F7" s="23"/>
-      <c r="G7" s="20"/>
-      <c r="I7" s="20"/>
-    </row>
-    <row r="8">
-      <c r="C8" s="24" t="s">
+      <c r="F10" s="23"/>
+      <c r="G10" s="20"/>
+      <c r="I10" s="20"/>
+    </row>
+    <row r="11">
+      <c r="C11" s="24" t="s">
         <v>138</v>
       </c>
-      <c r="D8" s="23"/>
-      <c r="E8" s="20"/>
-      <c r="I8" s="20"/>
-    </row>
-    <row r="9">
-      <c r="I9" s="21">
+      <c r="D11" s="23"/>
+      <c r="E11" s="20"/>
+      <c r="I11" s="20"/>
+    </row>
+    <row r="12">
+      <c r="I12" s="21">
         <v>70</v>
       </c>
     </row>
-    <row r="10">
-      <c r="I10" s="20"/>
-      <c r="J10" s="22"/>
-      <c r="K10" s="20"/>
-    </row>
-    <row r="11">
-      <c r="E11" s="24" t="s">
+    <row r="13">
+      <c r="I13" s="20"/>
+      <c r="J13" s="22"/>
+      <c r="K13" s="20"/>
+    </row>
+    <row r="14">
+      <c r="E14" s="24" t="s">
         <v>141</v>
       </c>
-      <c r="I11" s="20"/>
-      <c r="K11" s="20"/>
-    </row>
-    <row r="12">
-      <c r="F12" s="22"/>
-      <c r="G12" s="20"/>
-      <c r="I12" s="20"/>
-      <c r="K12" s="20"/>
-    </row>
-    <row r="13">
-      <c r="G13" s="21">
+      <c r="I14" s="20"/>
+      <c r="K14" s="20"/>
+    </row>
+    <row r="15">
+      <c r="F15" s="22"/>
+      <c r="G15" s="20"/>
+      <c r="I15" s="20"/>
+      <c r="K15" s="20"/>
+    </row>
+    <row r="16">
+      <c r="G16" s="21">
         <v>49</v>
       </c>
-      <c r="H13" s="23"/>
-      <c r="I13" s="20"/>
-      <c r="K13" s="20"/>
-    </row>
-    <row r="14">
-      <c r="C14" s="24" t="s">
+      <c r="H16" s="23"/>
+      <c r="I16" s="20"/>
+      <c r="K16" s="20"/>
+    </row>
+    <row r="17">
+      <c r="C17" s="24" t="s">
         <v>144</v>
       </c>
-      <c r="G14" s="20"/>
-      <c r="K14" s="20"/>
-    </row>
-    <row r="15">
-      <c r="D15" s="22"/>
-      <c r="E15" s="21">
+      <c r="G17" s="20"/>
+      <c r="K17" s="20"/>
+    </row>
+    <row r="18">
+      <c r="D18" s="22"/>
+      <c r="E18" s="21">
         <v>18</v>
       </c>
-      <c r="F15" s="23"/>
-      <c r="G15" s="20"/>
-      <c r="K15" s="20"/>
-    </row>
-    <row r="16">
-      <c r="C16" s="24" t="s">
+      <c r="F18" s="23"/>
+      <c r="G18" s="20"/>
+      <c r="K18" s="20"/>
+    </row>
+    <row r="19">
+      <c r="C19" s="24" t="s">
         <v>147</v>
       </c>
-      <c r="D16" s="23"/>
-      <c r="E16" s="20"/>
-      <c r="K16" s="20"/>
-    </row>
-    <row r="17">
-      <c r="K17" s="21">
+      <c r="D19" s="23"/>
+      <c r="E19" s="20"/>
+      <c r="K19" s="20"/>
+    </row>
+    <row r="20">
+      <c r="K20" s="21">
         <v>81</v>
       </c>
     </row>
-    <row r="18">
-      <c r="K18" s="20"/>
-    </row>
-    <row r="19">
-      <c r="E19" s="24" t="s">
+    <row r="21">
+      <c r="K21" s="20"/>
+    </row>
+    <row r="22">
+      <c r="E22" s="24" t="s">
         <v>150</v>
       </c>
-      <c r="K19" s="20"/>
-    </row>
-    <row r="20">
-      <c r="F20" s="22"/>
-      <c r="G20" s="20"/>
-      <c r="K20" s="20"/>
-    </row>
-    <row r="21">
-      <c r="G21" s="21">
+      <c r="K22" s="20"/>
+    </row>
+    <row r="23">
+      <c r="F23" s="22"/>
+      <c r="G23" s="20"/>
+      <c r="K23" s="20"/>
+    </row>
+    <row r="24">
+      <c r="G24" s="21">
         <v>50</v>
       </c>
-      <c r="K21" s="20"/>
-    </row>
-    <row r="22">
-      <c r="C22" s="24" t="s">
+      <c r="K24" s="20"/>
+    </row>
+    <row r="25">
+      <c r="C25" s="24" t="s">
         <v>153</v>
       </c>
-      <c r="G22" s="20"/>
-      <c r="H22" s="22"/>
-      <c r="I22" s="20"/>
-      <c r="K22" s="20"/>
-    </row>
-    <row r="23">
-      <c r="D23" s="22"/>
-      <c r="E23" s="21">
+      <c r="G25" s="20"/>
+      <c r="H25" s="22"/>
+      <c r="I25" s="20"/>
+      <c r="K25" s="20"/>
+    </row>
+    <row r="26">
+      <c r="D26" s="22"/>
+      <c r="E26" s="21">
         <v>19</v>
       </c>
-      <c r="F23" s="23"/>
-      <c r="G23" s="20"/>
-      <c r="I23" s="20"/>
-      <c r="K23" s="20"/>
-    </row>
-    <row r="24">
-      <c r="C24" s="24" t="s">
+      <c r="F26" s="23"/>
+      <c r="G26" s="20"/>
+      <c r="I26" s="20"/>
+      <c r="K26" s="20"/>
+    </row>
+    <row r="27">
+      <c r="C27" s="24" t="s">
         <v>156</v>
       </c>
-      <c r="D24" s="23"/>
-      <c r="E24" s="20"/>
-      <c r="I24" s="20"/>
-      <c r="K24" s="20"/>
-    </row>
-    <row r="25">
-      <c r="I25" s="21">
+      <c r="D27" s="23"/>
+      <c r="E27" s="20"/>
+      <c r="I27" s="20"/>
+      <c r="K27" s="20"/>
+    </row>
+    <row r="28">
+      <c r="I28" s="21">
         <v>71</v>
       </c>
-      <c r="J25" s="23"/>
-      <c r="K25" s="20"/>
-    </row>
-    <row r="26">
-      <c r="I26" s="20"/>
-    </row>
-    <row r="27">
-      <c r="E27" s="24" t="s">
+      <c r="J28" s="23"/>
+      <c r="K28" s="20"/>
+    </row>
+    <row r="29">
+      <c r="I29" s="20"/>
+    </row>
+    <row r="30">
+      <c r="E30" s="24" t="s">
         <v>158</v>
       </c>
-      <c r="I27" s="20"/>
-    </row>
-    <row r="28">
-      <c r="F28" s="22"/>
-      <c r="G28" s="20"/>
-      <c r="I28" s="20"/>
-    </row>
-    <row r="29">
-      <c r="G29" s="21">
+      <c r="I30" s="20"/>
+    </row>
+    <row r="31">
+      <c r="F31" s="22"/>
+      <c r="G31" s="20"/>
+      <c r="I31" s="20"/>
+    </row>
+    <row r="32">
+      <c r="G32" s="21">
         <v>51</v>
       </c>
-      <c r="H29" s="23"/>
-      <c r="I29" s="20"/>
-    </row>
-    <row r="30">
-      <c r="C30" s="24" t="s">
+      <c r="H32" s="23"/>
+      <c r="I32" s="20"/>
+    </row>
+    <row r="33">
+      <c r="C33" s="24" t="s">
         <v>160</v>
       </c>
-      <c r="G30" s="20"/>
-    </row>
-    <row r="31">
-      <c r="D31" s="22"/>
-      <c r="E31" s="21">
+      <c r="G33" s="20"/>
+    </row>
+    <row r="34">
+      <c r="D34" s="22"/>
+      <c r="E34" s="21">
         <v>20</v>
       </c>
-      <c r="F31" s="23"/>
-      <c r="G31" s="20"/>
-    </row>
-    <row r="32">
-      <c r="C32" s="24" t="s">
+      <c r="F34" s="23"/>
+      <c r="G34" s="20"/>
+    </row>
+    <row r="35">
+      <c r="C35" s="24" t="s">
         <v>162</v>
       </c>
-      <c r="D32" s="23"/>
-      <c r="E32" s="20"/>
+      <c r="D35" s="23"/>
+      <c r="E35" s="20"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="true" verticalCentered="true"/>
@@ -4966,192 +4976,192 @@
     <col customWidth="true" max="2" min="2" width="10"/>
   </cols>
   <sheetData>
-    <row r="3">
-      <c r="E3" s="24" t="s">
+    <row r="6">
+      <c r="E6" s="24" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="4">
-      <c r="F4" s="22"/>
-      <c r="G4" s="20"/>
-    </row>
-    <row r="5">
-      <c r="G5" s="21">
+    <row r="7">
+      <c r="F7" s="22"/>
+      <c r="G7" s="20"/>
+    </row>
+    <row r="8">
+      <c r="G8" s="21">
         <v>52</v>
       </c>
     </row>
-    <row r="6">
-      <c r="G6" s="20"/>
-      <c r="H6" s="22"/>
-      <c r="I6" s="20"/>
-    </row>
-    <row r="7">
-      <c r="E7" s="24" t="s">
+    <row r="9">
+      <c r="G9" s="20"/>
+      <c r="H9" s="22"/>
+      <c r="I9" s="20"/>
+    </row>
+    <row r="10">
+      <c r="E10" s="24" t="s">
         <v>166</v>
       </c>
-      <c r="F7" s="23"/>
-      <c r="G7" s="20"/>
-      <c r="I7" s="20"/>
-    </row>
-    <row r="8">
-      <c r="I8" s="20"/>
-    </row>
-    <row r="9">
-      <c r="I9" s="21">
+      <c r="F10" s="23"/>
+      <c r="G10" s="20"/>
+      <c r="I10" s="20"/>
+    </row>
+    <row r="11">
+      <c r="I11" s="20"/>
+    </row>
+    <row r="12">
+      <c r="I12" s="21">
         <v>72</v>
       </c>
     </row>
-    <row r="10">
-      <c r="I10" s="20"/>
-      <c r="J10" s="22"/>
-      <c r="K10" s="20"/>
-    </row>
-    <row r="11">
-      <c r="E11" s="24" t="s">
+    <row r="13">
+      <c r="I13" s="20"/>
+      <c r="J13" s="22"/>
+      <c r="K13" s="20"/>
+    </row>
+    <row r="14">
+      <c r="E14" s="24" t="s">
         <v>168</v>
       </c>
-      <c r="I11" s="20"/>
-      <c r="K11" s="20"/>
-    </row>
-    <row r="12">
-      <c r="F12" s="22"/>
-      <c r="G12" s="20"/>
-      <c r="I12" s="20"/>
-      <c r="K12" s="20"/>
-    </row>
-    <row r="13">
-      <c r="G13" s="21">
+      <c r="I14" s="20"/>
+      <c r="K14" s="20"/>
+    </row>
+    <row r="15">
+      <c r="F15" s="22"/>
+      <c r="G15" s="20"/>
+      <c r="I15" s="20"/>
+      <c r="K15" s="20"/>
+    </row>
+    <row r="16">
+      <c r="G16" s="21">
         <v>53</v>
       </c>
-      <c r="H13" s="23"/>
-      <c r="I13" s="20"/>
-      <c r="K13" s="20"/>
-    </row>
-    <row r="14">
-      <c r="C14" s="24" t="s">
+      <c r="H16" s="23"/>
+      <c r="I16" s="20"/>
+      <c r="K16" s="20"/>
+    </row>
+    <row r="17">
+      <c r="C17" s="24" t="s">
         <v>162</v>
       </c>
-      <c r="G14" s="20"/>
-      <c r="K14" s="20"/>
-    </row>
-    <row r="15">
-      <c r="D15" s="22"/>
-      <c r="E15" s="21">
+      <c r="G17" s="20"/>
+      <c r="K17" s="20"/>
+    </row>
+    <row r="18">
+      <c r="D18" s="22"/>
+      <c r="E18" s="21">
         <v>21</v>
       </c>
-      <c r="F15" s="23"/>
-      <c r="G15" s="20"/>
-      <c r="K15" s="20"/>
-    </row>
-    <row r="16">
-      <c r="C16" s="24" t="s">
+      <c r="F18" s="23"/>
+      <c r="G18" s="20"/>
+      <c r="K18" s="20"/>
+    </row>
+    <row r="19">
+      <c r="C19" s="24" t="s">
         <v>171</v>
       </c>
-      <c r="D16" s="23"/>
-      <c r="E16" s="20"/>
-      <c r="K16" s="20"/>
-    </row>
-    <row r="17">
-      <c r="K17" s="21">
+      <c r="D19" s="23"/>
+      <c r="E19" s="20"/>
+      <c r="K19" s="20"/>
+    </row>
+    <row r="20">
+      <c r="K20" s="21">
         <v>82</v>
       </c>
     </row>
-    <row r="18">
-      <c r="K18" s="20"/>
-    </row>
-    <row r="19">
-      <c r="E19" s="24" t="s">
+    <row r="21">
+      <c r="K21" s="20"/>
+    </row>
+    <row r="22">
+      <c r="E22" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="K19" s="20"/>
-    </row>
-    <row r="20">
-      <c r="F20" s="22"/>
-      <c r="G20" s="20"/>
-      <c r="K20" s="20"/>
-    </row>
-    <row r="21">
-      <c r="G21" s="21">
+      <c r="K22" s="20"/>
+    </row>
+    <row r="23">
+      <c r="F23" s="22"/>
+      <c r="G23" s="20"/>
+      <c r="K23" s="20"/>
+    </row>
+    <row r="24">
+      <c r="G24" s="21">
         <v>54</v>
       </c>
-      <c r="K21" s="20"/>
-    </row>
-    <row r="22">
-      <c r="C22" s="24" t="s">
+      <c r="K24" s="20"/>
+    </row>
+    <row r="25">
+      <c r="C25" s="24" t="s">
         <v>175</v>
       </c>
-      <c r="G22" s="20"/>
-      <c r="H22" s="22"/>
-      <c r="I22" s="20"/>
-      <c r="K22" s="20"/>
-    </row>
-    <row r="23">
-      <c r="D23" s="22"/>
-      <c r="E23" s="21">
+      <c r="G25" s="20"/>
+      <c r="H25" s="22"/>
+      <c r="I25" s="20"/>
+      <c r="K25" s="20"/>
+    </row>
+    <row r="26">
+      <c r="D26" s="22"/>
+      <c r="E26" s="21">
         <v>22</v>
       </c>
-      <c r="F23" s="23"/>
-      <c r="G23" s="20"/>
-      <c r="I23" s="20"/>
-      <c r="K23" s="20"/>
-    </row>
-    <row r="24">
-      <c r="C24" s="24" t="s">
+      <c r="F26" s="23"/>
+      <c r="G26" s="20"/>
+      <c r="I26" s="20"/>
+      <c r="K26" s="20"/>
+    </row>
+    <row r="27">
+      <c r="C27" s="24" t="s">
         <v>177</v>
       </c>
-      <c r="D24" s="23"/>
-      <c r="E24" s="20"/>
-      <c r="I24" s="20"/>
-      <c r="K24" s="20"/>
-    </row>
-    <row r="25">
-      <c r="I25" s="21">
+      <c r="D27" s="23"/>
+      <c r="E27" s="20"/>
+      <c r="I27" s="20"/>
+      <c r="K27" s="20"/>
+    </row>
+    <row r="28">
+      <c r="I28" s="21">
         <v>73</v>
       </c>
-      <c r="J25" s="23"/>
-      <c r="K25" s="20"/>
-    </row>
-    <row r="26">
-      <c r="I26" s="20"/>
-    </row>
-    <row r="27">
-      <c r="E27" s="24" t="s">
+      <c r="J28" s="23"/>
+      <c r="K28" s="20"/>
+    </row>
+    <row r="29">
+      <c r="I29" s="20"/>
+    </row>
+    <row r="30">
+      <c r="E30" s="24" t="s">
         <v>179</v>
       </c>
-      <c r="I27" s="20"/>
-    </row>
-    <row r="28">
-      <c r="F28" s="22"/>
-      <c r="G28" s="20"/>
-      <c r="I28" s="20"/>
-    </row>
-    <row r="29">
-      <c r="G29" s="21">
+      <c r="I30" s="20"/>
+    </row>
+    <row r="31">
+      <c r="F31" s="22"/>
+      <c r="G31" s="20"/>
+      <c r="I31" s="20"/>
+    </row>
+    <row r="32">
+      <c r="G32" s="21">
         <v>55</v>
       </c>
-      <c r="H29" s="23"/>
-      <c r="I29" s="20"/>
-    </row>
-    <row r="30">
-      <c r="C30" s="24" t="s">
+      <c r="H32" s="23"/>
+      <c r="I32" s="20"/>
+    </row>
+    <row r="33">
+      <c r="C33" s="24" t="s">
         <v>181</v>
       </c>
-      <c r="G30" s="20"/>
-    </row>
-    <row r="31">
-      <c r="D31" s="22"/>
-      <c r="E31" s="21">
+      <c r="G33" s="20"/>
+    </row>
+    <row r="34">
+      <c r="D34" s="22"/>
+      <c r="E34" s="21">
         <v>23</v>
       </c>
-      <c r="F31" s="23"/>
-      <c r="G31" s="20"/>
-    </row>
-    <row r="32">
-      <c r="C32" s="24" t="s">
+      <c r="F34" s="23"/>
+      <c r="G34" s="20"/>
+    </row>
+    <row r="35">
+      <c r="C35" s="24" t="s">
         <v>132</v>
       </c>
-      <c r="D32" s="23"/>
-      <c r="E32" s="20"/>
+      <c r="D35" s="23"/>
+      <c r="E35" s="20"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="true" verticalCentered="true"/>
@@ -5171,201 +5181,201 @@
     <col customWidth="true" max="2" min="2" width="10"/>
   </cols>
   <sheetData>
-    <row r="3">
-      <c r="E3" s="24" t="s">
+    <row r="6">
+      <c r="E6" s="24" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="4">
-      <c r="F4" s="22"/>
-      <c r="G4" s="20"/>
-    </row>
-    <row r="5">
-      <c r="G5" s="21">
+    <row r="7">
+      <c r="F7" s="22"/>
+      <c r="G7" s="20"/>
+    </row>
+    <row r="8">
+      <c r="G8" s="21">
         <v>56</v>
       </c>
     </row>
-    <row r="6">
-      <c r="C6" s="24" t="s">
+    <row r="9">
+      <c r="C9" s="24" t="s">
         <v>186</v>
       </c>
-      <c r="G6" s="20"/>
-      <c r="H6" s="22"/>
-      <c r="I6" s="20"/>
-    </row>
-    <row r="7">
-      <c r="D7" s="22"/>
-      <c r="E7" s="21">
+      <c r="G9" s="20"/>
+      <c r="H9" s="22"/>
+      <c r="I9" s="20"/>
+    </row>
+    <row r="10">
+      <c r="D10" s="22"/>
+      <c r="E10" s="21">
         <v>24</v>
       </c>
-      <c r="F7" s="23"/>
-      <c r="G7" s="20"/>
-      <c r="I7" s="20"/>
-    </row>
-    <row r="8">
-      <c r="C8" s="24" t="s">
+      <c r="F10" s="23"/>
+      <c r="G10" s="20"/>
+      <c r="I10" s="20"/>
+    </row>
+    <row r="11">
+      <c r="C11" s="24" t="s">
         <v>188</v>
       </c>
-      <c r="D8" s="23"/>
-      <c r="E8" s="20"/>
-      <c r="I8" s="20"/>
-    </row>
-    <row r="9">
-      <c r="I9" s="21">
+      <c r="D11" s="23"/>
+      <c r="E11" s="20"/>
+      <c r="I11" s="20"/>
+    </row>
+    <row r="12">
+      <c r="I12" s="21">
         <v>74</v>
       </c>
     </row>
-    <row r="10">
-      <c r="I10" s="20"/>
-      <c r="J10" s="22"/>
-      <c r="K10" s="20"/>
-    </row>
-    <row r="11">
-      <c r="E11" s="24" t="s">
+    <row r="13">
+      <c r="I13" s="20"/>
+      <c r="J13" s="22"/>
+      <c r="K13" s="20"/>
+    </row>
+    <row r="14">
+      <c r="E14" s="24" t="s">
         <v>190</v>
       </c>
-      <c r="I11" s="20"/>
-      <c r="K11" s="20"/>
-    </row>
-    <row r="12">
-      <c r="F12" s="22"/>
-      <c r="G12" s="20"/>
-      <c r="I12" s="20"/>
-      <c r="K12" s="20"/>
-    </row>
-    <row r="13">
-      <c r="G13" s="21">
+      <c r="I14" s="20"/>
+      <c r="K14" s="20"/>
+    </row>
+    <row r="15">
+      <c r="F15" s="22"/>
+      <c r="G15" s="20"/>
+      <c r="I15" s="20"/>
+      <c r="K15" s="20"/>
+    </row>
+    <row r="16">
+      <c r="G16" s="21">
         <v>57</v>
       </c>
-      <c r="H13" s="23"/>
-      <c r="I13" s="20"/>
-      <c r="K13" s="20"/>
-    </row>
-    <row r="14">
-      <c r="C14" s="24" t="s">
+      <c r="H16" s="23"/>
+      <c r="I16" s="20"/>
+      <c r="K16" s="20"/>
+    </row>
+    <row r="17">
+      <c r="C17" s="24" t="s">
         <v>192</v>
       </c>
-      <c r="G14" s="20"/>
-      <c r="K14" s="20"/>
-    </row>
-    <row r="15">
-      <c r="D15" s="22"/>
-      <c r="E15" s="21">
+      <c r="G17" s="20"/>
+      <c r="K17" s="20"/>
+    </row>
+    <row r="18">
+      <c r="D18" s="22"/>
+      <c r="E18" s="21">
         <v>25</v>
       </c>
-      <c r="F15" s="23"/>
-      <c r="G15" s="20"/>
-      <c r="K15" s="20"/>
-    </row>
-    <row r="16">
-      <c r="C16" s="24" t="s">
+      <c r="F18" s="23"/>
+      <c r="G18" s="20"/>
+      <c r="K18" s="20"/>
+    </row>
+    <row r="19">
+      <c r="C19" s="24" t="s">
         <v>194</v>
       </c>
-      <c r="D16" s="23"/>
-      <c r="E16" s="20"/>
-      <c r="K16" s="20"/>
-    </row>
-    <row r="17">
-      <c r="K17" s="21">
+      <c r="D19" s="23"/>
+      <c r="E19" s="20"/>
+      <c r="K19" s="20"/>
+    </row>
+    <row r="20">
+      <c r="K20" s="21">
         <v>83</v>
       </c>
     </row>
-    <row r="18">
-      <c r="K18" s="20"/>
-    </row>
-    <row r="19">
-      <c r="E19" s="24" t="s">
+    <row r="21">
+      <c r="K21" s="20"/>
+    </row>
+    <row r="22">
+      <c r="E22" s="24" t="s">
         <v>164</v>
       </c>
-      <c r="K19" s="20"/>
-    </row>
-    <row r="20">
-      <c r="F20" s="22"/>
-      <c r="G20" s="20"/>
-      <c r="K20" s="20"/>
-    </row>
-    <row r="21">
-      <c r="G21" s="21">
+      <c r="K22" s="20"/>
+    </row>
+    <row r="23">
+      <c r="F23" s="22"/>
+      <c r="G23" s="20"/>
+      <c r="K23" s="20"/>
+    </row>
+    <row r="24">
+      <c r="G24" s="21">
         <v>58</v>
       </c>
-      <c r="K21" s="20"/>
-    </row>
-    <row r="22">
-      <c r="C22" s="24" t="s">
+      <c r="K24" s="20"/>
+    </row>
+    <row r="25">
+      <c r="C25" s="24" t="s">
         <v>197</v>
       </c>
-      <c r="G22" s="20"/>
-      <c r="H22" s="22"/>
-      <c r="I22" s="20"/>
-      <c r="K22" s="20"/>
-    </row>
-    <row r="23">
-      <c r="D23" s="22"/>
-      <c r="E23" s="21">
+      <c r="G25" s="20"/>
+      <c r="H25" s="22"/>
+      <c r="I25" s="20"/>
+      <c r="K25" s="20"/>
+    </row>
+    <row r="26">
+      <c r="D26" s="22"/>
+      <c r="E26" s="21">
         <v>26</v>
       </c>
-      <c r="F23" s="23"/>
-      <c r="G23" s="20"/>
-      <c r="I23" s="20"/>
-      <c r="K23" s="20"/>
-    </row>
-    <row r="24">
-      <c r="C24" s="24" t="s">
+      <c r="F26" s="23"/>
+      <c r="G26" s="20"/>
+      <c r="I26" s="20"/>
+      <c r="K26" s="20"/>
+    </row>
+    <row r="27">
+      <c r="C27" s="24" t="s">
         <v>199</v>
       </c>
-      <c r="D24" s="23"/>
-      <c r="E24" s="20"/>
-      <c r="I24" s="20"/>
-      <c r="K24" s="20"/>
-    </row>
-    <row r="25">
-      <c r="I25" s="21">
+      <c r="D27" s="23"/>
+      <c r="E27" s="20"/>
+      <c r="I27" s="20"/>
+      <c r="K27" s="20"/>
+    </row>
+    <row r="28">
+      <c r="I28" s="21">
         <v>75</v>
       </c>
-      <c r="J25" s="23"/>
-      <c r="K25" s="20"/>
-    </row>
-    <row r="26">
-      <c r="I26" s="20"/>
-    </row>
-    <row r="27">
-      <c r="E27" s="24" t="s">
+      <c r="J28" s="23"/>
+      <c r="K28" s="20"/>
+    </row>
+    <row r="29">
+      <c r="I29" s="20"/>
+    </row>
+    <row r="30">
+      <c r="E30" s="24" t="s">
         <v>201</v>
       </c>
-      <c r="I27" s="20"/>
-    </row>
-    <row r="28">
-      <c r="F28" s="22"/>
-      <c r="G28" s="20"/>
-      <c r="I28" s="20"/>
-    </row>
-    <row r="29">
-      <c r="G29" s="21">
+      <c r="I30" s="20"/>
+    </row>
+    <row r="31">
+      <c r="F31" s="22"/>
+      <c r="G31" s="20"/>
+      <c r="I31" s="20"/>
+    </row>
+    <row r="32">
+      <c r="G32" s="21">
         <v>59</v>
       </c>
-      <c r="H29" s="23"/>
-      <c r="I29" s="20"/>
-    </row>
-    <row r="30">
-      <c r="C30" s="24" t="s">
+      <c r="H32" s="23"/>
+      <c r="I32" s="20"/>
+    </row>
+    <row r="33">
+      <c r="C33" s="24" t="s">
         <v>203</v>
       </c>
-      <c r="G30" s="20"/>
-    </row>
-    <row r="31">
-      <c r="D31" s="22"/>
-      <c r="E31" s="21">
+      <c r="G33" s="20"/>
+    </row>
+    <row r="34">
+      <c r="D34" s="22"/>
+      <c r="E34" s="21">
         <v>27</v>
       </c>
-      <c r="F31" s="23"/>
-      <c r="G31" s="20"/>
-    </row>
-    <row r="32">
-      <c r="C32" s="24" t="s">
+      <c r="F34" s="23"/>
+      <c r="G34" s="20"/>
+    </row>
+    <row r="35">
+      <c r="C35" s="24" t="s">
         <v>205</v>
       </c>
-      <c r="D32" s="23"/>
-      <c r="E32" s="20"/>
+      <c r="D35" s="23"/>
+      <c r="E35" s="20"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="true" verticalCentered="true"/>
@@ -5639,46 +5649,46 @@
       <c r="O3" s="27"/>
     </row>
     <row r="4">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="D4" s="29" t="s">
+      <c r="D4" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="30" t="s">
         <v>209</v>
       </c>
-      <c r="I4" s="28" t="s">
+      <c r="I4" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="L4" s="29" t="s">
+      <c r="L4" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="O4" t="s">
+      <c r="O4" s="30" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="29" t="str">
+      <c r="A5" s="28" t="str">
         <f>'data'!$B$5</f>
       </c>
-      <c r="B5" s="29"/>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29" t="str">
+      <c r="B5" s="28"/>
+      <c r="C5" s="28"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="28" t="str">
         <f>'data'!$B$34</f>
       </c>
-      <c r="I5" s="29" t="str">
+      <c r="I5" s="28" t="str">
         <f>'data'!$B$36</f>
       </c>
-      <c r="J5" s="29"/>
-      <c r="K5" s="29"/>
-      <c r="L5" s="29"/>
-      <c r="M5" s="29"/>
-      <c r="N5" s="29"/>
-      <c r="O5" s="29" t="str">
+      <c r="J5" s="28"/>
+      <c r="K5" s="28"/>
+      <c r="L5" s="28"/>
+      <c r="M5" s="28"/>
+      <c r="N5" s="28"/>
+      <c r="O5" s="28" t="str">
         <f>'data'!$B$37</f>
       </c>
     </row>
@@ -5723,46 +5733,46 @@
       <c r="O11" s="27"/>
     </row>
     <row r="12">
-      <c r="A12" s="28" t="s">
+      <c r="A12" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="D12" s="29" t="s">
+      <c r="D12" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="G12" t="s">
+      <c r="G12" s="30" t="s">
         <v>209</v>
       </c>
-      <c r="I12" s="28" t="s">
+      <c r="I12" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="L12" s="29" t="s">
+      <c r="L12" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="O12" t="s">
+      <c r="O12" s="30" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="29" t="str">
+      <c r="A13" s="28" t="str">
         <f>'data'!$B$39</f>
       </c>
-      <c r="B13" s="29"/>
-      <c r="C13" s="29"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="29"/>
-      <c r="F13" s="29"/>
-      <c r="G13" s="29" t="str">
+      <c r="B13" s="28"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="28" t="str">
         <f>'data'!$B$40</f>
       </c>
-      <c r="I13" s="29" t="str">
+      <c r="I13" s="28" t="str">
         <f>'data'!$B$16</f>
       </c>
-      <c r="J13" s="29"/>
-      <c r="K13" s="29"/>
-      <c r="L13" s="29"/>
-      <c r="M13" s="29"/>
-      <c r="N13" s="29"/>
-      <c r="O13" s="29" t="str">
+      <c r="J13" s="28"/>
+      <c r="K13" s="28"/>
+      <c r="L13" s="28"/>
+      <c r="M13" s="28"/>
+      <c r="N13" s="28"/>
+      <c r="O13" s="28" t="str">
         <f>'data'!$B$17</f>
       </c>
     </row>
@@ -5807,46 +5817,46 @@
       <c r="O19" s="27"/>
     </row>
     <row r="20">
-      <c r="A20" s="28" t="s">
+      <c r="A20" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="D20" s="29" t="s">
+      <c r="D20" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="G20" t="s">
+      <c r="G20" s="30" t="s">
         <v>209</v>
       </c>
-      <c r="I20" s="28" t="s">
+      <c r="I20" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="L20" s="29" t="s">
+      <c r="L20" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="O20" t="s">
+      <c r="O20" s="30" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="29" t="str">
+      <c r="A21" s="28" t="str">
         <f>'data'!$B$19</f>
       </c>
-      <c r="B21" s="29"/>
-      <c r="C21" s="29"/>
-      <c r="D21" s="29"/>
-      <c r="E21" s="29"/>
-      <c r="F21" s="29"/>
-      <c r="G21" s="29" t="str">
+      <c r="B21" s="28"/>
+      <c r="C21" s="28"/>
+      <c r="D21" s="28"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="28"/>
+      <c r="G21" s="28" t="str">
         <f>'data'!$B$20</f>
       </c>
-      <c r="I21" s="29" t="str">
+      <c r="I21" s="28" t="str">
         <f>'data'!$B$22</f>
       </c>
-      <c r="J21" s="29"/>
-      <c r="K21" s="29"/>
-      <c r="L21" s="29"/>
-      <c r="M21" s="29"/>
-      <c r="N21" s="29"/>
-      <c r="O21" s="29" t="str">
+      <c r="J21" s="28"/>
+      <c r="K21" s="28"/>
+      <c r="L21" s="28"/>
+      <c r="M21" s="28"/>
+      <c r="N21" s="28"/>
+      <c r="O21" s="28" t="str">
         <f>'data'!$B$23</f>
       </c>
     </row>
@@ -5891,46 +5901,46 @@
       <c r="O27" s="27"/>
     </row>
     <row r="28">
-      <c r="A28" s="28" t="s">
+      <c r="A28" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="D28" s="29" t="s">
+      <c r="D28" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="G28" t="s">
+      <c r="G28" s="30" t="s">
         <v>209</v>
       </c>
-      <c r="I28" s="28" t="s">
+      <c r="I28" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="L28" s="29" t="s">
+      <c r="L28" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="O28" t="s">
+      <c r="O28" s="30" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="29" t="str">
+      <c r="A29" s="28" t="str">
         <f>'data'!$B$27</f>
       </c>
-      <c r="B29" s="29"/>
-      <c r="C29" s="29"/>
-      <c r="D29" s="29"/>
-      <c r="E29" s="29"/>
-      <c r="F29" s="29"/>
-      <c r="G29" s="29" t="str">
+      <c r="B29" s="28"/>
+      <c r="C29" s="28"/>
+      <c r="D29" s="28"/>
+      <c r="E29" s="28"/>
+      <c r="F29" s="28"/>
+      <c r="G29" s="28" t="str">
         <f>'data'!$B$28</f>
       </c>
-      <c r="I29" s="29" t="str">
+      <c r="I29" s="28" t="str">
         <f>'data'!$B$30</f>
       </c>
-      <c r="J29" s="29"/>
-      <c r="K29" s="29"/>
-      <c r="L29" s="29"/>
-      <c r="M29" s="29"/>
-      <c r="N29" s="29"/>
-      <c r="O29" s="29" t="str">
+      <c r="J29" s="28"/>
+      <c r="K29" s="28"/>
+      <c r="L29" s="28"/>
+      <c r="M29" s="28"/>
+      <c r="N29" s="28"/>
+      <c r="O29" s="28" t="str">
         <f>'data'!$B$31</f>
       </c>
     </row>
@@ -5975,46 +5985,46 @@
       <c r="O35" s="27"/>
     </row>
     <row r="36">
-      <c r="A36" s="28" t="s">
+      <c r="A36" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="D36" s="29" t="s">
+      <c r="D36" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="G36" t="s">
+      <c r="G36" s="30" t="s">
         <v>209</v>
       </c>
-      <c r="I36" s="28" t="s">
+      <c r="I36" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="L36" s="29" t="s">
+      <c r="L36" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="O36" t="s">
+      <c r="O36" s="30" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="29" t="str">
+      <c r="A37" s="28" t="str">
         <f>'data'!$B$33</f>
       </c>
-      <c r="B37" s="29"/>
-      <c r="C37" s="29"/>
-      <c r="D37" s="29"/>
-      <c r="E37" s="29"/>
-      <c r="F37" s="29"/>
-      <c r="G37" s="29" t="str">
+      <c r="B37" s="28"/>
+      <c r="C37" s="28"/>
+      <c r="D37" s="28"/>
+      <c r="E37" s="28"/>
+      <c r="F37" s="28"/>
+      <c r="G37" s="28" t="str">
         <f>'data'!$B$34</f>
       </c>
-      <c r="I37" s="29" t="str">
+      <c r="I37" s="28" t="str">
         <f>'data'!$B$36</f>
       </c>
-      <c r="J37" s="29"/>
-      <c r="K37" s="29"/>
-      <c r="L37" s="29"/>
-      <c r="M37" s="29"/>
-      <c r="N37" s="29"/>
-      <c r="O37" s="29" t="str">
+      <c r="J37" s="28"/>
+      <c r="K37" s="28"/>
+      <c r="L37" s="28"/>
+      <c r="M37" s="28"/>
+      <c r="N37" s="28"/>
+      <c r="O37" s="28" t="str">
         <f>'data'!$B$37</f>
       </c>
     </row>
@@ -6059,46 +6069,46 @@
       <c r="O43" s="27"/>
     </row>
     <row r="44">
-      <c r="A44" s="28" t="s">
+      <c r="A44" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="D44" s="29" t="s">
+      <c r="D44" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="G44" t="s">
+      <c r="G44" s="30" t="s">
         <v>209</v>
       </c>
-      <c r="I44" s="28" t="s">
+      <c r="I44" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="L44" s="29" t="s">
+      <c r="L44" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="O44" t="s">
+      <c r="O44" s="30" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="29" t="str">
+      <c r="A45" s="28" t="str">
         <f>'data'!$B$39</f>
       </c>
-      <c r="B45" s="29"/>
-      <c r="C45" s="29"/>
-      <c r="D45" s="29"/>
-      <c r="E45" s="29"/>
-      <c r="F45" s="29"/>
-      <c r="G45" s="29" t="str">
+      <c r="B45" s="28"/>
+      <c r="C45" s="28"/>
+      <c r="D45" s="28"/>
+      <c r="E45" s="28"/>
+      <c r="F45" s="28"/>
+      <c r="G45" s="28" t="str">
         <f>'data'!$B$40</f>
       </c>
-      <c r="I45" s="29" t="str">
+      <c r="I45" s="28" t="str">
         <f>'data'!$B$42</f>
       </c>
-      <c r="J45" s="29"/>
-      <c r="K45" s="29"/>
-      <c r="L45" s="29"/>
-      <c r="M45" s="29"/>
-      <c r="N45" s="29"/>
-      <c r="O45" s="29" t="str">
+      <c r="J45" s="28"/>
+      <c r="K45" s="28"/>
+      <c r="L45" s="28"/>
+      <c r="M45" s="28"/>
+      <c r="N45" s="28"/>
+      <c r="O45" s="28" t="str">
         <f>'data'!$B$43</f>
       </c>
     </row>
@@ -6143,46 +6153,46 @@
       <c r="O51" s="27"/>
     </row>
     <row r="52">
-      <c r="A52" s="28" t="s">
+      <c r="A52" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="D52" s="29" t="s">
+      <c r="D52" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="G52" t="s">
+      <c r="G52" s="30" t="s">
         <v>209</v>
       </c>
-      <c r="I52" s="28" t="s">
+      <c r="I52" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="L52" s="29" t="s">
+      <c r="L52" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="O52" t="s">
+      <c r="O52" s="30" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="29" t="str">
+      <c r="A53" s="28" t="str">
         <f>'data'!$B$45</f>
       </c>
-      <c r="B53" s="29"/>
-      <c r="C53" s="29"/>
-      <c r="D53" s="29"/>
-      <c r="E53" s="29"/>
-      <c r="F53" s="29"/>
-      <c r="G53" s="29" t="str">
+      <c r="B53" s="28"/>
+      <c r="C53" s="28"/>
+      <c r="D53" s="28"/>
+      <c r="E53" s="28"/>
+      <c r="F53" s="28"/>
+      <c r="G53" s="28" t="str">
         <f>'data'!$B$46</f>
       </c>
-      <c r="I53" s="29" t="str">
+      <c r="I53" s="28" t="str">
         <f>'data'!$B$50</f>
       </c>
-      <c r="J53" s="29"/>
-      <c r="K53" s="29"/>
-      <c r="L53" s="29"/>
-      <c r="M53" s="29"/>
-      <c r="N53" s="29"/>
-      <c r="O53" s="29" t="str">
+      <c r="J53" s="28"/>
+      <c r="K53" s="28"/>
+      <c r="L53" s="28"/>
+      <c r="M53" s="28"/>
+      <c r="N53" s="28"/>
+      <c r="O53" s="28" t="str">
         <f>'data'!$B$51</f>
       </c>
     </row>
@@ -6227,46 +6237,46 @@
       <c r="O59" s="27"/>
     </row>
     <row r="60">
-      <c r="A60" s="28" t="s">
+      <c r="A60" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="D60" s="29" t="s">
+      <c r="D60" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="G60" t="s">
+      <c r="G60" s="30" t="s">
         <v>209</v>
       </c>
-      <c r="I60" s="28" t="s">
+      <c r="I60" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="L60" s="29" t="s">
+      <c r="L60" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="O60" t="s">
+      <c r="O60" s="30" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="29" t="str">
+      <c r="A61" s="28" t="str">
         <f>'data'!$B$53</f>
       </c>
-      <c r="B61" s="29"/>
-      <c r="C61" s="29"/>
-      <c r="D61" s="29"/>
-      <c r="E61" s="29"/>
-      <c r="F61" s="29"/>
-      <c r="G61" s="29" t="str">
+      <c r="B61" s="28"/>
+      <c r="C61" s="28"/>
+      <c r="D61" s="28"/>
+      <c r="E61" s="28"/>
+      <c r="F61" s="28"/>
+      <c r="G61" s="28" t="str">
         <f>'data'!$B$54</f>
       </c>
-      <c r="I61" s="29" t="str">
+      <c r="I61" s="28" t="str">
         <f>'data'!$B$56</f>
       </c>
-      <c r="J61" s="29"/>
-      <c r="K61" s="29"/>
-      <c r="L61" s="29"/>
-      <c r="M61" s="29"/>
-      <c r="N61" s="29"/>
-      <c r="O61" s="29" t="str">
+      <c r="J61" s="28"/>
+      <c r="K61" s="28"/>
+      <c r="L61" s="28"/>
+      <c r="M61" s="28"/>
+      <c r="N61" s="28"/>
+      <c r="O61" s="28" t="str">
         <f>'data'!$B$57</f>
       </c>
     </row>
@@ -6311,46 +6321,46 @@
       <c r="O67" s="27"/>
     </row>
     <row r="68">
-      <c r="A68" s="28" t="s">
+      <c r="A68" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="D68" s="29" t="s">
+      <c r="D68" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="G68" t="s">
+      <c r="G68" s="30" t="s">
         <v>209</v>
       </c>
-      <c r="I68" s="28" t="s">
+      <c r="I68" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="L68" s="29" t="s">
+      <c r="L68" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="O68" t="s">
+      <c r="O68" s="30" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="29" t="str">
+      <c r="A69" s="28" t="str">
         <f>'data'!$B$59</f>
       </c>
-      <c r="B69" s="29"/>
-      <c r="C69" s="29"/>
-      <c r="D69" s="29"/>
-      <c r="E69" s="29"/>
-      <c r="F69" s="29"/>
-      <c r="G69" s="29" t="str">
+      <c r="B69" s="28"/>
+      <c r="C69" s="28"/>
+      <c r="D69" s="28"/>
+      <c r="E69" s="28"/>
+      <c r="F69" s="28"/>
+      <c r="G69" s="28" t="str">
         <f>'data'!$B$60</f>
       </c>
-      <c r="I69" s="29" t="str">
+      <c r="I69" s="28" t="str">
         <f>'data'!$B$62</f>
       </c>
-      <c r="J69" s="29"/>
-      <c r="K69" s="29"/>
-      <c r="L69" s="29"/>
-      <c r="M69" s="29"/>
-      <c r="N69" s="29"/>
-      <c r="O69" s="29" t="str">
+      <c r="J69" s="28"/>
+      <c r="K69" s="28"/>
+      <c r="L69" s="28"/>
+      <c r="M69" s="28"/>
+      <c r="N69" s="28"/>
+      <c r="O69" s="28" t="str">
         <f>'data'!$B$63</f>
       </c>
     </row>
@@ -6395,46 +6405,46 @@
       <c r="O75" s="27"/>
     </row>
     <row r="76">
-      <c r="A76" s="28" t="s">
+      <c r="A76" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="D76" s="29" t="s">
+      <c r="D76" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="G76" t="s">
+      <c r="G76" s="30" t="s">
         <v>209</v>
       </c>
-      <c r="I76" s="28" t="s">
+      <c r="I76" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="L76" s="29" t="s">
+      <c r="L76" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="O76" t="s">
+      <c r="O76" s="30" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="29" t="str">
+      <c r="A77" s="28" t="str">
         <f>'data'!$B$65</f>
       </c>
-      <c r="B77" s="29"/>
-      <c r="C77" s="29"/>
-      <c r="D77" s="29"/>
-      <c r="E77" s="29"/>
-      <c r="F77" s="29"/>
-      <c r="G77" s="29" t="str">
+      <c r="B77" s="28"/>
+      <c r="C77" s="28"/>
+      <c r="D77" s="28"/>
+      <c r="E77" s="28"/>
+      <c r="F77" s="28"/>
+      <c r="G77" s="28" t="str">
         <f>'data'!$B$66</f>
       </c>
-      <c r="I77" s="29" t="str">
+      <c r="I77" s="28" t="str">
         <f>'data'!$B$68</f>
       </c>
-      <c r="J77" s="29"/>
-      <c r="K77" s="29"/>
-      <c r="L77" s="29"/>
-      <c r="M77" s="29"/>
-      <c r="N77" s="29"/>
-      <c r="O77" s="29" t="str">
+      <c r="J77" s="28"/>
+      <c r="K77" s="28"/>
+      <c r="L77" s="28"/>
+      <c r="M77" s="28"/>
+      <c r="N77" s="28"/>
+      <c r="O77" s="28" t="str">
         <f>'data'!$B$73</f>
       </c>
     </row>
@@ -6479,46 +6489,46 @@
       <c r="O83" s="27"/>
     </row>
     <row r="84">
-      <c r="A84" s="28" t="s">
+      <c r="A84" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="D84" s="29" t="s">
+      <c r="D84" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="G84" t="s">
+      <c r="G84" s="30" t="s">
         <v>209</v>
       </c>
-      <c r="I84" s="28" t="s">
+      <c r="I84" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="L84" s="29" t="s">
+      <c r="L84" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="O84" t="s">
+      <c r="O84" s="30" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="29" t="str">
+      <c r="A85" s="28" t="str">
         <f>'data'!$B$73</f>
       </c>
-      <c r="B85" s="29"/>
-      <c r="C85" s="29"/>
-      <c r="D85" s="29"/>
-      <c r="E85" s="29"/>
-      <c r="F85" s="29"/>
-      <c r="G85" s="29" t="str">
+      <c r="B85" s="28"/>
+      <c r="C85" s="28"/>
+      <c r="D85" s="28"/>
+      <c r="E85" s="28"/>
+      <c r="F85" s="28"/>
+      <c r="G85" s="28" t="str">
         <f>'data'!$B$74</f>
       </c>
-      <c r="I85" s="29" t="str">
+      <c r="I85" s="28" t="str">
         <f>'data'!$B$76</f>
       </c>
-      <c r="J85" s="29"/>
-      <c r="K85" s="29"/>
-      <c r="L85" s="29"/>
-      <c r="M85" s="29"/>
-      <c r="N85" s="29"/>
-      <c r="O85" s="29" t="str">
+      <c r="J85" s="28"/>
+      <c r="K85" s="28"/>
+      <c r="L85" s="28"/>
+      <c r="M85" s="28"/>
+      <c r="N85" s="28"/>
+      <c r="O85" s="28" t="str">
         <f>'data'!$B$77</f>
       </c>
     </row>
@@ -6563,46 +6573,46 @@
       <c r="O91" s="27"/>
     </row>
     <row r="92">
-      <c r="A92" s="28" t="s">
+      <c r="A92" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="D92" s="29" t="s">
+      <c r="D92" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="G92" t="s">
+      <c r="G92" s="30" t="s">
         <v>209</v>
       </c>
-      <c r="I92" s="28" t="s">
+      <c r="I92" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="L92" s="29" t="s">
+      <c r="L92" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="O92" t="s">
+      <c r="O92" s="30" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="29" t="str">
+      <c r="A93" s="28" t="str">
         <f>'data'!$B$79</f>
       </c>
-      <c r="B93" s="29"/>
-      <c r="C93" s="29"/>
-      <c r="D93" s="29"/>
-      <c r="E93" s="29"/>
-      <c r="F93" s="29"/>
-      <c r="G93" s="29" t="str">
+      <c r="B93" s="28"/>
+      <c r="C93" s="28"/>
+      <c r="D93" s="28"/>
+      <c r="E93" s="28"/>
+      <c r="F93" s="28"/>
+      <c r="G93" s="28" t="str">
         <f>'data'!$B$80</f>
       </c>
-      <c r="I93" s="29" t="str">
+      <c r="I93" s="28" t="str">
         <f>'data'!$B$82</f>
       </c>
-      <c r="J93" s="29"/>
-      <c r="K93" s="29"/>
-      <c r="L93" s="29"/>
-      <c r="M93" s="29"/>
-      <c r="N93" s="29"/>
-      <c r="O93" s="29" t="str">
+      <c r="J93" s="28"/>
+      <c r="K93" s="28"/>
+      <c r="L93" s="28"/>
+      <c r="M93" s="28"/>
+      <c r="N93" s="28"/>
+      <c r="O93" s="28" t="str">
         <f>'data'!$B$83</f>
       </c>
     </row>
@@ -6647,46 +6657,46 @@
       <c r="O99" s="27"/>
     </row>
     <row r="100">
-      <c r="A100" s="28" t="s">
+      <c r="A100" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="D100" s="29" t="s">
+      <c r="D100" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="G100" t="s">
+      <c r="G100" s="30" t="s">
         <v>209</v>
       </c>
-      <c r="I100" s="28" t="s">
+      <c r="I100" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="L100" s="29" t="s">
+      <c r="L100" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="O100" t="s">
+      <c r="O100" s="30" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="29" t="str">
+      <c r="A101" s="28" t="str">
         <f>'data'!$B$85</f>
       </c>
-      <c r="B101" s="29"/>
-      <c r="C101" s="29"/>
-      <c r="D101" s="29"/>
-      <c r="E101" s="29"/>
-      <c r="F101" s="29"/>
-      <c r="G101" s="29" t="str">
+      <c r="B101" s="28"/>
+      <c r="C101" s="28"/>
+      <c r="D101" s="28"/>
+      <c r="E101" s="28"/>
+      <c r="F101" s="28"/>
+      <c r="G101" s="28" t="str">
         <f>'data'!$B$86</f>
       </c>
-      <c r="I101" s="29" t="str">
+      <c r="I101" s="28" t="str">
         <f>'data'!$B$88</f>
       </c>
-      <c r="J101" s="29"/>
-      <c r="K101" s="29"/>
-      <c r="L101" s="29"/>
-      <c r="M101" s="29"/>
-      <c r="N101" s="29"/>
-      <c r="O101" s="29" t="str">
+      <c r="J101" s="28"/>
+      <c r="K101" s="28"/>
+      <c r="L101" s="28"/>
+      <c r="M101" s="28"/>
+      <c r="N101" s="28"/>
+      <c r="O101" s="28" t="str">
         <f>'data'!$B$89</f>
       </c>
     </row>
@@ -6722,26 +6732,26 @@
       <c r="G107" s="27"/>
     </row>
     <row r="108">
-      <c r="A108" s="28" t="s">
+      <c r="A108" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="D108" s="29" t="s">
+      <c r="D108" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="G108" t="s">
+      <c r="G108" s="30" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="29" t="str">
+      <c r="A109" s="28" t="str">
         <f>'data'!$B$91</f>
       </c>
-      <c r="B109" s="29"/>
-      <c r="C109" s="29"/>
-      <c r="D109" s="29"/>
-      <c r="E109" s="29"/>
-      <c r="F109" s="29"/>
-      <c r="G109" s="29" t="str">
+      <c r="B109" s="28"/>
+      <c r="C109" s="28"/>
+      <c r="D109" s="28"/>
+      <c r="E109" s="28"/>
+      <c r="F109" s="28"/>
+      <c r="G109" s="28" t="str">
         <f>'data'!$B$92</f>
       </c>
     </row>
@@ -6797,46 +6807,46 @@
       <c r="O122" s="27"/>
     </row>
     <row r="123">
-      <c r="A123" s="28" t="s">
+      <c r="A123" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="D123" s="29" t="s">
+      <c r="D123" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="G123" t="s">
+      <c r="G123" s="30" t="s">
         <v>209</v>
       </c>
-      <c r="I123" s="28" t="s">
+      <c r="I123" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="L123" s="29" t="s">
+      <c r="L123" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="O123" t="s">
+      <c r="O123" s="30" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="29" t="str">
+      <c r="A124" s="28" t="str">
         <f>'data'!$B$31</f>
       </c>
-      <c r="B124" s="29"/>
-      <c r="C124" s="29"/>
-      <c r="D124" s="29"/>
-      <c r="E124" s="29"/>
-      <c r="F124" s="29"/>
-      <c r="G124" s="29" t="str">
+      <c r="B124" s="28"/>
+      <c r="C124" s="28"/>
+      <c r="D124" s="28"/>
+      <c r="E124" s="28"/>
+      <c r="F124" s="28"/>
+      <c r="G124" s="28" t="str">
         <f>'data'!$B$32</f>
       </c>
-      <c r="I124" s="29" t="str">
+      <c r="I124" s="28" t="str">
         <f>'data'!$B$33</f>
       </c>
-      <c r="J124" s="29"/>
-      <c r="K124" s="29"/>
-      <c r="L124" s="29"/>
-      <c r="M124" s="29"/>
-      <c r="N124" s="29"/>
-      <c r="O124" s="29" t="str">
+      <c r="J124" s="28"/>
+      <c r="K124" s="28"/>
+      <c r="L124" s="28"/>
+      <c r="M124" s="28"/>
+      <c r="N124" s="28"/>
+      <c r="O124" s="28" t="str">
         <f>CONCATENATE("M 1 ",'Elimination Matches'!G7)</f>
       </c>
     </row>
@@ -6881,46 +6891,46 @@
       <c r="O130" s="27"/>
     </row>
     <row r="131">
-      <c r="A131" s="28" t="s">
+      <c r="A131" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="D131" s="29" t="s">
+      <c r="D131" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="G131" t="s">
+      <c r="G131" s="30" t="s">
         <v>209</v>
       </c>
-      <c r="I131" s="28" t="s">
+      <c r="I131" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="L131" s="29" t="s">
+      <c r="L131" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="O131" t="s">
+      <c r="O131" s="30" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="29" t="str">
+      <c r="A132" s="28" t="str">
         <f>'data'!$B$35</f>
       </c>
-      <c r="B132" s="29"/>
-      <c r="C132" s="29"/>
-      <c r="D132" s="29"/>
-      <c r="E132" s="29"/>
-      <c r="F132" s="29"/>
-      <c r="G132" s="29" t="str">
+      <c r="B132" s="28"/>
+      <c r="C132" s="28"/>
+      <c r="D132" s="28"/>
+      <c r="E132" s="28"/>
+      <c r="F132" s="28"/>
+      <c r="G132" s="28" t="str">
         <f>CONCATENATE("M 2 ",'Elimination Matches'!O7)</f>
       </c>
-      <c r="I132" s="29" t="str">
+      <c r="I132" s="28" t="str">
         <f>'data'!$B$38</f>
       </c>
-      <c r="J132" s="29"/>
-      <c r="K132" s="29"/>
-      <c r="L132" s="29"/>
-      <c r="M132" s="29"/>
-      <c r="N132" s="29"/>
-      <c r="O132" s="29" t="str">
+      <c r="J132" s="28"/>
+      <c r="K132" s="28"/>
+      <c r="L132" s="28"/>
+      <c r="M132" s="28"/>
+      <c r="N132" s="28"/>
+      <c r="O132" s="28" t="str">
         <f>CONCATENATE("M 3 ",'Elimination Matches'!G15)</f>
       </c>
     </row>
@@ -6965,46 +6975,46 @@
       <c r="O138" s="27"/>
     </row>
     <row r="139">
-      <c r="A139" s="28" t="s">
+      <c r="A139" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="D139" s="29" t="s">
+      <c r="D139" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="G139" t="s">
+      <c r="G139" s="30" t="s">
         <v>209</v>
       </c>
-      <c r="I139" s="28" t="s">
+      <c r="I139" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="L139" s="29" t="s">
+      <c r="L139" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="O139" t="s">
+      <c r="O139" s="30" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="29" t="str">
+      <c r="A140" s="28" t="str">
         <f>'data'!$B$41</f>
       </c>
-      <c r="B140" s="29"/>
-      <c r="C140" s="29"/>
-      <c r="D140" s="29"/>
-      <c r="E140" s="29"/>
-      <c r="F140" s="29"/>
-      <c r="G140" s="29" t="str">
+      <c r="B140" s="28"/>
+      <c r="C140" s="28"/>
+      <c r="D140" s="28"/>
+      <c r="E140" s="28"/>
+      <c r="F140" s="28"/>
+      <c r="G140" s="28" t="str">
         <f>'data'!$B$42</f>
       </c>
-      <c r="I140" s="29" t="str">
+      <c r="I140" s="28" t="str">
         <f>'data'!$B$15</f>
       </c>
-      <c r="J140" s="29"/>
-      <c r="K140" s="29"/>
-      <c r="L140" s="29"/>
-      <c r="M140" s="29"/>
-      <c r="N140" s="29"/>
-      <c r="O140" s="29" t="str">
+      <c r="J140" s="28"/>
+      <c r="K140" s="28"/>
+      <c r="L140" s="28"/>
+      <c r="M140" s="28"/>
+      <c r="N140" s="28"/>
+      <c r="O140" s="28" t="str">
         <f>CONCATENATE("M 4 ",'Elimination Matches'!O15)</f>
       </c>
     </row>
@@ -7049,46 +7059,46 @@
       <c r="O146" s="27"/>
     </row>
     <row r="147">
-      <c r="A147" s="28" t="s">
+      <c r="A147" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="D147" s="29" t="s">
+      <c r="D147" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="G147" t="s">
+      <c r="G147" s="30" t="s">
         <v>209</v>
       </c>
-      <c r="I147" s="28" t="s">
+      <c r="I147" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="L147" s="29" t="s">
+      <c r="L147" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="O147" t="s">
+      <c r="O147" s="30" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="29" t="str">
+      <c r="A148" s="28" t="str">
         <f>'data'!$B$29</f>
       </c>
-      <c r="B148" s="29"/>
-      <c r="C148" s="29"/>
-      <c r="D148" s="29"/>
-      <c r="E148" s="29"/>
-      <c r="F148" s="29"/>
-      <c r="G148" s="29" t="str">
+      <c r="B148" s="28"/>
+      <c r="C148" s="28"/>
+      <c r="D148" s="28"/>
+      <c r="E148" s="28"/>
+      <c r="F148" s="28"/>
+      <c r="G148" s="28" t="str">
         <f>CONCATENATE("M 5 ",'Elimination Matches'!G23)</f>
       </c>
-      <c r="I148" s="29" t="str">
+      <c r="I148" s="28" t="str">
         <f>'data'!$B$21</f>
       </c>
-      <c r="J148" s="29"/>
-      <c r="K148" s="29"/>
-      <c r="L148" s="29"/>
-      <c r="M148" s="29"/>
-      <c r="N148" s="29"/>
-      <c r="O148" s="29" t="str">
+      <c r="J148" s="28"/>
+      <c r="K148" s="28"/>
+      <c r="L148" s="28"/>
+      <c r="M148" s="28"/>
+      <c r="N148" s="28"/>
+      <c r="O148" s="28" t="str">
         <f>CONCATENATE("M 6 ",'Elimination Matches'!O23)</f>
       </c>
     </row>
@@ -7133,46 +7143,46 @@
       <c r="O154" s="27"/>
     </row>
     <row r="155">
-      <c r="A155" s="28" t="s">
+      <c r="A155" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="D155" s="29" t="s">
+      <c r="D155" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="G155" t="s">
+      <c r="G155" s="30" t="s">
         <v>209</v>
       </c>
-      <c r="I155" s="28" t="s">
+      <c r="I155" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="L155" s="29" t="s">
+      <c r="L155" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="O155" t="s">
+      <c r="O155" s="30" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="29" t="str">
+      <c r="A156" s="28" t="str">
         <f>'data'!$B$24</f>
       </c>
-      <c r="B156" s="29"/>
-      <c r="C156" s="29"/>
-      <c r="D156" s="29"/>
-      <c r="E156" s="29"/>
-      <c r="F156" s="29"/>
-      <c r="G156" s="29" t="str">
+      <c r="B156" s="28"/>
+      <c r="C156" s="28"/>
+      <c r="D156" s="28"/>
+      <c r="E156" s="28"/>
+      <c r="F156" s="28"/>
+      <c r="G156" s="28" t="str">
         <f>'data'!$B$25</f>
       </c>
-      <c r="I156" s="29" t="str">
+      <c r="I156" s="28" t="str">
         <f>'data'!$B$26</f>
       </c>
-      <c r="J156" s="29"/>
-      <c r="K156" s="29"/>
-      <c r="L156" s="29"/>
-      <c r="M156" s="29"/>
-      <c r="N156" s="29"/>
-      <c r="O156" s="29" t="str">
+      <c r="J156" s="28"/>
+      <c r="K156" s="28"/>
+      <c r="L156" s="28"/>
+      <c r="M156" s="28"/>
+      <c r="N156" s="28"/>
+      <c r="O156" s="28" t="str">
         <f>CONCATENATE("M 7 ",'Elimination Matches'!G31)</f>
       </c>
     </row>
@@ -7217,46 +7227,46 @@
       <c r="O162" s="27"/>
     </row>
     <row r="163">
-      <c r="A163" s="28" t="s">
+      <c r="A163" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="D163" s="29" t="s">
+      <c r="D163" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="G163" t="s">
+      <c r="G163" s="30" t="s">
         <v>209</v>
       </c>
-      <c r="I163" s="28" t="s">
+      <c r="I163" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="L163" s="29" t="s">
+      <c r="L163" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="O163" t="s">
+      <c r="O163" s="30" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="29" t="str">
+      <c r="A164" s="28" t="str">
         <f>'data'!$B$29</f>
       </c>
-      <c r="B164" s="29"/>
-      <c r="C164" s="29"/>
-      <c r="D164" s="29"/>
-      <c r="E164" s="29"/>
-      <c r="F164" s="29"/>
-      <c r="G164" s="29" t="str">
+      <c r="B164" s="28"/>
+      <c r="C164" s="28"/>
+      <c r="D164" s="28"/>
+      <c r="E164" s="28"/>
+      <c r="F164" s="28"/>
+      <c r="G164" s="28" t="str">
         <f>CONCATENATE("M 8 ",'Elimination Matches'!O31)</f>
       </c>
-      <c r="I164" s="29" t="str">
+      <c r="I164" s="28" t="str">
         <f>'data'!$B$32</f>
       </c>
-      <c r="J164" s="29"/>
-      <c r="K164" s="29"/>
-      <c r="L164" s="29"/>
-      <c r="M164" s="29"/>
-      <c r="N164" s="29"/>
-      <c r="O164" s="29" t="str">
+      <c r="J164" s="28"/>
+      <c r="K164" s="28"/>
+      <c r="L164" s="28"/>
+      <c r="M164" s="28"/>
+      <c r="N164" s="28"/>
+      <c r="O164" s="28" t="str">
         <f>CONCATENATE("M 9 ",'Elimination Matches'!G39)</f>
       </c>
     </row>
@@ -7301,46 +7311,46 @@
       <c r="O170" s="27"/>
     </row>
     <row r="171">
-      <c r="A171" s="28" t="s">
+      <c r="A171" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="D171" s="29" t="s">
+      <c r="D171" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="G171" t="s">
+      <c r="G171" s="30" t="s">
         <v>209</v>
       </c>
-      <c r="I171" s="28" t="s">
+      <c r="I171" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="L171" s="29" t="s">
+      <c r="L171" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="O171" t="s">
+      <c r="O171" s="30" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="29" t="str">
+      <c r="A172" s="28" t="str">
         <f>'data'!$B$35</f>
       </c>
-      <c r="B172" s="29"/>
-      <c r="C172" s="29"/>
-      <c r="D172" s="29"/>
-      <c r="E172" s="29"/>
-      <c r="F172" s="29"/>
-      <c r="G172" s="29" t="str">
+      <c r="B172" s="28"/>
+      <c r="C172" s="28"/>
+      <c r="D172" s="28"/>
+      <c r="E172" s="28"/>
+      <c r="F172" s="28"/>
+      <c r="G172" s="28" t="str">
         <f>CONCATENATE("M 10 ",'Elimination Matches'!O39)</f>
       </c>
-      <c r="I172" s="29" t="str">
+      <c r="I172" s="28" t="str">
         <f>'data'!$B$38</f>
       </c>
-      <c r="J172" s="29"/>
-      <c r="K172" s="29"/>
-      <c r="L172" s="29"/>
-      <c r="M172" s="29"/>
-      <c r="N172" s="29"/>
-      <c r="O172" s="29" t="str">
+      <c r="J172" s="28"/>
+      <c r="K172" s="28"/>
+      <c r="L172" s="28"/>
+      <c r="M172" s="28"/>
+      <c r="N172" s="28"/>
+      <c r="O172" s="28" t="str">
         <f>CONCATENATE("M 11 ",'Elimination Matches'!G47)</f>
       </c>
     </row>
@@ -7385,46 +7395,46 @@
       <c r="O178" s="27"/>
     </row>
     <row r="179">
-      <c r="A179" s="28" t="s">
+      <c r="A179" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="D179" s="29" t="s">
+      <c r="D179" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="G179" t="s">
+      <c r="G179" s="30" t="s">
         <v>209</v>
       </c>
-      <c r="I179" s="28" t="s">
+      <c r="I179" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="L179" s="29" t="s">
+      <c r="L179" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="O179" t="s">
+      <c r="O179" s="30" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="29" t="str">
+      <c r="A180" s="28" t="str">
         <f>'data'!$B$41</f>
       </c>
-      <c r="B180" s="29"/>
-      <c r="C180" s="29"/>
-      <c r="D180" s="29"/>
-      <c r="E180" s="29"/>
-      <c r="F180" s="29"/>
-      <c r="G180" s="29" t="str">
+      <c r="B180" s="28"/>
+      <c r="C180" s="28"/>
+      <c r="D180" s="28"/>
+      <c r="E180" s="28"/>
+      <c r="F180" s="28"/>
+      <c r="G180" s="28" t="str">
         <f>CONCATENATE("M 12 ",'Elimination Matches'!O47)</f>
       </c>
-      <c r="I180" s="29" t="str">
+      <c r="I180" s="28" t="str">
         <f>'data'!$B$44</f>
       </c>
-      <c r="J180" s="29"/>
-      <c r="K180" s="29"/>
-      <c r="L180" s="29"/>
-      <c r="M180" s="29"/>
-      <c r="N180" s="29"/>
-      <c r="O180" s="29" t="str">
+      <c r="J180" s="28"/>
+      <c r="K180" s="28"/>
+      <c r="L180" s="28"/>
+      <c r="M180" s="28"/>
+      <c r="N180" s="28"/>
+      <c r="O180" s="28" t="str">
         <f>CONCATENATE("M 13 ",'Elimination Matches'!G55)</f>
       </c>
     </row>
@@ -7469,46 +7479,46 @@
       <c r="O186" s="27"/>
     </row>
     <row r="187">
-      <c r="A187" s="28" t="s">
+      <c r="A187" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="D187" s="29" t="s">
+      <c r="D187" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="G187" t="s">
+      <c r="G187" s="30" t="s">
         <v>209</v>
       </c>
-      <c r="I187" s="28" t="s">
+      <c r="I187" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="L187" s="29" t="s">
+      <c r="L187" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="O187" t="s">
+      <c r="O187" s="30" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="29" t="str">
+      <c r="A188" s="28" t="str">
         <f>'data'!$B$47</f>
       </c>
-      <c r="B188" s="29"/>
-      <c r="C188" s="29"/>
-      <c r="D188" s="29"/>
-      <c r="E188" s="29"/>
-      <c r="F188" s="29"/>
-      <c r="G188" s="29" t="str">
+      <c r="B188" s="28"/>
+      <c r="C188" s="28"/>
+      <c r="D188" s="28"/>
+      <c r="E188" s="28"/>
+      <c r="F188" s="28"/>
+      <c r="G188" s="28" t="str">
         <f>'data'!$B$48</f>
       </c>
-      <c r="I188" s="29" t="str">
+      <c r="I188" s="28" t="str">
         <f>'data'!$B$49</f>
       </c>
-      <c r="J188" s="29"/>
-      <c r="K188" s="29"/>
-      <c r="L188" s="29"/>
-      <c r="M188" s="29"/>
-      <c r="N188" s="29"/>
-      <c r="O188" s="29" t="str">
+      <c r="J188" s="28"/>
+      <c r="K188" s="28"/>
+      <c r="L188" s="28"/>
+      <c r="M188" s="28"/>
+      <c r="N188" s="28"/>
+      <c r="O188" s="28" t="str">
         <f>CONCATENATE("M 14 ",'Elimination Matches'!O55)</f>
       </c>
     </row>
@@ -7553,46 +7563,46 @@
       <c r="O194" s="27"/>
     </row>
     <row r="195">
-      <c r="A195" s="28" t="s">
+      <c r="A195" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="D195" s="29" t="s">
+      <c r="D195" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="G195" t="s">
+      <c r="G195" s="30" t="s">
         <v>209</v>
       </c>
-      <c r="I195" s="28" t="s">
+      <c r="I195" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="L195" s="29" t="s">
+      <c r="L195" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="O195" t="s">
+      <c r="O195" s="30" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="29" t="str">
+      <c r="A196" s="28" t="str">
         <f>'data'!$B$52</f>
       </c>
-      <c r="B196" s="29"/>
-      <c r="C196" s="29"/>
-      <c r="D196" s="29"/>
-      <c r="E196" s="29"/>
-      <c r="F196" s="29"/>
-      <c r="G196" s="29" t="str">
+      <c r="B196" s="28"/>
+      <c r="C196" s="28"/>
+      <c r="D196" s="28"/>
+      <c r="E196" s="28"/>
+      <c r="F196" s="28"/>
+      <c r="G196" s="28" t="str">
         <f>CONCATENATE("M 15 ",'Elimination Matches'!G63)</f>
       </c>
-      <c r="I196" s="29" t="str">
+      <c r="I196" s="28" t="str">
         <f>'data'!$B$55</f>
       </c>
-      <c r="J196" s="29"/>
-      <c r="K196" s="29"/>
-      <c r="L196" s="29"/>
-      <c r="M196" s="29"/>
-      <c r="N196" s="29"/>
-      <c r="O196" s="29" t="str">
+      <c r="J196" s="28"/>
+      <c r="K196" s="28"/>
+      <c r="L196" s="28"/>
+      <c r="M196" s="28"/>
+      <c r="N196" s="28"/>
+      <c r="O196" s="28" t="str">
         <f>CONCATENATE("M 16 ",'Elimination Matches'!O63)</f>
       </c>
     </row>
@@ -7637,46 +7647,46 @@
       <c r="O202" s="27"/>
     </row>
     <row r="203">
-      <c r="A203" s="28" t="s">
+      <c r="A203" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="D203" s="29" t="s">
+      <c r="D203" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="G203" t="s">
+      <c r="G203" s="30" t="s">
         <v>209</v>
       </c>
-      <c r="I203" s="28" t="s">
+      <c r="I203" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="L203" s="29" t="s">
+      <c r="L203" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="O203" t="s">
+      <c r="O203" s="30" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="29" t="str">
+      <c r="A204" s="28" t="str">
         <f>'data'!$B$80</f>
       </c>
-      <c r="B204" s="29"/>
-      <c r="C204" s="29"/>
-      <c r="D204" s="29"/>
-      <c r="E204" s="29"/>
-      <c r="F204" s="29"/>
-      <c r="G204" s="29" t="str">
+      <c r="B204" s="28"/>
+      <c r="C204" s="28"/>
+      <c r="D204" s="28"/>
+      <c r="E204" s="28"/>
+      <c r="F204" s="28"/>
+      <c r="G204" s="28" t="str">
         <f>CONCATENATE("M 17 ",'Elimination Matches'!G71)</f>
       </c>
-      <c r="I204" s="29" t="str">
+      <c r="I204" s="28" t="str">
         <f>'data'!$B$61</f>
       </c>
-      <c r="J204" s="29"/>
-      <c r="K204" s="29"/>
-      <c r="L204" s="29"/>
-      <c r="M204" s="29"/>
-      <c r="N204" s="29"/>
-      <c r="O204" s="29" t="str">
+      <c r="J204" s="28"/>
+      <c r="K204" s="28"/>
+      <c r="L204" s="28"/>
+      <c r="M204" s="28"/>
+      <c r="N204" s="28"/>
+      <c r="O204" s="28" t="str">
         <f>CONCATENATE("M 18 ",'Elimination Matches'!O71)</f>
       </c>
     </row>
@@ -7721,46 +7731,46 @@
       <c r="O210" s="27"/>
     </row>
     <row r="211">
-      <c r="A211" s="28" t="s">
+      <c r="A211" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="D211" s="29" t="s">
+      <c r="D211" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="G211" t="s">
+      <c r="G211" s="30" t="s">
         <v>209</v>
       </c>
-      <c r="I211" s="28" t="s">
+      <c r="I211" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="L211" s="29" t="s">
+      <c r="L211" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="O211" t="s">
+      <c r="O211" s="30" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="29" t="str">
+      <c r="A212" s="28" t="str">
         <f>'data'!$B$64</f>
       </c>
-      <c r="B212" s="29"/>
-      <c r="C212" s="29"/>
-      <c r="D212" s="29"/>
-      <c r="E212" s="29"/>
-      <c r="F212" s="29"/>
-      <c r="G212" s="29" t="str">
+      <c r="B212" s="28"/>
+      <c r="C212" s="28"/>
+      <c r="D212" s="28"/>
+      <c r="E212" s="28"/>
+      <c r="F212" s="28"/>
+      <c r="G212" s="28" t="str">
         <f>CONCATENATE("M 19 ",'Elimination Matches'!G79)</f>
       </c>
-      <c r="I212" s="29" t="str">
+      <c r="I212" s="28" t="str">
         <f>'data'!$B$67</f>
       </c>
-      <c r="J212" s="29"/>
-      <c r="K212" s="29"/>
-      <c r="L212" s="29"/>
-      <c r="M212" s="29"/>
-      <c r="N212" s="29"/>
-      <c r="O212" s="29" t="str">
+      <c r="J212" s="28"/>
+      <c r="K212" s="28"/>
+      <c r="L212" s="28"/>
+      <c r="M212" s="28"/>
+      <c r="N212" s="28"/>
+      <c r="O212" s="28" t="str">
         <f>CONCATENATE("M 20 ",'Elimination Matches'!O79)</f>
       </c>
     </row>
@@ -7805,46 +7815,46 @@
       <c r="O218" s="27"/>
     </row>
     <row r="219">
-      <c r="A219" s="28" t="s">
+      <c r="A219" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="D219" s="29" t="s">
+      <c r="D219" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="G219" t="s">
+      <c r="G219" s="30" t="s">
         <v>209</v>
       </c>
-      <c r="I219" s="28" t="s">
+      <c r="I219" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="L219" s="29" t="s">
+      <c r="L219" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="O219" t="s">
+      <c r="O219" s="30" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="29" t="str">
+      <c r="A220" s="28" t="str">
         <f>'data'!$B$87</f>
       </c>
-      <c r="B220" s="29"/>
-      <c r="C220" s="29"/>
-      <c r="D220" s="29"/>
-      <c r="E220" s="29"/>
-      <c r="F220" s="29"/>
-      <c r="G220" s="29" t="str">
+      <c r="B220" s="28"/>
+      <c r="C220" s="28"/>
+      <c r="D220" s="28"/>
+      <c r="E220" s="28"/>
+      <c r="F220" s="28"/>
+      <c r="G220" s="28" t="str">
         <f>'data'!$B$71</f>
       </c>
-      <c r="I220" s="29" t="str">
+      <c r="I220" s="28" t="str">
         <f>'data'!$B$72</f>
       </c>
-      <c r="J220" s="29"/>
-      <c r="K220" s="29"/>
-      <c r="L220" s="29"/>
-      <c r="M220" s="29"/>
-      <c r="N220" s="29"/>
-      <c r="O220" s="29" t="str">
+      <c r="J220" s="28"/>
+      <c r="K220" s="28"/>
+      <c r="L220" s="28"/>
+      <c r="M220" s="28"/>
+      <c r="N220" s="28"/>
+      <c r="O220" s="28" t="str">
         <f>CONCATENATE("M 21 ",'Elimination Matches'!G87)</f>
       </c>
     </row>
@@ -7889,46 +7899,46 @@
       <c r="O226" s="27"/>
     </row>
     <row r="227">
-      <c r="A227" s="28" t="s">
+      <c r="A227" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="D227" s="29" t="s">
+      <c r="D227" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="G227" t="s">
+      <c r="G227" s="30" t="s">
         <v>209</v>
       </c>
-      <c r="I227" s="28" t="s">
+      <c r="I227" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="L227" s="29" t="s">
+      <c r="L227" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="O227" t="s">
+      <c r="O227" s="30" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="29" t="str">
+      <c r="A228" s="28" t="str">
         <f>'data'!$B$75</f>
       </c>
-      <c r="B228" s="29"/>
-      <c r="C228" s="29"/>
-      <c r="D228" s="29"/>
-      <c r="E228" s="29"/>
-      <c r="F228" s="29"/>
-      <c r="G228" s="29" t="str">
+      <c r="B228" s="28"/>
+      <c r="C228" s="28"/>
+      <c r="D228" s="28"/>
+      <c r="E228" s="28"/>
+      <c r="F228" s="28"/>
+      <c r="G228" s="28" t="str">
         <f>CONCATENATE("M 22 ",'Elimination Matches'!O87)</f>
       </c>
-      <c r="I228" s="29" t="str">
+      <c r="I228" s="28" t="str">
         <f>'data'!$B$78</f>
       </c>
-      <c r="J228" s="29"/>
-      <c r="K228" s="29"/>
-      <c r="L228" s="29"/>
-      <c r="M228" s="29"/>
-      <c r="N228" s="29"/>
-      <c r="O228" s="29" t="str">
+      <c r="J228" s="28"/>
+      <c r="K228" s="28"/>
+      <c r="L228" s="28"/>
+      <c r="M228" s="28"/>
+      <c r="N228" s="28"/>
+      <c r="O228" s="28" t="str">
         <f>CONCATENATE("M 23 ",'Elimination Matches'!G95)</f>
       </c>
     </row>
@@ -7973,46 +7983,46 @@
       <c r="O234" s="27"/>
     </row>
     <row r="235">
-      <c r="A235" s="28" t="s">
+      <c r="A235" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="D235" s="29" t="s">
+      <c r="D235" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="G235" t="s">
+      <c r="G235" s="30" t="s">
         <v>209</v>
       </c>
-      <c r="I235" s="28" t="s">
+      <c r="I235" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="L235" s="29" t="s">
+      <c r="L235" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="O235" t="s">
+      <c r="O235" s="30" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="29" t="str">
+      <c r="A236" s="28" t="str">
         <f>'data'!$B$81</f>
       </c>
-      <c r="B236" s="29"/>
-      <c r="C236" s="29"/>
-      <c r="D236" s="29"/>
-      <c r="E236" s="29"/>
-      <c r="F236" s="29"/>
-      <c r="G236" s="29" t="str">
+      <c r="B236" s="28"/>
+      <c r="C236" s="28"/>
+      <c r="D236" s="28"/>
+      <c r="E236" s="28"/>
+      <c r="F236" s="28"/>
+      <c r="G236" s="28" t="str">
         <f>CONCATENATE("M 24 ",'Elimination Matches'!O95)</f>
       </c>
-      <c r="I236" s="29" t="str">
+      <c r="I236" s="28" t="str">
         <f>'data'!$B$84</f>
       </c>
-      <c r="J236" s="29"/>
-      <c r="K236" s="29"/>
-      <c r="L236" s="29"/>
-      <c r="M236" s="29"/>
-      <c r="N236" s="29"/>
-      <c r="O236" s="29" t="str">
+      <c r="J236" s="28"/>
+      <c r="K236" s="28"/>
+      <c r="L236" s="28"/>
+      <c r="M236" s="28"/>
+      <c r="N236" s="28"/>
+      <c r="O236" s="28" t="str">
         <f>CONCATENATE("M 25 ",'Elimination Matches'!G103)</f>
       </c>
     </row>
@@ -8057,46 +8067,46 @@
       <c r="O242" s="27"/>
     </row>
     <row r="243">
-      <c r="A243" s="28" t="s">
+      <c r="A243" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="D243" s="29" t="s">
+      <c r="D243" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="G243" t="s">
+      <c r="G243" s="30" t="s">
         <v>209</v>
       </c>
-      <c r="I243" s="28" t="s">
+      <c r="I243" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="L243" s="29" t="s">
+      <c r="L243" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="O243" t="s">
+      <c r="O243" s="30" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="29" t="str">
+      <c r="A244" s="28" t="str">
         <f>'data'!$B$87</f>
       </c>
-      <c r="B244" s="29"/>
-      <c r="C244" s="29"/>
-      <c r="D244" s="29"/>
-      <c r="E244" s="29"/>
-      <c r="F244" s="29"/>
-      <c r="G244" s="29" t="str">
+      <c r="B244" s="28"/>
+      <c r="C244" s="28"/>
+      <c r="D244" s="28"/>
+      <c r="E244" s="28"/>
+      <c r="F244" s="28"/>
+      <c r="G244" s="28" t="str">
         <f>CONCATENATE("M 26 ",'Elimination Matches'!O103)</f>
       </c>
-      <c r="I244" s="29" t="str">
+      <c r="I244" s="28" t="str">
         <f>'data'!$B$90</f>
       </c>
-      <c r="J244" s="29"/>
-      <c r="K244" s="29"/>
-      <c r="L244" s="29"/>
-      <c r="M244" s="29"/>
-      <c r="N244" s="29"/>
-      <c r="O244" s="29" t="str">
+      <c r="J244" s="28"/>
+      <c r="K244" s="28"/>
+      <c r="L244" s="28"/>
+      <c r="M244" s="28"/>
+      <c r="N244" s="28"/>
+      <c r="O244" s="28" t="str">
         <f>CONCATENATE("M 27 ",'Elimination Matches'!G111)</f>
       </c>
     </row>
@@ -8160,46 +8170,46 @@
       <c r="O257" s="27"/>
     </row>
     <row r="258">
-      <c r="A258" s="28" t="s">
+      <c r="A258" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="D258" s="29" t="s">
+      <c r="D258" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="G258" t="s">
+      <c r="G258" s="30" t="s">
         <v>209</v>
       </c>
-      <c r="I258" s="28" t="s">
+      <c r="I258" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="L258" s="29" t="s">
+      <c r="L258" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="O258" t="s">
+      <c r="O258" s="30" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="29" t="str">
+      <c r="A259" s="28" t="str">
         <f>CONCATENATE("M 28 ",'Elimination Matches'!G126)</f>
       </c>
-      <c r="B259" s="29"/>
-      <c r="C259" s="29"/>
-      <c r="D259" s="29"/>
-      <c r="E259" s="29"/>
-      <c r="F259" s="29"/>
-      <c r="G259" s="29" t="str">
+      <c r="B259" s="28"/>
+      <c r="C259" s="28"/>
+      <c r="D259" s="28"/>
+      <c r="E259" s="28"/>
+      <c r="F259" s="28"/>
+      <c r="G259" s="28" t="str">
         <f>CONCATENATE("M 29 ",'Elimination Matches'!O126)</f>
       </c>
-      <c r="I259" s="29" t="str">
+      <c r="I259" s="28" t="str">
         <f>CONCATENATE("M 30 ",'Elimination Matches'!G134)</f>
       </c>
-      <c r="J259" s="29"/>
-      <c r="K259" s="29"/>
-      <c r="L259" s="29"/>
-      <c r="M259" s="29"/>
-      <c r="N259" s="29"/>
-      <c r="O259" s="29" t="str">
+      <c r="J259" s="28"/>
+      <c r="K259" s="28"/>
+      <c r="L259" s="28"/>
+      <c r="M259" s="28"/>
+      <c r="N259" s="28"/>
+      <c r="O259" s="28" t="str">
         <f>CONCATENATE("M 31 ",'Elimination Matches'!O134)</f>
       </c>
     </row>
@@ -8244,46 +8254,46 @@
       <c r="O265" s="27"/>
     </row>
     <row r="266">
-      <c r="A266" s="28" t="s">
+      <c r="A266" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="D266" s="29" t="s">
+      <c r="D266" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="G266" t="s">
+      <c r="G266" s="30" t="s">
         <v>209</v>
       </c>
-      <c r="I266" s="28" t="s">
+      <c r="I266" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="L266" s="29" t="s">
+      <c r="L266" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="O266" t="s">
+      <c r="O266" s="30" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="29" t="str">
+      <c r="A267" s="28" t="str">
         <f>CONCATENATE("M 32 ",'Elimination Matches'!G142)</f>
       </c>
-      <c r="B267" s="29"/>
-      <c r="C267" s="29"/>
-      <c r="D267" s="29"/>
-      <c r="E267" s="29"/>
-      <c r="F267" s="29"/>
-      <c r="G267" s="29" t="str">
+      <c r="B267" s="28"/>
+      <c r="C267" s="28"/>
+      <c r="D267" s="28"/>
+      <c r="E267" s="28"/>
+      <c r="F267" s="28"/>
+      <c r="G267" s="28" t="str">
         <f>CONCATENATE("M 33 ",'Elimination Matches'!O142)</f>
       </c>
-      <c r="I267" s="29" t="str">
+      <c r="I267" s="28" t="str">
         <f>CONCATENATE("M 34 ",'Elimination Matches'!G150)</f>
       </c>
-      <c r="J267" s="29"/>
-      <c r="K267" s="29"/>
-      <c r="L267" s="29"/>
-      <c r="M267" s="29"/>
-      <c r="N267" s="29"/>
-      <c r="O267" s="29" t="str">
+      <c r="J267" s="28"/>
+      <c r="K267" s="28"/>
+      <c r="L267" s="28"/>
+      <c r="M267" s="28"/>
+      <c r="N267" s="28"/>
+      <c r="O267" s="28" t="str">
         <f>CONCATENATE("M 35 ",'Elimination Matches'!O150)</f>
       </c>
     </row>
@@ -8328,46 +8338,46 @@
       <c r="O273" s="27"/>
     </row>
     <row r="274">
-      <c r="A274" s="28" t="s">
+      <c r="A274" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="D274" s="29" t="s">
+      <c r="D274" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="G274" t="s">
+      <c r="G274" s="30" t="s">
         <v>209</v>
       </c>
-      <c r="I274" s="28" t="s">
+      <c r="I274" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="L274" s="29" t="s">
+      <c r="L274" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="O274" t="s">
+      <c r="O274" s="30" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="29" t="str">
+      <c r="A275" s="28" t="str">
         <f>CONCATENATE("M 36 ",'Elimination Matches'!G158)</f>
       </c>
-      <c r="B275" s="29"/>
-      <c r="C275" s="29"/>
-      <c r="D275" s="29"/>
-      <c r="E275" s="29"/>
-      <c r="F275" s="29"/>
-      <c r="G275" s="29" t="str">
+      <c r="B275" s="28"/>
+      <c r="C275" s="28"/>
+      <c r="D275" s="28"/>
+      <c r="E275" s="28"/>
+      <c r="F275" s="28"/>
+      <c r="G275" s="28" t="str">
         <f>CONCATENATE("M 37 ",'Elimination Matches'!O158)</f>
       </c>
-      <c r="I275" s="29" t="str">
+      <c r="I275" s="28" t="str">
         <f>CONCATENATE("M 38 ",'Elimination Matches'!G166)</f>
       </c>
-      <c r="J275" s="29"/>
-      <c r="K275" s="29"/>
-      <c r="L275" s="29"/>
-      <c r="M275" s="29"/>
-      <c r="N275" s="29"/>
-      <c r="O275" s="29" t="str">
+      <c r="J275" s="28"/>
+      <c r="K275" s="28"/>
+      <c r="L275" s="28"/>
+      <c r="M275" s="28"/>
+      <c r="N275" s="28"/>
+      <c r="O275" s="28" t="str">
         <f>CONCATENATE("M 39 ",'Elimination Matches'!O166)</f>
       </c>
     </row>
@@ -8412,46 +8422,46 @@
       <c r="O281" s="27"/>
     </row>
     <row r="282">
-      <c r="A282" s="28" t="s">
+      <c r="A282" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="D282" s="29" t="s">
+      <c r="D282" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="G282" t="s">
+      <c r="G282" s="30" t="s">
         <v>209</v>
       </c>
-      <c r="I282" s="28" t="s">
+      <c r="I282" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="L282" s="29" t="s">
+      <c r="L282" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="O282" t="s">
+      <c r="O282" s="30" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="29" t="str">
+      <c r="A283" s="28" t="str">
         <f>CONCATENATE("M 40 ",'Elimination Matches'!G174)</f>
       </c>
-      <c r="B283" s="29"/>
-      <c r="C283" s="29"/>
-      <c r="D283" s="29"/>
-      <c r="E283" s="29"/>
-      <c r="F283" s="29"/>
-      <c r="G283" s="29" t="str">
+      <c r="B283" s="28"/>
+      <c r="C283" s="28"/>
+      <c r="D283" s="28"/>
+      <c r="E283" s="28"/>
+      <c r="F283" s="28"/>
+      <c r="G283" s="28" t="str">
         <f>CONCATENATE("M 41 ",'Elimination Matches'!O174)</f>
       </c>
-      <c r="I283" s="29" t="str">
+      <c r="I283" s="28" t="str">
         <f>CONCATENATE("M 42 ",'Elimination Matches'!G182)</f>
       </c>
-      <c r="J283" s="29"/>
-      <c r="K283" s="29"/>
-      <c r="L283" s="29"/>
-      <c r="M283" s="29"/>
-      <c r="N283" s="29"/>
-      <c r="O283" s="29" t="str">
+      <c r="J283" s="28"/>
+      <c r="K283" s="28"/>
+      <c r="L283" s="28"/>
+      <c r="M283" s="28"/>
+      <c r="N283" s="28"/>
+      <c r="O283" s="28" t="str">
         <f>CONCATENATE("M 43 ",'Elimination Matches'!O182)</f>
       </c>
     </row>
@@ -8496,46 +8506,46 @@
       <c r="O289" s="27"/>
     </row>
     <row r="290">
-      <c r="A290" s="28" t="s">
+      <c r="A290" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="D290" s="29" t="s">
+      <c r="D290" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="G290" t="s">
+      <c r="G290" s="30" t="s">
         <v>209</v>
       </c>
-      <c r="I290" s="28" t="s">
+      <c r="I290" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="L290" s="29" t="s">
+      <c r="L290" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="O290" t="s">
+      <c r="O290" s="30" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="29" t="str">
+      <c r="A291" s="28" t="str">
         <f>CONCATENATE("M 44 ",'Elimination Matches'!G190)</f>
       </c>
-      <c r="B291" s="29"/>
-      <c r="C291" s="29"/>
-      <c r="D291" s="29"/>
-      <c r="E291" s="29"/>
-      <c r="F291" s="29"/>
-      <c r="G291" s="29" t="str">
+      <c r="B291" s="28"/>
+      <c r="C291" s="28"/>
+      <c r="D291" s="28"/>
+      <c r="E291" s="28"/>
+      <c r="F291" s="28"/>
+      <c r="G291" s="28" t="str">
         <f>CONCATENATE("M 45 ",'Elimination Matches'!O190)</f>
       </c>
-      <c r="I291" s="29" t="str">
+      <c r="I291" s="28" t="str">
         <f>CONCATENATE("M 46 ",'Elimination Matches'!G198)</f>
       </c>
-      <c r="J291" s="29"/>
-      <c r="K291" s="29"/>
-      <c r="L291" s="29"/>
-      <c r="M291" s="29"/>
-      <c r="N291" s="29"/>
-      <c r="O291" s="29" t="str">
+      <c r="J291" s="28"/>
+      <c r="K291" s="28"/>
+      <c r="L291" s="28"/>
+      <c r="M291" s="28"/>
+      <c r="N291" s="28"/>
+      <c r="O291" s="28" t="str">
         <f>CONCATENATE("M 47 ",'Elimination Matches'!O198)</f>
       </c>
     </row>
@@ -8580,46 +8590,46 @@
       <c r="O297" s="27"/>
     </row>
     <row r="298">
-      <c r="A298" s="28" t="s">
+      <c r="A298" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="D298" s="29" t="s">
+      <c r="D298" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="G298" t="s">
+      <c r="G298" s="30" t="s">
         <v>209</v>
       </c>
-      <c r="I298" s="28" t="s">
+      <c r="I298" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="L298" s="29" t="s">
+      <c r="L298" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="O298" t="s">
+      <c r="O298" s="30" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="29" t="str">
+      <c r="A299" s="28" t="str">
         <f>CONCATENATE("M 48 ",'Elimination Matches'!G206)</f>
       </c>
-      <c r="B299" s="29"/>
-      <c r="C299" s="29"/>
-      <c r="D299" s="29"/>
-      <c r="E299" s="29"/>
-      <c r="F299" s="29"/>
-      <c r="G299" s="29" t="str">
+      <c r="B299" s="28"/>
+      <c r="C299" s="28"/>
+      <c r="D299" s="28"/>
+      <c r="E299" s="28"/>
+      <c r="F299" s="28"/>
+      <c r="G299" s="28" t="str">
         <f>CONCATENATE("M 49 ",'Elimination Matches'!O206)</f>
       </c>
-      <c r="I299" s="29" t="str">
+      <c r="I299" s="28" t="str">
         <f>CONCATENATE("M 50 ",'Elimination Matches'!G214)</f>
       </c>
-      <c r="J299" s="29"/>
-      <c r="K299" s="29"/>
-      <c r="L299" s="29"/>
-      <c r="M299" s="29"/>
-      <c r="N299" s="29"/>
-      <c r="O299" s="29" t="str">
+      <c r="J299" s="28"/>
+      <c r="K299" s="28"/>
+      <c r="L299" s="28"/>
+      <c r="M299" s="28"/>
+      <c r="N299" s="28"/>
+      <c r="O299" s="28" t="str">
         <f>CONCATENATE("M 51 ",'Elimination Matches'!O214)</f>
       </c>
     </row>
@@ -8664,46 +8674,46 @@
       <c r="O305" s="27"/>
     </row>
     <row r="306">
-      <c r="A306" s="28" t="s">
+      <c r="A306" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="D306" s="29" t="s">
+      <c r="D306" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="G306" t="s">
+      <c r="G306" s="30" t="s">
         <v>209</v>
       </c>
-      <c r="I306" s="28" t="s">
+      <c r="I306" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="L306" s="29" t="s">
+      <c r="L306" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="O306" t="s">
+      <c r="O306" s="30" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="29" t="str">
+      <c r="A307" s="28" t="str">
         <f>CONCATENATE("M 52 ",'Elimination Matches'!G222)</f>
       </c>
-      <c r="B307" s="29"/>
-      <c r="C307" s="29"/>
-      <c r="D307" s="29"/>
-      <c r="E307" s="29"/>
-      <c r="F307" s="29"/>
-      <c r="G307" s="29" t="str">
+      <c r="B307" s="28"/>
+      <c r="C307" s="28"/>
+      <c r="D307" s="28"/>
+      <c r="E307" s="28"/>
+      <c r="F307" s="28"/>
+      <c r="G307" s="28" t="str">
         <f>CONCATENATE("M 53 ",'Elimination Matches'!O222)</f>
       </c>
-      <c r="I307" s="29" t="str">
+      <c r="I307" s="28" t="str">
         <f>CONCATENATE("M 54 ",'Elimination Matches'!G230)</f>
       </c>
-      <c r="J307" s="29"/>
-      <c r="K307" s="29"/>
-      <c r="L307" s="29"/>
-      <c r="M307" s="29"/>
-      <c r="N307" s="29"/>
-      <c r="O307" s="29" t="str">
+      <c r="J307" s="28"/>
+      <c r="K307" s="28"/>
+      <c r="L307" s="28"/>
+      <c r="M307" s="28"/>
+      <c r="N307" s="28"/>
+      <c r="O307" s="28" t="str">
         <f>CONCATENATE("M 55 ",'Elimination Matches'!O230)</f>
       </c>
     </row>
@@ -8748,46 +8758,46 @@
       <c r="O313" s="27"/>
     </row>
     <row r="314">
-      <c r="A314" s="28" t="s">
+      <c r="A314" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="D314" s="29" t="s">
+      <c r="D314" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="G314" t="s">
+      <c r="G314" s="30" t="s">
         <v>209</v>
       </c>
-      <c r="I314" s="28" t="s">
+      <c r="I314" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="L314" s="29" t="s">
+      <c r="L314" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="O314" t="s">
+      <c r="O314" s="30" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="29" t="str">
+      <c r="A315" s="28" t="str">
         <f>CONCATENATE("M 56 ",'Elimination Matches'!G238)</f>
       </c>
-      <c r="B315" s="29"/>
-      <c r="C315" s="29"/>
-      <c r="D315" s="29"/>
-      <c r="E315" s="29"/>
-      <c r="F315" s="29"/>
-      <c r="G315" s="29" t="str">
+      <c r="B315" s="28"/>
+      <c r="C315" s="28"/>
+      <c r="D315" s="28"/>
+      <c r="E315" s="28"/>
+      <c r="F315" s="28"/>
+      <c r="G315" s="28" t="str">
         <f>CONCATENATE("M 57 ",'Elimination Matches'!O238)</f>
       </c>
-      <c r="I315" s="29" t="str">
+      <c r="I315" s="28" t="str">
         <f>CONCATENATE("M 58 ",'Elimination Matches'!G246)</f>
       </c>
-      <c r="J315" s="29"/>
-      <c r="K315" s="29"/>
-      <c r="L315" s="29"/>
-      <c r="M315" s="29"/>
-      <c r="N315" s="29"/>
-      <c r="O315" s="29" t="str">
+      <c r="J315" s="28"/>
+      <c r="K315" s="28"/>
+      <c r="L315" s="28"/>
+      <c r="M315" s="28"/>
+      <c r="N315" s="28"/>
+      <c r="O315" s="28" t="str">
         <f>CONCATENATE("M 59 ",'Elimination Matches'!O246)</f>
       </c>
     </row>
@@ -8851,46 +8861,46 @@
       <c r="O328" s="27"/>
     </row>
     <row r="329">
-      <c r="A329" s="28" t="s">
+      <c r="A329" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="D329" s="29" t="s">
+      <c r="D329" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="G329" t="s">
+      <c r="G329" s="30" t="s">
         <v>209</v>
       </c>
-      <c r="I329" s="28" t="s">
+      <c r="I329" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="L329" s="29" t="s">
+      <c r="L329" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="O329" t="s">
+      <c r="O329" s="30" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="330">
-      <c r="A330" s="29" t="str">
+      <c r="A330" s="28" t="str">
         <f>CONCATENATE("M 60 ",'Elimination Matches'!G261)</f>
       </c>
-      <c r="B330" s="29"/>
-      <c r="C330" s="29"/>
-      <c r="D330" s="29"/>
-      <c r="E330" s="29"/>
-      <c r="F330" s="29"/>
-      <c r="G330" s="29" t="str">
+      <c r="B330" s="28"/>
+      <c r="C330" s="28"/>
+      <c r="D330" s="28"/>
+      <c r="E330" s="28"/>
+      <c r="F330" s="28"/>
+      <c r="G330" s="28" t="str">
         <f>CONCATENATE("M 61 ",'Elimination Matches'!O261)</f>
       </c>
-      <c r="I330" s="29" t="str">
+      <c r="I330" s="28" t="str">
         <f>CONCATENATE("M 62 ",'Elimination Matches'!G269)</f>
       </c>
-      <c r="J330" s="29"/>
-      <c r="K330" s="29"/>
-      <c r="L330" s="29"/>
-      <c r="M330" s="29"/>
-      <c r="N330" s="29"/>
-      <c r="O330" s="29" t="str">
+      <c r="J330" s="28"/>
+      <c r="K330" s="28"/>
+      <c r="L330" s="28"/>
+      <c r="M330" s="28"/>
+      <c r="N330" s="28"/>
+      <c r="O330" s="28" t="str">
         <f>CONCATENATE("M 63 ",'Elimination Matches'!O269)</f>
       </c>
     </row>
@@ -8935,46 +8945,46 @@
       <c r="O336" s="27"/>
     </row>
     <row r="337">
-      <c r="A337" s="28" t="s">
+      <c r="A337" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="D337" s="29" t="s">
+      <c r="D337" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="G337" t="s">
+      <c r="G337" s="30" t="s">
         <v>209</v>
       </c>
-      <c r="I337" s="28" t="s">
+      <c r="I337" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="L337" s="29" t="s">
+      <c r="L337" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="O337" t="s">
+      <c r="O337" s="30" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="338">
-      <c r="A338" s="29" t="str">
+      <c r="A338" s="28" t="str">
         <f>CONCATENATE("M 64 ",'Elimination Matches'!G277)</f>
       </c>
-      <c r="B338" s="29"/>
-      <c r="C338" s="29"/>
-      <c r="D338" s="29"/>
-      <c r="E338" s="29"/>
-      <c r="F338" s="29"/>
-      <c r="G338" s="29" t="str">
+      <c r="B338" s="28"/>
+      <c r="C338" s="28"/>
+      <c r="D338" s="28"/>
+      <c r="E338" s="28"/>
+      <c r="F338" s="28"/>
+      <c r="G338" s="28" t="str">
         <f>CONCATENATE("M 65 ",'Elimination Matches'!O277)</f>
       </c>
-      <c r="I338" s="29" t="str">
+      <c r="I338" s="28" t="str">
         <f>CONCATENATE("M 66 ",'Elimination Matches'!G285)</f>
       </c>
-      <c r="J338" s="29"/>
-      <c r="K338" s="29"/>
-      <c r="L338" s="29"/>
-      <c r="M338" s="29"/>
-      <c r="N338" s="29"/>
-      <c r="O338" s="29" t="str">
+      <c r="J338" s="28"/>
+      <c r="K338" s="28"/>
+      <c r="L338" s="28"/>
+      <c r="M338" s="28"/>
+      <c r="N338" s="28"/>
+      <c r="O338" s="28" t="str">
         <f>CONCATENATE("M 67 ",'Elimination Matches'!O285)</f>
       </c>
     </row>
@@ -9019,46 +9029,46 @@
       <c r="O344" s="27"/>
     </row>
     <row r="345">
-      <c r="A345" s="28" t="s">
+      <c r="A345" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="D345" s="29" t="s">
+      <c r="D345" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="G345" t="s">
+      <c r="G345" s="30" t="s">
         <v>209</v>
       </c>
-      <c r="I345" s="28" t="s">
+      <c r="I345" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="L345" s="29" t="s">
+      <c r="L345" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="O345" t="s">
+      <c r="O345" s="30" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="346">
-      <c r="A346" s="29" t="str">
+      <c r="A346" s="28" t="str">
         <f>CONCATENATE("M 68 ",'Elimination Matches'!G293)</f>
       </c>
-      <c r="B346" s="29"/>
-      <c r="C346" s="29"/>
-      <c r="D346" s="29"/>
-      <c r="E346" s="29"/>
-      <c r="F346" s="29"/>
-      <c r="G346" s="29" t="str">
+      <c r="B346" s="28"/>
+      <c r="C346" s="28"/>
+      <c r="D346" s="28"/>
+      <c r="E346" s="28"/>
+      <c r="F346" s="28"/>
+      <c r="G346" s="28" t="str">
         <f>CONCATENATE("M 69 ",'Elimination Matches'!O293)</f>
       </c>
-      <c r="I346" s="29" t="str">
+      <c r="I346" s="28" t="str">
         <f>CONCATENATE("M 70 ",'Elimination Matches'!G301)</f>
       </c>
-      <c r="J346" s="29"/>
-      <c r="K346" s="29"/>
-      <c r="L346" s="29"/>
-      <c r="M346" s="29"/>
-      <c r="N346" s="29"/>
-      <c r="O346" s="29" t="str">
+      <c r="J346" s="28"/>
+      <c r="K346" s="28"/>
+      <c r="L346" s="28"/>
+      <c r="M346" s="28"/>
+      <c r="N346" s="28"/>
+      <c r="O346" s="28" t="str">
         <f>CONCATENATE("M 71 ",'Elimination Matches'!O301)</f>
       </c>
     </row>
@@ -9103,46 +9113,46 @@
       <c r="O352" s="27"/>
     </row>
     <row r="353">
-      <c r="A353" s="28" t="s">
+      <c r="A353" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="D353" s="29" t="s">
+      <c r="D353" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="G353" t="s">
+      <c r="G353" s="30" t="s">
         <v>209</v>
       </c>
-      <c r="I353" s="28" t="s">
+      <c r="I353" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="L353" s="29" t="s">
+      <c r="L353" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="O353" t="s">
+      <c r="O353" s="30" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="354">
-      <c r="A354" s="29" t="str">
+      <c r="A354" s="28" t="str">
         <f>CONCATENATE("M 72 ",'Elimination Matches'!G309)</f>
       </c>
-      <c r="B354" s="29"/>
-      <c r="C354" s="29"/>
-      <c r="D354" s="29"/>
-      <c r="E354" s="29"/>
-      <c r="F354" s="29"/>
-      <c r="G354" s="29" t="str">
+      <c r="B354" s="28"/>
+      <c r="C354" s="28"/>
+      <c r="D354" s="28"/>
+      <c r="E354" s="28"/>
+      <c r="F354" s="28"/>
+      <c r="G354" s="28" t="str">
         <f>CONCATENATE("M 73 ",'Elimination Matches'!O309)</f>
       </c>
-      <c r="I354" s="29" t="str">
+      <c r="I354" s="28" t="str">
         <f>CONCATENATE("M 74 ",'Elimination Matches'!G317)</f>
       </c>
-      <c r="J354" s="29"/>
-      <c r="K354" s="29"/>
-      <c r="L354" s="29"/>
-      <c r="M354" s="29"/>
-      <c r="N354" s="29"/>
-      <c r="O354" s="29" t="str">
+      <c r="J354" s="28"/>
+      <c r="K354" s="28"/>
+      <c r="L354" s="28"/>
+      <c r="M354" s="28"/>
+      <c r="N354" s="28"/>
+      <c r="O354" s="28" t="str">
         <f>CONCATENATE("M 75 ",'Elimination Matches'!O317)</f>
       </c>
     </row>
@@ -9206,46 +9216,46 @@
       <c r="O367" s="27"/>
     </row>
     <row r="368">
-      <c r="A368" s="28" t="s">
+      <c r="A368" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="D368" s="29" t="s">
+      <c r="D368" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="G368" t="s">
+      <c r="G368" s="30" t="s">
         <v>209</v>
       </c>
-      <c r="I368" s="28" t="s">
+      <c r="I368" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="L368" s="29" t="s">
+      <c r="L368" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="O368" t="s">
+      <c r="O368" s="30" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="369">
-      <c r="A369" s="29" t="str">
+      <c r="A369" s="28" t="str">
         <f>CONCATENATE("M 76 ",'Elimination Matches'!G332)</f>
       </c>
-      <c r="B369" s="29"/>
-      <c r="C369" s="29"/>
-      <c r="D369" s="29"/>
-      <c r="E369" s="29"/>
-      <c r="F369" s="29"/>
-      <c r="G369" s="29" t="str">
+      <c r="B369" s="28"/>
+      <c r="C369" s="28"/>
+      <c r="D369" s="28"/>
+      <c r="E369" s="28"/>
+      <c r="F369" s="28"/>
+      <c r="G369" s="28" t="str">
         <f>CONCATENATE("M 77 ",'Elimination Matches'!O332)</f>
       </c>
-      <c r="I369" s="29" t="str">
+      <c r="I369" s="28" t="str">
         <f>CONCATENATE("M 78 ",'Elimination Matches'!G340)</f>
       </c>
-      <c r="J369" s="29"/>
-      <c r="K369" s="29"/>
-      <c r="L369" s="29"/>
-      <c r="M369" s="29"/>
-      <c r="N369" s="29"/>
-      <c r="O369" s="29" t="str">
+      <c r="J369" s="28"/>
+      <c r="K369" s="28"/>
+      <c r="L369" s="28"/>
+      <c r="M369" s="28"/>
+      <c r="N369" s="28"/>
+      <c r="O369" s="28" t="str">
         <f>CONCATENATE("M 79 ",'Elimination Matches'!O340)</f>
       </c>
     </row>
@@ -9290,46 +9300,46 @@
       <c r="O375" s="27"/>
     </row>
     <row r="376">
-      <c r="A376" s="28" t="s">
+      <c r="A376" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="D376" s="29" t="s">
+      <c r="D376" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="G376" t="s">
+      <c r="G376" s="30" t="s">
         <v>209</v>
       </c>
-      <c r="I376" s="28" t="s">
+      <c r="I376" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="L376" s="29" t="s">
+      <c r="L376" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="O376" t="s">
+      <c r="O376" s="30" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="377">
-      <c r="A377" s="29" t="str">
+      <c r="A377" s="28" t="str">
         <f>CONCATENATE("M 80 ",'Elimination Matches'!G348)</f>
       </c>
-      <c r="B377" s="29"/>
-      <c r="C377" s="29"/>
-      <c r="D377" s="29"/>
-      <c r="E377" s="29"/>
-      <c r="F377" s="29"/>
-      <c r="G377" s="29" t="str">
+      <c r="B377" s="28"/>
+      <c r="C377" s="28"/>
+      <c r="D377" s="28"/>
+      <c r="E377" s="28"/>
+      <c r="F377" s="28"/>
+      <c r="G377" s="28" t="str">
         <f>CONCATENATE("M 81 ",'Elimination Matches'!O348)</f>
       </c>
-      <c r="I377" s="29" t="str">
+      <c r="I377" s="28" t="str">
         <f>CONCATENATE("M 82 ",'Elimination Matches'!G356)</f>
       </c>
-      <c r="J377" s="29"/>
-      <c r="K377" s="29"/>
-      <c r="L377" s="29"/>
-      <c r="M377" s="29"/>
-      <c r="N377" s="29"/>
-      <c r="O377" s="29" t="str">
+      <c r="J377" s="28"/>
+      <c r="K377" s="28"/>
+      <c r="L377" s="28"/>
+      <c r="M377" s="28"/>
+      <c r="N377" s="28"/>
+      <c r="O377" s="28" t="str">
         <f>CONCATENATE("M 83 ",'Elimination Matches'!O356)</f>
       </c>
     </row>
@@ -9393,46 +9403,46 @@
       <c r="O390" s="27"/>
     </row>
     <row r="391">
-      <c r="A391" s="28" t="s">
+      <c r="A391" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="D391" s="29" t="s">
+      <c r="D391" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="G391" t="s">
+      <c r="G391" s="30" t="s">
         <v>209</v>
       </c>
-      <c r="I391" s="28" t="s">
+      <c r="I391" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="L391" s="29" t="s">
+      <c r="L391" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="O391" t="s">
+      <c r="O391" s="30" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="392">
-      <c r="A392" s="29" t="str">
+      <c r="A392" s="28" t="str">
         <f>CONCATENATE("M 0 ",'Elimination Matches'!O379)</f>
       </c>
-      <c r="B392" s="29"/>
-      <c r="C392" s="29"/>
-      <c r="D392" s="29"/>
-      <c r="E392" s="29"/>
-      <c r="F392" s="29"/>
-      <c r="G392" s="29" t="str">
+      <c r="B392" s="28"/>
+      <c r="C392" s="28"/>
+      <c r="D392" s="28"/>
+      <c r="E392" s="28"/>
+      <c r="F392" s="28"/>
+      <c r="G392" s="28" t="str">
         <f>CONCATENATE("M 0 ",'Elimination Matches'!O379)</f>
       </c>
-      <c r="I392" s="29" t="str">
+      <c r="I392" s="28" t="str">
         <f>CONCATENATE("M 0 ",'Elimination Matches'!G394)</f>
       </c>
-      <c r="J392" s="29"/>
-      <c r="K392" s="29"/>
-      <c r="L392" s="29"/>
-      <c r="M392" s="29"/>
-      <c r="N392" s="29"/>
-      <c r="O392" s="29" t="str">
+      <c r="J392" s="28"/>
+      <c r="K392" s="28"/>
+      <c r="L392" s="28"/>
+      <c r="M392" s="28"/>
+      <c r="N392" s="28"/>
+      <c r="O392" s="28" t="str">
         <f>CONCATENATE("M 0 ",'Elimination Matches'!G394)</f>
       </c>
     </row>
@@ -9487,26 +9497,26 @@
       <c r="G405" s="27"/>
     </row>
     <row r="406">
-      <c r="A406" s="28" t="s">
+      <c r="A406" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="D406" s="29" t="s">
+      <c r="D406" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="G406" t="s">
+      <c r="G406" s="30" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="407">
-      <c r="A407" s="29" t="str">
+      <c r="A407" s="28" t="str">
         <f>CONCATENATE("M 0 ",'Elimination Matches'!O394)</f>
       </c>
-      <c r="B407" s="29"/>
-      <c r="C407" s="29"/>
-      <c r="D407" s="29"/>
-      <c r="E407" s="29"/>
-      <c r="F407" s="29"/>
-      <c r="G407" s="29" t="str">
+      <c r="B407" s="28"/>
+      <c r="C407" s="28"/>
+      <c r="D407" s="28"/>
+      <c r="E407" s="28"/>
+      <c r="F407" s="28"/>
+      <c r="G407" s="28" t="str">
         <f>CONCATENATE("M 0 ",'Elimination Matches'!O394)</f>
       </c>
     </row>
@@ -9634,8 +9644,8 @@
   <dimension ref="A1:B1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="115" customHeight="true"/>
   <cols>
-    <col customWidth="true" max="1" min="1" style="10" width="21.6640625"/>
-    <col customWidth="true" max="2" min="2" style="9" width="170.6640625"/>
+    <col customWidth="true" max="1" min="1" style="10" width="20"/>
+    <col customWidth="true" max="2" min="2" style="9" width="170"/>
     <col max="16384" min="3" style="8" width="10.83203125"/>
   </cols>
   <sheetData>
@@ -10827,6 +10837,6 @@
   </mergeCells>
   <printOptions horizontalCentered="true" verticalCentered="true"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup fitToHeight="0" horizontalDpi="0" orientation="landscape" paperSize="8" verticalDpi="0"/>
+  <pageSetup fitToHeight="0" fitToWidth="1" horizontalDpi="0" orientation="landscape" paperSize="8" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/playoffs-example-large.xlsx
+++ b/playoffs-example-large.xlsx
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="303">
   <si>
     <t>Elimination Round 1</t>
   </si>
@@ -85,6 +85,9 @@
   </si>
   <si>
     <t>Title prefix:</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>Number</t>
@@ -1518,23 +1521,25 @@
       <c r="A1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="1"/>
+      <c r="B1" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="2" spans="1:2" ht="12.75" customHeight="true">
       <c r="A2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="12.75" customHeight="true">
@@ -1542,13 +1547,13 @@
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="12.75" customHeight="true">
@@ -1556,13 +1561,13 @@
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="12.75" customHeight="true">
@@ -1570,13 +1575,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="12.75" customHeight="true">
@@ -1584,13 +1589,13 @@
         <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="12.75" customHeight="true">
@@ -1598,13 +1603,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="12.75" customHeight="true">
@@ -1612,13 +1617,13 @@
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="12.75" customHeight="true">
@@ -1626,13 +1631,13 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="12.75" customHeight="true">
@@ -1640,13 +1645,13 @@
         <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="12.75" customHeight="true">
@@ -1654,13 +1659,13 @@
         <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="12.75" customHeight="true">
@@ -1668,13 +1673,13 @@
         <v>9</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="12.75" customHeight="true">
@@ -1682,13 +1687,13 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="12.75" customHeight="true">
@@ -1696,13 +1701,13 @@
         <v>11</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="12.75" customHeight="true">
@@ -1710,13 +1715,13 @@
         <v>12</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C15" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D15" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="12.75" customHeight="true">
@@ -1724,13 +1729,13 @@
         <v>13</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="12.75" customHeight="true">
@@ -1738,13 +1743,13 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C17" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="12.75" customHeight="true">
@@ -1752,13 +1757,13 @@
         <v>15</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C18" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D18" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="12.75" customHeight="true">
@@ -1766,13 +1771,13 @@
         <v>16</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="12.75" customHeight="true">
@@ -1780,13 +1785,13 @@
         <v>17</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D20" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="12.75" customHeight="true">
@@ -1794,13 +1799,13 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C21" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D21" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="12.75" customHeight="true">
@@ -1808,13 +1813,13 @@
         <v>19</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C22" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D22" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="12.75" customHeight="true">
@@ -1822,13 +1827,13 @@
         <v>20</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C23" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D23" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="12.75" customHeight="true">
@@ -1836,13 +1841,13 @@
         <v>21</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C24" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D24" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="12.75" customHeight="true">
@@ -1850,13 +1855,13 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C25" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D25" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="12.75" customHeight="true">
@@ -1864,13 +1869,13 @@
         <v>23</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C26" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D26" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="12.75" customHeight="true">
@@ -1878,13 +1883,13 @@
         <v>24</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C27" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D27" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="12.75" customHeight="true">
@@ -1892,13 +1897,13 @@
         <v>25</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C28" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D28" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="12.75" customHeight="true">
@@ -1906,13 +1911,13 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C29" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D29" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="12.75" customHeight="true">
@@ -1920,13 +1925,13 @@
         <v>27</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C30" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="12.75" customHeight="true">
@@ -1934,13 +1939,13 @@
         <v>28</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C31" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D31" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="12.75" customHeight="true">
@@ -1948,13 +1953,13 @@
         <v>29</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C32" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D32" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="12.75" customHeight="true">
@@ -1962,13 +1967,13 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C33" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D33" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="12.75" customHeight="true">
@@ -1976,13 +1981,13 @@
         <v>31</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C34" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D34" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="12.75" customHeight="true">
@@ -1990,13 +1995,13 @@
         <v>32</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C35" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D35" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="12.75" customHeight="true">
@@ -2004,13 +2009,13 @@
         <v>33</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C36" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D36" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="12.75" customHeight="true">
@@ -2018,13 +2023,13 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C37" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D37" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="12.75" customHeight="true">
@@ -2032,13 +2037,13 @@
         <v>35</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C38" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D38" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="12.75" customHeight="true">
@@ -2046,13 +2051,13 @@
         <v>36</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C39" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D39" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="12.75" customHeight="true">
@@ -2060,13 +2065,13 @@
         <v>37</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C40" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D40" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="12.75" customHeight="true">
@@ -2074,13 +2079,13 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C41" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D41" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="12.75" customHeight="true">
@@ -2088,13 +2093,13 @@
         <v>39</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C42" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D42" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="12.75" customHeight="true">
@@ -2102,13 +2107,13 @@
         <v>40</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C43" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D43" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="12.75" customHeight="true">
@@ -2116,13 +2121,13 @@
         <v>41</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C44" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D44" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="12.75" customHeight="true">
@@ -2130,13 +2135,13 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C45" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D45" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="12.75" customHeight="true">
@@ -2144,13 +2149,13 @@
         <v>43</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C46" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D46" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="12.75" customHeight="true">
@@ -2158,13 +2163,13 @@
         <v>44</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C47" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D47" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="12.75" customHeight="true">
@@ -2172,13 +2177,13 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C48" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D48" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="49" ht="12.75" customHeight="true">
@@ -2186,13 +2191,13 @@
         <v>46</v>
       </c>
       <c r="B49" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C49" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D49" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="50" ht="12.75" customHeight="true">
@@ -2200,13 +2205,13 @@
         <v>47</v>
       </c>
       <c r="B50" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C50" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D50" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="51" ht="12.75" customHeight="true">
@@ -2214,13 +2219,13 @@
         <v>48</v>
       </c>
       <c r="B51" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C51" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D51" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="52" ht="12.75" customHeight="true">
@@ -2228,13 +2233,13 @@
         <v>49</v>
       </c>
       <c r="B52" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C52" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D52" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="53" ht="12.75" customHeight="true">
@@ -2242,13 +2247,13 @@
         <v>50</v>
       </c>
       <c r="B53" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C53" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D53" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="54" ht="12.75" customHeight="true">
@@ -2256,13 +2261,13 @@
         <v>51</v>
       </c>
       <c r="B54" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C54" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D54" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="55" ht="12.75" customHeight="true">
@@ -2270,13 +2275,13 @@
         <v>52</v>
       </c>
       <c r="B55" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C55" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D55" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="56" ht="12.75" customHeight="true">
@@ -2284,13 +2289,13 @@
         <v>53</v>
       </c>
       <c r="B56" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C56" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D56" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="57" ht="12.75" customHeight="true">
@@ -2298,13 +2303,13 @@
         <v>54</v>
       </c>
       <c r="B57" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C57" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D57" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="58" ht="12.75" customHeight="true">
@@ -2312,13 +2317,13 @@
         <v>55</v>
       </c>
       <c r="B58" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C58" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D58" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="59" ht="12.75" customHeight="true">
@@ -2326,13 +2331,13 @@
         <v>56</v>
       </c>
       <c r="B59" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C59" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D59" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="60" ht="12.75" customHeight="true">
@@ -2340,13 +2345,13 @@
         <v>57</v>
       </c>
       <c r="B60" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C60" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D60" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="61" ht="12.75" customHeight="true">
@@ -2354,13 +2359,13 @@
         <v>58</v>
       </c>
       <c r="B61" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C61" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D61" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="62" ht="12.75" customHeight="true">
@@ -2368,13 +2373,13 @@
         <v>59</v>
       </c>
       <c r="B62" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C62" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D62" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="63" ht="12.75" customHeight="true">
@@ -2382,13 +2387,13 @@
         <v>60</v>
       </c>
       <c r="B63" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C63" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D63" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="64" ht="12.75" customHeight="true">
@@ -2396,13 +2401,13 @@
         <v>61</v>
       </c>
       <c r="B64" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C64" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D64" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="65" ht="12.75" customHeight="true">
@@ -2410,13 +2415,13 @@
         <v>62</v>
       </c>
       <c r="B65" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C65" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D65" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="66" ht="12.75" customHeight="true">
@@ -2424,13 +2429,13 @@
         <v>63</v>
       </c>
       <c r="B66" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C66" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D66" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="67" ht="12.75" customHeight="true">
@@ -2438,13 +2443,13 @@
         <v>64</v>
       </c>
       <c r="B67" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C67" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D67" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="68" ht="12.75" customHeight="true">
@@ -2452,13 +2457,13 @@
         <v>65</v>
       </c>
       <c r="B68" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C68" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D68" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="69" ht="12.75" customHeight="true">
@@ -2466,13 +2471,13 @@
         <v>66</v>
       </c>
       <c r="B69" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C69" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D69" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="70" ht="12.75" customHeight="true">
@@ -2480,13 +2485,13 @@
         <v>67</v>
       </c>
       <c r="B70" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C70" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D70" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="71" ht="12.75" customHeight="true">
@@ -2494,13 +2499,13 @@
         <v>68</v>
       </c>
       <c r="B71" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C71" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D71" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="72" ht="12.75" customHeight="true">
@@ -2508,13 +2513,13 @@
         <v>69</v>
       </c>
       <c r="B72" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C72" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D72" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="73" ht="12.75" customHeight="true">
@@ -2522,13 +2527,13 @@
         <v>70</v>
       </c>
       <c r="B73" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C73" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D73" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="74" ht="12.75" customHeight="true">
@@ -2536,13 +2541,13 @@
         <v>71</v>
       </c>
       <c r="B74" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C74" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D74" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="75" ht="12.75" customHeight="true">
@@ -2550,13 +2555,13 @@
         <v>72</v>
       </c>
       <c r="B75" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C75" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D75" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="76" ht="12.75" customHeight="true">
@@ -2564,13 +2569,13 @@
         <v>73</v>
       </c>
       <c r="B76" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C76" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D76" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="77" ht="12.75" customHeight="true">
@@ -2578,13 +2583,13 @@
         <v>74</v>
       </c>
       <c r="B77" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C77" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D77" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="78" ht="12.75" customHeight="true">
@@ -2592,13 +2597,13 @@
         <v>75</v>
       </c>
       <c r="B78" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C78" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D78" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="79" ht="12.75" customHeight="true">
@@ -2606,13 +2611,13 @@
         <v>76</v>
       </c>
       <c r="B79" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C79" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D79" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="80" ht="12.75" customHeight="true">
@@ -2620,13 +2625,13 @@
         <v>77</v>
       </c>
       <c r="B80" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C80" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D80" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="81" ht="12.75" customHeight="true">
@@ -2634,13 +2639,13 @@
         <v>78</v>
       </c>
       <c r="B81" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C81" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D81" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="82" ht="12.75" customHeight="true">
@@ -2648,13 +2653,13 @@
         <v>79</v>
       </c>
       <c r="B82" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C82" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D82" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="83" ht="12.75" customHeight="true">
@@ -2662,13 +2667,13 @@
         <v>80</v>
       </c>
       <c r="B83" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C83" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D83" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="84" ht="12.75" customHeight="true">
@@ -2676,13 +2681,13 @@
         <v>81</v>
       </c>
       <c r="B84" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C84" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D84" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="85" ht="12.75" customHeight="true">
@@ -2690,13 +2695,13 @@
         <v>82</v>
       </c>
       <c r="B85" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C85" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D85" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="86" ht="12.75" customHeight="true">
@@ -2704,13 +2709,13 @@
         <v>83</v>
       </c>
       <c r="B86" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C86" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D86" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="87" ht="12.75" customHeight="true">
@@ -2718,13 +2723,13 @@
         <v>84</v>
       </c>
       <c r="B87" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C87" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D87" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="88" ht="12.75" customHeight="true">
@@ -2732,13 +2737,13 @@
         <v>85</v>
       </c>
       <c r="B88" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C88" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D88" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="89" ht="12.75" customHeight="true">
@@ -2746,13 +2751,13 @@
         <v>86</v>
       </c>
       <c r="B89" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C89" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D89" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="90" ht="12.75" customHeight="true">
@@ -2760,13 +2765,13 @@
         <v>87</v>
       </c>
       <c r="B90" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C90" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D90" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="91" ht="12.75" customHeight="true">
@@ -2774,13 +2779,13 @@
         <v>88</v>
       </c>
       <c r="B91" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C91" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D91" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="92" ht="12.75" customHeight="true">
@@ -2788,13 +2793,13 @@
         <v>89</v>
       </c>
       <c r="B92" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C92" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D92" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="93" ht="12.75" customHeight="true">
@@ -2802,13 +2807,13 @@
         <v>90</v>
       </c>
       <c r="B93" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C93" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D93" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="94" ht="12.75" customHeight="true"/>
@@ -3758,7 +3763,7 @@
     </row>
     <row r="6">
       <c r="E6" s="25" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
@@ -3777,7 +3782,7 @@
     </row>
     <row r="10">
       <c r="E10" s="25" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F10" s="24"/>
       <c r="G10" s="21"/>
@@ -3798,7 +3803,7 @@
     </row>
     <row r="14">
       <c r="E14" s="25" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I14" s="21"/>
       <c r="K14" s="21"/>
@@ -3819,7 +3824,7 @@
     </row>
     <row r="17">
       <c r="C17" s="25" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G17" s="21"/>
       <c r="K17" s="21"/>
@@ -3835,7 +3840,7 @@
     </row>
     <row r="19">
       <c r="C19" s="25" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D19" s="24"/>
       <c r="E19" s="21"/>
@@ -3851,7 +3856,7 @@
     </row>
     <row r="22">
       <c r="E22" s="25" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K22" s="21"/>
     </row>
@@ -3868,7 +3873,7 @@
     </row>
     <row r="25">
       <c r="C25" s="25" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G25" s="21"/>
       <c r="H25" s="23"/>
@@ -3887,7 +3892,7 @@
     </row>
     <row r="27">
       <c r="C27" s="25" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D27" s="24"/>
       <c r="E27" s="21"/>
@@ -3906,7 +3911,7 @@
     </row>
     <row r="30">
       <c r="E30" s="25" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I30" s="21"/>
     </row>
@@ -3924,7 +3929,7 @@
     </row>
     <row r="33">
       <c r="C33" s="25" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G33" s="21"/>
     </row>
@@ -3938,7 +3943,7 @@
     </row>
     <row r="35">
       <c r="C35" s="25" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D35" s="24"/>
       <c r="E35" s="21"/>
@@ -3986,7 +3991,7 @@
     </row>
     <row r="6">
       <c r="E6" s="25" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7">
@@ -4005,7 +4010,7 @@
     </row>
     <row r="10">
       <c r="E10" s="25" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F10" s="24"/>
       <c r="G10" s="21"/>
@@ -4026,7 +4031,7 @@
     </row>
     <row r="14">
       <c r="E14" s="25" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I14" s="21"/>
       <c r="K14" s="21"/>
@@ -4047,7 +4052,7 @@
     </row>
     <row r="17">
       <c r="C17" s="25" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G17" s="21"/>
       <c r="K17" s="21"/>
@@ -4063,7 +4068,7 @@
     </row>
     <row r="19">
       <c r="C19" s="25" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D19" s="24"/>
       <c r="E19" s="21"/>
@@ -4079,7 +4084,7 @@
     </row>
     <row r="22">
       <c r="E22" s="25" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K22" s="21"/>
     </row>
@@ -4096,7 +4101,7 @@
     </row>
     <row r="25">
       <c r="C25" s="25" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G25" s="21"/>
       <c r="H25" s="23"/>
@@ -4115,7 +4120,7 @@
     </row>
     <row r="27">
       <c r="C27" s="25" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D27" s="24"/>
       <c r="E27" s="21"/>
@@ -4134,7 +4139,7 @@
     </row>
     <row r="30">
       <c r="E30" s="25" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I30" s="21"/>
     </row>
@@ -4152,7 +4157,7 @@
     </row>
     <row r="33">
       <c r="C33" s="25" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G33" s="21"/>
     </row>
@@ -4166,7 +4171,7 @@
     </row>
     <row r="35">
       <c r="C35" s="25" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D35" s="24"/>
       <c r="E35" s="21"/>
@@ -4214,7 +4219,7 @@
     </row>
     <row r="6">
       <c r="E6" s="25" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7">
@@ -4233,7 +4238,7 @@
     </row>
     <row r="10">
       <c r="E10" s="25" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F10" s="24"/>
       <c r="G10" s="21"/>
@@ -4254,7 +4259,7 @@
     </row>
     <row r="14">
       <c r="E14" s="25" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I14" s="21"/>
       <c r="K14" s="21"/>
@@ -4275,7 +4280,7 @@
     </row>
     <row r="17">
       <c r="C17" s="25" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G17" s="21"/>
       <c r="K17" s="21"/>
@@ -4291,7 +4296,7 @@
     </row>
     <row r="19">
       <c r="C19" s="25" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D19" s="24"/>
       <c r="E19" s="21"/>
@@ -4307,7 +4312,7 @@
     </row>
     <row r="22">
       <c r="E22" s="25" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K22" s="21"/>
     </row>
@@ -4324,7 +4329,7 @@
     </row>
     <row r="25">
       <c r="C25" s="25" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G25" s="21"/>
       <c r="H25" s="23"/>
@@ -4343,7 +4348,7 @@
     </row>
     <row r="27">
       <c r="C27" s="25" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D27" s="24"/>
       <c r="E27" s="21"/>
@@ -4362,7 +4367,7 @@
     </row>
     <row r="30">
       <c r="E30" s="25" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I30" s="21"/>
     </row>
@@ -4380,7 +4385,7 @@
     </row>
     <row r="33">
       <c r="C33" s="25" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G33" s="21"/>
     </row>
@@ -4394,7 +4399,7 @@
     </row>
     <row r="35">
       <c r="C35" s="25" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D35" s="24"/>
       <c r="E35" s="21"/>
@@ -4442,7 +4447,7 @@
     </row>
     <row r="6">
       <c r="E6" s="25" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7">
@@ -4456,7 +4461,7 @@
     </row>
     <row r="9">
       <c r="C9" s="25" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G9" s="21"/>
       <c r="H9" s="23"/>
@@ -4473,7 +4478,7 @@
     </row>
     <row r="11">
       <c r="C11" s="25" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D11" s="24"/>
       <c r="E11" s="21"/>
@@ -4491,7 +4496,7 @@
     </row>
     <row r="14">
       <c r="E14" s="25" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I14" s="21"/>
       <c r="K14" s="21"/>
@@ -4512,7 +4517,7 @@
     </row>
     <row r="17">
       <c r="C17" s="25" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G17" s="21"/>
       <c r="K17" s="21"/>
@@ -4528,7 +4533,7 @@
     </row>
     <row r="19">
       <c r="C19" s="25" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D19" s="24"/>
       <c r="E19" s="21"/>
@@ -4544,7 +4549,7 @@
     </row>
     <row r="22">
       <c r="E22" s="25" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K22" s="21"/>
     </row>
@@ -4561,7 +4566,7 @@
     </row>
     <row r="25">
       <c r="C25" s="25" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G25" s="21"/>
       <c r="H25" s="23"/>
@@ -4580,7 +4585,7 @@
     </row>
     <row r="27">
       <c r="C27" s="25" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D27" s="24"/>
       <c r="E27" s="21"/>
@@ -4599,7 +4604,7 @@
     </row>
     <row r="30">
       <c r="E30" s="25" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I30" s="21"/>
     </row>
@@ -4617,7 +4622,7 @@
     </row>
     <row r="33">
       <c r="C33" s="25" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G33" s="21"/>
     </row>
@@ -4631,7 +4636,7 @@
     </row>
     <row r="35">
       <c r="C35" s="25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D35" s="24"/>
       <c r="E35" s="21"/>
@@ -4679,7 +4684,7 @@
     </row>
     <row r="6">
       <c r="E6" s="25" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7">
@@ -4698,7 +4703,7 @@
     </row>
     <row r="10">
       <c r="E10" s="25" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F10" s="24"/>
       <c r="G10" s="21"/>
@@ -4719,7 +4724,7 @@
     </row>
     <row r="14">
       <c r="E14" s="25" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I14" s="21"/>
       <c r="K14" s="21"/>
@@ -4740,7 +4745,7 @@
     </row>
     <row r="17">
       <c r="C17" s="25" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G17" s="21"/>
       <c r="K17" s="21"/>
@@ -4756,7 +4761,7 @@
     </row>
     <row r="19">
       <c r="C19" s="25" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D19" s="24"/>
       <c r="E19" s="21"/>
@@ -4772,7 +4777,7 @@
     </row>
     <row r="22">
       <c r="E22" s="25" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K22" s="21"/>
     </row>
@@ -4789,7 +4794,7 @@
     </row>
     <row r="25">
       <c r="C25" s="25" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G25" s="21"/>
       <c r="H25" s="23"/>
@@ -4808,7 +4813,7 @@
     </row>
     <row r="27">
       <c r="C27" s="25" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D27" s="24"/>
       <c r="E27" s="21"/>
@@ -4827,7 +4832,7 @@
     </row>
     <row r="30">
       <c r="E30" s="25" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I30" s="21"/>
     </row>
@@ -4845,7 +4850,7 @@
     </row>
     <row r="33">
       <c r="C33" s="25" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G33" s="21"/>
     </row>
@@ -4859,7 +4864,7 @@
     </row>
     <row r="35">
       <c r="C35" s="25" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D35" s="24"/>
       <c r="E35" s="21"/>
@@ -4907,7 +4912,7 @@
     </row>
     <row r="6">
       <c r="E6" s="25" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="7">
@@ -4921,7 +4926,7 @@
     </row>
     <row r="9">
       <c r="C9" s="25" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G9" s="21"/>
       <c r="H9" s="23"/>
@@ -4938,7 +4943,7 @@
     </row>
     <row r="11">
       <c r="C11" s="25" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D11" s="24"/>
       <c r="E11" s="21"/>
@@ -4956,7 +4961,7 @@
     </row>
     <row r="14">
       <c r="E14" s="25" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I14" s="21"/>
       <c r="K14" s="21"/>
@@ -4977,7 +4982,7 @@
     </row>
     <row r="17">
       <c r="C17" s="25" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G17" s="21"/>
       <c r="K17" s="21"/>
@@ -4993,7 +4998,7 @@
     </row>
     <row r="19">
       <c r="C19" s="25" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D19" s="24"/>
       <c r="E19" s="21"/>
@@ -5009,7 +5014,7 @@
     </row>
     <row r="22">
       <c r="E22" s="25" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K22" s="21"/>
     </row>
@@ -5026,7 +5031,7 @@
     </row>
     <row r="25">
       <c r="C25" s="25" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G25" s="21"/>
       <c r="H25" s="23"/>
@@ -5045,7 +5050,7 @@
     </row>
     <row r="27">
       <c r="C27" s="25" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D27" s="24"/>
       <c r="E27" s="21"/>
@@ -5064,7 +5069,7 @@
     </row>
     <row r="30">
       <c r="E30" s="25" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I30" s="21"/>
     </row>
@@ -5082,7 +5087,7 @@
     </row>
     <row r="33">
       <c r="C33" s="25" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G33" s="21"/>
     </row>
@@ -5096,7 +5101,7 @@
     </row>
     <row r="35">
       <c r="C35" s="25" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D35" s="24"/>
       <c r="E35" s="21"/>
@@ -5144,7 +5149,7 @@
     </row>
     <row r="6">
       <c r="E6" s="25" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="7">
@@ -5163,7 +5168,7 @@
     </row>
     <row r="10">
       <c r="E10" s="25" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F10" s="24"/>
       <c r="G10" s="21"/>
@@ -5184,7 +5189,7 @@
     </row>
     <row r="14">
       <c r="E14" s="25" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I14" s="21"/>
       <c r="K14" s="21"/>
@@ -5205,7 +5210,7 @@
     </row>
     <row r="17">
       <c r="C17" s="25" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G17" s="21"/>
       <c r="K17" s="21"/>
@@ -5221,7 +5226,7 @@
     </row>
     <row r="19">
       <c r="C19" s="25" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D19" s="24"/>
       <c r="E19" s="21"/>
@@ -5237,7 +5242,7 @@
     </row>
     <row r="22">
       <c r="E22" s="25" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K22" s="21"/>
     </row>
@@ -5254,7 +5259,7 @@
     </row>
     <row r="25">
       <c r="C25" s="25" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G25" s="21"/>
       <c r="H25" s="23"/>
@@ -5273,7 +5278,7 @@
     </row>
     <row r="27">
       <c r="C27" s="25" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D27" s="24"/>
       <c r="E27" s="21"/>
@@ -5292,7 +5297,7 @@
     </row>
     <row r="30">
       <c r="E30" s="25" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I30" s="21"/>
     </row>
@@ -5310,7 +5315,7 @@
     </row>
     <row r="33">
       <c r="C33" s="25" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G33" s="21"/>
     </row>
@@ -5324,7 +5329,7 @@
     </row>
     <row r="35">
       <c r="C35" s="25" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D35" s="24"/>
       <c r="E35" s="21"/>
@@ -5372,7 +5377,7 @@
     </row>
     <row r="6">
       <c r="E6" s="25" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="7">
@@ -5386,7 +5391,7 @@
     </row>
     <row r="9">
       <c r="C9" s="25" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G9" s="21"/>
       <c r="H9" s="23"/>
@@ -5403,7 +5408,7 @@
     </row>
     <row r="11">
       <c r="C11" s="25" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D11" s="24"/>
       <c r="E11" s="21"/>
@@ -5421,7 +5426,7 @@
     </row>
     <row r="14">
       <c r="E14" s="25" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I14" s="21"/>
       <c r="K14" s="21"/>
@@ -5442,7 +5447,7 @@
     </row>
     <row r="17">
       <c r="C17" s="25" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G17" s="21"/>
       <c r="K17" s="21"/>
@@ -5458,7 +5463,7 @@
     </row>
     <row r="19">
       <c r="C19" s="25" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D19" s="24"/>
       <c r="E19" s="21"/>
@@ -5474,7 +5479,7 @@
     </row>
     <row r="22">
       <c r="E22" s="25" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K22" s="21"/>
     </row>
@@ -5491,7 +5496,7 @@
     </row>
     <row r="25">
       <c r="C25" s="25" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G25" s="21"/>
       <c r="H25" s="23"/>
@@ -5510,7 +5515,7 @@
     </row>
     <row r="27">
       <c r="C27" s="25" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D27" s="24"/>
       <c r="E27" s="21"/>
@@ -5529,7 +5534,7 @@
     </row>
     <row r="30">
       <c r="E30" s="25" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I30" s="21"/>
     </row>
@@ -5547,7 +5552,7 @@
     </row>
     <row r="33">
       <c r="C33" s="25" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G33" s="21"/>
     </row>
@@ -5561,7 +5566,7 @@
     </row>
     <row r="35">
       <c r="C35" s="25" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D35" s="24"/>
       <c r="E35" s="21"/>
@@ -5787,18 +5792,19 @@
   <dimension ref="A1:O1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col customWidth="true" max="1" min="1" style="7" width="34"/>
-    <col customWidth="true" max="3" min="2" style="7" width="3.83203125"/>
+    <col customWidth="true" max="1" min="1" style="7" width="30"/>
+    <col customWidth="true" max="3" min="2" style="7" width="5"/>
     <col customWidth="true" max="4" min="4" style="7" width="3"/>
-    <col customWidth="true" max="6" min="5" style="7" width="3.83203125"/>
-    <col customWidth="true" max="7" min="7" style="7" width="34"/>
-    <col customWidth="true" max="8" min="8" style="7" width="3.83203125"/>
-    <col customWidth="true" max="9" min="9" style="7" width="34"/>
-    <col customWidth="true" max="11" min="10" style="7" width="3.83203125"/>
+    <col customWidth="true" max="6" min="5" style="7" width="5"/>
+    <col customWidth="true" max="7" min="7" style="7" width="30"/>
+    <col customWidth="true" max="8" min="8" style="7" width="2"/>
+    <col customWidth="true" max="9" min="9" style="7" width="30"/>
+    <col customWidth="true" max="11" min="10" style="7" width="5"/>
     <col customWidth="true" max="12" min="12" style="7" width="3"/>
-    <col customWidth="true" max="14" min="13" style="7" width="3.83203125"/>
-    <col customWidth="true" max="15" min="15" style="7" width="34"/>
-    <col max="16384" min="16" style="7" width="10.83203125"/>
+    <col customWidth="true" max="14" min="13" style="7" width="5"/>
+    <col customWidth="true" max="15" min="15" style="7" width="30"/>
+    <col customWidth="true" max="16" min="16" style="7" width="2"/>
+    <col max="16384" min="17" style="7" width="10.83203125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="17" thickBot="true">
@@ -5822,7 +5828,7 @@
     </row>
     <row r="3">
       <c r="A3" s="20" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B3" s="20"/>
       <c r="C3" s="20"/>
@@ -5831,7 +5837,7 @@
       <c r="F3" s="20"/>
       <c r="G3" s="20"/>
       <c r="I3" s="20" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J3" s="20"/>
       <c r="K3" s="20"/>
@@ -5842,22 +5848,22 @@
     </row>
     <row r="4">
       <c r="A4" s="29" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D4" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="G4" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="I4" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="G4" s="30" t="s">
+      <c r="L4" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="I4" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="L4" s="28" t="s">
-        <v>209</v>
-      </c>
       <c r="O4" s="30" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="5">
@@ -5886,27 +5892,27 @@
     </row>
     <row r="7">
       <c r="F7" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G7" s="24"/>
       <c r="N7" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O7" s="24"/>
     </row>
     <row r="8">
       <c r="F8" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G8" s="24"/>
       <c r="N8" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O8" s="24"/>
     </row>
     <row r="11">
       <c r="A11" s="20" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B11" s="20"/>
       <c r="C11" s="20"/>
@@ -5915,7 +5921,7 @@
       <c r="F11" s="20"/>
       <c r="G11" s="20"/>
       <c r="I11" s="20" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J11" s="20"/>
       <c r="K11" s="20"/>
@@ -5926,22 +5932,22 @@
     </row>
     <row r="12">
       <c r="A12" s="29" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D12" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="G12" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="I12" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="G12" s="30" t="s">
+      <c r="L12" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="I12" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="L12" s="28" t="s">
-        <v>209</v>
-      </c>
       <c r="O12" s="30" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13">
@@ -5970,27 +5976,27 @@
     </row>
     <row r="15">
       <c r="F15" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G15" s="24"/>
       <c r="N15" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O15" s="24"/>
     </row>
     <row r="16">
       <c r="F16" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G16" s="24"/>
       <c r="N16" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O16" s="24"/>
     </row>
     <row r="19">
       <c r="A19" s="20" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B19" s="20"/>
       <c r="C19" s="20"/>
@@ -5999,7 +6005,7 @@
       <c r="F19" s="20"/>
       <c r="G19" s="20"/>
       <c r="I19" s="20" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="J19" s="20"/>
       <c r="K19" s="20"/>
@@ -6010,22 +6016,22 @@
     </row>
     <row r="20">
       <c r="A20" s="29" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D20" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="G20" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="I20" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="G20" s="30" t="s">
+      <c r="L20" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="I20" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="L20" s="28" t="s">
-        <v>209</v>
-      </c>
       <c r="O20" s="30" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="21">
@@ -6054,27 +6060,27 @@
     </row>
     <row r="23">
       <c r="F23" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G23" s="24"/>
       <c r="N23" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O23" s="24"/>
     </row>
     <row r="24">
       <c r="F24" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G24" s="24"/>
       <c r="N24" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O24" s="24"/>
     </row>
     <row r="27">
       <c r="A27" s="20" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B27" s="20"/>
       <c r="C27" s="20"/>
@@ -6083,7 +6089,7 @@
       <c r="F27" s="20"/>
       <c r="G27" s="20"/>
       <c r="I27" s="20" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="J27" s="20"/>
       <c r="K27" s="20"/>
@@ -6094,22 +6100,22 @@
     </row>
     <row r="28">
       <c r="A28" s="29" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D28" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="G28" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="I28" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="G28" s="30" t="s">
+      <c r="L28" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="I28" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="L28" s="28" t="s">
-        <v>209</v>
-      </c>
       <c r="O28" s="30" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="29">
@@ -6138,27 +6144,27 @@
     </row>
     <row r="31">
       <c r="F31" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G31" s="24"/>
       <c r="N31" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O31" s="24"/>
     </row>
     <row r="32">
       <c r="F32" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G32" s="24"/>
       <c r="N32" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O32" s="24"/>
     </row>
     <row r="35">
       <c r="A35" s="20" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B35" s="20"/>
       <c r="C35" s="20"/>
@@ -6167,7 +6173,7 @@
       <c r="F35" s="20"/>
       <c r="G35" s="20"/>
       <c r="I35" s="20" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="J35" s="20"/>
       <c r="K35" s="20"/>
@@ -6178,22 +6184,22 @@
     </row>
     <row r="36">
       <c r="A36" s="29" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D36" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="G36" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="I36" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="G36" s="30" t="s">
+      <c r="L36" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="I36" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="L36" s="28" t="s">
-        <v>209</v>
-      </c>
       <c r="O36" s="30" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="37">
@@ -6222,27 +6228,27 @@
     </row>
     <row r="39">
       <c r="F39" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G39" s="24"/>
       <c r="N39" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O39" s="24"/>
     </row>
     <row r="40">
       <c r="F40" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G40" s="24"/>
       <c r="N40" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O40" s="24"/>
     </row>
     <row r="43">
       <c r="A43" s="20" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B43" s="20"/>
       <c r="C43" s="20"/>
@@ -6251,7 +6257,7 @@
       <c r="F43" s="20"/>
       <c r="G43" s="20"/>
       <c r="I43" s="20" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J43" s="20"/>
       <c r="K43" s="20"/>
@@ -6262,22 +6268,22 @@
     </row>
     <row r="44">
       <c r="A44" s="29" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D44" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="G44" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="I44" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="G44" s="30" t="s">
+      <c r="L44" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="I44" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="L44" s="28" t="s">
-        <v>209</v>
-      </c>
       <c r="O44" s="30" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="45">
@@ -6306,27 +6312,27 @@
     </row>
     <row r="47">
       <c r="F47" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G47" s="24"/>
       <c r="N47" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O47" s="24"/>
     </row>
     <row r="48">
       <c r="F48" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G48" s="24"/>
       <c r="N48" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O48" s="24"/>
     </row>
     <row r="51">
       <c r="A51" s="20" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B51" s="20"/>
       <c r="C51" s="20"/>
@@ -6335,7 +6341,7 @@
       <c r="F51" s="20"/>
       <c r="G51" s="20"/>
       <c r="I51" s="20" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="J51" s="20"/>
       <c r="K51" s="20"/>
@@ -6346,22 +6352,22 @@
     </row>
     <row r="52">
       <c r="A52" s="29" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D52" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="G52" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="I52" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="G52" s="30" t="s">
+      <c r="L52" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="I52" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="L52" s="28" t="s">
-        <v>209</v>
-      </c>
       <c r="O52" s="30" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="53">
@@ -6390,27 +6396,27 @@
     </row>
     <row r="55">
       <c r="F55" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G55" s="24"/>
       <c r="N55" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O55" s="24"/>
     </row>
     <row r="56">
       <c r="F56" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G56" s="24"/>
       <c r="N56" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O56" s="24"/>
     </row>
     <row r="59">
       <c r="A59" s="20" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B59" s="20"/>
       <c r="C59" s="20"/>
@@ -6419,7 +6425,7 @@
       <c r="F59" s="20"/>
       <c r="G59" s="20"/>
       <c r="I59" s="20" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="J59" s="20"/>
       <c r="K59" s="20"/>
@@ -6430,22 +6436,22 @@
     </row>
     <row r="60">
       <c r="A60" s="29" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D60" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="G60" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="I60" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="G60" s="30" t="s">
+      <c r="L60" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="I60" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="L60" s="28" t="s">
-        <v>209</v>
-      </c>
       <c r="O60" s="30" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="61">
@@ -6474,27 +6480,27 @@
     </row>
     <row r="63">
       <c r="F63" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G63" s="24"/>
       <c r="N63" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O63" s="24"/>
     </row>
     <row r="64">
       <c r="F64" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G64" s="24"/>
       <c r="N64" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O64" s="24"/>
     </row>
     <row r="67">
       <c r="A67" s="20" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B67" s="20"/>
       <c r="C67" s="20"/>
@@ -6503,7 +6509,7 @@
       <c r="F67" s="20"/>
       <c r="G67" s="20"/>
       <c r="I67" s="20" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="J67" s="20"/>
       <c r="K67" s="20"/>
@@ -6514,22 +6520,22 @@
     </row>
     <row r="68">
       <c r="A68" s="29" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D68" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="G68" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="I68" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="G68" s="30" t="s">
+      <c r="L68" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="I68" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="L68" s="28" t="s">
-        <v>209</v>
-      </c>
       <c r="O68" s="30" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="69">
@@ -6558,27 +6564,27 @@
     </row>
     <row r="71">
       <c r="F71" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G71" s="24"/>
       <c r="N71" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O71" s="24"/>
     </row>
     <row r="72">
       <c r="F72" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G72" s="24"/>
       <c r="N72" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O72" s="24"/>
     </row>
     <row r="75">
       <c r="A75" s="20" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B75" s="20"/>
       <c r="C75" s="20"/>
@@ -6587,7 +6593,7 @@
       <c r="F75" s="20"/>
       <c r="G75" s="20"/>
       <c r="I75" s="20" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="J75" s="20"/>
       <c r="K75" s="20"/>
@@ -6598,22 +6604,22 @@
     </row>
     <row r="76">
       <c r="A76" s="29" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D76" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="G76" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="I76" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="G76" s="30" t="s">
+      <c r="L76" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="I76" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="L76" s="28" t="s">
-        <v>209</v>
-      </c>
       <c r="O76" s="30" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="77">
@@ -6642,27 +6648,27 @@
     </row>
     <row r="79">
       <c r="F79" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G79" s="24"/>
       <c r="N79" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O79" s="24"/>
     </row>
     <row r="80">
       <c r="F80" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G80" s="24"/>
       <c r="N80" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O80" s="24"/>
     </row>
     <row r="83">
       <c r="A83" s="20" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B83" s="20"/>
       <c r="C83" s="20"/>
@@ -6671,7 +6677,7 @@
       <c r="F83" s="20"/>
       <c r="G83" s="20"/>
       <c r="I83" s="20" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="J83" s="20"/>
       <c r="K83" s="20"/>
@@ -6682,22 +6688,22 @@
     </row>
     <row r="84">
       <c r="A84" s="29" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D84" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="G84" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="I84" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="G84" s="30" t="s">
+      <c r="L84" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="I84" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="L84" s="28" t="s">
-        <v>209</v>
-      </c>
       <c r="O84" s="30" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="85">
@@ -6726,27 +6732,27 @@
     </row>
     <row r="87">
       <c r="F87" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G87" s="24"/>
       <c r="N87" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O87" s="24"/>
     </row>
     <row r="88">
       <c r="F88" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G88" s="24"/>
       <c r="N88" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O88" s="24"/>
     </row>
     <row r="91">
       <c r="A91" s="20" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B91" s="20"/>
       <c r="C91" s="20"/>
@@ -6755,7 +6761,7 @@
       <c r="F91" s="20"/>
       <c r="G91" s="20"/>
       <c r="I91" s="20" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="J91" s="20"/>
       <c r="K91" s="20"/>
@@ -6766,22 +6772,22 @@
     </row>
     <row r="92">
       <c r="A92" s="29" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D92" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="G92" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="I92" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="G92" s="30" t="s">
+      <c r="L92" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="I92" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="L92" s="28" t="s">
-        <v>209</v>
-      </c>
       <c r="O92" s="30" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="93">
@@ -6810,27 +6816,27 @@
     </row>
     <row r="95">
       <c r="F95" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G95" s="24"/>
       <c r="N95" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O95" s="24"/>
     </row>
     <row r="96">
       <c r="F96" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G96" s="24"/>
       <c r="N96" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O96" s="24"/>
     </row>
     <row r="99">
       <c r="A99" s="20" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B99" s="20"/>
       <c r="C99" s="20"/>
@@ -6839,7 +6845,7 @@
       <c r="F99" s="20"/>
       <c r="G99" s="20"/>
       <c r="I99" s="20" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="J99" s="20"/>
       <c r="K99" s="20"/>
@@ -6850,22 +6856,22 @@
     </row>
     <row r="100">
       <c r="A100" s="29" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D100" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="G100" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="I100" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="G100" s="30" t="s">
+      <c r="L100" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="I100" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="L100" s="28" t="s">
-        <v>209</v>
-      </c>
       <c r="O100" s="30" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="101">
@@ -6894,27 +6900,27 @@
     </row>
     <row r="103">
       <c r="F103" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G103" s="24"/>
       <c r="N103" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O103" s="24"/>
     </row>
     <row r="104">
       <c r="F104" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G104" s="24"/>
       <c r="N104" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O104" s="24"/>
     </row>
     <row r="107">
       <c r="A107" s="20" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B107" s="20"/>
       <c r="C107" s="20"/>
@@ -6925,13 +6931,13 @@
     </row>
     <row r="108">
       <c r="A108" s="29" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D108" s="28" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G108" s="30" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="109">
@@ -6949,19 +6955,19 @@
     </row>
     <row r="111">
       <c r="F111" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G111" s="24"/>
     </row>
     <row r="112">
       <c r="F112" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G112" s="24"/>
     </row>
     <row r="120">
       <c r="A120" s="20" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B120" s="20"/>
       <c r="C120" s="20"/>
@@ -6980,7 +6986,7 @@
     </row>
     <row r="122">
       <c r="A122" s="20" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B122" s="20"/>
       <c r="C122" s="20"/>
@@ -6989,7 +6995,7 @@
       <c r="F122" s="20"/>
       <c r="G122" s="20"/>
       <c r="I122" s="20" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="J122" s="20"/>
       <c r="K122" s="20"/>
@@ -7000,22 +7006,22 @@
     </row>
     <row r="123">
       <c r="A123" s="29" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D123" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="G123" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="I123" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="G123" s="30" t="s">
+      <c r="L123" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="I123" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="L123" s="28" t="s">
-        <v>209</v>
-      </c>
       <c r="O123" s="30" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="124">
@@ -7044,27 +7050,27 @@
     </row>
     <row r="126">
       <c r="F126" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G126" s="24"/>
       <c r="N126" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O126" s="24"/>
     </row>
     <row r="127">
       <c r="F127" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G127" s="24"/>
       <c r="N127" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O127" s="24"/>
     </row>
     <row r="130">
       <c r="A130" s="20" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B130" s="20"/>
       <c r="C130" s="20"/>
@@ -7073,7 +7079,7 @@
       <c r="F130" s="20"/>
       <c r="G130" s="20"/>
       <c r="I130" s="20" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="J130" s="20"/>
       <c r="K130" s="20"/>
@@ -7084,22 +7090,22 @@
     </row>
     <row r="131">
       <c r="A131" s="29" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D131" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="G131" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="I131" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="G131" s="30" t="s">
+      <c r="L131" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="I131" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="L131" s="28" t="s">
-        <v>209</v>
-      </c>
       <c r="O131" s="30" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="132">
@@ -7128,27 +7134,27 @@
     </row>
     <row r="134">
       <c r="F134" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G134" s="24"/>
       <c r="N134" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O134" s="24"/>
     </row>
     <row r="135">
       <c r="F135" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G135" s="24"/>
       <c r="N135" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O135" s="24"/>
     </row>
     <row r="138">
       <c r="A138" s="20" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B138" s="20"/>
       <c r="C138" s="20"/>
@@ -7157,7 +7163,7 @@
       <c r="F138" s="20"/>
       <c r="G138" s="20"/>
       <c r="I138" s="20" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="J138" s="20"/>
       <c r="K138" s="20"/>
@@ -7168,22 +7174,22 @@
     </row>
     <row r="139">
       <c r="A139" s="29" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D139" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="G139" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="I139" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="G139" s="30" t="s">
+      <c r="L139" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="I139" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="L139" s="28" t="s">
-        <v>209</v>
-      </c>
       <c r="O139" s="30" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="140">
@@ -7212,27 +7218,27 @@
     </row>
     <row r="142">
       <c r="F142" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G142" s="24"/>
       <c r="N142" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O142" s="24"/>
     </row>
     <row r="143">
       <c r="F143" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G143" s="24"/>
       <c r="N143" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O143" s="24"/>
     </row>
     <row r="146">
       <c r="A146" s="20" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B146" s="20"/>
       <c r="C146" s="20"/>
@@ -7241,7 +7247,7 @@
       <c r="F146" s="20"/>
       <c r="G146" s="20"/>
       <c r="I146" s="20" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="J146" s="20"/>
       <c r="K146" s="20"/>
@@ -7252,22 +7258,22 @@
     </row>
     <row r="147">
       <c r="A147" s="29" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D147" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="G147" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="I147" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="G147" s="30" t="s">
+      <c r="L147" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="I147" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="L147" s="28" t="s">
-        <v>209</v>
-      </c>
       <c r="O147" s="30" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="148">
@@ -7296,27 +7302,27 @@
     </row>
     <row r="150">
       <c r="F150" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G150" s="24"/>
       <c r="N150" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O150" s="24"/>
     </row>
     <row r="151">
       <c r="F151" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G151" s="24"/>
       <c r="N151" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O151" s="24"/>
     </row>
     <row r="154">
       <c r="A154" s="20" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B154" s="20"/>
       <c r="C154" s="20"/>
@@ -7325,7 +7331,7 @@
       <c r="F154" s="20"/>
       <c r="G154" s="20"/>
       <c r="I154" s="20" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="J154" s="20"/>
       <c r="K154" s="20"/>
@@ -7336,22 +7342,22 @@
     </row>
     <row r="155">
       <c r="A155" s="29" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D155" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="G155" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="I155" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="G155" s="30" t="s">
+      <c r="L155" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="I155" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="L155" s="28" t="s">
-        <v>209</v>
-      </c>
       <c r="O155" s="30" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="156">
@@ -7380,27 +7386,27 @@
     </row>
     <row r="158">
       <c r="F158" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G158" s="24"/>
       <c r="N158" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O158" s="24"/>
     </row>
     <row r="159">
       <c r="F159" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G159" s="24"/>
       <c r="N159" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O159" s="24"/>
     </row>
     <row r="162">
       <c r="A162" s="20" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B162" s="20"/>
       <c r="C162" s="20"/>
@@ -7409,7 +7415,7 @@
       <c r="F162" s="20"/>
       <c r="G162" s="20"/>
       <c r="I162" s="20" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="J162" s="20"/>
       <c r="K162" s="20"/>
@@ -7420,22 +7426,22 @@
     </row>
     <row r="163">
       <c r="A163" s="29" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D163" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="G163" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="I163" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="G163" s="30" t="s">
+      <c r="L163" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="I163" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="L163" s="28" t="s">
-        <v>209</v>
-      </c>
       <c r="O163" s="30" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="164">
@@ -7464,27 +7470,27 @@
     </row>
     <row r="166">
       <c r="F166" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G166" s="24"/>
       <c r="N166" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O166" s="24"/>
     </row>
     <row r="167">
       <c r="F167" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G167" s="24"/>
       <c r="N167" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O167" s="24"/>
     </row>
     <row r="170">
       <c r="A170" s="20" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B170" s="20"/>
       <c r="C170" s="20"/>
@@ -7493,7 +7499,7 @@
       <c r="F170" s="20"/>
       <c r="G170" s="20"/>
       <c r="I170" s="20" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="J170" s="20"/>
       <c r="K170" s="20"/>
@@ -7504,22 +7510,22 @@
     </row>
     <row r="171">
       <c r="A171" s="29" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D171" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="G171" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="I171" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="G171" s="30" t="s">
+      <c r="L171" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="I171" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="L171" s="28" t="s">
-        <v>209</v>
-      </c>
       <c r="O171" s="30" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="172">
@@ -7548,27 +7554,27 @@
     </row>
     <row r="174">
       <c r="F174" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G174" s="24"/>
       <c r="N174" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O174" s="24"/>
     </row>
     <row r="175">
       <c r="F175" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G175" s="24"/>
       <c r="N175" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O175" s="24"/>
     </row>
     <row r="178">
       <c r="A178" s="20" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B178" s="20"/>
       <c r="C178" s="20"/>
@@ -7577,7 +7583,7 @@
       <c r="F178" s="20"/>
       <c r="G178" s="20"/>
       <c r="I178" s="20" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="J178" s="20"/>
       <c r="K178" s="20"/>
@@ -7588,22 +7594,22 @@
     </row>
     <row r="179">
       <c r="A179" s="29" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D179" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="G179" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="I179" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="G179" s="30" t="s">
+      <c r="L179" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="I179" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="L179" s="28" t="s">
-        <v>209</v>
-      </c>
       <c r="O179" s="30" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="180">
@@ -7632,27 +7638,27 @@
     </row>
     <row r="182">
       <c r="F182" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G182" s="24"/>
       <c r="N182" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O182" s="24"/>
     </row>
     <row r="183">
       <c r="F183" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G183" s="24"/>
       <c r="N183" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O183" s="24"/>
     </row>
     <row r="186">
       <c r="A186" s="20" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B186" s="20"/>
       <c r="C186" s="20"/>
@@ -7661,7 +7667,7 @@
       <c r="F186" s="20"/>
       <c r="G186" s="20"/>
       <c r="I186" s="20" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="J186" s="20"/>
       <c r="K186" s="20"/>
@@ -7672,22 +7678,22 @@
     </row>
     <row r="187">
       <c r="A187" s="29" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D187" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="G187" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="I187" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="G187" s="30" t="s">
+      <c r="L187" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="I187" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="L187" s="28" t="s">
-        <v>209</v>
-      </c>
       <c r="O187" s="30" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="188">
@@ -7716,27 +7722,27 @@
     </row>
     <row r="190">
       <c r="F190" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G190" s="24"/>
       <c r="N190" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O190" s="24"/>
     </row>
     <row r="191">
       <c r="F191" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G191" s="24"/>
       <c r="N191" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O191" s="24"/>
     </row>
     <row r="194">
       <c r="A194" s="20" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B194" s="20"/>
       <c r="C194" s="20"/>
@@ -7745,7 +7751,7 @@
       <c r="F194" s="20"/>
       <c r="G194" s="20"/>
       <c r="I194" s="20" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="J194" s="20"/>
       <c r="K194" s="20"/>
@@ -7756,22 +7762,22 @@
     </row>
     <row r="195">
       <c r="A195" s="29" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D195" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="G195" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="I195" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="G195" s="30" t="s">
+      <c r="L195" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="I195" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="L195" s="28" t="s">
-        <v>209</v>
-      </c>
       <c r="O195" s="30" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="196">
@@ -7800,27 +7806,27 @@
     </row>
     <row r="198">
       <c r="F198" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G198" s="24"/>
       <c r="N198" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O198" s="24"/>
     </row>
     <row r="199">
       <c r="F199" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G199" s="24"/>
       <c r="N199" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O199" s="24"/>
     </row>
     <row r="202">
       <c r="A202" s="20" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B202" s="20"/>
       <c r="C202" s="20"/>
@@ -7829,7 +7835,7 @@
       <c r="F202" s="20"/>
       <c r="G202" s="20"/>
       <c r="I202" s="20" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="J202" s="20"/>
       <c r="K202" s="20"/>
@@ -7840,22 +7846,22 @@
     </row>
     <row r="203">
       <c r="A203" s="29" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D203" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="G203" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="I203" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="G203" s="30" t="s">
+      <c r="L203" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="I203" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="L203" s="28" t="s">
-        <v>209</v>
-      </c>
       <c r="O203" s="30" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="204">
@@ -7884,27 +7890,27 @@
     </row>
     <row r="206">
       <c r="F206" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G206" s="24"/>
       <c r="N206" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O206" s="24"/>
     </row>
     <row r="207">
       <c r="F207" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G207" s="24"/>
       <c r="N207" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O207" s="24"/>
     </row>
     <row r="210">
       <c r="A210" s="20" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B210" s="20"/>
       <c r="C210" s="20"/>
@@ -7913,7 +7919,7 @@
       <c r="F210" s="20"/>
       <c r="G210" s="20"/>
       <c r="I210" s="20" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="J210" s="20"/>
       <c r="K210" s="20"/>
@@ -7924,22 +7930,22 @@
     </row>
     <row r="211">
       <c r="A211" s="29" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D211" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="G211" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="I211" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="G211" s="30" t="s">
+      <c r="L211" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="I211" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="L211" s="28" t="s">
-        <v>209</v>
-      </c>
       <c r="O211" s="30" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="212">
@@ -7968,27 +7974,27 @@
     </row>
     <row r="214">
       <c r="F214" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G214" s="24"/>
       <c r="N214" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O214" s="24"/>
     </row>
     <row r="215">
       <c r="F215" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G215" s="24"/>
       <c r="N215" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O215" s="24"/>
     </row>
     <row r="218">
       <c r="A218" s="20" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B218" s="20"/>
       <c r="C218" s="20"/>
@@ -7997,7 +8003,7 @@
       <c r="F218" s="20"/>
       <c r="G218" s="20"/>
       <c r="I218" s="20" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="J218" s="20"/>
       <c r="K218" s="20"/>
@@ -8008,22 +8014,22 @@
     </row>
     <row r="219">
       <c r="A219" s="29" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D219" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="G219" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="I219" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="G219" s="30" t="s">
+      <c r="L219" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="I219" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="L219" s="28" t="s">
-        <v>209</v>
-      </c>
       <c r="O219" s="30" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="220">
@@ -8052,27 +8058,27 @@
     </row>
     <row r="222">
       <c r="F222" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G222" s="24"/>
       <c r="N222" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O222" s="24"/>
     </row>
     <row r="223">
       <c r="F223" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G223" s="24"/>
       <c r="N223" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O223" s="24"/>
     </row>
     <row r="226">
       <c r="A226" s="20" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B226" s="20"/>
       <c r="C226" s="20"/>
@@ -8081,7 +8087,7 @@
       <c r="F226" s="20"/>
       <c r="G226" s="20"/>
       <c r="I226" s="20" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="J226" s="20"/>
       <c r="K226" s="20"/>
@@ -8092,22 +8098,22 @@
     </row>
     <row r="227">
       <c r="A227" s="29" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D227" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="G227" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="I227" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="G227" s="30" t="s">
+      <c r="L227" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="I227" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="L227" s="28" t="s">
-        <v>209</v>
-      </c>
       <c r="O227" s="30" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="228">
@@ -8136,27 +8142,27 @@
     </row>
     <row r="230">
       <c r="F230" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G230" s="24"/>
       <c r="N230" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O230" s="24"/>
     </row>
     <row r="231">
       <c r="F231" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G231" s="24"/>
       <c r="N231" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O231" s="24"/>
     </row>
     <row r="234">
       <c r="A234" s="20" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B234" s="20"/>
       <c r="C234" s="20"/>
@@ -8165,7 +8171,7 @@
       <c r="F234" s="20"/>
       <c r="G234" s="20"/>
       <c r="I234" s="20" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="J234" s="20"/>
       <c r="K234" s="20"/>
@@ -8176,22 +8182,22 @@
     </row>
     <row r="235">
       <c r="A235" s="29" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D235" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="G235" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="I235" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="G235" s="30" t="s">
+      <c r="L235" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="I235" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="L235" s="28" t="s">
-        <v>209</v>
-      </c>
       <c r="O235" s="30" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="236">
@@ -8220,27 +8226,27 @@
     </row>
     <row r="238">
       <c r="F238" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G238" s="24"/>
       <c r="N238" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O238" s="24"/>
     </row>
     <row r="239">
       <c r="F239" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G239" s="24"/>
       <c r="N239" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O239" s="24"/>
     </row>
     <row r="242">
       <c r="A242" s="20" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B242" s="20"/>
       <c r="C242" s="20"/>
@@ -8249,7 +8255,7 @@
       <c r="F242" s="20"/>
       <c r="G242" s="20"/>
       <c r="I242" s="20" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="J242" s="20"/>
       <c r="K242" s="20"/>
@@ -8260,22 +8266,22 @@
     </row>
     <row r="243">
       <c r="A243" s="29" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D243" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="G243" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="I243" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="G243" s="30" t="s">
+      <c r="L243" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="I243" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="L243" s="28" t="s">
-        <v>209</v>
-      </c>
       <c r="O243" s="30" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="244">
@@ -8304,27 +8310,27 @@
     </row>
     <row r="246">
       <c r="F246" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G246" s="24"/>
       <c r="N246" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O246" s="24"/>
     </row>
     <row r="247">
       <c r="F247" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G247" s="24"/>
       <c r="N247" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O247" s="24"/>
     </row>
     <row r="255">
       <c r="A255" s="20" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B255" s="20"/>
       <c r="C255" s="20"/>
@@ -8343,7 +8349,7 @@
     </row>
     <row r="257">
       <c r="A257" s="20" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B257" s="20"/>
       <c r="C257" s="20"/>
@@ -8352,7 +8358,7 @@
       <c r="F257" s="20"/>
       <c r="G257" s="20"/>
       <c r="I257" s="20" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="J257" s="20"/>
       <c r="K257" s="20"/>
@@ -8363,22 +8369,22 @@
     </row>
     <row r="258">
       <c r="A258" s="29" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D258" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="G258" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="I258" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="G258" s="30" t="s">
+      <c r="L258" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="I258" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="L258" s="28" t="s">
-        <v>209</v>
-      </c>
       <c r="O258" s="30" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="259">
@@ -8407,27 +8413,27 @@
     </row>
     <row r="261">
       <c r="F261" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G261" s="24"/>
       <c r="N261" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O261" s="24"/>
     </row>
     <row r="262">
       <c r="F262" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G262" s="24"/>
       <c r="N262" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O262" s="24"/>
     </row>
     <row r="265">
       <c r="A265" s="20" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B265" s="20"/>
       <c r="C265" s="20"/>
@@ -8436,7 +8442,7 @@
       <c r="F265" s="20"/>
       <c r="G265" s="20"/>
       <c r="I265" s="20" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="J265" s="20"/>
       <c r="K265" s="20"/>
@@ -8447,22 +8453,22 @@
     </row>
     <row r="266">
       <c r="A266" s="29" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D266" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="G266" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="I266" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="G266" s="30" t="s">
+      <c r="L266" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="I266" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="L266" s="28" t="s">
-        <v>209</v>
-      </c>
       <c r="O266" s="30" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="267">
@@ -8491,27 +8497,27 @@
     </row>
     <row r="269">
       <c r="F269" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G269" s="24"/>
       <c r="N269" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O269" s="24"/>
     </row>
     <row r="270">
       <c r="F270" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G270" s="24"/>
       <c r="N270" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O270" s="24"/>
     </row>
     <row r="273">
       <c r="A273" s="20" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B273" s="20"/>
       <c r="C273" s="20"/>
@@ -8520,7 +8526,7 @@
       <c r="F273" s="20"/>
       <c r="G273" s="20"/>
       <c r="I273" s="20" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="J273" s="20"/>
       <c r="K273" s="20"/>
@@ -8531,22 +8537,22 @@
     </row>
     <row r="274">
       <c r="A274" s="29" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D274" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="G274" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="I274" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="G274" s="30" t="s">
+      <c r="L274" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="I274" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="L274" s="28" t="s">
-        <v>209</v>
-      </c>
       <c r="O274" s="30" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="275">
@@ -8575,27 +8581,27 @@
     </row>
     <row r="277">
       <c r="F277" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G277" s="24"/>
       <c r="N277" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O277" s="24"/>
     </row>
     <row r="278">
       <c r="F278" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G278" s="24"/>
       <c r="N278" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O278" s="24"/>
     </row>
     <row r="281">
       <c r="A281" s="20" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B281" s="20"/>
       <c r="C281" s="20"/>
@@ -8604,7 +8610,7 @@
       <c r="F281" s="20"/>
       <c r="G281" s="20"/>
       <c r="I281" s="20" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J281" s="20"/>
       <c r="K281" s="20"/>
@@ -8615,22 +8621,22 @@
     </row>
     <row r="282">
       <c r="A282" s="29" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D282" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="G282" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="I282" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="G282" s="30" t="s">
+      <c r="L282" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="I282" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="L282" s="28" t="s">
-        <v>209</v>
-      </c>
       <c r="O282" s="30" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="283">
@@ -8659,27 +8665,27 @@
     </row>
     <row r="285">
       <c r="F285" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G285" s="24"/>
       <c r="N285" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O285" s="24"/>
     </row>
     <row r="286">
       <c r="F286" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G286" s="24"/>
       <c r="N286" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O286" s="24"/>
     </row>
     <row r="289">
       <c r="A289" s="20" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B289" s="20"/>
       <c r="C289" s="20"/>
@@ -8688,7 +8694,7 @@
       <c r="F289" s="20"/>
       <c r="G289" s="20"/>
       <c r="I289" s="20" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="J289" s="20"/>
       <c r="K289" s="20"/>
@@ -8699,22 +8705,22 @@
     </row>
     <row r="290">
       <c r="A290" s="29" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D290" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="G290" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="I290" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="G290" s="30" t="s">
+      <c r="L290" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="I290" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="L290" s="28" t="s">
-        <v>209</v>
-      </c>
       <c r="O290" s="30" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="291">
@@ -8743,27 +8749,27 @@
     </row>
     <row r="293">
       <c r="F293" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G293" s="24"/>
       <c r="N293" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O293" s="24"/>
     </row>
     <row r="294">
       <c r="F294" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G294" s="24"/>
       <c r="N294" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O294" s="24"/>
     </row>
     <row r="297">
       <c r="A297" s="20" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B297" s="20"/>
       <c r="C297" s="20"/>
@@ -8772,7 +8778,7 @@
       <c r="F297" s="20"/>
       <c r="G297" s="20"/>
       <c r="I297" s="20" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="J297" s="20"/>
       <c r="K297" s="20"/>
@@ -8783,22 +8789,22 @@
     </row>
     <row r="298">
       <c r="A298" s="29" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D298" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="G298" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="I298" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="G298" s="30" t="s">
+      <c r="L298" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="I298" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="L298" s="28" t="s">
-        <v>209</v>
-      </c>
       <c r="O298" s="30" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="299">
@@ -8827,27 +8833,27 @@
     </row>
     <row r="301">
       <c r="F301" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G301" s="24"/>
       <c r="N301" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O301" s="24"/>
     </row>
     <row r="302">
       <c r="F302" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G302" s="24"/>
       <c r="N302" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O302" s="24"/>
     </row>
     <row r="305">
       <c r="A305" s="20" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B305" s="20"/>
       <c r="C305" s="20"/>
@@ -8856,7 +8862,7 @@
       <c r="F305" s="20"/>
       <c r="G305" s="20"/>
       <c r="I305" s="20" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="J305" s="20"/>
       <c r="K305" s="20"/>
@@ -8867,22 +8873,22 @@
     </row>
     <row r="306">
       <c r="A306" s="29" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D306" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="G306" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="I306" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="G306" s="30" t="s">
+      <c r="L306" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="I306" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="L306" s="28" t="s">
-        <v>209</v>
-      </c>
       <c r="O306" s="30" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="307">
@@ -8911,27 +8917,27 @@
     </row>
     <row r="309">
       <c r="F309" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G309" s="24"/>
       <c r="N309" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O309" s="24"/>
     </row>
     <row r="310">
       <c r="F310" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G310" s="24"/>
       <c r="N310" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O310" s="24"/>
     </row>
     <row r="313">
       <c r="A313" s="20" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B313" s="20"/>
       <c r="C313" s="20"/>
@@ -8940,7 +8946,7 @@
       <c r="F313" s="20"/>
       <c r="G313" s="20"/>
       <c r="I313" s="20" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="J313" s="20"/>
       <c r="K313" s="20"/>
@@ -8951,22 +8957,22 @@
     </row>
     <row r="314">
       <c r="A314" s="29" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D314" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="G314" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="I314" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="G314" s="30" t="s">
+      <c r="L314" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="I314" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="L314" s="28" t="s">
-        <v>209</v>
-      </c>
       <c r="O314" s="30" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="315">
@@ -8995,27 +9001,27 @@
     </row>
     <row r="317">
       <c r="F317" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G317" s="24"/>
       <c r="N317" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O317" s="24"/>
     </row>
     <row r="318">
       <c r="F318" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G318" s="24"/>
       <c r="N318" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O318" s="24"/>
     </row>
     <row r="326">
       <c r="A326" s="20" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B326" s="20"/>
       <c r="C326" s="20"/>
@@ -9034,7 +9040,7 @@
     </row>
     <row r="328">
       <c r="A328" s="20" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B328" s="20"/>
       <c r="C328" s="20"/>
@@ -9043,7 +9049,7 @@
       <c r="F328" s="20"/>
       <c r="G328" s="20"/>
       <c r="I328" s="20" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="J328" s="20"/>
       <c r="K328" s="20"/>
@@ -9054,22 +9060,22 @@
     </row>
     <row r="329">
       <c r="A329" s="29" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D329" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="G329" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="I329" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="G329" s="30" t="s">
+      <c r="L329" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="I329" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="L329" s="28" t="s">
-        <v>209</v>
-      </c>
       <c r="O329" s="30" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="330">
@@ -9098,27 +9104,27 @@
     </row>
     <row r="332">
       <c r="F332" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G332" s="24"/>
       <c r="N332" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O332" s="24"/>
     </row>
     <row r="333">
       <c r="F333" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G333" s="24"/>
       <c r="N333" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O333" s="24"/>
     </row>
     <row r="336">
       <c r="A336" s="20" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B336" s="20"/>
       <c r="C336" s="20"/>
@@ -9127,7 +9133,7 @@
       <c r="F336" s="20"/>
       <c r="G336" s="20"/>
       <c r="I336" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="J336" s="20"/>
       <c r="K336" s="20"/>
@@ -9138,22 +9144,22 @@
     </row>
     <row r="337">
       <c r="A337" s="29" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D337" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="G337" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="I337" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="G337" s="30" t="s">
+      <c r="L337" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="I337" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="L337" s="28" t="s">
-        <v>209</v>
-      </c>
       <c r="O337" s="30" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="338">
@@ -9182,27 +9188,27 @@
     </row>
     <row r="340">
       <c r="F340" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G340" s="24"/>
       <c r="N340" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O340" s="24"/>
     </row>
     <row r="341">
       <c r="F341" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G341" s="24"/>
       <c r="N341" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O341" s="24"/>
     </row>
     <row r="344">
       <c r="A344" s="20" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B344" s="20"/>
       <c r="C344" s="20"/>
@@ -9211,7 +9217,7 @@
       <c r="F344" s="20"/>
       <c r="G344" s="20"/>
       <c r="I344" s="20" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="J344" s="20"/>
       <c r="K344" s="20"/>
@@ -9222,22 +9228,22 @@
     </row>
     <row r="345">
       <c r="A345" s="29" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D345" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="G345" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="I345" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="G345" s="30" t="s">
+      <c r="L345" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="I345" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="L345" s="28" t="s">
-        <v>209</v>
-      </c>
       <c r="O345" s="30" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="346">
@@ -9266,27 +9272,27 @@
     </row>
     <row r="348">
       <c r="F348" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G348" s="24"/>
       <c r="N348" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O348" s="24"/>
     </row>
     <row r="349">
       <c r="F349" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G349" s="24"/>
       <c r="N349" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O349" s="24"/>
     </row>
     <row r="352">
       <c r="A352" s="20" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B352" s="20"/>
       <c r="C352" s="20"/>
@@ -9295,7 +9301,7 @@
       <c r="F352" s="20"/>
       <c r="G352" s="20"/>
       <c r="I352" s="20" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="J352" s="20"/>
       <c r="K352" s="20"/>
@@ -9306,22 +9312,22 @@
     </row>
     <row r="353">
       <c r="A353" s="29" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D353" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="G353" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="I353" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="G353" s="30" t="s">
+      <c r="L353" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="I353" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="L353" s="28" t="s">
-        <v>209</v>
-      </c>
       <c r="O353" s="30" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="354">
@@ -9350,27 +9356,27 @@
     </row>
     <row r="356">
       <c r="F356" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G356" s="24"/>
       <c r="N356" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O356" s="24"/>
     </row>
     <row r="357">
       <c r="F357" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G357" s="24"/>
       <c r="N357" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O357" s="24"/>
     </row>
     <row r="365">
       <c r="A365" s="20" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B365" s="20"/>
       <c r="C365" s="20"/>
@@ -9389,7 +9395,7 @@
     </row>
     <row r="367">
       <c r="A367" s="20" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B367" s="20"/>
       <c r="C367" s="20"/>
@@ -9398,7 +9404,7 @@
       <c r="F367" s="20"/>
       <c r="G367" s="20"/>
       <c r="I367" s="20" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J367" s="20"/>
       <c r="K367" s="20"/>
@@ -9409,22 +9415,22 @@
     </row>
     <row r="368">
       <c r="A368" s="29" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D368" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="G368" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="I368" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="G368" s="30" t="s">
+      <c r="L368" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="I368" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="L368" s="28" t="s">
-        <v>209</v>
-      </c>
       <c r="O368" s="30" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="369">
@@ -9453,27 +9459,27 @@
     </row>
     <row r="371">
       <c r="F371" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G371" s="24"/>
       <c r="N371" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O371" s="24"/>
     </row>
     <row r="372">
       <c r="F372" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G372" s="24"/>
       <c r="N372" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O372" s="24"/>
     </row>
     <row r="375">
       <c r="A375" s="20" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B375" s="20"/>
       <c r="C375" s="20"/>
@@ -9482,7 +9488,7 @@
       <c r="F375" s="20"/>
       <c r="G375" s="20"/>
       <c r="I375" s="20" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J375" s="20"/>
       <c r="K375" s="20"/>
@@ -9493,22 +9499,22 @@
     </row>
     <row r="376">
       <c r="A376" s="29" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D376" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="G376" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="I376" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="G376" s="30" t="s">
+      <c r="L376" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="I376" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="L376" s="28" t="s">
-        <v>209</v>
-      </c>
       <c r="O376" s="30" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="377">
@@ -9537,27 +9543,27 @@
     </row>
     <row r="379">
       <c r="F379" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G379" s="24"/>
       <c r="N379" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O379" s="24"/>
     </row>
     <row r="380">
       <c r="F380" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G380" s="24"/>
       <c r="N380" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O380" s="24"/>
     </row>
     <row r="388">
       <c r="A388" s="20" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B388" s="20"/>
       <c r="C388" s="20"/>
@@ -9576,7 +9582,7 @@
     </row>
     <row r="390">
       <c r="A390" s="20" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B390" s="20"/>
       <c r="C390" s="20"/>
@@ -9585,7 +9591,7 @@
       <c r="F390" s="20"/>
       <c r="G390" s="20"/>
       <c r="I390" s="20" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J390" s="20"/>
       <c r="K390" s="20"/>
@@ -9596,22 +9602,22 @@
     </row>
     <row r="391">
       <c r="A391" s="29" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D391" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="G391" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="I391" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="G391" s="30" t="s">
+      <c r="L391" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="I391" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="L391" s="28" t="s">
-        <v>209</v>
-      </c>
       <c r="O391" s="30" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="392">
@@ -9640,27 +9646,27 @@
     </row>
     <row r="394">
       <c r="F394" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G394" s="24"/>
       <c r="N394" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O394" s="24"/>
     </row>
     <row r="395">
       <c r="F395" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G395" s="24"/>
       <c r="N395" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O395" s="24"/>
     </row>
     <row r="403">
       <c r="A403" s="20" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B403" s="20"/>
       <c r="C403" s="20"/>
@@ -9679,7 +9685,7 @@
     </row>
     <row r="405">
       <c r="A405" s="20" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B405" s="20"/>
       <c r="C405" s="20"/>
@@ -9690,13 +9696,13 @@
     </row>
     <row r="406">
       <c r="A406" s="29" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D406" s="28" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G406" s="30" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="407">
@@ -9714,13 +9720,13 @@
     </row>
     <row r="409">
       <c r="F409" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G409" s="24"/>
     </row>
     <row r="410">
       <c r="F410" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G410" s="24"/>
     </row>

--- a/playoffs-example-large.xlsx
+++ b/playoffs-example-large.xlsx
@@ -678,13 +678,13 @@
     <t>Match 1</t>
   </si>
   <si>
+    <t>White</t>
+  </si>
+  <si>
+    <t>vs</t>
+  </si>
+  <si>
     <t>Red</t>
-  </si>
-  <si>
-    <t>vs</t>
-  </si>
-  <si>
-    <t>White</t>
   </si>
   <si>
     <t>1.</t>
@@ -5847,28 +5847,28 @@
       <c r="O3" s="20"/>
     </row>
     <row r="4">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="30" t="s">
         <v>209</v>
       </c>
       <c r="D4" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="G4" s="30" t="s">
+      <c r="G4" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="I4" s="29" t="s">
+      <c r="I4" s="30" t="s">
         <v>209</v>
       </c>
       <c r="L4" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="O4" s="30" t="s">
+      <c r="O4" s="29" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="28" t="str">
-        <f>'data'!$B$6</f>
+        <f>'data'!$B$35</f>
       </c>
       <c r="B5" s="28"/>
       <c r="C5" s="28"/>
@@ -5876,10 +5876,10 @@
       <c r="E5" s="28"/>
       <c r="F5" s="28"/>
       <c r="G5" s="28" t="str">
-        <f>'data'!$B$35</f>
+        <f>'data'!$B$6</f>
       </c>
       <c r="I5" s="28" t="str">
-        <f>'data'!$B$37</f>
+        <f>'data'!$B$38</f>
       </c>
       <c r="J5" s="28"/>
       <c r="K5" s="28"/>
@@ -5887,7 +5887,7 @@
       <c r="M5" s="28"/>
       <c r="N5" s="28"/>
       <c r="O5" s="28" t="str">
-        <f>'data'!$B$38</f>
+        <f>'data'!$B$37</f>
       </c>
     </row>
     <row r="7">
@@ -5931,28 +5931,28 @@
       <c r="O11" s="20"/>
     </row>
     <row r="12">
-      <c r="A12" s="29" t="s">
+      <c r="A12" s="30" t="s">
         <v>209</v>
       </c>
       <c r="D12" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="G12" s="30" t="s">
+      <c r="G12" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="I12" s="29" t="s">
+      <c r="I12" s="30" t="s">
         <v>209</v>
       </c>
       <c r="L12" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="O12" s="30" t="s">
+      <c r="O12" s="29" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="28" t="str">
-        <f>'data'!$B$40</f>
+        <f>'data'!$B$41</f>
       </c>
       <c r="B13" s="28"/>
       <c r="C13" s="28"/>
@@ -5960,10 +5960,10 @@
       <c r="E13" s="28"/>
       <c r="F13" s="28"/>
       <c r="G13" s="28" t="str">
-        <f>'data'!$B$41</f>
+        <f>'data'!$B$40</f>
       </c>
       <c r="I13" s="28" t="str">
-        <f>'data'!$B$17</f>
+        <f>'data'!$B$18</f>
       </c>
       <c r="J13" s="28"/>
       <c r="K13" s="28"/>
@@ -5971,7 +5971,7 @@
       <c r="M13" s="28"/>
       <c r="N13" s="28"/>
       <c r="O13" s="28" t="str">
-        <f>'data'!$B$18</f>
+        <f>'data'!$B$17</f>
       </c>
     </row>
     <row r="15">
@@ -6015,28 +6015,28 @@
       <c r="O19" s="20"/>
     </row>
     <row r="20">
-      <c r="A20" s="29" t="s">
+      <c r="A20" s="30" t="s">
         <v>209</v>
       </c>
       <c r="D20" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="G20" s="30" t="s">
+      <c r="G20" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="I20" s="29" t="s">
+      <c r="I20" s="30" t="s">
         <v>209</v>
       </c>
       <c r="L20" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="O20" s="30" t="s">
+      <c r="O20" s="29" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="28" t="str">
-        <f>'data'!$B$20</f>
+        <f>'data'!$B$21</f>
       </c>
       <c r="B21" s="28"/>
       <c r="C21" s="28"/>
@@ -6044,10 +6044,10 @@
       <c r="E21" s="28"/>
       <c r="F21" s="28"/>
       <c r="G21" s="28" t="str">
-        <f>'data'!$B$21</f>
+        <f>'data'!$B$20</f>
       </c>
       <c r="I21" s="28" t="str">
-        <f>'data'!$B$23</f>
+        <f>'data'!$B$24</f>
       </c>
       <c r="J21" s="28"/>
       <c r="K21" s="28"/>
@@ -6055,7 +6055,7 @@
       <c r="M21" s="28"/>
       <c r="N21" s="28"/>
       <c r="O21" s="28" t="str">
-        <f>'data'!$B$24</f>
+        <f>'data'!$B$23</f>
       </c>
     </row>
     <row r="23">
@@ -6099,28 +6099,28 @@
       <c r="O27" s="20"/>
     </row>
     <row r="28">
-      <c r="A28" s="29" t="s">
+      <c r="A28" s="30" t="s">
         <v>209</v>
       </c>
       <c r="D28" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="G28" s="30" t="s">
+      <c r="G28" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="I28" s="29" t="s">
+      <c r="I28" s="30" t="s">
         <v>209</v>
       </c>
       <c r="L28" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="O28" s="30" t="s">
+      <c r="O28" s="29" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="28" t="str">
-        <f>'data'!$B$28</f>
+        <f>'data'!$B$29</f>
       </c>
       <c r="B29" s="28"/>
       <c r="C29" s="28"/>
@@ -6128,10 +6128,10 @@
       <c r="E29" s="28"/>
       <c r="F29" s="28"/>
       <c r="G29" s="28" t="str">
-        <f>'data'!$B$29</f>
+        <f>'data'!$B$28</f>
       </c>
       <c r="I29" s="28" t="str">
-        <f>'data'!$B$31</f>
+        <f>'data'!$B$32</f>
       </c>
       <c r="J29" s="28"/>
       <c r="K29" s="28"/>
@@ -6139,7 +6139,7 @@
       <c r="M29" s="28"/>
       <c r="N29" s="28"/>
       <c r="O29" s="28" t="str">
-        <f>'data'!$B$32</f>
+        <f>'data'!$B$31</f>
       </c>
     </row>
     <row r="31">
@@ -6183,28 +6183,28 @@
       <c r="O35" s="20"/>
     </row>
     <row r="36">
-      <c r="A36" s="29" t="s">
+      <c r="A36" s="30" t="s">
         <v>209</v>
       </c>
       <c r="D36" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="G36" s="30" t="s">
+      <c r="G36" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="I36" s="29" t="s">
+      <c r="I36" s="30" t="s">
         <v>209</v>
       </c>
       <c r="L36" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="O36" s="30" t="s">
+      <c r="O36" s="29" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="28" t="str">
-        <f>'data'!$B$34</f>
+        <f>'data'!$B$35</f>
       </c>
       <c r="B37" s="28"/>
       <c r="C37" s="28"/>
@@ -6212,10 +6212,10 @@
       <c r="E37" s="28"/>
       <c r="F37" s="28"/>
       <c r="G37" s="28" t="str">
-        <f>'data'!$B$35</f>
+        <f>'data'!$B$34</f>
       </c>
       <c r="I37" s="28" t="str">
-        <f>'data'!$B$37</f>
+        <f>'data'!$B$38</f>
       </c>
       <c r="J37" s="28"/>
       <c r="K37" s="28"/>
@@ -6223,7 +6223,7 @@
       <c r="M37" s="28"/>
       <c r="N37" s="28"/>
       <c r="O37" s="28" t="str">
-        <f>'data'!$B$38</f>
+        <f>'data'!$B$37</f>
       </c>
     </row>
     <row r="39">
@@ -6267,28 +6267,28 @@
       <c r="O43" s="20"/>
     </row>
     <row r="44">
-      <c r="A44" s="29" t="s">
+      <c r="A44" s="30" t="s">
         <v>209</v>
       </c>
       <c r="D44" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="G44" s="30" t="s">
+      <c r="G44" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="I44" s="29" t="s">
+      <c r="I44" s="30" t="s">
         <v>209</v>
       </c>
       <c r="L44" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="O44" s="30" t="s">
+      <c r="O44" s="29" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="28" t="str">
-        <f>'data'!$B$40</f>
+        <f>'data'!$B$41</f>
       </c>
       <c r="B45" s="28"/>
       <c r="C45" s="28"/>
@@ -6296,10 +6296,10 @@
       <c r="E45" s="28"/>
       <c r="F45" s="28"/>
       <c r="G45" s="28" t="str">
-        <f>'data'!$B$41</f>
+        <f>'data'!$B$40</f>
       </c>
       <c r="I45" s="28" t="str">
-        <f>'data'!$B$43</f>
+        <f>'data'!$B$44</f>
       </c>
       <c r="J45" s="28"/>
       <c r="K45" s="28"/>
@@ -6307,7 +6307,7 @@
       <c r="M45" s="28"/>
       <c r="N45" s="28"/>
       <c r="O45" s="28" t="str">
-        <f>'data'!$B$44</f>
+        <f>'data'!$B$43</f>
       </c>
     </row>
     <row r="47">
@@ -6351,28 +6351,28 @@
       <c r="O51" s="20"/>
     </row>
     <row r="52">
-      <c r="A52" s="29" t="s">
+      <c r="A52" s="30" t="s">
         <v>209</v>
       </c>
       <c r="D52" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="G52" s="30" t="s">
+      <c r="G52" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="I52" s="29" t="s">
+      <c r="I52" s="30" t="s">
         <v>209</v>
       </c>
       <c r="L52" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="O52" s="30" t="s">
+      <c r="O52" s="29" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="28" t="str">
-        <f>'data'!$B$46</f>
+        <f>'data'!$B$47</f>
       </c>
       <c r="B53" s="28"/>
       <c r="C53" s="28"/>
@@ -6380,10 +6380,10 @@
       <c r="E53" s="28"/>
       <c r="F53" s="28"/>
       <c r="G53" s="28" t="str">
-        <f>'data'!$B$47</f>
+        <f>'data'!$B$46</f>
       </c>
       <c r="I53" s="28" t="str">
-        <f>'data'!$B$51</f>
+        <f>'data'!$B$52</f>
       </c>
       <c r="J53" s="28"/>
       <c r="K53" s="28"/>
@@ -6391,7 +6391,7 @@
       <c r="M53" s="28"/>
       <c r="N53" s="28"/>
       <c r="O53" s="28" t="str">
-        <f>'data'!$B$52</f>
+        <f>'data'!$B$51</f>
       </c>
     </row>
     <row r="55">
@@ -6435,28 +6435,28 @@
       <c r="O59" s="20"/>
     </row>
     <row r="60">
-      <c r="A60" s="29" t="s">
+      <c r="A60" s="30" t="s">
         <v>209</v>
       </c>
       <c r="D60" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="G60" s="30" t="s">
+      <c r="G60" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="I60" s="29" t="s">
+      <c r="I60" s="30" t="s">
         <v>209</v>
       </c>
       <c r="L60" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="O60" s="30" t="s">
+      <c r="O60" s="29" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="28" t="str">
-        <f>'data'!$B$54</f>
+        <f>'data'!$B$55</f>
       </c>
       <c r="B61" s="28"/>
       <c r="C61" s="28"/>
@@ -6464,10 +6464,10 @@
       <c r="E61" s="28"/>
       <c r="F61" s="28"/>
       <c r="G61" s="28" t="str">
-        <f>'data'!$B$55</f>
+        <f>'data'!$B$54</f>
       </c>
       <c r="I61" s="28" t="str">
-        <f>'data'!$B$57</f>
+        <f>'data'!$B$58</f>
       </c>
       <c r="J61" s="28"/>
       <c r="K61" s="28"/>
@@ -6475,7 +6475,7 @@
       <c r="M61" s="28"/>
       <c r="N61" s="28"/>
       <c r="O61" s="28" t="str">
-        <f>'data'!$B$58</f>
+        <f>'data'!$B$57</f>
       </c>
     </row>
     <row r="63">
@@ -6519,28 +6519,28 @@
       <c r="O67" s="20"/>
     </row>
     <row r="68">
-      <c r="A68" s="29" t="s">
+      <c r="A68" s="30" t="s">
         <v>209</v>
       </c>
       <c r="D68" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="G68" s="30" t="s">
+      <c r="G68" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="I68" s="29" t="s">
+      <c r="I68" s="30" t="s">
         <v>209</v>
       </c>
       <c r="L68" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="O68" s="30" t="s">
+      <c r="O68" s="29" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="28" t="str">
-        <f>'data'!$B$60</f>
+        <f>'data'!$B$61</f>
       </c>
       <c r="B69" s="28"/>
       <c r="C69" s="28"/>
@@ -6548,10 +6548,10 @@
       <c r="E69" s="28"/>
       <c r="F69" s="28"/>
       <c r="G69" s="28" t="str">
-        <f>'data'!$B$61</f>
+        <f>'data'!$B$60</f>
       </c>
       <c r="I69" s="28" t="str">
-        <f>'data'!$B$63</f>
+        <f>'data'!$B$64</f>
       </c>
       <c r="J69" s="28"/>
       <c r="K69" s="28"/>
@@ -6559,7 +6559,7 @@
       <c r="M69" s="28"/>
       <c r="N69" s="28"/>
       <c r="O69" s="28" t="str">
-        <f>'data'!$B$64</f>
+        <f>'data'!$B$63</f>
       </c>
     </row>
     <row r="71">
@@ -6603,28 +6603,28 @@
       <c r="O75" s="20"/>
     </row>
     <row r="76">
-      <c r="A76" s="29" t="s">
+      <c r="A76" s="30" t="s">
         <v>209</v>
       </c>
       <c r="D76" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="G76" s="30" t="s">
+      <c r="G76" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="I76" s="29" t="s">
+      <c r="I76" s="30" t="s">
         <v>209</v>
       </c>
       <c r="L76" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="O76" s="30" t="s">
+      <c r="O76" s="29" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="28" t="str">
-        <f>'data'!$B$66</f>
+        <f>'data'!$B$67</f>
       </c>
       <c r="B77" s="28"/>
       <c r="C77" s="28"/>
@@ -6632,10 +6632,10 @@
       <c r="E77" s="28"/>
       <c r="F77" s="28"/>
       <c r="G77" s="28" t="str">
-        <f>'data'!$B$67</f>
+        <f>'data'!$B$66</f>
       </c>
       <c r="I77" s="28" t="str">
-        <f>'data'!$B$69</f>
+        <f>'data'!$B$74</f>
       </c>
       <c r="J77" s="28"/>
       <c r="K77" s="28"/>
@@ -6643,7 +6643,7 @@
       <c r="M77" s="28"/>
       <c r="N77" s="28"/>
       <c r="O77" s="28" t="str">
-        <f>'data'!$B$74</f>
+        <f>'data'!$B$69</f>
       </c>
     </row>
     <row r="79">
@@ -6687,28 +6687,28 @@
       <c r="O83" s="20"/>
     </row>
     <row r="84">
-      <c r="A84" s="29" t="s">
+      <c r="A84" s="30" t="s">
         <v>209</v>
       </c>
       <c r="D84" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="G84" s="30" t="s">
+      <c r="G84" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="I84" s="29" t="s">
+      <c r="I84" s="30" t="s">
         <v>209</v>
       </c>
       <c r="L84" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="O84" s="30" t="s">
+      <c r="O84" s="29" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="28" t="str">
-        <f>'data'!$B$74</f>
+        <f>'data'!$B$75</f>
       </c>
       <c r="B85" s="28"/>
       <c r="C85" s="28"/>
@@ -6716,10 +6716,10 @@
       <c r="E85" s="28"/>
       <c r="F85" s="28"/>
       <c r="G85" s="28" t="str">
-        <f>'data'!$B$75</f>
+        <f>'data'!$B$74</f>
       </c>
       <c r="I85" s="28" t="str">
-        <f>'data'!$B$77</f>
+        <f>'data'!$B$78</f>
       </c>
       <c r="J85" s="28"/>
       <c r="K85" s="28"/>
@@ -6727,7 +6727,7 @@
       <c r="M85" s="28"/>
       <c r="N85" s="28"/>
       <c r="O85" s="28" t="str">
-        <f>'data'!$B$78</f>
+        <f>'data'!$B$77</f>
       </c>
     </row>
     <row r="87">
@@ -6771,28 +6771,28 @@
       <c r="O91" s="20"/>
     </row>
     <row r="92">
-      <c r="A92" s="29" t="s">
+      <c r="A92" s="30" t="s">
         <v>209</v>
       </c>
       <c r="D92" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="G92" s="30" t="s">
+      <c r="G92" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="I92" s="29" t="s">
+      <c r="I92" s="30" t="s">
         <v>209</v>
       </c>
       <c r="L92" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="O92" s="30" t="s">
+      <c r="O92" s="29" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="28" t="str">
-        <f>'data'!$B$80</f>
+        <f>'data'!$B$81</f>
       </c>
       <c r="B93" s="28"/>
       <c r="C93" s="28"/>
@@ -6800,10 +6800,10 @@
       <c r="E93" s="28"/>
       <c r="F93" s="28"/>
       <c r="G93" s="28" t="str">
-        <f>'data'!$B$81</f>
+        <f>'data'!$B$80</f>
       </c>
       <c r="I93" s="28" t="str">
-        <f>'data'!$B$83</f>
+        <f>'data'!$B$84</f>
       </c>
       <c r="J93" s="28"/>
       <c r="K93" s="28"/>
@@ -6811,7 +6811,7 @@
       <c r="M93" s="28"/>
       <c r="N93" s="28"/>
       <c r="O93" s="28" t="str">
-        <f>'data'!$B$84</f>
+        <f>'data'!$B$83</f>
       </c>
     </row>
     <row r="95">
@@ -6855,28 +6855,28 @@
       <c r="O99" s="20"/>
     </row>
     <row r="100">
-      <c r="A100" s="29" t="s">
+      <c r="A100" s="30" t="s">
         <v>209</v>
       </c>
       <c r="D100" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="G100" s="30" t="s">
+      <c r="G100" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="I100" s="29" t="s">
+      <c r="I100" s="30" t="s">
         <v>209</v>
       </c>
       <c r="L100" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="O100" s="30" t="s">
+      <c r="O100" s="29" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="28" t="str">
-        <f>'data'!$B$86</f>
+        <f>'data'!$B$87</f>
       </c>
       <c r="B101" s="28"/>
       <c r="C101" s="28"/>
@@ -6884,10 +6884,10 @@
       <c r="E101" s="28"/>
       <c r="F101" s="28"/>
       <c r="G101" s="28" t="str">
-        <f>'data'!$B$87</f>
+        <f>'data'!$B$86</f>
       </c>
       <c r="I101" s="28" t="str">
-        <f>'data'!$B$89</f>
+        <f>'data'!$B$90</f>
       </c>
       <c r="J101" s="28"/>
       <c r="K101" s="28"/>
@@ -6895,7 +6895,7 @@
       <c r="M101" s="28"/>
       <c r="N101" s="28"/>
       <c r="O101" s="28" t="str">
-        <f>'data'!$B$90</f>
+        <f>'data'!$B$89</f>
       </c>
     </row>
     <row r="103">
@@ -6930,19 +6930,19 @@
       <c r="G107" s="20"/>
     </row>
     <row r="108">
-      <c r="A108" s="29" t="s">
+      <c r="A108" s="30" t="s">
         <v>209</v>
       </c>
       <c r="D108" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="G108" s="30" t="s">
+      <c r="G108" s="29" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="28" t="str">
-        <f>'data'!$B$92</f>
+        <f>'data'!$B$93</f>
       </c>
       <c r="B109" s="28"/>
       <c r="C109" s="28"/>
@@ -6950,7 +6950,7 @@
       <c r="E109" s="28"/>
       <c r="F109" s="28"/>
       <c r="G109" s="28" t="str">
-        <f>'data'!$B$93</f>
+        <f>'data'!$B$92</f>
       </c>
     </row>
     <row r="111">
@@ -7005,28 +7005,28 @@
       <c r="O122" s="20"/>
     </row>
     <row r="123">
-      <c r="A123" s="29" t="s">
+      <c r="A123" s="30" t="s">
         <v>209</v>
       </c>
       <c r="D123" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="G123" s="30" t="s">
+      <c r="G123" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="I123" s="29" t="s">
+      <c r="I123" s="30" t="s">
         <v>209</v>
       </c>
       <c r="L123" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="O123" s="30" t="s">
+      <c r="O123" s="29" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="28" t="str">
-        <f>'data'!$B$32</f>
+        <f>'data'!$B$33</f>
       </c>
       <c r="B124" s="28"/>
       <c r="C124" s="28"/>
@@ -7034,10 +7034,10 @@
       <c r="E124" s="28"/>
       <c r="F124" s="28"/>
       <c r="G124" s="28" t="str">
-        <f>'data'!$B$33</f>
+        <f>'data'!$B$32</f>
       </c>
       <c r="I124" s="28" t="str">
-        <f>'data'!$B$34</f>
+        <f>CONCATENATE("M 1 ",'Elimination Matches'!G7)</f>
       </c>
       <c r="J124" s="28"/>
       <c r="K124" s="28"/>
@@ -7045,7 +7045,7 @@
       <c r="M124" s="28"/>
       <c r="N124" s="28"/>
       <c r="O124" s="28" t="str">
-        <f>CONCATENATE("M 1 ",'Elimination Matches'!G7)</f>
+        <f>'data'!$B$34</f>
       </c>
     </row>
     <row r="126">
@@ -7089,28 +7089,28 @@
       <c r="O130" s="20"/>
     </row>
     <row r="131">
-      <c r="A131" s="29" t="s">
+      <c r="A131" s="30" t="s">
         <v>209</v>
       </c>
       <c r="D131" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="G131" s="30" t="s">
+      <c r="G131" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="I131" s="29" t="s">
+      <c r="I131" s="30" t="s">
         <v>209</v>
       </c>
       <c r="L131" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="O131" s="30" t="s">
+      <c r="O131" s="29" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="28" t="str">
-        <f>'data'!$B$36</f>
+        <f>CONCATENATE("M 2 ",'Elimination Matches'!O7)</f>
       </c>
       <c r="B132" s="28"/>
       <c r="C132" s="28"/>
@@ -7118,10 +7118,10 @@
       <c r="E132" s="28"/>
       <c r="F132" s="28"/>
       <c r="G132" s="28" t="str">
-        <f>CONCATENATE("M 2 ",'Elimination Matches'!O7)</f>
+        <f>'data'!$B$36</f>
       </c>
       <c r="I132" s="28" t="str">
-        <f>'data'!$B$39</f>
+        <f>CONCATENATE("M 3 ",'Elimination Matches'!G15)</f>
       </c>
       <c r="J132" s="28"/>
       <c r="K132" s="28"/>
@@ -7129,7 +7129,7 @@
       <c r="M132" s="28"/>
       <c r="N132" s="28"/>
       <c r="O132" s="28" t="str">
-        <f>CONCATENATE("M 3 ",'Elimination Matches'!G15)</f>
+        <f>'data'!$B$39</f>
       </c>
     </row>
     <row r="134">
@@ -7173,28 +7173,28 @@
       <c r="O138" s="20"/>
     </row>
     <row r="139">
-      <c r="A139" s="29" t="s">
+      <c r="A139" s="30" t="s">
         <v>209</v>
       </c>
       <c r="D139" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="G139" s="30" t="s">
+      <c r="G139" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="I139" s="29" t="s">
+      <c r="I139" s="30" t="s">
         <v>209</v>
       </c>
       <c r="L139" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="O139" s="30" t="s">
+      <c r="O139" s="29" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="28" t="str">
-        <f>'data'!$B$42</f>
+        <f>'data'!$B$43</f>
       </c>
       <c r="B140" s="28"/>
       <c r="C140" s="28"/>
@@ -7202,10 +7202,10 @@
       <c r="E140" s="28"/>
       <c r="F140" s="28"/>
       <c r="G140" s="28" t="str">
-        <f>'data'!$B$43</f>
+        <f>'data'!$B$42</f>
       </c>
       <c r="I140" s="28" t="str">
-        <f>'data'!$B$16</f>
+        <f>CONCATENATE("M 4 ",'Elimination Matches'!O15)</f>
       </c>
       <c r="J140" s="28"/>
       <c r="K140" s="28"/>
@@ -7213,7 +7213,7 @@
       <c r="M140" s="28"/>
       <c r="N140" s="28"/>
       <c r="O140" s="28" t="str">
-        <f>CONCATENATE("M 4 ",'Elimination Matches'!O15)</f>
+        <f>'data'!$B$16</f>
       </c>
     </row>
     <row r="142">
@@ -7257,28 +7257,28 @@
       <c r="O146" s="20"/>
     </row>
     <row r="147">
-      <c r="A147" s="29" t="s">
+      <c r="A147" s="30" t="s">
         <v>209</v>
       </c>
       <c r="D147" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="G147" s="30" t="s">
+      <c r="G147" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="I147" s="29" t="s">
+      <c r="I147" s="30" t="s">
         <v>209</v>
       </c>
       <c r="L147" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="O147" s="30" t="s">
+      <c r="O147" s="29" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="28" t="str">
-        <f>'data'!$B$30</f>
+        <f>CONCATENATE("M 5 ",'Elimination Matches'!G23)</f>
       </c>
       <c r="B148" s="28"/>
       <c r="C148" s="28"/>
@@ -7286,10 +7286,10 @@
       <c r="E148" s="28"/>
       <c r="F148" s="28"/>
       <c r="G148" s="28" t="str">
-        <f>CONCATENATE("M 5 ",'Elimination Matches'!G23)</f>
+        <f>'data'!$B$30</f>
       </c>
       <c r="I148" s="28" t="str">
-        <f>'data'!$B$22</f>
+        <f>CONCATENATE("M 6 ",'Elimination Matches'!O23)</f>
       </c>
       <c r="J148" s="28"/>
       <c r="K148" s="28"/>
@@ -7297,7 +7297,7 @@
       <c r="M148" s="28"/>
       <c r="N148" s="28"/>
       <c r="O148" s="28" t="str">
-        <f>CONCATENATE("M 6 ",'Elimination Matches'!O23)</f>
+        <f>'data'!$B$22</f>
       </c>
     </row>
     <row r="150">
@@ -7341,28 +7341,28 @@
       <c r="O154" s="20"/>
     </row>
     <row r="155">
-      <c r="A155" s="29" t="s">
+      <c r="A155" s="30" t="s">
         <v>209</v>
       </c>
       <c r="D155" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="G155" s="30" t="s">
+      <c r="G155" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="I155" s="29" t="s">
+      <c r="I155" s="30" t="s">
         <v>209</v>
       </c>
       <c r="L155" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="O155" s="30" t="s">
+      <c r="O155" s="29" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="28" t="str">
-        <f>'data'!$B$25</f>
+        <f>'data'!$B$26</f>
       </c>
       <c r="B156" s="28"/>
       <c r="C156" s="28"/>
@@ -7370,10 +7370,10 @@
       <c r="E156" s="28"/>
       <c r="F156" s="28"/>
       <c r="G156" s="28" t="str">
-        <f>'data'!$B$26</f>
+        <f>'data'!$B$25</f>
       </c>
       <c r="I156" s="28" t="str">
-        <f>'data'!$B$27</f>
+        <f>CONCATENATE("M 7 ",'Elimination Matches'!G31)</f>
       </c>
       <c r="J156" s="28"/>
       <c r="K156" s="28"/>
@@ -7381,7 +7381,7 @@
       <c r="M156" s="28"/>
       <c r="N156" s="28"/>
       <c r="O156" s="28" t="str">
-        <f>CONCATENATE("M 7 ",'Elimination Matches'!G31)</f>
+        <f>'data'!$B$27</f>
       </c>
     </row>
     <row r="158">
@@ -7425,28 +7425,28 @@
       <c r="O162" s="20"/>
     </row>
     <row r="163">
-      <c r="A163" s="29" t="s">
+      <c r="A163" s="30" t="s">
         <v>209</v>
       </c>
       <c r="D163" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="G163" s="30" t="s">
+      <c r="G163" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="I163" s="29" t="s">
+      <c r="I163" s="30" t="s">
         <v>209</v>
       </c>
       <c r="L163" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="O163" s="30" t="s">
+      <c r="O163" s="29" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="28" t="str">
-        <f>'data'!$B$30</f>
+        <f>CONCATENATE("M 8 ",'Elimination Matches'!O31)</f>
       </c>
       <c r="B164" s="28"/>
       <c r="C164" s="28"/>
@@ -7454,10 +7454,10 @@
       <c r="E164" s="28"/>
       <c r="F164" s="28"/>
       <c r="G164" s="28" t="str">
-        <f>CONCATENATE("M 8 ",'Elimination Matches'!O31)</f>
+        <f>'data'!$B$30</f>
       </c>
       <c r="I164" s="28" t="str">
-        <f>'data'!$B$33</f>
+        <f>CONCATENATE("M 9 ",'Elimination Matches'!G39)</f>
       </c>
       <c r="J164" s="28"/>
       <c r="K164" s="28"/>
@@ -7465,7 +7465,7 @@
       <c r="M164" s="28"/>
       <c r="N164" s="28"/>
       <c r="O164" s="28" t="str">
-        <f>CONCATENATE("M 9 ",'Elimination Matches'!G39)</f>
+        <f>'data'!$B$33</f>
       </c>
     </row>
     <row r="166">
@@ -7509,28 +7509,28 @@
       <c r="O170" s="20"/>
     </row>
     <row r="171">
-      <c r="A171" s="29" t="s">
+      <c r="A171" s="30" t="s">
         <v>209</v>
       </c>
       <c r="D171" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="G171" s="30" t="s">
+      <c r="G171" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="I171" s="29" t="s">
+      <c r="I171" s="30" t="s">
         <v>209</v>
       </c>
       <c r="L171" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="O171" s="30" t="s">
+      <c r="O171" s="29" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="28" t="str">
-        <f>'data'!$B$36</f>
+        <f>CONCATENATE("M 10 ",'Elimination Matches'!O39)</f>
       </c>
       <c r="B172" s="28"/>
       <c r="C172" s="28"/>
@@ -7538,10 +7538,10 @@
       <c r="E172" s="28"/>
       <c r="F172" s="28"/>
       <c r="G172" s="28" t="str">
-        <f>CONCATENATE("M 10 ",'Elimination Matches'!O39)</f>
+        <f>'data'!$B$36</f>
       </c>
       <c r="I172" s="28" t="str">
-        <f>'data'!$B$39</f>
+        <f>CONCATENATE("M 11 ",'Elimination Matches'!G47)</f>
       </c>
       <c r="J172" s="28"/>
       <c r="K172" s="28"/>
@@ -7549,7 +7549,7 @@
       <c r="M172" s="28"/>
       <c r="N172" s="28"/>
       <c r="O172" s="28" t="str">
-        <f>CONCATENATE("M 11 ",'Elimination Matches'!G47)</f>
+        <f>'data'!$B$39</f>
       </c>
     </row>
     <row r="174">
@@ -7593,28 +7593,28 @@
       <c r="O178" s="20"/>
     </row>
     <row r="179">
-      <c r="A179" s="29" t="s">
+      <c r="A179" s="30" t="s">
         <v>209</v>
       </c>
       <c r="D179" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="G179" s="30" t="s">
+      <c r="G179" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="I179" s="29" t="s">
+      <c r="I179" s="30" t="s">
         <v>209</v>
       </c>
       <c r="L179" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="O179" s="30" t="s">
+      <c r="O179" s="29" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="28" t="str">
-        <f>'data'!$B$42</f>
+        <f>CONCATENATE("M 12 ",'Elimination Matches'!O47)</f>
       </c>
       <c r="B180" s="28"/>
       <c r="C180" s="28"/>
@@ -7622,10 +7622,10 @@
       <c r="E180" s="28"/>
       <c r="F180" s="28"/>
       <c r="G180" s="28" t="str">
-        <f>CONCATENATE("M 12 ",'Elimination Matches'!O47)</f>
+        <f>'data'!$B$42</f>
       </c>
       <c r="I180" s="28" t="str">
-        <f>'data'!$B$45</f>
+        <f>CONCATENATE("M 13 ",'Elimination Matches'!G55)</f>
       </c>
       <c r="J180" s="28"/>
       <c r="K180" s="28"/>
@@ -7633,7 +7633,7 @@
       <c r="M180" s="28"/>
       <c r="N180" s="28"/>
       <c r="O180" s="28" t="str">
-        <f>CONCATENATE("M 13 ",'Elimination Matches'!G55)</f>
+        <f>'data'!$B$45</f>
       </c>
     </row>
     <row r="182">
@@ -7677,28 +7677,28 @@
       <c r="O186" s="20"/>
     </row>
     <row r="187">
-      <c r="A187" s="29" t="s">
+      <c r="A187" s="30" t="s">
         <v>209</v>
       </c>
       <c r="D187" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="G187" s="30" t="s">
+      <c r="G187" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="I187" s="29" t="s">
+      <c r="I187" s="30" t="s">
         <v>209</v>
       </c>
       <c r="L187" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="O187" s="30" t="s">
+      <c r="O187" s="29" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="28" t="str">
-        <f>'data'!$B$48</f>
+        <f>'data'!$B$49</f>
       </c>
       <c r="B188" s="28"/>
       <c r="C188" s="28"/>
@@ -7706,10 +7706,10 @@
       <c r="E188" s="28"/>
       <c r="F188" s="28"/>
       <c r="G188" s="28" t="str">
-        <f>'data'!$B$49</f>
+        <f>'data'!$B$48</f>
       </c>
       <c r="I188" s="28" t="str">
-        <f>'data'!$B$50</f>
+        <f>CONCATENATE("M 14 ",'Elimination Matches'!O55)</f>
       </c>
       <c r="J188" s="28"/>
       <c r="K188" s="28"/>
@@ -7717,7 +7717,7 @@
       <c r="M188" s="28"/>
       <c r="N188" s="28"/>
       <c r="O188" s="28" t="str">
-        <f>CONCATENATE("M 14 ",'Elimination Matches'!O55)</f>
+        <f>'data'!$B$50</f>
       </c>
     </row>
     <row r="190">
@@ -7761,28 +7761,28 @@
       <c r="O194" s="20"/>
     </row>
     <row r="195">
-      <c r="A195" s="29" t="s">
+      <c r="A195" s="30" t="s">
         <v>209</v>
       </c>
       <c r="D195" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="G195" s="30" t="s">
+      <c r="G195" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="I195" s="29" t="s">
+      <c r="I195" s="30" t="s">
         <v>209</v>
       </c>
       <c r="L195" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="O195" s="30" t="s">
+      <c r="O195" s="29" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="28" t="str">
-        <f>'data'!$B$53</f>
+        <f>CONCATENATE("M 15 ",'Elimination Matches'!G63)</f>
       </c>
       <c r="B196" s="28"/>
       <c r="C196" s="28"/>
@@ -7790,10 +7790,10 @@
       <c r="E196" s="28"/>
       <c r="F196" s="28"/>
       <c r="G196" s="28" t="str">
-        <f>CONCATENATE("M 15 ",'Elimination Matches'!G63)</f>
+        <f>'data'!$B$53</f>
       </c>
       <c r="I196" s="28" t="str">
-        <f>'data'!$B$56</f>
+        <f>CONCATENATE("M 16 ",'Elimination Matches'!O63)</f>
       </c>
       <c r="J196" s="28"/>
       <c r="K196" s="28"/>
@@ -7801,7 +7801,7 @@
       <c r="M196" s="28"/>
       <c r="N196" s="28"/>
       <c r="O196" s="28" t="str">
-        <f>CONCATENATE("M 16 ",'Elimination Matches'!O63)</f>
+        <f>'data'!$B$56</f>
       </c>
     </row>
     <row r="198">
@@ -7845,28 +7845,28 @@
       <c r="O202" s="20"/>
     </row>
     <row r="203">
-      <c r="A203" s="29" t="s">
+      <c r="A203" s="30" t="s">
         <v>209</v>
       </c>
       <c r="D203" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="G203" s="30" t="s">
+      <c r="G203" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="I203" s="29" t="s">
+      <c r="I203" s="30" t="s">
         <v>209</v>
       </c>
       <c r="L203" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="O203" s="30" t="s">
+      <c r="O203" s="29" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="28" t="str">
-        <f>'data'!$B$81</f>
+        <f>CONCATENATE("M 17 ",'Elimination Matches'!G71)</f>
       </c>
       <c r="B204" s="28"/>
       <c r="C204" s="28"/>
@@ -7874,10 +7874,10 @@
       <c r="E204" s="28"/>
       <c r="F204" s="28"/>
       <c r="G204" s="28" t="str">
-        <f>CONCATENATE("M 17 ",'Elimination Matches'!G71)</f>
+        <f>'data'!$B$81</f>
       </c>
       <c r="I204" s="28" t="str">
-        <f>'data'!$B$62</f>
+        <f>CONCATENATE("M 18 ",'Elimination Matches'!O71)</f>
       </c>
       <c r="J204" s="28"/>
       <c r="K204" s="28"/>
@@ -7885,7 +7885,7 @@
       <c r="M204" s="28"/>
       <c r="N204" s="28"/>
       <c r="O204" s="28" t="str">
-        <f>CONCATENATE("M 18 ",'Elimination Matches'!O71)</f>
+        <f>'data'!$B$62</f>
       </c>
     </row>
     <row r="206">
@@ -7929,28 +7929,28 @@
       <c r="O210" s="20"/>
     </row>
     <row r="211">
-      <c r="A211" s="29" t="s">
+      <c r="A211" s="30" t="s">
         <v>209</v>
       </c>
       <c r="D211" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="G211" s="30" t="s">
+      <c r="G211" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="I211" s="29" t="s">
+      <c r="I211" s="30" t="s">
         <v>209</v>
       </c>
       <c r="L211" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="O211" s="30" t="s">
+      <c r="O211" s="29" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="28" t="str">
-        <f>'data'!$B$65</f>
+        <f>CONCATENATE("M 19 ",'Elimination Matches'!G79)</f>
       </c>
       <c r="B212" s="28"/>
       <c r="C212" s="28"/>
@@ -7958,10 +7958,10 @@
       <c r="E212" s="28"/>
       <c r="F212" s="28"/>
       <c r="G212" s="28" t="str">
-        <f>CONCATENATE("M 19 ",'Elimination Matches'!G79)</f>
+        <f>'data'!$B$65</f>
       </c>
       <c r="I212" s="28" t="str">
-        <f>'data'!$B$68</f>
+        <f>CONCATENATE("M 20 ",'Elimination Matches'!O79)</f>
       </c>
       <c r="J212" s="28"/>
       <c r="K212" s="28"/>
@@ -7969,7 +7969,7 @@
       <c r="M212" s="28"/>
       <c r="N212" s="28"/>
       <c r="O212" s="28" t="str">
-        <f>CONCATENATE("M 20 ",'Elimination Matches'!O79)</f>
+        <f>'data'!$B$68</f>
       </c>
     </row>
     <row r="214">
@@ -8013,28 +8013,28 @@
       <c r="O218" s="20"/>
     </row>
     <row r="219">
-      <c r="A219" s="29" t="s">
+      <c r="A219" s="30" t="s">
         <v>209</v>
       </c>
       <c r="D219" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="G219" s="30" t="s">
+      <c r="G219" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="I219" s="29" t="s">
+      <c r="I219" s="30" t="s">
         <v>209</v>
       </c>
       <c r="L219" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="O219" s="30" t="s">
+      <c r="O219" s="29" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="28" t="str">
-        <f>'data'!$B$88</f>
+        <f>'data'!$B$72</f>
       </c>
       <c r="B220" s="28"/>
       <c r="C220" s="28"/>
@@ -8042,10 +8042,10 @@
       <c r="E220" s="28"/>
       <c r="F220" s="28"/>
       <c r="G220" s="28" t="str">
-        <f>'data'!$B$72</f>
+        <f>'data'!$B$88</f>
       </c>
       <c r="I220" s="28" t="str">
-        <f>'data'!$B$73</f>
+        <f>CONCATENATE("M 21 ",'Elimination Matches'!G87)</f>
       </c>
       <c r="J220" s="28"/>
       <c r="K220" s="28"/>
@@ -8053,7 +8053,7 @@
       <c r="M220" s="28"/>
       <c r="N220" s="28"/>
       <c r="O220" s="28" t="str">
-        <f>CONCATENATE("M 21 ",'Elimination Matches'!G87)</f>
+        <f>'data'!$B$73</f>
       </c>
     </row>
     <row r="222">
@@ -8097,28 +8097,28 @@
       <c r="O226" s="20"/>
     </row>
     <row r="227">
-      <c r="A227" s="29" t="s">
+      <c r="A227" s="30" t="s">
         <v>209</v>
       </c>
       <c r="D227" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="G227" s="30" t="s">
+      <c r="G227" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="I227" s="29" t="s">
+      <c r="I227" s="30" t="s">
         <v>209</v>
       </c>
       <c r="L227" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="O227" s="30" t="s">
+      <c r="O227" s="29" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="28" t="str">
-        <f>'data'!$B$76</f>
+        <f>CONCATENATE("M 22 ",'Elimination Matches'!O87)</f>
       </c>
       <c r="B228" s="28"/>
       <c r="C228" s="28"/>
@@ -8126,10 +8126,10 @@
       <c r="E228" s="28"/>
       <c r="F228" s="28"/>
       <c r="G228" s="28" t="str">
-        <f>CONCATENATE("M 22 ",'Elimination Matches'!O87)</f>
+        <f>'data'!$B$76</f>
       </c>
       <c r="I228" s="28" t="str">
-        <f>'data'!$B$79</f>
+        <f>CONCATENATE("M 23 ",'Elimination Matches'!G95)</f>
       </c>
       <c r="J228" s="28"/>
       <c r="K228" s="28"/>
@@ -8137,7 +8137,7 @@
       <c r="M228" s="28"/>
       <c r="N228" s="28"/>
       <c r="O228" s="28" t="str">
-        <f>CONCATENATE("M 23 ",'Elimination Matches'!G95)</f>
+        <f>'data'!$B$79</f>
       </c>
     </row>
     <row r="230">
@@ -8181,28 +8181,28 @@
       <c r="O234" s="20"/>
     </row>
     <row r="235">
-      <c r="A235" s="29" t="s">
+      <c r="A235" s="30" t="s">
         <v>209</v>
       </c>
       <c r="D235" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="G235" s="30" t="s">
+      <c r="G235" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="I235" s="29" t="s">
+      <c r="I235" s="30" t="s">
         <v>209</v>
       </c>
       <c r="L235" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="O235" s="30" t="s">
+      <c r="O235" s="29" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="28" t="str">
-        <f>'data'!$B$82</f>
+        <f>CONCATENATE("M 24 ",'Elimination Matches'!O95)</f>
       </c>
       <c r="B236" s="28"/>
       <c r="C236" s="28"/>
@@ -8210,10 +8210,10 @@
       <c r="E236" s="28"/>
       <c r="F236" s="28"/>
       <c r="G236" s="28" t="str">
-        <f>CONCATENATE("M 24 ",'Elimination Matches'!O95)</f>
+        <f>'data'!$B$82</f>
       </c>
       <c r="I236" s="28" t="str">
-        <f>'data'!$B$85</f>
+        <f>CONCATENATE("M 25 ",'Elimination Matches'!G103)</f>
       </c>
       <c r="J236" s="28"/>
       <c r="K236" s="28"/>
@@ -8221,7 +8221,7 @@
       <c r="M236" s="28"/>
       <c r="N236" s="28"/>
       <c r="O236" s="28" t="str">
-        <f>CONCATENATE("M 25 ",'Elimination Matches'!G103)</f>
+        <f>'data'!$B$85</f>
       </c>
     </row>
     <row r="238">
@@ -8265,28 +8265,28 @@
       <c r="O242" s="20"/>
     </row>
     <row r="243">
-      <c r="A243" s="29" t="s">
+      <c r="A243" s="30" t="s">
         <v>209</v>
       </c>
       <c r="D243" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="G243" s="30" t="s">
+      <c r="G243" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="I243" s="29" t="s">
+      <c r="I243" s="30" t="s">
         <v>209</v>
       </c>
       <c r="L243" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="O243" s="30" t="s">
+      <c r="O243" s="29" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="28" t="str">
-        <f>'data'!$B$88</f>
+        <f>CONCATENATE("M 26 ",'Elimination Matches'!O103)</f>
       </c>
       <c r="B244" s="28"/>
       <c r="C244" s="28"/>
@@ -8294,10 +8294,10 @@
       <c r="E244" s="28"/>
       <c r="F244" s="28"/>
       <c r="G244" s="28" t="str">
-        <f>CONCATENATE("M 26 ",'Elimination Matches'!O103)</f>
+        <f>'data'!$B$88</f>
       </c>
       <c r="I244" s="28" t="str">
-        <f>'data'!$B$91</f>
+        <f>CONCATENATE("M 27 ",'Elimination Matches'!G111)</f>
       </c>
       <c r="J244" s="28"/>
       <c r="K244" s="28"/>
@@ -8305,7 +8305,7 @@
       <c r="M244" s="28"/>
       <c r="N244" s="28"/>
       <c r="O244" s="28" t="str">
-        <f>CONCATENATE("M 27 ",'Elimination Matches'!G111)</f>
+        <f>'data'!$B$91</f>
       </c>
     </row>
     <row r="246">
@@ -8368,28 +8368,28 @@
       <c r="O257" s="20"/>
     </row>
     <row r="258">
-      <c r="A258" s="29" t="s">
+      <c r="A258" s="30" t="s">
         <v>209</v>
       </c>
       <c r="D258" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="G258" s="30" t="s">
+      <c r="G258" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="I258" s="29" t="s">
+      <c r="I258" s="30" t="s">
         <v>209</v>
       </c>
       <c r="L258" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="O258" s="30" t="s">
+      <c r="O258" s="29" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="28" t="str">
-        <f>CONCATENATE("M 28 ",'Elimination Matches'!G126)</f>
+        <f>CONCATENATE("M 29 ",'Elimination Matches'!O126)</f>
       </c>
       <c r="B259" s="28"/>
       <c r="C259" s="28"/>
@@ -8397,10 +8397,10 @@
       <c r="E259" s="28"/>
       <c r="F259" s="28"/>
       <c r="G259" s="28" t="str">
-        <f>CONCATENATE("M 29 ",'Elimination Matches'!O126)</f>
+        <f>CONCATENATE("M 28 ",'Elimination Matches'!G126)</f>
       </c>
       <c r="I259" s="28" t="str">
-        <f>CONCATENATE("M 30 ",'Elimination Matches'!G134)</f>
+        <f>CONCATENATE("M 31 ",'Elimination Matches'!O134)</f>
       </c>
       <c r="J259" s="28"/>
       <c r="K259" s="28"/>
@@ -8408,7 +8408,7 @@
       <c r="M259" s="28"/>
       <c r="N259" s="28"/>
       <c r="O259" s="28" t="str">
-        <f>CONCATENATE("M 31 ",'Elimination Matches'!O134)</f>
+        <f>CONCATENATE("M 30 ",'Elimination Matches'!G134)</f>
       </c>
     </row>
     <row r="261">
@@ -8452,28 +8452,28 @@
       <c r="O265" s="20"/>
     </row>
     <row r="266">
-      <c r="A266" s="29" t="s">
+      <c r="A266" s="30" t="s">
         <v>209</v>
       </c>
       <c r="D266" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="G266" s="30" t="s">
+      <c r="G266" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="I266" s="29" t="s">
+      <c r="I266" s="30" t="s">
         <v>209</v>
       </c>
       <c r="L266" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="O266" s="30" t="s">
+      <c r="O266" s="29" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="28" t="str">
-        <f>CONCATENATE("M 32 ",'Elimination Matches'!G142)</f>
+        <f>CONCATENATE("M 33 ",'Elimination Matches'!O142)</f>
       </c>
       <c r="B267" s="28"/>
       <c r="C267" s="28"/>
@@ -8481,10 +8481,10 @@
       <c r="E267" s="28"/>
       <c r="F267" s="28"/>
       <c r="G267" s="28" t="str">
-        <f>CONCATENATE("M 33 ",'Elimination Matches'!O142)</f>
+        <f>CONCATENATE("M 32 ",'Elimination Matches'!G142)</f>
       </c>
       <c r="I267" s="28" t="str">
-        <f>CONCATENATE("M 34 ",'Elimination Matches'!G150)</f>
+        <f>CONCATENATE("M 35 ",'Elimination Matches'!O150)</f>
       </c>
       <c r="J267" s="28"/>
       <c r="K267" s="28"/>
@@ -8492,7 +8492,7 @@
       <c r="M267" s="28"/>
       <c r="N267" s="28"/>
       <c r="O267" s="28" t="str">
-        <f>CONCATENATE("M 35 ",'Elimination Matches'!O150)</f>
+        <f>CONCATENATE("M 34 ",'Elimination Matches'!G150)</f>
       </c>
     </row>
     <row r="269">
@@ -8536,28 +8536,28 @@
       <c r="O273" s="20"/>
     </row>
     <row r="274">
-      <c r="A274" s="29" t="s">
+      <c r="A274" s="30" t="s">
         <v>209</v>
       </c>
       <c r="D274" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="G274" s="30" t="s">
+      <c r="G274" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="I274" s="29" t="s">
+      <c r="I274" s="30" t="s">
         <v>209</v>
       </c>
       <c r="L274" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="O274" s="30" t="s">
+      <c r="O274" s="29" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="28" t="str">
-        <f>CONCATENATE("M 36 ",'Elimination Matches'!G158)</f>
+        <f>CONCATENATE("M 37 ",'Elimination Matches'!O158)</f>
       </c>
       <c r="B275" s="28"/>
       <c r="C275" s="28"/>
@@ -8565,10 +8565,10 @@
       <c r="E275" s="28"/>
       <c r="F275" s="28"/>
       <c r="G275" s="28" t="str">
-        <f>CONCATENATE("M 37 ",'Elimination Matches'!O158)</f>
+        <f>CONCATENATE("M 36 ",'Elimination Matches'!G158)</f>
       </c>
       <c r="I275" s="28" t="str">
-        <f>CONCATENATE("M 38 ",'Elimination Matches'!G166)</f>
+        <f>CONCATENATE("M 39 ",'Elimination Matches'!O166)</f>
       </c>
       <c r="J275" s="28"/>
       <c r="K275" s="28"/>
@@ -8576,7 +8576,7 @@
       <c r="M275" s="28"/>
       <c r="N275" s="28"/>
       <c r="O275" s="28" t="str">
-        <f>CONCATENATE("M 39 ",'Elimination Matches'!O166)</f>
+        <f>CONCATENATE("M 38 ",'Elimination Matches'!G166)</f>
       </c>
     </row>
     <row r="277">
@@ -8620,28 +8620,28 @@
       <c r="O281" s="20"/>
     </row>
     <row r="282">
-      <c r="A282" s="29" t="s">
+      <c r="A282" s="30" t="s">
         <v>209</v>
       </c>
       <c r="D282" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="G282" s="30" t="s">
+      <c r="G282" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="I282" s="29" t="s">
+      <c r="I282" s="30" t="s">
         <v>209</v>
       </c>
       <c r="L282" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="O282" s="30" t="s">
+      <c r="O282" s="29" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="28" t="str">
-        <f>CONCATENATE("M 40 ",'Elimination Matches'!G174)</f>
+        <f>CONCATENATE("M 41 ",'Elimination Matches'!O174)</f>
       </c>
       <c r="B283" s="28"/>
       <c r="C283" s="28"/>
@@ -8649,10 +8649,10 @@
       <c r="E283" s="28"/>
       <c r="F283" s="28"/>
       <c r="G283" s="28" t="str">
-        <f>CONCATENATE("M 41 ",'Elimination Matches'!O174)</f>
+        <f>CONCATENATE("M 40 ",'Elimination Matches'!G174)</f>
       </c>
       <c r="I283" s="28" t="str">
-        <f>CONCATENATE("M 42 ",'Elimination Matches'!G182)</f>
+        <f>CONCATENATE("M 43 ",'Elimination Matches'!O182)</f>
       </c>
       <c r="J283" s="28"/>
       <c r="K283" s="28"/>
@@ -8660,7 +8660,7 @@
       <c r="M283" s="28"/>
       <c r="N283" s="28"/>
       <c r="O283" s="28" t="str">
-        <f>CONCATENATE("M 43 ",'Elimination Matches'!O182)</f>
+        <f>CONCATENATE("M 42 ",'Elimination Matches'!G182)</f>
       </c>
     </row>
     <row r="285">
@@ -8704,28 +8704,28 @@
       <c r="O289" s="20"/>
     </row>
     <row r="290">
-      <c r="A290" s="29" t="s">
+      <c r="A290" s="30" t="s">
         <v>209</v>
       </c>
       <c r="D290" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="G290" s="30" t="s">
+      <c r="G290" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="I290" s="29" t="s">
+      <c r="I290" s="30" t="s">
         <v>209</v>
       </c>
       <c r="L290" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="O290" s="30" t="s">
+      <c r="O290" s="29" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="28" t="str">
-        <f>CONCATENATE("M 44 ",'Elimination Matches'!G190)</f>
+        <f>CONCATENATE("M 45 ",'Elimination Matches'!O190)</f>
       </c>
       <c r="B291" s="28"/>
       <c r="C291" s="28"/>
@@ -8733,10 +8733,10 @@
       <c r="E291" s="28"/>
       <c r="F291" s="28"/>
       <c r="G291" s="28" t="str">
-        <f>CONCATENATE("M 45 ",'Elimination Matches'!O190)</f>
+        <f>CONCATENATE("M 44 ",'Elimination Matches'!G190)</f>
       </c>
       <c r="I291" s="28" t="str">
-        <f>CONCATENATE("M 46 ",'Elimination Matches'!G198)</f>
+        <f>CONCATENATE("M 47 ",'Elimination Matches'!O198)</f>
       </c>
       <c r="J291" s="28"/>
       <c r="K291" s="28"/>
@@ -8744,7 +8744,7 @@
       <c r="M291" s="28"/>
       <c r="N291" s="28"/>
       <c r="O291" s="28" t="str">
-        <f>CONCATENATE("M 47 ",'Elimination Matches'!O198)</f>
+        <f>CONCATENATE("M 46 ",'Elimination Matches'!G198)</f>
       </c>
     </row>
     <row r="293">
@@ -8788,28 +8788,28 @@
       <c r="O297" s="20"/>
     </row>
     <row r="298">
-      <c r="A298" s="29" t="s">
+      <c r="A298" s="30" t="s">
         <v>209</v>
       </c>
       <c r="D298" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="G298" s="30" t="s">
+      <c r="G298" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="I298" s="29" t="s">
+      <c r="I298" s="30" t="s">
         <v>209</v>
       </c>
       <c r="L298" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="O298" s="30" t="s">
+      <c r="O298" s="29" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="28" t="str">
-        <f>CONCATENATE("M 48 ",'Elimination Matches'!G206)</f>
+        <f>CONCATENATE("M 49 ",'Elimination Matches'!O206)</f>
       </c>
       <c r="B299" s="28"/>
       <c r="C299" s="28"/>
@@ -8817,10 +8817,10 @@
       <c r="E299" s="28"/>
       <c r="F299" s="28"/>
       <c r="G299" s="28" t="str">
-        <f>CONCATENATE("M 49 ",'Elimination Matches'!O206)</f>
+        <f>CONCATENATE("M 48 ",'Elimination Matches'!G206)</f>
       </c>
       <c r="I299" s="28" t="str">
-        <f>CONCATENATE("M 50 ",'Elimination Matches'!G214)</f>
+        <f>CONCATENATE("M 51 ",'Elimination Matches'!O214)</f>
       </c>
       <c r="J299" s="28"/>
       <c r="K299" s="28"/>
@@ -8828,7 +8828,7 @@
       <c r="M299" s="28"/>
       <c r="N299" s="28"/>
       <c r="O299" s="28" t="str">
-        <f>CONCATENATE("M 51 ",'Elimination Matches'!O214)</f>
+        <f>CONCATENATE("M 50 ",'Elimination Matches'!G214)</f>
       </c>
     </row>
     <row r="301">
@@ -8872,28 +8872,28 @@
       <c r="O305" s="20"/>
     </row>
     <row r="306">
-      <c r="A306" s="29" t="s">
+      <c r="A306" s="30" t="s">
         <v>209</v>
       </c>
       <c r="D306" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="G306" s="30" t="s">
+      <c r="G306" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="I306" s="29" t="s">
+      <c r="I306" s="30" t="s">
         <v>209</v>
       </c>
       <c r="L306" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="O306" s="30" t="s">
+      <c r="O306" s="29" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="28" t="str">
-        <f>CONCATENATE("M 52 ",'Elimination Matches'!G222)</f>
+        <f>CONCATENATE("M 53 ",'Elimination Matches'!O222)</f>
       </c>
       <c r="B307" s="28"/>
       <c r="C307" s="28"/>
@@ -8901,10 +8901,10 @@
       <c r="E307" s="28"/>
       <c r="F307" s="28"/>
       <c r="G307" s="28" t="str">
-        <f>CONCATENATE("M 53 ",'Elimination Matches'!O222)</f>
+        <f>CONCATENATE("M 52 ",'Elimination Matches'!G222)</f>
       </c>
       <c r="I307" s="28" t="str">
-        <f>CONCATENATE("M 54 ",'Elimination Matches'!G230)</f>
+        <f>CONCATENATE("M 55 ",'Elimination Matches'!O230)</f>
       </c>
       <c r="J307" s="28"/>
       <c r="K307" s="28"/>
@@ -8912,7 +8912,7 @@
       <c r="M307" s="28"/>
       <c r="N307" s="28"/>
       <c r="O307" s="28" t="str">
-        <f>CONCATENATE("M 55 ",'Elimination Matches'!O230)</f>
+        <f>CONCATENATE("M 54 ",'Elimination Matches'!G230)</f>
       </c>
     </row>
     <row r="309">
@@ -8956,28 +8956,28 @@
       <c r="O313" s="20"/>
     </row>
     <row r="314">
-      <c r="A314" s="29" t="s">
+      <c r="A314" s="30" t="s">
         <v>209</v>
       </c>
       <c r="D314" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="G314" s="30" t="s">
+      <c r="G314" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="I314" s="29" t="s">
+      <c r="I314" s="30" t="s">
         <v>209</v>
       </c>
       <c r="L314" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="O314" s="30" t="s">
+      <c r="O314" s="29" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="28" t="str">
-        <f>CONCATENATE("M 56 ",'Elimination Matches'!G238)</f>
+        <f>CONCATENATE("M 57 ",'Elimination Matches'!O238)</f>
       </c>
       <c r="B315" s="28"/>
       <c r="C315" s="28"/>
@@ -8985,10 +8985,10 @@
       <c r="E315" s="28"/>
       <c r="F315" s="28"/>
       <c r="G315" s="28" t="str">
-        <f>CONCATENATE("M 57 ",'Elimination Matches'!O238)</f>
+        <f>CONCATENATE("M 56 ",'Elimination Matches'!G238)</f>
       </c>
       <c r="I315" s="28" t="str">
-        <f>CONCATENATE("M 58 ",'Elimination Matches'!G246)</f>
+        <f>CONCATENATE("M 59 ",'Elimination Matches'!O246)</f>
       </c>
       <c r="J315" s="28"/>
       <c r="K315" s="28"/>
@@ -8996,7 +8996,7 @@
       <c r="M315" s="28"/>
       <c r="N315" s="28"/>
       <c r="O315" s="28" t="str">
-        <f>CONCATENATE("M 59 ",'Elimination Matches'!O246)</f>
+        <f>CONCATENATE("M 58 ",'Elimination Matches'!G246)</f>
       </c>
     </row>
     <row r="317">
@@ -9059,28 +9059,28 @@
       <c r="O328" s="20"/>
     </row>
     <row r="329">
-      <c r="A329" s="29" t="s">
+      <c r="A329" s="30" t="s">
         <v>209</v>
       </c>
       <c r="D329" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="G329" s="30" t="s">
+      <c r="G329" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="I329" s="29" t="s">
+      <c r="I329" s="30" t="s">
         <v>209</v>
       </c>
       <c r="L329" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="O329" s="30" t="s">
+      <c r="O329" s="29" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="28" t="str">
-        <f>CONCATENATE("M 60 ",'Elimination Matches'!G261)</f>
+        <f>CONCATENATE("M 61 ",'Elimination Matches'!O261)</f>
       </c>
       <c r="B330" s="28"/>
       <c r="C330" s="28"/>
@@ -9088,10 +9088,10 @@
       <c r="E330" s="28"/>
       <c r="F330" s="28"/>
       <c r="G330" s="28" t="str">
-        <f>CONCATENATE("M 61 ",'Elimination Matches'!O261)</f>
+        <f>CONCATENATE("M 60 ",'Elimination Matches'!G261)</f>
       </c>
       <c r="I330" s="28" t="str">
-        <f>CONCATENATE("M 62 ",'Elimination Matches'!G269)</f>
+        <f>CONCATENATE("M 63 ",'Elimination Matches'!O269)</f>
       </c>
       <c r="J330" s="28"/>
       <c r="K330" s="28"/>
@@ -9099,7 +9099,7 @@
       <c r="M330" s="28"/>
       <c r="N330" s="28"/>
       <c r="O330" s="28" t="str">
-        <f>CONCATENATE("M 63 ",'Elimination Matches'!O269)</f>
+        <f>CONCATENATE("M 62 ",'Elimination Matches'!G269)</f>
       </c>
     </row>
     <row r="332">
@@ -9143,28 +9143,28 @@
       <c r="O336" s="20"/>
     </row>
     <row r="337">
-      <c r="A337" s="29" t="s">
+      <c r="A337" s="30" t="s">
         <v>209</v>
       </c>
       <c r="D337" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="G337" s="30" t="s">
+      <c r="G337" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="I337" s="29" t="s">
+      <c r="I337" s="30" t="s">
         <v>209</v>
       </c>
       <c r="L337" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="O337" s="30" t="s">
+      <c r="O337" s="29" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="28" t="str">
-        <f>CONCATENATE("M 64 ",'Elimination Matches'!G277)</f>
+        <f>CONCATENATE("M 65 ",'Elimination Matches'!O277)</f>
       </c>
       <c r="B338" s="28"/>
       <c r="C338" s="28"/>
@@ -9172,10 +9172,10 @@
       <c r="E338" s="28"/>
       <c r="F338" s="28"/>
       <c r="G338" s="28" t="str">
-        <f>CONCATENATE("M 65 ",'Elimination Matches'!O277)</f>
+        <f>CONCATENATE("M 64 ",'Elimination Matches'!G277)</f>
       </c>
       <c r="I338" s="28" t="str">
-        <f>CONCATENATE("M 66 ",'Elimination Matches'!G285)</f>
+        <f>CONCATENATE("M 67 ",'Elimination Matches'!O285)</f>
       </c>
       <c r="J338" s="28"/>
       <c r="K338" s="28"/>
@@ -9183,7 +9183,7 @@
       <c r="M338" s="28"/>
       <c r="N338" s="28"/>
       <c r="O338" s="28" t="str">
-        <f>CONCATENATE("M 67 ",'Elimination Matches'!O285)</f>
+        <f>CONCATENATE("M 66 ",'Elimination Matches'!G285)</f>
       </c>
     </row>
     <row r="340">
@@ -9227,28 +9227,28 @@
       <c r="O344" s="20"/>
     </row>
     <row r="345">
-      <c r="A345" s="29" t="s">
+      <c r="A345" s="30" t="s">
         <v>209</v>
       </c>
       <c r="D345" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="G345" s="30" t="s">
+      <c r="G345" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="I345" s="29" t="s">
+      <c r="I345" s="30" t="s">
         <v>209</v>
       </c>
       <c r="L345" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="O345" s="30" t="s">
+      <c r="O345" s="29" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="28" t="str">
-        <f>CONCATENATE("M 68 ",'Elimination Matches'!G293)</f>
+        <f>CONCATENATE("M 69 ",'Elimination Matches'!O293)</f>
       </c>
       <c r="B346" s="28"/>
       <c r="C346" s="28"/>
@@ -9256,10 +9256,10 @@
       <c r="E346" s="28"/>
       <c r="F346" s="28"/>
       <c r="G346" s="28" t="str">
-        <f>CONCATENATE("M 69 ",'Elimination Matches'!O293)</f>
+        <f>CONCATENATE("M 68 ",'Elimination Matches'!G293)</f>
       </c>
       <c r="I346" s="28" t="str">
-        <f>CONCATENATE("M 70 ",'Elimination Matches'!G301)</f>
+        <f>CONCATENATE("M 71 ",'Elimination Matches'!O301)</f>
       </c>
       <c r="J346" s="28"/>
       <c r="K346" s="28"/>
@@ -9267,7 +9267,7 @@
       <c r="M346" s="28"/>
       <c r="N346" s="28"/>
       <c r="O346" s="28" t="str">
-        <f>CONCATENATE("M 71 ",'Elimination Matches'!O301)</f>
+        <f>CONCATENATE("M 70 ",'Elimination Matches'!G301)</f>
       </c>
     </row>
     <row r="348">
@@ -9311,28 +9311,28 @@
       <c r="O352" s="20"/>
     </row>
     <row r="353">
-      <c r="A353" s="29" t="s">
+      <c r="A353" s="30" t="s">
         <v>209</v>
       </c>
       <c r="D353" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="G353" s="30" t="s">
+      <c r="G353" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="I353" s="29" t="s">
+      <c r="I353" s="30" t="s">
         <v>209</v>
       </c>
       <c r="L353" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="O353" s="30" t="s">
+      <c r="O353" s="29" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="28" t="str">
-        <f>CONCATENATE("M 72 ",'Elimination Matches'!G309)</f>
+        <f>CONCATENATE("M 73 ",'Elimination Matches'!O309)</f>
       </c>
       <c r="B354" s="28"/>
       <c r="C354" s="28"/>
@@ -9340,10 +9340,10 @@
       <c r="E354" s="28"/>
       <c r="F354" s="28"/>
       <c r="G354" s="28" t="str">
-        <f>CONCATENATE("M 73 ",'Elimination Matches'!O309)</f>
+        <f>CONCATENATE("M 72 ",'Elimination Matches'!G309)</f>
       </c>
       <c r="I354" s="28" t="str">
-        <f>CONCATENATE("M 74 ",'Elimination Matches'!G317)</f>
+        <f>CONCATENATE("M 75 ",'Elimination Matches'!O317)</f>
       </c>
       <c r="J354" s="28"/>
       <c r="K354" s="28"/>
@@ -9351,7 +9351,7 @@
       <c r="M354" s="28"/>
       <c r="N354" s="28"/>
       <c r="O354" s="28" t="str">
-        <f>CONCATENATE("M 75 ",'Elimination Matches'!O317)</f>
+        <f>CONCATENATE("M 74 ",'Elimination Matches'!G317)</f>
       </c>
     </row>
     <row r="356">
@@ -9414,28 +9414,28 @@
       <c r="O367" s="20"/>
     </row>
     <row r="368">
-      <c r="A368" s="29" t="s">
+      <c r="A368" s="30" t="s">
         <v>209</v>
       </c>
       <c r="D368" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="G368" s="30" t="s">
+      <c r="G368" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="I368" s="29" t="s">
+      <c r="I368" s="30" t="s">
         <v>209</v>
       </c>
       <c r="L368" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="O368" s="30" t="s">
+      <c r="O368" s="29" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="28" t="str">
-        <f>CONCATENATE("M 76 ",'Elimination Matches'!G332)</f>
+        <f>CONCATENATE("M 77 ",'Elimination Matches'!O332)</f>
       </c>
       <c r="B369" s="28"/>
       <c r="C369" s="28"/>
@@ -9443,10 +9443,10 @@
       <c r="E369" s="28"/>
       <c r="F369" s="28"/>
       <c r="G369" s="28" t="str">
-        <f>CONCATENATE("M 77 ",'Elimination Matches'!O332)</f>
+        <f>CONCATENATE("M 76 ",'Elimination Matches'!G332)</f>
       </c>
       <c r="I369" s="28" t="str">
-        <f>CONCATENATE("M 78 ",'Elimination Matches'!G340)</f>
+        <f>CONCATENATE("M 79 ",'Elimination Matches'!O340)</f>
       </c>
       <c r="J369" s="28"/>
       <c r="K369" s="28"/>
@@ -9454,7 +9454,7 @@
       <c r="M369" s="28"/>
       <c r="N369" s="28"/>
       <c r="O369" s="28" t="str">
-        <f>CONCATENATE("M 79 ",'Elimination Matches'!O340)</f>
+        <f>CONCATENATE("M 78 ",'Elimination Matches'!G340)</f>
       </c>
     </row>
     <row r="371">
@@ -9498,28 +9498,28 @@
       <c r="O375" s="20"/>
     </row>
     <row r="376">
-      <c r="A376" s="29" t="s">
+      <c r="A376" s="30" t="s">
         <v>209</v>
       </c>
       <c r="D376" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="G376" s="30" t="s">
+      <c r="G376" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="I376" s="29" t="s">
+      <c r="I376" s="30" t="s">
         <v>209</v>
       </c>
       <c r="L376" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="O376" s="30" t="s">
+      <c r="O376" s="29" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="28" t="str">
-        <f>CONCATENATE("M 80 ",'Elimination Matches'!G348)</f>
+        <f>CONCATENATE("M 81 ",'Elimination Matches'!O348)</f>
       </c>
       <c r="B377" s="28"/>
       <c r="C377" s="28"/>
@@ -9527,10 +9527,10 @@
       <c r="E377" s="28"/>
       <c r="F377" s="28"/>
       <c r="G377" s="28" t="str">
-        <f>CONCATENATE("M 81 ",'Elimination Matches'!O348)</f>
+        <f>CONCATENATE("M 80 ",'Elimination Matches'!G348)</f>
       </c>
       <c r="I377" s="28" t="str">
-        <f>CONCATENATE("M 82 ",'Elimination Matches'!G356)</f>
+        <f>CONCATENATE("M 83 ",'Elimination Matches'!O356)</f>
       </c>
       <c r="J377" s="28"/>
       <c r="K377" s="28"/>
@@ -9538,7 +9538,7 @@
       <c r="M377" s="28"/>
       <c r="N377" s="28"/>
       <c r="O377" s="28" t="str">
-        <f>CONCATENATE("M 83 ",'Elimination Matches'!O356)</f>
+        <f>CONCATENATE("M 82 ",'Elimination Matches'!G356)</f>
       </c>
     </row>
     <row r="379">
@@ -9601,22 +9601,22 @@
       <c r="O390" s="20"/>
     </row>
     <row r="391">
-      <c r="A391" s="29" t="s">
+      <c r="A391" s="30" t="s">
         <v>209</v>
       </c>
       <c r="D391" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="G391" s="30" t="s">
+      <c r="G391" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="I391" s="29" t="s">
+      <c r="I391" s="30" t="s">
         <v>209</v>
       </c>
       <c r="L391" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="O391" s="30" t="s">
+      <c r="O391" s="29" t="s">
         <v>211</v>
       </c>
     </row>
@@ -9695,13 +9695,13 @@
       <c r="G405" s="20"/>
     </row>
     <row r="406">
-      <c r="A406" s="29" t="s">
+      <c r="A406" s="30" t="s">
         <v>209</v>
       </c>
       <c r="D406" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="G406" s="30" t="s">
+      <c r="G406" s="29" t="s">
         <v>211</v>
       </c>
     </row>

--- a/playoffs-example-large.xlsx
+++ b/playoffs-example-large.xlsx
@@ -1453,11 +1453,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="15"/>
-    <col customWidth="true" max="26" min="2" width="30"/>
+    <col customWidth="true" max="1" min="1" width="9"/>
+    <col customWidth="true" max="3" min="2" width="20"/>
+    <col customWidth="true" max="26" min="4" width="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2760,7 +2764,8 @@
       </c>
     </row>
   </sheetData>
-  <pageSetup orientation="landscape"/>
+  <printOptions horizontalCentered="true" verticalCentered="true"/>
+  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
@@ -2768,7 +2773,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="20.83"/>
+    <col customWidth="true" max="1" min="1" width="25"/>
     <col customWidth="true" max="2" min="2" width="10"/>
     <col customWidth="true" max="26" min="3" width="3.5"/>
   </cols>
@@ -2991,7 +2996,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="20.83"/>
+    <col customWidth="true" max="1" min="1" width="25"/>
     <col customWidth="true" max="2" min="2" width="10"/>
     <col customWidth="true" max="26" min="3" width="3.5"/>
   </cols>
@@ -3223,7 +3228,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="20.83"/>
+    <col customWidth="true" max="1" min="1" width="25"/>
     <col customWidth="true" max="2" min="2" width="10"/>
     <col customWidth="true" max="26" min="3" width="3.5"/>
   </cols>
@@ -3446,7 +3451,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="20.83"/>
+    <col customWidth="true" max="1" min="1" width="25"/>
     <col customWidth="true" max="2" min="2" width="10"/>
     <col customWidth="true" max="26" min="3" width="3.5"/>
   </cols>
@@ -3678,7 +3683,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="20.83"/>
+    <col customWidth="true" max="1" min="1" width="25"/>
     <col customWidth="true" max="2" min="2" width="10"/>
     <col customWidth="true" max="26" min="3" width="3.5"/>
   </cols>
@@ -3901,7 +3906,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="20.83"/>
+    <col customWidth="true" max="1" min="1" width="25"/>
     <col customWidth="true" max="2" min="2" width="10"/>
     <col customWidth="true" max="26" min="3" width="3.5"/>
   </cols>
@@ -9131,7 +9136,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="20.83"/>
+    <col customWidth="true" max="1" min="1" width="25"/>
     <col customWidth="true" max="2" min="2" width="10"/>
     <col customWidth="true" max="26" min="3" width="3.5"/>
   </cols>
@@ -9354,7 +9359,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="20.83"/>
+    <col customWidth="true" max="1" min="1" width="25"/>
     <col customWidth="true" max="2" min="2" width="10"/>
     <col customWidth="true" max="26" min="3" width="3.5"/>
   </cols>

--- a/playoffs-example-large.xlsx
+++ b/playoffs-example-large.xlsx
@@ -10,7 +10,6 @@
     <sheet name="data" sheetId="1" r:id="rId1"/>
     <sheet name="Time Estimator" sheetId="2" r:id="rId4"/>
     <sheet name="Elimination Matches" sheetId="5" r:id="rId7"/>
-    <sheet name="Names to Print" sheetId="6" r:id="rId8"/>
     <sheet name="Tree 1" sheetId="8" r:id="rId11"/>
     <sheet name="Tree 2" sheetId="9" r:id="rId12"/>
     <sheet name="Tree 3" sheetId="10" r:id="rId13"/>
@@ -19,9 +18,12 @@
     <sheet name="Tree 6" sheetId="13" r:id="rId16"/>
     <sheet name="Tree 7" sheetId="14" r:id="rId17"/>
     <sheet name="Tree 8" sheetId="15" r:id="rId18"/>
+    <sheet name="Names to Print A" sheetId="16" r:id="rId19"/>
+    <sheet name="Names to Print B" sheetId="17" r:id="rId20"/>
   </sheets>
   <definedNames>
-    <definedName localSheetId="3" name="_xlnm.Print_Area">'Names to Print'!$A$1:$B$91</definedName>
+    <definedName localSheetId="11" name="_xlnm.Print_Area">'Names to Print A'!$A$1:$B$46</definedName>
+    <definedName localSheetId="12" name="_xlnm.Print_Area">'Names to Print B'!$A$1:$B$45</definedName>
     <definedName localSheetId="2" name="_xlnm.Print_Area">'Elimination Matches'!$A$1:$O$404</definedName>
   </definedNames>
   <calcPr calcId="122211"/>
@@ -29,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="310">
   <si>
     <t>Number of pools</t>
   </si>
@@ -919,13 +921,25 @@
     <t>Round 4 - Match 83</t>
   </si>
   <si>
-    <t>Round 5 - Match 0</t>
-  </si>
-  <si>
-    <t>Round 6 - Match 0</t>
-  </si>
-  <si>
-    <t>Round 7 - Match 0</t>
+    <t>Round 5 - Match 84</t>
+  </si>
+  <si>
+    <t>Round 5 - Match 86</t>
+  </si>
+  <si>
+    <t>Round 5 - Match 85</t>
+  </si>
+  <si>
+    <t>Round 5 - Match 87</t>
+  </si>
+  <si>
+    <t>Round 6 - Match 88</t>
+  </si>
+  <si>
+    <t>Round 6 - Match 89</t>
+  </si>
+  <si>
+    <t>Round 7 - Match 90</t>
   </si>
   <si>
     <t>Tournament Summary</t>
@@ -4134,6 +4148,798 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <cols>
+    <col customWidth="true" max="1" min="1" width="30"/>
+    <col customWidth="true" max="2" min="2" width="160"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="270" customHeight="true">
+      <c r="A1" s="17">
+        <v>0</v>
+      </c>
+      <c r="B1" s="18" t="str">
+        <f>data!D3</f>
+      </c>
+    </row>
+    <row r="2" ht="270" customHeight="true">
+      <c r="A2" s="17">
+        <v>1</v>
+      </c>
+      <c r="B2" s="18" t="str">
+        <f>data!D4</f>
+      </c>
+    </row>
+    <row r="3" ht="270" customHeight="true">
+      <c r="A3" s="17">
+        <v>2</v>
+      </c>
+      <c r="B3" s="18" t="str">
+        <f>data!D5</f>
+      </c>
+    </row>
+    <row r="4" ht="270" customHeight="true">
+      <c r="A4" s="17">
+        <v>3</v>
+      </c>
+      <c r="B4" s="18" t="str">
+        <f>data!D6</f>
+      </c>
+    </row>
+    <row r="5" ht="270" customHeight="true">
+      <c r="A5" s="17">
+        <v>4</v>
+      </c>
+      <c r="B5" s="18" t="str">
+        <f>data!D7</f>
+      </c>
+    </row>
+    <row r="6" ht="270" customHeight="true">
+      <c r="A6" s="17">
+        <v>5</v>
+      </c>
+      <c r="B6" s="18" t="str">
+        <f>data!D8</f>
+      </c>
+    </row>
+    <row r="7" ht="270" customHeight="true">
+      <c r="A7" s="17">
+        <v>6</v>
+      </c>
+      <c r="B7" s="18" t="str">
+        <f>data!D9</f>
+      </c>
+    </row>
+    <row r="8" ht="270" customHeight="true">
+      <c r="A8" s="17">
+        <v>7</v>
+      </c>
+      <c r="B8" s="18" t="str">
+        <f>data!D10</f>
+      </c>
+    </row>
+    <row r="9" ht="270" customHeight="true">
+      <c r="A9" s="17">
+        <v>8</v>
+      </c>
+      <c r="B9" s="18" t="str">
+        <f>data!D11</f>
+      </c>
+    </row>
+    <row r="10" ht="270" customHeight="true">
+      <c r="A10" s="17">
+        <v>9</v>
+      </c>
+      <c r="B10" s="18" t="str">
+        <f>data!D12</f>
+      </c>
+    </row>
+    <row r="11" ht="270" customHeight="true">
+      <c r="A11" s="17">
+        <v>10</v>
+      </c>
+      <c r="B11" s="18" t="str">
+        <f>data!D13</f>
+      </c>
+    </row>
+    <row r="12" ht="270" customHeight="true">
+      <c r="A12" s="17">
+        <v>11</v>
+      </c>
+      <c r="B12" s="18" t="str">
+        <f>data!D14</f>
+      </c>
+    </row>
+    <row r="13" ht="270" customHeight="true">
+      <c r="A13" s="17">
+        <v>12</v>
+      </c>
+      <c r="B13" s="18" t="str">
+        <f>data!D15</f>
+      </c>
+    </row>
+    <row r="14" ht="270" customHeight="true">
+      <c r="A14" s="17">
+        <v>13</v>
+      </c>
+      <c r="B14" s="18" t="str">
+        <f>data!D16</f>
+      </c>
+    </row>
+    <row r="15" ht="270" customHeight="true">
+      <c r="A15" s="17">
+        <v>14</v>
+      </c>
+      <c r="B15" s="18" t="str">
+        <f>data!D17</f>
+      </c>
+    </row>
+    <row r="16" ht="270" customHeight="true">
+      <c r="A16" s="17">
+        <v>15</v>
+      </c>
+      <c r="B16" s="18" t="str">
+        <f>data!D18</f>
+      </c>
+    </row>
+    <row r="17" ht="270" customHeight="true">
+      <c r="A17" s="17">
+        <v>16</v>
+      </c>
+      <c r="B17" s="18" t="str">
+        <f>data!D19</f>
+      </c>
+    </row>
+    <row r="18" ht="270" customHeight="true">
+      <c r="A18" s="17">
+        <v>17</v>
+      </c>
+      <c r="B18" s="18" t="str">
+        <f>data!D20</f>
+      </c>
+    </row>
+    <row r="19" ht="270" customHeight="true">
+      <c r="A19" s="17">
+        <v>18</v>
+      </c>
+      <c r="B19" s="18" t="str">
+        <f>data!D21</f>
+      </c>
+    </row>
+    <row r="20" ht="270" customHeight="true">
+      <c r="A20" s="17">
+        <v>19</v>
+      </c>
+      <c r="B20" s="18" t="str">
+        <f>data!D22</f>
+      </c>
+    </row>
+    <row r="21" ht="270" customHeight="true">
+      <c r="A21" s="17">
+        <v>20</v>
+      </c>
+      <c r="B21" s="18" t="str">
+        <f>data!D23</f>
+      </c>
+    </row>
+    <row r="22" ht="270" customHeight="true">
+      <c r="A22" s="17">
+        <v>21</v>
+      </c>
+      <c r="B22" s="18" t="str">
+        <f>data!D24</f>
+      </c>
+    </row>
+    <row r="23" ht="270" customHeight="true">
+      <c r="A23" s="17">
+        <v>22</v>
+      </c>
+      <c r="B23" s="18" t="str">
+        <f>data!D25</f>
+      </c>
+    </row>
+    <row r="24" ht="270" customHeight="true">
+      <c r="A24" s="17">
+        <v>23</v>
+      </c>
+      <c r="B24" s="18" t="str">
+        <f>data!D26</f>
+      </c>
+    </row>
+    <row r="25" ht="270" customHeight="true">
+      <c r="A25" s="17">
+        <v>24</v>
+      </c>
+      <c r="B25" s="18" t="str">
+        <f>data!D27</f>
+      </c>
+    </row>
+    <row r="26" ht="270" customHeight="true">
+      <c r="A26" s="17">
+        <v>25</v>
+      </c>
+      <c r="B26" s="18" t="str">
+        <f>data!D28</f>
+      </c>
+    </row>
+    <row r="27" ht="270" customHeight="true">
+      <c r="A27" s="17">
+        <v>26</v>
+      </c>
+      <c r="B27" s="18" t="str">
+        <f>data!D29</f>
+      </c>
+    </row>
+    <row r="28" ht="270" customHeight="true">
+      <c r="A28" s="17">
+        <v>27</v>
+      </c>
+      <c r="B28" s="18" t="str">
+        <f>data!D30</f>
+      </c>
+    </row>
+    <row r="29" ht="270" customHeight="true">
+      <c r="A29" s="17">
+        <v>28</v>
+      </c>
+      <c r="B29" s="18" t="str">
+        <f>data!D31</f>
+      </c>
+    </row>
+    <row r="30" ht="270" customHeight="true">
+      <c r="A30" s="17">
+        <v>29</v>
+      </c>
+      <c r="B30" s="18" t="str">
+        <f>data!D32</f>
+      </c>
+    </row>
+    <row r="31" ht="270" customHeight="true">
+      <c r="A31" s="17">
+        <v>30</v>
+      </c>
+      <c r="B31" s="18" t="str">
+        <f>data!D33</f>
+      </c>
+    </row>
+    <row r="32" ht="270" customHeight="true">
+      <c r="A32" s="17">
+        <v>31</v>
+      </c>
+      <c r="B32" s="18" t="str">
+        <f>data!D34</f>
+      </c>
+    </row>
+    <row r="33" ht="270" customHeight="true">
+      <c r="A33" s="17">
+        <v>32</v>
+      </c>
+      <c r="B33" s="18" t="str">
+        <f>data!D35</f>
+      </c>
+    </row>
+    <row r="34" ht="270" customHeight="true">
+      <c r="A34" s="17">
+        <v>33</v>
+      </c>
+      <c r="B34" s="18" t="str">
+        <f>data!D36</f>
+      </c>
+    </row>
+    <row r="35" ht="270" customHeight="true">
+      <c r="A35" s="17">
+        <v>34</v>
+      </c>
+      <c r="B35" s="18" t="str">
+        <f>data!D37</f>
+      </c>
+    </row>
+    <row r="36" ht="270" customHeight="true">
+      <c r="A36" s="17">
+        <v>35</v>
+      </c>
+      <c r="B36" s="18" t="str">
+        <f>data!D38</f>
+      </c>
+    </row>
+    <row r="37" ht="270" customHeight="true">
+      <c r="A37" s="17">
+        <v>36</v>
+      </c>
+      <c r="B37" s="18" t="str">
+        <f>data!D39</f>
+      </c>
+    </row>
+    <row r="38" ht="270" customHeight="true">
+      <c r="A38" s="17">
+        <v>37</v>
+      </c>
+      <c r="B38" s="18" t="str">
+        <f>data!D40</f>
+      </c>
+    </row>
+    <row r="39" ht="270" customHeight="true">
+      <c r="A39" s="17">
+        <v>38</v>
+      </c>
+      <c r="B39" s="18" t="str">
+        <f>data!D41</f>
+      </c>
+    </row>
+    <row r="40" ht="270" customHeight="true">
+      <c r="A40" s="17">
+        <v>39</v>
+      </c>
+      <c r="B40" s="18" t="str">
+        <f>data!D42</f>
+      </c>
+    </row>
+    <row r="41" ht="270" customHeight="true">
+      <c r="A41" s="17">
+        <v>40</v>
+      </c>
+      <c r="B41" s="18" t="str">
+        <f>data!D43</f>
+      </c>
+    </row>
+    <row r="42" ht="270" customHeight="true">
+      <c r="A42" s="17">
+        <v>41</v>
+      </c>
+      <c r="B42" s="18" t="str">
+        <f>data!D44</f>
+      </c>
+    </row>
+    <row r="43" ht="270" customHeight="true">
+      <c r="A43" s="17">
+        <v>42</v>
+      </c>
+      <c r="B43" s="18" t="str">
+        <f>data!D45</f>
+      </c>
+    </row>
+    <row r="44" ht="270" customHeight="true">
+      <c r="A44" s="17">
+        <v>43</v>
+      </c>
+      <c r="B44" s="18" t="str">
+        <f>data!D46</f>
+      </c>
+    </row>
+    <row r="45" ht="270" customHeight="true">
+      <c r="A45" s="17">
+        <v>44</v>
+      </c>
+      <c r="B45" s="18" t="str">
+        <f>data!D47</f>
+      </c>
+    </row>
+    <row r="46" ht="270" customHeight="true">
+      <c r="A46" s="17">
+        <v>45</v>
+      </c>
+      <c r="B46" s="18" t="str">
+        <f>data!D48</f>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.1" right="0.1" top="0.1" bottom="0.1" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="8"/>
+  <rowBreaks count="15" manualBreakCount="15">
+    <brk id="3" max="16383" man="true"/>
+    <brk id="6" max="16383" man="true"/>
+    <brk id="9" max="16383" man="true"/>
+    <brk id="12" max="16383" man="true"/>
+    <brk id="15" max="16383" man="true"/>
+    <brk id="18" max="16383" man="true"/>
+    <brk id="21" max="16383" man="true"/>
+    <brk id="24" max="16383" man="true"/>
+    <brk id="27" max="16383" man="true"/>
+    <brk id="30" max="16383" man="true"/>
+    <brk id="33" max="16383" man="true"/>
+    <brk id="36" max="16383" man="true"/>
+    <brk id="39" max="16383" man="true"/>
+    <brk id="42" max="16383" man="true"/>
+    <brk id="45" max="16383" man="true"/>
+  </rowBreaks>
+  <colBreaks/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <cols>
+    <col customWidth="true" max="1" min="1" width="30"/>
+    <col customWidth="true" max="2" min="2" width="160"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="270" customHeight="true">
+      <c r="A1" s="17">
+        <v>46</v>
+      </c>
+      <c r="B1" s="18" t="str">
+        <f>data!D49</f>
+      </c>
+    </row>
+    <row r="2" ht="270" customHeight="true">
+      <c r="A2" s="17">
+        <v>47</v>
+      </c>
+      <c r="B2" s="18" t="str">
+        <f>data!D50</f>
+      </c>
+    </row>
+    <row r="3" ht="270" customHeight="true">
+      <c r="A3" s="17">
+        <v>48</v>
+      </c>
+      <c r="B3" s="18" t="str">
+        <f>data!D51</f>
+      </c>
+    </row>
+    <row r="4" ht="270" customHeight="true">
+      <c r="A4" s="17">
+        <v>49</v>
+      </c>
+      <c r="B4" s="18" t="str">
+        <f>data!D52</f>
+      </c>
+    </row>
+    <row r="5" ht="270" customHeight="true">
+      <c r="A5" s="17">
+        <v>50</v>
+      </c>
+      <c r="B5" s="18" t="str">
+        <f>data!D53</f>
+      </c>
+    </row>
+    <row r="6" ht="270" customHeight="true">
+      <c r="A6" s="17">
+        <v>51</v>
+      </c>
+      <c r="B6" s="18" t="str">
+        <f>data!D54</f>
+      </c>
+    </row>
+    <row r="7" ht="270" customHeight="true">
+      <c r="A7" s="17">
+        <v>52</v>
+      </c>
+      <c r="B7" s="18" t="str">
+        <f>data!D55</f>
+      </c>
+    </row>
+    <row r="8" ht="270" customHeight="true">
+      <c r="A8" s="17">
+        <v>53</v>
+      </c>
+      <c r="B8" s="18" t="str">
+        <f>data!D56</f>
+      </c>
+    </row>
+    <row r="9" ht="270" customHeight="true">
+      <c r="A9" s="17">
+        <v>54</v>
+      </c>
+      <c r="B9" s="18" t="str">
+        <f>data!D57</f>
+      </c>
+    </row>
+    <row r="10" ht="270" customHeight="true">
+      <c r="A10" s="17">
+        <v>55</v>
+      </c>
+      <c r="B10" s="18" t="str">
+        <f>data!D58</f>
+      </c>
+    </row>
+    <row r="11" ht="270" customHeight="true">
+      <c r="A11" s="17">
+        <v>56</v>
+      </c>
+      <c r="B11" s="18" t="str">
+        <f>data!D59</f>
+      </c>
+    </row>
+    <row r="12" ht="270" customHeight="true">
+      <c r="A12" s="17">
+        <v>57</v>
+      </c>
+      <c r="B12" s="18" t="str">
+        <f>data!D60</f>
+      </c>
+    </row>
+    <row r="13" ht="270" customHeight="true">
+      <c r="A13" s="17">
+        <v>58</v>
+      </c>
+      <c r="B13" s="18" t="str">
+        <f>data!D61</f>
+      </c>
+    </row>
+    <row r="14" ht="270" customHeight="true">
+      <c r="A14" s="17">
+        <v>59</v>
+      </c>
+      <c r="B14" s="18" t="str">
+        <f>data!D62</f>
+      </c>
+    </row>
+    <row r="15" ht="270" customHeight="true">
+      <c r="A15" s="17">
+        <v>60</v>
+      </c>
+      <c r="B15" s="18" t="str">
+        <f>data!D63</f>
+      </c>
+    </row>
+    <row r="16" ht="270" customHeight="true">
+      <c r="A16" s="17">
+        <v>61</v>
+      </c>
+      <c r="B16" s="18" t="str">
+        <f>data!D64</f>
+      </c>
+    </row>
+    <row r="17" ht="270" customHeight="true">
+      <c r="A17" s="17">
+        <v>62</v>
+      </c>
+      <c r="B17" s="18" t="str">
+        <f>data!D65</f>
+      </c>
+    </row>
+    <row r="18" ht="270" customHeight="true">
+      <c r="A18" s="17">
+        <v>63</v>
+      </c>
+      <c r="B18" s="18" t="str">
+        <f>data!D66</f>
+      </c>
+    </row>
+    <row r="19" ht="270" customHeight="true">
+      <c r="A19" s="17">
+        <v>64</v>
+      </c>
+      <c r="B19" s="18" t="str">
+        <f>data!D67</f>
+      </c>
+    </row>
+    <row r="20" ht="270" customHeight="true">
+      <c r="A20" s="17">
+        <v>65</v>
+      </c>
+      <c r="B20" s="18" t="str">
+        <f>data!D68</f>
+      </c>
+    </row>
+    <row r="21" ht="270" customHeight="true">
+      <c r="A21" s="17">
+        <v>66</v>
+      </c>
+      <c r="B21" s="18" t="str">
+        <f>data!D69</f>
+      </c>
+    </row>
+    <row r="22" ht="270" customHeight="true">
+      <c r="A22" s="17">
+        <v>67</v>
+      </c>
+      <c r="B22" s="18" t="str">
+        <f>data!D70</f>
+      </c>
+    </row>
+    <row r="23" ht="270" customHeight="true">
+      <c r="A23" s="17">
+        <v>68</v>
+      </c>
+      <c r="B23" s="18" t="str">
+        <f>data!D71</f>
+      </c>
+    </row>
+    <row r="24" ht="270" customHeight="true">
+      <c r="A24" s="17">
+        <v>69</v>
+      </c>
+      <c r="B24" s="18" t="str">
+        <f>data!D72</f>
+      </c>
+    </row>
+    <row r="25" ht="270" customHeight="true">
+      <c r="A25" s="17">
+        <v>70</v>
+      </c>
+      <c r="B25" s="18" t="str">
+        <f>data!D73</f>
+      </c>
+    </row>
+    <row r="26" ht="270" customHeight="true">
+      <c r="A26" s="17">
+        <v>71</v>
+      </c>
+      <c r="B26" s="18" t="str">
+        <f>data!D74</f>
+      </c>
+    </row>
+    <row r="27" ht="270" customHeight="true">
+      <c r="A27" s="17">
+        <v>72</v>
+      </c>
+      <c r="B27" s="18" t="str">
+        <f>data!D75</f>
+      </c>
+    </row>
+    <row r="28" ht="270" customHeight="true">
+      <c r="A28" s="17">
+        <v>73</v>
+      </c>
+      <c r="B28" s="18" t="str">
+        <f>data!D76</f>
+      </c>
+    </row>
+    <row r="29" ht="270" customHeight="true">
+      <c r="A29" s="17">
+        <v>74</v>
+      </c>
+      <c r="B29" s="18" t="str">
+        <f>data!D77</f>
+      </c>
+    </row>
+    <row r="30" ht="270" customHeight="true">
+      <c r="A30" s="17">
+        <v>75</v>
+      </c>
+      <c r="B30" s="18" t="str">
+        <f>data!D78</f>
+      </c>
+    </row>
+    <row r="31" ht="270" customHeight="true">
+      <c r="A31" s="17">
+        <v>76</v>
+      </c>
+      <c r="B31" s="18" t="str">
+        <f>data!D79</f>
+      </c>
+    </row>
+    <row r="32" ht="270" customHeight="true">
+      <c r="A32" s="17">
+        <v>77</v>
+      </c>
+      <c r="B32" s="18" t="str">
+        <f>data!D80</f>
+      </c>
+    </row>
+    <row r="33" ht="270" customHeight="true">
+      <c r="A33" s="17">
+        <v>78</v>
+      </c>
+      <c r="B33" s="18" t="str">
+        <f>data!D81</f>
+      </c>
+    </row>
+    <row r="34" ht="270" customHeight="true">
+      <c r="A34" s="17">
+        <v>79</v>
+      </c>
+      <c r="B34" s="18" t="str">
+        <f>data!D82</f>
+      </c>
+    </row>
+    <row r="35" ht="270" customHeight="true">
+      <c r="A35" s="17">
+        <v>80</v>
+      </c>
+      <c r="B35" s="18" t="str">
+        <f>data!D83</f>
+      </c>
+    </row>
+    <row r="36" ht="270" customHeight="true">
+      <c r="A36" s="17">
+        <v>81</v>
+      </c>
+      <c r="B36" s="18" t="str">
+        <f>data!D84</f>
+      </c>
+    </row>
+    <row r="37" ht="270" customHeight="true">
+      <c r="A37" s="17">
+        <v>82</v>
+      </c>
+      <c r="B37" s="18" t="str">
+        <f>data!D85</f>
+      </c>
+    </row>
+    <row r="38" ht="270" customHeight="true">
+      <c r="A38" s="17">
+        <v>83</v>
+      </c>
+      <c r="B38" s="18" t="str">
+        <f>data!D86</f>
+      </c>
+    </row>
+    <row r="39" ht="270" customHeight="true">
+      <c r="A39" s="17">
+        <v>84</v>
+      </c>
+      <c r="B39" s="18" t="str">
+        <f>data!D87</f>
+      </c>
+    </row>
+    <row r="40" ht="270" customHeight="true">
+      <c r="A40" s="17">
+        <v>85</v>
+      </c>
+      <c r="B40" s="18" t="str">
+        <f>data!D88</f>
+      </c>
+    </row>
+    <row r="41" ht="270" customHeight="true">
+      <c r="A41" s="17">
+        <v>86</v>
+      </c>
+      <c r="B41" s="18" t="str">
+        <f>data!D89</f>
+      </c>
+    </row>
+    <row r="42" ht="270" customHeight="true">
+      <c r="A42" s="17">
+        <v>87</v>
+      </c>
+      <c r="B42" s="18" t="str">
+        <f>data!D90</f>
+      </c>
+    </row>
+    <row r="43" ht="270" customHeight="true">
+      <c r="A43" s="17">
+        <v>88</v>
+      </c>
+      <c r="B43" s="18" t="str">
+        <f>data!D91</f>
+      </c>
+    </row>
+    <row r="44" ht="270" customHeight="true">
+      <c r="A44" s="17">
+        <v>89</v>
+      </c>
+      <c r="B44" s="18" t="str">
+        <f>data!D92</f>
+      </c>
+    </row>
+    <row r="45" ht="270" customHeight="true">
+      <c r="A45" s="17">
+        <v>90</v>
+      </c>
+      <c r="B45" s="18" t="str">
+        <f>data!D93</f>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.1" right="0.1" top="0.1" bottom="0.1" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="8"/>
+  <rowBreaks count="15" manualBreakCount="15">
+    <brk id="3" max="16383" man="true"/>
+    <brk id="6" max="16383" man="true"/>
+    <brk id="9" max="16383" man="true"/>
+    <brk id="12" max="16383" man="true"/>
+    <brk id="15" max="16383" man="true"/>
+    <brk id="18" max="16383" man="true"/>
+    <brk id="21" max="16383" man="true"/>
+    <brk id="24" max="16383" man="true"/>
+    <brk id="27" max="16383" man="true"/>
+    <brk id="30" max="16383" man="true"/>
+    <brk id="33" max="16383" man="true"/>
+    <brk id="36" max="16383" man="true"/>
+    <brk id="39" max="16383" man="true"/>
+    <brk id="42" max="16383" man="true"/>
+    <brk id="45" max="16383" man="true"/>
+  </rowBreaks>
+  <colBreaks/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
@@ -4334,7 +5140,7 @@
     </row>
     <row r="13">
       <c r="E13" s="11" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="F13" s="11"/>
       <c r="G13" s="11"/>
@@ -4345,7 +5151,7 @@
         <v>2</v>
       </c>
       <c r="E14" s="19" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="F14" s="19"/>
       <c r="G14" s="19"/>
@@ -4355,7 +5161,7 @@
     </row>
     <row r="15">
       <c r="E15" s="19" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="F15" s="19"/>
       <c r="G15" s="19"/>
@@ -4365,7 +5171,7 @@
     </row>
     <row r="16">
       <c r="E16" s="19" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="F16" s="19"/>
       <c r="G16" s="19"/>
@@ -4375,7 +5181,7 @@
     </row>
     <row r="17">
       <c r="E17" s="19" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="F17" s="19"/>
       <c r="G17" s="19"/>
@@ -4385,7 +5191,7 @@
     </row>
     <row r="18">
       <c r="E18" s="11" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="F18" s="11"/>
       <c r="G18" s="11"/>
@@ -4395,7 +5201,7 @@
     </row>
     <row r="19">
       <c r="E19" s="11" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="F19" s="11"/>
       <c r="G19" s="11"/>
@@ -7955,7 +8761,7 @@
       <c r="F358" s="11"/>
       <c r="G358" s="11"/>
       <c r="I358" s="11" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J358" s="11"/>
       <c r="K358" s="11"/>
@@ -8030,7 +8836,7 @@
     </row>
     <row r="366">
       <c r="A366" s="11" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B366" s="11"/>
       <c r="C366" s="11"/>
@@ -8039,7 +8845,7 @@
       <c r="F366" s="11"/>
       <c r="G366" s="11"/>
       <c r="I366" s="11" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="J366" s="11"/>
       <c r="K366" s="11"/>
@@ -8114,7 +8920,7 @@
     </row>
     <row r="379">
       <c r="A379" s="11" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B379" s="11"/>
       <c r="C379" s="11"/>
@@ -8123,7 +8929,7 @@
       <c r="F379" s="11"/>
       <c r="G379" s="11"/>
       <c r="I379" s="11" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="J379" s="11"/>
       <c r="K379" s="11"/>
@@ -8154,7 +8960,7 @@
     </row>
     <row r="381">
       <c r="A381" s="19" t="str">
-        <f>CONCATENATE("M 0 ",O370)</f>
+        <f>CONCATENATE("M 85 ",G370)</f>
       </c>
       <c r="B381" s="19"/>
       <c r="C381" s="19"/>
@@ -8162,10 +8968,10 @@
       <c r="E381" s="19"/>
       <c r="F381" s="19"/>
       <c r="G381" s="19" t="str">
-        <f>CONCATENATE("M 0 ",O370)</f>
+        <f>CONCATENATE("M 84 ",G362)</f>
       </c>
       <c r="I381" s="19" t="str">
-        <f>CONCATENATE("M 0 ",G383)</f>
+        <f>CONCATENATE("M 87 ",O370)</f>
       </c>
       <c r="J381" s="19"/>
       <c r="K381" s="19"/>
@@ -8173,7 +8979,7 @@
       <c r="M381" s="19"/>
       <c r="N381" s="19"/>
       <c r="O381" s="19" t="str">
-        <f>CONCATENATE("M 0 ",G383)</f>
+        <f>CONCATENATE("M 86 ",O362)</f>
       </c>
     </row>
     <row r="383">
@@ -8198,7 +9004,7 @@
     </row>
     <row r="392">
       <c r="A392" s="11" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B392" s="11"/>
       <c r="C392" s="11"/>
@@ -8220,7 +9026,7 @@
     </row>
     <row r="394">
       <c r="A394" s="19" t="str">
-        <f>CONCATENATE("M 0 ",O383)</f>
+        <f>CONCATENATE("M 89 ",O383)</f>
       </c>
       <c r="B394" s="19"/>
       <c r="C394" s="19"/>
@@ -8228,7 +9034,7 @@
       <c r="E394" s="19"/>
       <c r="F394" s="19"/>
       <c r="G394" s="19" t="str">
-        <f>CONCATENATE("M 0 ",O383)</f>
+        <f>CONCATENATE("M 88 ",G383)</f>
       </c>
     </row>
     <row r="396">
@@ -8357,781 +9163,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1"/>
-  <cols>
-    <col customWidth="true" max="1" min="1" style="9" width="30"/>
-    <col customWidth="true" max="2" min="2" style="10" width="160"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="270" customHeight="true">
-      <c r="A1" s="17">
-        <v>0</v>
-      </c>
-      <c r="B1" s="18" t="str">
-        <f>data!D3</f>
-      </c>
-    </row>
-    <row r="2" ht="270" customHeight="true">
-      <c r="A2" s="17">
-        <v>1</v>
-      </c>
-      <c r="B2" s="18" t="str">
-        <f>data!D4</f>
-      </c>
-    </row>
-    <row r="3" ht="270" customHeight="true">
-      <c r="A3" s="17">
-        <v>2</v>
-      </c>
-      <c r="B3" s="18" t="str">
-        <f>data!D5</f>
-      </c>
-    </row>
-    <row r="4" ht="270" customHeight="true">
-      <c r="A4" s="17">
-        <v>3</v>
-      </c>
-      <c r="B4" s="18" t="str">
-        <f>data!D6</f>
-      </c>
-    </row>
-    <row r="5" ht="270" customHeight="true">
-      <c r="A5" s="17">
-        <v>4</v>
-      </c>
-      <c r="B5" s="18" t="str">
-        <f>data!D7</f>
-      </c>
-    </row>
-    <row r="6" ht="270" customHeight="true">
-      <c r="A6" s="17">
-        <v>5</v>
-      </c>
-      <c r="B6" s="18" t="str">
-        <f>data!D8</f>
-      </c>
-    </row>
-    <row r="7" ht="270" customHeight="true">
-      <c r="A7" s="17">
-        <v>6</v>
-      </c>
-      <c r="B7" s="18" t="str">
-        <f>data!D9</f>
-      </c>
-    </row>
-    <row r="8" ht="270" customHeight="true">
-      <c r="A8" s="17">
-        <v>7</v>
-      </c>
-      <c r="B8" s="18" t="str">
-        <f>data!D10</f>
-      </c>
-    </row>
-    <row r="9" ht="270" customHeight="true">
-      <c r="A9" s="17">
-        <v>8</v>
-      </c>
-      <c r="B9" s="18" t="str">
-        <f>data!D11</f>
-      </c>
-    </row>
-    <row r="10" ht="270" customHeight="true">
-      <c r="A10" s="17">
-        <v>9</v>
-      </c>
-      <c r="B10" s="18" t="str">
-        <f>data!D12</f>
-      </c>
-    </row>
-    <row r="11" ht="270" customHeight="true">
-      <c r="A11" s="17">
-        <v>10</v>
-      </c>
-      <c r="B11" s="18" t="str">
-        <f>data!D13</f>
-      </c>
-    </row>
-    <row r="12" ht="270" customHeight="true">
-      <c r="A12" s="17">
-        <v>11</v>
-      </c>
-      <c r="B12" s="18" t="str">
-        <f>data!D14</f>
-      </c>
-    </row>
-    <row r="13" ht="270" customHeight="true">
-      <c r="A13" s="17">
-        <v>12</v>
-      </c>
-      <c r="B13" s="18" t="str">
-        <f>data!D15</f>
-      </c>
-    </row>
-    <row r="14" ht="270" customHeight="true">
-      <c r="A14" s="17">
-        <v>13</v>
-      </c>
-      <c r="B14" s="18" t="str">
-        <f>data!D16</f>
-      </c>
-    </row>
-    <row r="15" ht="270" customHeight="true">
-      <c r="A15" s="17">
-        <v>14</v>
-      </c>
-      <c r="B15" s="18" t="str">
-        <f>data!D17</f>
-      </c>
-    </row>
-    <row r="16" ht="270" customHeight="true">
-      <c r="A16" s="17">
-        <v>15</v>
-      </c>
-      <c r="B16" s="18" t="str">
-        <f>data!D18</f>
-      </c>
-    </row>
-    <row r="17" ht="270" customHeight="true">
-      <c r="A17" s="17">
-        <v>16</v>
-      </c>
-      <c r="B17" s="18" t="str">
-        <f>data!D19</f>
-      </c>
-    </row>
-    <row r="18" ht="270" customHeight="true">
-      <c r="A18" s="17">
-        <v>17</v>
-      </c>
-      <c r="B18" s="18" t="str">
-        <f>data!D20</f>
-      </c>
-    </row>
-    <row r="19" ht="270" customHeight="true">
-      <c r="A19" s="17">
-        <v>18</v>
-      </c>
-      <c r="B19" s="18" t="str">
-        <f>data!D21</f>
-      </c>
-    </row>
-    <row r="20" ht="270" customHeight="true">
-      <c r="A20" s="17">
-        <v>19</v>
-      </c>
-      <c r="B20" s="18" t="str">
-        <f>data!D22</f>
-      </c>
-    </row>
-    <row r="21" ht="270" customHeight="true">
-      <c r="A21" s="17">
-        <v>20</v>
-      </c>
-      <c r="B21" s="18" t="str">
-        <f>data!D23</f>
-      </c>
-    </row>
-    <row r="22" ht="270" customHeight="true">
-      <c r="A22" s="17">
-        <v>21</v>
-      </c>
-      <c r="B22" s="18" t="str">
-        <f>data!D24</f>
-      </c>
-    </row>
-    <row r="23" ht="270" customHeight="true">
-      <c r="A23" s="17">
-        <v>22</v>
-      </c>
-      <c r="B23" s="18" t="str">
-        <f>data!D25</f>
-      </c>
-    </row>
-    <row r="24" ht="270" customHeight="true">
-      <c r="A24" s="17">
-        <v>23</v>
-      </c>
-      <c r="B24" s="18" t="str">
-        <f>data!D26</f>
-      </c>
-    </row>
-    <row r="25" ht="270" customHeight="true">
-      <c r="A25" s="17">
-        <v>24</v>
-      </c>
-      <c r="B25" s="18" t="str">
-        <f>data!D27</f>
-      </c>
-    </row>
-    <row r="26" ht="270" customHeight="true">
-      <c r="A26" s="17">
-        <v>25</v>
-      </c>
-      <c r="B26" s="18" t="str">
-        <f>data!D28</f>
-      </c>
-    </row>
-    <row r="27" ht="270" customHeight="true">
-      <c r="A27" s="17">
-        <v>26</v>
-      </c>
-      <c r="B27" s="18" t="str">
-        <f>data!D29</f>
-      </c>
-    </row>
-    <row r="28" ht="270" customHeight="true">
-      <c r="A28" s="17">
-        <v>27</v>
-      </c>
-      <c r="B28" s="18" t="str">
-        <f>data!D30</f>
-      </c>
-    </row>
-    <row r="29" ht="270" customHeight="true">
-      <c r="A29" s="17">
-        <v>28</v>
-      </c>
-      <c r="B29" s="18" t="str">
-        <f>data!D31</f>
-      </c>
-    </row>
-    <row r="30" ht="270" customHeight="true">
-      <c r="A30" s="17">
-        <v>29</v>
-      </c>
-      <c r="B30" s="18" t="str">
-        <f>data!D32</f>
-      </c>
-    </row>
-    <row r="31" ht="270" customHeight="true">
-      <c r="A31" s="17">
-        <v>30</v>
-      </c>
-      <c r="B31" s="18" t="str">
-        <f>data!D33</f>
-      </c>
-    </row>
-    <row r="32" ht="270" customHeight="true">
-      <c r="A32" s="17">
-        <v>31</v>
-      </c>
-      <c r="B32" s="18" t="str">
-        <f>data!D34</f>
-      </c>
-    </row>
-    <row r="33" ht="270" customHeight="true">
-      <c r="A33" s="17">
-        <v>32</v>
-      </c>
-      <c r="B33" s="18" t="str">
-        <f>data!D35</f>
-      </c>
-    </row>
-    <row r="34" ht="270" customHeight="true">
-      <c r="A34" s="17">
-        <v>33</v>
-      </c>
-      <c r="B34" s="18" t="str">
-        <f>data!D36</f>
-      </c>
-    </row>
-    <row r="35" ht="270" customHeight="true">
-      <c r="A35" s="17">
-        <v>34</v>
-      </c>
-      <c r="B35" s="18" t="str">
-        <f>data!D37</f>
-      </c>
-    </row>
-    <row r="36" ht="270" customHeight="true">
-      <c r="A36" s="17">
-        <v>35</v>
-      </c>
-      <c r="B36" s="18" t="str">
-        <f>data!D38</f>
-      </c>
-    </row>
-    <row r="37" ht="270" customHeight="true">
-      <c r="A37" s="17">
-        <v>36</v>
-      </c>
-      <c r="B37" s="18" t="str">
-        <f>data!D39</f>
-      </c>
-    </row>
-    <row r="38" ht="270" customHeight="true">
-      <c r="A38" s="17">
-        <v>37</v>
-      </c>
-      <c r="B38" s="18" t="str">
-        <f>data!D40</f>
-      </c>
-    </row>
-    <row r="39" ht="270" customHeight="true">
-      <c r="A39" s="17">
-        <v>38</v>
-      </c>
-      <c r="B39" s="18" t="str">
-        <f>data!D41</f>
-      </c>
-    </row>
-    <row r="40" ht="270" customHeight="true">
-      <c r="A40" s="17">
-        <v>39</v>
-      </c>
-      <c r="B40" s="18" t="str">
-        <f>data!D42</f>
-      </c>
-    </row>
-    <row r="41" ht="270" customHeight="true">
-      <c r="A41" s="17">
-        <v>40</v>
-      </c>
-      <c r="B41" s="18" t="str">
-        <f>data!D43</f>
-      </c>
-    </row>
-    <row r="42" ht="270" customHeight="true">
-      <c r="A42" s="17">
-        <v>41</v>
-      </c>
-      <c r="B42" s="18" t="str">
-        <f>data!D44</f>
-      </c>
-    </row>
-    <row r="43" ht="270" customHeight="true">
-      <c r="A43" s="17">
-        <v>42</v>
-      </c>
-      <c r="B43" s="18" t="str">
-        <f>data!D45</f>
-      </c>
-    </row>
-    <row r="44" ht="270" customHeight="true">
-      <c r="A44" s="17">
-        <v>43</v>
-      </c>
-      <c r="B44" s="18" t="str">
-        <f>data!D46</f>
-      </c>
-    </row>
-    <row r="45" ht="270" customHeight="true">
-      <c r="A45" s="17">
-        <v>44</v>
-      </c>
-      <c r="B45" s="18" t="str">
-        <f>data!D47</f>
-      </c>
-    </row>
-    <row r="46" ht="270" customHeight="true">
-      <c r="A46" s="17">
-        <v>45</v>
-      </c>
-      <c r="B46" s="18" t="str">
-        <f>data!D48</f>
-      </c>
-    </row>
-    <row r="47" ht="270" customHeight="true">
-      <c r="A47" s="17">
-        <v>46</v>
-      </c>
-      <c r="B47" s="18" t="str">
-        <f>data!D49</f>
-      </c>
-    </row>
-    <row r="48" ht="270" customHeight="true">
-      <c r="A48" s="17">
-        <v>47</v>
-      </c>
-      <c r="B48" s="18" t="str">
-        <f>data!D50</f>
-      </c>
-    </row>
-    <row r="49" ht="270" customHeight="true">
-      <c r="A49" s="17">
-        <v>48</v>
-      </c>
-      <c r="B49" s="18" t="str">
-        <f>data!D51</f>
-      </c>
-    </row>
-    <row r="50" ht="270" customHeight="true">
-      <c r="A50" s="17">
-        <v>49</v>
-      </c>
-      <c r="B50" s="18" t="str">
-        <f>data!D52</f>
-      </c>
-    </row>
-    <row r="51" ht="270" customHeight="true">
-      <c r="A51" s="17">
-        <v>50</v>
-      </c>
-      <c r="B51" s="18" t="str">
-        <f>data!D53</f>
-      </c>
-    </row>
-    <row r="52" ht="270" customHeight="true">
-      <c r="A52" s="17">
-        <v>51</v>
-      </c>
-      <c r="B52" s="18" t="str">
-        <f>data!D54</f>
-      </c>
-    </row>
-    <row r="53" ht="270" customHeight="true">
-      <c r="A53" s="17">
-        <v>52</v>
-      </c>
-      <c r="B53" s="18" t="str">
-        <f>data!D55</f>
-      </c>
-    </row>
-    <row r="54" ht="270" customHeight="true">
-      <c r="A54" s="17">
-        <v>53</v>
-      </c>
-      <c r="B54" s="18" t="str">
-        <f>data!D56</f>
-      </c>
-    </row>
-    <row r="55" ht="270" customHeight="true">
-      <c r="A55" s="17">
-        <v>54</v>
-      </c>
-      <c r="B55" s="18" t="str">
-        <f>data!D57</f>
-      </c>
-    </row>
-    <row r="56" ht="270" customHeight="true">
-      <c r="A56" s="17">
-        <v>55</v>
-      </c>
-      <c r="B56" s="18" t="str">
-        <f>data!D58</f>
-      </c>
-    </row>
-    <row r="57" ht="270" customHeight="true">
-      <c r="A57" s="17">
-        <v>56</v>
-      </c>
-      <c r="B57" s="18" t="str">
-        <f>data!D59</f>
-      </c>
-    </row>
-    <row r="58" ht="270" customHeight="true">
-      <c r="A58" s="17">
-        <v>57</v>
-      </c>
-      <c r="B58" s="18" t="str">
-        <f>data!D60</f>
-      </c>
-    </row>
-    <row r="59" ht="270" customHeight="true">
-      <c r="A59" s="17">
-        <v>58</v>
-      </c>
-      <c r="B59" s="18" t="str">
-        <f>data!D61</f>
-      </c>
-    </row>
-    <row r="60" ht="270" customHeight="true">
-      <c r="A60" s="17">
-        <v>59</v>
-      </c>
-      <c r="B60" s="18" t="str">
-        <f>data!D62</f>
-      </c>
-    </row>
-    <row r="61" ht="270" customHeight="true">
-      <c r="A61" s="17">
-        <v>60</v>
-      </c>
-      <c r="B61" s="18" t="str">
-        <f>data!D63</f>
-      </c>
-    </row>
-    <row r="62" ht="270" customHeight="true">
-      <c r="A62" s="17">
-        <v>61</v>
-      </c>
-      <c r="B62" s="18" t="str">
-        <f>data!D64</f>
-      </c>
-    </row>
-    <row r="63" ht="270" customHeight="true">
-      <c r="A63" s="17">
-        <v>62</v>
-      </c>
-      <c r="B63" s="18" t="str">
-        <f>data!D65</f>
-      </c>
-    </row>
-    <row r="64" ht="270" customHeight="true">
-      <c r="A64" s="17">
-        <v>63</v>
-      </c>
-      <c r="B64" s="18" t="str">
-        <f>data!D66</f>
-      </c>
-    </row>
-    <row r="65" ht="270" customHeight="true">
-      <c r="A65" s="17">
-        <v>64</v>
-      </c>
-      <c r="B65" s="18" t="str">
-        <f>data!D67</f>
-      </c>
-    </row>
-    <row r="66" ht="270" customHeight="true">
-      <c r="A66" s="17">
-        <v>65</v>
-      </c>
-      <c r="B66" s="18" t="str">
-        <f>data!D68</f>
-      </c>
-    </row>
-    <row r="67" ht="270" customHeight="true">
-      <c r="A67" s="17">
-        <v>66</v>
-      </c>
-      <c r="B67" s="18" t="str">
-        <f>data!D69</f>
-      </c>
-    </row>
-    <row r="68" ht="270" customHeight="true">
-      <c r="A68" s="17">
-        <v>67</v>
-      </c>
-      <c r="B68" s="18" t="str">
-        <f>data!D70</f>
-      </c>
-    </row>
-    <row r="69" ht="270" customHeight="true">
-      <c r="A69" s="17">
-        <v>68</v>
-      </c>
-      <c r="B69" s="18" t="str">
-        <f>data!D71</f>
-      </c>
-    </row>
-    <row r="70" ht="270" customHeight="true">
-      <c r="A70" s="17">
-        <v>69</v>
-      </c>
-      <c r="B70" s="18" t="str">
-        <f>data!D72</f>
-      </c>
-    </row>
-    <row r="71" ht="270" customHeight="true">
-      <c r="A71" s="17">
-        <v>70</v>
-      </c>
-      <c r="B71" s="18" t="str">
-        <f>data!D73</f>
-      </c>
-    </row>
-    <row r="72" ht="270" customHeight="true">
-      <c r="A72" s="17">
-        <v>71</v>
-      </c>
-      <c r="B72" s="18" t="str">
-        <f>data!D74</f>
-      </c>
-    </row>
-    <row r="73" ht="270" customHeight="true">
-      <c r="A73" s="17">
-        <v>72</v>
-      </c>
-      <c r="B73" s="18" t="str">
-        <f>data!D75</f>
-      </c>
-    </row>
-    <row r="74" ht="270" customHeight="true">
-      <c r="A74" s="17">
-        <v>73</v>
-      </c>
-      <c r="B74" s="18" t="str">
-        <f>data!D76</f>
-      </c>
-    </row>
-    <row r="75" ht="270" customHeight="true">
-      <c r="A75" s="17">
-        <v>74</v>
-      </c>
-      <c r="B75" s="18" t="str">
-        <f>data!D77</f>
-      </c>
-    </row>
-    <row r="76" ht="270" customHeight="true">
-      <c r="A76" s="17">
-        <v>75</v>
-      </c>
-      <c r="B76" s="18" t="str">
-        <f>data!D78</f>
-      </c>
-    </row>
-    <row r="77" ht="270" customHeight="true">
-      <c r="A77" s="17">
-        <v>76</v>
-      </c>
-      <c r="B77" s="18" t="str">
-        <f>data!D79</f>
-      </c>
-    </row>
-    <row r="78" ht="270" customHeight="true">
-      <c r="A78" s="17">
-        <v>77</v>
-      </c>
-      <c r="B78" s="18" t="str">
-        <f>data!D80</f>
-      </c>
-    </row>
-    <row r="79" ht="270" customHeight="true">
-      <c r="A79" s="17">
-        <v>78</v>
-      </c>
-      <c r="B79" s="18" t="str">
-        <f>data!D81</f>
-      </c>
-    </row>
-    <row r="80" ht="270" customHeight="true">
-      <c r="A80" s="17">
-        <v>79</v>
-      </c>
-      <c r="B80" s="18" t="str">
-        <f>data!D82</f>
-      </c>
-    </row>
-    <row r="81" ht="270" customHeight="true">
-      <c r="A81" s="17">
-        <v>80</v>
-      </c>
-      <c r="B81" s="18" t="str">
-        <f>data!D83</f>
-      </c>
-    </row>
-    <row r="82" ht="270" customHeight="true">
-      <c r="A82" s="17">
-        <v>81</v>
-      </c>
-      <c r="B82" s="18" t="str">
-        <f>data!D84</f>
-      </c>
-    </row>
-    <row r="83" ht="270" customHeight="true">
-      <c r="A83" s="17">
-        <v>82</v>
-      </c>
-      <c r="B83" s="18" t="str">
-        <f>data!D85</f>
-      </c>
-    </row>
-    <row r="84" ht="270" customHeight="true">
-      <c r="A84" s="17">
-        <v>83</v>
-      </c>
-      <c r="B84" s="18" t="str">
-        <f>data!D86</f>
-      </c>
-    </row>
-    <row r="85" ht="270" customHeight="true">
-      <c r="A85" s="17">
-        <v>84</v>
-      </c>
-      <c r="B85" s="18" t="str">
-        <f>data!D87</f>
-      </c>
-    </row>
-    <row r="86" ht="270" customHeight="true">
-      <c r="A86" s="17">
-        <v>85</v>
-      </c>
-      <c r="B86" s="18" t="str">
-        <f>data!D88</f>
-      </c>
-    </row>
-    <row r="87" ht="270" customHeight="true">
-      <c r="A87" s="17">
-        <v>86</v>
-      </c>
-      <c r="B87" s="18" t="str">
-        <f>data!D89</f>
-      </c>
-    </row>
-    <row r="88" ht="270" customHeight="true">
-      <c r="A88" s="17">
-        <v>87</v>
-      </c>
-      <c r="B88" s="18" t="str">
-        <f>data!D90</f>
-      </c>
-    </row>
-    <row r="89" ht="270" customHeight="true">
-      <c r="A89" s="17">
-        <v>88</v>
-      </c>
-      <c r="B89" s="18" t="str">
-        <f>data!D91</f>
-      </c>
-    </row>
-    <row r="90" ht="270" customHeight="true">
-      <c r="A90" s="17">
-        <v>89</v>
-      </c>
-      <c r="B90" s="18" t="str">
-        <f>data!D92</f>
-      </c>
-    </row>
-    <row r="91" ht="270" customHeight="true">
-      <c r="A91" s="17">
-        <v>90</v>
-      </c>
-      <c r="B91" s="18" t="str">
-        <f>data!D93</f>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.1" right="0.1" top="0.1" bottom="0.1" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="8"/>
-  <rowBreaks count="30" manualBreakCount="30">
-    <brk id="3" max="16383" man="true"/>
-    <brk id="6" max="16383" man="true"/>
-    <brk id="9" max="16383" man="true"/>
-    <brk id="12" max="16383" man="true"/>
-    <brk id="15" max="16383" man="true"/>
-    <brk id="18" max="16383" man="true"/>
-    <brk id="21" max="16383" man="true"/>
-    <brk id="24" max="16383" man="true"/>
-    <brk id="27" max="16383" man="true"/>
-    <brk id="30" max="16383" man="true"/>
-    <brk id="33" max="16383" man="true"/>
-    <brk id="36" max="16383" man="true"/>
-    <brk id="39" max="16383" man="true"/>
-    <brk id="42" max="16383" man="true"/>
-    <brk id="45" max="16383" man="true"/>
-    <brk id="48" max="16383" man="true"/>
-    <brk id="51" max="16383" man="true"/>
-    <brk id="54" max="16383" man="true"/>
-    <brk id="57" max="16383" man="true"/>
-    <brk id="60" max="16383" man="true"/>
-    <brk id="63" max="16383" man="true"/>
-    <brk id="66" max="16383" man="true"/>
-    <brk id="69" max="16383" man="true"/>
-    <brk id="72" max="16383" man="true"/>
-    <brk id="75" max="16383" man="true"/>
-    <brk id="78" max="16383" man="true"/>
-    <brk id="81" max="16383" man="true"/>
-    <brk id="84" max="16383" man="true"/>
-    <brk id="87" max="16383" man="true"/>
-    <brk id="90" max="16383" man="true"/>
-  </rowBreaks>
-  <colBreaks/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>

--- a/playoffs-example-large.xlsx
+++ b/playoffs-example-large.xlsx
@@ -1048,12 +1048,17 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFEFEF"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1129,7 +1134,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
@@ -1176,7 +1181,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true" applyAlignment="false">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
@@ -1185,16 +1190,27 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center"/>
+      <protection hidden="false" locked="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true" applyAlignment="false" applyProtection="true">
+      <alignment/>
+      <protection hidden="false" locked="false"/>
+    </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="20" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
@@ -3000,6 +3016,7 @@
       <c r="E35" s="12"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <mergeCells count="1">
     <mergeCell ref="A1:P1"/>
   </mergeCells>
@@ -3232,6 +3249,7 @@
       <c r="E35" s="12"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <mergeCells count="1">
     <mergeCell ref="A1:P1"/>
   </mergeCells>
@@ -3455,6 +3473,7 @@
       <c r="E35" s="12"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <mergeCells count="1">
     <mergeCell ref="A1:P1"/>
   </mergeCells>
@@ -3687,6 +3706,7 @@
       <c r="E35" s="12"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <mergeCells count="1">
     <mergeCell ref="A1:P1"/>
   </mergeCells>
@@ -3910,6 +3930,7 @@
       <c r="E35" s="12"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <mergeCells count="1">
     <mergeCell ref="A1:P1"/>
   </mergeCells>
@@ -4142,6 +4163,7 @@
       <c r="E35" s="12"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <mergeCells count="1">
     <mergeCell ref="A1:P1"/>
   </mergeCells>
@@ -4525,6 +4547,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <pageMargins left="0.1" right="0.1" top="0.1" bottom="0.1" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="8"/>
   <rowBreaks count="15" manualBreakCount="15">
@@ -4917,6 +4940,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <pageMargins left="0.1" right="0.1" top="0.1" bottom="0.1" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="8"/>
   <rowBreaks count="15" manualBreakCount="15">
@@ -5000,7 +5024,7 @@
       <c r="G2" s="3">
         <v>0.020833333333333332</v>
       </c>
-      <c r="H2" s="22" t="str">
+      <c r="H2" s="24" t="str">
         <f>C2*I2+J2</f>
       </c>
     </row>
@@ -5104,7 +5128,7 @@
       <c r="G8" s="3">
         <v>0.020833333333333332</v>
       </c>
-      <c r="H8" s="22" t="str">
+      <c r="H8" s="24" t="str">
         <f>E8+(A8*F8)+G8</f>
       </c>
     </row>
@@ -5150,42 +5174,42 @@
       <c r="A14">
         <v>2</v>
       </c>
-      <c r="E14" s="19" t="s">
+      <c r="E14" s="25" t="s">
         <v>304</v>
       </c>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="22" t="str">
+      <c r="F14" s="25"/>
+      <c r="G14" s="25"/>
+      <c r="H14" s="24" t="str">
         <f>H2</f>
       </c>
     </row>
     <row r="15">
-      <c r="E15" s="19" t="s">
+      <c r="E15" s="25" t="s">
         <v>305</v>
       </c>
-      <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="22" t="str">
+      <c r="F15" s="25"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="24" t="str">
         <f>H8</f>
       </c>
     </row>
     <row r="16">
-      <c r="E16" s="19" t="s">
+      <c r="E16" s="25" t="s">
         <v>306</v>
       </c>
-      <c r="F16" s="19"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="22" t="str">
+      <c r="F16" s="25"/>
+      <c r="G16" s="25"/>
+      <c r="H16" s="24" t="str">
         <f>H14+H15</f>
       </c>
     </row>
     <row r="17">
-      <c r="E17" s="19" t="s">
+      <c r="E17" s="25" t="s">
         <v>307</v>
       </c>
-      <c r="F17" s="19"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="22" t="str">
+      <c r="F17" s="25"/>
+      <c r="G17" s="25"/>
+      <c r="H17" s="24" t="str">
         <f>H16/A14</f>
       </c>
     </row>
@@ -5195,7 +5219,7 @@
       </c>
       <c r="F18" s="11"/>
       <c r="G18" s="11"/>
-      <c r="H18" s="23">
+      <c r="H18" s="26">
         <v>0.375</v>
       </c>
     </row>
@@ -5205,7 +5229,7 @@
       </c>
       <c r="F19" s="11"/>
       <c r="G19" s="11"/>
-      <c r="H19" s="23" t="str">
+      <c r="H19" s="26" t="str">
         <f>H18+H17</f>
       </c>
     </row>
@@ -5229,14 +5253,15 @@
     <col customWidth="true" max="4" min="4" width="3"/>
     <col customWidth="true" max="6" min="5" width="5"/>
     <col customWidth="true" max="7" min="7" width="30"/>
-    <col customWidth="true" max="8" min="8" width="2"/>
+    <col customWidth="true" max="8" min="8" width="5"/>
     <col customWidth="true" max="9" min="9" width="30"/>
     <col customWidth="true" max="11" min="10" width="5"/>
     <col customWidth="true" max="12" min="12" width="3"/>
     <col customWidth="true" max="14" min="13" width="5"/>
     <col customWidth="true" max="15" min="15" width="30"/>
-    <col customWidth="true" max="16" min="16" width="2"/>
-    <col customWidth="true" max="20" min="17" width="10.83"/>
+    <col customWidth="true" max="18" min="16" width="5"/>
+    <col customWidth="true" max="19" min="19" width="30"/>
+    <col customWidth="true" max="20" min="20" width="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5303,22 +5328,22 @@
       <c r="A4" s="19" t="str">
         <f>'data'!$B$35</f>
       </c>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
       <c r="G4" s="19" t="str">
         <f>'data'!$B$6</f>
       </c>
       <c r="I4" s="19" t="str">
         <f>'data'!$B$52</f>
       </c>
-      <c r="J4" s="19"/>
-      <c r="K4" s="19"/>
-      <c r="L4" s="19"/>
-      <c r="M4" s="19"/>
-      <c r="N4" s="19"/>
+      <c r="J4" s="22"/>
+      <c r="K4" s="22"/>
+      <c r="L4" s="22"/>
+      <c r="M4" s="22"/>
+      <c r="N4" s="22"/>
       <c r="O4" s="19" t="str">
         <f>'data'!$B$51</f>
       </c>
@@ -5327,21 +5352,21 @@
       <c r="F6" t="s">
         <v>212</v>
       </c>
-      <c r="G6" s="15"/>
+      <c r="G6" s="23"/>
       <c r="N6" t="s">
         <v>212</v>
       </c>
-      <c r="O6" s="15"/>
+      <c r="O6" s="23"/>
     </row>
     <row r="7">
       <c r="F7" t="s">
         <v>213</v>
       </c>
-      <c r="G7" s="15"/>
+      <c r="G7" s="23"/>
       <c r="N7" t="s">
         <v>213</v>
       </c>
-      <c r="O7" s="15"/>
+      <c r="O7" s="23"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="s">
@@ -5387,22 +5412,22 @@
       <c r="A12" s="19" t="str">
         <f>'data'!$B$38</f>
       </c>
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
+      <c r="B12" s="22"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="22"/>
+      <c r="E12" s="22"/>
+      <c r="F12" s="22"/>
       <c r="G12" s="19" t="str">
         <f>'data'!$B$37</f>
       </c>
       <c r="I12" s="19" t="str">
         <f>'data'!$B$55</f>
       </c>
-      <c r="J12" s="19"/>
-      <c r="K12" s="19"/>
-      <c r="L12" s="19"/>
-      <c r="M12" s="19"/>
-      <c r="N12" s="19"/>
+      <c r="J12" s="22"/>
+      <c r="K12" s="22"/>
+      <c r="L12" s="22"/>
+      <c r="M12" s="22"/>
+      <c r="N12" s="22"/>
       <c r="O12" s="19" t="str">
         <f>'data'!$B$54</f>
       </c>
@@ -5411,21 +5436,21 @@
       <c r="F14" t="s">
         <v>212</v>
       </c>
-      <c r="G14" s="15"/>
+      <c r="G14" s="23"/>
       <c r="N14" t="s">
         <v>212</v>
       </c>
-      <c r="O14" s="15"/>
+      <c r="O14" s="23"/>
     </row>
     <row r="15">
       <c r="F15" t="s">
         <v>213</v>
       </c>
-      <c r="G15" s="15"/>
+      <c r="G15" s="23"/>
       <c r="N15" t="s">
         <v>213</v>
       </c>
-      <c r="O15" s="15"/>
+      <c r="O15" s="23"/>
     </row>
     <row r="18">
       <c r="A18" s="11" t="s">
@@ -5471,22 +5496,22 @@
       <c r="A20" s="19" t="str">
         <f>'data'!$B$41</f>
       </c>
-      <c r="B20" s="19"/>
-      <c r="C20" s="19"/>
-      <c r="D20" s="19"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="19"/>
+      <c r="B20" s="22"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
       <c r="G20" s="19" t="str">
         <f>'data'!$B$40</f>
       </c>
       <c r="I20" s="19" t="str">
         <f>'data'!$B$58</f>
       </c>
-      <c r="J20" s="19"/>
-      <c r="K20" s="19"/>
-      <c r="L20" s="19"/>
-      <c r="M20" s="19"/>
-      <c r="N20" s="19"/>
+      <c r="J20" s="22"/>
+      <c r="K20" s="22"/>
+      <c r="L20" s="22"/>
+      <c r="M20" s="22"/>
+      <c r="N20" s="22"/>
       <c r="O20" s="19" t="str">
         <f>'data'!$B$57</f>
       </c>
@@ -5495,21 +5520,21 @@
       <c r="F22" t="s">
         <v>212</v>
       </c>
-      <c r="G22" s="15"/>
+      <c r="G22" s="23"/>
       <c r="N22" t="s">
         <v>212</v>
       </c>
-      <c r="O22" s="15"/>
+      <c r="O22" s="23"/>
     </row>
     <row r="23">
       <c r="F23" t="s">
         <v>213</v>
       </c>
-      <c r="G23" s="15"/>
+      <c r="G23" s="23"/>
       <c r="N23" t="s">
         <v>213</v>
       </c>
-      <c r="O23" s="15"/>
+      <c r="O23" s="23"/>
     </row>
     <row r="26">
       <c r="A26" s="11" t="s">
@@ -5555,22 +5580,22 @@
       <c r="A28" s="19" t="str">
         <f>'data'!$B$18</f>
       </c>
-      <c r="B28" s="19"/>
-      <c r="C28" s="19"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
+      <c r="B28" s="22"/>
+      <c r="C28" s="22"/>
+      <c r="D28" s="22"/>
+      <c r="E28" s="22"/>
+      <c r="F28" s="22"/>
       <c r="G28" s="19" t="str">
         <f>'data'!$B$17</f>
       </c>
       <c r="I28" s="19" t="str">
         <f>'data'!$B$61</f>
       </c>
-      <c r="J28" s="19"/>
-      <c r="K28" s="19"/>
-      <c r="L28" s="19"/>
-      <c r="M28" s="19"/>
-      <c r="N28" s="19"/>
+      <c r="J28" s="22"/>
+      <c r="K28" s="22"/>
+      <c r="L28" s="22"/>
+      <c r="M28" s="22"/>
+      <c r="N28" s="22"/>
       <c r="O28" s="19" t="str">
         <f>'data'!$B$60</f>
       </c>
@@ -5579,21 +5604,21 @@
       <c r="F30" t="s">
         <v>212</v>
       </c>
-      <c r="G30" s="15"/>
+      <c r="G30" s="23"/>
       <c r="N30" t="s">
         <v>212</v>
       </c>
-      <c r="O30" s="15"/>
+      <c r="O30" s="23"/>
     </row>
     <row r="31">
       <c r="F31" t="s">
         <v>213</v>
       </c>
-      <c r="G31" s="15"/>
+      <c r="G31" s="23"/>
       <c r="N31" t="s">
         <v>213</v>
       </c>
-      <c r="O31" s="15"/>
+      <c r="O31" s="23"/>
     </row>
     <row r="34">
       <c r="A34" s="11" t="s">
@@ -5639,22 +5664,22 @@
       <c r="A36" s="19" t="str">
         <f>'data'!$B$21</f>
       </c>
-      <c r="B36" s="19"/>
-      <c r="C36" s="19"/>
-      <c r="D36" s="19"/>
-      <c r="E36" s="19"/>
-      <c r="F36" s="19"/>
+      <c r="B36" s="22"/>
+      <c r="C36" s="22"/>
+      <c r="D36" s="22"/>
+      <c r="E36" s="22"/>
+      <c r="F36" s="22"/>
       <c r="G36" s="19" t="str">
         <f>'data'!$B$20</f>
       </c>
       <c r="I36" s="19" t="str">
         <f>'data'!$B$64</f>
       </c>
-      <c r="J36" s="19"/>
-      <c r="K36" s="19"/>
-      <c r="L36" s="19"/>
-      <c r="M36" s="19"/>
-      <c r="N36" s="19"/>
+      <c r="J36" s="22"/>
+      <c r="K36" s="22"/>
+      <c r="L36" s="22"/>
+      <c r="M36" s="22"/>
+      <c r="N36" s="22"/>
       <c r="O36" s="19" t="str">
         <f>'data'!$B$63</f>
       </c>
@@ -5663,21 +5688,21 @@
       <c r="F38" t="s">
         <v>212</v>
       </c>
-      <c r="G38" s="15"/>
+      <c r="G38" s="23"/>
       <c r="N38" t="s">
         <v>212</v>
       </c>
-      <c r="O38" s="15"/>
+      <c r="O38" s="23"/>
     </row>
     <row r="39">
       <c r="F39" t="s">
         <v>213</v>
       </c>
-      <c r="G39" s="15"/>
+      <c r="G39" s="23"/>
       <c r="N39" t="s">
         <v>213</v>
       </c>
-      <c r="O39" s="15"/>
+      <c r="O39" s="23"/>
     </row>
     <row r="42">
       <c r="A42" s="11" t="s">
@@ -5723,22 +5748,22 @@
       <c r="A44" s="19" t="str">
         <f>'data'!$B$24</f>
       </c>
-      <c r="B44" s="19"/>
-      <c r="C44" s="19"/>
-      <c r="D44" s="19"/>
-      <c r="E44" s="19"/>
-      <c r="F44" s="19"/>
+      <c r="B44" s="22"/>
+      <c r="C44" s="22"/>
+      <c r="D44" s="22"/>
+      <c r="E44" s="22"/>
+      <c r="F44" s="22"/>
       <c r="G44" s="19" t="str">
         <f>'data'!$B$23</f>
       </c>
       <c r="I44" s="19" t="str">
         <f>'data'!$B$67</f>
       </c>
-      <c r="J44" s="19"/>
-      <c r="K44" s="19"/>
-      <c r="L44" s="19"/>
-      <c r="M44" s="19"/>
-      <c r="N44" s="19"/>
+      <c r="J44" s="22"/>
+      <c r="K44" s="22"/>
+      <c r="L44" s="22"/>
+      <c r="M44" s="22"/>
+      <c r="N44" s="22"/>
       <c r="O44" s="19" t="str">
         <f>'data'!$B$66</f>
       </c>
@@ -5747,21 +5772,21 @@
       <c r="F46" t="s">
         <v>212</v>
       </c>
-      <c r="G46" s="15"/>
+      <c r="G46" s="23"/>
       <c r="N46" t="s">
         <v>212</v>
       </c>
-      <c r="O46" s="15"/>
+      <c r="O46" s="23"/>
     </row>
     <row r="47">
       <c r="F47" t="s">
         <v>213</v>
       </c>
-      <c r="G47" s="15"/>
+      <c r="G47" s="23"/>
       <c r="N47" t="s">
         <v>213</v>
       </c>
-      <c r="O47" s="15"/>
+      <c r="O47" s="23"/>
     </row>
     <row r="50">
       <c r="A50" s="11" t="s">
@@ -5807,22 +5832,22 @@
       <c r="A52" s="19" t="str">
         <f>'data'!$B$29</f>
       </c>
-      <c r="B52" s="19"/>
-      <c r="C52" s="19"/>
-      <c r="D52" s="19"/>
-      <c r="E52" s="19"/>
-      <c r="F52" s="19"/>
+      <c r="B52" s="22"/>
+      <c r="C52" s="22"/>
+      <c r="D52" s="22"/>
+      <c r="E52" s="22"/>
+      <c r="F52" s="22"/>
       <c r="G52" s="19" t="str">
         <f>'data'!$B$28</f>
       </c>
       <c r="I52" s="19" t="str">
         <f>'data'!$B$74</f>
       </c>
-      <c r="J52" s="19"/>
-      <c r="K52" s="19"/>
-      <c r="L52" s="19"/>
-      <c r="M52" s="19"/>
-      <c r="N52" s="19"/>
+      <c r="J52" s="22"/>
+      <c r="K52" s="22"/>
+      <c r="L52" s="22"/>
+      <c r="M52" s="22"/>
+      <c r="N52" s="22"/>
       <c r="O52" s="19" t="str">
         <f>'data'!$B$69</f>
       </c>
@@ -5831,21 +5856,21 @@
       <c r="F54" t="s">
         <v>212</v>
       </c>
-      <c r="G54" s="15"/>
+      <c r="G54" s="23"/>
       <c r="N54" t="s">
         <v>212</v>
       </c>
-      <c r="O54" s="15"/>
+      <c r="O54" s="23"/>
     </row>
     <row r="55">
       <c r="F55" t="s">
         <v>213</v>
       </c>
-      <c r="G55" s="15"/>
+      <c r="G55" s="23"/>
       <c r="N55" t="s">
         <v>213</v>
       </c>
-      <c r="O55" s="15"/>
+      <c r="O55" s="23"/>
     </row>
     <row r="58">
       <c r="A58" s="11" t="s">
@@ -5891,22 +5916,22 @@
       <c r="A60" s="19" t="str">
         <f>'data'!$B$32</f>
       </c>
-      <c r="B60" s="19"/>
-      <c r="C60" s="19"/>
-      <c r="D60" s="19"/>
-      <c r="E60" s="19"/>
-      <c r="F60" s="19"/>
+      <c r="B60" s="22"/>
+      <c r="C60" s="22"/>
+      <c r="D60" s="22"/>
+      <c r="E60" s="22"/>
+      <c r="F60" s="22"/>
       <c r="G60" s="19" t="str">
         <f>'data'!$B$31</f>
       </c>
       <c r="I60" s="19" t="str">
         <f>'data'!$B$75</f>
       </c>
-      <c r="J60" s="19"/>
-      <c r="K60" s="19"/>
-      <c r="L60" s="19"/>
-      <c r="M60" s="19"/>
-      <c r="N60" s="19"/>
+      <c r="J60" s="22"/>
+      <c r="K60" s="22"/>
+      <c r="L60" s="22"/>
+      <c r="M60" s="22"/>
+      <c r="N60" s="22"/>
       <c r="O60" s="19" t="str">
         <f>'data'!$B$74</f>
       </c>
@@ -5915,21 +5940,21 @@
       <c r="F62" t="s">
         <v>212</v>
       </c>
-      <c r="G62" s="15"/>
+      <c r="G62" s="23"/>
       <c r="N62" t="s">
         <v>212</v>
       </c>
-      <c r="O62" s="15"/>
+      <c r="O62" s="23"/>
     </row>
     <row r="63">
       <c r="F63" t="s">
         <v>213</v>
       </c>
-      <c r="G63" s="15"/>
+      <c r="G63" s="23"/>
       <c r="N63" t="s">
         <v>213</v>
       </c>
-      <c r="O63" s="15"/>
+      <c r="O63" s="23"/>
     </row>
     <row r="66">
       <c r="A66" s="11" t="s">
@@ -5975,22 +6000,22 @@
       <c r="A68" s="19" t="str">
         <f>'data'!$B$35</f>
       </c>
-      <c r="B68" s="19"/>
-      <c r="C68" s="19"/>
-      <c r="D68" s="19"/>
-      <c r="E68" s="19"/>
-      <c r="F68" s="19"/>
+      <c r="B68" s="22"/>
+      <c r="C68" s="22"/>
+      <c r="D68" s="22"/>
+      <c r="E68" s="22"/>
+      <c r="F68" s="22"/>
       <c r="G68" s="19" t="str">
         <f>'data'!$B$34</f>
       </c>
       <c r="I68" s="19" t="str">
         <f>'data'!$B$78</f>
       </c>
-      <c r="J68" s="19"/>
-      <c r="K68" s="19"/>
-      <c r="L68" s="19"/>
-      <c r="M68" s="19"/>
-      <c r="N68" s="19"/>
+      <c r="J68" s="22"/>
+      <c r="K68" s="22"/>
+      <c r="L68" s="22"/>
+      <c r="M68" s="22"/>
+      <c r="N68" s="22"/>
       <c r="O68" s="19" t="str">
         <f>'data'!$B$77</f>
       </c>
@@ -5999,21 +6024,21 @@
       <c r="F70" t="s">
         <v>212</v>
       </c>
-      <c r="G70" s="15"/>
+      <c r="G70" s="23"/>
       <c r="N70" t="s">
         <v>212</v>
       </c>
-      <c r="O70" s="15"/>
+      <c r="O70" s="23"/>
     </row>
     <row r="71">
       <c r="F71" t="s">
         <v>213</v>
       </c>
-      <c r="G71" s="15"/>
+      <c r="G71" s="23"/>
       <c r="N71" t="s">
         <v>213</v>
       </c>
-      <c r="O71" s="15"/>
+      <c r="O71" s="23"/>
     </row>
     <row r="74">
       <c r="A74" s="11" t="s">
@@ -6059,22 +6084,22 @@
       <c r="A76" s="19" t="str">
         <f>'data'!$B$38</f>
       </c>
-      <c r="B76" s="19"/>
-      <c r="C76" s="19"/>
-      <c r="D76" s="19"/>
-      <c r="E76" s="19"/>
-      <c r="F76" s="19"/>
+      <c r="B76" s="22"/>
+      <c r="C76" s="22"/>
+      <c r="D76" s="22"/>
+      <c r="E76" s="22"/>
+      <c r="F76" s="22"/>
       <c r="G76" s="19" t="str">
         <f>'data'!$B$37</f>
       </c>
       <c r="I76" s="19" t="str">
         <f>'data'!$B$81</f>
       </c>
-      <c r="J76" s="19"/>
-      <c r="K76" s="19"/>
-      <c r="L76" s="19"/>
-      <c r="M76" s="19"/>
-      <c r="N76" s="19"/>
+      <c r="J76" s="22"/>
+      <c r="K76" s="22"/>
+      <c r="L76" s="22"/>
+      <c r="M76" s="22"/>
+      <c r="N76" s="22"/>
       <c r="O76" s="19" t="str">
         <f>'data'!$B$80</f>
       </c>
@@ -6083,21 +6108,21 @@
       <c r="F78" t="s">
         <v>212</v>
       </c>
-      <c r="G78" s="15"/>
+      <c r="G78" s="23"/>
       <c r="N78" t="s">
         <v>212</v>
       </c>
-      <c r="O78" s="15"/>
+      <c r="O78" s="23"/>
     </row>
     <row r="79">
       <c r="F79" t="s">
         <v>213</v>
       </c>
-      <c r="G79" s="15"/>
+      <c r="G79" s="23"/>
       <c r="N79" t="s">
         <v>213</v>
       </c>
-      <c r="O79" s="15"/>
+      <c r="O79" s="23"/>
     </row>
     <row r="82">
       <c r="A82" s="11" t="s">
@@ -6143,22 +6168,22 @@
       <c r="A84" s="19" t="str">
         <f>'data'!$B$41</f>
       </c>
-      <c r="B84" s="19"/>
-      <c r="C84" s="19"/>
-      <c r="D84" s="19"/>
-      <c r="E84" s="19"/>
-      <c r="F84" s="19"/>
+      <c r="B84" s="22"/>
+      <c r="C84" s="22"/>
+      <c r="D84" s="22"/>
+      <c r="E84" s="22"/>
+      <c r="F84" s="22"/>
       <c r="G84" s="19" t="str">
         <f>'data'!$B$40</f>
       </c>
       <c r="I84" s="19" t="str">
         <f>'data'!$B$84</f>
       </c>
-      <c r="J84" s="19"/>
-      <c r="K84" s="19"/>
-      <c r="L84" s="19"/>
-      <c r="M84" s="19"/>
-      <c r="N84" s="19"/>
+      <c r="J84" s="22"/>
+      <c r="K84" s="22"/>
+      <c r="L84" s="22"/>
+      <c r="M84" s="22"/>
+      <c r="N84" s="22"/>
       <c r="O84" s="19" t="str">
         <f>'data'!$B$83</f>
       </c>
@@ -6167,21 +6192,21 @@
       <c r="F86" t="s">
         <v>212</v>
       </c>
-      <c r="G86" s="15"/>
+      <c r="G86" s="23"/>
       <c r="N86" t="s">
         <v>212</v>
       </c>
-      <c r="O86" s="15"/>
+      <c r="O86" s="23"/>
     </row>
     <row r="87">
       <c r="F87" t="s">
         <v>213</v>
       </c>
-      <c r="G87" s="15"/>
+      <c r="G87" s="23"/>
       <c r="N87" t="s">
         <v>213</v>
       </c>
-      <c r="O87" s="15"/>
+      <c r="O87" s="23"/>
     </row>
     <row r="90">
       <c r="A90" s="11" t="s">
@@ -6227,22 +6252,22 @@
       <c r="A92" s="19" t="str">
         <f>'data'!$B$44</f>
       </c>
-      <c r="B92" s="19"/>
-      <c r="C92" s="19"/>
-      <c r="D92" s="19"/>
-      <c r="E92" s="19"/>
-      <c r="F92" s="19"/>
+      <c r="B92" s="22"/>
+      <c r="C92" s="22"/>
+      <c r="D92" s="22"/>
+      <c r="E92" s="22"/>
+      <c r="F92" s="22"/>
       <c r="G92" s="19" t="str">
         <f>'data'!$B$43</f>
       </c>
       <c r="I92" s="19" t="str">
         <f>'data'!$B$87</f>
       </c>
-      <c r="J92" s="19"/>
-      <c r="K92" s="19"/>
-      <c r="L92" s="19"/>
-      <c r="M92" s="19"/>
-      <c r="N92" s="19"/>
+      <c r="J92" s="22"/>
+      <c r="K92" s="22"/>
+      <c r="L92" s="22"/>
+      <c r="M92" s="22"/>
+      <c r="N92" s="22"/>
       <c r="O92" s="19" t="str">
         <f>'data'!$B$86</f>
       </c>
@@ -6251,21 +6276,21 @@
       <c r="F94" t="s">
         <v>212</v>
       </c>
-      <c r="G94" s="15"/>
+      <c r="G94" s="23"/>
       <c r="N94" t="s">
         <v>212</v>
       </c>
-      <c r="O94" s="15"/>
+      <c r="O94" s="23"/>
     </row>
     <row r="95">
       <c r="F95" t="s">
         <v>213</v>
       </c>
-      <c r="G95" s="15"/>
+      <c r="G95" s="23"/>
       <c r="N95" t="s">
         <v>213</v>
       </c>
-      <c r="O95" s="15"/>
+      <c r="O95" s="23"/>
     </row>
     <row r="98">
       <c r="A98" s="11" t="s">
@@ -6311,22 +6336,22 @@
       <c r="A100" s="19" t="str">
         <f>'data'!$B$47</f>
       </c>
-      <c r="B100" s="19"/>
-      <c r="C100" s="19"/>
-      <c r="D100" s="19"/>
-      <c r="E100" s="19"/>
-      <c r="F100" s="19"/>
+      <c r="B100" s="22"/>
+      <c r="C100" s="22"/>
+      <c r="D100" s="22"/>
+      <c r="E100" s="22"/>
+      <c r="F100" s="22"/>
       <c r="G100" s="19" t="str">
         <f>'data'!$B$46</f>
       </c>
       <c r="I100" s="19" t="str">
         <f>'data'!$B$90</f>
       </c>
-      <c r="J100" s="19"/>
-      <c r="K100" s="19"/>
-      <c r="L100" s="19"/>
-      <c r="M100" s="19"/>
-      <c r="N100" s="19"/>
+      <c r="J100" s="22"/>
+      <c r="K100" s="22"/>
+      <c r="L100" s="22"/>
+      <c r="M100" s="22"/>
+      <c r="N100" s="22"/>
       <c r="O100" s="19" t="str">
         <f>'data'!$B$89</f>
       </c>
@@ -6335,21 +6360,21 @@
       <c r="F102" t="s">
         <v>212</v>
       </c>
-      <c r="G102" s="15"/>
+      <c r="G102" s="23"/>
       <c r="N102" t="s">
         <v>212</v>
       </c>
-      <c r="O102" s="15"/>
+      <c r="O102" s="23"/>
     </row>
     <row r="103">
       <c r="F103" t="s">
         <v>213</v>
       </c>
-      <c r="G103" s="15"/>
+      <c r="G103" s="23"/>
       <c r="N103" t="s">
         <v>213</v>
       </c>
-      <c r="O103" s="15"/>
+      <c r="O103" s="23"/>
     </row>
     <row r="106">
       <c r="I106" s="11" t="s">
@@ -6377,11 +6402,11 @@
       <c r="I108" s="19" t="str">
         <f>'data'!$B$93</f>
       </c>
-      <c r="J108" s="19"/>
-      <c r="K108" s="19"/>
-      <c r="L108" s="19"/>
-      <c r="M108" s="19"/>
-      <c r="N108" s="19"/>
+      <c r="J108" s="22"/>
+      <c r="K108" s="22"/>
+      <c r="L108" s="22"/>
+      <c r="M108" s="22"/>
+      <c r="N108" s="22"/>
       <c r="O108" s="19" t="str">
         <f>'data'!$B$92</f>
       </c>
@@ -6390,13 +6415,13 @@
       <c r="N110" t="s">
         <v>212</v>
       </c>
-      <c r="O110" s="15"/>
+      <c r="O110" s="23"/>
     </row>
     <row r="111">
       <c r="N111" t="s">
         <v>213</v>
       </c>
-      <c r="O111" s="15"/>
+      <c r="O111" s="23"/>
     </row>
     <row r="119">
       <c r="A119" s="11" t="s">
@@ -6442,22 +6467,22 @@
       <c r="A121" s="19" t="str">
         <f>'data'!$B$33</f>
       </c>
-      <c r="B121" s="19"/>
-      <c r="C121" s="19"/>
-      <c r="D121" s="19"/>
-      <c r="E121" s="19"/>
-      <c r="F121" s="19"/>
+      <c r="B121" s="22"/>
+      <c r="C121" s="22"/>
+      <c r="D121" s="22"/>
+      <c r="E121" s="22"/>
+      <c r="F121" s="22"/>
       <c r="G121" s="19" t="str">
         <f>'data'!$B$32</f>
       </c>
       <c r="I121" s="19" t="str">
         <f>'data'!$B$49</f>
       </c>
-      <c r="J121" s="19"/>
-      <c r="K121" s="19"/>
-      <c r="L121" s="19"/>
-      <c r="M121" s="19"/>
-      <c r="N121" s="19"/>
+      <c r="J121" s="22"/>
+      <c r="K121" s="22"/>
+      <c r="L121" s="22"/>
+      <c r="M121" s="22"/>
+      <c r="N121" s="22"/>
       <c r="O121" s="19" t="str">
         <f>'data'!$B$48</f>
       </c>
@@ -6466,21 +6491,21 @@
       <c r="F123" t="s">
         <v>212</v>
       </c>
-      <c r="G123" s="15"/>
+      <c r="G123" s="23"/>
       <c r="N123" t="s">
         <v>212</v>
       </c>
-      <c r="O123" s="15"/>
+      <c r="O123" s="23"/>
     </row>
     <row r="124">
       <c r="F124" t="s">
         <v>213</v>
       </c>
-      <c r="G124" s="15"/>
+      <c r="G124" s="23"/>
       <c r="N124" t="s">
         <v>213</v>
       </c>
-      <c r="O124" s="15"/>
+      <c r="O124" s="23"/>
     </row>
     <row r="127">
       <c r="A127" s="11" t="s">
@@ -6526,22 +6551,22 @@
       <c r="A129" s="19" t="str">
         <f>CONCATENATE("M 1 ",G6)</f>
       </c>
-      <c r="B129" s="19"/>
-      <c r="C129" s="19"/>
-      <c r="D129" s="19"/>
-      <c r="E129" s="19"/>
-      <c r="F129" s="19"/>
+      <c r="B129" s="22"/>
+      <c r="C129" s="22"/>
+      <c r="D129" s="22"/>
+      <c r="E129" s="22"/>
+      <c r="F129" s="22"/>
       <c r="G129" s="19" t="str">
         <f>'data'!$B$34</f>
       </c>
       <c r="I129" s="19" t="str">
         <f>CONCATENATE("M 14 ",O6)</f>
       </c>
-      <c r="J129" s="19"/>
-      <c r="K129" s="19"/>
-      <c r="L129" s="19"/>
-      <c r="M129" s="19"/>
-      <c r="N129" s="19"/>
+      <c r="J129" s="22"/>
+      <c r="K129" s="22"/>
+      <c r="L129" s="22"/>
+      <c r="M129" s="22"/>
+      <c r="N129" s="22"/>
       <c r="O129" s="19" t="str">
         <f>'data'!$B$50</f>
       </c>
@@ -6550,21 +6575,21 @@
       <c r="F131" t="s">
         <v>212</v>
       </c>
-      <c r="G131" s="15"/>
+      <c r="G131" s="23"/>
       <c r="N131" t="s">
         <v>212</v>
       </c>
-      <c r="O131" s="15"/>
+      <c r="O131" s="23"/>
     </row>
     <row r="132">
       <c r="F132" t="s">
         <v>213</v>
       </c>
-      <c r="G132" s="15"/>
+      <c r="G132" s="23"/>
       <c r="N132" t="s">
         <v>213</v>
       </c>
-      <c r="O132" s="15"/>
+      <c r="O132" s="23"/>
     </row>
     <row r="135">
       <c r="A135" s="11" t="s">
@@ -6610,22 +6635,22 @@
       <c r="A137" s="19" t="str">
         <f>CONCATENATE("M 2 ",G14)</f>
       </c>
-      <c r="B137" s="19"/>
-      <c r="C137" s="19"/>
-      <c r="D137" s="19"/>
-      <c r="E137" s="19"/>
-      <c r="F137" s="19"/>
+      <c r="B137" s="22"/>
+      <c r="C137" s="22"/>
+      <c r="D137" s="22"/>
+      <c r="E137" s="22"/>
+      <c r="F137" s="22"/>
       <c r="G137" s="19" t="str">
         <f>'data'!$B$36</f>
       </c>
       <c r="I137" s="19" t="str">
         <f>CONCATENATE("M 15 ",O14)</f>
       </c>
-      <c r="J137" s="19"/>
-      <c r="K137" s="19"/>
-      <c r="L137" s="19"/>
-      <c r="M137" s="19"/>
-      <c r="N137" s="19"/>
+      <c r="J137" s="22"/>
+      <c r="K137" s="22"/>
+      <c r="L137" s="22"/>
+      <c r="M137" s="22"/>
+      <c r="N137" s="22"/>
       <c r="O137" s="19" t="str">
         <f>'data'!$B$53</f>
       </c>
@@ -6634,21 +6659,21 @@
       <c r="F139" t="s">
         <v>212</v>
       </c>
-      <c r="G139" s="15"/>
+      <c r="G139" s="23"/>
       <c r="N139" t="s">
         <v>212</v>
       </c>
-      <c r="O139" s="15"/>
+      <c r="O139" s="23"/>
     </row>
     <row r="140">
       <c r="F140" t="s">
         <v>213</v>
       </c>
-      <c r="G140" s="15"/>
+      <c r="G140" s="23"/>
       <c r="N140" t="s">
         <v>213</v>
       </c>
-      <c r="O140" s="15"/>
+      <c r="O140" s="23"/>
     </row>
     <row r="143">
       <c r="A143" s="11" t="s">
@@ -6694,22 +6719,22 @@
       <c r="A145" s="19" t="str">
         <f>CONCATENATE("M 3 ",G22)</f>
       </c>
-      <c r="B145" s="19"/>
-      <c r="C145" s="19"/>
-      <c r="D145" s="19"/>
-      <c r="E145" s="19"/>
-      <c r="F145" s="19"/>
+      <c r="B145" s="22"/>
+      <c r="C145" s="22"/>
+      <c r="D145" s="22"/>
+      <c r="E145" s="22"/>
+      <c r="F145" s="22"/>
       <c r="G145" s="19" t="str">
         <f>'data'!$B$39</f>
       </c>
       <c r="I145" s="19" t="str">
         <f>CONCATENATE("M 16 ",O22)</f>
       </c>
-      <c r="J145" s="19"/>
-      <c r="K145" s="19"/>
-      <c r="L145" s="19"/>
-      <c r="M145" s="19"/>
-      <c r="N145" s="19"/>
+      <c r="J145" s="22"/>
+      <c r="K145" s="22"/>
+      <c r="L145" s="22"/>
+      <c r="M145" s="22"/>
+      <c r="N145" s="22"/>
       <c r="O145" s="19" t="str">
         <f>'data'!$B$56</f>
       </c>
@@ -6718,21 +6743,21 @@
       <c r="F147" t="s">
         <v>212</v>
       </c>
-      <c r="G147" s="15"/>
+      <c r="G147" s="23"/>
       <c r="N147" t="s">
         <v>212</v>
       </c>
-      <c r="O147" s="15"/>
+      <c r="O147" s="23"/>
     </row>
     <row r="148">
       <c r="F148" t="s">
         <v>213</v>
       </c>
-      <c r="G148" s="15"/>
+      <c r="G148" s="23"/>
       <c r="N148" t="s">
         <v>213</v>
       </c>
-      <c r="O148" s="15"/>
+      <c r="O148" s="23"/>
     </row>
     <row r="151">
       <c r="A151" s="11" t="s">
@@ -6778,22 +6803,22 @@
       <c r="A153" s="19" t="str">
         <f>'data'!$B$43</f>
       </c>
-      <c r="B153" s="19"/>
-      <c r="C153" s="19"/>
-      <c r="D153" s="19"/>
-      <c r="E153" s="19"/>
-      <c r="F153" s="19"/>
+      <c r="B153" s="22"/>
+      <c r="C153" s="22"/>
+      <c r="D153" s="22"/>
+      <c r="E153" s="22"/>
+      <c r="F153" s="22"/>
       <c r="G153" s="19" t="str">
         <f>'data'!$B$42</f>
       </c>
       <c r="I153" s="19" t="str">
         <f>CONCATENATE("M 17 ",O30)</f>
       </c>
-      <c r="J153" s="19"/>
-      <c r="K153" s="19"/>
-      <c r="L153" s="19"/>
-      <c r="M153" s="19"/>
-      <c r="N153" s="19"/>
+      <c r="J153" s="22"/>
+      <c r="K153" s="22"/>
+      <c r="L153" s="22"/>
+      <c r="M153" s="22"/>
+      <c r="N153" s="22"/>
       <c r="O153" s="19" t="str">
         <f>'data'!$B$81</f>
       </c>
@@ -6802,21 +6827,21 @@
       <c r="F155" t="s">
         <v>212</v>
       </c>
-      <c r="G155" s="15"/>
+      <c r="G155" s="23"/>
       <c r="N155" t="s">
         <v>212</v>
       </c>
-      <c r="O155" s="15"/>
+      <c r="O155" s="23"/>
     </row>
     <row r="156">
       <c r="F156" t="s">
         <v>213</v>
       </c>
-      <c r="G156" s="15"/>
+      <c r="G156" s="23"/>
       <c r="N156" t="s">
         <v>213</v>
       </c>
-      <c r="O156" s="15"/>
+      <c r="O156" s="23"/>
     </row>
     <row r="159">
       <c r="A159" s="11" t="s">
@@ -6862,22 +6887,22 @@
       <c r="A161" s="19" t="str">
         <f>CONCATENATE("M 4 ",G30)</f>
       </c>
-      <c r="B161" s="19"/>
-      <c r="C161" s="19"/>
-      <c r="D161" s="19"/>
-      <c r="E161" s="19"/>
-      <c r="F161" s="19"/>
+      <c r="B161" s="22"/>
+      <c r="C161" s="22"/>
+      <c r="D161" s="22"/>
+      <c r="E161" s="22"/>
+      <c r="F161" s="22"/>
       <c r="G161" s="19" t="str">
         <f>'data'!$B$16</f>
       </c>
       <c r="I161" s="19" t="str">
         <f>CONCATENATE("M 18 ",O38)</f>
       </c>
-      <c r="J161" s="19"/>
-      <c r="K161" s="19"/>
-      <c r="L161" s="19"/>
-      <c r="M161" s="19"/>
-      <c r="N161" s="19"/>
+      <c r="J161" s="22"/>
+      <c r="K161" s="22"/>
+      <c r="L161" s="22"/>
+      <c r="M161" s="22"/>
+      <c r="N161" s="22"/>
       <c r="O161" s="19" t="str">
         <f>'data'!$B$62</f>
       </c>
@@ -6886,21 +6911,21 @@
       <c r="F163" t="s">
         <v>212</v>
       </c>
-      <c r="G163" s="15"/>
+      <c r="G163" s="23"/>
       <c r="N163" t="s">
         <v>212</v>
       </c>
-      <c r="O163" s="15"/>
+      <c r="O163" s="23"/>
     </row>
     <row r="164">
       <c r="F164" t="s">
         <v>213</v>
       </c>
-      <c r="G164" s="15"/>
+      <c r="G164" s="23"/>
       <c r="N164" t="s">
         <v>213</v>
       </c>
-      <c r="O164" s="15"/>
+      <c r="O164" s="23"/>
     </row>
     <row r="167">
       <c r="A167" s="11" t="s">
@@ -6946,22 +6971,22 @@
       <c r="A169" s="19" t="str">
         <f>CONCATENATE("M 5 ",G38)</f>
       </c>
-      <c r="B169" s="19"/>
-      <c r="C169" s="19"/>
-      <c r="D169" s="19"/>
-      <c r="E169" s="19"/>
-      <c r="F169" s="19"/>
+      <c r="B169" s="22"/>
+      <c r="C169" s="22"/>
+      <c r="D169" s="22"/>
+      <c r="E169" s="22"/>
+      <c r="F169" s="22"/>
       <c r="G169" s="19" t="str">
         <f>'data'!$B$30</f>
       </c>
       <c r="I169" s="19" t="str">
         <f>CONCATENATE("M 19 ",O46)</f>
       </c>
-      <c r="J169" s="19"/>
-      <c r="K169" s="19"/>
-      <c r="L169" s="19"/>
-      <c r="M169" s="19"/>
-      <c r="N169" s="19"/>
+      <c r="J169" s="22"/>
+      <c r="K169" s="22"/>
+      <c r="L169" s="22"/>
+      <c r="M169" s="22"/>
+      <c r="N169" s="22"/>
       <c r="O169" s="19" t="str">
         <f>'data'!$B$65</f>
       </c>
@@ -6970,21 +6995,21 @@
       <c r="F171" t="s">
         <v>212</v>
       </c>
-      <c r="G171" s="15"/>
+      <c r="G171" s="23"/>
       <c r="N171" t="s">
         <v>212</v>
       </c>
-      <c r="O171" s="15"/>
+      <c r="O171" s="23"/>
     </row>
     <row r="172">
       <c r="F172" t="s">
         <v>213</v>
       </c>
-      <c r="G172" s="15"/>
+      <c r="G172" s="23"/>
       <c r="N172" t="s">
         <v>213</v>
       </c>
-      <c r="O172" s="15"/>
+      <c r="O172" s="23"/>
     </row>
     <row r="175">
       <c r="A175" s="11" t="s">
@@ -7030,22 +7055,22 @@
       <c r="A177" s="19" t="str">
         <f>CONCATENATE("M 6 ",G46)</f>
       </c>
-      <c r="B177" s="19"/>
-      <c r="C177" s="19"/>
-      <c r="D177" s="19"/>
-      <c r="E177" s="19"/>
-      <c r="F177" s="19"/>
+      <c r="B177" s="22"/>
+      <c r="C177" s="22"/>
+      <c r="D177" s="22"/>
+      <c r="E177" s="22"/>
+      <c r="F177" s="22"/>
       <c r="G177" s="19" t="str">
         <f>'data'!$B$22</f>
       </c>
       <c r="I177" s="19" t="str">
         <f>CONCATENATE("M 20 ",O54)</f>
       </c>
-      <c r="J177" s="19"/>
-      <c r="K177" s="19"/>
-      <c r="L177" s="19"/>
-      <c r="M177" s="19"/>
-      <c r="N177" s="19"/>
+      <c r="J177" s="22"/>
+      <c r="K177" s="22"/>
+      <c r="L177" s="22"/>
+      <c r="M177" s="22"/>
+      <c r="N177" s="22"/>
       <c r="O177" s="19" t="str">
         <f>'data'!$B$68</f>
       </c>
@@ -7054,21 +7079,21 @@
       <c r="F179" t="s">
         <v>212</v>
       </c>
-      <c r="G179" s="15"/>
+      <c r="G179" s="23"/>
       <c r="N179" t="s">
         <v>212</v>
       </c>
-      <c r="O179" s="15"/>
+      <c r="O179" s="23"/>
     </row>
     <row r="180">
       <c r="F180" t="s">
         <v>213</v>
       </c>
-      <c r="G180" s="15"/>
+      <c r="G180" s="23"/>
       <c r="N180" t="s">
         <v>213</v>
       </c>
-      <c r="O180" s="15"/>
+      <c r="O180" s="23"/>
     </row>
     <row r="183">
       <c r="A183" s="11" t="s">
@@ -7114,22 +7139,22 @@
       <c r="A185" s="19" t="str">
         <f>'data'!$B$26</f>
       </c>
-      <c r="B185" s="19"/>
-      <c r="C185" s="19"/>
-      <c r="D185" s="19"/>
-      <c r="E185" s="19"/>
-      <c r="F185" s="19"/>
+      <c r="B185" s="22"/>
+      <c r="C185" s="22"/>
+      <c r="D185" s="22"/>
+      <c r="E185" s="22"/>
+      <c r="F185" s="22"/>
       <c r="G185" s="19" t="str">
         <f>'data'!$B$25</f>
       </c>
       <c r="I185" s="19" t="str">
         <f>'data'!$B$72</f>
       </c>
-      <c r="J185" s="19"/>
-      <c r="K185" s="19"/>
-      <c r="L185" s="19"/>
-      <c r="M185" s="19"/>
-      <c r="N185" s="19"/>
+      <c r="J185" s="22"/>
+      <c r="K185" s="22"/>
+      <c r="L185" s="22"/>
+      <c r="M185" s="22"/>
+      <c r="N185" s="22"/>
       <c r="O185" s="19" t="str">
         <f>'data'!$B$88</f>
       </c>
@@ -7138,21 +7163,21 @@
       <c r="F187" t="s">
         <v>212</v>
       </c>
-      <c r="G187" s="15"/>
+      <c r="G187" s="23"/>
       <c r="N187" t="s">
         <v>212</v>
       </c>
-      <c r="O187" s="15"/>
+      <c r="O187" s="23"/>
     </row>
     <row r="188">
       <c r="F188" t="s">
         <v>213</v>
       </c>
-      <c r="G188" s="15"/>
+      <c r="G188" s="23"/>
       <c r="N188" t="s">
         <v>213</v>
       </c>
-      <c r="O188" s="15"/>
+      <c r="O188" s="23"/>
     </row>
     <row r="191">
       <c r="A191" s="11" t="s">
@@ -7198,22 +7223,22 @@
       <c r="A193" s="19" t="str">
         <f>CONCATENATE("M 7 ",G54)</f>
       </c>
-      <c r="B193" s="19"/>
-      <c r="C193" s="19"/>
-      <c r="D193" s="19"/>
-      <c r="E193" s="19"/>
-      <c r="F193" s="19"/>
+      <c r="B193" s="22"/>
+      <c r="C193" s="22"/>
+      <c r="D193" s="22"/>
+      <c r="E193" s="22"/>
+      <c r="F193" s="22"/>
       <c r="G193" s="19" t="str">
         <f>'data'!$B$27</f>
       </c>
       <c r="I193" s="19" t="str">
         <f>CONCATENATE("M 21 ",O62)</f>
       </c>
-      <c r="J193" s="19"/>
-      <c r="K193" s="19"/>
-      <c r="L193" s="19"/>
-      <c r="M193" s="19"/>
-      <c r="N193" s="19"/>
+      <c r="J193" s="22"/>
+      <c r="K193" s="22"/>
+      <c r="L193" s="22"/>
+      <c r="M193" s="22"/>
+      <c r="N193" s="22"/>
       <c r="O193" s="19" t="str">
         <f>'data'!$B$73</f>
       </c>
@@ -7222,21 +7247,21 @@
       <c r="F195" t="s">
         <v>212</v>
       </c>
-      <c r="G195" s="15"/>
+      <c r="G195" s="23"/>
       <c r="N195" t="s">
         <v>212</v>
       </c>
-      <c r="O195" s="15"/>
+      <c r="O195" s="23"/>
     </row>
     <row r="196">
       <c r="F196" t="s">
         <v>213</v>
       </c>
-      <c r="G196" s="15"/>
+      <c r="G196" s="23"/>
       <c r="N196" t="s">
         <v>213</v>
       </c>
-      <c r="O196" s="15"/>
+      <c r="O196" s="23"/>
     </row>
     <row r="199">
       <c r="A199" s="11" t="s">
@@ -7282,22 +7307,22 @@
       <c r="A201" s="19" t="str">
         <f>CONCATENATE("M 8 ",G62)</f>
       </c>
-      <c r="B201" s="19"/>
-      <c r="C201" s="19"/>
-      <c r="D201" s="19"/>
-      <c r="E201" s="19"/>
-      <c r="F201" s="19"/>
+      <c r="B201" s="22"/>
+      <c r="C201" s="22"/>
+      <c r="D201" s="22"/>
+      <c r="E201" s="22"/>
+      <c r="F201" s="22"/>
       <c r="G201" s="19" t="str">
         <f>'data'!$B$30</f>
       </c>
       <c r="I201" s="19" t="str">
         <f>CONCATENATE("M 22 ",O70)</f>
       </c>
-      <c r="J201" s="19"/>
-      <c r="K201" s="19"/>
-      <c r="L201" s="19"/>
-      <c r="M201" s="19"/>
-      <c r="N201" s="19"/>
+      <c r="J201" s="22"/>
+      <c r="K201" s="22"/>
+      <c r="L201" s="22"/>
+      <c r="M201" s="22"/>
+      <c r="N201" s="22"/>
       <c r="O201" s="19" t="str">
         <f>'data'!$B$76</f>
       </c>
@@ -7306,21 +7331,21 @@
       <c r="F203" t="s">
         <v>212</v>
       </c>
-      <c r="G203" s="15"/>
+      <c r="G203" s="23"/>
       <c r="N203" t="s">
         <v>212</v>
       </c>
-      <c r="O203" s="15"/>
+      <c r="O203" s="23"/>
     </row>
     <row r="204">
       <c r="F204" t="s">
         <v>213</v>
       </c>
-      <c r="G204" s="15"/>
+      <c r="G204" s="23"/>
       <c r="N204" t="s">
         <v>213</v>
       </c>
-      <c r="O204" s="15"/>
+      <c r="O204" s="23"/>
     </row>
     <row r="207">
       <c r="A207" s="11" t="s">
@@ -7366,22 +7391,22 @@
       <c r="A209" s="19" t="str">
         <f>CONCATENATE("M 9 ",G70)</f>
       </c>
-      <c r="B209" s="19"/>
-      <c r="C209" s="19"/>
-      <c r="D209" s="19"/>
-      <c r="E209" s="19"/>
-      <c r="F209" s="19"/>
+      <c r="B209" s="22"/>
+      <c r="C209" s="22"/>
+      <c r="D209" s="22"/>
+      <c r="E209" s="22"/>
+      <c r="F209" s="22"/>
       <c r="G209" s="19" t="str">
         <f>'data'!$B$33</f>
       </c>
       <c r="I209" s="19" t="str">
         <f>CONCATENATE("M 23 ",O78)</f>
       </c>
-      <c r="J209" s="19"/>
-      <c r="K209" s="19"/>
-      <c r="L209" s="19"/>
-      <c r="M209" s="19"/>
-      <c r="N209" s="19"/>
+      <c r="J209" s="22"/>
+      <c r="K209" s="22"/>
+      <c r="L209" s="22"/>
+      <c r="M209" s="22"/>
+      <c r="N209" s="22"/>
       <c r="O209" s="19" t="str">
         <f>'data'!$B$79</f>
       </c>
@@ -7390,21 +7415,21 @@
       <c r="F211" t="s">
         <v>212</v>
       </c>
-      <c r="G211" s="15"/>
+      <c r="G211" s="23"/>
       <c r="N211" t="s">
         <v>212</v>
       </c>
-      <c r="O211" s="15"/>
+      <c r="O211" s="23"/>
     </row>
     <row r="212">
       <c r="F212" t="s">
         <v>213</v>
       </c>
-      <c r="G212" s="15"/>
+      <c r="G212" s="23"/>
       <c r="N212" t="s">
         <v>213</v>
       </c>
-      <c r="O212" s="15"/>
+      <c r="O212" s="23"/>
     </row>
     <row r="215">
       <c r="A215" s="11" t="s">
@@ -7450,22 +7475,22 @@
       <c r="A217" s="19" t="str">
         <f>CONCATENATE("M 10 ",G78)</f>
       </c>
-      <c r="B217" s="19"/>
-      <c r="C217" s="19"/>
-      <c r="D217" s="19"/>
-      <c r="E217" s="19"/>
-      <c r="F217" s="19"/>
+      <c r="B217" s="22"/>
+      <c r="C217" s="22"/>
+      <c r="D217" s="22"/>
+      <c r="E217" s="22"/>
+      <c r="F217" s="22"/>
       <c r="G217" s="19" t="str">
         <f>'data'!$B$36</f>
       </c>
       <c r="I217" s="19" t="str">
         <f>CONCATENATE("M 24 ",O86)</f>
       </c>
-      <c r="J217" s="19"/>
-      <c r="K217" s="19"/>
-      <c r="L217" s="19"/>
-      <c r="M217" s="19"/>
-      <c r="N217" s="19"/>
+      <c r="J217" s="22"/>
+      <c r="K217" s="22"/>
+      <c r="L217" s="22"/>
+      <c r="M217" s="22"/>
+      <c r="N217" s="22"/>
       <c r="O217" s="19" t="str">
         <f>'data'!$B$82</f>
       </c>
@@ -7474,21 +7499,21 @@
       <c r="F219" t="s">
         <v>212</v>
       </c>
-      <c r="G219" s="15"/>
+      <c r="G219" s="23"/>
       <c r="N219" t="s">
         <v>212</v>
       </c>
-      <c r="O219" s="15"/>
+      <c r="O219" s="23"/>
     </row>
     <row r="220">
       <c r="F220" t="s">
         <v>213</v>
       </c>
-      <c r="G220" s="15"/>
+      <c r="G220" s="23"/>
       <c r="N220" t="s">
         <v>213</v>
       </c>
-      <c r="O220" s="15"/>
+      <c r="O220" s="23"/>
     </row>
     <row r="223">
       <c r="A223" s="11" t="s">
@@ -7534,22 +7559,22 @@
       <c r="A225" s="19" t="str">
         <f>CONCATENATE("M 11 ",G86)</f>
       </c>
-      <c r="B225" s="19"/>
-      <c r="C225" s="19"/>
-      <c r="D225" s="19"/>
-      <c r="E225" s="19"/>
-      <c r="F225" s="19"/>
+      <c r="B225" s="22"/>
+      <c r="C225" s="22"/>
+      <c r="D225" s="22"/>
+      <c r="E225" s="22"/>
+      <c r="F225" s="22"/>
       <c r="G225" s="19" t="str">
         <f>'data'!$B$39</f>
       </c>
       <c r="I225" s="19" t="str">
         <f>CONCATENATE("M 25 ",O94)</f>
       </c>
-      <c r="J225" s="19"/>
-      <c r="K225" s="19"/>
-      <c r="L225" s="19"/>
-      <c r="M225" s="19"/>
-      <c r="N225" s="19"/>
+      <c r="J225" s="22"/>
+      <c r="K225" s="22"/>
+      <c r="L225" s="22"/>
+      <c r="M225" s="22"/>
+      <c r="N225" s="22"/>
       <c r="O225" s="19" t="str">
         <f>'data'!$B$85</f>
       </c>
@@ -7558,21 +7583,21 @@
       <c r="F227" t="s">
         <v>212</v>
       </c>
-      <c r="G227" s="15"/>
+      <c r="G227" s="23"/>
       <c r="N227" t="s">
         <v>212</v>
       </c>
-      <c r="O227" s="15"/>
+      <c r="O227" s="23"/>
     </row>
     <row r="228">
       <c r="F228" t="s">
         <v>213</v>
       </c>
-      <c r="G228" s="15"/>
+      <c r="G228" s="23"/>
       <c r="N228" t="s">
         <v>213</v>
       </c>
-      <c r="O228" s="15"/>
+      <c r="O228" s="23"/>
     </row>
     <row r="231">
       <c r="A231" s="11" t="s">
@@ -7618,22 +7643,22 @@
       <c r="A233" s="19" t="str">
         <f>CONCATENATE("M 12 ",G94)</f>
       </c>
-      <c r="B233" s="19"/>
-      <c r="C233" s="19"/>
-      <c r="D233" s="19"/>
-      <c r="E233" s="19"/>
-      <c r="F233" s="19"/>
+      <c r="B233" s="22"/>
+      <c r="C233" s="22"/>
+      <c r="D233" s="22"/>
+      <c r="E233" s="22"/>
+      <c r="F233" s="22"/>
       <c r="G233" s="19" t="str">
         <f>'data'!$B$42</f>
       </c>
       <c r="I233" s="19" t="str">
         <f>CONCATENATE("M 26 ",O102)</f>
       </c>
-      <c r="J233" s="19"/>
-      <c r="K233" s="19"/>
-      <c r="L233" s="19"/>
-      <c r="M233" s="19"/>
-      <c r="N233" s="19"/>
+      <c r="J233" s="22"/>
+      <c r="K233" s="22"/>
+      <c r="L233" s="22"/>
+      <c r="M233" s="22"/>
+      <c r="N233" s="22"/>
       <c r="O233" s="19" t="str">
         <f>'data'!$B$88</f>
       </c>
@@ -7642,21 +7667,21 @@
       <c r="F235" t="s">
         <v>212</v>
       </c>
-      <c r="G235" s="15"/>
+      <c r="G235" s="23"/>
       <c r="N235" t="s">
         <v>212</v>
       </c>
-      <c r="O235" s="15"/>
+      <c r="O235" s="23"/>
     </row>
     <row r="236">
       <c r="F236" t="s">
         <v>213</v>
       </c>
-      <c r="G236" s="15"/>
+      <c r="G236" s="23"/>
       <c r="N236" t="s">
         <v>213</v>
       </c>
-      <c r="O236" s="15"/>
+      <c r="O236" s="23"/>
     </row>
     <row r="239">
       <c r="A239" s="11" t="s">
@@ -7702,22 +7727,22 @@
       <c r="A241" s="19" t="str">
         <f>CONCATENATE("M 13 ",G102)</f>
       </c>
-      <c r="B241" s="19"/>
-      <c r="C241" s="19"/>
-      <c r="D241" s="19"/>
-      <c r="E241" s="19"/>
-      <c r="F241" s="19"/>
+      <c r="B241" s="22"/>
+      <c r="C241" s="22"/>
+      <c r="D241" s="22"/>
+      <c r="E241" s="22"/>
+      <c r="F241" s="22"/>
       <c r="G241" s="19" t="str">
         <f>'data'!$B$45</f>
       </c>
       <c r="I241" s="19" t="str">
         <f>CONCATENATE("M 27 ",O110)</f>
       </c>
-      <c r="J241" s="19"/>
-      <c r="K241" s="19"/>
-      <c r="L241" s="19"/>
-      <c r="M241" s="19"/>
-      <c r="N241" s="19"/>
+      <c r="J241" s="22"/>
+      <c r="K241" s="22"/>
+      <c r="L241" s="22"/>
+      <c r="M241" s="22"/>
+      <c r="N241" s="22"/>
       <c r="O241" s="19" t="str">
         <f>'data'!$B$91</f>
       </c>
@@ -7726,21 +7751,21 @@
       <c r="F243" t="s">
         <v>212</v>
       </c>
-      <c r="G243" s="15"/>
+      <c r="G243" s="23"/>
       <c r="N243" t="s">
         <v>212</v>
       </c>
-      <c r="O243" s="15"/>
+      <c r="O243" s="23"/>
     </row>
     <row r="244">
       <c r="F244" t="s">
         <v>213</v>
       </c>
-      <c r="G244" s="15"/>
+      <c r="G244" s="23"/>
       <c r="N244" t="s">
         <v>213</v>
       </c>
-      <c r="O244" s="15"/>
+      <c r="O244" s="23"/>
     </row>
     <row r="252">
       <c r="A252" s="11" t="s">
@@ -7786,22 +7811,22 @@
       <c r="A254" s="19" t="str">
         <f>CONCATENATE("M 29 ",G131)</f>
       </c>
-      <c r="B254" s="19"/>
-      <c r="C254" s="19"/>
-      <c r="D254" s="19"/>
-      <c r="E254" s="19"/>
-      <c r="F254" s="19"/>
+      <c r="B254" s="22"/>
+      <c r="C254" s="22"/>
+      <c r="D254" s="22"/>
+      <c r="E254" s="22"/>
+      <c r="F254" s="22"/>
       <c r="G254" s="19" t="str">
         <f>CONCATENATE("M 28 ",G123)</f>
       </c>
       <c r="I254" s="19" t="str">
         <f>CONCATENATE("M 45 ",O131)</f>
       </c>
-      <c r="J254" s="19"/>
-      <c r="K254" s="19"/>
-      <c r="L254" s="19"/>
-      <c r="M254" s="19"/>
-      <c r="N254" s="19"/>
+      <c r="J254" s="22"/>
+      <c r="K254" s="22"/>
+      <c r="L254" s="22"/>
+      <c r="M254" s="22"/>
+      <c r="N254" s="22"/>
       <c r="O254" s="19" t="str">
         <f>CONCATENATE("M 44 ",O123)</f>
       </c>
@@ -7810,21 +7835,21 @@
       <c r="F256" t="s">
         <v>212</v>
       </c>
-      <c r="G256" s="15"/>
+      <c r="G256" s="23"/>
       <c r="N256" t="s">
         <v>212</v>
       </c>
-      <c r="O256" s="15"/>
+      <c r="O256" s="23"/>
     </row>
     <row r="257">
       <c r="F257" t="s">
         <v>213</v>
       </c>
-      <c r="G257" s="15"/>
+      <c r="G257" s="23"/>
       <c r="N257" t="s">
         <v>213</v>
       </c>
-      <c r="O257" s="15"/>
+      <c r="O257" s="23"/>
     </row>
     <row r="260">
       <c r="A260" s="11" t="s">
@@ -7870,22 +7895,22 @@
       <c r="A262" s="19" t="str">
         <f>CONCATENATE("M 31 ",G147)</f>
       </c>
-      <c r="B262" s="19"/>
-      <c r="C262" s="19"/>
-      <c r="D262" s="19"/>
-      <c r="E262" s="19"/>
-      <c r="F262" s="19"/>
+      <c r="B262" s="22"/>
+      <c r="C262" s="22"/>
+      <c r="D262" s="22"/>
+      <c r="E262" s="22"/>
+      <c r="F262" s="22"/>
       <c r="G262" s="19" t="str">
         <f>CONCATENATE("M 30 ",G139)</f>
       </c>
       <c r="I262" s="19" t="str">
         <f>CONCATENATE("M 47 ",O147)</f>
       </c>
-      <c r="J262" s="19"/>
-      <c r="K262" s="19"/>
-      <c r="L262" s="19"/>
-      <c r="M262" s="19"/>
-      <c r="N262" s="19"/>
+      <c r="J262" s="22"/>
+      <c r="K262" s="22"/>
+      <c r="L262" s="22"/>
+      <c r="M262" s="22"/>
+      <c r="N262" s="22"/>
       <c r="O262" s="19" t="str">
         <f>CONCATENATE("M 46 ",O139)</f>
       </c>
@@ -7894,21 +7919,21 @@
       <c r="F264" t="s">
         <v>212</v>
       </c>
-      <c r="G264" s="15"/>
+      <c r="G264" s="23"/>
       <c r="N264" t="s">
         <v>212</v>
       </c>
-      <c r="O264" s="15"/>
+      <c r="O264" s="23"/>
     </row>
     <row r="265">
       <c r="F265" t="s">
         <v>213</v>
       </c>
-      <c r="G265" s="15"/>
+      <c r="G265" s="23"/>
       <c r="N265" t="s">
         <v>213</v>
       </c>
-      <c r="O265" s="15"/>
+      <c r="O265" s="23"/>
     </row>
     <row r="268">
       <c r="A268" s="11" t="s">
@@ -7954,22 +7979,22 @@
       <c r="A270" s="19" t="str">
         <f>CONCATENATE("M 33 ",G163)</f>
       </c>
-      <c r="B270" s="19"/>
-      <c r="C270" s="19"/>
-      <c r="D270" s="19"/>
-      <c r="E270" s="19"/>
-      <c r="F270" s="19"/>
+      <c r="B270" s="22"/>
+      <c r="C270" s="22"/>
+      <c r="D270" s="22"/>
+      <c r="E270" s="22"/>
+      <c r="F270" s="22"/>
       <c r="G270" s="19" t="str">
         <f>CONCATENATE("M 32 ",G155)</f>
       </c>
       <c r="I270" s="19" t="str">
         <f>CONCATENATE("M 49 ",O163)</f>
       </c>
-      <c r="J270" s="19"/>
-      <c r="K270" s="19"/>
-      <c r="L270" s="19"/>
-      <c r="M270" s="19"/>
-      <c r="N270" s="19"/>
+      <c r="J270" s="22"/>
+      <c r="K270" s="22"/>
+      <c r="L270" s="22"/>
+      <c r="M270" s="22"/>
+      <c r="N270" s="22"/>
       <c r="O270" s="19" t="str">
         <f>CONCATENATE("M 48 ",O155)</f>
       </c>
@@ -7978,21 +8003,21 @@
       <c r="F272" t="s">
         <v>212</v>
       </c>
-      <c r="G272" s="15"/>
+      <c r="G272" s="23"/>
       <c r="N272" t="s">
         <v>212</v>
       </c>
-      <c r="O272" s="15"/>
+      <c r="O272" s="23"/>
     </row>
     <row r="273">
       <c r="F273" t="s">
         <v>213</v>
       </c>
-      <c r="G273" s="15"/>
+      <c r="G273" s="23"/>
       <c r="N273" t="s">
         <v>213</v>
       </c>
-      <c r="O273" s="15"/>
+      <c r="O273" s="23"/>
     </row>
     <row r="276">
       <c r="A276" s="11" t="s">
@@ -8038,22 +8063,22 @@
       <c r="A278" s="19" t="str">
         <f>CONCATENATE("M 35 ",G179)</f>
       </c>
-      <c r="B278" s="19"/>
-      <c r="C278" s="19"/>
-      <c r="D278" s="19"/>
-      <c r="E278" s="19"/>
-      <c r="F278" s="19"/>
+      <c r="B278" s="22"/>
+      <c r="C278" s="22"/>
+      <c r="D278" s="22"/>
+      <c r="E278" s="22"/>
+      <c r="F278" s="22"/>
       <c r="G278" s="19" t="str">
         <f>CONCATENATE("M 34 ",G171)</f>
       </c>
       <c r="I278" s="19" t="str">
         <f>CONCATENATE("M 51 ",O179)</f>
       </c>
-      <c r="J278" s="19"/>
-      <c r="K278" s="19"/>
-      <c r="L278" s="19"/>
-      <c r="M278" s="19"/>
-      <c r="N278" s="19"/>
+      <c r="J278" s="22"/>
+      <c r="K278" s="22"/>
+      <c r="L278" s="22"/>
+      <c r="M278" s="22"/>
+      <c r="N278" s="22"/>
       <c r="O278" s="19" t="str">
         <f>CONCATENATE("M 50 ",O171)</f>
       </c>
@@ -8062,21 +8087,21 @@
       <c r="F280" t="s">
         <v>212</v>
       </c>
-      <c r="G280" s="15"/>
+      <c r="G280" s="23"/>
       <c r="N280" t="s">
         <v>212</v>
       </c>
-      <c r="O280" s="15"/>
+      <c r="O280" s="23"/>
     </row>
     <row r="281">
       <c r="F281" t="s">
         <v>213</v>
       </c>
-      <c r="G281" s="15"/>
+      <c r="G281" s="23"/>
       <c r="N281" t="s">
         <v>213</v>
       </c>
-      <c r="O281" s="15"/>
+      <c r="O281" s="23"/>
     </row>
     <row r="284">
       <c r="A284" s="11" t="s">
@@ -8122,22 +8147,22 @@
       <c r="A286" s="19" t="str">
         <f>CONCATENATE("M 37 ",G195)</f>
       </c>
-      <c r="B286" s="19"/>
-      <c r="C286" s="19"/>
-      <c r="D286" s="19"/>
-      <c r="E286" s="19"/>
-      <c r="F286" s="19"/>
+      <c r="B286" s="22"/>
+      <c r="C286" s="22"/>
+      <c r="D286" s="22"/>
+      <c r="E286" s="22"/>
+      <c r="F286" s="22"/>
       <c r="G286" s="19" t="str">
         <f>CONCATENATE("M 36 ",G187)</f>
       </c>
       <c r="I286" s="19" t="str">
         <f>CONCATENATE("M 53 ",O195)</f>
       </c>
-      <c r="J286" s="19"/>
-      <c r="K286" s="19"/>
-      <c r="L286" s="19"/>
-      <c r="M286" s="19"/>
-      <c r="N286" s="19"/>
+      <c r="J286" s="22"/>
+      <c r="K286" s="22"/>
+      <c r="L286" s="22"/>
+      <c r="M286" s="22"/>
+      <c r="N286" s="22"/>
       <c r="O286" s="19" t="str">
         <f>CONCATENATE("M 52 ",O187)</f>
       </c>
@@ -8146,21 +8171,21 @@
       <c r="F288" t="s">
         <v>212</v>
       </c>
-      <c r="G288" s="15"/>
+      <c r="G288" s="23"/>
       <c r="N288" t="s">
         <v>212</v>
       </c>
-      <c r="O288" s="15"/>
+      <c r="O288" s="23"/>
     </row>
     <row r="289">
       <c r="F289" t="s">
         <v>213</v>
       </c>
-      <c r="G289" s="15"/>
+      <c r="G289" s="23"/>
       <c r="N289" t="s">
         <v>213</v>
       </c>
-      <c r="O289" s="15"/>
+      <c r="O289" s="23"/>
     </row>
     <row r="292">
       <c r="A292" s="11" t="s">
@@ -8206,22 +8231,22 @@
       <c r="A294" s="19" t="str">
         <f>CONCATENATE("M 39 ",G211)</f>
       </c>
-      <c r="B294" s="19"/>
-      <c r="C294" s="19"/>
-      <c r="D294" s="19"/>
-      <c r="E294" s="19"/>
-      <c r="F294" s="19"/>
+      <c r="B294" s="22"/>
+      <c r="C294" s="22"/>
+      <c r="D294" s="22"/>
+      <c r="E294" s="22"/>
+      <c r="F294" s="22"/>
       <c r="G294" s="19" t="str">
         <f>CONCATENATE("M 38 ",G203)</f>
       </c>
       <c r="I294" s="19" t="str">
         <f>CONCATENATE("M 55 ",O211)</f>
       </c>
-      <c r="J294" s="19"/>
-      <c r="K294" s="19"/>
-      <c r="L294" s="19"/>
-      <c r="M294" s="19"/>
-      <c r="N294" s="19"/>
+      <c r="J294" s="22"/>
+      <c r="K294" s="22"/>
+      <c r="L294" s="22"/>
+      <c r="M294" s="22"/>
+      <c r="N294" s="22"/>
       <c r="O294" s="19" t="str">
         <f>CONCATENATE("M 54 ",O203)</f>
       </c>
@@ -8230,21 +8255,21 @@
       <c r="F296" t="s">
         <v>212</v>
       </c>
-      <c r="G296" s="15"/>
+      <c r="G296" s="23"/>
       <c r="N296" t="s">
         <v>212</v>
       </c>
-      <c r="O296" s="15"/>
+      <c r="O296" s="23"/>
     </row>
     <row r="297">
       <c r="F297" t="s">
         <v>213</v>
       </c>
-      <c r="G297" s="15"/>
+      <c r="G297" s="23"/>
       <c r="N297" t="s">
         <v>213</v>
       </c>
-      <c r="O297" s="15"/>
+      <c r="O297" s="23"/>
     </row>
     <row r="300">
       <c r="A300" s="11" t="s">
@@ -8290,22 +8315,22 @@
       <c r="A302" s="19" t="str">
         <f>CONCATENATE("M 41 ",G227)</f>
       </c>
-      <c r="B302" s="19"/>
-      <c r="C302" s="19"/>
-      <c r="D302" s="19"/>
-      <c r="E302" s="19"/>
-      <c r="F302" s="19"/>
+      <c r="B302" s="22"/>
+      <c r="C302" s="22"/>
+      <c r="D302" s="22"/>
+      <c r="E302" s="22"/>
+      <c r="F302" s="22"/>
       <c r="G302" s="19" t="str">
         <f>CONCATENATE("M 40 ",G219)</f>
       </c>
       <c r="I302" s="19" t="str">
         <f>CONCATENATE("M 57 ",O227)</f>
       </c>
-      <c r="J302" s="19"/>
-      <c r="K302" s="19"/>
-      <c r="L302" s="19"/>
-      <c r="M302" s="19"/>
-      <c r="N302" s="19"/>
+      <c r="J302" s="22"/>
+      <c r="K302" s="22"/>
+      <c r="L302" s="22"/>
+      <c r="M302" s="22"/>
+      <c r="N302" s="22"/>
       <c r="O302" s="19" t="str">
         <f>CONCATENATE("M 56 ",O219)</f>
       </c>
@@ -8314,21 +8339,21 @@
       <c r="F304" t="s">
         <v>212</v>
       </c>
-      <c r="G304" s="15"/>
+      <c r="G304" s="23"/>
       <c r="N304" t="s">
         <v>212</v>
       </c>
-      <c r="O304" s="15"/>
+      <c r="O304" s="23"/>
     </row>
     <row r="305">
       <c r="F305" t="s">
         <v>213</v>
       </c>
-      <c r="G305" s="15"/>
+      <c r="G305" s="23"/>
       <c r="N305" t="s">
         <v>213</v>
       </c>
-      <c r="O305" s="15"/>
+      <c r="O305" s="23"/>
     </row>
     <row r="308">
       <c r="A308" s="11" t="s">
@@ -8374,22 +8399,22 @@
       <c r="A310" s="19" t="str">
         <f>CONCATENATE("M 43 ",G243)</f>
       </c>
-      <c r="B310" s="19"/>
-      <c r="C310" s="19"/>
-      <c r="D310" s="19"/>
-      <c r="E310" s="19"/>
-      <c r="F310" s="19"/>
+      <c r="B310" s="22"/>
+      <c r="C310" s="22"/>
+      <c r="D310" s="22"/>
+      <c r="E310" s="22"/>
+      <c r="F310" s="22"/>
       <c r="G310" s="19" t="str">
         <f>CONCATENATE("M 42 ",G235)</f>
       </c>
       <c r="I310" s="19" t="str">
         <f>CONCATENATE("M 59 ",O243)</f>
       </c>
-      <c r="J310" s="19"/>
-      <c r="K310" s="19"/>
-      <c r="L310" s="19"/>
-      <c r="M310" s="19"/>
-      <c r="N310" s="19"/>
+      <c r="J310" s="22"/>
+      <c r="K310" s="22"/>
+      <c r="L310" s="22"/>
+      <c r="M310" s="22"/>
+      <c r="N310" s="22"/>
       <c r="O310" s="19" t="str">
         <f>CONCATENATE("M 58 ",O235)</f>
       </c>
@@ -8398,21 +8423,21 @@
       <c r="F312" t="s">
         <v>212</v>
       </c>
-      <c r="G312" s="15"/>
+      <c r="G312" s="23"/>
       <c r="N312" t="s">
         <v>212</v>
       </c>
-      <c r="O312" s="15"/>
+      <c r="O312" s="23"/>
     </row>
     <row r="313">
       <c r="F313" t="s">
         <v>213</v>
       </c>
-      <c r="G313" s="15"/>
+      <c r="G313" s="23"/>
       <c r="N313" t="s">
         <v>213</v>
       </c>
-      <c r="O313" s="15"/>
+      <c r="O313" s="23"/>
     </row>
     <row r="321">
       <c r="A321" s="11" t="s">
@@ -8458,22 +8483,22 @@
       <c r="A323" s="19" t="str">
         <f>CONCATENATE("M 61 ",G264)</f>
       </c>
-      <c r="B323" s="19"/>
-      <c r="C323" s="19"/>
-      <c r="D323" s="19"/>
-      <c r="E323" s="19"/>
-      <c r="F323" s="19"/>
+      <c r="B323" s="22"/>
+      <c r="C323" s="22"/>
+      <c r="D323" s="22"/>
+      <c r="E323" s="22"/>
+      <c r="F323" s="22"/>
       <c r="G323" s="19" t="str">
         <f>CONCATENATE("M 60 ",G256)</f>
       </c>
       <c r="I323" s="19" t="str">
         <f>CONCATENATE("M 69 ",O264)</f>
       </c>
-      <c r="J323" s="19"/>
-      <c r="K323" s="19"/>
-      <c r="L323" s="19"/>
-      <c r="M323" s="19"/>
-      <c r="N323" s="19"/>
+      <c r="J323" s="22"/>
+      <c r="K323" s="22"/>
+      <c r="L323" s="22"/>
+      <c r="M323" s="22"/>
+      <c r="N323" s="22"/>
       <c r="O323" s="19" t="str">
         <f>CONCATENATE("M 68 ",O256)</f>
       </c>
@@ -8482,21 +8507,21 @@
       <c r="F325" t="s">
         <v>212</v>
       </c>
-      <c r="G325" s="15"/>
+      <c r="G325" s="23"/>
       <c r="N325" t="s">
         <v>212</v>
       </c>
-      <c r="O325" s="15"/>
+      <c r="O325" s="23"/>
     </row>
     <row r="326">
       <c r="F326" t="s">
         <v>213</v>
       </c>
-      <c r="G326" s="15"/>
+      <c r="G326" s="23"/>
       <c r="N326" t="s">
         <v>213</v>
       </c>
-      <c r="O326" s="15"/>
+      <c r="O326" s="23"/>
     </row>
     <row r="329">
       <c r="A329" s="11" t="s">
@@ -8542,22 +8567,22 @@
       <c r="A331" s="19" t="str">
         <f>CONCATENATE("M 63 ",G280)</f>
       </c>
-      <c r="B331" s="19"/>
-      <c r="C331" s="19"/>
-      <c r="D331" s="19"/>
-      <c r="E331" s="19"/>
-      <c r="F331" s="19"/>
+      <c r="B331" s="22"/>
+      <c r="C331" s="22"/>
+      <c r="D331" s="22"/>
+      <c r="E331" s="22"/>
+      <c r="F331" s="22"/>
       <c r="G331" s="19" t="str">
         <f>CONCATENATE("M 62 ",G272)</f>
       </c>
       <c r="I331" s="19" t="str">
         <f>CONCATENATE("M 71 ",O280)</f>
       </c>
-      <c r="J331" s="19"/>
-      <c r="K331" s="19"/>
-      <c r="L331" s="19"/>
-      <c r="M331" s="19"/>
-      <c r="N331" s="19"/>
+      <c r="J331" s="22"/>
+      <c r="K331" s="22"/>
+      <c r="L331" s="22"/>
+      <c r="M331" s="22"/>
+      <c r="N331" s="22"/>
       <c r="O331" s="19" t="str">
         <f>CONCATENATE("M 70 ",O272)</f>
       </c>
@@ -8566,21 +8591,21 @@
       <c r="F333" t="s">
         <v>212</v>
       </c>
-      <c r="G333" s="15"/>
+      <c r="G333" s="23"/>
       <c r="N333" t="s">
         <v>212</v>
       </c>
-      <c r="O333" s="15"/>
+      <c r="O333" s="23"/>
     </row>
     <row r="334">
       <c r="F334" t="s">
         <v>213</v>
       </c>
-      <c r="G334" s="15"/>
+      <c r="G334" s="23"/>
       <c r="N334" t="s">
         <v>213</v>
       </c>
-      <c r="O334" s="15"/>
+      <c r="O334" s="23"/>
     </row>
     <row r="337">
       <c r="A337" s="11" t="s">
@@ -8626,22 +8651,22 @@
       <c r="A339" s="19" t="str">
         <f>CONCATENATE("M 65 ",G296)</f>
       </c>
-      <c r="B339" s="19"/>
-      <c r="C339" s="19"/>
-      <c r="D339" s="19"/>
-      <c r="E339" s="19"/>
-      <c r="F339" s="19"/>
+      <c r="B339" s="22"/>
+      <c r="C339" s="22"/>
+      <c r="D339" s="22"/>
+      <c r="E339" s="22"/>
+      <c r="F339" s="22"/>
       <c r="G339" s="19" t="str">
         <f>CONCATENATE("M 64 ",G288)</f>
       </c>
       <c r="I339" s="19" t="str">
         <f>CONCATENATE("M 73 ",O296)</f>
       </c>
-      <c r="J339" s="19"/>
-      <c r="K339" s="19"/>
-      <c r="L339" s="19"/>
-      <c r="M339" s="19"/>
-      <c r="N339" s="19"/>
+      <c r="J339" s="22"/>
+      <c r="K339" s="22"/>
+      <c r="L339" s="22"/>
+      <c r="M339" s="22"/>
+      <c r="N339" s="22"/>
       <c r="O339" s="19" t="str">
         <f>CONCATENATE("M 72 ",O288)</f>
       </c>
@@ -8650,21 +8675,21 @@
       <c r="F341" t="s">
         <v>212</v>
       </c>
-      <c r="G341" s="15"/>
+      <c r="G341" s="23"/>
       <c r="N341" t="s">
         <v>212</v>
       </c>
-      <c r="O341" s="15"/>
+      <c r="O341" s="23"/>
     </row>
     <row r="342">
       <c r="F342" t="s">
         <v>213</v>
       </c>
-      <c r="G342" s="15"/>
+      <c r="G342" s="23"/>
       <c r="N342" t="s">
         <v>213</v>
       </c>
-      <c r="O342" s="15"/>
+      <c r="O342" s="23"/>
     </row>
     <row r="345">
       <c r="A345" s="11" t="s">
@@ -8710,22 +8735,22 @@
       <c r="A347" s="19" t="str">
         <f>CONCATENATE("M 67 ",G312)</f>
       </c>
-      <c r="B347" s="19"/>
-      <c r="C347" s="19"/>
-      <c r="D347" s="19"/>
-      <c r="E347" s="19"/>
-      <c r="F347" s="19"/>
+      <c r="B347" s="22"/>
+      <c r="C347" s="22"/>
+      <c r="D347" s="22"/>
+      <c r="E347" s="22"/>
+      <c r="F347" s="22"/>
       <c r="G347" s="19" t="str">
         <f>CONCATENATE("M 66 ",G304)</f>
       </c>
       <c r="I347" s="19" t="str">
         <f>CONCATENATE("M 75 ",O312)</f>
       </c>
-      <c r="J347" s="19"/>
-      <c r="K347" s="19"/>
-      <c r="L347" s="19"/>
-      <c r="M347" s="19"/>
-      <c r="N347" s="19"/>
+      <c r="J347" s="22"/>
+      <c r="K347" s="22"/>
+      <c r="L347" s="22"/>
+      <c r="M347" s="22"/>
+      <c r="N347" s="22"/>
       <c r="O347" s="19" t="str">
         <f>CONCATENATE("M 74 ",O304)</f>
       </c>
@@ -8734,21 +8759,21 @@
       <c r="F349" t="s">
         <v>212</v>
       </c>
-      <c r="G349" s="15"/>
+      <c r="G349" s="23"/>
       <c r="N349" t="s">
         <v>212</v>
       </c>
-      <c r="O349" s="15"/>
+      <c r="O349" s="23"/>
     </row>
     <row r="350">
       <c r="F350" t="s">
         <v>213</v>
       </c>
-      <c r="G350" s="15"/>
+      <c r="G350" s="23"/>
       <c r="N350" t="s">
         <v>213</v>
       </c>
-      <c r="O350" s="15"/>
+      <c r="O350" s="23"/>
     </row>
     <row r="358">
       <c r="A358" s="11" t="s">
@@ -8794,22 +8819,22 @@
       <c r="A360" s="19" t="str">
         <f>CONCATENATE("M 77 ",G333)</f>
       </c>
-      <c r="B360" s="19"/>
-      <c r="C360" s="19"/>
-      <c r="D360" s="19"/>
-      <c r="E360" s="19"/>
-      <c r="F360" s="19"/>
+      <c r="B360" s="22"/>
+      <c r="C360" s="22"/>
+      <c r="D360" s="22"/>
+      <c r="E360" s="22"/>
+      <c r="F360" s="22"/>
       <c r="G360" s="19" t="str">
         <f>CONCATENATE("M 76 ",G325)</f>
       </c>
       <c r="I360" s="19" t="str">
         <f>CONCATENATE("M 81 ",O333)</f>
       </c>
-      <c r="J360" s="19"/>
-      <c r="K360" s="19"/>
-      <c r="L360" s="19"/>
-      <c r="M360" s="19"/>
-      <c r="N360" s="19"/>
+      <c r="J360" s="22"/>
+      <c r="K360" s="22"/>
+      <c r="L360" s="22"/>
+      <c r="M360" s="22"/>
+      <c r="N360" s="22"/>
       <c r="O360" s="19" t="str">
         <f>CONCATENATE("M 80 ",O325)</f>
       </c>
@@ -8818,21 +8843,21 @@
       <c r="F362" t="s">
         <v>212</v>
       </c>
-      <c r="G362" s="15"/>
+      <c r="G362" s="23"/>
       <c r="N362" t="s">
         <v>212</v>
       </c>
-      <c r="O362" s="15"/>
+      <c r="O362" s="23"/>
     </row>
     <row r="363">
       <c r="F363" t="s">
         <v>213</v>
       </c>
-      <c r="G363" s="15"/>
+      <c r="G363" s="23"/>
       <c r="N363" t="s">
         <v>213</v>
       </c>
-      <c r="O363" s="15"/>
+      <c r="O363" s="23"/>
     </row>
     <row r="366">
       <c r="A366" s="11" t="s">
@@ -8878,22 +8903,22 @@
       <c r="A368" s="19" t="str">
         <f>CONCATENATE("M 79 ",G349)</f>
       </c>
-      <c r="B368" s="19"/>
-      <c r="C368" s="19"/>
-      <c r="D368" s="19"/>
-      <c r="E368" s="19"/>
-      <c r="F368" s="19"/>
+      <c r="B368" s="22"/>
+      <c r="C368" s="22"/>
+      <c r="D368" s="22"/>
+      <c r="E368" s="22"/>
+      <c r="F368" s="22"/>
       <c r="G368" s="19" t="str">
         <f>CONCATENATE("M 78 ",G341)</f>
       </c>
       <c r="I368" s="19" t="str">
         <f>CONCATENATE("M 83 ",O349)</f>
       </c>
-      <c r="J368" s="19"/>
-      <c r="K368" s="19"/>
-      <c r="L368" s="19"/>
-      <c r="M368" s="19"/>
-      <c r="N368" s="19"/>
+      <c r="J368" s="22"/>
+      <c r="K368" s="22"/>
+      <c r="L368" s="22"/>
+      <c r="M368" s="22"/>
+      <c r="N368" s="22"/>
       <c r="O368" s="19" t="str">
         <f>CONCATENATE("M 82 ",O341)</f>
       </c>
@@ -8902,21 +8927,21 @@
       <c r="F370" t="s">
         <v>212</v>
       </c>
-      <c r="G370" s="15"/>
+      <c r="G370" s="23"/>
       <c r="N370" t="s">
         <v>212</v>
       </c>
-      <c r="O370" s="15"/>
+      <c r="O370" s="23"/>
     </row>
     <row r="371">
       <c r="F371" t="s">
         <v>213</v>
       </c>
-      <c r="G371" s="15"/>
+      <c r="G371" s="23"/>
       <c r="N371" t="s">
         <v>213</v>
       </c>
-      <c r="O371" s="15"/>
+      <c r="O371" s="23"/>
     </row>
     <row r="379">
       <c r="A379" s="11" t="s">
@@ -8962,22 +8987,22 @@
       <c r="A381" s="19" t="str">
         <f>CONCATENATE("M 85 ",G370)</f>
       </c>
-      <c r="B381" s="19"/>
-      <c r="C381" s="19"/>
-      <c r="D381" s="19"/>
-      <c r="E381" s="19"/>
-      <c r="F381" s="19"/>
+      <c r="B381" s="22"/>
+      <c r="C381" s="22"/>
+      <c r="D381" s="22"/>
+      <c r="E381" s="22"/>
+      <c r="F381" s="22"/>
       <c r="G381" s="19" t="str">
         <f>CONCATENATE("M 84 ",G362)</f>
       </c>
       <c r="I381" s="19" t="str">
         <f>CONCATENATE("M 87 ",O370)</f>
       </c>
-      <c r="J381" s="19"/>
-      <c r="K381" s="19"/>
-      <c r="L381" s="19"/>
-      <c r="M381" s="19"/>
-      <c r="N381" s="19"/>
+      <c r="J381" s="22"/>
+      <c r="K381" s="22"/>
+      <c r="L381" s="22"/>
+      <c r="M381" s="22"/>
+      <c r="N381" s="22"/>
       <c r="O381" s="19" t="str">
         <f>CONCATENATE("M 86 ",O362)</f>
       </c>
@@ -8986,21 +9011,21 @@
       <c r="F383" t="s">
         <v>212</v>
       </c>
-      <c r="G383" s="15"/>
+      <c r="G383" s="23"/>
       <c r="N383" t="s">
         <v>212</v>
       </c>
-      <c r="O383" s="15"/>
+      <c r="O383" s="23"/>
     </row>
     <row r="384">
       <c r="F384" t="s">
         <v>213</v>
       </c>
-      <c r="G384" s="15"/>
+      <c r="G384" s="23"/>
       <c r="N384" t="s">
         <v>213</v>
       </c>
-      <c r="O384" s="15"/>
+      <c r="O384" s="23"/>
     </row>
     <row r="392">
       <c r="A392" s="11" t="s">
@@ -9028,11 +9053,11 @@
       <c r="A394" s="19" t="str">
         <f>CONCATENATE("M 89 ",O383)</f>
       </c>
-      <c r="B394" s="19"/>
-      <c r="C394" s="19"/>
-      <c r="D394" s="19"/>
-      <c r="E394" s="19"/>
-      <c r="F394" s="19"/>
+      <c r="B394" s="22"/>
+      <c r="C394" s="22"/>
+      <c r="D394" s="22"/>
+      <c r="E394" s="22"/>
+      <c r="F394" s="22"/>
       <c r="G394" s="19" t="str">
         <f>CONCATENATE("M 88 ",G383)</f>
       </c>
@@ -9041,15 +9066,16 @@
       <c r="F396" t="s">
         <v>212</v>
       </c>
-      <c r="G396" s="15"/>
+      <c r="G396" s="23"/>
     </row>
     <row r="397">
       <c r="F397" t="s">
         <v>213</v>
       </c>
-      <c r="G397" s="15"/>
+      <c r="G397" s="23"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <mergeCells count="92">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="I1:O1"/>
@@ -9380,6 +9406,7 @@
       <c r="E35" s="12"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <mergeCells count="1">
     <mergeCell ref="A1:P1"/>
   </mergeCells>
@@ -9603,6 +9630,7 @@
       <c r="E35" s="12"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <mergeCells count="1">
     <mergeCell ref="A1:P1"/>
   </mergeCells>

--- a/playoffs-example-large.xlsx
+++ b/playoffs-example-large.xlsx
@@ -24,7 +24,7 @@
   <definedNames>
     <definedName localSheetId="11" name="_xlnm.Print_Area">'Names to Print A'!$A$1:$B$46</definedName>
     <definedName localSheetId="12" name="_xlnm.Print_Area">'Names to Print B'!$A$1:$B$45</definedName>
-    <definedName localSheetId="2" name="_xlnm.Print_Area">'Elimination Matches'!$A$1:$O$404</definedName>
+    <definedName localSheetId="2" name="_xlnm.Print_Area">'Elimination Matches'!$A$1:$P$404</definedName>
   </definedNames>
   <calcPr calcId="122211"/>
 </workbook>
@@ -4183,7 +4183,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="18" t="str">
-        <f>data!D3</f>
+        <f>'data'!D3</f>
       </c>
     </row>
     <row r="2" ht="270" customHeight="true">
@@ -4191,7 +4191,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="18" t="str">
-        <f>data!D4</f>
+        <f>'data'!D4</f>
       </c>
     </row>
     <row r="3" ht="270" customHeight="true">
@@ -4199,7 +4199,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="18" t="str">
-        <f>data!D5</f>
+        <f>'data'!D5</f>
       </c>
     </row>
     <row r="4" ht="270" customHeight="true">
@@ -4207,7 +4207,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="18" t="str">
-        <f>data!D6</f>
+        <f>'data'!D6</f>
       </c>
     </row>
     <row r="5" ht="270" customHeight="true">
@@ -4215,7 +4215,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="18" t="str">
-        <f>data!D7</f>
+        <f>'data'!D7</f>
       </c>
     </row>
     <row r="6" ht="270" customHeight="true">
@@ -4223,7 +4223,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="18" t="str">
-        <f>data!D8</f>
+        <f>'data'!D8</f>
       </c>
     </row>
     <row r="7" ht="270" customHeight="true">
@@ -4231,7 +4231,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="18" t="str">
-        <f>data!D9</f>
+        <f>'data'!D9</f>
       </c>
     </row>
     <row r="8" ht="270" customHeight="true">
@@ -4239,7 +4239,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="18" t="str">
-        <f>data!D10</f>
+        <f>'data'!D10</f>
       </c>
     </row>
     <row r="9" ht="270" customHeight="true">
@@ -4247,7 +4247,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="18" t="str">
-        <f>data!D11</f>
+        <f>'data'!D11</f>
       </c>
     </row>
     <row r="10" ht="270" customHeight="true">
@@ -4255,7 +4255,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="18" t="str">
-        <f>data!D12</f>
+        <f>'data'!D12</f>
       </c>
     </row>
     <row r="11" ht="270" customHeight="true">
@@ -4263,7 +4263,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="18" t="str">
-        <f>data!D13</f>
+        <f>'data'!D13</f>
       </c>
     </row>
     <row r="12" ht="270" customHeight="true">
@@ -4271,7 +4271,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="18" t="str">
-        <f>data!D14</f>
+        <f>'data'!D14</f>
       </c>
     </row>
     <row r="13" ht="270" customHeight="true">
@@ -4279,7 +4279,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="18" t="str">
-        <f>data!D15</f>
+        <f>'data'!D15</f>
       </c>
     </row>
     <row r="14" ht="270" customHeight="true">
@@ -4287,7 +4287,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="18" t="str">
-        <f>data!D16</f>
+        <f>'data'!D16</f>
       </c>
     </row>
     <row r="15" ht="270" customHeight="true">
@@ -4295,7 +4295,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="18" t="str">
-        <f>data!D17</f>
+        <f>'data'!D17</f>
       </c>
     </row>
     <row r="16" ht="270" customHeight="true">
@@ -4303,7 +4303,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="18" t="str">
-        <f>data!D18</f>
+        <f>'data'!D18</f>
       </c>
     </row>
     <row r="17" ht="270" customHeight="true">
@@ -4311,7 +4311,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="18" t="str">
-        <f>data!D19</f>
+        <f>'data'!D19</f>
       </c>
     </row>
     <row r="18" ht="270" customHeight="true">
@@ -4319,7 +4319,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="18" t="str">
-        <f>data!D20</f>
+        <f>'data'!D20</f>
       </c>
     </row>
     <row r="19" ht="270" customHeight="true">
@@ -4327,7 +4327,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="18" t="str">
-        <f>data!D21</f>
+        <f>'data'!D21</f>
       </c>
     </row>
     <row r="20" ht="270" customHeight="true">
@@ -4335,7 +4335,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="18" t="str">
-        <f>data!D22</f>
+        <f>'data'!D22</f>
       </c>
     </row>
     <row r="21" ht="270" customHeight="true">
@@ -4343,7 +4343,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="18" t="str">
-        <f>data!D23</f>
+        <f>'data'!D23</f>
       </c>
     </row>
     <row r="22" ht="270" customHeight="true">
@@ -4351,7 +4351,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="18" t="str">
-        <f>data!D24</f>
+        <f>'data'!D24</f>
       </c>
     </row>
     <row r="23" ht="270" customHeight="true">
@@ -4359,7 +4359,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="18" t="str">
-        <f>data!D25</f>
+        <f>'data'!D25</f>
       </c>
     </row>
     <row r="24" ht="270" customHeight="true">
@@ -4367,7 +4367,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="18" t="str">
-        <f>data!D26</f>
+        <f>'data'!D26</f>
       </c>
     </row>
     <row r="25" ht="270" customHeight="true">
@@ -4375,7 +4375,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="18" t="str">
-        <f>data!D27</f>
+        <f>'data'!D27</f>
       </c>
     </row>
     <row r="26" ht="270" customHeight="true">
@@ -4383,7 +4383,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="18" t="str">
-        <f>data!D28</f>
+        <f>'data'!D28</f>
       </c>
     </row>
     <row r="27" ht="270" customHeight="true">
@@ -4391,7 +4391,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="18" t="str">
-        <f>data!D29</f>
+        <f>'data'!D29</f>
       </c>
     </row>
     <row r="28" ht="270" customHeight="true">
@@ -4399,7 +4399,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="18" t="str">
-        <f>data!D30</f>
+        <f>'data'!D30</f>
       </c>
     </row>
     <row r="29" ht="270" customHeight="true">
@@ -4407,7 +4407,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="18" t="str">
-        <f>data!D31</f>
+        <f>'data'!D31</f>
       </c>
     </row>
     <row r="30" ht="270" customHeight="true">
@@ -4415,7 +4415,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="18" t="str">
-        <f>data!D32</f>
+        <f>'data'!D32</f>
       </c>
     </row>
     <row r="31" ht="270" customHeight="true">
@@ -4423,7 +4423,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="18" t="str">
-        <f>data!D33</f>
+        <f>'data'!D33</f>
       </c>
     </row>
     <row r="32" ht="270" customHeight="true">
@@ -4431,7 +4431,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="18" t="str">
-        <f>data!D34</f>
+        <f>'data'!D34</f>
       </c>
     </row>
     <row r="33" ht="270" customHeight="true">
@@ -4439,7 +4439,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="18" t="str">
-        <f>data!D35</f>
+        <f>'data'!D35</f>
       </c>
     </row>
     <row r="34" ht="270" customHeight="true">
@@ -4447,7 +4447,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="18" t="str">
-        <f>data!D36</f>
+        <f>'data'!D36</f>
       </c>
     </row>
     <row r="35" ht="270" customHeight="true">
@@ -4455,7 +4455,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="18" t="str">
-        <f>data!D37</f>
+        <f>'data'!D37</f>
       </c>
     </row>
     <row r="36" ht="270" customHeight="true">
@@ -4463,7 +4463,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="18" t="str">
-        <f>data!D38</f>
+        <f>'data'!D38</f>
       </c>
     </row>
     <row r="37" ht="270" customHeight="true">
@@ -4471,7 +4471,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="18" t="str">
-        <f>data!D39</f>
+        <f>'data'!D39</f>
       </c>
     </row>
     <row r="38" ht="270" customHeight="true">
@@ -4479,7 +4479,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="18" t="str">
-        <f>data!D40</f>
+        <f>'data'!D40</f>
       </c>
     </row>
     <row r="39" ht="270" customHeight="true">
@@ -4487,7 +4487,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="18" t="str">
-        <f>data!D41</f>
+        <f>'data'!D41</f>
       </c>
     </row>
     <row r="40" ht="270" customHeight="true">
@@ -4495,7 +4495,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="18" t="str">
-        <f>data!D42</f>
+        <f>'data'!D42</f>
       </c>
     </row>
     <row r="41" ht="270" customHeight="true">
@@ -4503,7 +4503,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="18" t="str">
-        <f>data!D43</f>
+        <f>'data'!D43</f>
       </c>
     </row>
     <row r="42" ht="270" customHeight="true">
@@ -4511,7 +4511,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="18" t="str">
-        <f>data!D44</f>
+        <f>'data'!D44</f>
       </c>
     </row>
     <row r="43" ht="270" customHeight="true">
@@ -4519,7 +4519,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="18" t="str">
-        <f>data!D45</f>
+        <f>'data'!D45</f>
       </c>
     </row>
     <row r="44" ht="270" customHeight="true">
@@ -4527,7 +4527,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="18" t="str">
-        <f>data!D46</f>
+        <f>'data'!D46</f>
       </c>
     </row>
     <row r="45" ht="270" customHeight="true">
@@ -4535,7 +4535,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="18" t="str">
-        <f>data!D47</f>
+        <f>'data'!D47</f>
       </c>
     </row>
     <row r="46" ht="270" customHeight="true">
@@ -4543,7 +4543,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="18" t="str">
-        <f>data!D48</f>
+        <f>'data'!D48</f>
       </c>
     </row>
   </sheetData>
@@ -4584,7 +4584,7 @@
         <v>46</v>
       </c>
       <c r="B1" s="18" t="str">
-        <f>data!D49</f>
+        <f>'data'!D49</f>
       </c>
     </row>
     <row r="2" ht="270" customHeight="true">
@@ -4592,7 +4592,7 @@
         <v>47</v>
       </c>
       <c r="B2" s="18" t="str">
-        <f>data!D50</f>
+        <f>'data'!D50</f>
       </c>
     </row>
     <row r="3" ht="270" customHeight="true">
@@ -4600,7 +4600,7 @@
         <v>48</v>
       </c>
       <c r="B3" s="18" t="str">
-        <f>data!D51</f>
+        <f>'data'!D51</f>
       </c>
     </row>
     <row r="4" ht="270" customHeight="true">
@@ -4608,7 +4608,7 @@
         <v>49</v>
       </c>
       <c r="B4" s="18" t="str">
-        <f>data!D52</f>
+        <f>'data'!D52</f>
       </c>
     </row>
     <row r="5" ht="270" customHeight="true">
@@ -4616,7 +4616,7 @@
         <v>50</v>
       </c>
       <c r="B5" s="18" t="str">
-        <f>data!D53</f>
+        <f>'data'!D53</f>
       </c>
     </row>
     <row r="6" ht="270" customHeight="true">
@@ -4624,7 +4624,7 @@
         <v>51</v>
       </c>
       <c r="B6" s="18" t="str">
-        <f>data!D54</f>
+        <f>'data'!D54</f>
       </c>
     </row>
     <row r="7" ht="270" customHeight="true">
@@ -4632,7 +4632,7 @@
         <v>52</v>
       </c>
       <c r="B7" s="18" t="str">
-        <f>data!D55</f>
+        <f>'data'!D55</f>
       </c>
     </row>
     <row r="8" ht="270" customHeight="true">
@@ -4640,7 +4640,7 @@
         <v>53</v>
       </c>
       <c r="B8" s="18" t="str">
-        <f>data!D56</f>
+        <f>'data'!D56</f>
       </c>
     </row>
     <row r="9" ht="270" customHeight="true">
@@ -4648,7 +4648,7 @@
         <v>54</v>
       </c>
       <c r="B9" s="18" t="str">
-        <f>data!D57</f>
+        <f>'data'!D57</f>
       </c>
     </row>
     <row r="10" ht="270" customHeight="true">
@@ -4656,7 +4656,7 @@
         <v>55</v>
       </c>
       <c r="B10" s="18" t="str">
-        <f>data!D58</f>
+        <f>'data'!D58</f>
       </c>
     </row>
     <row r="11" ht="270" customHeight="true">
@@ -4664,7 +4664,7 @@
         <v>56</v>
       </c>
       <c r="B11" s="18" t="str">
-        <f>data!D59</f>
+        <f>'data'!D59</f>
       </c>
     </row>
     <row r="12" ht="270" customHeight="true">
@@ -4672,7 +4672,7 @@
         <v>57</v>
       </c>
       <c r="B12" s="18" t="str">
-        <f>data!D60</f>
+        <f>'data'!D60</f>
       </c>
     </row>
     <row r="13" ht="270" customHeight="true">
@@ -4680,7 +4680,7 @@
         <v>58</v>
       </c>
       <c r="B13" s="18" t="str">
-        <f>data!D61</f>
+        <f>'data'!D61</f>
       </c>
     </row>
     <row r="14" ht="270" customHeight="true">
@@ -4688,7 +4688,7 @@
         <v>59</v>
       </c>
       <c r="B14" s="18" t="str">
-        <f>data!D62</f>
+        <f>'data'!D62</f>
       </c>
     </row>
     <row r="15" ht="270" customHeight="true">
@@ -4696,7 +4696,7 @@
         <v>60</v>
       </c>
       <c r="B15" s="18" t="str">
-        <f>data!D63</f>
+        <f>'data'!D63</f>
       </c>
     </row>
     <row r="16" ht="270" customHeight="true">
@@ -4704,7 +4704,7 @@
         <v>61</v>
       </c>
       <c r="B16" s="18" t="str">
-        <f>data!D64</f>
+        <f>'data'!D64</f>
       </c>
     </row>
     <row r="17" ht="270" customHeight="true">
@@ -4712,7 +4712,7 @@
         <v>62</v>
       </c>
       <c r="B17" s="18" t="str">
-        <f>data!D65</f>
+        <f>'data'!D65</f>
       </c>
     </row>
     <row r="18" ht="270" customHeight="true">
@@ -4720,7 +4720,7 @@
         <v>63</v>
       </c>
       <c r="B18" s="18" t="str">
-        <f>data!D66</f>
+        <f>'data'!D66</f>
       </c>
     </row>
     <row r="19" ht="270" customHeight="true">
@@ -4728,7 +4728,7 @@
         <v>64</v>
       </c>
       <c r="B19" s="18" t="str">
-        <f>data!D67</f>
+        <f>'data'!D67</f>
       </c>
     </row>
     <row r="20" ht="270" customHeight="true">
@@ -4736,7 +4736,7 @@
         <v>65</v>
       </c>
       <c r="B20" s="18" t="str">
-        <f>data!D68</f>
+        <f>'data'!D68</f>
       </c>
     </row>
     <row r="21" ht="270" customHeight="true">
@@ -4744,7 +4744,7 @@
         <v>66</v>
       </c>
       <c r="B21" s="18" t="str">
-        <f>data!D69</f>
+        <f>'data'!D69</f>
       </c>
     </row>
     <row r="22" ht="270" customHeight="true">
@@ -4752,7 +4752,7 @@
         <v>67</v>
       </c>
       <c r="B22" s="18" t="str">
-        <f>data!D70</f>
+        <f>'data'!D70</f>
       </c>
     </row>
     <row r="23" ht="270" customHeight="true">
@@ -4760,7 +4760,7 @@
         <v>68</v>
       </c>
       <c r="B23" s="18" t="str">
-        <f>data!D71</f>
+        <f>'data'!D71</f>
       </c>
     </row>
     <row r="24" ht="270" customHeight="true">
@@ -4768,7 +4768,7 @@
         <v>69</v>
       </c>
       <c r="B24" s="18" t="str">
-        <f>data!D72</f>
+        <f>'data'!D72</f>
       </c>
     </row>
     <row r="25" ht="270" customHeight="true">
@@ -4776,7 +4776,7 @@
         <v>70</v>
       </c>
       <c r="B25" s="18" t="str">
-        <f>data!D73</f>
+        <f>'data'!D73</f>
       </c>
     </row>
     <row r="26" ht="270" customHeight="true">
@@ -4784,7 +4784,7 @@
         <v>71</v>
       </c>
       <c r="B26" s="18" t="str">
-        <f>data!D74</f>
+        <f>'data'!D74</f>
       </c>
     </row>
     <row r="27" ht="270" customHeight="true">
@@ -4792,7 +4792,7 @@
         <v>72</v>
       </c>
       <c r="B27" s="18" t="str">
-        <f>data!D75</f>
+        <f>'data'!D75</f>
       </c>
     </row>
     <row r="28" ht="270" customHeight="true">
@@ -4800,7 +4800,7 @@
         <v>73</v>
       </c>
       <c r="B28" s="18" t="str">
-        <f>data!D76</f>
+        <f>'data'!D76</f>
       </c>
     </row>
     <row r="29" ht="270" customHeight="true">
@@ -4808,7 +4808,7 @@
         <v>74</v>
       </c>
       <c r="B29" s="18" t="str">
-        <f>data!D77</f>
+        <f>'data'!D77</f>
       </c>
     </row>
     <row r="30" ht="270" customHeight="true">
@@ -4816,7 +4816,7 @@
         <v>75</v>
       </c>
       <c r="B30" s="18" t="str">
-        <f>data!D78</f>
+        <f>'data'!D78</f>
       </c>
     </row>
     <row r="31" ht="270" customHeight="true">
@@ -4824,7 +4824,7 @@
         <v>76</v>
       </c>
       <c r="B31" s="18" t="str">
-        <f>data!D79</f>
+        <f>'data'!D79</f>
       </c>
     </row>
     <row r="32" ht="270" customHeight="true">
@@ -4832,7 +4832,7 @@
         <v>77</v>
       </c>
       <c r="B32" s="18" t="str">
-        <f>data!D80</f>
+        <f>'data'!D80</f>
       </c>
     </row>
     <row r="33" ht="270" customHeight="true">
@@ -4840,7 +4840,7 @@
         <v>78</v>
       </c>
       <c r="B33" s="18" t="str">
-        <f>data!D81</f>
+        <f>'data'!D81</f>
       </c>
     </row>
     <row r="34" ht="270" customHeight="true">
@@ -4848,7 +4848,7 @@
         <v>79</v>
       </c>
       <c r="B34" s="18" t="str">
-        <f>data!D82</f>
+        <f>'data'!D82</f>
       </c>
     </row>
     <row r="35" ht="270" customHeight="true">
@@ -4856,7 +4856,7 @@
         <v>80</v>
       </c>
       <c r="B35" s="18" t="str">
-        <f>data!D83</f>
+        <f>'data'!D83</f>
       </c>
     </row>
     <row r="36" ht="270" customHeight="true">
@@ -4864,7 +4864,7 @@
         <v>81</v>
       </c>
       <c r="B36" s="18" t="str">
-        <f>data!D84</f>
+        <f>'data'!D84</f>
       </c>
     </row>
     <row r="37" ht="270" customHeight="true">
@@ -4872,7 +4872,7 @@
         <v>82</v>
       </c>
       <c r="B37" s="18" t="str">
-        <f>data!D85</f>
+        <f>'data'!D85</f>
       </c>
     </row>
     <row r="38" ht="270" customHeight="true">
@@ -4880,7 +4880,7 @@
         <v>83</v>
       </c>
       <c r="B38" s="18" t="str">
-        <f>data!D86</f>
+        <f>'data'!D86</f>
       </c>
     </row>
     <row r="39" ht="270" customHeight="true">
@@ -4888,7 +4888,7 @@
         <v>84</v>
       </c>
       <c r="B39" s="18" t="str">
-        <f>data!D87</f>
+        <f>'data'!D87</f>
       </c>
     </row>
     <row r="40" ht="270" customHeight="true">
@@ -4896,7 +4896,7 @@
         <v>85</v>
       </c>
       <c r="B40" s="18" t="str">
-        <f>data!D88</f>
+        <f>'data'!D88</f>
       </c>
     </row>
     <row r="41" ht="270" customHeight="true">
@@ -4904,7 +4904,7 @@
         <v>86</v>
       </c>
       <c r="B41" s="18" t="str">
-        <f>data!D89</f>
+        <f>'data'!D89</f>
       </c>
     </row>
     <row r="42" ht="270" customHeight="true">
@@ -4912,7 +4912,7 @@
         <v>87</v>
       </c>
       <c r="B42" s="18" t="str">
-        <f>data!D90</f>
+        <f>'data'!D90</f>
       </c>
     </row>
     <row r="43" ht="270" customHeight="true">
@@ -4920,7 +4920,7 @@
         <v>88</v>
       </c>
       <c r="B43" s="18" t="str">
-        <f>data!D91</f>
+        <f>'data'!D91</f>
       </c>
     </row>
     <row r="44" ht="270" customHeight="true">
@@ -4928,7 +4928,7 @@
         <v>89</v>
       </c>
       <c r="B44" s="18" t="str">
-        <f>data!D92</f>
+        <f>'data'!D92</f>
       </c>
     </row>
     <row r="45" ht="270" customHeight="true">
@@ -4936,7 +4936,7 @@
         <v>90</v>
       </c>
       <c r="B45" s="18" t="str">
-        <f>data!D93</f>
+        <f>'data'!D93</f>
       </c>
     </row>
   </sheetData>
@@ -5249,19 +5249,14 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" max="1" min="1" width="30"/>
-    <col customWidth="true" max="3" min="2" width="5"/>
-    <col customWidth="true" max="4" min="4" width="3"/>
-    <col customWidth="true" max="6" min="5" width="5"/>
+    <col customWidth="true" max="6" min="2" width="5"/>
     <col customWidth="true" max="7" min="7" width="30"/>
     <col customWidth="true" max="8" min="8" width="5"/>
     <col customWidth="true" max="9" min="9" width="30"/>
-    <col customWidth="true" max="11" min="10" width="5"/>
-    <col customWidth="true" max="12" min="12" width="3"/>
-    <col customWidth="true" max="14" min="13" width="5"/>
+    <col customWidth="true" max="14" min="10" width="5"/>
     <col customWidth="true" max="15" min="15" width="30"/>
-    <col customWidth="true" max="18" min="16" width="5"/>
-    <col customWidth="true" max="19" min="19" width="30"/>
-    <col customWidth="true" max="20" min="20" width="2"/>
+    <col customWidth="true" max="16" min="16" width="5"/>
+    <col customWidth="true" max="20" min="17" width="10.83"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/playoffs-example-large.xlsx
+++ b/playoffs-example-large.xlsx
@@ -22,6 +22,14 @@
     <sheet name="Names to Print B" sheetId="17" r:id="rId20"/>
   </sheets>
   <definedNames>
+    <definedName localSheetId="3" name="_xlnm.Print_Area">'Tree 1'!$A$1:$K$35</definedName>
+    <definedName localSheetId="4" name="_xlnm.Print_Area">'Tree 2'!$A$1:$K$35</definedName>
+    <definedName localSheetId="5" name="_xlnm.Print_Area">'Tree 3'!$A$1:$K$35</definedName>
+    <definedName localSheetId="6" name="_xlnm.Print_Area">'Tree 4'!$A$1:$K$35</definedName>
+    <definedName localSheetId="7" name="_xlnm.Print_Area">'Tree 5'!$A$1:$K$35</definedName>
+    <definedName localSheetId="8" name="_xlnm.Print_Area">'Tree 6'!$A$1:$K$35</definedName>
+    <definedName localSheetId="9" name="_xlnm.Print_Area">'Tree 7'!$A$1:$K$35</definedName>
+    <definedName localSheetId="10" name="_xlnm.Print_Area">'Tree 8'!$A$1:$K$35</definedName>
     <definedName localSheetId="11" name="_xlnm.Print_Area">'Names to Print A'!$A$1:$B$46</definedName>
     <definedName localSheetId="12" name="_xlnm.Print_Area">'Names to Print B'!$A$1:$B$45</definedName>
     <definedName localSheetId="2" name="_xlnm.Print_Area">'Elimination Matches'!$A$1:$P$404</definedName>
@@ -2800,12 +2808,17 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
   <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" max="1" min="1" width="25"/>
-    <col customWidth="true" max="2" min="2" width="10"/>
-    <col customWidth="true" max="26" min="3" width="3.5"/>
+    <col customWidth="true" max="2" min="2" width="4"/>
+    <col customWidth="true" max="3" min="3" width="28"/>
+    <col customWidth="true" max="26" min="4" width="3.5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2822,11 +2835,6 @@
       <c r="I1" s="11"/>
       <c r="J1" s="11"/>
       <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11"/>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11"/>
-      <c r="P1" s="11"/>
     </row>
     <row r="6">
       <c r="E6" s="16" t="s">
@@ -3018,18 +3026,25 @@
   </sheetData>
   <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
+  <printOptions horizontalCentered="true" verticalCentered="true"/>
+  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
   <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" max="1" min="1" width="25"/>
-    <col customWidth="true" max="2" min="2" width="10"/>
-    <col customWidth="true" max="26" min="3" width="3.5"/>
+    <col customWidth="true" max="2" min="2" width="4"/>
+    <col customWidth="true" max="3" min="3" width="28"/>
+    <col customWidth="true" max="26" min="4" width="3.5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3046,11 +3061,6 @@
       <c r="I1" s="11"/>
       <c r="J1" s="11"/>
       <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11"/>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11"/>
-      <c r="P1" s="11"/>
     </row>
     <row r="6">
       <c r="E6" s="16" t="s">
@@ -3251,18 +3261,25 @@
   </sheetData>
   <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
+  <printOptions horizontalCentered="true" verticalCentered="true"/>
+  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
   <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" max="1" min="1" width="25"/>
-    <col customWidth="true" max="2" min="2" width="10"/>
-    <col customWidth="true" max="26" min="3" width="3.5"/>
+    <col customWidth="true" max="2" min="2" width="4"/>
+    <col customWidth="true" max="3" min="3" width="28"/>
+    <col customWidth="true" max="26" min="4" width="3.5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3279,11 +3296,6 @@
       <c r="I1" s="11"/>
       <c r="J1" s="11"/>
       <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11"/>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11"/>
-      <c r="P1" s="11"/>
     </row>
     <row r="6">
       <c r="E6" s="16" t="s">
@@ -3475,18 +3487,25 @@
   </sheetData>
   <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
+  <printOptions horizontalCentered="true" verticalCentered="true"/>
+  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
   <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" max="1" min="1" width="25"/>
-    <col customWidth="true" max="2" min="2" width="10"/>
-    <col customWidth="true" max="26" min="3" width="3.5"/>
+    <col customWidth="true" max="2" min="2" width="4"/>
+    <col customWidth="true" max="3" min="3" width="28"/>
+    <col customWidth="true" max="26" min="4" width="3.5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3503,11 +3522,6 @@
       <c r="I1" s="11"/>
       <c r="J1" s="11"/>
       <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11"/>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11"/>
-      <c r="P1" s="11"/>
     </row>
     <row r="6">
       <c r="E6" s="16" t="s">
@@ -3708,18 +3722,25 @@
   </sheetData>
   <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
+  <printOptions horizontalCentered="true" verticalCentered="true"/>
+  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
   <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" max="1" min="1" width="25"/>
-    <col customWidth="true" max="2" min="2" width="10"/>
-    <col customWidth="true" max="26" min="3" width="3.5"/>
+    <col customWidth="true" max="2" min="2" width="4"/>
+    <col customWidth="true" max="3" min="3" width="28"/>
+    <col customWidth="true" max="26" min="4" width="3.5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3736,11 +3757,6 @@
       <c r="I1" s="11"/>
       <c r="J1" s="11"/>
       <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11"/>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11"/>
-      <c r="P1" s="11"/>
     </row>
     <row r="6">
       <c r="E6" s="16" t="s">
@@ -3932,18 +3948,25 @@
   </sheetData>
   <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
+  <printOptions horizontalCentered="true" verticalCentered="true"/>
+  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
   <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" max="1" min="1" width="25"/>
-    <col customWidth="true" max="2" min="2" width="10"/>
-    <col customWidth="true" max="26" min="3" width="3.5"/>
+    <col customWidth="true" max="2" min="2" width="4"/>
+    <col customWidth="true" max="3" min="3" width="28"/>
+    <col customWidth="true" max="26" min="4" width="3.5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3960,11 +3983,6 @@
       <c r="I1" s="11"/>
       <c r="J1" s="11"/>
       <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11"/>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11"/>
-      <c r="P1" s="11"/>
     </row>
     <row r="6">
       <c r="E6" s="16" t="s">
@@ -4165,8 +4183,10 @@
   </sheetData>
   <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
+  <printOptions horizontalCentered="true" verticalCentered="true"/>
+  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
@@ -9185,12 +9205,17 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
   <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" max="1" min="1" width="25"/>
-    <col customWidth="true" max="2" min="2" width="10"/>
-    <col customWidth="true" max="26" min="3" width="3.5"/>
+    <col customWidth="true" max="2" min="2" width="4"/>
+    <col customWidth="true" max="3" min="3" width="28"/>
+    <col customWidth="true" max="26" min="4" width="3.5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9207,11 +9232,6 @@
       <c r="I1" s="11"/>
       <c r="J1" s="11"/>
       <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11"/>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11"/>
-      <c r="P1" s="11"/>
     </row>
     <row r="6">
       <c r="E6" s="16" t="s">
@@ -9403,18 +9423,25 @@
   </sheetData>
   <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
+  <printOptions horizontalCentered="true" verticalCentered="true"/>
+  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
   <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" max="1" min="1" width="25"/>
-    <col customWidth="true" max="2" min="2" width="10"/>
-    <col customWidth="true" max="26" min="3" width="3.5"/>
+    <col customWidth="true" max="2" min="2" width="4"/>
+    <col customWidth="true" max="3" min="3" width="28"/>
+    <col customWidth="true" max="26" min="4" width="3.5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9431,11 +9458,6 @@
       <c r="I1" s="11"/>
       <c r="J1" s="11"/>
       <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11"/>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11"/>
-      <c r="P1" s="11"/>
     </row>
     <row r="6">
       <c r="E6" s="16" t="s">
@@ -9627,7 +9649,9 @@
   </sheetData>
   <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
+  <printOptions horizontalCentered="true" verticalCentered="true"/>
+  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/playoffs-example-large.xlsx
+++ b/playoffs-example-large.xlsx
@@ -1189,7 +1189,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true" applyAlignment="false">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
@@ -2837,6 +2837,8 @@
       <c r="K1" s="11"/>
     </row>
     <row r="6">
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
       <c r="E6" s="16" t="s">
         <v>68</v>
       </c>
@@ -2856,6 +2858,8 @@
       <c r="I9" s="12"/>
     </row>
     <row r="10">
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
       <c r="E10" s="16" t="s">
         <v>71</v>
       </c>
@@ -2877,6 +2881,8 @@
       <c r="K13" s="12"/>
     </row>
     <row r="14">
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
         <v>74</v>
       </c>
@@ -2930,6 +2936,8 @@
       <c r="K21" s="12"/>
     </row>
     <row r="22">
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
       <c r="E22" s="16" t="s">
         <v>54</v>
       </c>
@@ -2985,6 +2993,8 @@
       <c r="I29" s="12"/>
     </row>
     <row r="30">
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
         <v>21</v>
       </c>
@@ -3063,6 +3073,8 @@
       <c r="K1" s="11"/>
     </row>
     <row r="6">
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
       <c r="E6" s="16" t="s">
         <v>32</v>
       </c>
@@ -3112,6 +3124,8 @@
       <c r="K13" s="12"/>
     </row>
     <row r="14">
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
         <v>38</v>
       </c>
@@ -3165,6 +3179,8 @@
       <c r="K21" s="12"/>
     </row>
     <row r="22">
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
       <c r="E22" s="16" t="s">
         <v>44</v>
       </c>
@@ -3220,6 +3236,8 @@
       <c r="I29" s="12"/>
     </row>
     <row r="30">
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
         <v>98</v>
       </c>
@@ -3298,6 +3316,8 @@
       <c r="K1" s="11"/>
     </row>
     <row r="6">
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
       <c r="E6" s="16" t="s">
         <v>104</v>
       </c>
@@ -3317,6 +3337,8 @@
       <c r="I9" s="12"/>
     </row>
     <row r="10">
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
       <c r="E10" s="16" t="s">
         <v>106</v>
       </c>
@@ -3338,6 +3360,8 @@
       <c r="K13" s="12"/>
     </row>
     <row r="14">
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
         <v>108</v>
       </c>
@@ -3391,6 +3415,8 @@
       <c r="K21" s="12"/>
     </row>
     <row r="22">
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
       <c r="E22" s="16" t="s">
         <v>114</v>
       </c>
@@ -3446,6 +3472,8 @@
       <c r="I29" s="12"/>
     </row>
     <row r="30">
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
         <v>123</v>
       </c>
@@ -3524,6 +3552,8 @@
       <c r="K1" s="11"/>
     </row>
     <row r="6">
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
       <c r="E6" s="16" t="s">
         <v>132</v>
       </c>
@@ -3573,6 +3603,8 @@
       <c r="K13" s="12"/>
     </row>
     <row r="14">
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
         <v>141</v>
       </c>
@@ -3626,6 +3658,8 @@
       <c r="K21" s="12"/>
     </row>
     <row r="22">
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
       <c r="E22" s="16" t="s">
         <v>150</v>
       </c>
@@ -3681,6 +3715,8 @@
       <c r="I29" s="12"/>
     </row>
     <row r="30">
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
         <v>158</v>
       </c>
@@ -3759,6 +3795,8 @@
       <c r="K1" s="11"/>
     </row>
     <row r="6">
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
       <c r="E6" s="16" t="s">
         <v>164</v>
       </c>
@@ -3778,6 +3816,8 @@
       <c r="I9" s="12"/>
     </row>
     <row r="10">
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
       <c r="E10" s="16" t="s">
         <v>166</v>
       </c>
@@ -3799,6 +3839,8 @@
       <c r="K13" s="12"/>
     </row>
     <row r="14">
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
         <v>168</v>
       </c>
@@ -3852,6 +3894,8 @@
       <c r="K21" s="12"/>
     </row>
     <row r="22">
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
       <c r="E22" s="16" t="s">
         <v>173</v>
       </c>
@@ -3907,6 +3951,8 @@
       <c r="I29" s="12"/>
     </row>
     <row r="30">
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
         <v>179</v>
       </c>
@@ -3985,6 +4031,8 @@
       <c r="K1" s="11"/>
     </row>
     <row r="6">
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
       <c r="E6" s="16" t="s">
         <v>184</v>
       </c>
@@ -4034,6 +4082,8 @@
       <c r="K13" s="12"/>
     </row>
     <row r="14">
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
         <v>190</v>
       </c>
@@ -4087,6 +4137,8 @@
       <c r="K21" s="12"/>
     </row>
     <row r="22">
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
       <c r="E22" s="16" t="s">
         <v>164</v>
       </c>
@@ -4142,6 +4194,8 @@
       <c r="I29" s="12"/>
     </row>
     <row r="30">
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
         <v>201</v>
       </c>
@@ -9234,6 +9288,8 @@
       <c r="K1" s="11"/>
     </row>
     <row r="6">
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
       <c r="E6" s="16" t="s">
         <v>18</v>
       </c>
@@ -9253,6 +9309,8 @@
       <c r="I9" s="12"/>
     </row>
     <row r="10">
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
       <c r="E10" s="16" t="s">
         <v>21</v>
       </c>
@@ -9274,6 +9332,8 @@
       <c r="K13" s="12"/>
     </row>
     <row r="14">
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
         <v>24</v>
       </c>
@@ -9327,6 +9387,8 @@
       <c r="K21" s="12"/>
     </row>
     <row r="22">
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
       <c r="E22" s="16" t="s">
         <v>32</v>
       </c>
@@ -9382,6 +9444,8 @@
       <c r="I29" s="12"/>
     </row>
     <row r="30">
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
         <v>38</v>
       </c>
@@ -9460,6 +9524,8 @@
       <c r="K1" s="11"/>
     </row>
     <row r="6">
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
       <c r="E6" s="16" t="s">
         <v>44</v>
       </c>
@@ -9479,6 +9545,8 @@
       <c r="I9" s="12"/>
     </row>
     <row r="10">
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
       <c r="E10" s="16" t="s">
         <v>46</v>
       </c>
@@ -9500,6 +9568,8 @@
       <c r="K13" s="12"/>
     </row>
     <row r="14">
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
         <v>48</v>
       </c>
@@ -9553,6 +9623,8 @@
       <c r="K21" s="12"/>
     </row>
     <row r="22">
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
       <c r="E22" s="16" t="s">
         <v>54</v>
       </c>
@@ -9608,6 +9680,8 @@
       <c r="I29" s="12"/>
     </row>
     <row r="30">
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
         <v>60</v>
       </c>

--- a/playoffs-example-large.xlsx
+++ b/playoffs-example-large.xlsx
@@ -683,175 +683,175 @@
     <t>2.</t>
   </si>
   <si>
+    <t>Round 1 - Match 17</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 2</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 18</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 3</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 19</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 4</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 20</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 5</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 21</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 6</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 22</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 7</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 23</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 8</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 24</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 9</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 25</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 10</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 26</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 11</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 27</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 12</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 28</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 13</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 29</t>
+  </si>
+  <si>
     <t>Round 1 - Match 14</t>
   </si>
   <si>
-    <t>Round 1 - Match 2</t>
+    <t>Round 1 - Match 30</t>
   </si>
   <si>
     <t>Round 1 - Match 15</t>
   </si>
   <si>
-    <t>Round 1 - Match 3</t>
+    <t>Round 1 - Match 31</t>
   </si>
   <si>
     <t>Round 1 - Match 16</t>
   </si>
   <si>
-    <t>Round 1 - Match 4</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 17</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 5</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 18</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 6</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 19</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 7</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 20</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 8</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 21</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 9</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 22</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 10</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 23</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 11</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 24</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 12</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 25</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 13</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 26</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 27</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 28</t>
+    <t>Round 1 - Match 32</t>
+  </si>
+  <si>
+    <t>Round 2 - Match 33</t>
+  </si>
+  <si>
+    <t>Round 2 - Match 46</t>
+  </si>
+  <si>
+    <t>Round 2 - Match 34</t>
+  </si>
+  <si>
+    <t>Round 2 - Match 47</t>
+  </si>
+  <si>
+    <t>Round 2 - Match 35</t>
+  </si>
+  <si>
+    <t>Round 2 - Match 48</t>
+  </si>
+  <si>
+    <t>Round 2 - Match 36</t>
+  </si>
+  <si>
+    <t>Round 2 - Match 49</t>
+  </si>
+  <si>
+    <t>Round 2 - Match 37</t>
+  </si>
+  <si>
+    <t>Round 2 - Match 50</t>
+  </si>
+  <si>
+    <t>Round 2 - Match 38</t>
+  </si>
+  <si>
+    <t>Round 2 - Match 51</t>
+  </si>
+  <si>
+    <t>Round 2 - Match 39</t>
+  </si>
+  <si>
+    <t>Round 2 - Match 52</t>
+  </si>
+  <si>
+    <t>Round 2 - Match 40</t>
+  </si>
+  <si>
+    <t>Round 2 - Match 53</t>
+  </si>
+  <si>
+    <t>Round 2 - Match 41</t>
+  </si>
+  <si>
+    <t>Round 2 - Match 54</t>
+  </si>
+  <si>
+    <t>Round 2 - Match 42</t>
+  </si>
+  <si>
+    <t>Round 2 - Match 55</t>
+  </si>
+  <si>
+    <t>Round 2 - Match 43</t>
+  </si>
+  <si>
+    <t>Round 2 - Match 56</t>
   </si>
   <si>
     <t>Round 2 - Match 44</t>
   </si>
   <si>
-    <t>Round 2 - Match 29</t>
+    <t>Round 2 - Match 57</t>
   </si>
   <si>
     <t>Round 2 - Match 45</t>
   </si>
   <si>
-    <t>Round 2 - Match 30</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 46</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 31</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 47</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 32</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 48</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 33</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 49</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 34</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 50</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 35</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 51</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 36</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 52</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 37</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 53</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 38</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 54</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 39</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 55</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 40</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 56</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 41</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 57</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 42</t>
-  </si>
-  <si>
     <t>Round 2 - Match 58</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 43</t>
   </si>
   <si>
     <t>Round 2 - Match 59</t>
@@ -2836,35 +2836,29 @@
       <c r="J1" s="11"/>
       <c r="K1" s="11"/>
     </row>
+    <row r="5">
+      <c r="C5" s="16" t="s">
+        <v>68</v>
+      </c>
+    </row>
     <row r="6">
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16" t="s">
-        <v>68</v>
+      <c r="D6" s="14"/>
+      <c r="E6" s="13">
+        <v>9</v>
       </c>
     </row>
     <row r="7">
-      <c r="F7" s="14"/>
-      <c r="G7" s="12"/>
-    </row>
-    <row r="8">
-      <c r="G8" s="13">
-        <v>36</v>
-      </c>
+      <c r="C7" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="D7" s="15"/>
+      <c r="E7" s="12"/>
     </row>
     <row r="9">
-      <c r="G9" s="12"/>
       <c r="H9" s="14"/>
       <c r="I9" s="12"/>
     </row>
     <row r="10">
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="F10" s="15"/>
-      <c r="G10" s="12"/>
       <c r="I10" s="12"/>
     </row>
     <row r="11">
@@ -2897,7 +2891,7 @@
     </row>
     <row r="16">
       <c r="G16" s="13">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H16" s="15"/>
       <c r="I16" s="12"/>
@@ -2913,7 +2907,7 @@
     <row r="18">
       <c r="D18" s="14"/>
       <c r="E18" s="13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F18" s="15"/>
       <c r="G18" s="12"/>
@@ -2950,7 +2944,7 @@
     </row>
     <row r="24">
       <c r="G24" s="13">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K24" s="12"/>
     </row>
@@ -2966,7 +2960,7 @@
     <row r="26">
       <c r="D26" s="14"/>
       <c r="E26" s="13">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F26" s="15"/>
       <c r="G26" s="12"/>
@@ -3007,7 +3001,7 @@
     </row>
     <row r="32">
       <c r="G32" s="13">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H32" s="15"/>
       <c r="I32" s="12"/>
@@ -3021,7 +3015,7 @@
     <row r="34">
       <c r="D34" s="14"/>
       <c r="E34" s="13">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F34" s="15"/>
       <c r="G34" s="12"/>
@@ -3085,7 +3079,7 @@
     </row>
     <row r="8">
       <c r="G8" s="13">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9">
@@ -3099,7 +3093,7 @@
     <row r="10">
       <c r="D10" s="14"/>
       <c r="E10" s="13">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F10" s="15"/>
       <c r="G10" s="12"/>
@@ -3140,7 +3134,7 @@
     </row>
     <row r="16">
       <c r="G16" s="13">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H16" s="15"/>
       <c r="I16" s="12"/>
@@ -3156,7 +3150,7 @@
     <row r="18">
       <c r="D18" s="14"/>
       <c r="E18" s="13">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F18" s="15"/>
       <c r="G18" s="12"/>
@@ -3193,7 +3187,7 @@
     </row>
     <row r="24">
       <c r="G24" s="13">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K24" s="12"/>
     </row>
@@ -3209,7 +3203,7 @@
     <row r="26">
       <c r="D26" s="14"/>
       <c r="E26" s="13">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F26" s="15"/>
       <c r="G26" s="12"/>
@@ -3250,7 +3244,7 @@
     </row>
     <row r="32">
       <c r="G32" s="13">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H32" s="15"/>
       <c r="I32" s="12"/>
@@ -3264,7 +3258,7 @@
     <row r="34">
       <c r="D34" s="14"/>
       <c r="E34" s="13">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F34" s="15"/>
       <c r="G34" s="12"/>
@@ -3315,35 +3309,29 @@
       <c r="J1" s="11"/>
       <c r="K1" s="11"/>
     </row>
+    <row r="5">
+      <c r="C5" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
     <row r="6">
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16" t="s">
-        <v>104</v>
+      <c r="D6" s="14"/>
+      <c r="E6" s="13">
+        <v>17</v>
       </c>
     </row>
     <row r="7">
-      <c r="F7" s="14"/>
-      <c r="G7" s="12"/>
-    </row>
-    <row r="8">
-      <c r="G8" s="13">
-        <v>44</v>
-      </c>
+      <c r="C7" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="D7" s="15"/>
+      <c r="E7" s="12"/>
     </row>
     <row r="9">
-      <c r="G9" s="12"/>
       <c r="H9" s="14"/>
       <c r="I9" s="12"/>
     </row>
     <row r="10">
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16" t="s">
-        <v>106</v>
-      </c>
-      <c r="F10" s="15"/>
-      <c r="G10" s="12"/>
       <c r="I10" s="12"/>
     </row>
     <row r="11">
@@ -3376,7 +3364,7 @@
     </row>
     <row r="16">
       <c r="G16" s="13">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H16" s="15"/>
       <c r="I16" s="12"/>
@@ -3392,7 +3380,7 @@
     <row r="18">
       <c r="D18" s="14"/>
       <c r="E18" s="13">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F18" s="15"/>
       <c r="G18" s="12"/>
@@ -3429,7 +3417,7 @@
     </row>
     <row r="24">
       <c r="G24" s="13">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K24" s="12"/>
     </row>
@@ -3445,7 +3433,7 @@
     <row r="26">
       <c r="D26" s="14"/>
       <c r="E26" s="13">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F26" s="15"/>
       <c r="G26" s="12"/>
@@ -3486,7 +3474,7 @@
     </row>
     <row r="32">
       <c r="G32" s="13">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H32" s="15"/>
       <c r="I32" s="12"/>
@@ -3500,7 +3488,7 @@
     <row r="34">
       <c r="D34" s="14"/>
       <c r="E34" s="13">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F34" s="15"/>
       <c r="G34" s="12"/>
@@ -3564,7 +3552,7 @@
     </row>
     <row r="8">
       <c r="G8" s="13">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9">
@@ -3578,7 +3566,7 @@
     <row r="10">
       <c r="D10" s="14"/>
       <c r="E10" s="13">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F10" s="15"/>
       <c r="G10" s="12"/>
@@ -3619,7 +3607,7 @@
     </row>
     <row r="16">
       <c r="G16" s="13">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H16" s="15"/>
       <c r="I16" s="12"/>
@@ -3635,7 +3623,7 @@
     <row r="18">
       <c r="D18" s="14"/>
       <c r="E18" s="13">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F18" s="15"/>
       <c r="G18" s="12"/>
@@ -3672,7 +3660,7 @@
     </row>
     <row r="24">
       <c r="G24" s="13">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K24" s="12"/>
     </row>
@@ -3688,7 +3676,7 @@
     <row r="26">
       <c r="D26" s="14"/>
       <c r="E26" s="13">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F26" s="15"/>
       <c r="G26" s="12"/>
@@ -3729,7 +3717,7 @@
     </row>
     <row r="32">
       <c r="G32" s="13">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H32" s="15"/>
       <c r="I32" s="12"/>
@@ -3743,7 +3731,7 @@
     <row r="34">
       <c r="D34" s="14"/>
       <c r="E34" s="13">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F34" s="15"/>
       <c r="G34" s="12"/>
@@ -3794,35 +3782,29 @@
       <c r="J1" s="11"/>
       <c r="K1" s="11"/>
     </row>
+    <row r="5">
+      <c r="C5" s="16" t="s">
+        <v>164</v>
+      </c>
+    </row>
     <row r="6">
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16" t="s">
-        <v>164</v>
+      <c r="D6" s="14"/>
+      <c r="E6" s="13">
+        <v>25</v>
       </c>
     </row>
     <row r="7">
-      <c r="F7" s="14"/>
-      <c r="G7" s="12"/>
-    </row>
-    <row r="8">
-      <c r="G8" s="13">
-        <v>52</v>
-      </c>
+      <c r="C7" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="D7" s="15"/>
+      <c r="E7" s="12"/>
     </row>
     <row r="9">
-      <c r="G9" s="12"/>
       <c r="H9" s="14"/>
       <c r="I9" s="12"/>
     </row>
     <row r="10">
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="F10" s="15"/>
-      <c r="G10" s="12"/>
       <c r="I10" s="12"/>
     </row>
     <row r="11">
@@ -3871,7 +3853,7 @@
     <row r="18">
       <c r="D18" s="14"/>
       <c r="E18" s="13">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F18" s="15"/>
       <c r="G18" s="12"/>
@@ -3924,7 +3906,7 @@
     <row r="26">
       <c r="D26" s="14"/>
       <c r="E26" s="13">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F26" s="15"/>
       <c r="G26" s="12"/>
@@ -3979,7 +3961,7 @@
     <row r="34">
       <c r="D34" s="14"/>
       <c r="E34" s="13">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F34" s="15"/>
       <c r="G34" s="12"/>
@@ -4057,7 +4039,7 @@
     <row r="10">
       <c r="D10" s="14"/>
       <c r="E10" s="13">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F10" s="15"/>
       <c r="G10" s="12"/>
@@ -4114,7 +4096,7 @@
     <row r="18">
       <c r="D18" s="14"/>
       <c r="E18" s="13">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F18" s="15"/>
       <c r="G18" s="12"/>
@@ -4167,7 +4149,7 @@
     <row r="26">
       <c r="D26" s="14"/>
       <c r="E26" s="13">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F26" s="15"/>
       <c r="G26" s="12"/>
@@ -4222,7 +4204,7 @@
     <row r="34">
       <c r="D34" s="14"/>
       <c r="E34" s="13">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F34" s="15"/>
       <c r="G34" s="12"/>
@@ -5395,7 +5377,7 @@
     </row>
     <row r="4">
       <c r="A4" s="19" t="str">
-        <f>'data'!$B$35</f>
+        <f>'data'!$B$33</f>
       </c>
       <c r="B4" s="22"/>
       <c r="C4" s="22"/>
@@ -5403,10 +5385,10 @@
       <c r="E4" s="22"/>
       <c r="F4" s="22"/>
       <c r="G4" s="19" t="str">
-        <f>'data'!$B$6</f>
+        <f>'data'!$B$32</f>
       </c>
       <c r="I4" s="19" t="str">
-        <f>'data'!$B$52</f>
+        <f>'data'!$B$49</f>
       </c>
       <c r="J4" s="22"/>
       <c r="K4" s="22"/>
@@ -5414,7 +5396,7 @@
       <c r="M4" s="22"/>
       <c r="N4" s="22"/>
       <c r="O4" s="19" t="str">
-        <f>'data'!$B$51</f>
+        <f>'data'!$B$48</f>
       </c>
     </row>
     <row r="6">
@@ -5479,7 +5461,7 @@
     </row>
     <row r="12">
       <c r="A12" s="19" t="str">
-        <f>'data'!$B$38</f>
+        <f>'data'!$B$35</f>
       </c>
       <c r="B12" s="22"/>
       <c r="C12" s="22"/>
@@ -5487,10 +5469,10 @@
       <c r="E12" s="22"/>
       <c r="F12" s="22"/>
       <c r="G12" s="19" t="str">
-        <f>'data'!$B$37</f>
+        <f>'data'!$B$6</f>
       </c>
       <c r="I12" s="19" t="str">
-        <f>'data'!$B$55</f>
+        <f>'data'!$B$52</f>
       </c>
       <c r="J12" s="22"/>
       <c r="K12" s="22"/>
@@ -5498,7 +5480,7 @@
       <c r="M12" s="22"/>
       <c r="N12" s="22"/>
       <c r="O12" s="19" t="str">
-        <f>'data'!$B$54</f>
+        <f>'data'!$B$51</f>
       </c>
     </row>
     <row r="14">
@@ -5563,7 +5545,7 @@
     </row>
     <row r="20">
       <c r="A20" s="19" t="str">
-        <f>'data'!$B$41</f>
+        <f>'data'!$B$38</f>
       </c>
       <c r="B20" s="22"/>
       <c r="C20" s="22"/>
@@ -5571,10 +5553,10 @@
       <c r="E20" s="22"/>
       <c r="F20" s="22"/>
       <c r="G20" s="19" t="str">
-        <f>'data'!$B$40</f>
+        <f>'data'!$B$37</f>
       </c>
       <c r="I20" s="19" t="str">
-        <f>'data'!$B$58</f>
+        <f>'data'!$B$55</f>
       </c>
       <c r="J20" s="22"/>
       <c r="K20" s="22"/>
@@ -5582,7 +5564,7 @@
       <c r="M20" s="22"/>
       <c r="N20" s="22"/>
       <c r="O20" s="19" t="str">
-        <f>'data'!$B$57</f>
+        <f>'data'!$B$54</f>
       </c>
     </row>
     <row r="22">
@@ -5647,7 +5629,7 @@
     </row>
     <row r="28">
       <c r="A28" s="19" t="str">
-        <f>'data'!$B$18</f>
+        <f>'data'!$B$41</f>
       </c>
       <c r="B28" s="22"/>
       <c r="C28" s="22"/>
@@ -5655,10 +5637,10 @@
       <c r="E28" s="22"/>
       <c r="F28" s="22"/>
       <c r="G28" s="19" t="str">
-        <f>'data'!$B$17</f>
+        <f>'data'!$B$40</f>
       </c>
       <c r="I28" s="19" t="str">
-        <f>'data'!$B$61</f>
+        <f>'data'!$B$58</f>
       </c>
       <c r="J28" s="22"/>
       <c r="K28" s="22"/>
@@ -5666,7 +5648,7 @@
       <c r="M28" s="22"/>
       <c r="N28" s="22"/>
       <c r="O28" s="19" t="str">
-        <f>'data'!$B$60</f>
+        <f>'data'!$B$57</f>
       </c>
     </row>
     <row r="30">
@@ -5731,7 +5713,7 @@
     </row>
     <row r="36">
       <c r="A36" s="19" t="str">
-        <f>'data'!$B$21</f>
+        <f>'data'!$B$43</f>
       </c>
       <c r="B36" s="22"/>
       <c r="C36" s="22"/>
@@ -5739,10 +5721,10 @@
       <c r="E36" s="22"/>
       <c r="F36" s="22"/>
       <c r="G36" s="19" t="str">
-        <f>'data'!$B$20</f>
+        <f>'data'!$B$42</f>
       </c>
       <c r="I36" s="19" t="str">
-        <f>'data'!$B$64</f>
+        <f>'data'!$B$61</f>
       </c>
       <c r="J36" s="22"/>
       <c r="K36" s="22"/>
@@ -5750,7 +5732,7 @@
       <c r="M36" s="22"/>
       <c r="N36" s="22"/>
       <c r="O36" s="19" t="str">
-        <f>'data'!$B$63</f>
+        <f>'data'!$B$60</f>
       </c>
     </row>
     <row r="38">
@@ -5815,7 +5797,7 @@
     </row>
     <row r="44">
       <c r="A44" s="19" t="str">
-        <f>'data'!$B$24</f>
+        <f>'data'!$B$18</f>
       </c>
       <c r="B44" s="22"/>
       <c r="C44" s="22"/>
@@ -5823,10 +5805,10 @@
       <c r="E44" s="22"/>
       <c r="F44" s="22"/>
       <c r="G44" s="19" t="str">
-        <f>'data'!$B$23</f>
+        <f>'data'!$B$17</f>
       </c>
       <c r="I44" s="19" t="str">
-        <f>'data'!$B$67</f>
+        <f>'data'!$B$64</f>
       </c>
       <c r="J44" s="22"/>
       <c r="K44" s="22"/>
@@ -5834,7 +5816,7 @@
       <c r="M44" s="22"/>
       <c r="N44" s="22"/>
       <c r="O44" s="19" t="str">
-        <f>'data'!$B$66</f>
+        <f>'data'!$B$63</f>
       </c>
     </row>
     <row r="46">
@@ -5899,7 +5881,7 @@
     </row>
     <row r="52">
       <c r="A52" s="19" t="str">
-        <f>'data'!$B$29</f>
+        <f>'data'!$B$21</f>
       </c>
       <c r="B52" s="22"/>
       <c r="C52" s="22"/>
@@ -5907,10 +5889,10 @@
       <c r="E52" s="22"/>
       <c r="F52" s="22"/>
       <c r="G52" s="19" t="str">
-        <f>'data'!$B$28</f>
+        <f>'data'!$B$20</f>
       </c>
       <c r="I52" s="19" t="str">
-        <f>'data'!$B$74</f>
+        <f>'data'!$B$67</f>
       </c>
       <c r="J52" s="22"/>
       <c r="K52" s="22"/>
@@ -5918,7 +5900,7 @@
       <c r="M52" s="22"/>
       <c r="N52" s="22"/>
       <c r="O52" s="19" t="str">
-        <f>'data'!$B$69</f>
+        <f>'data'!$B$66</f>
       </c>
     </row>
     <row r="54">
@@ -5983,7 +5965,7 @@
     </row>
     <row r="60">
       <c r="A60" s="19" t="str">
-        <f>'data'!$B$32</f>
+        <f>'data'!$B$24</f>
       </c>
       <c r="B60" s="22"/>
       <c r="C60" s="22"/>
@@ -5991,10 +5973,10 @@
       <c r="E60" s="22"/>
       <c r="F60" s="22"/>
       <c r="G60" s="19" t="str">
-        <f>'data'!$B$31</f>
+        <f>'data'!$B$23</f>
       </c>
       <c r="I60" s="19" t="str">
-        <f>'data'!$B$75</f>
+        <f>'data'!$B$74</f>
       </c>
       <c r="J60" s="22"/>
       <c r="K60" s="22"/>
@@ -6002,7 +5984,7 @@
       <c r="M60" s="22"/>
       <c r="N60" s="22"/>
       <c r="O60" s="19" t="str">
-        <f>'data'!$B$74</f>
+        <f>'data'!$B$69</f>
       </c>
     </row>
     <row r="62">
@@ -6067,7 +6049,7 @@
     </row>
     <row r="68">
       <c r="A68" s="19" t="str">
-        <f>'data'!$B$35</f>
+        <f>'data'!$B$26</f>
       </c>
       <c r="B68" s="22"/>
       <c r="C68" s="22"/>
@@ -6075,10 +6057,10 @@
       <c r="E68" s="22"/>
       <c r="F68" s="22"/>
       <c r="G68" s="19" t="str">
-        <f>'data'!$B$34</f>
+        <f>'data'!$B$25</f>
       </c>
       <c r="I68" s="19" t="str">
-        <f>'data'!$B$78</f>
+        <f>'data'!$B$72</f>
       </c>
       <c r="J68" s="22"/>
       <c r="K68" s="22"/>
@@ -6086,7 +6068,7 @@
       <c r="M68" s="22"/>
       <c r="N68" s="22"/>
       <c r="O68" s="19" t="str">
-        <f>'data'!$B$77</f>
+        <f>'data'!$B$88</f>
       </c>
     </row>
     <row r="70">
@@ -6151,7 +6133,7 @@
     </row>
     <row r="76">
       <c r="A76" s="19" t="str">
-        <f>'data'!$B$38</f>
+        <f>'data'!$B$29</f>
       </c>
       <c r="B76" s="22"/>
       <c r="C76" s="22"/>
@@ -6159,10 +6141,10 @@
       <c r="E76" s="22"/>
       <c r="F76" s="22"/>
       <c r="G76" s="19" t="str">
-        <f>'data'!$B$37</f>
+        <f>'data'!$B$28</f>
       </c>
       <c r="I76" s="19" t="str">
-        <f>'data'!$B$81</f>
+        <f>'data'!$B$75</f>
       </c>
       <c r="J76" s="22"/>
       <c r="K76" s="22"/>
@@ -6170,7 +6152,7 @@
       <c r="M76" s="22"/>
       <c r="N76" s="22"/>
       <c r="O76" s="19" t="str">
-        <f>'data'!$B$80</f>
+        <f>'data'!$B$74</f>
       </c>
     </row>
     <row r="78">
@@ -6235,7 +6217,7 @@
     </row>
     <row r="84">
       <c r="A84" s="19" t="str">
-        <f>'data'!$B$41</f>
+        <f>'data'!$B$32</f>
       </c>
       <c r="B84" s="22"/>
       <c r="C84" s="22"/>
@@ -6243,10 +6225,10 @@
       <c r="E84" s="22"/>
       <c r="F84" s="22"/>
       <c r="G84" s="19" t="str">
-        <f>'data'!$B$40</f>
+        <f>'data'!$B$31</f>
       </c>
       <c r="I84" s="19" t="str">
-        <f>'data'!$B$84</f>
+        <f>'data'!$B$78</f>
       </c>
       <c r="J84" s="22"/>
       <c r="K84" s="22"/>
@@ -6254,7 +6236,7 @@
       <c r="M84" s="22"/>
       <c r="N84" s="22"/>
       <c r="O84" s="19" t="str">
-        <f>'data'!$B$83</f>
+        <f>'data'!$B$77</f>
       </c>
     </row>
     <row r="86">
@@ -6319,7 +6301,7 @@
     </row>
     <row r="92">
       <c r="A92" s="19" t="str">
-        <f>'data'!$B$44</f>
+        <f>'data'!$B$35</f>
       </c>
       <c r="B92" s="22"/>
       <c r="C92" s="22"/>
@@ -6327,10 +6309,10 @@
       <c r="E92" s="22"/>
       <c r="F92" s="22"/>
       <c r="G92" s="19" t="str">
-        <f>'data'!$B$43</f>
+        <f>'data'!$B$34</f>
       </c>
       <c r="I92" s="19" t="str">
-        <f>'data'!$B$87</f>
+        <f>'data'!$B$81</f>
       </c>
       <c r="J92" s="22"/>
       <c r="K92" s="22"/>
@@ -6338,7 +6320,7 @@
       <c r="M92" s="22"/>
       <c r="N92" s="22"/>
       <c r="O92" s="19" t="str">
-        <f>'data'!$B$86</f>
+        <f>'data'!$B$80</f>
       </c>
     </row>
     <row r="94">
@@ -6403,7 +6385,7 @@
     </row>
     <row r="100">
       <c r="A100" s="19" t="str">
-        <f>'data'!$B$47</f>
+        <f>'data'!$B$38</f>
       </c>
       <c r="B100" s="22"/>
       <c r="C100" s="22"/>
@@ -6411,10 +6393,10 @@
       <c r="E100" s="22"/>
       <c r="F100" s="22"/>
       <c r="G100" s="19" t="str">
-        <f>'data'!$B$46</f>
+        <f>'data'!$B$37</f>
       </c>
       <c r="I100" s="19" t="str">
-        <f>'data'!$B$90</f>
+        <f>'data'!$B$84</f>
       </c>
       <c r="J100" s="22"/>
       <c r="K100" s="22"/>
@@ -6422,7 +6404,7 @@
       <c r="M100" s="22"/>
       <c r="N100" s="22"/>
       <c r="O100" s="19" t="str">
-        <f>'data'!$B$89</f>
+        <f>'data'!$B$83</f>
       </c>
     </row>
     <row r="102">
@@ -6446,8 +6428,17 @@
       <c r="O103" s="23"/>
     </row>
     <row r="106">
+      <c r="A106" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="B106" s="11"/>
+      <c r="C106" s="11"/>
+      <c r="D106" s="11"/>
+      <c r="E106" s="11"/>
+      <c r="F106" s="11"/>
+      <c r="G106" s="11"/>
       <c r="I106" s="11" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="J106" s="11"/>
       <c r="K106" s="11"/>
@@ -6457,6 +6448,15 @@
       <c r="O106" s="11"/>
     </row>
     <row r="107">
+      <c r="A107" s="21" t="s">
+        <v>209</v>
+      </c>
+      <c r="D107" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="G107" s="20" t="s">
+        <v>211</v>
+      </c>
       <c r="I107" s="21" t="s">
         <v>209</v>
       </c>
@@ -6468,8 +6468,19 @@
       </c>
     </row>
     <row r="108">
+      <c r="A108" s="19" t="str">
+        <f>'data'!$B$41</f>
+      </c>
+      <c r="B108" s="22"/>
+      <c r="C108" s="22"/>
+      <c r="D108" s="22"/>
+      <c r="E108" s="22"/>
+      <c r="F108" s="22"/>
+      <c r="G108" s="19" t="str">
+        <f>'data'!$B$40</f>
+      </c>
       <c r="I108" s="19" t="str">
-        <f>'data'!$B$93</f>
+        <f>'data'!$B$87</f>
       </c>
       <c r="J108" s="22"/>
       <c r="K108" s="22"/>
@@ -6477,192 +6488,200 @@
       <c r="M108" s="22"/>
       <c r="N108" s="22"/>
       <c r="O108" s="19" t="str">
-        <f>'data'!$B$92</f>
+        <f>'data'!$B$86</f>
       </c>
     </row>
     <row r="110">
+      <c r="F110" t="s">
+        <v>212</v>
+      </c>
+      <c r="G110" s="23"/>
       <c r="N110" t="s">
         <v>212</v>
       </c>
       <c r="O110" s="23"/>
     </row>
     <row r="111">
+      <c r="F111" t="s">
+        <v>213</v>
+      </c>
+      <c r="G111" s="23"/>
       <c r="N111" t="s">
         <v>213</v>
       </c>
       <c r="O111" s="23"/>
     </row>
+    <row r="114">
+      <c r="A114" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="B114" s="11"/>
+      <c r="C114" s="11"/>
+      <c r="D114" s="11"/>
+      <c r="E114" s="11"/>
+      <c r="F114" s="11"/>
+      <c r="G114" s="11"/>
+      <c r="I114" s="11" t="s">
+        <v>242</v>
+      </c>
+      <c r="J114" s="11"/>
+      <c r="K114" s="11"/>
+      <c r="L114" s="11"/>
+      <c r="M114" s="11"/>
+      <c r="N114" s="11"/>
+      <c r="O114" s="11"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="21" t="s">
+        <v>209</v>
+      </c>
+      <c r="D115" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="G115" s="20" t="s">
+        <v>211</v>
+      </c>
+      <c r="I115" s="21" t="s">
+        <v>209</v>
+      </c>
+      <c r="L115" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="O115" s="20" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="19" t="str">
+        <f>'data'!$B$44</f>
+      </c>
+      <c r="B116" s="22"/>
+      <c r="C116" s="22"/>
+      <c r="D116" s="22"/>
+      <c r="E116" s="22"/>
+      <c r="F116" s="22"/>
+      <c r="G116" s="19" t="str">
+        <f>'data'!$B$43</f>
+      </c>
+      <c r="I116" s="19" t="str">
+        <f>'data'!$B$90</f>
+      </c>
+      <c r="J116" s="22"/>
+      <c r="K116" s="22"/>
+      <c r="L116" s="22"/>
+      <c r="M116" s="22"/>
+      <c r="N116" s="22"/>
+      <c r="O116" s="19" t="str">
+        <f>'data'!$B$89</f>
+      </c>
+    </row>
+    <row r="118">
+      <c r="F118" t="s">
+        <v>212</v>
+      </c>
+      <c r="G118" s="23"/>
+      <c r="N118" t="s">
+        <v>212</v>
+      </c>
+      <c r="O118" s="23"/>
+    </row>
     <row r="119">
-      <c r="A119" s="11" t="s">
-        <v>240</v>
-      </c>
-      <c r="B119" s="11"/>
-      <c r="C119" s="11"/>
-      <c r="D119" s="11"/>
-      <c r="E119" s="11"/>
-      <c r="F119" s="11"/>
-      <c r="G119" s="11"/>
-      <c r="I119" s="11" t="s">
-        <v>241</v>
-      </c>
-      <c r="J119" s="11"/>
-      <c r="K119" s="11"/>
-      <c r="L119" s="11"/>
-      <c r="M119" s="11"/>
-      <c r="N119" s="11"/>
-      <c r="O119" s="11"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="21" t="s">
+      <c r="F119" t="s">
+        <v>213</v>
+      </c>
+      <c r="G119" s="23"/>
+      <c r="N119" t="s">
+        <v>213</v>
+      </c>
+      <c r="O119" s="23"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="B122" s="11"/>
+      <c r="C122" s="11"/>
+      <c r="D122" s="11"/>
+      <c r="E122" s="11"/>
+      <c r="F122" s="11"/>
+      <c r="G122" s="11"/>
+      <c r="I122" s="11" t="s">
+        <v>244</v>
+      </c>
+      <c r="J122" s="11"/>
+      <c r="K122" s="11"/>
+      <c r="L122" s="11"/>
+      <c r="M122" s="11"/>
+      <c r="N122" s="11"/>
+      <c r="O122" s="11"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="21" t="s">
         <v>209</v>
       </c>
-      <c r="D120" s="19" t="s">
+      <c r="D123" s="19" t="s">
         <v>210</v>
       </c>
-      <c r="G120" s="20" t="s">
+      <c r="G123" s="20" t="s">
         <v>211</v>
       </c>
-      <c r="I120" s="21" t="s">
+      <c r="I123" s="21" t="s">
         <v>209</v>
       </c>
-      <c r="L120" s="19" t="s">
+      <c r="L123" s="19" t="s">
         <v>210</v>
       </c>
-      <c r="O120" s="20" t="s">
+      <c r="O123" s="20" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="19" t="str">
-        <f>'data'!$B$33</f>
-      </c>
-      <c r="B121" s="22"/>
-      <c r="C121" s="22"/>
-      <c r="D121" s="22"/>
-      <c r="E121" s="22"/>
-      <c r="F121" s="22"/>
-      <c r="G121" s="19" t="str">
-        <f>'data'!$B$32</f>
-      </c>
-      <c r="I121" s="19" t="str">
-        <f>'data'!$B$49</f>
-      </c>
-      <c r="J121" s="22"/>
-      <c r="K121" s="22"/>
-      <c r="L121" s="22"/>
-      <c r="M121" s="22"/>
-      <c r="N121" s="22"/>
-      <c r="O121" s="19" t="str">
-        <f>'data'!$B$48</f>
-      </c>
-    </row>
-    <row r="123">
-      <c r="F123" t="s">
+    <row r="124">
+      <c r="A124" s="19" t="str">
+        <f>'data'!$B$47</f>
+      </c>
+      <c r="B124" s="22"/>
+      <c r="C124" s="22"/>
+      <c r="D124" s="22"/>
+      <c r="E124" s="22"/>
+      <c r="F124" s="22"/>
+      <c r="G124" s="19" t="str">
+        <f>'data'!$B$46</f>
+      </c>
+      <c r="I124" s="19" t="str">
+        <f>'data'!$B$93</f>
+      </c>
+      <c r="J124" s="22"/>
+      <c r="K124" s="22"/>
+      <c r="L124" s="22"/>
+      <c r="M124" s="22"/>
+      <c r="N124" s="22"/>
+      <c r="O124" s="19" t="str">
+        <f>'data'!$B$92</f>
+      </c>
+    </row>
+    <row r="126">
+      <c r="F126" t="s">
         <v>212</v>
       </c>
-      <c r="G123" s="23"/>
-      <c r="N123" t="s">
+      <c r="G126" s="23"/>
+      <c r="N126" t="s">
         <v>212</v>
       </c>
-      <c r="O123" s="23"/>
-    </row>
-    <row r="124">
-      <c r="F124" t="s">
+      <c r="O126" s="23"/>
+    </row>
+    <row r="127">
+      <c r="F127" t="s">
         <v>213</v>
       </c>
-      <c r="G124" s="23"/>
-      <c r="N124" t="s">
+      <c r="G127" s="23"/>
+      <c r="N127" t="s">
         <v>213</v>
       </c>
-      <c r="O124" s="23"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="11" t="s">
-        <v>242</v>
-      </c>
-      <c r="B127" s="11"/>
-      <c r="C127" s="11"/>
-      <c r="D127" s="11"/>
-      <c r="E127" s="11"/>
-      <c r="F127" s="11"/>
-      <c r="G127" s="11"/>
-      <c r="I127" s="11" t="s">
-        <v>243</v>
-      </c>
-      <c r="J127" s="11"/>
-      <c r="K127" s="11"/>
-      <c r="L127" s="11"/>
-      <c r="M127" s="11"/>
-      <c r="N127" s="11"/>
-      <c r="O127" s="11"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="21" t="s">
-        <v>209</v>
-      </c>
-      <c r="D128" s="19" t="s">
-        <v>210</v>
-      </c>
-      <c r="G128" s="20" t="s">
-        <v>211</v>
-      </c>
-      <c r="I128" s="21" t="s">
-        <v>209</v>
-      </c>
-      <c r="L128" s="19" t="s">
-        <v>210</v>
-      </c>
-      <c r="O128" s="20" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="19" t="str">
-        <f>CONCATENATE("M 1 ",G6)</f>
-      </c>
-      <c r="B129" s="22"/>
-      <c r="C129" s="22"/>
-      <c r="D129" s="22"/>
-      <c r="E129" s="22"/>
-      <c r="F129" s="22"/>
-      <c r="G129" s="19" t="str">
-        <f>'data'!$B$34</f>
-      </c>
-      <c r="I129" s="19" t="str">
-        <f>CONCATENATE("M 14 ",O6)</f>
-      </c>
-      <c r="J129" s="22"/>
-      <c r="K129" s="22"/>
-      <c r="L129" s="22"/>
-      <c r="M129" s="22"/>
-      <c r="N129" s="22"/>
-      <c r="O129" s="19" t="str">
-        <f>'data'!$B$50</f>
-      </c>
-    </row>
-    <row r="131">
-      <c r="F131" t="s">
-        <v>212</v>
-      </c>
-      <c r="G131" s="23"/>
-      <c r="N131" t="s">
-        <v>212</v>
-      </c>
-      <c r="O131" s="23"/>
-    </row>
-    <row r="132">
-      <c r="F132" t="s">
-        <v>213</v>
-      </c>
-      <c r="G132" s="23"/>
-      <c r="N132" t="s">
-        <v>213</v>
-      </c>
-      <c r="O132" s="23"/>
+      <c r="O127" s="23"/>
     </row>
     <row r="135">
       <c r="A135" s="11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B135" s="11"/>
       <c r="C135" s="11"/>
@@ -6671,7 +6690,7 @@
       <c r="F135" s="11"/>
       <c r="G135" s="11"/>
       <c r="I135" s="11" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="J135" s="11"/>
       <c r="K135" s="11"/>
@@ -6710,10 +6729,10 @@
       <c r="E137" s="22"/>
       <c r="F137" s="22"/>
       <c r="G137" s="19" t="str">
-        <f>'data'!$B$36</f>
+        <f>'data'!$B$34</f>
       </c>
       <c r="I137" s="19" t="str">
-        <f>CONCATENATE("M 15 ",O14)</f>
+        <f>CONCATENATE("M 18 ",O14)</f>
       </c>
       <c r="J137" s="22"/>
       <c r="K137" s="22"/>
@@ -6721,7 +6740,7 @@
       <c r="M137" s="22"/>
       <c r="N137" s="22"/>
       <c r="O137" s="19" t="str">
-        <f>'data'!$B$53</f>
+        <f>'data'!$B$50</f>
       </c>
     </row>
     <row r="139">
@@ -6746,7 +6765,7 @@
     </row>
     <row r="143">
       <c r="A143" s="11" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B143" s="11"/>
       <c r="C143" s="11"/>
@@ -6755,7 +6774,7 @@
       <c r="F143" s="11"/>
       <c r="G143" s="11"/>
       <c r="I143" s="11" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="J143" s="11"/>
       <c r="K143" s="11"/>
@@ -6794,10 +6813,10 @@
       <c r="E145" s="22"/>
       <c r="F145" s="22"/>
       <c r="G145" s="19" t="str">
-        <f>'data'!$B$39</f>
+        <f>'data'!$B$36</f>
       </c>
       <c r="I145" s="19" t="str">
-        <f>CONCATENATE("M 16 ",O22)</f>
+        <f>CONCATENATE("M 19 ",O22)</f>
       </c>
       <c r="J145" s="22"/>
       <c r="K145" s="22"/>
@@ -6805,7 +6824,7 @@
       <c r="M145" s="22"/>
       <c r="N145" s="22"/>
       <c r="O145" s="19" t="str">
-        <f>'data'!$B$56</f>
+        <f>'data'!$B$53</f>
       </c>
     </row>
     <row r="147">
@@ -6830,7 +6849,7 @@
     </row>
     <row r="151">
       <c r="A151" s="11" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B151" s="11"/>
       <c r="C151" s="11"/>
@@ -6839,7 +6858,7 @@
       <c r="F151" s="11"/>
       <c r="G151" s="11"/>
       <c r="I151" s="11" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="J151" s="11"/>
       <c r="K151" s="11"/>
@@ -6870,7 +6889,7 @@
     </row>
     <row r="153">
       <c r="A153" s="19" t="str">
-        <f>'data'!$B$43</f>
+        <f>CONCATENATE("M 4 ",G30)</f>
       </c>
       <c r="B153" s="22"/>
       <c r="C153" s="22"/>
@@ -6878,10 +6897,10 @@
       <c r="E153" s="22"/>
       <c r="F153" s="22"/>
       <c r="G153" s="19" t="str">
-        <f>'data'!$B$42</f>
+        <f>'data'!$B$39</f>
       </c>
       <c r="I153" s="19" t="str">
-        <f>CONCATENATE("M 17 ",O30)</f>
+        <f>CONCATENATE("M 20 ",O30)</f>
       </c>
       <c r="J153" s="22"/>
       <c r="K153" s="22"/>
@@ -6889,7 +6908,7 @@
       <c r="M153" s="22"/>
       <c r="N153" s="22"/>
       <c r="O153" s="19" t="str">
-        <f>'data'!$B$81</f>
+        <f>'data'!$B$56</f>
       </c>
     </row>
     <row r="155">
@@ -6914,7 +6933,7 @@
     </row>
     <row r="159">
       <c r="A159" s="11" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B159" s="11"/>
       <c r="C159" s="11"/>
@@ -6923,7 +6942,7 @@
       <c r="F159" s="11"/>
       <c r="G159" s="11"/>
       <c r="I159" s="11" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="J159" s="11"/>
       <c r="K159" s="11"/>
@@ -6954,7 +6973,7 @@
     </row>
     <row r="161">
       <c r="A161" s="19" t="str">
-        <f>CONCATENATE("M 4 ",G30)</f>
+        <f>CONCATENATE("M 6 ",G46)</f>
       </c>
       <c r="B161" s="22"/>
       <c r="C161" s="22"/>
@@ -6965,7 +6984,7 @@
         <f>'data'!$B$16</f>
       </c>
       <c r="I161" s="19" t="str">
-        <f>CONCATENATE("M 18 ",O38)</f>
+        <f>CONCATENATE("M 21 ",O38)</f>
       </c>
       <c r="J161" s="22"/>
       <c r="K161" s="22"/>
@@ -6973,7 +6992,7 @@
       <c r="M161" s="22"/>
       <c r="N161" s="22"/>
       <c r="O161" s="19" t="str">
-        <f>'data'!$B$62</f>
+        <f>'data'!$B$81</f>
       </c>
     </row>
     <row r="163">
@@ -6998,7 +7017,7 @@
     </row>
     <row r="167">
       <c r="A167" s="11" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B167" s="11"/>
       <c r="C167" s="11"/>
@@ -7007,7 +7026,7 @@
       <c r="F167" s="11"/>
       <c r="G167" s="11"/>
       <c r="I167" s="11" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="J167" s="11"/>
       <c r="K167" s="11"/>
@@ -7038,7 +7057,7 @@
     </row>
     <row r="169">
       <c r="A169" s="19" t="str">
-        <f>CONCATENATE("M 5 ",G38)</f>
+        <f>CONCATENATE("M 7 ",G54)</f>
       </c>
       <c r="B169" s="22"/>
       <c r="C169" s="22"/>
@@ -7049,7 +7068,7 @@
         <f>'data'!$B$30</f>
       </c>
       <c r="I169" s="19" t="str">
-        <f>CONCATENATE("M 19 ",O46)</f>
+        <f>CONCATENATE("M 22 ",O46)</f>
       </c>
       <c r="J169" s="22"/>
       <c r="K169" s="22"/>
@@ -7057,7 +7076,7 @@
       <c r="M169" s="22"/>
       <c r="N169" s="22"/>
       <c r="O169" s="19" t="str">
-        <f>'data'!$B$65</f>
+        <f>'data'!$B$62</f>
       </c>
     </row>
     <row r="171">
@@ -7082,7 +7101,7 @@
     </row>
     <row r="175">
       <c r="A175" s="11" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B175" s="11"/>
       <c r="C175" s="11"/>
@@ -7091,7 +7110,7 @@
       <c r="F175" s="11"/>
       <c r="G175" s="11"/>
       <c r="I175" s="11" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="J175" s="11"/>
       <c r="K175" s="11"/>
@@ -7122,7 +7141,7 @@
     </row>
     <row r="177">
       <c r="A177" s="19" t="str">
-        <f>CONCATENATE("M 6 ",G46)</f>
+        <f>CONCATENATE("M 8 ",G62)</f>
       </c>
       <c r="B177" s="22"/>
       <c r="C177" s="22"/>
@@ -7133,7 +7152,7 @@
         <f>'data'!$B$22</f>
       </c>
       <c r="I177" s="19" t="str">
-        <f>CONCATENATE("M 20 ",O54)</f>
+        <f>CONCATENATE("M 23 ",O54)</f>
       </c>
       <c r="J177" s="22"/>
       <c r="K177" s="22"/>
@@ -7141,7 +7160,7 @@
       <c r="M177" s="22"/>
       <c r="N177" s="22"/>
       <c r="O177" s="19" t="str">
-        <f>'data'!$B$68</f>
+        <f>'data'!$B$65</f>
       </c>
     </row>
     <row r="179">
@@ -7166,7 +7185,7 @@
     </row>
     <row r="183">
       <c r="A183" s="11" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B183" s="11"/>
       <c r="C183" s="11"/>
@@ -7175,7 +7194,7 @@
       <c r="F183" s="11"/>
       <c r="G183" s="11"/>
       <c r="I183" s="11" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="J183" s="11"/>
       <c r="K183" s="11"/>
@@ -7206,7 +7225,7 @@
     </row>
     <row r="185">
       <c r="A185" s="19" t="str">
-        <f>'data'!$B$26</f>
+        <f>CONCATENATE("M 10 ",G78)</f>
       </c>
       <c r="B185" s="22"/>
       <c r="C185" s="22"/>
@@ -7214,10 +7233,10 @@
       <c r="E185" s="22"/>
       <c r="F185" s="22"/>
       <c r="G185" s="19" t="str">
-        <f>'data'!$B$25</f>
+        <f>'data'!$B$27</f>
       </c>
       <c r="I185" s="19" t="str">
-        <f>'data'!$B$72</f>
+        <f>CONCATENATE("M 24 ",O62)</f>
       </c>
       <c r="J185" s="22"/>
       <c r="K185" s="22"/>
@@ -7225,7 +7244,7 @@
       <c r="M185" s="22"/>
       <c r="N185" s="22"/>
       <c r="O185" s="19" t="str">
-        <f>'data'!$B$88</f>
+        <f>'data'!$B$68</f>
       </c>
     </row>
     <row r="187">
@@ -7250,7 +7269,7 @@
     </row>
     <row r="191">
       <c r="A191" s="11" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B191" s="11"/>
       <c r="C191" s="11"/>
@@ -7259,7 +7278,7 @@
       <c r="F191" s="11"/>
       <c r="G191" s="11"/>
       <c r="I191" s="11" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="J191" s="11"/>
       <c r="K191" s="11"/>
@@ -7290,7 +7309,7 @@
     </row>
     <row r="193">
       <c r="A193" s="19" t="str">
-        <f>CONCATENATE("M 7 ",G54)</f>
+        <f>CONCATENATE("M 11 ",G86)</f>
       </c>
       <c r="B193" s="22"/>
       <c r="C193" s="22"/>
@@ -7298,10 +7317,10 @@
       <c r="E193" s="22"/>
       <c r="F193" s="22"/>
       <c r="G193" s="19" t="str">
-        <f>'data'!$B$27</f>
+        <f>'data'!$B$30</f>
       </c>
       <c r="I193" s="19" t="str">
-        <f>CONCATENATE("M 21 ",O62)</f>
+        <f>CONCATENATE("M 26 ",O78)</f>
       </c>
       <c r="J193" s="22"/>
       <c r="K193" s="22"/>
@@ -7334,7 +7353,7 @@
     </row>
     <row r="199">
       <c r="A199" s="11" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B199" s="11"/>
       <c r="C199" s="11"/>
@@ -7343,7 +7362,7 @@
       <c r="F199" s="11"/>
       <c r="G199" s="11"/>
       <c r="I199" s="11" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="J199" s="11"/>
       <c r="K199" s="11"/>
@@ -7374,7 +7393,7 @@
     </row>
     <row r="201">
       <c r="A201" s="19" t="str">
-        <f>CONCATENATE("M 8 ",G62)</f>
+        <f>CONCATENATE("M 12 ",G94)</f>
       </c>
       <c r="B201" s="22"/>
       <c r="C201" s="22"/>
@@ -7382,10 +7401,10 @@
       <c r="E201" s="22"/>
       <c r="F201" s="22"/>
       <c r="G201" s="19" t="str">
-        <f>'data'!$B$30</f>
+        <f>'data'!$B$33</f>
       </c>
       <c r="I201" s="19" t="str">
-        <f>CONCATENATE("M 22 ",O70)</f>
+        <f>CONCATENATE("M 27 ",O86)</f>
       </c>
       <c r="J201" s="22"/>
       <c r="K201" s="22"/>
@@ -7418,7 +7437,7 @@
     </row>
     <row r="207">
       <c r="A207" s="11" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B207" s="11"/>
       <c r="C207" s="11"/>
@@ -7427,7 +7446,7 @@
       <c r="F207" s="11"/>
       <c r="G207" s="11"/>
       <c r="I207" s="11" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="J207" s="11"/>
       <c r="K207" s="11"/>
@@ -7458,7 +7477,7 @@
     </row>
     <row r="209">
       <c r="A209" s="19" t="str">
-        <f>CONCATENATE("M 9 ",G70)</f>
+        <f>CONCATENATE("M 13 ",G102)</f>
       </c>
       <c r="B209" s="22"/>
       <c r="C209" s="22"/>
@@ -7466,10 +7485,10 @@
       <c r="E209" s="22"/>
       <c r="F209" s="22"/>
       <c r="G209" s="19" t="str">
-        <f>'data'!$B$33</f>
+        <f>'data'!$B$36</f>
       </c>
       <c r="I209" s="19" t="str">
-        <f>CONCATENATE("M 23 ",O78)</f>
+        <f>CONCATENATE("M 28 ",O94)</f>
       </c>
       <c r="J209" s="22"/>
       <c r="K209" s="22"/>
@@ -7502,7 +7521,7 @@
     </row>
     <row r="215">
       <c r="A215" s="11" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B215" s="11"/>
       <c r="C215" s="11"/>
@@ -7511,7 +7530,7 @@
       <c r="F215" s="11"/>
       <c r="G215" s="11"/>
       <c r="I215" s="11" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="J215" s="11"/>
       <c r="K215" s="11"/>
@@ -7542,7 +7561,7 @@
     </row>
     <row r="217">
       <c r="A217" s="19" t="str">
-        <f>CONCATENATE("M 10 ",G78)</f>
+        <f>CONCATENATE("M 14 ",G110)</f>
       </c>
       <c r="B217" s="22"/>
       <c r="C217" s="22"/>
@@ -7550,10 +7569,10 @@
       <c r="E217" s="22"/>
       <c r="F217" s="22"/>
       <c r="G217" s="19" t="str">
-        <f>'data'!$B$36</f>
+        <f>'data'!$B$39</f>
       </c>
       <c r="I217" s="19" t="str">
-        <f>CONCATENATE("M 24 ",O86)</f>
+        <f>CONCATENATE("M 29 ",O102)</f>
       </c>
       <c r="J217" s="22"/>
       <c r="K217" s="22"/>
@@ -7586,7 +7605,7 @@
     </row>
     <row r="223">
       <c r="A223" s="11" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B223" s="11"/>
       <c r="C223" s="11"/>
@@ -7595,7 +7614,7 @@
       <c r="F223" s="11"/>
       <c r="G223" s="11"/>
       <c r="I223" s="11" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="J223" s="11"/>
       <c r="K223" s="11"/>
@@ -7626,7 +7645,7 @@
     </row>
     <row r="225">
       <c r="A225" s="19" t="str">
-        <f>CONCATENATE("M 11 ",G86)</f>
+        <f>CONCATENATE("M 15 ",G118)</f>
       </c>
       <c r="B225" s="22"/>
       <c r="C225" s="22"/>
@@ -7634,10 +7653,10 @@
       <c r="E225" s="22"/>
       <c r="F225" s="22"/>
       <c r="G225" s="19" t="str">
-        <f>'data'!$B$39</f>
+        <f>'data'!$B$42</f>
       </c>
       <c r="I225" s="19" t="str">
-        <f>CONCATENATE("M 25 ",O94)</f>
+        <f>CONCATENATE("M 30 ",O110)</f>
       </c>
       <c r="J225" s="22"/>
       <c r="K225" s="22"/>
@@ -7670,7 +7689,7 @@
     </row>
     <row r="231">
       <c r="A231" s="11" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B231" s="11"/>
       <c r="C231" s="11"/>
@@ -7679,7 +7698,7 @@
       <c r="F231" s="11"/>
       <c r="G231" s="11"/>
       <c r="I231" s="11" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="J231" s="11"/>
       <c r="K231" s="11"/>
@@ -7710,7 +7729,7 @@
     </row>
     <row r="233">
       <c r="A233" s="19" t="str">
-        <f>CONCATENATE("M 12 ",G94)</f>
+        <f>CONCATENATE("M 16 ",G126)</f>
       </c>
       <c r="B233" s="22"/>
       <c r="C233" s="22"/>
@@ -7718,10 +7737,10 @@
       <c r="E233" s="22"/>
       <c r="F233" s="22"/>
       <c r="G233" s="19" t="str">
-        <f>'data'!$B$42</f>
+        <f>'data'!$B$45</f>
       </c>
       <c r="I233" s="19" t="str">
-        <f>CONCATENATE("M 26 ",O102)</f>
+        <f>CONCATENATE("M 31 ",O118)</f>
       </c>
       <c r="J233" s="22"/>
       <c r="K233" s="22"/>
@@ -7753,15 +7772,6 @@
       <c r="O236" s="23"/>
     </row>
     <row r="239">
-      <c r="A239" s="11" t="s">
-        <v>270</v>
-      </c>
-      <c r="B239" s="11"/>
-      <c r="C239" s="11"/>
-      <c r="D239" s="11"/>
-      <c r="E239" s="11"/>
-      <c r="F239" s="11"/>
-      <c r="G239" s="11"/>
       <c r="I239" s="11" t="s">
         <v>271</v>
       </c>
@@ -7773,15 +7783,6 @@
       <c r="O239" s="11"/>
     </row>
     <row r="240">
-      <c r="A240" s="21" t="s">
-        <v>209</v>
-      </c>
-      <c r="D240" s="19" t="s">
-        <v>210</v>
-      </c>
-      <c r="G240" s="20" t="s">
-        <v>211</v>
-      </c>
       <c r="I240" s="21" t="s">
         <v>209</v>
       </c>
@@ -7793,19 +7794,8 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="19" t="str">
-        <f>CONCATENATE("M 13 ",G102)</f>
-      </c>
-      <c r="B241" s="22"/>
-      <c r="C241" s="22"/>
-      <c r="D241" s="22"/>
-      <c r="E241" s="22"/>
-      <c r="F241" s="22"/>
-      <c r="G241" s="19" t="str">
-        <f>'data'!$B$45</f>
-      </c>
       <c r="I241" s="19" t="str">
-        <f>CONCATENATE("M 27 ",O110)</f>
+        <f>CONCATENATE("M 32 ",O126)</f>
       </c>
       <c r="J241" s="22"/>
       <c r="K241" s="22"/>
@@ -7817,20 +7807,12 @@
       </c>
     </row>
     <row r="243">
-      <c r="F243" t="s">
-        <v>212</v>
-      </c>
-      <c r="G243" s="23"/>
       <c r="N243" t="s">
         <v>212</v>
       </c>
       <c r="O243" s="23"/>
     </row>
     <row r="244">
-      <c r="F244" t="s">
-        <v>213</v>
-      </c>
-      <c r="G244" s="23"/>
       <c r="N244" t="s">
         <v>213</v>
       </c>
@@ -7878,7 +7860,7 @@
     </row>
     <row r="254">
       <c r="A254" s="19" t="str">
-        <f>CONCATENATE("M 29 ",G131)</f>
+        <f>CONCATENATE("M 33 ",G139)</f>
       </c>
       <c r="B254" s="22"/>
       <c r="C254" s="22"/>
@@ -7886,10 +7868,10 @@
       <c r="E254" s="22"/>
       <c r="F254" s="22"/>
       <c r="G254" s="19" t="str">
-        <f>CONCATENATE("M 28 ",G123)</f>
+        <f>CONCATENATE("M 1 ",G6)</f>
       </c>
       <c r="I254" s="19" t="str">
-        <f>CONCATENATE("M 45 ",O131)</f>
+        <f>CONCATENATE("M 46 ",O139)</f>
       </c>
       <c r="J254" s="22"/>
       <c r="K254" s="22"/>
@@ -7897,7 +7879,7 @@
       <c r="M254" s="22"/>
       <c r="N254" s="22"/>
       <c r="O254" s="19" t="str">
-        <f>CONCATENATE("M 44 ",O123)</f>
+        <f>CONCATENATE("M 17 ",O6)</f>
       </c>
     </row>
     <row r="256">
@@ -7962,7 +7944,7 @@
     </row>
     <row r="262">
       <c r="A262" s="19" t="str">
-        <f>CONCATENATE("M 31 ",G147)</f>
+        <f>CONCATENATE("M 35 ",G155)</f>
       </c>
       <c r="B262" s="22"/>
       <c r="C262" s="22"/>
@@ -7970,10 +7952,10 @@
       <c r="E262" s="22"/>
       <c r="F262" s="22"/>
       <c r="G262" s="19" t="str">
-        <f>CONCATENATE("M 30 ",G139)</f>
+        <f>CONCATENATE("M 34 ",G147)</f>
       </c>
       <c r="I262" s="19" t="str">
-        <f>CONCATENATE("M 47 ",O147)</f>
+        <f>CONCATENATE("M 48 ",O155)</f>
       </c>
       <c r="J262" s="22"/>
       <c r="K262" s="22"/>
@@ -7981,7 +7963,7 @@
       <c r="M262" s="22"/>
       <c r="N262" s="22"/>
       <c r="O262" s="19" t="str">
-        <f>CONCATENATE("M 46 ",O139)</f>
+        <f>CONCATENATE("M 47 ",O147)</f>
       </c>
     </row>
     <row r="264">
@@ -8046,7 +8028,7 @@
     </row>
     <row r="270">
       <c r="A270" s="19" t="str">
-        <f>CONCATENATE("M 33 ",G163)</f>
+        <f>CONCATENATE("M 36 ",G163)</f>
       </c>
       <c r="B270" s="22"/>
       <c r="C270" s="22"/>
@@ -8054,10 +8036,10 @@
       <c r="E270" s="22"/>
       <c r="F270" s="22"/>
       <c r="G270" s="19" t="str">
-        <f>CONCATENATE("M 32 ",G155)</f>
+        <f>CONCATENATE("M 5 ",G38)</f>
       </c>
       <c r="I270" s="19" t="str">
-        <f>CONCATENATE("M 49 ",O163)</f>
+        <f>CONCATENATE("M 50 ",O171)</f>
       </c>
       <c r="J270" s="22"/>
       <c r="K270" s="22"/>
@@ -8065,7 +8047,7 @@
       <c r="M270" s="22"/>
       <c r="N270" s="22"/>
       <c r="O270" s="19" t="str">
-        <f>CONCATENATE("M 48 ",O155)</f>
+        <f>CONCATENATE("M 49 ",O163)</f>
       </c>
     </row>
     <row r="272">
@@ -8130,7 +8112,7 @@
     </row>
     <row r="278">
       <c r="A278" s="19" t="str">
-        <f>CONCATENATE("M 35 ",G179)</f>
+        <f>CONCATENATE("M 38 ",G179)</f>
       </c>
       <c r="B278" s="22"/>
       <c r="C278" s="22"/>
@@ -8138,10 +8120,10 @@
       <c r="E278" s="22"/>
       <c r="F278" s="22"/>
       <c r="G278" s="19" t="str">
-        <f>CONCATENATE("M 34 ",G171)</f>
+        <f>CONCATENATE("M 37 ",G171)</f>
       </c>
       <c r="I278" s="19" t="str">
-        <f>CONCATENATE("M 51 ",O179)</f>
+        <f>CONCATENATE("M 52 ",O187)</f>
       </c>
       <c r="J278" s="22"/>
       <c r="K278" s="22"/>
@@ -8149,7 +8131,7 @@
       <c r="M278" s="22"/>
       <c r="N278" s="22"/>
       <c r="O278" s="19" t="str">
-        <f>CONCATENATE("M 50 ",O171)</f>
+        <f>CONCATENATE("M 51 ",O179)</f>
       </c>
     </row>
     <row r="280">
@@ -8214,7 +8196,7 @@
     </row>
     <row r="286">
       <c r="A286" s="19" t="str">
-        <f>CONCATENATE("M 37 ",G195)</f>
+        <f>CONCATENATE("M 39 ",G187)</f>
       </c>
       <c r="B286" s="22"/>
       <c r="C286" s="22"/>
@@ -8222,7 +8204,7 @@
       <c r="E286" s="22"/>
       <c r="F286" s="22"/>
       <c r="G286" s="19" t="str">
-        <f>CONCATENATE("M 36 ",G187)</f>
+        <f>CONCATENATE("M 9 ",G70)</f>
       </c>
       <c r="I286" s="19" t="str">
         <f>CONCATENATE("M 53 ",O195)</f>
@@ -8233,7 +8215,7 @@
       <c r="M286" s="22"/>
       <c r="N286" s="22"/>
       <c r="O286" s="19" t="str">
-        <f>CONCATENATE("M 52 ",O187)</f>
+        <f>CONCATENATE("M 25 ",O70)</f>
       </c>
     </row>
     <row r="288">
@@ -8298,7 +8280,7 @@
     </row>
     <row r="294">
       <c r="A294" s="19" t="str">
-        <f>CONCATENATE("M 39 ",G211)</f>
+        <f>CONCATENATE("M 41 ",G203)</f>
       </c>
       <c r="B294" s="22"/>
       <c r="C294" s="22"/>
@@ -8306,7 +8288,7 @@
       <c r="E294" s="22"/>
       <c r="F294" s="22"/>
       <c r="G294" s="19" t="str">
-        <f>CONCATENATE("M 38 ",G203)</f>
+        <f>CONCATENATE("M 40 ",G195)</f>
       </c>
       <c r="I294" s="19" t="str">
         <f>CONCATENATE("M 55 ",O211)</f>
@@ -8382,7 +8364,7 @@
     </row>
     <row r="302">
       <c r="A302" s="19" t="str">
-        <f>CONCATENATE("M 41 ",G227)</f>
+        <f>CONCATENATE("M 43 ",G219)</f>
       </c>
       <c r="B302" s="22"/>
       <c r="C302" s="22"/>
@@ -8390,7 +8372,7 @@
       <c r="E302" s="22"/>
       <c r="F302" s="22"/>
       <c r="G302" s="19" t="str">
-        <f>CONCATENATE("M 40 ",G219)</f>
+        <f>CONCATENATE("M 42 ",G211)</f>
       </c>
       <c r="I302" s="19" t="str">
         <f>CONCATENATE("M 57 ",O227)</f>
@@ -8466,7 +8448,7 @@
     </row>
     <row r="310">
       <c r="A310" s="19" t="str">
-        <f>CONCATENATE("M 43 ",G243)</f>
+        <f>CONCATENATE("M 45 ",G235)</f>
       </c>
       <c r="B310" s="22"/>
       <c r="C310" s="22"/>
@@ -8474,7 +8456,7 @@
       <c r="E310" s="22"/>
       <c r="F310" s="22"/>
       <c r="G310" s="19" t="str">
-        <f>CONCATENATE("M 42 ",G235)</f>
+        <f>CONCATENATE("M 44 ",G227)</f>
       </c>
       <c r="I310" s="19" t="str">
         <f>CONCATENATE("M 59 ",O243)</f>
@@ -9174,11 +9156,12 @@
     <mergeCell ref="I90:O90"/>
     <mergeCell ref="A98:G98"/>
     <mergeCell ref="I98:O98"/>
+    <mergeCell ref="A106:G106"/>
     <mergeCell ref="I106:O106"/>
-    <mergeCell ref="A119:G119"/>
-    <mergeCell ref="I119:O119"/>
-    <mergeCell ref="A127:G127"/>
-    <mergeCell ref="I127:O127"/>
+    <mergeCell ref="A114:G114"/>
+    <mergeCell ref="I114:O114"/>
+    <mergeCell ref="A122:G122"/>
+    <mergeCell ref="I122:O122"/>
     <mergeCell ref="A135:G135"/>
     <mergeCell ref="I135:O135"/>
     <mergeCell ref="A143:G143"/>
@@ -9205,7 +9188,6 @@
     <mergeCell ref="I223:O223"/>
     <mergeCell ref="A231:G231"/>
     <mergeCell ref="I231:O231"/>
-    <mergeCell ref="A239:G239"/>
     <mergeCell ref="I239:O239"/>
     <mergeCell ref="A252:G252"/>
     <mergeCell ref="I252:O252"/>
@@ -9244,7 +9226,7 @@
   <rowBreaks count="9" manualBreakCount="9">
     <brk id="41" max="16383" man="true"/>
     <brk id="81" max="16383" man="true"/>
-    <brk id="118" max="16383" man="true"/>
+    <brk id="121" max="16383" man="true"/>
     <brk id="158" max="16383" man="true"/>
     <brk id="198" max="16383" man="true"/>
     <brk id="238" max="16383" man="true"/>
@@ -9287,35 +9269,29 @@
       <c r="J1" s="11"/>
       <c r="K1" s="11"/>
     </row>
+    <row r="5">
+      <c r="C5" s="16" t="s">
+        <v>18</v>
+      </c>
+    </row>
     <row r="6">
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16" t="s">
-        <v>18</v>
+      <c r="D6" s="14"/>
+      <c r="E6" s="13">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="F7" s="14"/>
-      <c r="G7" s="12"/>
-    </row>
-    <row r="8">
-      <c r="G8" s="13">
-        <v>28</v>
-      </c>
+      <c r="C7" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="15"/>
+      <c r="E7" s="12"/>
     </row>
     <row r="9">
-      <c r="G9" s="12"/>
       <c r="H9" s="14"/>
       <c r="I9" s="12"/>
     </row>
     <row r="10">
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="F10" s="15"/>
-      <c r="G10" s="12"/>
       <c r="I10" s="12"/>
     </row>
     <row r="11">
@@ -9348,7 +9324,7 @@
     </row>
     <row r="16">
       <c r="G16" s="13">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H16" s="15"/>
       <c r="I16" s="12"/>
@@ -9364,7 +9340,7 @@
     <row r="18">
       <c r="D18" s="14"/>
       <c r="E18" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18" s="15"/>
       <c r="G18" s="12"/>
@@ -9401,7 +9377,7 @@
     </row>
     <row r="24">
       <c r="G24" s="13">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="K24" s="12"/>
     </row>
@@ -9417,7 +9393,7 @@
     <row r="26">
       <c r="D26" s="14"/>
       <c r="E26" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F26" s="15"/>
       <c r="G26" s="12"/>
@@ -9458,7 +9434,7 @@
     </row>
     <row r="32">
       <c r="G32" s="13">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H32" s="15"/>
       <c r="I32" s="12"/>
@@ -9472,7 +9448,7 @@
     <row r="34">
       <c r="D34" s="14"/>
       <c r="E34" s="13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F34" s="15"/>
       <c r="G34" s="12"/>
@@ -9523,35 +9499,29 @@
       <c r="J1" s="11"/>
       <c r="K1" s="11"/>
     </row>
+    <row r="5">
+      <c r="C5" s="16" t="s">
+        <v>44</v>
+      </c>
+    </row>
     <row r="6">
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16" t="s">
-        <v>44</v>
+      <c r="D6" s="14"/>
+      <c r="E6" s="13">
+        <v>5</v>
       </c>
     </row>
     <row r="7">
-      <c r="F7" s="14"/>
-      <c r="G7" s="12"/>
-    </row>
-    <row r="8">
-      <c r="G8" s="13">
-        <v>32</v>
-      </c>
+      <c r="C7" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="D7" s="15"/>
+      <c r="E7" s="12"/>
     </row>
     <row r="9">
-      <c r="G9" s="12"/>
       <c r="H9" s="14"/>
       <c r="I9" s="12"/>
     </row>
     <row r="10">
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="F10" s="15"/>
-      <c r="G10" s="12"/>
       <c r="I10" s="12"/>
     </row>
     <row r="11">
@@ -9584,7 +9554,7 @@
     </row>
     <row r="16">
       <c r="G16" s="13">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H16" s="15"/>
       <c r="I16" s="12"/>
@@ -9600,7 +9570,7 @@
     <row r="18">
       <c r="D18" s="14"/>
       <c r="E18" s="13">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F18" s="15"/>
       <c r="G18" s="12"/>
@@ -9637,7 +9607,7 @@
     </row>
     <row r="24">
       <c r="G24" s="13">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="K24" s="12"/>
     </row>
@@ -9653,7 +9623,7 @@
     <row r="26">
       <c r="D26" s="14"/>
       <c r="E26" s="13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F26" s="15"/>
       <c r="G26" s="12"/>
@@ -9694,7 +9664,7 @@
     </row>
     <row r="32">
       <c r="G32" s="13">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H32" s="15"/>
       <c r="I32" s="12"/>
@@ -9708,7 +9678,7 @@
     <row r="34">
       <c r="D34" s="14"/>
       <c r="E34" s="13">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F34" s="15"/>
       <c r="G34" s="12"/>

--- a/playoffs-example-large.xlsx
+++ b/playoffs-example-large.xlsx
@@ -3193,7 +3193,7 @@
     </row>
     <row r="25">
       <c r="C25" s="16" t="s">
-        <v>46</v>
+        <v>117</v>
       </c>
       <c r="G25" s="12"/>
       <c r="H25" s="14"/>
@@ -3372,7 +3372,7 @@
     </row>
     <row r="17">
       <c r="C17" s="16" t="s">
-        <v>110</v>
+        <v>42</v>
       </c>
       <c r="G17" s="12"/>
       <c r="K17" s="12"/>
@@ -3423,7 +3423,7 @@
     </row>
     <row r="25">
       <c r="C25" s="16" t="s">
-        <v>117</v>
+        <v>46</v>
       </c>
       <c r="G25" s="12"/>
       <c r="H25" s="14"/>
@@ -3706,7 +3706,7 @@
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="I30" s="12"/>
     </row>
@@ -3861,7 +3861,7 @@
     </row>
     <row r="19">
       <c r="C19" s="16" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="12"/>
@@ -3936,7 +3936,7 @@
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
-        <v>179</v>
+        <v>27</v>
       </c>
       <c r="I30" s="12"/>
     </row>
@@ -3954,7 +3954,7 @@
     </row>
     <row r="33">
       <c r="C33" s="16" t="s">
-        <v>181</v>
+        <v>30</v>
       </c>
       <c r="G33" s="12"/>
     </row>
@@ -4030,7 +4030,7 @@
     </row>
     <row r="9">
       <c r="C9" s="16" t="s">
-        <v>186</v>
+        <v>18</v>
       </c>
       <c r="G9" s="12"/>
       <c r="H9" s="14"/>
@@ -4047,7 +4047,7 @@
     </row>
     <row r="11">
       <c r="C11" s="16" t="s">
-        <v>188</v>
+        <v>24</v>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="12"/>
@@ -4067,7 +4067,7 @@
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
-        <v>190</v>
+        <v>38</v>
       </c>
       <c r="I14" s="12"/>
       <c r="K14" s="12"/>
@@ -4088,7 +4088,7 @@
     </row>
     <row r="17">
       <c r="C17" s="16" t="s">
-        <v>192</v>
+        <v>40</v>
       </c>
       <c r="G17" s="12"/>
       <c r="K17" s="12"/>
@@ -4197,7 +4197,7 @@
     </row>
     <row r="33">
       <c r="C33" s="16" t="s">
-        <v>203</v>
+        <v>21</v>
       </c>
       <c r="G33" s="12"/>
     </row>
@@ -4236,42 +4236,42 @@
   <sheetData>
     <row r="1" ht="270" customHeight="true">
       <c r="A1" s="17">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="B1" s="18" t="str">
-        <f>'data'!D3</f>
+        <f>'data'!D92</f>
       </c>
     </row>
     <row r="2" ht="270" customHeight="true">
       <c r="A2" s="17">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="B2" s="18" t="str">
-        <f>'data'!D4</f>
+        <f>'data'!D83</f>
       </c>
     </row>
     <row r="3" ht="270" customHeight="true">
       <c r="A3" s="17">
-        <v>2</v>
+        <v>81</v>
       </c>
       <c r="B3" s="18" t="str">
-        <f>'data'!D5</f>
+        <f>'data'!D84</f>
       </c>
     </row>
     <row r="4" ht="270" customHeight="true">
       <c r="A4" s="17">
-        <v>3</v>
+        <v>76</v>
       </c>
       <c r="B4" s="18" t="str">
-        <f>'data'!D6</f>
+        <f>'data'!D79</f>
       </c>
     </row>
     <row r="5" ht="270" customHeight="true">
       <c r="A5" s="17">
-        <v>4</v>
+        <v>77</v>
       </c>
       <c r="B5" s="18" t="str">
-        <f>'data'!D7</f>
+        <f>'data'!D80</f>
       </c>
     </row>
     <row r="6" ht="270" customHeight="true">
@@ -4300,26 +4300,26 @@
     </row>
     <row r="9" ht="270" customHeight="true">
       <c r="A9" s="17">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="B9" s="18" t="str">
-        <f>'data'!D11</f>
+        <f>'data'!D85</f>
       </c>
     </row>
     <row r="10" ht="270" customHeight="true">
       <c r="A10" s="17">
-        <v>9</v>
+        <v>83</v>
       </c>
       <c r="B10" s="18" t="str">
-        <f>'data'!D12</f>
+        <f>'data'!D86</f>
       </c>
     </row>
     <row r="11" ht="270" customHeight="true">
       <c r="A11" s="17">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="B11" s="18" t="str">
-        <f>'data'!D13</f>
+        <f>'data'!D51</f>
       </c>
     </row>
     <row r="12" ht="270" customHeight="true">
@@ -4556,10 +4556,10 @@
     </row>
     <row r="41" ht="270" customHeight="true">
       <c r="A41" s="17">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="B41" s="18" t="str">
-        <f>'data'!D43</f>
+        <f>'data'!D54</f>
       </c>
     </row>
     <row r="42" ht="270" customHeight="true">
@@ -4653,10 +4653,10 @@
     </row>
     <row r="3" ht="270" customHeight="true">
       <c r="A3" s="17">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="B3" s="18" t="str">
-        <f>'data'!D51</f>
+        <f>'data'!D13</f>
       </c>
     </row>
     <row r="4" ht="270" customHeight="true">
@@ -4677,10 +4677,10 @@
     </row>
     <row r="6" ht="270" customHeight="true">
       <c r="A6" s="17">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="B6" s="18" t="str">
-        <f>'data'!D54</f>
+        <f>'data'!D43</f>
       </c>
     </row>
     <row r="7" ht="270" customHeight="true">
@@ -4789,10 +4789,10 @@
     </row>
     <row r="20" ht="270" customHeight="true">
       <c r="A20" s="17">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="B20" s="18" t="str">
-        <f>'data'!D68</f>
+        <f>'data'!D75</f>
       </c>
     </row>
     <row r="21" ht="270" customHeight="true">
@@ -4845,10 +4845,10 @@
     </row>
     <row r="27" ht="270" customHeight="true">
       <c r="A27" s="17">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="B27" s="18" t="str">
-        <f>'data'!D75</f>
+        <f>'data'!D68</f>
       </c>
     </row>
     <row r="28" ht="270" customHeight="true">
@@ -4877,18 +4877,18 @@
     </row>
     <row r="31" ht="270" customHeight="true">
       <c r="A31" s="17">
-        <v>76</v>
+        <v>3</v>
       </c>
       <c r="B31" s="18" t="str">
-        <f>'data'!D79</f>
+        <f>'data'!D6</f>
       </c>
     </row>
     <row r="32" ht="270" customHeight="true">
       <c r="A32" s="17">
-        <v>77</v>
+        <v>4</v>
       </c>
       <c r="B32" s="18" t="str">
-        <f>'data'!D80</f>
+        <f>'data'!D7</f>
       </c>
     </row>
     <row r="33" ht="270" customHeight="true">
@@ -4909,34 +4909,34 @@
     </row>
     <row r="35" ht="270" customHeight="true">
       <c r="A35" s="17">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="B35" s="18" t="str">
-        <f>'data'!D83</f>
+        <f>'data'!D3</f>
       </c>
     </row>
     <row r="36" ht="270" customHeight="true">
       <c r="A36" s="17">
-        <v>81</v>
+        <v>2</v>
       </c>
       <c r="B36" s="18" t="str">
-        <f>'data'!D84</f>
+        <f>'data'!D5</f>
       </c>
     </row>
     <row r="37" ht="270" customHeight="true">
       <c r="A37" s="17">
-        <v>82</v>
+        <v>8</v>
       </c>
       <c r="B37" s="18" t="str">
-        <f>'data'!D85</f>
+        <f>'data'!D11</f>
       </c>
     </row>
     <row r="38" ht="270" customHeight="true">
       <c r="A38" s="17">
-        <v>83</v>
+        <v>9</v>
       </c>
       <c r="B38" s="18" t="str">
-        <f>'data'!D86</f>
+        <f>'data'!D12</f>
       </c>
     </row>
     <row r="39" ht="270" customHeight="true">
@@ -4981,10 +4981,10 @@
     </row>
     <row r="44" ht="270" customHeight="true">
       <c r="A44" s="17">
-        <v>89</v>
+        <v>1</v>
       </c>
       <c r="B44" s="18" t="str">
-        <f>'data'!D92</f>
+        <f>'data'!D4</f>
       </c>
     </row>
     <row r="45" ht="270" customHeight="true">
@@ -5377,7 +5377,7 @@
     </row>
     <row r="4">
       <c r="A4" s="19" t="str">
-        <f>'data'!$B$33</f>
+        <f>'data'!$B$83</f>
       </c>
       <c r="B4" s="22"/>
       <c r="C4" s="22"/>
@@ -5385,7 +5385,7 @@
       <c r="E4" s="22"/>
       <c r="F4" s="22"/>
       <c r="G4" s="19" t="str">
-        <f>'data'!$B$32</f>
+        <f>'data'!$B$92</f>
       </c>
       <c r="I4" s="19" t="str">
         <f>'data'!$B$49</f>
@@ -5461,7 +5461,7 @@
     </row>
     <row r="12">
       <c r="A12" s="19" t="str">
-        <f>'data'!$B$35</f>
+        <f>'data'!$B$80</f>
       </c>
       <c r="B12" s="22"/>
       <c r="C12" s="22"/>
@@ -5469,7 +5469,7 @@
       <c r="E12" s="22"/>
       <c r="F12" s="22"/>
       <c r="G12" s="19" t="str">
-        <f>'data'!$B$6</f>
+        <f>'data'!$B$79</f>
       </c>
       <c r="I12" s="19" t="str">
         <f>'data'!$B$52</f>
@@ -5480,7 +5480,7 @@
       <c r="M12" s="22"/>
       <c r="N12" s="22"/>
       <c r="O12" s="19" t="str">
-        <f>'data'!$B$51</f>
+        <f>'data'!$B$13</f>
       </c>
     </row>
     <row r="14">
@@ -5564,7 +5564,7 @@
       <c r="M20" s="22"/>
       <c r="N20" s="22"/>
       <c r="O20" s="19" t="str">
-        <f>'data'!$B$54</f>
+        <f>'data'!$B$43</f>
       </c>
     </row>
     <row r="22">
@@ -5629,7 +5629,7 @@
     </row>
     <row r="28">
       <c r="A28" s="19" t="str">
-        <f>'data'!$B$41</f>
+        <f>'data'!$B$51</f>
       </c>
       <c r="B28" s="22"/>
       <c r="C28" s="22"/>
@@ -5637,7 +5637,7 @@
       <c r="E28" s="22"/>
       <c r="F28" s="22"/>
       <c r="G28" s="19" t="str">
-        <f>'data'!$B$40</f>
+        <f>'data'!$B$86</f>
       </c>
       <c r="I28" s="19" t="str">
         <f>'data'!$B$58</f>
@@ -6144,7 +6144,7 @@
         <f>'data'!$B$28</f>
       </c>
       <c r="I76" s="19" t="str">
-        <f>'data'!$B$75</f>
+        <f>'data'!$B$68</f>
       </c>
       <c r="J76" s="22"/>
       <c r="K76" s="22"/>
@@ -6217,7 +6217,7 @@
     </row>
     <row r="84">
       <c r="A84" s="19" t="str">
-        <f>'data'!$B$32</f>
+        <f>'data'!$B$3</f>
       </c>
       <c r="B84" s="22"/>
       <c r="C84" s="22"/>
@@ -6301,7 +6301,7 @@
     </row>
     <row r="92">
       <c r="A92" s="19" t="str">
-        <f>'data'!$B$35</f>
+        <f>'data'!$B$7</f>
       </c>
       <c r="B92" s="22"/>
       <c r="C92" s="22"/>
@@ -6309,7 +6309,7 @@
       <c r="E92" s="22"/>
       <c r="F92" s="22"/>
       <c r="G92" s="19" t="str">
-        <f>'data'!$B$34</f>
+        <f>'data'!$B$5</f>
       </c>
       <c r="I92" s="19" t="str">
         <f>'data'!$B$81</f>
@@ -6320,7 +6320,7 @@
       <c r="M92" s="22"/>
       <c r="N92" s="22"/>
       <c r="O92" s="19" t="str">
-        <f>'data'!$B$80</f>
+        <f>'data'!$B$7</f>
       </c>
     </row>
     <row r="94">
@@ -6396,7 +6396,7 @@
         <f>'data'!$B$37</f>
       </c>
       <c r="I100" s="19" t="str">
-        <f>'data'!$B$84</f>
+        <f>'data'!$B$5</f>
       </c>
       <c r="J100" s="22"/>
       <c r="K100" s="22"/>
@@ -6404,7 +6404,7 @@
       <c r="M100" s="22"/>
       <c r="N100" s="22"/>
       <c r="O100" s="19" t="str">
-        <f>'data'!$B$83</f>
+        <f>'data'!$B$3</f>
       </c>
     </row>
     <row r="102">
@@ -6469,7 +6469,7 @@
     </row>
     <row r="108">
       <c r="A108" s="19" t="str">
-        <f>'data'!$B$41</f>
+        <f>'data'!$B$13</f>
       </c>
       <c r="B108" s="22"/>
       <c r="C108" s="22"/>
@@ -6477,7 +6477,7 @@
       <c r="E108" s="22"/>
       <c r="F108" s="22"/>
       <c r="G108" s="19" t="str">
-        <f>'data'!$B$40</f>
+        <f>'data'!$B$12</f>
       </c>
       <c r="I108" s="19" t="str">
         <f>'data'!$B$87</f>
@@ -6488,7 +6488,7 @@
       <c r="M108" s="22"/>
       <c r="N108" s="22"/>
       <c r="O108" s="19" t="str">
-        <f>'data'!$B$86</f>
+        <f>'data'!$B$12</f>
       </c>
     </row>
     <row r="110">
@@ -6561,7 +6561,7 @@
       <c r="E116" s="22"/>
       <c r="F116" s="22"/>
       <c r="G116" s="19" t="str">
-        <f>'data'!$B$43</f>
+        <f>'data'!$B$54</f>
       </c>
       <c r="I116" s="19" t="str">
         <f>'data'!$B$90</f>
@@ -6656,7 +6656,7 @@
       <c r="M124" s="22"/>
       <c r="N124" s="22"/>
       <c r="O124" s="19" t="str">
-        <f>'data'!$B$92</f>
+        <f>'data'!$B$4</f>
       </c>
     </row>
     <row r="126">
@@ -6729,7 +6729,7 @@
       <c r="E137" s="22"/>
       <c r="F137" s="22"/>
       <c r="G137" s="19" t="str">
-        <f>'data'!$B$34</f>
+        <f>'data'!$B$84</f>
       </c>
       <c r="I137" s="19" t="str">
         <f>CONCATENATE("M 18 ",O14)</f>
@@ -6897,7 +6897,7 @@
       <c r="E153" s="22"/>
       <c r="F153" s="22"/>
       <c r="G153" s="19" t="str">
-        <f>'data'!$B$39</f>
+        <f>'data'!$B$85</f>
       </c>
       <c r="I153" s="19" t="str">
         <f>CONCATENATE("M 20 ",O30)</f>
@@ -7244,7 +7244,7 @@
       <c r="M185" s="22"/>
       <c r="N185" s="22"/>
       <c r="O185" s="19" t="str">
-        <f>'data'!$B$68</f>
+        <f>'data'!$B$75</f>
       </c>
     </row>
     <row r="187">
@@ -7401,7 +7401,7 @@
       <c r="E201" s="22"/>
       <c r="F201" s="22"/>
       <c r="G201" s="19" t="str">
-        <f>'data'!$B$33</f>
+        <f>'data'!$B$4</f>
       </c>
       <c r="I201" s="19" t="str">
         <f>CONCATENATE("M 27 ",O86)</f>
@@ -7496,7 +7496,7 @@
       <c r="M209" s="22"/>
       <c r="N209" s="22"/>
       <c r="O209" s="19" t="str">
-        <f>'data'!$B$79</f>
+        <f>'data'!$B$6</f>
       </c>
     </row>
     <row r="211">
@@ -7569,7 +7569,7 @@
       <c r="E217" s="22"/>
       <c r="F217" s="22"/>
       <c r="G217" s="19" t="str">
-        <f>'data'!$B$39</f>
+        <f>'data'!$B$11</f>
       </c>
       <c r="I217" s="19" t="str">
         <f>CONCATENATE("M 29 ",O102)</f>
@@ -7664,7 +7664,7 @@
       <c r="M225" s="22"/>
       <c r="N225" s="22"/>
       <c r="O225" s="19" t="str">
-        <f>'data'!$B$85</f>
+        <f>'data'!$B$11</f>
       </c>
     </row>
     <row r="227">
@@ -9271,7 +9271,7 @@
     </row>
     <row r="5">
       <c r="C5" s="16" t="s">
-        <v>18</v>
+        <v>203</v>
       </c>
     </row>
     <row r="6">
@@ -9282,7 +9282,7 @@
     </row>
     <row r="7">
       <c r="C7" s="16" t="s">
-        <v>21</v>
+        <v>186</v>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="12"/>
@@ -9311,7 +9311,7 @@
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
-        <v>24</v>
+        <v>188</v>
       </c>
       <c r="I14" s="12"/>
       <c r="K14" s="12"/>
@@ -9332,7 +9332,7 @@
     </row>
     <row r="17">
       <c r="C17" s="16" t="s">
-        <v>27</v>
+        <v>179</v>
       </c>
       <c r="G17" s="12"/>
       <c r="K17" s="12"/>
@@ -9348,7 +9348,7 @@
     </row>
     <row r="19">
       <c r="C19" s="16" t="s">
-        <v>30</v>
+        <v>181</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="12"/>
@@ -9423,7 +9423,7 @@
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
-        <v>38</v>
+        <v>190</v>
       </c>
       <c r="I30" s="12"/>
     </row>
@@ -9441,7 +9441,7 @@
     </row>
     <row r="33">
       <c r="C33" s="16" t="s">
-        <v>40</v>
+        <v>192</v>
       </c>
       <c r="G33" s="12"/>
     </row>
@@ -9455,7 +9455,7 @@
     </row>
     <row r="35">
       <c r="C35" s="16" t="s">
-        <v>42</v>
+        <v>110</v>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="12"/>

--- a/playoffs-example-large.xlsx
+++ b/playoffs-example-large.xlsx
@@ -3022,7 +3022,7 @@
     </row>
     <row r="35">
       <c r="C35" s="16" t="s">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="12"/>
@@ -3442,7 +3442,7 @@
     </row>
     <row r="27">
       <c r="C27" s="16" t="s">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="12"/>
@@ -3594,7 +3594,7 @@
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
-        <v>141</v>
+        <v>56</v>
       </c>
       <c r="I14" s="12"/>
       <c r="K14" s="12"/>
@@ -3615,7 +3615,7 @@
     </row>
     <row r="17">
       <c r="C17" s="16" t="s">
-        <v>144</v>
+        <v>58</v>
       </c>
       <c r="G17" s="12"/>
       <c r="K17" s="12"/>
@@ -3631,7 +3631,7 @@
     </row>
     <row r="19">
       <c r="C19" s="16" t="s">
-        <v>147</v>
+        <v>60</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="12"/>
@@ -3968,7 +3968,7 @@
     </row>
     <row r="35">
       <c r="C35" s="16" t="s">
-        <v>132</v>
+        <v>34</v>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="12"/>
@@ -4016,7 +4016,7 @@
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
       <c r="E6" s="16" t="s">
-        <v>184</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7">
@@ -4236,10 +4236,10 @@
   <sheetData>
     <row r="1" ht="270" customHeight="true">
       <c r="A1" s="17">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="B1" s="18" t="str">
-        <f>'data'!D92</f>
+        <f>'data'!D24</f>
       </c>
     </row>
     <row r="2" ht="270" customHeight="true">
@@ -4284,18 +4284,18 @@
     </row>
     <row r="7" ht="270" customHeight="true">
       <c r="A7" s="17">
-        <v>6</v>
+        <v>78</v>
       </c>
       <c r="B7" s="18" t="str">
-        <f>'data'!D9</f>
+        <f>'data'!D81</f>
       </c>
     </row>
     <row r="8" ht="270" customHeight="true">
       <c r="A8" s="17">
-        <v>7</v>
+        <v>79</v>
       </c>
       <c r="B8" s="18" t="str">
-        <f>'data'!D10</f>
+        <f>'data'!D82</f>
       </c>
     </row>
     <row r="9" ht="270" customHeight="true">
@@ -4372,26 +4372,26 @@
     </row>
     <row r="18" ht="270" customHeight="true">
       <c r="A18" s="17">
-        <v>17</v>
+        <v>59</v>
       </c>
       <c r="B18" s="18" t="str">
-        <f>'data'!D20</f>
+        <f>'data'!D62</f>
       </c>
     </row>
     <row r="19" ht="270" customHeight="true">
       <c r="A19" s="17">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="B19" s="18" t="str">
-        <f>'data'!D21</f>
+        <f>'data'!D63</f>
       </c>
     </row>
     <row r="20" ht="270" customHeight="true">
       <c r="A20" s="17">
-        <v>19</v>
+        <v>61</v>
       </c>
       <c r="B20" s="18" t="str">
-        <f>'data'!D22</f>
+        <f>'data'!D64</f>
       </c>
     </row>
     <row r="21" ht="270" customHeight="true">
@@ -4404,10 +4404,10 @@
     </row>
     <row r="22" ht="270" customHeight="true">
       <c r="A22" s="17">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="B22" s="18" t="str">
-        <f>'data'!D24</f>
+        <f>'data'!D92</f>
       </c>
     </row>
     <row r="23" ht="270" customHeight="true">
@@ -4492,10 +4492,10 @@
     </row>
     <row r="33" ht="270" customHeight="true">
       <c r="A33" s="17">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="B33" s="18" t="str">
-        <f>'data'!D35</f>
+        <f>'data'!D55</f>
       </c>
     </row>
     <row r="34" ht="270" customHeight="true">
@@ -4685,10 +4685,10 @@
     </row>
     <row r="7" ht="270" customHeight="true">
       <c r="A7" s="17">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="B7" s="18" t="str">
-        <f>'data'!D55</f>
+        <f>'data'!D35</f>
       </c>
     </row>
     <row r="8" ht="270" customHeight="true">
@@ -4741,26 +4741,26 @@
     </row>
     <row r="14" ht="270" customHeight="true">
       <c r="A14" s="17">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="B14" s="18" t="str">
-        <f>'data'!D62</f>
+        <f>'data'!D20</f>
       </c>
     </row>
     <row r="15" ht="270" customHeight="true">
       <c r="A15" s="17">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="B15" s="18" t="str">
-        <f>'data'!D63</f>
+        <f>'data'!D21</f>
       </c>
     </row>
     <row r="16" ht="270" customHeight="true">
       <c r="A16" s="17">
-        <v>61</v>
+        <v>19</v>
       </c>
       <c r="B16" s="18" t="str">
-        <f>'data'!D64</f>
+        <f>'data'!D22</f>
       </c>
     </row>
     <row r="17" ht="270" customHeight="true">
@@ -4893,18 +4893,18 @@
     </row>
     <row r="33" ht="270" customHeight="true">
       <c r="A33" s="17">
-        <v>78</v>
+        <v>6</v>
       </c>
       <c r="B33" s="18" t="str">
-        <f>'data'!D81</f>
+        <f>'data'!D9</f>
       </c>
     </row>
     <row r="34" ht="270" customHeight="true">
       <c r="A34" s="17">
-        <v>79</v>
+        <v>7</v>
       </c>
       <c r="B34" s="18" t="str">
-        <f>'data'!D82</f>
+        <f>'data'!D10</f>
       </c>
     </row>
     <row r="35" ht="270" customHeight="true">
@@ -5385,7 +5385,7 @@
       <c r="E4" s="22"/>
       <c r="F4" s="22"/>
       <c r="G4" s="19" t="str">
-        <f>'data'!$B$92</f>
+        <f>'data'!$B$24</f>
       </c>
       <c r="I4" s="19" t="str">
         <f>'data'!$B$49</f>
@@ -5545,7 +5545,7 @@
     </row>
     <row r="20">
       <c r="A20" s="19" t="str">
-        <f>'data'!$B$38</f>
+        <f>'data'!$B$82</f>
       </c>
       <c r="B20" s="22"/>
       <c r="C20" s="22"/>
@@ -5553,10 +5553,10 @@
       <c r="E20" s="22"/>
       <c r="F20" s="22"/>
       <c r="G20" s="19" t="str">
-        <f>'data'!$B$37</f>
+        <f>'data'!$B$59</f>
       </c>
       <c r="I20" s="19" t="str">
-        <f>'data'!$B$55</f>
+        <f>'data'!$B$7</f>
       </c>
       <c r="J20" s="22"/>
       <c r="K20" s="22"/>
@@ -5808,7 +5808,7 @@
         <f>'data'!$B$17</f>
       </c>
       <c r="I44" s="19" t="str">
-        <f>'data'!$B$64</f>
+        <f>'data'!$B$22</f>
       </c>
       <c r="J44" s="22"/>
       <c r="K44" s="22"/>
@@ -5816,7 +5816,7 @@
       <c r="M44" s="22"/>
       <c r="N44" s="22"/>
       <c r="O44" s="19" t="str">
-        <f>'data'!$B$63</f>
+        <f>'data'!$B$21</f>
       </c>
     </row>
     <row r="46">
@@ -5881,7 +5881,7 @@
     </row>
     <row r="52">
       <c r="A52" s="19" t="str">
-        <f>'data'!$B$21</f>
+        <f>'data'!$B$63</f>
       </c>
       <c r="B52" s="22"/>
       <c r="C52" s="22"/>
@@ -5889,7 +5889,7 @@
       <c r="E52" s="22"/>
       <c r="F52" s="22"/>
       <c r="G52" s="19" t="str">
-        <f>'data'!$B$20</f>
+        <f>'data'!$B$62</f>
       </c>
       <c r="I52" s="19" t="str">
         <f>'data'!$B$67</f>
@@ -5965,7 +5965,7 @@
     </row>
     <row r="60">
       <c r="A60" s="19" t="str">
-        <f>'data'!$B$24</f>
+        <f>'data'!$B$92</f>
       </c>
       <c r="B60" s="22"/>
       <c r="C60" s="22"/>
@@ -6301,7 +6301,7 @@
     </row>
     <row r="92">
       <c r="A92" s="19" t="str">
-        <f>'data'!$B$7</f>
+        <f>'data'!$B$55</f>
       </c>
       <c r="B92" s="22"/>
       <c r="C92" s="22"/>
@@ -6312,7 +6312,7 @@
         <f>'data'!$B$5</f>
       </c>
       <c r="I92" s="19" t="str">
-        <f>'data'!$B$81</f>
+        <f>'data'!$B$9</f>
       </c>
       <c r="J92" s="22"/>
       <c r="K92" s="22"/>
@@ -6385,7 +6385,7 @@
     </row>
     <row r="100">
       <c r="A100" s="19" t="str">
-        <f>'data'!$B$38</f>
+        <f>'data'!$B$10</f>
       </c>
       <c r="B100" s="22"/>
       <c r="C100" s="22"/>
@@ -6393,7 +6393,7 @@
       <c r="E100" s="22"/>
       <c r="F100" s="22"/>
       <c r="G100" s="19" t="str">
-        <f>'data'!$B$37</f>
+        <f>'data'!$B$9</f>
       </c>
       <c r="I100" s="19" t="str">
         <f>'data'!$B$5</f>
@@ -6992,7 +6992,7 @@
       <c r="M161" s="22"/>
       <c r="N161" s="22"/>
       <c r="O161" s="19" t="str">
-        <f>'data'!$B$81</f>
+        <f>'data'!$B$59</f>
       </c>
     </row>
     <row r="163">
@@ -7076,7 +7076,7 @@
       <c r="M169" s="22"/>
       <c r="N169" s="22"/>
       <c r="O169" s="19" t="str">
-        <f>'data'!$B$62</f>
+        <f>'data'!$B$20</f>
       </c>
     </row>
     <row r="171">
@@ -7149,7 +7149,7 @@
       <c r="E177" s="22"/>
       <c r="F177" s="22"/>
       <c r="G177" s="19" t="str">
-        <f>'data'!$B$22</f>
+        <f>'data'!$B$64</f>
       </c>
       <c r="I177" s="19" t="str">
         <f>CONCATENATE("M 23 ",O54)</f>
@@ -7580,7 +7580,7 @@
       <c r="M217" s="22"/>
       <c r="N217" s="22"/>
       <c r="O217" s="19" t="str">
-        <f>'data'!$B$82</f>
+        <f>'data'!$B$10</f>
       </c>
     </row>
     <row r="219">
@@ -9271,7 +9271,7 @@
     </row>
     <row r="5">
       <c r="C5" s="16" t="s">
-        <v>203</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6">
@@ -9383,7 +9383,7 @@
     </row>
     <row r="25">
       <c r="C25" s="16" t="s">
-        <v>34</v>
+        <v>132</v>
       </c>
       <c r="G25" s="12"/>
       <c r="H25" s="14"/>
@@ -9402,7 +9402,7 @@
     </row>
     <row r="27">
       <c r="C27" s="16" t="s">
-        <v>36</v>
+        <v>184</v>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="12"/>
@@ -9613,7 +9613,7 @@
     </row>
     <row r="25">
       <c r="C25" s="16" t="s">
-        <v>56</v>
+        <v>141</v>
       </c>
       <c r="G25" s="12"/>
       <c r="H25" s="14"/>
@@ -9632,7 +9632,7 @@
     </row>
     <row r="27">
       <c r="C27" s="16" t="s">
-        <v>58</v>
+        <v>144</v>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="12"/>
@@ -9653,7 +9653,7 @@
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
-        <v>60</v>
+        <v>147</v>
       </c>
       <c r="I30" s="12"/>
     </row>
@@ -9685,7 +9685,7 @@
     </row>
     <row r="35">
       <c r="C35" s="16" t="s">
-        <v>65</v>
+        <v>203</v>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="12"/>

--- a/playoffs-example-large.xlsx
+++ b/playoffs-example-large.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="402">
   <si>
     <t>Number of pools</t>
   </si>
@@ -86,6 +86,9 @@
     <t>Display Name</t>
   </si>
   <si>
+    <t>Player Number</t>
+  </si>
+  <si>
     <t>Metadata</t>
   </si>
   <si>
@@ -98,6 +101,9 @@
     <t>CLARK</t>
   </si>
   <si>
+    <t>K1</t>
+  </si>
+  <si>
     <t>Luke Rodriguez</t>
   </si>
   <si>
@@ -107,6 +113,9 @@
     <t>RODRIGUEZ</t>
   </si>
   <si>
+    <t>K2</t>
+  </si>
+  <si>
     <t>Michael Lewis</t>
   </si>
   <si>
@@ -116,6 +125,9 @@
     <t>LEWIS</t>
   </si>
   <si>
+    <t>K3</t>
+  </si>
+  <si>
     <t>Nathan Lee</t>
   </si>
   <si>
@@ -125,6 +137,9 @@
     <t>LEE</t>
   </si>
   <si>
+    <t>K4</t>
+  </si>
+  <si>
     <t>Oliver Walker</t>
   </si>
   <si>
@@ -134,102 +149,153 @@
     <t>WALKER</t>
   </si>
   <si>
+    <t>K5</t>
+  </si>
+  <si>
     <t>Paul Hall</t>
   </si>
   <si>
     <t>HALL</t>
   </si>
   <si>
+    <t>K6</t>
+  </si>
+  <si>
     <t>Quentin Allen</t>
   </si>
   <si>
     <t>ALLEN</t>
   </si>
   <si>
+    <t>K7</t>
+  </si>
+  <si>
     <t>Robert Young</t>
   </si>
   <si>
     <t>YOUNG</t>
   </si>
   <si>
+    <t>K8</t>
+  </si>
+  <si>
     <t>Steven Hernandez</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>K9</t>
+  </si>
+  <si>
     <t>Thomas King</t>
   </si>
   <si>
     <t>KING</t>
   </si>
   <si>
+    <t>K10</t>
+  </si>
+  <si>
     <t>Uriel Wright</t>
   </si>
   <si>
     <t>WRIGHT</t>
   </si>
   <si>
+    <t>K11</t>
+  </si>
+  <si>
     <t>Victor Lopez</t>
   </si>
   <si>
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>K12</t>
+  </si>
+  <si>
     <t>William Hill</t>
   </si>
   <si>
     <t>HILL</t>
   </si>
   <si>
+    <t>K13</t>
+  </si>
+  <si>
     <t>Xavier Scott</t>
   </si>
   <si>
     <t>SCOTT</t>
   </si>
   <si>
+    <t>K14</t>
+  </si>
+  <si>
     <t>Yosef Green</t>
   </si>
   <si>
     <t>GREEN</t>
   </si>
   <si>
+    <t>K15</t>
+  </si>
+  <si>
     <t>Zachary Adams</t>
   </si>
   <si>
     <t>ADAMS</t>
   </si>
   <si>
+    <t>K16</t>
+  </si>
+  <si>
     <t>Aaron Thompson</t>
   </si>
   <si>
     <t>THOMPSON</t>
   </si>
   <si>
+    <t>K17</t>
+  </si>
+  <si>
     <t>Benjamin Evans</t>
   </si>
   <si>
     <t>EVANS</t>
   </si>
   <si>
+    <t>K18</t>
+  </si>
+  <si>
     <t>Caleb Wilson</t>
   </si>
   <si>
     <t>WILSON</t>
   </si>
   <si>
+    <t>K19</t>
+  </si>
+  <si>
     <t>Dylan Moore</t>
   </si>
   <si>
     <t>MOORE</t>
   </si>
   <si>
+    <t>K20</t>
+  </si>
+  <si>
     <t>Elijah Taylor</t>
   </si>
   <si>
     <t>TAYLOR</t>
   </si>
   <si>
+    <t>K21</t>
+  </si>
+  <si>
     <t>Finn Anderson</t>
   </si>
   <si>
@@ -239,6 +305,9 @@
     <t>ANDERSON</t>
   </si>
   <si>
+    <t>K22</t>
+  </si>
+  <si>
     <t>Gabriel Thomas</t>
   </si>
   <si>
@@ -248,6 +317,9 @@
     <t>THOMAS</t>
   </si>
   <si>
+    <t>K23</t>
+  </si>
+  <si>
     <t>Hudson Jackson</t>
   </si>
   <si>
@@ -257,6 +329,9 @@
     <t>JACKSON</t>
   </si>
   <si>
+    <t>K24</t>
+  </si>
+  <si>
     <t>Isaac White</t>
   </si>
   <si>
@@ -266,6 +341,9 @@
     <t>WHITE</t>
   </si>
   <si>
+    <t>K25</t>
+  </si>
+  <si>
     <t>Jackson Harris</t>
   </si>
   <si>
@@ -275,117 +353,195 @@
     <t>HARRIS</t>
   </si>
   <si>
+    <t>K26</t>
+  </si>
+  <si>
     <t>Kaden Martin</t>
   </si>
   <si>
     <t>MARTIN</t>
   </si>
   <si>
+    <t>K27</t>
+  </si>
+  <si>
     <t>Liam Thompson</t>
   </si>
   <si>
+    <t>K28</t>
+  </si>
+  <si>
     <t>Mason Martinez</t>
   </si>
   <si>
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>K29</t>
+  </si>
+  <si>
     <t>Nolan Clark</t>
   </si>
   <si>
+    <t>K30</t>
+  </si>
+  <si>
     <t>Owen Rodriguez</t>
   </si>
   <si>
+    <t>K31</t>
+  </si>
+  <si>
     <t>Parker Lewis</t>
   </si>
   <si>
+    <t>K32</t>
+  </si>
+  <si>
     <t>Quinn Walker</t>
   </si>
   <si>
+    <t>K33</t>
+  </si>
+  <si>
     <t>Ryan Hall</t>
   </si>
   <si>
+    <t>K34</t>
+  </si>
+  <si>
     <t>Sebastian Allen</t>
   </si>
   <si>
+    <t>K35</t>
+  </si>
+  <si>
     <t>Tristan Young</t>
   </si>
   <si>
+    <t>K36</t>
+  </si>
+  <si>
     <t>Ulysses Hernandez</t>
   </si>
   <si>
+    <t>K37</t>
+  </si>
+  <si>
     <t>Vincent King</t>
   </si>
   <si>
+    <t>K38</t>
+  </si>
+  <si>
     <t>William Wright</t>
   </si>
   <si>
+    <t>K39</t>
+  </si>
+  <si>
     <t>Xavier Lopez</t>
   </si>
   <si>
+    <t>K40</t>
+  </si>
+  <si>
     <t>Yosef Hill</t>
   </si>
   <si>
+    <t>K41</t>
+  </si>
+  <si>
     <t>Arthur Conan</t>
   </si>
   <si>
     <t>CONAN</t>
   </si>
   <si>
+    <t>K42</t>
+  </si>
+  <si>
     <t>Bram Stoker</t>
   </si>
   <si>
     <t>STOKER</t>
   </si>
   <si>
+    <t>K43</t>
+  </si>
+  <si>
     <t>Charles Dickens</t>
   </si>
   <si>
     <t>DICKENS</t>
   </si>
   <si>
+    <t>K44</t>
+  </si>
+  <si>
     <t>Daniel Defoe</t>
   </si>
   <si>
     <t>DEFOE</t>
   </si>
   <si>
+    <t>K45</t>
+  </si>
+  <si>
     <t>Emily Bronte</t>
   </si>
   <si>
     <t>BRONTE</t>
   </si>
   <si>
+    <t>K46</t>
+  </si>
+  <si>
     <t>Fyodor Dostoevsky</t>
   </si>
   <si>
     <t>DOSTOEVSKY</t>
   </si>
   <si>
+    <t>K47</t>
+  </si>
+  <si>
     <t>George Orwell</t>
   </si>
   <si>
     <t>ORWELL</t>
   </si>
   <si>
+    <t>K48</t>
+  </si>
+  <si>
     <t>Herman Melville</t>
   </si>
   <si>
     <t>MELVILLE</t>
   </si>
   <si>
+    <t>K49</t>
+  </si>
+  <si>
     <t>Isaac Asimov</t>
   </si>
   <si>
     <t>ASIMOV</t>
   </si>
   <si>
+    <t>K50</t>
+  </si>
+  <si>
     <t>Jane Austen</t>
   </si>
   <si>
     <t>AUSTEN</t>
   </si>
   <si>
+    <t>K51</t>
+  </si>
+  <si>
     <t>Kurt Vonnegut</t>
   </si>
   <si>
@@ -395,6 +551,9 @@
     <t>VONNEGUT</t>
   </si>
   <si>
+    <t>K52</t>
+  </si>
+  <si>
     <t>Lewis Carroll</t>
   </si>
   <si>
@@ -404,6 +563,9 @@
     <t>CARROLL</t>
   </si>
   <si>
+    <t>K53</t>
+  </si>
+  <si>
     <t>Mary Shelley</t>
   </si>
   <si>
@@ -413,6 +575,9 @@
     <t>SHELLEY</t>
   </si>
   <si>
+    <t>K54</t>
+  </si>
+  <si>
     <t>Nathaniel Hawthorne</t>
   </si>
   <si>
@@ -422,6 +587,9 @@
     <t>HAWTHORNE</t>
   </si>
   <si>
+    <t>K55</t>
+  </si>
+  <si>
     <t>Oscar Wilde</t>
   </si>
   <si>
@@ -431,6 +599,9 @@
     <t>WILDE</t>
   </si>
   <si>
+    <t>K56</t>
+  </si>
+  <si>
     <t>Philip K Dick</t>
   </si>
   <si>
@@ -440,6 +611,9 @@
     <t>DICK</t>
   </si>
   <si>
+    <t>K57</t>
+  </si>
+  <si>
     <t>Quentin Blake</t>
   </si>
   <si>
@@ -449,6 +623,9 @@
     <t>BLAKE</t>
   </si>
   <si>
+    <t>K58</t>
+  </si>
+  <si>
     <t>Ray Bradbury</t>
   </si>
   <si>
@@ -458,6 +635,9 @@
     <t>BRADBURY</t>
   </si>
   <si>
+    <t>K59</t>
+  </si>
+  <si>
     <t>Sylvia Plath</t>
   </si>
   <si>
@@ -467,6 +647,9 @@
     <t>PLATH</t>
   </si>
   <si>
+    <t>K60</t>
+  </si>
+  <si>
     <t>Thomas Hardy</t>
   </si>
   <si>
@@ -476,6 +659,9 @@
     <t>HARDY</t>
   </si>
   <si>
+    <t>K61</t>
+  </si>
+  <si>
     <t>Ursula K Le Guin</t>
   </si>
   <si>
@@ -485,6 +671,9 @@
     <t>LE GUIN</t>
   </si>
   <si>
+    <t>K62</t>
+  </si>
+  <si>
     <t>Virginia Woolf</t>
   </si>
   <si>
@@ -494,6 +683,9 @@
     <t>WOOLF</t>
   </si>
   <si>
+    <t>K63</t>
+  </si>
+  <si>
     <t>William Shakespeare</t>
   </si>
   <si>
@@ -503,6 +695,9 @@
     <t>SHAKESPEARE</t>
   </si>
   <si>
+    <t>K64</t>
+  </si>
+  <si>
     <t>Xavier Herbert</t>
   </si>
   <si>
@@ -512,151 +707,232 @@
     <t>HERBERT</t>
   </si>
   <si>
+    <t>K65</t>
+  </si>
+  <si>
     <t>Yann Martel</t>
   </si>
   <si>
     <t>MARTEL</t>
   </si>
   <si>
+    <t>K66</t>
+  </si>
+  <si>
     <t>Albus Dumbledore</t>
   </si>
   <si>
     <t>DUMBLEDORE</t>
   </si>
   <si>
+    <t>K67</t>
+  </si>
+  <si>
     <t>Bilbo Baggins</t>
   </si>
   <si>
     <t>BAGGINS</t>
   </si>
   <si>
+    <t>K68</t>
+  </si>
+  <si>
     <t>Cersei Lannister</t>
   </si>
   <si>
     <t>LANNISTER</t>
   </si>
   <si>
+    <t>K69</t>
+  </si>
+  <si>
     <t>Daenerys Targaryen</t>
   </si>
   <si>
     <t>TARGARYEN</t>
   </si>
   <si>
+    <t>K70</t>
+  </si>
+  <si>
     <t>Eddard Stark</t>
   </si>
   <si>
     <t>STARK</t>
   </si>
   <si>
+    <t>K71</t>
+  </si>
+  <si>
     <t>Frodo Baggins</t>
   </si>
   <si>
+    <t>K72</t>
+  </si>
+  <si>
     <t>Gandalf The Grey</t>
   </si>
   <si>
     <t>GANDALF</t>
   </si>
   <si>
+    <t>K73</t>
+  </si>
+  <si>
     <t>Hermione Granger</t>
   </si>
   <si>
     <t>GRANGER</t>
   </si>
   <si>
+    <t>K74</t>
+  </si>
+  <si>
     <t>Inigo Montoya</t>
   </si>
   <si>
     <t>MONTOYA</t>
   </si>
   <si>
+    <t>K75</t>
+  </si>
+  <si>
     <t>Jon Snow</t>
   </si>
   <si>
     <t>SNOW</t>
   </si>
   <si>
+    <t>K76</t>
+  </si>
+  <si>
     <t>Katniss Everdeen</t>
   </si>
   <si>
     <t>EVERDEEN</t>
   </si>
   <si>
+    <t>K77</t>
+  </si>
+  <si>
     <t>Legolas Greenleaf</t>
   </si>
   <si>
     <t>GREENLEAF</t>
   </si>
   <si>
+    <t>K78</t>
+  </si>
+  <si>
     <t>Moby Dick</t>
   </si>
   <si>
+    <t>K79</t>
+  </si>
+  <si>
     <t>Neville Longbottom</t>
   </si>
   <si>
     <t>LONGBOTTOM</t>
   </si>
   <si>
+    <t>K80</t>
+  </si>
+  <si>
     <t>Othello</t>
   </si>
   <si>
     <t>OTHELLO</t>
   </si>
   <si>
+    <t>K81</t>
+  </si>
+  <si>
     <t>Petyr Baelish</t>
   </si>
   <si>
     <t>BAELISH</t>
   </si>
   <si>
+    <t>K82</t>
+  </si>
+  <si>
     <t>Quirinus Quirrell</t>
   </si>
   <si>
     <t>QUIRRELL</t>
   </si>
   <si>
+    <t>K83</t>
+  </si>
+  <si>
     <t>Ron Weasley</t>
   </si>
   <si>
     <t>WEASLEY</t>
   </si>
   <si>
+    <t>K84</t>
+  </si>
+  <si>
     <t>Samwise Gamgee</t>
   </si>
   <si>
     <t>GAMGEE</t>
   </si>
   <si>
+    <t>K85</t>
+  </si>
+  <si>
     <t>Tyrion Lannister</t>
   </si>
   <si>
+    <t>K86</t>
+  </si>
+  <si>
     <t>Ulysses</t>
   </si>
   <si>
     <t>ULYSSES</t>
   </si>
   <si>
+    <t>K87</t>
+  </si>
+  <si>
     <t>Voldemort</t>
   </si>
   <si>
     <t>VOLDEMORT</t>
   </si>
   <si>
+    <t>K88</t>
+  </si>
+  <si>
     <t>Willy Wonka</t>
   </si>
   <si>
     <t>WONKA</t>
   </si>
   <si>
+    <t>K89</t>
+  </si>
+  <si>
     <t>Xaro Xhoan Daxos</t>
   </si>
   <si>
     <t>DAXOS</t>
   </si>
   <si>
+    <t>K90</t>
+  </si>
+  <si>
     <t>Ygritte</t>
   </si>
   <si>
     <t>YGRITTE</t>
+  </si>
+  <si>
+    <t>K91</t>
   </si>
   <si>
     <t>Shiaijo A</t>
@@ -1526,19 +1802,25 @@
       <c r="E2" t="s">
         <v>15</v>
       </c>
+      <c r="F2" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3">
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="E3" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -1546,13 +1828,16 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="E4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="5">
@@ -1560,13 +1845,16 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D5" t="s">
-        <v>24</v>
+        <v>27</v>
+      </c>
+      <c r="E5" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="6">
@@ -1574,13 +1862,16 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>27</v>
+        <v>31</v>
+      </c>
+      <c r="E6" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="7">
@@ -1588,13 +1879,16 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>30</v>
+        <v>35</v>
+      </c>
+      <c r="E7" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="8">
@@ -1602,13 +1896,16 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D8" t="s">
-        <v>32</v>
+        <v>38</v>
+      </c>
+      <c r="E8" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="9">
@@ -1616,13 +1913,16 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D9" t="s">
-        <v>34</v>
+        <v>41</v>
+      </c>
+      <c r="E9" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="10">
@@ -1630,13 +1930,16 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D10" t="s">
-        <v>36</v>
+        <v>44</v>
+      </c>
+      <c r="E10" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="11">
@@ -1644,13 +1947,16 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D11" t="s">
-        <v>38</v>
+        <v>47</v>
+      </c>
+      <c r="E11" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="12">
@@ -1658,13 +1964,16 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C12" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D12" t="s">
-        <v>40</v>
+        <v>50</v>
+      </c>
+      <c r="E12" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="13">
@@ -1672,13 +1981,16 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="C13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D13" t="s">
-        <v>42</v>
+        <v>53</v>
+      </c>
+      <c r="E13" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="14">
@@ -1686,13 +1998,16 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="C14" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D14" t="s">
-        <v>44</v>
+        <v>56</v>
+      </c>
+      <c r="E14" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="15">
@@ -1700,13 +2015,16 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="C15" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D15" t="s">
-        <v>46</v>
+        <v>59</v>
+      </c>
+      <c r="E15" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="16">
@@ -1714,13 +2032,16 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="C16" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D16" t="s">
-        <v>48</v>
+        <v>62</v>
+      </c>
+      <c r="E16" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -1728,13 +2049,16 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="C17" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D17" t="s">
-        <v>50</v>
+        <v>65</v>
+      </c>
+      <c r="E17" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="18">
@@ -1742,13 +2066,16 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D18" t="s">
-        <v>52</v>
+        <v>68</v>
+      </c>
+      <c r="E18" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="19">
@@ -1756,13 +2083,16 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="C19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D19" t="s">
-        <v>54</v>
+        <v>71</v>
+      </c>
+      <c r="E19" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="20">
@@ -1770,13 +2100,16 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="C20" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D20" t="s">
-        <v>56</v>
+        <v>74</v>
+      </c>
+      <c r="E20" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="21">
@@ -1784,13 +2117,16 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="C21" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D21" t="s">
-        <v>58</v>
+        <v>77</v>
+      </c>
+      <c r="E21" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="22">
@@ -1798,13 +2134,16 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="C22" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D22" t="s">
-        <v>60</v>
+        <v>80</v>
+      </c>
+      <c r="E22" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="23">
@@ -1812,13 +2151,16 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="C23" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D23" t="s">
-        <v>62</v>
+        <v>83</v>
+      </c>
+      <c r="E23" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="24">
@@ -1826,13 +2168,16 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="C24" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="D24" t="s">
-        <v>65</v>
+        <v>87</v>
+      </c>
+      <c r="E24" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="25">
@@ -1840,13 +2185,16 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="C25" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="D25" t="s">
-        <v>68</v>
+        <v>91</v>
+      </c>
+      <c r="E25" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="26">
@@ -1854,13 +2202,16 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="C26" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="D26" t="s">
-        <v>71</v>
+        <v>95</v>
+      </c>
+      <c r="E26" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="27">
@@ -1868,13 +2219,16 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="C27" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D27" t="s">
-        <v>74</v>
+        <v>99</v>
+      </c>
+      <c r="E27" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="28">
@@ -1882,13 +2236,16 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>75</v>
+        <v>101</v>
       </c>
       <c r="C28" t="s">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="D28" t="s">
-        <v>77</v>
+        <v>103</v>
+      </c>
+      <c r="E28" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="29">
@@ -1896,13 +2253,16 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>78</v>
+        <v>105</v>
       </c>
       <c r="C29" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D29" t="s">
-        <v>79</v>
+        <v>106</v>
+      </c>
+      <c r="E29" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="30">
@@ -1910,13 +2270,16 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="C30" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D30" t="s">
-        <v>54</v>
+        <v>71</v>
+      </c>
+      <c r="E30" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="31">
@@ -1924,13 +2287,16 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="C31" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D31" t="s">
-        <v>82</v>
+        <v>111</v>
+      </c>
+      <c r="E31" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="32">
@@ -1938,13 +2304,16 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="C32" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D32" t="s">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="E32" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="33">
@@ -1952,13 +2321,16 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>84</v>
+        <v>115</v>
       </c>
       <c r="C33" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D33" t="s">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="E33" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="34">
@@ -1966,13 +2338,16 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>85</v>
+        <v>117</v>
       </c>
       <c r="C34" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="D34" t="s">
-        <v>24</v>
+        <v>27</v>
+      </c>
+      <c r="E34" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="35">
@@ -1980,13 +2355,16 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>86</v>
+        <v>119</v>
       </c>
       <c r="C35" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="D35" t="s">
-        <v>30</v>
+        <v>35</v>
+      </c>
+      <c r="E35" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="36">
@@ -1994,13 +2372,16 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>87</v>
+        <v>121</v>
       </c>
       <c r="C36" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="D36" t="s">
-        <v>32</v>
+        <v>38</v>
+      </c>
+      <c r="E36" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="37">
@@ -2008,13 +2389,16 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>88</v>
+        <v>123</v>
       </c>
       <c r="C37" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D37" t="s">
-        <v>34</v>
+        <v>41</v>
+      </c>
+      <c r="E37" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="38">
@@ -2022,13 +2406,16 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>89</v>
+        <v>125</v>
       </c>
       <c r="C38" t="s">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="D38" t="s">
-        <v>36</v>
+        <v>44</v>
+      </c>
+      <c r="E38" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="39">
@@ -2036,13 +2423,16 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>90</v>
+        <v>127</v>
       </c>
       <c r="C39" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D39" t="s">
-        <v>38</v>
+        <v>47</v>
+      </c>
+      <c r="E39" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="40">
@@ -2050,13 +2440,16 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>91</v>
+        <v>129</v>
       </c>
       <c r="C40" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D40" t="s">
-        <v>40</v>
+        <v>50</v>
+      </c>
+      <c r="E40" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="41">
@@ -2064,13 +2457,16 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>92</v>
+        <v>131</v>
       </c>
       <c r="C41" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D41" t="s">
-        <v>42</v>
+        <v>53</v>
+      </c>
+      <c r="E41" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="42">
@@ -2078,13 +2474,16 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>93</v>
+        <v>133</v>
       </c>
       <c r="C42" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D42" t="s">
-        <v>44</v>
+        <v>56</v>
+      </c>
+      <c r="E42" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="43">
@@ -2092,13 +2491,16 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>94</v>
+        <v>135</v>
       </c>
       <c r="C43" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D43" t="s">
-        <v>46</v>
+        <v>59</v>
+      </c>
+      <c r="E43" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="44">
@@ -2106,13 +2508,16 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>95</v>
+        <v>137</v>
       </c>
       <c r="C44" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D44" t="s">
-        <v>96</v>
+        <v>138</v>
+      </c>
+      <c r="E44" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="45">
@@ -2120,13 +2525,16 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>97</v>
+        <v>140</v>
       </c>
       <c r="C45" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D45" t="s">
-        <v>98</v>
+        <v>141</v>
+      </c>
+      <c r="E45" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="46">
@@ -2134,13 +2542,16 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>99</v>
+        <v>143</v>
       </c>
       <c r="C46" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D46" t="s">
-        <v>100</v>
+        <v>144</v>
+      </c>
+      <c r="E46" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="47">
@@ -2148,13 +2559,16 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>101</v>
+        <v>146</v>
       </c>
       <c r="C47" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D47" t="s">
-        <v>102</v>
+        <v>147</v>
+      </c>
+      <c r="E47" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="48">
@@ -2162,13 +2576,16 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>103</v>
+        <v>149</v>
       </c>
       <c r="C48" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D48" t="s">
-        <v>104</v>
+        <v>150</v>
+      </c>
+      <c r="E48" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="49">
@@ -2176,13 +2593,16 @@
         <v>46</v>
       </c>
       <c r="B49" t="s">
-        <v>105</v>
+        <v>152</v>
       </c>
       <c r="C49" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="D49" t="s">
-        <v>106</v>
+        <v>153</v>
+      </c>
+      <c r="E49" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="50">
@@ -2190,13 +2610,16 @@
         <v>47</v>
       </c>
       <c r="B50" t="s">
-        <v>107</v>
+        <v>155</v>
       </c>
       <c r="C50" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="D50" t="s">
-        <v>108</v>
+        <v>156</v>
+      </c>
+      <c r="E50" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="51">
@@ -2204,13 +2627,16 @@
         <v>48</v>
       </c>
       <c r="B51" t="s">
-        <v>109</v>
+        <v>158</v>
       </c>
       <c r="C51" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="D51" t="s">
-        <v>110</v>
+        <v>159</v>
+      </c>
+      <c r="E51" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="52">
@@ -2218,13 +2644,16 @@
         <v>49</v>
       </c>
       <c r="B52" t="s">
-        <v>111</v>
+        <v>161</v>
       </c>
       <c r="C52" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D52" t="s">
-        <v>112</v>
+        <v>162</v>
+      </c>
+      <c r="E52" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="53">
@@ -2232,13 +2661,16 @@
         <v>50</v>
       </c>
       <c r="B53" t="s">
-        <v>113</v>
+        <v>164</v>
       </c>
       <c r="C53" t="s">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="D53" t="s">
-        <v>114</v>
+        <v>165</v>
+      </c>
+      <c r="E53" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="54">
@@ -2246,13 +2678,16 @@
         <v>51</v>
       </c>
       <c r="B54" t="s">
-        <v>115</v>
+        <v>167</v>
       </c>
       <c r="C54" t="s">
-        <v>116</v>
+        <v>168</v>
       </c>
       <c r="D54" t="s">
-        <v>117</v>
+        <v>169</v>
+      </c>
+      <c r="E54" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="55">
@@ -2260,13 +2695,16 @@
         <v>52</v>
       </c>
       <c r="B55" t="s">
-        <v>118</v>
+        <v>171</v>
       </c>
       <c r="C55" t="s">
-        <v>119</v>
+        <v>172</v>
       </c>
       <c r="D55" t="s">
-        <v>120</v>
+        <v>173</v>
+      </c>
+      <c r="E55" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="56">
@@ -2274,13 +2712,16 @@
         <v>53</v>
       </c>
       <c r="B56" t="s">
-        <v>121</v>
+        <v>175</v>
       </c>
       <c r="C56" t="s">
-        <v>122</v>
+        <v>176</v>
       </c>
       <c r="D56" t="s">
-        <v>123</v>
+        <v>177</v>
+      </c>
+      <c r="E56" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="57">
@@ -2288,13 +2729,16 @@
         <v>54</v>
       </c>
       <c r="B57" t="s">
-        <v>124</v>
+        <v>179</v>
       </c>
       <c r="C57" t="s">
-        <v>125</v>
+        <v>180</v>
       </c>
       <c r="D57" t="s">
-        <v>126</v>
+        <v>181</v>
+      </c>
+      <c r="E57" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="58">
@@ -2302,13 +2746,16 @@
         <v>55</v>
       </c>
       <c r="B58" t="s">
-        <v>127</v>
+        <v>183</v>
       </c>
       <c r="C58" t="s">
-        <v>128</v>
+        <v>184</v>
       </c>
       <c r="D58" t="s">
-        <v>129</v>
+        <v>185</v>
+      </c>
+      <c r="E58" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="59">
@@ -2316,13 +2763,16 @@
         <v>56</v>
       </c>
       <c r="B59" t="s">
-        <v>130</v>
+        <v>187</v>
       </c>
       <c r="C59" t="s">
-        <v>131</v>
+        <v>188</v>
       </c>
       <c r="D59" t="s">
-        <v>132</v>
+        <v>189</v>
+      </c>
+      <c r="E59" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="60">
@@ -2330,13 +2780,16 @@
         <v>57</v>
       </c>
       <c r="B60" t="s">
-        <v>133</v>
+        <v>191</v>
       </c>
       <c r="C60" t="s">
-        <v>134</v>
+        <v>192</v>
       </c>
       <c r="D60" t="s">
-        <v>135</v>
+        <v>193</v>
+      </c>
+      <c r="E60" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="61">
@@ -2344,13 +2797,16 @@
         <v>58</v>
       </c>
       <c r="B61" t="s">
-        <v>136</v>
+        <v>195</v>
       </c>
       <c r="C61" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="D61" t="s">
-        <v>138</v>
+        <v>197</v>
+      </c>
+      <c r="E61" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="62">
@@ -2358,13 +2814,16 @@
         <v>59</v>
       </c>
       <c r="B62" t="s">
-        <v>139</v>
+        <v>199</v>
       </c>
       <c r="C62" t="s">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="D62" t="s">
-        <v>141</v>
+        <v>201</v>
+      </c>
+      <c r="E62" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="63">
@@ -2372,13 +2831,16 @@
         <v>60</v>
       </c>
       <c r="B63" t="s">
-        <v>142</v>
+        <v>203</v>
       </c>
       <c r="C63" t="s">
-        <v>143</v>
+        <v>204</v>
       </c>
       <c r="D63" t="s">
-        <v>144</v>
+        <v>205</v>
+      </c>
+      <c r="E63" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="64">
@@ -2386,13 +2848,16 @@
         <v>61</v>
       </c>
       <c r="B64" t="s">
-        <v>145</v>
+        <v>207</v>
       </c>
       <c r="C64" t="s">
-        <v>146</v>
+        <v>208</v>
       </c>
       <c r="D64" t="s">
-        <v>147</v>
+        <v>209</v>
+      </c>
+      <c r="E64" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="65">
@@ -2400,13 +2865,16 @@
         <v>62</v>
       </c>
       <c r="B65" t="s">
-        <v>148</v>
+        <v>211</v>
       </c>
       <c r="C65" t="s">
-        <v>149</v>
+        <v>212</v>
       </c>
       <c r="D65" t="s">
-        <v>150</v>
+        <v>213</v>
+      </c>
+      <c r="E65" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="66">
@@ -2414,13 +2882,16 @@
         <v>63</v>
       </c>
       <c r="B66" t="s">
-        <v>151</v>
+        <v>215</v>
       </c>
       <c r="C66" t="s">
-        <v>152</v>
+        <v>216</v>
       </c>
       <c r="D66" t="s">
-        <v>153</v>
+        <v>217</v>
+      </c>
+      <c r="E66" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="67">
@@ -2428,13 +2899,16 @@
         <v>64</v>
       </c>
       <c r="B67" t="s">
-        <v>154</v>
+        <v>219</v>
       </c>
       <c r="C67" t="s">
-        <v>155</v>
+        <v>220</v>
       </c>
       <c r="D67" t="s">
-        <v>156</v>
+        <v>221</v>
+      </c>
+      <c r="E67" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="68">
@@ -2442,13 +2916,16 @@
         <v>65</v>
       </c>
       <c r="B68" t="s">
-        <v>157</v>
+        <v>223</v>
       </c>
       <c r="C68" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D68" t="s">
-        <v>158</v>
+        <v>224</v>
+      </c>
+      <c r="E68" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="69">
@@ -2456,13 +2933,16 @@
         <v>66</v>
       </c>
       <c r="B69" t="s">
-        <v>159</v>
+        <v>226</v>
       </c>
       <c r="C69" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D69" t="s">
-        <v>160</v>
+        <v>227</v>
+      </c>
+      <c r="E69" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="70">
@@ -2470,13 +2950,16 @@
         <v>67</v>
       </c>
       <c r="B70" t="s">
-        <v>161</v>
+        <v>229</v>
       </c>
       <c r="C70" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D70" t="s">
-        <v>162</v>
+        <v>230</v>
+      </c>
+      <c r="E70" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="71">
@@ -2484,13 +2967,16 @@
         <v>68</v>
       </c>
       <c r="B71" t="s">
-        <v>163</v>
+        <v>232</v>
       </c>
       <c r="C71" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D71" t="s">
-        <v>164</v>
+        <v>233</v>
+      </c>
+      <c r="E71" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="72">
@@ -2498,13 +2984,16 @@
         <v>69</v>
       </c>
       <c r="B72" t="s">
-        <v>165</v>
+        <v>235</v>
       </c>
       <c r="C72" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D72" t="s">
-        <v>166</v>
+        <v>236</v>
+      </c>
+      <c r="E72" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="73">
@@ -2512,13 +3001,16 @@
         <v>70</v>
       </c>
       <c r="B73" t="s">
-        <v>167</v>
+        <v>238</v>
       </c>
       <c r="C73" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D73" t="s">
-        <v>168</v>
+        <v>239</v>
+      </c>
+      <c r="E73" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="74">
@@ -2526,13 +3018,16 @@
         <v>71</v>
       </c>
       <c r="B74" t="s">
-        <v>169</v>
+        <v>241</v>
       </c>
       <c r="C74" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="D74" t="s">
-        <v>162</v>
+        <v>230</v>
+      </c>
+      <c r="E74" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="75">
@@ -2540,13 +3035,16 @@
         <v>72</v>
       </c>
       <c r="B75" t="s">
-        <v>170</v>
+        <v>243</v>
       </c>
       <c r="C75" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="D75" t="s">
-        <v>171</v>
+        <v>244</v>
+      </c>
+      <c r="E75" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="76">
@@ -2554,13 +3052,16 @@
         <v>73</v>
       </c>
       <c r="B76" t="s">
-        <v>172</v>
+        <v>246</v>
       </c>
       <c r="C76" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="D76" t="s">
-        <v>173</v>
+        <v>247</v>
+      </c>
+      <c r="E76" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="77">
@@ -2568,13 +3069,16 @@
         <v>74</v>
       </c>
       <c r="B77" t="s">
-        <v>174</v>
+        <v>249</v>
       </c>
       <c r="C77" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D77" t="s">
-        <v>175</v>
+        <v>250</v>
+      </c>
+      <c r="E77" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="78">
@@ -2582,13 +3086,16 @@
         <v>75</v>
       </c>
       <c r="B78" t="s">
-        <v>176</v>
+        <v>252</v>
       </c>
       <c r="C78" t="s">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="D78" t="s">
-        <v>177</v>
+        <v>253</v>
+      </c>
+      <c r="E78" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="79">
@@ -2596,13 +3103,16 @@
         <v>76</v>
       </c>
       <c r="B79" t="s">
-        <v>178</v>
+        <v>255</v>
       </c>
       <c r="C79" t="s">
-        <v>116</v>
+        <v>168</v>
       </c>
       <c r="D79" t="s">
-        <v>179</v>
+        <v>256</v>
+      </c>
+      <c r="E79" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="80">
@@ -2610,13 +3120,16 @@
         <v>77</v>
       </c>
       <c r="B80" t="s">
-        <v>180</v>
+        <v>258</v>
       </c>
       <c r="C80" t="s">
-        <v>119</v>
+        <v>172</v>
       </c>
       <c r="D80" t="s">
-        <v>181</v>
+        <v>259</v>
+      </c>
+      <c r="E80" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="81">
@@ -2624,13 +3137,16 @@
         <v>78</v>
       </c>
       <c r="B81" t="s">
-        <v>182</v>
+        <v>261</v>
       </c>
       <c r="C81" t="s">
-        <v>122</v>
+        <v>176</v>
       </c>
       <c r="D81" t="s">
-        <v>132</v>
+        <v>189</v>
+      </c>
+      <c r="E81" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="82">
@@ -2638,13 +3154,16 @@
         <v>79</v>
       </c>
       <c r="B82" t="s">
-        <v>183</v>
+        <v>263</v>
       </c>
       <c r="C82" t="s">
-        <v>125</v>
+        <v>180</v>
       </c>
       <c r="D82" t="s">
-        <v>184</v>
+        <v>264</v>
+      </c>
+      <c r="E82" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="83">
@@ -2652,13 +3171,16 @@
         <v>80</v>
       </c>
       <c r="B83" t="s">
-        <v>185</v>
+        <v>266</v>
       </c>
       <c r="C83" t="s">
-        <v>128</v>
+        <v>184</v>
       </c>
       <c r="D83" t="s">
-        <v>186</v>
+        <v>267</v>
+      </c>
+      <c r="E83" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="84">
@@ -2666,13 +3188,16 @@
         <v>81</v>
       </c>
       <c r="B84" t="s">
-        <v>187</v>
+        <v>269</v>
       </c>
       <c r="C84" t="s">
-        <v>131</v>
+        <v>188</v>
       </c>
       <c r="D84" t="s">
-        <v>188</v>
+        <v>270</v>
+      </c>
+      <c r="E84" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="85">
@@ -2680,13 +3205,16 @@
         <v>82</v>
       </c>
       <c r="B85" t="s">
-        <v>189</v>
+        <v>272</v>
       </c>
       <c r="C85" t="s">
-        <v>134</v>
+        <v>192</v>
       </c>
       <c r="D85" t="s">
-        <v>190</v>
+        <v>273</v>
+      </c>
+      <c r="E85" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="86">
@@ -2694,13 +3222,16 @@
         <v>83</v>
       </c>
       <c r="B86" t="s">
-        <v>191</v>
+        <v>275</v>
       </c>
       <c r="C86" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="D86" t="s">
-        <v>192</v>
+        <v>276</v>
+      </c>
+      <c r="E86" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="87">
@@ -2708,13 +3239,16 @@
         <v>84</v>
       </c>
       <c r="B87" t="s">
-        <v>193</v>
+        <v>278</v>
       </c>
       <c r="C87" t="s">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="D87" t="s">
-        <v>194</v>
+        <v>279</v>
+      </c>
+      <c r="E87" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="88">
@@ -2722,13 +3256,16 @@
         <v>85</v>
       </c>
       <c r="B88" t="s">
-        <v>195</v>
+        <v>281</v>
       </c>
       <c r="C88" t="s">
-        <v>143</v>
+        <v>204</v>
       </c>
       <c r="D88" t="s">
-        <v>164</v>
+        <v>233</v>
+      </c>
+      <c r="E88" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="89">
@@ -2736,13 +3273,16 @@
         <v>86</v>
       </c>
       <c r="B89" t="s">
-        <v>196</v>
+        <v>283</v>
       </c>
       <c r="C89" t="s">
-        <v>146</v>
+        <v>208</v>
       </c>
       <c r="D89" t="s">
-        <v>197</v>
+        <v>284</v>
+      </c>
+      <c r="E89" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="90">
@@ -2750,13 +3290,16 @@
         <v>87</v>
       </c>
       <c r="B90" t="s">
-        <v>198</v>
+        <v>286</v>
       </c>
       <c r="C90" t="s">
-        <v>149</v>
+        <v>212</v>
       </c>
       <c r="D90" t="s">
-        <v>199</v>
+        <v>287</v>
+      </c>
+      <c r="E90" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="91">
@@ -2764,13 +3307,16 @@
         <v>88</v>
       </c>
       <c r="B91" t="s">
-        <v>200</v>
+        <v>289</v>
       </c>
       <c r="C91" t="s">
-        <v>152</v>
+        <v>216</v>
       </c>
       <c r="D91" t="s">
-        <v>201</v>
+        <v>290</v>
+      </c>
+      <c r="E91" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="92">
@@ -2778,13 +3324,16 @@
         <v>89</v>
       </c>
       <c r="B92" t="s">
-        <v>202</v>
+        <v>292</v>
       </c>
       <c r="C92" t="s">
-        <v>155</v>
+        <v>220</v>
       </c>
       <c r="D92" t="s">
-        <v>203</v>
+        <v>293</v>
+      </c>
+      <c r="E92" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="93">
@@ -2792,13 +3341,16 @@
         <v>90</v>
       </c>
       <c r="B93" t="s">
-        <v>204</v>
+        <v>295</v>
       </c>
       <c r="C93" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D93" t="s">
-        <v>205</v>
+        <v>296</v>
+      </c>
+      <c r="E93" t="s">
+        <v>297</v>
       </c>
     </row>
   </sheetData>
@@ -2838,7 +3390,7 @@
     </row>
     <row r="5">
       <c r="C5" s="16" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6">
@@ -2849,7 +3401,7 @@
     </row>
     <row r="7">
       <c r="C7" s="16" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="12"/>
@@ -2878,7 +3430,7 @@
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="I14" s="12"/>
       <c r="K14" s="12"/>
@@ -2899,7 +3451,7 @@
     </row>
     <row r="17">
       <c r="C17" s="16" t="s">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="G17" s="12"/>
       <c r="K17" s="12"/>
@@ -2915,7 +3467,7 @@
     </row>
     <row r="19">
       <c r="C19" s="16" t="s">
-        <v>79</v>
+        <v>106</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="12"/>
@@ -2933,7 +3485,7 @@
       <c r="C22" s="16"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="K22" s="12"/>
     </row>
@@ -2950,7 +3502,7 @@
     </row>
     <row r="25">
       <c r="C25" s="16" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="G25" s="12"/>
       <c r="H25" s="14"/>
@@ -2969,7 +3521,7 @@
     </row>
     <row r="27">
       <c r="C27" s="16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="12"/>
@@ -2990,7 +3542,7 @@
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I30" s="12"/>
     </row>
@@ -3008,7 +3560,7 @@
     </row>
     <row r="33">
       <c r="C33" s="16" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G33" s="12"/>
     </row>
@@ -3022,7 +3574,7 @@
     </row>
     <row r="35">
       <c r="C35" s="16" t="s">
-        <v>120</v>
+        <v>173</v>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="12"/>
@@ -3070,7 +3622,7 @@
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
       <c r="E6" s="16" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7">
@@ -3084,7 +3636,7 @@
     </row>
     <row r="9">
       <c r="C9" s="16" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="G9" s="12"/>
       <c r="H9" s="14"/>
@@ -3101,7 +3653,7 @@
     </row>
     <row r="11">
       <c r="C11" s="16" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="12"/>
@@ -3121,7 +3673,7 @@
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="I14" s="12"/>
       <c r="K14" s="12"/>
@@ -3142,7 +3694,7 @@
     </row>
     <row r="17">
       <c r="C17" s="16" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G17" s="12"/>
       <c r="K17" s="12"/>
@@ -3158,7 +3710,7 @@
     </row>
     <row r="19">
       <c r="C19" s="16" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="12"/>
@@ -3176,7 +3728,7 @@
       <c r="C22" s="16"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="K22" s="12"/>
     </row>
@@ -3193,7 +3745,7 @@
     </row>
     <row r="25">
       <c r="C25" s="16" t="s">
-        <v>117</v>
+        <v>169</v>
       </c>
       <c r="G25" s="12"/>
       <c r="H25" s="14"/>
@@ -3212,7 +3764,7 @@
     </row>
     <row r="27">
       <c r="C27" s="16" t="s">
-        <v>96</v>
+        <v>138</v>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="12"/>
@@ -3233,7 +3785,7 @@
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
-        <v>98</v>
+        <v>141</v>
       </c>
       <c r="I30" s="12"/>
     </row>
@@ -3251,7 +3803,7 @@
     </row>
     <row r="33">
       <c r="C33" s="16" t="s">
-        <v>100</v>
+        <v>144</v>
       </c>
       <c r="G33" s="12"/>
     </row>
@@ -3265,7 +3817,7 @@
     </row>
     <row r="35">
       <c r="C35" s="16" t="s">
-        <v>102</v>
+        <v>147</v>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="12"/>
@@ -3311,7 +3863,7 @@
     </row>
     <row r="5">
       <c r="C5" s="16" t="s">
-        <v>104</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6">
@@ -3322,7 +3874,7 @@
     </row>
     <row r="7">
       <c r="C7" s="16" t="s">
-        <v>106</v>
+        <v>153</v>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="12"/>
@@ -3351,7 +3903,7 @@
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
-        <v>108</v>
+        <v>156</v>
       </c>
       <c r="I14" s="12"/>
       <c r="K14" s="12"/>
@@ -3372,7 +3924,7 @@
     </row>
     <row r="17">
       <c r="C17" s="16" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="G17" s="12"/>
       <c r="K17" s="12"/>
@@ -3388,7 +3940,7 @@
     </row>
     <row r="19">
       <c r="C19" s="16" t="s">
-        <v>112</v>
+        <v>162</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="12"/>
@@ -3406,7 +3958,7 @@
       <c r="C22" s="16"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16" t="s">
-        <v>114</v>
+        <v>165</v>
       </c>
       <c r="K22" s="12"/>
     </row>
@@ -3423,7 +3975,7 @@
     </row>
     <row r="25">
       <c r="C25" s="16" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="G25" s="12"/>
       <c r="H25" s="14"/>
@@ -3442,7 +3994,7 @@
     </row>
     <row r="27">
       <c r="C27" s="16" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="12"/>
@@ -3463,7 +4015,7 @@
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
-        <v>123</v>
+        <v>177</v>
       </c>
       <c r="I30" s="12"/>
     </row>
@@ -3481,7 +4033,7 @@
     </row>
     <row r="33">
       <c r="C33" s="16" t="s">
-        <v>126</v>
+        <v>181</v>
       </c>
       <c r="G33" s="12"/>
     </row>
@@ -3495,7 +4047,7 @@
     </row>
     <row r="35">
       <c r="C35" s="16" t="s">
-        <v>129</v>
+        <v>185</v>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="12"/>
@@ -3543,7 +4095,7 @@
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
       <c r="E6" s="16" t="s">
-        <v>132</v>
+        <v>189</v>
       </c>
     </row>
     <row r="7">
@@ -3557,7 +4109,7 @@
     </row>
     <row r="9">
       <c r="C9" s="16" t="s">
-        <v>135</v>
+        <v>193</v>
       </c>
       <c r="G9" s="12"/>
       <c r="H9" s="14"/>
@@ -3574,7 +4126,7 @@
     </row>
     <row r="11">
       <c r="C11" s="16" t="s">
-        <v>138</v>
+        <v>197</v>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="12"/>
@@ -3594,7 +4146,7 @@
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="I14" s="12"/>
       <c r="K14" s="12"/>
@@ -3615,7 +4167,7 @@
     </row>
     <row r="17">
       <c r="C17" s="16" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="G17" s="12"/>
       <c r="K17" s="12"/>
@@ -3631,7 +4183,7 @@
     </row>
     <row r="19">
       <c r="C19" s="16" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="12"/>
@@ -3649,7 +4201,7 @@
       <c r="C22" s="16"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16" t="s">
-        <v>150</v>
+        <v>213</v>
       </c>
       <c r="K22" s="12"/>
     </row>
@@ -3666,7 +4218,7 @@
     </row>
     <row r="25">
       <c r="C25" s="16" t="s">
-        <v>153</v>
+        <v>217</v>
       </c>
       <c r="G25" s="12"/>
       <c r="H25" s="14"/>
@@ -3685,7 +4237,7 @@
     </row>
     <row r="27">
       <c r="C27" s="16" t="s">
-        <v>156</v>
+        <v>221</v>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="12"/>
@@ -3706,7 +4258,7 @@
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
-        <v>171</v>
+        <v>244</v>
       </c>
       <c r="I30" s="12"/>
     </row>
@@ -3724,7 +4276,7 @@
     </row>
     <row r="33">
       <c r="C33" s="16" t="s">
-        <v>160</v>
+        <v>227</v>
       </c>
       <c r="G33" s="12"/>
     </row>
@@ -3738,7 +4290,7 @@
     </row>
     <row r="35">
       <c r="C35" s="16" t="s">
-        <v>162</v>
+        <v>230</v>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="12"/>
@@ -3784,7 +4336,7 @@
     </row>
     <row r="5">
       <c r="C5" s="16" t="s">
-        <v>164</v>
+        <v>233</v>
       </c>
     </row>
     <row r="6">
@@ -3795,7 +4347,7 @@
     </row>
     <row r="7">
       <c r="C7" s="16" t="s">
-        <v>166</v>
+        <v>236</v>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="12"/>
@@ -3824,7 +4376,7 @@
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
-        <v>168</v>
+        <v>239</v>
       </c>
       <c r="I14" s="12"/>
       <c r="K14" s="12"/>
@@ -3845,7 +4397,7 @@
     </row>
     <row r="17">
       <c r="C17" s="16" t="s">
-        <v>162</v>
+        <v>230</v>
       </c>
       <c r="G17" s="12"/>
       <c r="K17" s="12"/>
@@ -3861,7 +4413,7 @@
     </row>
     <row r="19">
       <c r="C19" s="16" t="s">
-        <v>158</v>
+        <v>224</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="12"/>
@@ -3879,7 +4431,7 @@
       <c r="C22" s="16"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16" t="s">
-        <v>173</v>
+        <v>247</v>
       </c>
       <c r="K22" s="12"/>
     </row>
@@ -3896,7 +4448,7 @@
     </row>
     <row r="25">
       <c r="C25" s="16" t="s">
-        <v>175</v>
+        <v>250</v>
       </c>
       <c r="G25" s="12"/>
       <c r="H25" s="14"/>
@@ -3915,7 +4467,7 @@
     </row>
     <row r="27">
       <c r="C27" s="16" t="s">
-        <v>177</v>
+        <v>253</v>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="12"/>
@@ -3936,7 +4488,7 @@
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I30" s="12"/>
     </row>
@@ -3954,7 +4506,7 @@
     </row>
     <row r="33">
       <c r="C33" s="16" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G33" s="12"/>
     </row>
@@ -3968,7 +4520,7 @@
     </row>
     <row r="35">
       <c r="C35" s="16" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="12"/>
@@ -4016,7 +4568,7 @@
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
       <c r="E6" s="16" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7">
@@ -4030,7 +4582,7 @@
     </row>
     <row r="9">
       <c r="C9" s="16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G9" s="12"/>
       <c r="H9" s="14"/>
@@ -4047,7 +4599,7 @@
     </row>
     <row r="11">
       <c r="C11" s="16" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="12"/>
@@ -4067,7 +4619,7 @@
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="I14" s="12"/>
       <c r="K14" s="12"/>
@@ -4088,7 +4640,7 @@
     </row>
     <row r="17">
       <c r="C17" s="16" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G17" s="12"/>
       <c r="K17" s="12"/>
@@ -4104,7 +4656,7 @@
     </row>
     <row r="19">
       <c r="C19" s="16" t="s">
-        <v>194</v>
+        <v>279</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="12"/>
@@ -4122,7 +4674,7 @@
       <c r="C22" s="16"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16" t="s">
-        <v>164</v>
+        <v>233</v>
       </c>
       <c r="K22" s="12"/>
     </row>
@@ -4139,7 +4691,7 @@
     </row>
     <row r="25">
       <c r="C25" s="16" t="s">
-        <v>197</v>
+        <v>284</v>
       </c>
       <c r="G25" s="12"/>
       <c r="H25" s="14"/>
@@ -4158,7 +4710,7 @@
     </row>
     <row r="27">
       <c r="C27" s="16" t="s">
-        <v>199</v>
+        <v>287</v>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="12"/>
@@ -4179,7 +4731,7 @@
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
-        <v>201</v>
+        <v>290</v>
       </c>
       <c r="I30" s="12"/>
     </row>
@@ -4197,7 +4749,7 @@
     </row>
     <row r="33">
       <c r="C33" s="16" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G33" s="12"/>
     </row>
@@ -4211,7 +4763,7 @@
     </row>
     <row r="35">
       <c r="C35" s="16" t="s">
-        <v>205</v>
+        <v>296</v>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="12"/>
@@ -4235,368 +4787,368 @@
   </cols>
   <sheetData>
     <row r="1" ht="270" customHeight="true">
-      <c r="A1" s="17">
-        <v>21</v>
+      <c r="A1" s="17" t="str">
+        <f>'data'!$E$24</f>
       </c>
       <c r="B1" s="18" t="str">
         <f>'data'!D24</f>
       </c>
     </row>
     <row r="2" ht="270" customHeight="true">
-      <c r="A2" s="17">
-        <v>80</v>
+      <c r="A2" s="17" t="str">
+        <f>'data'!$E$83</f>
       </c>
       <c r="B2" s="18" t="str">
         <f>'data'!D83</f>
       </c>
     </row>
     <row r="3" ht="270" customHeight="true">
-      <c r="A3" s="17">
-        <v>81</v>
+      <c r="A3" s="17" t="str">
+        <f>'data'!$E$84</f>
       </c>
       <c r="B3" s="18" t="str">
         <f>'data'!D84</f>
       </c>
     </row>
     <row r="4" ht="270" customHeight="true">
-      <c r="A4" s="17">
-        <v>76</v>
+      <c r="A4" s="17" t="str">
+        <f>'data'!$E$79</f>
       </c>
       <c r="B4" s="18" t="str">
         <f>'data'!D79</f>
       </c>
     </row>
     <row r="5" ht="270" customHeight="true">
-      <c r="A5" s="17">
-        <v>77</v>
+      <c r="A5" s="17" t="str">
+        <f>'data'!$E$80</f>
       </c>
       <c r="B5" s="18" t="str">
         <f>'data'!D80</f>
       </c>
     </row>
     <row r="6" ht="270" customHeight="true">
-      <c r="A6" s="17">
-        <v>5</v>
+      <c r="A6" s="17" t="str">
+        <f>'data'!$E$8</f>
       </c>
       <c r="B6" s="18" t="str">
         <f>'data'!D8</f>
       </c>
     </row>
     <row r="7" ht="270" customHeight="true">
-      <c r="A7" s="17">
-        <v>78</v>
+      <c r="A7" s="17" t="str">
+        <f>'data'!$E$81</f>
       </c>
       <c r="B7" s="18" t="str">
         <f>'data'!D81</f>
       </c>
     </row>
     <row r="8" ht="270" customHeight="true">
-      <c r="A8" s="17">
-        <v>79</v>
+      <c r="A8" s="17" t="str">
+        <f>'data'!$E$82</f>
       </c>
       <c r="B8" s="18" t="str">
         <f>'data'!D82</f>
       </c>
     </row>
     <row r="9" ht="270" customHeight="true">
-      <c r="A9" s="17">
-        <v>82</v>
+      <c r="A9" s="17" t="str">
+        <f>'data'!$E$85</f>
       </c>
       <c r="B9" s="18" t="str">
         <f>'data'!D85</f>
       </c>
     </row>
     <row r="10" ht="270" customHeight="true">
-      <c r="A10" s="17">
-        <v>83</v>
+      <c r="A10" s="17" t="str">
+        <f>'data'!$E$86</f>
       </c>
       <c r="B10" s="18" t="str">
         <f>'data'!D86</f>
       </c>
     </row>
     <row r="11" ht="270" customHeight="true">
-      <c r="A11" s="17">
-        <v>48</v>
+      <c r="A11" s="17" t="str">
+        <f>'data'!$E$51</f>
       </c>
       <c r="B11" s="18" t="str">
         <f>'data'!D51</f>
       </c>
     </row>
     <row r="12" ht="270" customHeight="true">
-      <c r="A12" s="17">
-        <v>11</v>
+      <c r="A12" s="17" t="str">
+        <f>'data'!$E$14</f>
       </c>
       <c r="B12" s="18" t="str">
         <f>'data'!D14</f>
       </c>
     </row>
     <row r="13" ht="270" customHeight="true">
-      <c r="A13" s="17">
-        <v>12</v>
+      <c r="A13" s="17" t="str">
+        <f>'data'!$E$15</f>
       </c>
       <c r="B13" s="18" t="str">
         <f>'data'!D15</f>
       </c>
     </row>
     <row r="14" ht="270" customHeight="true">
-      <c r="A14" s="17">
-        <v>13</v>
+      <c r="A14" s="17" t="str">
+        <f>'data'!$E$16</f>
       </c>
       <c r="B14" s="18" t="str">
         <f>'data'!D16</f>
       </c>
     </row>
     <row r="15" ht="270" customHeight="true">
-      <c r="A15" s="17">
-        <v>14</v>
+      <c r="A15" s="17" t="str">
+        <f>'data'!$E$17</f>
       </c>
       <c r="B15" s="18" t="str">
         <f>'data'!D17</f>
       </c>
     </row>
     <row r="16" ht="270" customHeight="true">
-      <c r="A16" s="17">
-        <v>15</v>
+      <c r="A16" s="17" t="str">
+        <f>'data'!$E$18</f>
       </c>
       <c r="B16" s="18" t="str">
         <f>'data'!D18</f>
       </c>
     </row>
     <row r="17" ht="270" customHeight="true">
-      <c r="A17" s="17">
-        <v>16</v>
+      <c r="A17" s="17" t="str">
+        <f>'data'!$E$19</f>
       </c>
       <c r="B17" s="18" t="str">
         <f>'data'!D19</f>
       </c>
     </row>
     <row r="18" ht="270" customHeight="true">
-      <c r="A18" s="17">
-        <v>59</v>
+      <c r="A18" s="17" t="str">
+        <f>'data'!$E$62</f>
       </c>
       <c r="B18" s="18" t="str">
         <f>'data'!D62</f>
       </c>
     </row>
     <row r="19" ht="270" customHeight="true">
-      <c r="A19" s="17">
-        <v>60</v>
+      <c r="A19" s="17" t="str">
+        <f>'data'!$E$63</f>
       </c>
       <c r="B19" s="18" t="str">
         <f>'data'!D63</f>
       </c>
     </row>
     <row r="20" ht="270" customHeight="true">
-      <c r="A20" s="17">
-        <v>61</v>
+      <c r="A20" s="17" t="str">
+        <f>'data'!$E$64</f>
       </c>
       <c r="B20" s="18" t="str">
         <f>'data'!D64</f>
       </c>
     </row>
     <row r="21" ht="270" customHeight="true">
-      <c r="A21" s="17">
-        <v>20</v>
+      <c r="A21" s="17" t="str">
+        <f>'data'!$E$23</f>
       </c>
       <c r="B21" s="18" t="str">
         <f>'data'!D23</f>
       </c>
     </row>
     <row r="22" ht="270" customHeight="true">
-      <c r="A22" s="17">
-        <v>89</v>
+      <c r="A22" s="17" t="str">
+        <f>'data'!$E$92</f>
       </c>
       <c r="B22" s="18" t="str">
         <f>'data'!D92</f>
       </c>
     </row>
     <row r="23" ht="270" customHeight="true">
-      <c r="A23" s="17">
-        <v>22</v>
+      <c r="A23" s="17" t="str">
+        <f>'data'!$E$25</f>
       </c>
       <c r="B23" s="18" t="str">
         <f>'data'!D25</f>
       </c>
     </row>
     <row r="24" ht="270" customHeight="true">
-      <c r="A24" s="17">
-        <v>23</v>
+      <c r="A24" s="17" t="str">
+        <f>'data'!$E$26</f>
       </c>
       <c r="B24" s="18" t="str">
         <f>'data'!D26</f>
       </c>
     </row>
     <row r="25" ht="270" customHeight="true">
-      <c r="A25" s="17">
-        <v>24</v>
+      <c r="A25" s="17" t="str">
+        <f>'data'!$E$27</f>
       </c>
       <c r="B25" s="18" t="str">
         <f>'data'!D27</f>
       </c>
     </row>
     <row r="26" ht="270" customHeight="true">
-      <c r="A26" s="17">
-        <v>25</v>
+      <c r="A26" s="17" t="str">
+        <f>'data'!$E$28</f>
       </c>
       <c r="B26" s="18" t="str">
         <f>'data'!D28</f>
       </c>
     </row>
     <row r="27" ht="270" customHeight="true">
-      <c r="A27" s="17">
-        <v>26</v>
+      <c r="A27" s="17" t="str">
+        <f>'data'!$E$29</f>
       </c>
       <c r="B27" s="18" t="str">
         <f>'data'!D29</f>
       </c>
     </row>
     <row r="28" ht="270" customHeight="true">
-      <c r="A28" s="17">
-        <v>27</v>
+      <c r="A28" s="17" t="str">
+        <f>'data'!$E$30</f>
       </c>
       <c r="B28" s="18" t="str">
         <f>'data'!D30</f>
       </c>
     </row>
     <row r="29" ht="270" customHeight="true">
-      <c r="A29" s="17">
-        <v>28</v>
+      <c r="A29" s="17" t="str">
+        <f>'data'!$E$31</f>
       </c>
       <c r="B29" s="18" t="str">
         <f>'data'!D31</f>
       </c>
     </row>
     <row r="30" ht="270" customHeight="true">
-      <c r="A30" s="17">
-        <v>29</v>
+      <c r="A30" s="17" t="str">
+        <f>'data'!$E$32</f>
       </c>
       <c r="B30" s="18" t="str">
         <f>'data'!D32</f>
       </c>
     </row>
     <row r="31" ht="270" customHeight="true">
-      <c r="A31" s="17">
-        <v>30</v>
+      <c r="A31" s="17" t="str">
+        <f>'data'!$E$33</f>
       </c>
       <c r="B31" s="18" t="str">
         <f>'data'!D33</f>
       </c>
     </row>
     <row r="32" ht="270" customHeight="true">
-      <c r="A32" s="17">
-        <v>31</v>
+      <c r="A32" s="17" t="str">
+        <f>'data'!$E$34</f>
       </c>
       <c r="B32" s="18" t="str">
         <f>'data'!D34</f>
       </c>
     </row>
     <row r="33" ht="270" customHeight="true">
-      <c r="A33" s="17">
-        <v>52</v>
+      <c r="A33" s="17" t="str">
+        <f>'data'!$E$55</f>
       </c>
       <c r="B33" s="18" t="str">
         <f>'data'!D55</f>
       </c>
     </row>
     <row r="34" ht="270" customHeight="true">
-      <c r="A34" s="17">
-        <v>33</v>
+      <c r="A34" s="17" t="str">
+        <f>'data'!$E$36</f>
       </c>
       <c r="B34" s="18" t="str">
         <f>'data'!D36</f>
       </c>
     </row>
     <row r="35" ht="270" customHeight="true">
-      <c r="A35" s="17">
-        <v>34</v>
+      <c r="A35" s="17" t="str">
+        <f>'data'!$E$37</f>
       </c>
       <c r="B35" s="18" t="str">
         <f>'data'!D37</f>
       </c>
     </row>
     <row r="36" ht="270" customHeight="true">
-      <c r="A36" s="17">
-        <v>35</v>
+      <c r="A36" s="17" t="str">
+        <f>'data'!$E$38</f>
       </c>
       <c r="B36" s="18" t="str">
         <f>'data'!D38</f>
       </c>
     </row>
     <row r="37" ht="270" customHeight="true">
-      <c r="A37" s="17">
-        <v>36</v>
+      <c r="A37" s="17" t="str">
+        <f>'data'!$E$39</f>
       </c>
       <c r="B37" s="18" t="str">
         <f>'data'!D39</f>
       </c>
     </row>
     <row r="38" ht="270" customHeight="true">
-      <c r="A38" s="17">
-        <v>37</v>
+      <c r="A38" s="17" t="str">
+        <f>'data'!$E$40</f>
       </c>
       <c r="B38" s="18" t="str">
         <f>'data'!D40</f>
       </c>
     </row>
     <row r="39" ht="270" customHeight="true">
-      <c r="A39" s="17">
-        <v>38</v>
+      <c r="A39" s="17" t="str">
+        <f>'data'!$E$41</f>
       </c>
       <c r="B39" s="18" t="str">
         <f>'data'!D41</f>
       </c>
     </row>
     <row r="40" ht="270" customHeight="true">
-      <c r="A40" s="17">
-        <v>39</v>
+      <c r="A40" s="17" t="str">
+        <f>'data'!$E$42</f>
       </c>
       <c r="B40" s="18" t="str">
         <f>'data'!D42</f>
       </c>
     </row>
     <row r="41" ht="270" customHeight="true">
-      <c r="A41" s="17">
-        <v>51</v>
+      <c r="A41" s="17" t="str">
+        <f>'data'!$E$54</f>
       </c>
       <c r="B41" s="18" t="str">
         <f>'data'!D54</f>
       </c>
     </row>
     <row r="42" ht="270" customHeight="true">
-      <c r="A42" s="17">
-        <v>41</v>
+      <c r="A42" s="17" t="str">
+        <f>'data'!$E$44</f>
       </c>
       <c r="B42" s="18" t="str">
         <f>'data'!D44</f>
       </c>
     </row>
     <row r="43" ht="270" customHeight="true">
-      <c r="A43" s="17">
-        <v>42</v>
+      <c r="A43" s="17" t="str">
+        <f>'data'!$E$45</f>
       </c>
       <c r="B43" s="18" t="str">
         <f>'data'!D45</f>
       </c>
     </row>
     <row r="44" ht="270" customHeight="true">
-      <c r="A44" s="17">
-        <v>43</v>
+      <c r="A44" s="17" t="str">
+        <f>'data'!$E$46</f>
       </c>
       <c r="B44" s="18" t="str">
         <f>'data'!D46</f>
       </c>
     </row>
     <row r="45" ht="270" customHeight="true">
-      <c r="A45" s="17">
-        <v>44</v>
+      <c r="A45" s="17" t="str">
+        <f>'data'!$E$47</f>
       </c>
       <c r="B45" s="18" t="str">
         <f>'data'!D47</f>
       </c>
     </row>
     <row r="46" ht="270" customHeight="true">
-      <c r="A46" s="17">
-        <v>45</v>
+      <c r="A46" s="17" t="str">
+        <f>'data'!$E$48</f>
       </c>
       <c r="B46" s="18" t="str">
         <f>'data'!D48</f>
@@ -4636,360 +5188,360 @@
   </cols>
   <sheetData>
     <row r="1" ht="270" customHeight="true">
-      <c r="A1" s="17">
-        <v>46</v>
+      <c r="A1" s="17" t="str">
+        <f>'data'!$E$49</f>
       </c>
       <c r="B1" s="18" t="str">
         <f>'data'!D49</f>
       </c>
     </row>
     <row r="2" ht="270" customHeight="true">
-      <c r="A2" s="17">
-        <v>47</v>
+      <c r="A2" s="17" t="str">
+        <f>'data'!$E$50</f>
       </c>
       <c r="B2" s="18" t="str">
         <f>'data'!D50</f>
       </c>
     </row>
     <row r="3" ht="270" customHeight="true">
-      <c r="A3" s="17">
-        <v>10</v>
+      <c r="A3" s="17" t="str">
+        <f>'data'!$E$13</f>
       </c>
       <c r="B3" s="18" t="str">
         <f>'data'!D13</f>
       </c>
     </row>
     <row r="4" ht="270" customHeight="true">
-      <c r="A4" s="17">
-        <v>49</v>
+      <c r="A4" s="17" t="str">
+        <f>'data'!$E$52</f>
       </c>
       <c r="B4" s="18" t="str">
         <f>'data'!D52</f>
       </c>
     </row>
     <row r="5" ht="270" customHeight="true">
-      <c r="A5" s="17">
-        <v>50</v>
+      <c r="A5" s="17" t="str">
+        <f>'data'!$E$53</f>
       </c>
       <c r="B5" s="18" t="str">
         <f>'data'!D53</f>
       </c>
     </row>
     <row r="6" ht="270" customHeight="true">
-      <c r="A6" s="17">
-        <v>40</v>
+      <c r="A6" s="17" t="str">
+        <f>'data'!$E$43</f>
       </c>
       <c r="B6" s="18" t="str">
         <f>'data'!D43</f>
       </c>
     </row>
     <row r="7" ht="270" customHeight="true">
-      <c r="A7" s="17">
-        <v>32</v>
+      <c r="A7" s="17" t="str">
+        <f>'data'!$E$35</f>
       </c>
       <c r="B7" s="18" t="str">
         <f>'data'!D35</f>
       </c>
     </row>
     <row r="8" ht="270" customHeight="true">
-      <c r="A8" s="17">
-        <v>53</v>
+      <c r="A8" s="17" t="str">
+        <f>'data'!$E$56</f>
       </c>
       <c r="B8" s="18" t="str">
         <f>'data'!D56</f>
       </c>
     </row>
     <row r="9" ht="270" customHeight="true">
-      <c r="A9" s="17">
-        <v>54</v>
+      <c r="A9" s="17" t="str">
+        <f>'data'!$E$57</f>
       </c>
       <c r="B9" s="18" t="str">
         <f>'data'!D57</f>
       </c>
     </row>
     <row r="10" ht="270" customHeight="true">
-      <c r="A10" s="17">
-        <v>55</v>
+      <c r="A10" s="17" t="str">
+        <f>'data'!$E$58</f>
       </c>
       <c r="B10" s="18" t="str">
         <f>'data'!D58</f>
       </c>
     </row>
     <row r="11" ht="270" customHeight="true">
-      <c r="A11" s="17">
-        <v>56</v>
+      <c r="A11" s="17" t="str">
+        <f>'data'!$E$59</f>
       </c>
       <c r="B11" s="18" t="str">
         <f>'data'!D59</f>
       </c>
     </row>
     <row r="12" ht="270" customHeight="true">
-      <c r="A12" s="17">
-        <v>57</v>
+      <c r="A12" s="17" t="str">
+        <f>'data'!$E$60</f>
       </c>
       <c r="B12" s="18" t="str">
         <f>'data'!D60</f>
       </c>
     </row>
     <row r="13" ht="270" customHeight="true">
-      <c r="A13" s="17">
-        <v>58</v>
+      <c r="A13" s="17" t="str">
+        <f>'data'!$E$61</f>
       </c>
       <c r="B13" s="18" t="str">
         <f>'data'!D61</f>
       </c>
     </row>
     <row r="14" ht="270" customHeight="true">
-      <c r="A14" s="17">
-        <v>17</v>
+      <c r="A14" s="17" t="str">
+        <f>'data'!$E$20</f>
       </c>
       <c r="B14" s="18" t="str">
         <f>'data'!D20</f>
       </c>
     </row>
     <row r="15" ht="270" customHeight="true">
-      <c r="A15" s="17">
-        <v>18</v>
+      <c r="A15" s="17" t="str">
+        <f>'data'!$E$21</f>
       </c>
       <c r="B15" s="18" t="str">
         <f>'data'!D21</f>
       </c>
     </row>
     <row r="16" ht="270" customHeight="true">
-      <c r="A16" s="17">
-        <v>19</v>
+      <c r="A16" s="17" t="str">
+        <f>'data'!$E$22</f>
       </c>
       <c r="B16" s="18" t="str">
         <f>'data'!D22</f>
       </c>
     </row>
     <row r="17" ht="270" customHeight="true">
-      <c r="A17" s="17">
-        <v>62</v>
+      <c r="A17" s="17" t="str">
+        <f>'data'!$E$65</f>
       </c>
       <c r="B17" s="18" t="str">
         <f>'data'!D65</f>
       </c>
     </row>
     <row r="18" ht="270" customHeight="true">
-      <c r="A18" s="17">
-        <v>63</v>
+      <c r="A18" s="17" t="str">
+        <f>'data'!$E$66</f>
       </c>
       <c r="B18" s="18" t="str">
         <f>'data'!D66</f>
       </c>
     </row>
     <row r="19" ht="270" customHeight="true">
-      <c r="A19" s="17">
-        <v>64</v>
+      <c r="A19" s="17" t="str">
+        <f>'data'!$E$67</f>
       </c>
       <c r="B19" s="18" t="str">
         <f>'data'!D67</f>
       </c>
     </row>
     <row r="20" ht="270" customHeight="true">
-      <c r="A20" s="17">
-        <v>72</v>
+      <c r="A20" s="17" t="str">
+        <f>'data'!$E$75</f>
       </c>
       <c r="B20" s="18" t="str">
         <f>'data'!D75</f>
       </c>
     </row>
     <row r="21" ht="270" customHeight="true">
-      <c r="A21" s="17">
-        <v>66</v>
+      <c r="A21" s="17" t="str">
+        <f>'data'!$E$69</f>
       </c>
       <c r="B21" s="18" t="str">
         <f>'data'!D69</f>
       </c>
     </row>
     <row r="22" ht="270" customHeight="true">
-      <c r="A22" s="17">
-        <v>67</v>
+      <c r="A22" s="17" t="str">
+        <f>'data'!$E$70</f>
       </c>
       <c r="B22" s="18" t="str">
         <f>'data'!D70</f>
       </c>
     </row>
     <row r="23" ht="270" customHeight="true">
-      <c r="A23" s="17">
-        <v>68</v>
+      <c r="A23" s="17" t="str">
+        <f>'data'!$E$71</f>
       </c>
       <c r="B23" s="18" t="str">
         <f>'data'!D71</f>
       </c>
     </row>
     <row r="24" ht="270" customHeight="true">
-      <c r="A24" s="17">
-        <v>69</v>
+      <c r="A24" s="17" t="str">
+        <f>'data'!$E$72</f>
       </c>
       <c r="B24" s="18" t="str">
         <f>'data'!D72</f>
       </c>
     </row>
     <row r="25" ht="270" customHeight="true">
-      <c r="A25" s="17">
-        <v>70</v>
+      <c r="A25" s="17" t="str">
+        <f>'data'!$E$73</f>
       </c>
       <c r="B25" s="18" t="str">
         <f>'data'!D73</f>
       </c>
     </row>
     <row r="26" ht="270" customHeight="true">
-      <c r="A26" s="17">
-        <v>71</v>
+      <c r="A26" s="17" t="str">
+        <f>'data'!$E$74</f>
       </c>
       <c r="B26" s="18" t="str">
         <f>'data'!D74</f>
       </c>
     </row>
     <row r="27" ht="270" customHeight="true">
-      <c r="A27" s="17">
-        <v>65</v>
+      <c r="A27" s="17" t="str">
+        <f>'data'!$E$68</f>
       </c>
       <c r="B27" s="18" t="str">
         <f>'data'!D68</f>
       </c>
     </row>
     <row r="28" ht="270" customHeight="true">
-      <c r="A28" s="17">
-        <v>73</v>
+      <c r="A28" s="17" t="str">
+        <f>'data'!$E$76</f>
       </c>
       <c r="B28" s="18" t="str">
         <f>'data'!D76</f>
       </c>
     </row>
     <row r="29" ht="270" customHeight="true">
-      <c r="A29" s="17">
-        <v>74</v>
+      <c r="A29" s="17" t="str">
+        <f>'data'!$E$77</f>
       </c>
       <c r="B29" s="18" t="str">
         <f>'data'!D77</f>
       </c>
     </row>
     <row r="30" ht="270" customHeight="true">
-      <c r="A30" s="17">
-        <v>75</v>
+      <c r="A30" s="17" t="str">
+        <f>'data'!$E$78</f>
       </c>
       <c r="B30" s="18" t="str">
         <f>'data'!D78</f>
       </c>
     </row>
     <row r="31" ht="270" customHeight="true">
-      <c r="A31" s="17">
-        <v>3</v>
+      <c r="A31" s="17" t="str">
+        <f>'data'!$E$6</f>
       </c>
       <c r="B31" s="18" t="str">
         <f>'data'!D6</f>
       </c>
     </row>
     <row r="32" ht="270" customHeight="true">
-      <c r="A32" s="17">
-        <v>4</v>
+      <c r="A32" s="17" t="str">
+        <f>'data'!$E$7</f>
       </c>
       <c r="B32" s="18" t="str">
         <f>'data'!D7</f>
       </c>
     </row>
     <row r="33" ht="270" customHeight="true">
-      <c r="A33" s="17">
-        <v>6</v>
+      <c r="A33" s="17" t="str">
+        <f>'data'!$E$9</f>
       </c>
       <c r="B33" s="18" t="str">
         <f>'data'!D9</f>
       </c>
     </row>
     <row r="34" ht="270" customHeight="true">
-      <c r="A34" s="17">
-        <v>7</v>
+      <c r="A34" s="17" t="str">
+        <f>'data'!$E$10</f>
       </c>
       <c r="B34" s="18" t="str">
         <f>'data'!D10</f>
       </c>
     </row>
     <row r="35" ht="270" customHeight="true">
-      <c r="A35" s="17">
-        <v>0</v>
+      <c r="A35" s="17" t="str">
+        <f>'data'!$E$3</f>
       </c>
       <c r="B35" s="18" t="str">
         <f>'data'!D3</f>
       </c>
     </row>
     <row r="36" ht="270" customHeight="true">
-      <c r="A36" s="17">
-        <v>2</v>
+      <c r="A36" s="17" t="str">
+        <f>'data'!$E$5</f>
       </c>
       <c r="B36" s="18" t="str">
         <f>'data'!D5</f>
       </c>
     </row>
     <row r="37" ht="270" customHeight="true">
-      <c r="A37" s="17">
-        <v>8</v>
+      <c r="A37" s="17" t="str">
+        <f>'data'!$E$11</f>
       </c>
       <c r="B37" s="18" t="str">
         <f>'data'!D11</f>
       </c>
     </row>
     <row r="38" ht="270" customHeight="true">
-      <c r="A38" s="17">
-        <v>9</v>
+      <c r="A38" s="17" t="str">
+        <f>'data'!$E$12</f>
       </c>
       <c r="B38" s="18" t="str">
         <f>'data'!D12</f>
       </c>
     </row>
     <row r="39" ht="270" customHeight="true">
-      <c r="A39" s="17">
-        <v>84</v>
+      <c r="A39" s="17" t="str">
+        <f>'data'!$E$87</f>
       </c>
       <c r="B39" s="18" t="str">
         <f>'data'!D87</f>
       </c>
     </row>
     <row r="40" ht="270" customHeight="true">
-      <c r="A40" s="17">
-        <v>85</v>
+      <c r="A40" s="17" t="str">
+        <f>'data'!$E$88</f>
       </c>
       <c r="B40" s="18" t="str">
         <f>'data'!D88</f>
       </c>
     </row>
     <row r="41" ht="270" customHeight="true">
-      <c r="A41" s="17">
-        <v>86</v>
+      <c r="A41" s="17" t="str">
+        <f>'data'!$E$89</f>
       </c>
       <c r="B41" s="18" t="str">
         <f>'data'!D89</f>
       </c>
     </row>
     <row r="42" ht="270" customHeight="true">
-      <c r="A42" s="17">
-        <v>87</v>
+      <c r="A42" s="17" t="str">
+        <f>'data'!$E$90</f>
       </c>
       <c r="B42" s="18" t="str">
         <f>'data'!D90</f>
       </c>
     </row>
     <row r="43" ht="270" customHeight="true">
-      <c r="A43" s="17">
-        <v>88</v>
+      <c r="A43" s="17" t="str">
+        <f>'data'!$E$91</f>
       </c>
       <c r="B43" s="18" t="str">
         <f>'data'!D91</f>
       </c>
     </row>
     <row r="44" ht="270" customHeight="true">
-      <c r="A44" s="17">
-        <v>1</v>
+      <c r="A44" s="17" t="str">
+        <f>'data'!$E$4</f>
       </c>
       <c r="B44" s="18" t="str">
         <f>'data'!D4</f>
       </c>
     </row>
     <row r="45" ht="270" customHeight="true">
-      <c r="A45" s="17">
-        <v>90</v>
+      <c r="A45" s="17" t="str">
+        <f>'data'!$E$93</f>
       </c>
       <c r="B45" s="18" t="str">
         <f>'data'!D93</f>
@@ -5220,7 +5772,7 @@
     </row>
     <row r="13">
       <c r="E13" s="11" t="s">
-        <v>303</v>
+        <v>395</v>
       </c>
       <c r="F13" s="11"/>
       <c r="G13" s="11"/>
@@ -5231,7 +5783,7 @@
         <v>2</v>
       </c>
       <c r="E14" s="25" t="s">
-        <v>304</v>
+        <v>396</v>
       </c>
       <c r="F14" s="25"/>
       <c r="G14" s="25"/>
@@ -5241,7 +5793,7 @@
     </row>
     <row r="15">
       <c r="E15" s="25" t="s">
-        <v>305</v>
+        <v>397</v>
       </c>
       <c r="F15" s="25"/>
       <c r="G15" s="25"/>
@@ -5251,7 +5803,7 @@
     </row>
     <row r="16">
       <c r="E16" s="25" t="s">
-        <v>306</v>
+        <v>398</v>
       </c>
       <c r="F16" s="25"/>
       <c r="G16" s="25"/>
@@ -5261,7 +5813,7 @@
     </row>
     <row r="17">
       <c r="E17" s="25" t="s">
-        <v>307</v>
+        <v>399</v>
       </c>
       <c r="F17" s="25"/>
       <c r="G17" s="25"/>
@@ -5271,7 +5823,7 @@
     </row>
     <row r="18">
       <c r="E18" s="11" t="s">
-        <v>308</v>
+        <v>400</v>
       </c>
       <c r="F18" s="11"/>
       <c r="G18" s="11"/>
@@ -5281,7 +5833,7 @@
     </row>
     <row r="19">
       <c r="E19" s="11" t="s">
-        <v>309</v>
+        <v>401</v>
       </c>
       <c r="F19" s="11"/>
       <c r="G19" s="11"/>
@@ -5317,7 +5869,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="11" t="s">
-        <v>206</v>
+        <v>298</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -5326,7 +5878,7 @@
       <c r="F1" s="11"/>
       <c r="G1" s="11"/>
       <c r="I1" s="11" t="s">
-        <v>207</v>
+        <v>299</v>
       </c>
       <c r="J1" s="11"/>
       <c r="K1" s="11"/>
@@ -5337,7 +5889,7 @@
     </row>
     <row r="2">
       <c r="A2" s="11" t="s">
-        <v>208</v>
+        <v>300</v>
       </c>
       <c r="B2" s="11"/>
       <c r="C2" s="11"/>
@@ -5346,7 +5898,7 @@
       <c r="F2" s="11"/>
       <c r="G2" s="11"/>
       <c r="I2" s="11" t="s">
-        <v>214</v>
+        <v>306</v>
       </c>
       <c r="J2" s="11"/>
       <c r="K2" s="11"/>
@@ -5357,22 +5909,22 @@
     </row>
     <row r="3">
       <c r="A3" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G3" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I3" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L3" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O3" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="4">
@@ -5401,27 +5953,27 @@
     </row>
     <row r="6">
       <c r="F6" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G6" s="23"/>
       <c r="N6" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O6" s="23"/>
     </row>
     <row r="7">
       <c r="F7" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G7" s="23"/>
       <c r="N7" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O7" s="23"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="s">
-        <v>215</v>
+        <v>307</v>
       </c>
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
@@ -5430,7 +5982,7 @@
       <c r="F10" s="11"/>
       <c r="G10" s="11"/>
       <c r="I10" s="11" t="s">
-        <v>216</v>
+        <v>308</v>
       </c>
       <c r="J10" s="11"/>
       <c r="K10" s="11"/>
@@ -5441,22 +5993,22 @@
     </row>
     <row r="11">
       <c r="A11" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G11" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I11" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L11" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O11" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="12">
@@ -5485,27 +6037,27 @@
     </row>
     <row r="14">
       <c r="F14" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G14" s="23"/>
       <c r="N14" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O14" s="23"/>
     </row>
     <row r="15">
       <c r="F15" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G15" s="23"/>
       <c r="N15" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O15" s="23"/>
     </row>
     <row r="18">
       <c r="A18" s="11" t="s">
-        <v>217</v>
+        <v>309</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -5514,7 +6066,7 @@
       <c r="F18" s="11"/>
       <c r="G18" s="11"/>
       <c r="I18" s="11" t="s">
-        <v>218</v>
+        <v>310</v>
       </c>
       <c r="J18" s="11"/>
       <c r="K18" s="11"/>
@@ -5525,22 +6077,22 @@
     </row>
     <row r="19">
       <c r="A19" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G19" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I19" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L19" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O19" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="20">
@@ -5569,27 +6121,27 @@
     </row>
     <row r="22">
       <c r="F22" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G22" s="23"/>
       <c r="N22" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O22" s="23"/>
     </row>
     <row r="23">
       <c r="F23" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G23" s="23"/>
       <c r="N23" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O23" s="23"/>
     </row>
     <row r="26">
       <c r="A26" s="11" t="s">
-        <v>219</v>
+        <v>311</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -5598,7 +6150,7 @@
       <c r="F26" s="11"/>
       <c r="G26" s="11"/>
       <c r="I26" s="11" t="s">
-        <v>220</v>
+        <v>312</v>
       </c>
       <c r="J26" s="11"/>
       <c r="K26" s="11"/>
@@ -5609,22 +6161,22 @@
     </row>
     <row r="27">
       <c r="A27" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D27" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G27" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I27" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L27" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O27" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="28">
@@ -5653,27 +6205,27 @@
     </row>
     <row r="30">
       <c r="F30" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G30" s="23"/>
       <c r="N30" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O30" s="23"/>
     </row>
     <row r="31">
       <c r="F31" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G31" s="23"/>
       <c r="N31" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O31" s="23"/>
     </row>
     <row r="34">
       <c r="A34" s="11" t="s">
-        <v>221</v>
+        <v>313</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -5682,7 +6234,7 @@
       <c r="F34" s="11"/>
       <c r="G34" s="11"/>
       <c r="I34" s="11" t="s">
-        <v>222</v>
+        <v>314</v>
       </c>
       <c r="J34" s="11"/>
       <c r="K34" s="11"/>
@@ -5693,22 +6245,22 @@
     </row>
     <row r="35">
       <c r="A35" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D35" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G35" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I35" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L35" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O35" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="36">
@@ -5737,27 +6289,27 @@
     </row>
     <row r="38">
       <c r="F38" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G38" s="23"/>
       <c r="N38" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O38" s="23"/>
     </row>
     <row r="39">
       <c r="F39" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G39" s="23"/>
       <c r="N39" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O39" s="23"/>
     </row>
     <row r="42">
       <c r="A42" s="11" t="s">
-        <v>223</v>
+        <v>315</v>
       </c>
       <c r="B42" s="11"/>
       <c r="C42" s="11"/>
@@ -5766,7 +6318,7 @@
       <c r="F42" s="11"/>
       <c r="G42" s="11"/>
       <c r="I42" s="11" t="s">
-        <v>224</v>
+        <v>316</v>
       </c>
       <c r="J42" s="11"/>
       <c r="K42" s="11"/>
@@ -5777,22 +6329,22 @@
     </row>
     <row r="43">
       <c r="A43" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D43" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G43" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I43" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L43" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O43" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="44">
@@ -5821,27 +6373,27 @@
     </row>
     <row r="46">
       <c r="F46" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G46" s="23"/>
       <c r="N46" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O46" s="23"/>
     </row>
     <row r="47">
       <c r="F47" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G47" s="23"/>
       <c r="N47" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O47" s="23"/>
     </row>
     <row r="50">
       <c r="A50" s="11" t="s">
-        <v>225</v>
+        <v>317</v>
       </c>
       <c r="B50" s="11"/>
       <c r="C50" s="11"/>
@@ -5850,7 +6402,7 @@
       <c r="F50" s="11"/>
       <c r="G50" s="11"/>
       <c r="I50" s="11" t="s">
-        <v>226</v>
+        <v>318</v>
       </c>
       <c r="J50" s="11"/>
       <c r="K50" s="11"/>
@@ -5861,22 +6413,22 @@
     </row>
     <row r="51">
       <c r="A51" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D51" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G51" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I51" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L51" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O51" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="52">
@@ -5905,27 +6457,27 @@
     </row>
     <row r="54">
       <c r="F54" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G54" s="23"/>
       <c r="N54" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O54" s="23"/>
     </row>
     <row r="55">
       <c r="F55" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G55" s="23"/>
       <c r="N55" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O55" s="23"/>
     </row>
     <row r="58">
       <c r="A58" s="11" t="s">
-        <v>227</v>
+        <v>319</v>
       </c>
       <c r="B58" s="11"/>
       <c r="C58" s="11"/>
@@ -5934,7 +6486,7 @@
       <c r="F58" s="11"/>
       <c r="G58" s="11"/>
       <c r="I58" s="11" t="s">
-        <v>228</v>
+        <v>320</v>
       </c>
       <c r="J58" s="11"/>
       <c r="K58" s="11"/>
@@ -5945,22 +6497,22 @@
     </row>
     <row r="59">
       <c r="A59" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D59" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G59" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I59" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L59" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O59" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="60">
@@ -5989,27 +6541,27 @@
     </row>
     <row r="62">
       <c r="F62" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G62" s="23"/>
       <c r="N62" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O62" s="23"/>
     </row>
     <row r="63">
       <c r="F63" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G63" s="23"/>
       <c r="N63" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O63" s="23"/>
     </row>
     <row r="66">
       <c r="A66" s="11" t="s">
-        <v>229</v>
+        <v>321</v>
       </c>
       <c r="B66" s="11"/>
       <c r="C66" s="11"/>
@@ -6018,7 +6570,7 @@
       <c r="F66" s="11"/>
       <c r="G66" s="11"/>
       <c r="I66" s="11" t="s">
-        <v>230</v>
+        <v>322</v>
       </c>
       <c r="J66" s="11"/>
       <c r="K66" s="11"/>
@@ -6029,22 +6581,22 @@
     </row>
     <row r="67">
       <c r="A67" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D67" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G67" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I67" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L67" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O67" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="68">
@@ -6073,27 +6625,27 @@
     </row>
     <row r="70">
       <c r="F70" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G70" s="23"/>
       <c r="N70" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O70" s="23"/>
     </row>
     <row r="71">
       <c r="F71" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G71" s="23"/>
       <c r="N71" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O71" s="23"/>
     </row>
     <row r="74">
       <c r="A74" s="11" t="s">
-        <v>231</v>
+        <v>323</v>
       </c>
       <c r="B74" s="11"/>
       <c r="C74" s="11"/>
@@ -6102,7 +6654,7 @@
       <c r="F74" s="11"/>
       <c r="G74" s="11"/>
       <c r="I74" s="11" t="s">
-        <v>232</v>
+        <v>324</v>
       </c>
       <c r="J74" s="11"/>
       <c r="K74" s="11"/>
@@ -6113,22 +6665,22 @@
     </row>
     <row r="75">
       <c r="A75" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D75" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G75" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I75" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L75" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O75" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="76">
@@ -6157,27 +6709,27 @@
     </row>
     <row r="78">
       <c r="F78" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G78" s="23"/>
       <c r="N78" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O78" s="23"/>
     </row>
     <row r="79">
       <c r="F79" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G79" s="23"/>
       <c r="N79" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O79" s="23"/>
     </row>
     <row r="82">
       <c r="A82" s="11" t="s">
-        <v>233</v>
+        <v>325</v>
       </c>
       <c r="B82" s="11"/>
       <c r="C82" s="11"/>
@@ -6186,7 +6738,7 @@
       <c r="F82" s="11"/>
       <c r="G82" s="11"/>
       <c r="I82" s="11" t="s">
-        <v>234</v>
+        <v>326</v>
       </c>
       <c r="J82" s="11"/>
       <c r="K82" s="11"/>
@@ -6197,22 +6749,22 @@
     </row>
     <row r="83">
       <c r="A83" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D83" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G83" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I83" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L83" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O83" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="84">
@@ -6241,27 +6793,27 @@
     </row>
     <row r="86">
       <c r="F86" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G86" s="23"/>
       <c r="N86" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O86" s="23"/>
     </row>
     <row r="87">
       <c r="F87" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G87" s="23"/>
       <c r="N87" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O87" s="23"/>
     </row>
     <row r="90">
       <c r="A90" s="11" t="s">
-        <v>235</v>
+        <v>327</v>
       </c>
       <c r="B90" s="11"/>
       <c r="C90" s="11"/>
@@ -6270,7 +6822,7 @@
       <c r="F90" s="11"/>
       <c r="G90" s="11"/>
       <c r="I90" s="11" t="s">
-        <v>236</v>
+        <v>328</v>
       </c>
       <c r="J90" s="11"/>
       <c r="K90" s="11"/>
@@ -6281,22 +6833,22 @@
     </row>
     <row r="91">
       <c r="A91" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D91" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G91" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I91" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L91" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O91" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="92">
@@ -6325,27 +6877,27 @@
     </row>
     <row r="94">
       <c r="F94" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G94" s="23"/>
       <c r="N94" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O94" s="23"/>
     </row>
     <row r="95">
       <c r="F95" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G95" s="23"/>
       <c r="N95" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O95" s="23"/>
     </row>
     <row r="98">
       <c r="A98" s="11" t="s">
-        <v>237</v>
+        <v>329</v>
       </c>
       <c r="B98" s="11"/>
       <c r="C98" s="11"/>
@@ -6354,7 +6906,7 @@
       <c r="F98" s="11"/>
       <c r="G98" s="11"/>
       <c r="I98" s="11" t="s">
-        <v>238</v>
+        <v>330</v>
       </c>
       <c r="J98" s="11"/>
       <c r="K98" s="11"/>
@@ -6365,22 +6917,22 @@
     </row>
     <row r="99">
       <c r="A99" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D99" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G99" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I99" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L99" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O99" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="100">
@@ -6409,27 +6961,27 @@
     </row>
     <row r="102">
       <c r="F102" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G102" s="23"/>
       <c r="N102" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O102" s="23"/>
     </row>
     <row r="103">
       <c r="F103" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G103" s="23"/>
       <c r="N103" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O103" s="23"/>
     </row>
     <row r="106">
       <c r="A106" s="11" t="s">
-        <v>239</v>
+        <v>331</v>
       </c>
       <c r="B106" s="11"/>
       <c r="C106" s="11"/>
@@ -6438,7 +6990,7 @@
       <c r="F106" s="11"/>
       <c r="G106" s="11"/>
       <c r="I106" s="11" t="s">
-        <v>240</v>
+        <v>332</v>
       </c>
       <c r="J106" s="11"/>
       <c r="K106" s="11"/>
@@ -6449,22 +7001,22 @@
     </row>
     <row r="107">
       <c r="A107" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D107" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G107" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I107" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L107" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O107" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="108">
@@ -6493,27 +7045,27 @@
     </row>
     <row r="110">
       <c r="F110" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G110" s="23"/>
       <c r="N110" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O110" s="23"/>
     </row>
     <row r="111">
       <c r="F111" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G111" s="23"/>
       <c r="N111" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O111" s="23"/>
     </row>
     <row r="114">
       <c r="A114" s="11" t="s">
-        <v>241</v>
+        <v>333</v>
       </c>
       <c r="B114" s="11"/>
       <c r="C114" s="11"/>
@@ -6522,7 +7074,7 @@
       <c r="F114" s="11"/>
       <c r="G114" s="11"/>
       <c r="I114" s="11" t="s">
-        <v>242</v>
+        <v>334</v>
       </c>
       <c r="J114" s="11"/>
       <c r="K114" s="11"/>
@@ -6533,22 +7085,22 @@
     </row>
     <row r="115">
       <c r="A115" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D115" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G115" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I115" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L115" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O115" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="116">
@@ -6577,27 +7129,27 @@
     </row>
     <row r="118">
       <c r="F118" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G118" s="23"/>
       <c r="N118" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O118" s="23"/>
     </row>
     <row r="119">
       <c r="F119" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G119" s="23"/>
       <c r="N119" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O119" s="23"/>
     </row>
     <row r="122">
       <c r="A122" s="11" t="s">
-        <v>243</v>
+        <v>335</v>
       </c>
       <c r="B122" s="11"/>
       <c r="C122" s="11"/>
@@ -6606,7 +7158,7 @@
       <c r="F122" s="11"/>
       <c r="G122" s="11"/>
       <c r="I122" s="11" t="s">
-        <v>244</v>
+        <v>336</v>
       </c>
       <c r="J122" s="11"/>
       <c r="K122" s="11"/>
@@ -6617,22 +7169,22 @@
     </row>
     <row r="123">
       <c r="A123" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D123" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G123" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I123" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L123" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O123" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="124">
@@ -6661,27 +7213,27 @@
     </row>
     <row r="126">
       <c r="F126" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G126" s="23"/>
       <c r="N126" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O126" s="23"/>
     </row>
     <row r="127">
       <c r="F127" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G127" s="23"/>
       <c r="N127" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O127" s="23"/>
     </row>
     <row r="135">
       <c r="A135" s="11" t="s">
-        <v>245</v>
+        <v>337</v>
       </c>
       <c r="B135" s="11"/>
       <c r="C135" s="11"/>
@@ -6690,7 +7242,7 @@
       <c r="F135" s="11"/>
       <c r="G135" s="11"/>
       <c r="I135" s="11" t="s">
-        <v>246</v>
+        <v>338</v>
       </c>
       <c r="J135" s="11"/>
       <c r="K135" s="11"/>
@@ -6701,22 +7253,22 @@
     </row>
     <row r="136">
       <c r="A136" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D136" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G136" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I136" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L136" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O136" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="137">
@@ -6745,27 +7297,27 @@
     </row>
     <row r="139">
       <c r="F139" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G139" s="23"/>
       <c r="N139" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O139" s="23"/>
     </row>
     <row r="140">
       <c r="F140" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G140" s="23"/>
       <c r="N140" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O140" s="23"/>
     </row>
     <row r="143">
       <c r="A143" s="11" t="s">
-        <v>247</v>
+        <v>339</v>
       </c>
       <c r="B143" s="11"/>
       <c r="C143" s="11"/>
@@ -6774,7 +7326,7 @@
       <c r="F143" s="11"/>
       <c r="G143" s="11"/>
       <c r="I143" s="11" t="s">
-        <v>248</v>
+        <v>340</v>
       </c>
       <c r="J143" s="11"/>
       <c r="K143" s="11"/>
@@ -6785,22 +7337,22 @@
     </row>
     <row r="144">
       <c r="A144" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D144" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G144" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I144" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L144" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O144" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="145">
@@ -6829,27 +7381,27 @@
     </row>
     <row r="147">
       <c r="F147" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G147" s="23"/>
       <c r="N147" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O147" s="23"/>
     </row>
     <row r="148">
       <c r="F148" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G148" s="23"/>
       <c r="N148" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O148" s="23"/>
     </row>
     <row r="151">
       <c r="A151" s="11" t="s">
-        <v>249</v>
+        <v>341</v>
       </c>
       <c r="B151" s="11"/>
       <c r="C151" s="11"/>
@@ -6858,7 +7410,7 @@
       <c r="F151" s="11"/>
       <c r="G151" s="11"/>
       <c r="I151" s="11" t="s">
-        <v>250</v>
+        <v>342</v>
       </c>
       <c r="J151" s="11"/>
       <c r="K151" s="11"/>
@@ -6869,22 +7421,22 @@
     </row>
     <row r="152">
       <c r="A152" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D152" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G152" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I152" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L152" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O152" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="153">
@@ -6913,27 +7465,27 @@
     </row>
     <row r="155">
       <c r="F155" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G155" s="23"/>
       <c r="N155" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O155" s="23"/>
     </row>
     <row r="156">
       <c r="F156" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G156" s="23"/>
       <c r="N156" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O156" s="23"/>
     </row>
     <row r="159">
       <c r="A159" s="11" t="s">
-        <v>251</v>
+        <v>343</v>
       </c>
       <c r="B159" s="11"/>
       <c r="C159" s="11"/>
@@ -6942,7 +7494,7 @@
       <c r="F159" s="11"/>
       <c r="G159" s="11"/>
       <c r="I159" s="11" t="s">
-        <v>252</v>
+        <v>344</v>
       </c>
       <c r="J159" s="11"/>
       <c r="K159" s="11"/>
@@ -6953,22 +7505,22 @@
     </row>
     <row r="160">
       <c r="A160" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D160" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G160" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I160" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L160" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O160" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="161">
@@ -6997,27 +7549,27 @@
     </row>
     <row r="163">
       <c r="F163" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G163" s="23"/>
       <c r="N163" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O163" s="23"/>
     </row>
     <row r="164">
       <c r="F164" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G164" s="23"/>
       <c r="N164" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O164" s="23"/>
     </row>
     <row r="167">
       <c r="A167" s="11" t="s">
-        <v>253</v>
+        <v>345</v>
       </c>
       <c r="B167" s="11"/>
       <c r="C167" s="11"/>
@@ -7026,7 +7578,7 @@
       <c r="F167" s="11"/>
       <c r="G167" s="11"/>
       <c r="I167" s="11" t="s">
-        <v>254</v>
+        <v>346</v>
       </c>
       <c r="J167" s="11"/>
       <c r="K167" s="11"/>
@@ -7037,22 +7589,22 @@
     </row>
     <row r="168">
       <c r="A168" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D168" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G168" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I168" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L168" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O168" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="169">
@@ -7081,27 +7633,27 @@
     </row>
     <row r="171">
       <c r="F171" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G171" s="23"/>
       <c r="N171" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O171" s="23"/>
     </row>
     <row r="172">
       <c r="F172" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G172" s="23"/>
       <c r="N172" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O172" s="23"/>
     </row>
     <row r="175">
       <c r="A175" s="11" t="s">
-        <v>255</v>
+        <v>347</v>
       </c>
       <c r="B175" s="11"/>
       <c r="C175" s="11"/>
@@ -7110,7 +7662,7 @@
       <c r="F175" s="11"/>
       <c r="G175" s="11"/>
       <c r="I175" s="11" t="s">
-        <v>256</v>
+        <v>348</v>
       </c>
       <c r="J175" s="11"/>
       <c r="K175" s="11"/>
@@ -7121,22 +7673,22 @@
     </row>
     <row r="176">
       <c r="A176" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D176" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G176" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I176" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L176" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O176" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="177">
@@ -7165,27 +7717,27 @@
     </row>
     <row r="179">
       <c r="F179" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G179" s="23"/>
       <c r="N179" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O179" s="23"/>
     </row>
     <row r="180">
       <c r="F180" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G180" s="23"/>
       <c r="N180" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O180" s="23"/>
     </row>
     <row r="183">
       <c r="A183" s="11" t="s">
-        <v>257</v>
+        <v>349</v>
       </c>
       <c r="B183" s="11"/>
       <c r="C183" s="11"/>
@@ -7194,7 +7746,7 @@
       <c r="F183" s="11"/>
       <c r="G183" s="11"/>
       <c r="I183" s="11" t="s">
-        <v>258</v>
+        <v>350</v>
       </c>
       <c r="J183" s="11"/>
       <c r="K183" s="11"/>
@@ -7205,22 +7757,22 @@
     </row>
     <row r="184">
       <c r="A184" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D184" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G184" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I184" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L184" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O184" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="185">
@@ -7249,27 +7801,27 @@
     </row>
     <row r="187">
       <c r="F187" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G187" s="23"/>
       <c r="N187" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O187" s="23"/>
     </row>
     <row r="188">
       <c r="F188" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G188" s="23"/>
       <c r="N188" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O188" s="23"/>
     </row>
     <row r="191">
       <c r="A191" s="11" t="s">
-        <v>259</v>
+        <v>351</v>
       </c>
       <c r="B191" s="11"/>
       <c r="C191" s="11"/>
@@ -7278,7 +7830,7 @@
       <c r="F191" s="11"/>
       <c r="G191" s="11"/>
       <c r="I191" s="11" t="s">
-        <v>260</v>
+        <v>352</v>
       </c>
       <c r="J191" s="11"/>
       <c r="K191" s="11"/>
@@ -7289,22 +7841,22 @@
     </row>
     <row r="192">
       <c r="A192" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D192" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G192" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I192" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L192" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O192" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="193">
@@ -7333,27 +7885,27 @@
     </row>
     <row r="195">
       <c r="F195" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G195" s="23"/>
       <c r="N195" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O195" s="23"/>
     </row>
     <row r="196">
       <c r="F196" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G196" s="23"/>
       <c r="N196" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O196" s="23"/>
     </row>
     <row r="199">
       <c r="A199" s="11" t="s">
-        <v>261</v>
+        <v>353</v>
       </c>
       <c r="B199" s="11"/>
       <c r="C199" s="11"/>
@@ -7362,7 +7914,7 @@
       <c r="F199" s="11"/>
       <c r="G199" s="11"/>
       <c r="I199" s="11" t="s">
-        <v>262</v>
+        <v>354</v>
       </c>
       <c r="J199" s="11"/>
       <c r="K199" s="11"/>
@@ -7373,22 +7925,22 @@
     </row>
     <row r="200">
       <c r="A200" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D200" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G200" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I200" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L200" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O200" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="201">
@@ -7417,27 +7969,27 @@
     </row>
     <row r="203">
       <c r="F203" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G203" s="23"/>
       <c r="N203" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O203" s="23"/>
     </row>
     <row r="204">
       <c r="F204" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G204" s="23"/>
       <c r="N204" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O204" s="23"/>
     </row>
     <row r="207">
       <c r="A207" s="11" t="s">
-        <v>263</v>
+        <v>355</v>
       </c>
       <c r="B207" s="11"/>
       <c r="C207" s="11"/>
@@ -7446,7 +7998,7 @@
       <c r="F207" s="11"/>
       <c r="G207" s="11"/>
       <c r="I207" s="11" t="s">
-        <v>264</v>
+        <v>356</v>
       </c>
       <c r="J207" s="11"/>
       <c r="K207" s="11"/>
@@ -7457,22 +8009,22 @@
     </row>
     <row r="208">
       <c r="A208" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D208" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G208" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I208" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L208" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O208" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="209">
@@ -7501,27 +8053,27 @@
     </row>
     <row r="211">
       <c r="F211" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G211" s="23"/>
       <c r="N211" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O211" s="23"/>
     </row>
     <row r="212">
       <c r="F212" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G212" s="23"/>
       <c r="N212" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O212" s="23"/>
     </row>
     <row r="215">
       <c r="A215" s="11" t="s">
-        <v>265</v>
+        <v>357</v>
       </c>
       <c r="B215" s="11"/>
       <c r="C215" s="11"/>
@@ -7530,7 +8082,7 @@
       <c r="F215" s="11"/>
       <c r="G215" s="11"/>
       <c r="I215" s="11" t="s">
-        <v>266</v>
+        <v>358</v>
       </c>
       <c r="J215" s="11"/>
       <c r="K215" s="11"/>
@@ -7541,22 +8093,22 @@
     </row>
     <row r="216">
       <c r="A216" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D216" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G216" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I216" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L216" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O216" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="217">
@@ -7585,27 +8137,27 @@
     </row>
     <row r="219">
       <c r="F219" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G219" s="23"/>
       <c r="N219" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O219" s="23"/>
     </row>
     <row r="220">
       <c r="F220" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G220" s="23"/>
       <c r="N220" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O220" s="23"/>
     </row>
     <row r="223">
       <c r="A223" s="11" t="s">
-        <v>267</v>
+        <v>359</v>
       </c>
       <c r="B223" s="11"/>
       <c r="C223" s="11"/>
@@ -7614,7 +8166,7 @@
       <c r="F223" s="11"/>
       <c r="G223" s="11"/>
       <c r="I223" s="11" t="s">
-        <v>268</v>
+        <v>360</v>
       </c>
       <c r="J223" s="11"/>
       <c r="K223" s="11"/>
@@ -7625,22 +8177,22 @@
     </row>
     <row r="224">
       <c r="A224" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D224" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G224" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I224" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L224" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O224" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="225">
@@ -7669,27 +8221,27 @@
     </row>
     <row r="227">
       <c r="F227" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G227" s="23"/>
       <c r="N227" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O227" s="23"/>
     </row>
     <row r="228">
       <c r="F228" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G228" s="23"/>
       <c r="N228" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O228" s="23"/>
     </row>
     <row r="231">
       <c r="A231" s="11" t="s">
-        <v>269</v>
+        <v>361</v>
       </c>
       <c r="B231" s="11"/>
       <c r="C231" s="11"/>
@@ -7698,7 +8250,7 @@
       <c r="F231" s="11"/>
       <c r="G231" s="11"/>
       <c r="I231" s="11" t="s">
-        <v>270</v>
+        <v>362</v>
       </c>
       <c r="J231" s="11"/>
       <c r="K231" s="11"/>
@@ -7709,22 +8261,22 @@
     </row>
     <row r="232">
       <c r="A232" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D232" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G232" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I232" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L232" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O232" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="233">
@@ -7753,27 +8305,27 @@
     </row>
     <row r="235">
       <c r="F235" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G235" s="23"/>
       <c r="N235" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O235" s="23"/>
     </row>
     <row r="236">
       <c r="F236" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G236" s="23"/>
       <c r="N236" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O236" s="23"/>
     </row>
     <row r="239">
       <c r="I239" s="11" t="s">
-        <v>271</v>
+        <v>363</v>
       </c>
       <c r="J239" s="11"/>
       <c r="K239" s="11"/>
@@ -7784,13 +8336,13 @@
     </row>
     <row r="240">
       <c r="I240" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L240" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O240" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="241">
@@ -7808,19 +8360,19 @@
     </row>
     <row r="243">
       <c r="N243" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O243" s="23"/>
     </row>
     <row r="244">
       <c r="N244" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O244" s="23"/>
     </row>
     <row r="252">
       <c r="A252" s="11" t="s">
-        <v>272</v>
+        <v>364</v>
       </c>
       <c r="B252" s="11"/>
       <c r="C252" s="11"/>
@@ -7829,7 +8381,7 @@
       <c r="F252" s="11"/>
       <c r="G252" s="11"/>
       <c r="I252" s="11" t="s">
-        <v>273</v>
+        <v>365</v>
       </c>
       <c r="J252" s="11"/>
       <c r="K252" s="11"/>
@@ -7840,22 +8392,22 @@
     </row>
     <row r="253">
       <c r="A253" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D253" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G253" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I253" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L253" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O253" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="254">
@@ -7884,27 +8436,27 @@
     </row>
     <row r="256">
       <c r="F256" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G256" s="23"/>
       <c r="N256" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O256" s="23"/>
     </row>
     <row r="257">
       <c r="F257" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G257" s="23"/>
       <c r="N257" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O257" s="23"/>
     </row>
     <row r="260">
       <c r="A260" s="11" t="s">
-        <v>274</v>
+        <v>366</v>
       </c>
       <c r="B260" s="11"/>
       <c r="C260" s="11"/>
@@ -7913,7 +8465,7 @@
       <c r="F260" s="11"/>
       <c r="G260" s="11"/>
       <c r="I260" s="11" t="s">
-        <v>275</v>
+        <v>367</v>
       </c>
       <c r="J260" s="11"/>
       <c r="K260" s="11"/>
@@ -7924,22 +8476,22 @@
     </row>
     <row r="261">
       <c r="A261" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D261" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G261" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I261" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L261" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O261" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="262">
@@ -7968,27 +8520,27 @@
     </row>
     <row r="264">
       <c r="F264" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G264" s="23"/>
       <c r="N264" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O264" s="23"/>
     </row>
     <row r="265">
       <c r="F265" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G265" s="23"/>
       <c r="N265" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O265" s="23"/>
     </row>
     <row r="268">
       <c r="A268" s="11" t="s">
-        <v>276</v>
+        <v>368</v>
       </c>
       <c r="B268" s="11"/>
       <c r="C268" s="11"/>
@@ -7997,7 +8549,7 @@
       <c r="F268" s="11"/>
       <c r="G268" s="11"/>
       <c r="I268" s="11" t="s">
-        <v>277</v>
+        <v>369</v>
       </c>
       <c r="J268" s="11"/>
       <c r="K268" s="11"/>
@@ -8008,22 +8560,22 @@
     </row>
     <row r="269">
       <c r="A269" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D269" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G269" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I269" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L269" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O269" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="270">
@@ -8052,27 +8604,27 @@
     </row>
     <row r="272">
       <c r="F272" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G272" s="23"/>
       <c r="N272" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O272" s="23"/>
     </row>
     <row r="273">
       <c r="F273" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G273" s="23"/>
       <c r="N273" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O273" s="23"/>
     </row>
     <row r="276">
       <c r="A276" s="11" t="s">
-        <v>278</v>
+        <v>370</v>
       </c>
       <c r="B276" s="11"/>
       <c r="C276" s="11"/>
@@ -8081,7 +8633,7 @@
       <c r="F276" s="11"/>
       <c r="G276" s="11"/>
       <c r="I276" s="11" t="s">
-        <v>279</v>
+        <v>371</v>
       </c>
       <c r="J276" s="11"/>
       <c r="K276" s="11"/>
@@ -8092,22 +8644,22 @@
     </row>
     <row r="277">
       <c r="A277" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D277" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G277" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I277" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L277" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O277" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="278">
@@ -8136,27 +8688,27 @@
     </row>
     <row r="280">
       <c r="F280" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G280" s="23"/>
       <c r="N280" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O280" s="23"/>
     </row>
     <row r="281">
       <c r="F281" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G281" s="23"/>
       <c r="N281" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O281" s="23"/>
     </row>
     <row r="284">
       <c r="A284" s="11" t="s">
-        <v>280</v>
+        <v>372</v>
       </c>
       <c r="B284" s="11"/>
       <c r="C284" s="11"/>
@@ -8165,7 +8717,7 @@
       <c r="F284" s="11"/>
       <c r="G284" s="11"/>
       <c r="I284" s="11" t="s">
-        <v>281</v>
+        <v>373</v>
       </c>
       <c r="J284" s="11"/>
       <c r="K284" s="11"/>
@@ -8176,22 +8728,22 @@
     </row>
     <row r="285">
       <c r="A285" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D285" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G285" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I285" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L285" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O285" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="286">
@@ -8220,27 +8772,27 @@
     </row>
     <row r="288">
       <c r="F288" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G288" s="23"/>
       <c r="N288" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O288" s="23"/>
     </row>
     <row r="289">
       <c r="F289" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G289" s="23"/>
       <c r="N289" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O289" s="23"/>
     </row>
     <row r="292">
       <c r="A292" s="11" t="s">
-        <v>282</v>
+        <v>374</v>
       </c>
       <c r="B292" s="11"/>
       <c r="C292" s="11"/>
@@ -8249,7 +8801,7 @@
       <c r="F292" s="11"/>
       <c r="G292" s="11"/>
       <c r="I292" s="11" t="s">
-        <v>283</v>
+        <v>375</v>
       </c>
       <c r="J292" s="11"/>
       <c r="K292" s="11"/>
@@ -8260,22 +8812,22 @@
     </row>
     <row r="293">
       <c r="A293" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D293" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G293" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I293" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L293" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O293" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="294">
@@ -8304,27 +8856,27 @@
     </row>
     <row r="296">
       <c r="F296" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G296" s="23"/>
       <c r="N296" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O296" s="23"/>
     </row>
     <row r="297">
       <c r="F297" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G297" s="23"/>
       <c r="N297" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O297" s="23"/>
     </row>
     <row r="300">
       <c r="A300" s="11" t="s">
-        <v>284</v>
+        <v>376</v>
       </c>
       <c r="B300" s="11"/>
       <c r="C300" s="11"/>
@@ -8333,7 +8885,7 @@
       <c r="F300" s="11"/>
       <c r="G300" s="11"/>
       <c r="I300" s="11" t="s">
-        <v>285</v>
+        <v>377</v>
       </c>
       <c r="J300" s="11"/>
       <c r="K300" s="11"/>
@@ -8344,22 +8896,22 @@
     </row>
     <row r="301">
       <c r="A301" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D301" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G301" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I301" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L301" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O301" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="302">
@@ -8388,27 +8940,27 @@
     </row>
     <row r="304">
       <c r="F304" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G304" s="23"/>
       <c r="N304" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O304" s="23"/>
     </row>
     <row r="305">
       <c r="F305" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G305" s="23"/>
       <c r="N305" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O305" s="23"/>
     </row>
     <row r="308">
       <c r="A308" s="11" t="s">
-        <v>286</v>
+        <v>378</v>
       </c>
       <c r="B308" s="11"/>
       <c r="C308" s="11"/>
@@ -8417,7 +8969,7 @@
       <c r="F308" s="11"/>
       <c r="G308" s="11"/>
       <c r="I308" s="11" t="s">
-        <v>287</v>
+        <v>379</v>
       </c>
       <c r="J308" s="11"/>
       <c r="K308" s="11"/>
@@ -8428,22 +8980,22 @@
     </row>
     <row r="309">
       <c r="A309" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D309" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G309" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I309" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L309" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O309" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="310">
@@ -8472,27 +9024,27 @@
     </row>
     <row r="312">
       <c r="F312" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G312" s="23"/>
       <c r="N312" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O312" s="23"/>
     </row>
     <row r="313">
       <c r="F313" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G313" s="23"/>
       <c r="N313" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O313" s="23"/>
     </row>
     <row r="321">
       <c r="A321" s="11" t="s">
-        <v>288</v>
+        <v>380</v>
       </c>
       <c r="B321" s="11"/>
       <c r="C321" s="11"/>
@@ -8501,7 +9053,7 @@
       <c r="F321" s="11"/>
       <c r="G321" s="11"/>
       <c r="I321" s="11" t="s">
-        <v>289</v>
+        <v>381</v>
       </c>
       <c r="J321" s="11"/>
       <c r="K321" s="11"/>
@@ -8512,22 +9064,22 @@
     </row>
     <row r="322">
       <c r="A322" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D322" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G322" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I322" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L322" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O322" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="323">
@@ -8556,27 +9108,27 @@
     </row>
     <row r="325">
       <c r="F325" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G325" s="23"/>
       <c r="N325" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O325" s="23"/>
     </row>
     <row r="326">
       <c r="F326" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G326" s="23"/>
       <c r="N326" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O326" s="23"/>
     </row>
     <row r="329">
       <c r="A329" s="11" t="s">
-        <v>290</v>
+        <v>382</v>
       </c>
       <c r="B329" s="11"/>
       <c r="C329" s="11"/>
@@ -8585,7 +9137,7 @@
       <c r="F329" s="11"/>
       <c r="G329" s="11"/>
       <c r="I329" s="11" t="s">
-        <v>291</v>
+        <v>383</v>
       </c>
       <c r="J329" s="11"/>
       <c r="K329" s="11"/>
@@ -8596,22 +9148,22 @@
     </row>
     <row r="330">
       <c r="A330" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D330" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G330" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I330" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L330" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O330" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="331">
@@ -8640,27 +9192,27 @@
     </row>
     <row r="333">
       <c r="F333" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G333" s="23"/>
       <c r="N333" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O333" s="23"/>
     </row>
     <row r="334">
       <c r="F334" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G334" s="23"/>
       <c r="N334" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O334" s="23"/>
     </row>
     <row r="337">
       <c r="A337" s="11" t="s">
-        <v>292</v>
+        <v>384</v>
       </c>
       <c r="B337" s="11"/>
       <c r="C337" s="11"/>
@@ -8669,7 +9221,7 @@
       <c r="F337" s="11"/>
       <c r="G337" s="11"/>
       <c r="I337" s="11" t="s">
-        <v>293</v>
+        <v>385</v>
       </c>
       <c r="J337" s="11"/>
       <c r="K337" s="11"/>
@@ -8680,22 +9232,22 @@
     </row>
     <row r="338">
       <c r="A338" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D338" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G338" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I338" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L338" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O338" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="339">
@@ -8724,27 +9276,27 @@
     </row>
     <row r="341">
       <c r="F341" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G341" s="23"/>
       <c r="N341" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O341" s="23"/>
     </row>
     <row r="342">
       <c r="F342" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G342" s="23"/>
       <c r="N342" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O342" s="23"/>
     </row>
     <row r="345">
       <c r="A345" s="11" t="s">
-        <v>294</v>
+        <v>386</v>
       </c>
       <c r="B345" s="11"/>
       <c r="C345" s="11"/>
@@ -8753,7 +9305,7 @@
       <c r="F345" s="11"/>
       <c r="G345" s="11"/>
       <c r="I345" s="11" t="s">
-        <v>295</v>
+        <v>387</v>
       </c>
       <c r="J345" s="11"/>
       <c r="K345" s="11"/>
@@ -8764,22 +9316,22 @@
     </row>
     <row r="346">
       <c r="A346" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D346" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G346" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I346" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L346" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O346" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="347">
@@ -8808,27 +9360,27 @@
     </row>
     <row r="349">
       <c r="F349" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G349" s="23"/>
       <c r="N349" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O349" s="23"/>
     </row>
     <row r="350">
       <c r="F350" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G350" s="23"/>
       <c r="N350" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O350" s="23"/>
     </row>
     <row r="358">
       <c r="A358" s="11" t="s">
-        <v>296</v>
+        <v>388</v>
       </c>
       <c r="B358" s="11"/>
       <c r="C358" s="11"/>
@@ -8837,7 +9389,7 @@
       <c r="F358" s="11"/>
       <c r="G358" s="11"/>
       <c r="I358" s="11" t="s">
-        <v>297</v>
+        <v>389</v>
       </c>
       <c r="J358" s="11"/>
       <c r="K358" s="11"/>
@@ -8848,22 +9400,22 @@
     </row>
     <row r="359">
       <c r="A359" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D359" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G359" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I359" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L359" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O359" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="360">
@@ -8892,27 +9444,27 @@
     </row>
     <row r="362">
       <c r="F362" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G362" s="23"/>
       <c r="N362" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O362" s="23"/>
     </row>
     <row r="363">
       <c r="F363" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G363" s="23"/>
       <c r="N363" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O363" s="23"/>
     </row>
     <row r="366">
       <c r="A366" s="11" t="s">
-        <v>298</v>
+        <v>390</v>
       </c>
       <c r="B366" s="11"/>
       <c r="C366" s="11"/>
@@ -8921,7 +9473,7 @@
       <c r="F366" s="11"/>
       <c r="G366" s="11"/>
       <c r="I366" s="11" t="s">
-        <v>299</v>
+        <v>391</v>
       </c>
       <c r="J366" s="11"/>
       <c r="K366" s="11"/>
@@ -8932,22 +9484,22 @@
     </row>
     <row r="367">
       <c r="A367" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D367" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G367" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I367" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L367" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O367" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="368">
@@ -8976,27 +9528,27 @@
     </row>
     <row r="370">
       <c r="F370" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G370" s="23"/>
       <c r="N370" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O370" s="23"/>
     </row>
     <row r="371">
       <c r="F371" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G371" s="23"/>
       <c r="N371" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O371" s="23"/>
     </row>
     <row r="379">
       <c r="A379" s="11" t="s">
-        <v>300</v>
+        <v>392</v>
       </c>
       <c r="B379" s="11"/>
       <c r="C379" s="11"/>
@@ -9005,7 +9557,7 @@
       <c r="F379" s="11"/>
       <c r="G379" s="11"/>
       <c r="I379" s="11" t="s">
-        <v>301</v>
+        <v>393</v>
       </c>
       <c r="J379" s="11"/>
       <c r="K379" s="11"/>
@@ -9016,22 +9568,22 @@
     </row>
     <row r="380">
       <c r="A380" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D380" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G380" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="I380" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="L380" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="O380" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="381">
@@ -9060,27 +9612,27 @@
     </row>
     <row r="383">
       <c r="F383" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G383" s="23"/>
       <c r="N383" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="O383" s="23"/>
     </row>
     <row r="384">
       <c r="F384" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G384" s="23"/>
       <c r="N384" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="O384" s="23"/>
     </row>
     <row r="392">
       <c r="A392" s="11" t="s">
-        <v>302</v>
+        <v>394</v>
       </c>
       <c r="B392" s="11"/>
       <c r="C392" s="11"/>
@@ -9091,13 +9643,13 @@
     </row>
     <row r="393">
       <c r="A393" s="21" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="D393" s="19" t="s">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G393" s="20" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
     </row>
     <row r="394">
@@ -9115,13 +9667,13 @@
     </row>
     <row r="396">
       <c r="F396" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="G396" s="23"/>
     </row>
     <row r="397">
       <c r="F397" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G397" s="23"/>
     </row>
@@ -9271,7 +9823,7 @@
     </row>
     <row r="5">
       <c r="C5" s="16" t="s">
-        <v>65</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6">
@@ -9282,7 +9834,7 @@
     </row>
     <row r="7">
       <c r="C7" s="16" t="s">
-        <v>186</v>
+        <v>267</v>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="12"/>
@@ -9311,7 +9863,7 @@
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
-        <v>188</v>
+        <v>270</v>
       </c>
       <c r="I14" s="12"/>
       <c r="K14" s="12"/>
@@ -9332,7 +9884,7 @@
     </row>
     <row r="17">
       <c r="C17" s="16" t="s">
-        <v>179</v>
+        <v>256</v>
       </c>
       <c r="G17" s="12"/>
       <c r="K17" s="12"/>
@@ -9348,7 +9900,7 @@
     </row>
     <row r="19">
       <c r="C19" s="16" t="s">
-        <v>181</v>
+        <v>259</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="12"/>
@@ -9366,7 +9918,7 @@
       <c r="C22" s="16"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="K22" s="12"/>
     </row>
@@ -9383,7 +9935,7 @@
     </row>
     <row r="25">
       <c r="C25" s="16" t="s">
-        <v>132</v>
+        <v>189</v>
       </c>
       <c r="G25" s="12"/>
       <c r="H25" s="14"/>
@@ -9402,7 +9954,7 @@
     </row>
     <row r="27">
       <c r="C27" s="16" t="s">
-        <v>184</v>
+        <v>264</v>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="12"/>
@@ -9423,7 +9975,7 @@
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
-        <v>190</v>
+        <v>273</v>
       </c>
       <c r="I30" s="12"/>
     </row>
@@ -9441,7 +9993,7 @@
     </row>
     <row r="33">
       <c r="C33" s="16" t="s">
-        <v>192</v>
+        <v>276</v>
       </c>
       <c r="G33" s="12"/>
     </row>
@@ -9455,7 +10007,7 @@
     </row>
     <row r="35">
       <c r="C35" s="16" t="s">
-        <v>110</v>
+        <v>159</v>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="12"/>
@@ -9501,7 +10053,7 @@
     </row>
     <row r="5">
       <c r="C5" s="16" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6">
@@ -9512,7 +10064,7 @@
     </row>
     <row r="7">
       <c r="C7" s="16" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="12"/>
@@ -9541,7 +10093,7 @@
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="I14" s="12"/>
       <c r="K14" s="12"/>
@@ -9562,7 +10114,7 @@
     </row>
     <row r="17">
       <c r="C17" s="16" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="G17" s="12"/>
       <c r="K17" s="12"/>
@@ -9578,7 +10130,7 @@
     </row>
     <row r="19">
       <c r="C19" s="16" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="12"/>
@@ -9596,7 +10148,7 @@
       <c r="C22" s="16"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="K22" s="12"/>
     </row>
@@ -9613,7 +10165,7 @@
     </row>
     <row r="25">
       <c r="C25" s="16" t="s">
-        <v>141</v>
+        <v>201</v>
       </c>
       <c r="G25" s="12"/>
       <c r="H25" s="14"/>
@@ -9632,7 +10184,7 @@
     </row>
     <row r="27">
       <c r="C27" s="16" t="s">
-        <v>144</v>
+        <v>205</v>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="12"/>
@@ -9653,7 +10205,7 @@
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
-        <v>147</v>
+        <v>209</v>
       </c>
       <c r="I30" s="12"/>
     </row>
@@ -9671,7 +10223,7 @@
     </row>
     <row r="33">
       <c r="C33" s="16" t="s">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="G33" s="12"/>
     </row>
@@ -9685,7 +10237,7 @@
     </row>
     <row r="35">
       <c r="C35" s="16" t="s">
-        <v>203</v>
+        <v>293</v>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="12"/>

--- a/playoffs-example-large.xlsx
+++ b/playoffs-example-large.xlsx
@@ -74,7 +74,7 @@
     <t/>
   </si>
   <si>
-    <t>Number</t>
+    <t>Draw order</t>
   </si>
   <si>
     <t>Player Name</t>
@@ -1469,7 +1469,7 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" shrinkToFit="true" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
@@ -1808,7 +1808,7 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B3" t="s">
         <v>17</v>
@@ -1825,7 +1825,7 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
@@ -1842,7 +1842,7 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
@@ -1859,7 +1859,7 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
         <v>29</v>
@@ -1876,7 +1876,7 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
         <v>33</v>
@@ -1893,7 +1893,7 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
         <v>37</v>
@@ -1910,7 +1910,7 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B9" t="s">
         <v>40</v>
@@ -1927,7 +1927,7 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B10" t="s">
         <v>43</v>
@@ -1944,7 +1944,7 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B11" t="s">
         <v>46</v>
@@ -1961,7 +1961,7 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B12" t="s">
         <v>49</v>
@@ -1978,7 +1978,7 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B13" t="s">
         <v>52</v>
@@ -1995,7 +1995,7 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B14" t="s">
         <v>55</v>
@@ -2012,7 +2012,7 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B15" t="s">
         <v>58</v>
@@ -2029,7 +2029,7 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B16" t="s">
         <v>61</v>
@@ -2046,7 +2046,7 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B17" t="s">
         <v>64</v>
@@ -2063,7 +2063,7 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B18" t="s">
         <v>67</v>
@@ -2080,7 +2080,7 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
         <v>70</v>
@@ -2097,7 +2097,7 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B20" t="s">
         <v>73</v>
@@ -2114,7 +2114,7 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B21" t="s">
         <v>76</v>
@@ -2131,7 +2131,7 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B22" t="s">
         <v>79</v>
@@ -2148,7 +2148,7 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B23" t="s">
         <v>82</v>
@@ -2165,7 +2165,7 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B24" t="s">
         <v>85</v>
@@ -2182,7 +2182,7 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B25" t="s">
         <v>89</v>
@@ -2199,7 +2199,7 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B26" t="s">
         <v>93</v>
@@ -2216,7 +2216,7 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B27" t="s">
         <v>97</v>
@@ -2233,7 +2233,7 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B28" t="s">
         <v>101</v>
@@ -2250,7 +2250,7 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B29" t="s">
         <v>105</v>
@@ -2267,7 +2267,7 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B30" t="s">
         <v>108</v>
@@ -2284,7 +2284,7 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B31" t="s">
         <v>110</v>
@@ -2301,7 +2301,7 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B32" t="s">
         <v>113</v>
@@ -2318,7 +2318,7 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B33" t="s">
         <v>115</v>
@@ -2335,7 +2335,7 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B34" t="s">
         <v>117</v>
@@ -2352,7 +2352,7 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B35" t="s">
         <v>119</v>
@@ -2369,7 +2369,7 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B36" t="s">
         <v>121</v>
@@ -2386,7 +2386,7 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B37" t="s">
         <v>123</v>
@@ -2403,7 +2403,7 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B38" t="s">
         <v>125</v>
@@ -2420,7 +2420,7 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B39" t="s">
         <v>127</v>
@@ -2437,7 +2437,7 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B40" t="s">
         <v>129</v>
@@ -2454,7 +2454,7 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B41" t="s">
         <v>131</v>
@@ -2471,7 +2471,7 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B42" t="s">
         <v>133</v>
@@ -2488,7 +2488,7 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B43" t="s">
         <v>135</v>
@@ -2505,7 +2505,7 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B44" t="s">
         <v>137</v>
@@ -2522,7 +2522,7 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B45" t="s">
         <v>140</v>
@@ -2539,7 +2539,7 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B46" t="s">
         <v>143</v>
@@ -2556,7 +2556,7 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B47" t="s">
         <v>146</v>
@@ -2573,7 +2573,7 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B48" t="s">
         <v>149</v>
@@ -2590,7 +2590,7 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B49" t="s">
         <v>152</v>
@@ -2607,7 +2607,7 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B50" t="s">
         <v>155</v>
@@ -2624,7 +2624,7 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B51" t="s">
         <v>158</v>
@@ -2641,7 +2641,7 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B52" t="s">
         <v>161</v>
@@ -2658,7 +2658,7 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B53" t="s">
         <v>164</v>
@@ -2675,7 +2675,7 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B54" t="s">
         <v>167</v>
@@ -2692,7 +2692,7 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B55" t="s">
         <v>171</v>
@@ -2709,7 +2709,7 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B56" t="s">
         <v>175</v>
@@ -2726,7 +2726,7 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B57" t="s">
         <v>179</v>
@@ -2743,7 +2743,7 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B58" t="s">
         <v>183</v>
@@ -2760,7 +2760,7 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B59" t="s">
         <v>187</v>
@@ -2777,7 +2777,7 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B60" t="s">
         <v>191</v>
@@ -2794,7 +2794,7 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B61" t="s">
         <v>195</v>
@@ -2811,7 +2811,7 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B62" t="s">
         <v>199</v>
@@ -2828,7 +2828,7 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B63" t="s">
         <v>203</v>
@@ -2845,7 +2845,7 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B64" t="s">
         <v>207</v>
@@ -2862,7 +2862,7 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B65" t="s">
         <v>211</v>
@@ -2879,7 +2879,7 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B66" t="s">
         <v>215</v>
@@ -2896,7 +2896,7 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B67" t="s">
         <v>219</v>
@@ -2913,7 +2913,7 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B68" t="s">
         <v>223</v>
@@ -2930,7 +2930,7 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B69" t="s">
         <v>226</v>
@@ -2947,7 +2947,7 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B70" t="s">
         <v>229</v>
@@ -2964,7 +2964,7 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B71" t="s">
         <v>232</v>
@@ -2981,7 +2981,7 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B72" t="s">
         <v>235</v>
@@ -2998,7 +2998,7 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B73" t="s">
         <v>238</v>
@@ -3015,7 +3015,7 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B74" t="s">
         <v>241</v>
@@ -3032,7 +3032,7 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B75" t="s">
         <v>243</v>
@@ -3049,7 +3049,7 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B76" t="s">
         <v>246</v>
@@ -3066,7 +3066,7 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B77" t="s">
         <v>249</v>
@@ -3083,7 +3083,7 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B78" t="s">
         <v>252</v>
@@ -3100,7 +3100,7 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B79" t="s">
         <v>255</v>
@@ -3117,7 +3117,7 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B80" t="s">
         <v>258</v>
@@ -3134,7 +3134,7 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B81" t="s">
         <v>261</v>
@@ -3151,7 +3151,7 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B82" t="s">
         <v>263</v>
@@ -3168,7 +3168,7 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B83" t="s">
         <v>266</v>
@@ -3185,7 +3185,7 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B84" t="s">
         <v>269</v>
@@ -3202,7 +3202,7 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B85" t="s">
         <v>272</v>
@@ -3219,7 +3219,7 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B86" t="s">
         <v>275</v>
@@ -3236,7 +3236,7 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B87" t="s">
         <v>278</v>
@@ -3253,7 +3253,7 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B88" t="s">
         <v>281</v>
@@ -3270,7 +3270,7 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B89" t="s">
         <v>283</v>
@@ -3287,7 +3287,7 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B90" t="s">
         <v>286</v>
@@ -3304,7 +3304,7 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B91" t="s">
         <v>289</v>
@@ -3321,7 +3321,7 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B92" t="s">
         <v>292</v>
@@ -3338,7 +3338,7 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B93" t="s">
         <v>295</v>

--- a/playoffs-example-large.xlsx
+++ b/playoffs-example-large.xlsx
@@ -2849,7 +2849,7 @@
     </row>
     <row r="7">
       <c r="C7" s="16" t="s">
-        <v>71</v>
+        <v>184</v>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="12"/>
@@ -2878,7 +2878,7 @@
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
-        <v>74</v>
+        <v>129</v>
       </c>
       <c r="I14" s="12"/>
       <c r="K14" s="12"/>
@@ -2899,7 +2899,7 @@
     </row>
     <row r="17">
       <c r="C17" s="16" t="s">
-        <v>77</v>
+        <v>132</v>
       </c>
       <c r="G17" s="12"/>
       <c r="K17" s="12"/>
@@ -2915,7 +2915,7 @@
     </row>
     <row r="19">
       <c r="C19" s="16" t="s">
-        <v>79</v>
+        <v>123</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="12"/>
@@ -3022,7 +3022,7 @@
     </row>
     <row r="35">
       <c r="C35" s="16" t="s">
-        <v>120</v>
+        <v>52</v>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="12"/>
@@ -3142,7 +3142,7 @@
     </row>
     <row r="17">
       <c r="C17" s="16" t="s">
-        <v>40</v>
+        <v>199</v>
       </c>
       <c r="G17" s="12"/>
       <c r="K17" s="12"/>
@@ -3158,7 +3158,7 @@
     </row>
     <row r="19">
       <c r="C19" s="16" t="s">
-        <v>42</v>
+        <v>201</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="12"/>
@@ -3176,7 +3176,7 @@
       <c r="C22" s="16"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16" t="s">
-        <v>44</v>
+        <v>120</v>
       </c>
       <c r="K22" s="12"/>
     </row>
@@ -3193,7 +3193,7 @@
     </row>
     <row r="25">
       <c r="C25" s="16" t="s">
-        <v>117</v>
+        <v>46</v>
       </c>
       <c r="G25" s="12"/>
       <c r="H25" s="14"/>
@@ -3311,7 +3311,7 @@
     </row>
     <row r="5">
       <c r="C5" s="16" t="s">
-        <v>104</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6">
@@ -3322,7 +3322,7 @@
     </row>
     <row r="7">
       <c r="C7" s="16" t="s">
-        <v>106</v>
+        <v>50</v>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="12"/>
@@ -3372,7 +3372,7 @@
     </row>
     <row r="17">
       <c r="C17" s="16" t="s">
-        <v>42</v>
+        <v>110</v>
       </c>
       <c r="G17" s="12"/>
       <c r="K17" s="12"/>
@@ -3423,7 +3423,7 @@
     </row>
     <row r="25">
       <c r="C25" s="16" t="s">
-        <v>46</v>
+        <v>117</v>
       </c>
       <c r="G25" s="12"/>
       <c r="H25" s="14"/>
@@ -3442,7 +3442,7 @@
     </row>
     <row r="27">
       <c r="C27" s="16" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="12"/>
@@ -3463,7 +3463,7 @@
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
-        <v>123</v>
+        <v>18</v>
       </c>
       <c r="I30" s="12"/>
     </row>
@@ -3495,7 +3495,7 @@
     </row>
     <row r="35">
       <c r="C35" s="16" t="s">
-        <v>129</v>
+        <v>24</v>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="12"/>
@@ -3543,7 +3543,7 @@
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
       <c r="E6" s="16" t="s">
-        <v>132</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7">
@@ -3574,7 +3574,7 @@
     </row>
     <row r="11">
       <c r="C11" s="16" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="12"/>
@@ -3594,7 +3594,7 @@
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="I14" s="12"/>
       <c r="K14" s="12"/>
@@ -3615,7 +3615,7 @@
     </row>
     <row r="17">
       <c r="C17" s="16" t="s">
-        <v>58</v>
+        <v>144</v>
       </c>
       <c r="G17" s="12"/>
       <c r="K17" s="12"/>
@@ -3631,7 +3631,7 @@
     </row>
     <row r="19">
       <c r="C19" s="16" t="s">
-        <v>60</v>
+        <v>106</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="12"/>
@@ -3706,7 +3706,7 @@
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
-        <v>171</v>
+        <v>104</v>
       </c>
       <c r="I30" s="12"/>
     </row>
@@ -3845,7 +3845,7 @@
     </row>
     <row r="17">
       <c r="C17" s="16" t="s">
-        <v>162</v>
+        <v>21</v>
       </c>
       <c r="G17" s="12"/>
       <c r="K17" s="12"/>
@@ -3861,7 +3861,7 @@
     </row>
     <row r="19">
       <c r="C19" s="16" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="12"/>
@@ -3936,7 +3936,7 @@
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="I30" s="12"/>
     </row>
@@ -3954,7 +3954,7 @@
     </row>
     <row r="33">
       <c r="C33" s="16" t="s">
-        <v>30</v>
+        <v>181</v>
       </c>
       <c r="G33" s="12"/>
     </row>
@@ -3968,7 +3968,7 @@
     </row>
     <row r="35">
       <c r="C35" s="16" t="s">
-        <v>34</v>
+        <v>132</v>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="12"/>
@@ -4016,7 +4016,7 @@
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
       <c r="E6" s="16" t="s">
-        <v>36</v>
+        <v>162</v>
       </c>
     </row>
     <row r="7">
@@ -4030,7 +4030,7 @@
     </row>
     <row r="9">
       <c r="C9" s="16" t="s">
-        <v>18</v>
+        <v>186</v>
       </c>
       <c r="G9" s="12"/>
       <c r="H9" s="14"/>
@@ -4047,7 +4047,7 @@
     </row>
     <row r="11">
       <c r="C11" s="16" t="s">
-        <v>24</v>
+        <v>188</v>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="12"/>
@@ -4067,7 +4067,7 @@
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="I14" s="12"/>
       <c r="K14" s="12"/>
@@ -4088,7 +4088,7 @@
     </row>
     <row r="17">
       <c r="C17" s="16" t="s">
-        <v>40</v>
+        <v>192</v>
       </c>
       <c r="G17" s="12"/>
       <c r="K17" s="12"/>
@@ -4122,7 +4122,7 @@
       <c r="C22" s="16"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16" t="s">
-        <v>164</v>
+        <v>48</v>
       </c>
       <c r="K22" s="12"/>
     </row>
@@ -4158,7 +4158,7 @@
     </row>
     <row r="27">
       <c r="C27" s="16" t="s">
-        <v>199</v>
+        <v>40</v>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="12"/>
@@ -4179,7 +4179,7 @@
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
-        <v>201</v>
+        <v>42</v>
       </c>
       <c r="I30" s="12"/>
     </row>
@@ -4197,7 +4197,7 @@
     </row>
     <row r="33">
       <c r="C33" s="16" t="s">
-        <v>21</v>
+        <v>203</v>
       </c>
       <c r="G33" s="12"/>
     </row>
@@ -4236,130 +4236,130 @@
   <sheetData>
     <row r="1" ht="270" customHeight="true">
       <c r="A1" s="17">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B1" s="18" t="str">
-        <f>'data'!D24</f>
+        <f>'data'!D29</f>
       </c>
     </row>
     <row r="2" ht="270" customHeight="true">
       <c r="A2" s="17">
-        <v>80</v>
+        <v>23</v>
       </c>
       <c r="B2" s="18" t="str">
-        <f>'data'!D83</f>
+        <f>'data'!D26</f>
       </c>
     </row>
     <row r="3" ht="270" customHeight="true">
       <c r="A3" s="17">
-        <v>81</v>
+        <v>24</v>
       </c>
       <c r="B3" s="18" t="str">
-        <f>'data'!D84</f>
+        <f>'data'!D27</f>
       </c>
     </row>
     <row r="4" ht="270" customHeight="true">
       <c r="A4" s="17">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="B4" s="18" t="str">
-        <f>'data'!D79</f>
+        <f>'data'!D28</f>
       </c>
     </row>
     <row r="5" ht="270" customHeight="true">
       <c r="A5" s="17">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B5" s="18" t="str">
-        <f>'data'!D80</f>
+        <f>'data'!D85</f>
       </c>
     </row>
     <row r="6" ht="270" customHeight="true">
       <c r="A6" s="17">
-        <v>5</v>
+        <v>76</v>
       </c>
       <c r="B6" s="18" t="str">
-        <f>'data'!D8</f>
+        <f>'data'!D79</f>
       </c>
     </row>
     <row r="7" ht="270" customHeight="true">
       <c r="A7" s="17">
-        <v>78</v>
+        <v>6</v>
       </c>
       <c r="B7" s="18" t="str">
-        <f>'data'!D81</f>
+        <f>'data'!D9</f>
       </c>
     </row>
     <row r="8" ht="270" customHeight="true">
       <c r="A8" s="17">
-        <v>79</v>
+        <v>7</v>
       </c>
       <c r="B8" s="18" t="str">
-        <f>'data'!D82</f>
+        <f>'data'!D10</f>
       </c>
     </row>
     <row r="9" ht="270" customHeight="true">
       <c r="A9" s="17">
-        <v>82</v>
+        <v>8</v>
       </c>
       <c r="B9" s="18" t="str">
-        <f>'data'!D85</f>
+        <f>'data'!D11</f>
       </c>
     </row>
     <row r="10" ht="270" customHeight="true">
       <c r="A10" s="17">
-        <v>83</v>
+        <v>9</v>
       </c>
       <c r="B10" s="18" t="str">
-        <f>'data'!D86</f>
+        <f>'data'!D12</f>
       </c>
     </row>
     <row r="11" ht="270" customHeight="true">
       <c r="A11" s="17">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="B11" s="18" t="str">
-        <f>'data'!D51</f>
+        <f>'data'!D13</f>
       </c>
     </row>
     <row r="12" ht="270" customHeight="true">
       <c r="A12" s="17">
-        <v>11</v>
+        <v>58</v>
       </c>
       <c r="B12" s="18" t="str">
-        <f>'data'!D14</f>
+        <f>'data'!D61</f>
       </c>
     </row>
     <row r="13" ht="270" customHeight="true">
       <c r="A13" s="17">
-        <v>12</v>
+        <v>59</v>
       </c>
       <c r="B13" s="18" t="str">
-        <f>'data'!D15</f>
+        <f>'data'!D62</f>
       </c>
     </row>
     <row r="14" ht="270" customHeight="true">
       <c r="A14" s="17">
-        <v>13</v>
+        <v>85</v>
       </c>
       <c r="B14" s="18" t="str">
-        <f>'data'!D16</f>
+        <f>'data'!D88</f>
       </c>
     </row>
     <row r="15" ht="270" customHeight="true">
       <c r="A15" s="17">
-        <v>14</v>
+        <v>61</v>
       </c>
       <c r="B15" s="18" t="str">
-        <f>'data'!D17</f>
+        <f>'data'!D64</f>
       </c>
     </row>
     <row r="16" ht="270" customHeight="true">
       <c r="A16" s="17">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="B16" s="18" t="str">
-        <f>'data'!D18</f>
+        <f>'data'!D35</f>
       </c>
     </row>
     <row r="17" ht="270" customHeight="true">
@@ -4372,26 +4372,26 @@
     </row>
     <row r="18" ht="270" customHeight="true">
       <c r="A18" s="17">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="B18" s="18" t="str">
-        <f>'data'!D62</f>
+        <f>'data'!D20</f>
       </c>
     </row>
     <row r="19" ht="270" customHeight="true">
       <c r="A19" s="17">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="B19" s="18" t="str">
-        <f>'data'!D63</f>
+        <f>'data'!D21</f>
       </c>
     </row>
     <row r="20" ht="270" customHeight="true">
       <c r="A20" s="17">
-        <v>61</v>
+        <v>19</v>
       </c>
       <c r="B20" s="18" t="str">
-        <f>'data'!D64</f>
+        <f>'data'!D22</f>
       </c>
     </row>
     <row r="21" ht="270" customHeight="true">
@@ -4404,10 +4404,10 @@
     </row>
     <row r="22" ht="270" customHeight="true">
       <c r="A22" s="17">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="B22" s="18" t="str">
-        <f>'data'!D92</f>
+        <f>'data'!D24</f>
       </c>
     </row>
     <row r="23" ht="270" customHeight="true">
@@ -4420,34 +4420,34 @@
     </row>
     <row r="24" ht="270" customHeight="true">
       <c r="A24" s="17">
-        <v>23</v>
+        <v>79</v>
       </c>
       <c r="B24" s="18" t="str">
-        <f>'data'!D26</f>
+        <f>'data'!D82</f>
       </c>
     </row>
     <row r="25" ht="270" customHeight="true">
       <c r="A25" s="17">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="B25" s="18" t="str">
-        <f>'data'!D27</f>
+        <f>'data'!D58</f>
       </c>
     </row>
     <row r="26" ht="270" customHeight="true">
       <c r="A26" s="17">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="B26" s="18" t="str">
-        <f>'data'!D28</f>
+        <f>'data'!D59</f>
       </c>
     </row>
     <row r="27" ht="270" customHeight="true">
       <c r="A27" s="17">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="B27" s="18" t="str">
-        <f>'data'!D29</f>
+        <f>'data'!D56</f>
       </c>
     </row>
     <row r="28" ht="270" customHeight="true">
@@ -4492,10 +4492,10 @@
     </row>
     <row r="33" ht="270" customHeight="true">
       <c r="A33" s="17">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="B33" s="18" t="str">
-        <f>'data'!D55</f>
+        <f>'data'!D18</f>
       </c>
     </row>
     <row r="34" ht="270" customHeight="true">
@@ -4532,34 +4532,34 @@
     </row>
     <row r="38" ht="270" customHeight="true">
       <c r="A38" s="17">
-        <v>37</v>
+        <v>87</v>
       </c>
       <c r="B38" s="18" t="str">
-        <f>'data'!D40</f>
+        <f>'data'!D90</f>
       </c>
     </row>
     <row r="39" ht="270" customHeight="true">
       <c r="A39" s="17">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="B39" s="18" t="str">
-        <f>'data'!D41</f>
+        <f>'data'!D91</f>
       </c>
     </row>
     <row r="40" ht="270" customHeight="true">
       <c r="A40" s="17">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="B40" s="18" t="str">
-        <f>'data'!D42</f>
+        <f>'data'!D55</f>
       </c>
     </row>
     <row r="41" ht="270" customHeight="true">
       <c r="A41" s="17">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="B41" s="18" t="str">
-        <f>'data'!D54</f>
+        <f>'data'!D43</f>
       </c>
     </row>
     <row r="42" ht="270" customHeight="true">
@@ -4596,10 +4596,10 @@
     </row>
     <row r="46" ht="270" customHeight="true">
       <c r="A46" s="17">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="B46" s="18" t="str">
-        <f>'data'!D48</f>
+        <f>'data'!D14</f>
       </c>
     </row>
   </sheetData>
@@ -4637,10 +4637,10 @@
   <sheetData>
     <row r="1" ht="270" customHeight="true">
       <c r="A1" s="17">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="B1" s="18" t="str">
-        <f>'data'!D49</f>
+        <f>'data'!D17</f>
       </c>
     </row>
     <row r="2" ht="270" customHeight="true">
@@ -4653,10 +4653,10 @@
     </row>
     <row r="3" ht="270" customHeight="true">
       <c r="A3" s="17">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="B3" s="18" t="str">
-        <f>'data'!D13</f>
+        <f>'data'!D51</f>
       </c>
     </row>
     <row r="4" ht="270" customHeight="true">
@@ -4677,26 +4677,26 @@
     </row>
     <row r="6" ht="270" customHeight="true">
       <c r="A6" s="17">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="B6" s="18" t="str">
-        <f>'data'!D43</f>
+        <f>'data'!D54</f>
       </c>
     </row>
     <row r="7" ht="270" customHeight="true">
       <c r="A7" s="17">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="B7" s="18" t="str">
-        <f>'data'!D35</f>
+        <f>'data'!D42</f>
       </c>
     </row>
     <row r="8" ht="270" customHeight="true">
       <c r="A8" s="17">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="B8" s="18" t="str">
-        <f>'data'!D56</f>
+        <f>'data'!D3</f>
       </c>
     </row>
     <row r="9" ht="270" customHeight="true">
@@ -4709,18 +4709,18 @@
     </row>
     <row r="10" ht="270" customHeight="true">
       <c r="A10" s="17">
-        <v>55</v>
+        <v>2</v>
       </c>
       <c r="B10" s="18" t="str">
-        <f>'data'!D58</f>
+        <f>'data'!D5</f>
       </c>
     </row>
     <row r="11" ht="270" customHeight="true">
       <c r="A11" s="17">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="B11" s="18" t="str">
-        <f>'data'!D59</f>
+        <f>'data'!D6</f>
       </c>
     </row>
     <row r="12" ht="270" customHeight="true">
@@ -4733,34 +4733,34 @@
     </row>
     <row r="13" ht="270" customHeight="true">
       <c r="A13" s="17">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="B13" s="18" t="str">
-        <f>'data'!D61</f>
+        <f>'data'!D68</f>
       </c>
     </row>
     <row r="14" ht="270" customHeight="true">
       <c r="A14" s="17">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B14" s="18" t="str">
-        <f>'data'!D20</f>
+        <f>'data'!D15</f>
       </c>
     </row>
     <row r="15" ht="270" customHeight="true">
       <c r="A15" s="17">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="B15" s="18" t="str">
-        <f>'data'!D21</f>
+        <f>'data'!D63</f>
       </c>
     </row>
     <row r="16" ht="270" customHeight="true">
       <c r="A16" s="17">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="B16" s="18" t="str">
-        <f>'data'!D22</f>
+        <f>'data'!D49</f>
       </c>
     </row>
     <row r="17" ht="270" customHeight="true">
@@ -4789,10 +4789,10 @@
     </row>
     <row r="20" ht="270" customHeight="true">
       <c r="A20" s="17">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="B20" s="18" t="str">
-        <f>'data'!D75</f>
+        <f>'data'!D48</f>
       </c>
     </row>
     <row r="21" ht="270" customHeight="true">
@@ -4837,18 +4837,18 @@
     </row>
     <row r="26" ht="270" customHeight="true">
       <c r="A26" s="17">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="B26" s="18" t="str">
-        <f>'data'!D74</f>
+        <f>'data'!D4</f>
       </c>
     </row>
     <row r="27" ht="270" customHeight="true">
       <c r="A27" s="17">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="B27" s="18" t="str">
-        <f>'data'!D68</f>
+        <f>'data'!D75</f>
       </c>
     </row>
     <row r="28" ht="270" customHeight="true">
@@ -4877,66 +4877,66 @@
     </row>
     <row r="31" ht="270" customHeight="true">
       <c r="A31" s="17">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B31" s="18" t="str">
-        <f>'data'!D6</f>
+        <f>'data'!D8</f>
       </c>
     </row>
     <row r="32" ht="270" customHeight="true">
       <c r="A32" s="17">
-        <v>4</v>
+        <v>77</v>
       </c>
       <c r="B32" s="18" t="str">
-        <f>'data'!D7</f>
+        <f>'data'!D80</f>
       </c>
     </row>
     <row r="33" ht="270" customHeight="true">
       <c r="A33" s="17">
-        <v>6</v>
+        <v>78</v>
       </c>
       <c r="B33" s="18" t="str">
-        <f>'data'!D9</f>
+        <f>'data'!D81</f>
       </c>
     </row>
     <row r="34" ht="270" customHeight="true">
       <c r="A34" s="17">
-        <v>7</v>
+        <v>71</v>
       </c>
       <c r="B34" s="18" t="str">
-        <f>'data'!D10</f>
+        <f>'data'!D74</f>
       </c>
     </row>
     <row r="35" ht="270" customHeight="true">
       <c r="A35" s="17">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="B35" s="18" t="str">
-        <f>'data'!D3</f>
+        <f>'data'!D83</f>
       </c>
     </row>
     <row r="36" ht="270" customHeight="true">
       <c r="A36" s="17">
-        <v>2</v>
+        <v>81</v>
       </c>
       <c r="B36" s="18" t="str">
-        <f>'data'!D5</f>
+        <f>'data'!D84</f>
       </c>
     </row>
     <row r="37" ht="270" customHeight="true">
       <c r="A37" s="17">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B37" s="18" t="str">
-        <f>'data'!D11</f>
+        <f>'data'!D7</f>
       </c>
     </row>
     <row r="38" ht="270" customHeight="true">
       <c r="A38" s="17">
-        <v>9</v>
+        <v>83</v>
       </c>
       <c r="B38" s="18" t="str">
-        <f>'data'!D12</f>
+        <f>'data'!D86</f>
       </c>
     </row>
     <row r="39" ht="270" customHeight="true">
@@ -4949,10 +4949,10 @@
     </row>
     <row r="40" ht="270" customHeight="true">
       <c r="A40" s="17">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="B40" s="18" t="str">
-        <f>'data'!D88</f>
+        <f>'data'!D16</f>
       </c>
     </row>
     <row r="41" ht="270" customHeight="true">
@@ -4965,26 +4965,26 @@
     </row>
     <row r="42" ht="270" customHeight="true">
       <c r="A42" s="17">
-        <v>87</v>
+        <v>37</v>
       </c>
       <c r="B42" s="18" t="str">
-        <f>'data'!D90</f>
+        <f>'data'!D40</f>
       </c>
     </row>
     <row r="43" ht="270" customHeight="true">
       <c r="A43" s="17">
-        <v>88</v>
+        <v>38</v>
       </c>
       <c r="B43" s="18" t="str">
-        <f>'data'!D91</f>
+        <f>'data'!D41</f>
       </c>
     </row>
     <row r="44" ht="270" customHeight="true">
       <c r="A44" s="17">
-        <v>1</v>
+        <v>89</v>
       </c>
       <c r="B44" s="18" t="str">
-        <f>'data'!D4</f>
+        <f>'data'!D92</f>
       </c>
     </row>
     <row r="45" ht="270" customHeight="true">
@@ -5377,7 +5377,7 @@
     </row>
     <row r="4">
       <c r="A4" s="19" t="str">
-        <f>'data'!$B$83</f>
+        <f>'data'!$B$26</f>
       </c>
       <c r="B4" s="22"/>
       <c r="C4" s="22"/>
@@ -5385,10 +5385,10 @@
       <c r="E4" s="22"/>
       <c r="F4" s="22"/>
       <c r="G4" s="19" t="str">
-        <f>'data'!$B$24</f>
+        <f>'data'!$B$29</f>
       </c>
       <c r="I4" s="19" t="str">
-        <f>'data'!$B$49</f>
+        <f>'data'!$B$17</f>
       </c>
       <c r="J4" s="22"/>
       <c r="K4" s="22"/>
@@ -5396,7 +5396,7 @@
       <c r="M4" s="22"/>
       <c r="N4" s="22"/>
       <c r="O4" s="19" t="str">
-        <f>'data'!$B$48</f>
+        <f>'data'!$B$42</f>
       </c>
     </row>
     <row r="6">
@@ -5461,7 +5461,7 @@
     </row>
     <row r="12">
       <c r="A12" s="19" t="str">
-        <f>'data'!$B$80</f>
+        <f>'data'!$B$85</f>
       </c>
       <c r="B12" s="22"/>
       <c r="C12" s="22"/>
@@ -5469,7 +5469,7 @@
       <c r="E12" s="22"/>
       <c r="F12" s="22"/>
       <c r="G12" s="19" t="str">
-        <f>'data'!$B$79</f>
+        <f>'data'!$B$28</f>
       </c>
       <c r="I12" s="19" t="str">
         <f>'data'!$B$52</f>
@@ -5480,7 +5480,7 @@
       <c r="M12" s="22"/>
       <c r="N12" s="22"/>
       <c r="O12" s="19" t="str">
-        <f>'data'!$B$13</f>
+        <f>'data'!$B$51</f>
       </c>
     </row>
     <row r="14">
@@ -5545,7 +5545,7 @@
     </row>
     <row r="20">
       <c r="A20" s="19" t="str">
-        <f>'data'!$B$82</f>
+        <f>'data'!$B$38</f>
       </c>
       <c r="B20" s="22"/>
       <c r="C20" s="22"/>
@@ -5553,10 +5553,10 @@
       <c r="E20" s="22"/>
       <c r="F20" s="22"/>
       <c r="G20" s="19" t="str">
-        <f>'data'!$B$59</f>
+        <f>'data'!$B$37</f>
       </c>
       <c r="I20" s="19" t="str">
-        <f>'data'!$B$7</f>
+        <f>'data'!$B$42</f>
       </c>
       <c r="J20" s="22"/>
       <c r="K20" s="22"/>
@@ -5564,7 +5564,7 @@
       <c r="M20" s="22"/>
       <c r="N20" s="22"/>
       <c r="O20" s="19" t="str">
-        <f>'data'!$B$43</f>
+        <f>'data'!$B$54</f>
       </c>
     </row>
     <row r="22">
@@ -5629,7 +5629,7 @@
     </row>
     <row r="28">
       <c r="A28" s="19" t="str">
-        <f>'data'!$B$51</f>
+        <f>'data'!$B$41</f>
       </c>
       <c r="B28" s="22"/>
       <c r="C28" s="22"/>
@@ -5637,10 +5637,10 @@
       <c r="E28" s="22"/>
       <c r="F28" s="22"/>
       <c r="G28" s="19" t="str">
-        <f>'data'!$B$86</f>
+        <f>'data'!$B$40</f>
       </c>
       <c r="I28" s="19" t="str">
-        <f>'data'!$B$58</f>
+        <f>'data'!$B$5</f>
       </c>
       <c r="J28" s="22"/>
       <c r="K28" s="22"/>
@@ -5713,7 +5713,7 @@
     </row>
     <row r="36">
       <c r="A36" s="19" t="str">
-        <f>'data'!$B$43</f>
+        <f>'data'!$B$62</f>
       </c>
       <c r="B36" s="22"/>
       <c r="C36" s="22"/>
@@ -5721,10 +5721,10 @@
       <c r="E36" s="22"/>
       <c r="F36" s="22"/>
       <c r="G36" s="19" t="str">
-        <f>'data'!$B$42</f>
+        <f>'data'!$B$61</f>
       </c>
       <c r="I36" s="19" t="str">
-        <f>'data'!$B$61</f>
+        <f>'data'!$B$68</f>
       </c>
       <c r="J36" s="22"/>
       <c r="K36" s="22"/>
@@ -5797,7 +5797,7 @@
     </row>
     <row r="44">
       <c r="A44" s="19" t="str">
-        <f>'data'!$B$18</f>
+        <f>'data'!$B$7</f>
       </c>
       <c r="B44" s="22"/>
       <c r="C44" s="22"/>
@@ -5805,10 +5805,10 @@
       <c r="E44" s="22"/>
       <c r="F44" s="22"/>
       <c r="G44" s="19" t="str">
-        <f>'data'!$B$17</f>
+        <f>'data'!$B$64</f>
       </c>
       <c r="I44" s="19" t="str">
-        <f>'data'!$B$22</f>
+        <f>'data'!$B$49</f>
       </c>
       <c r="J44" s="22"/>
       <c r="K44" s="22"/>
@@ -5816,7 +5816,7 @@
       <c r="M44" s="22"/>
       <c r="N44" s="22"/>
       <c r="O44" s="19" t="str">
-        <f>'data'!$B$21</f>
+        <f>'data'!$B$63</f>
       </c>
     </row>
     <row r="46">
@@ -5881,7 +5881,7 @@
     </row>
     <row r="52">
       <c r="A52" s="19" t="str">
-        <f>'data'!$B$63</f>
+        <f>'data'!$B$21</f>
       </c>
       <c r="B52" s="22"/>
       <c r="C52" s="22"/>
@@ -5889,7 +5889,7 @@
       <c r="E52" s="22"/>
       <c r="F52" s="22"/>
       <c r="G52" s="19" t="str">
-        <f>'data'!$B$62</f>
+        <f>'data'!$B$20</f>
       </c>
       <c r="I52" s="19" t="str">
         <f>'data'!$B$67</f>
@@ -5965,7 +5965,7 @@
     </row>
     <row r="60">
       <c r="A60" s="19" t="str">
-        <f>'data'!$B$92</f>
+        <f>'data'!$B$24</f>
       </c>
       <c r="B60" s="22"/>
       <c r="C60" s="22"/>
@@ -6049,7 +6049,7 @@
     </row>
     <row r="68">
       <c r="A68" s="19" t="str">
-        <f>'data'!$B$26</f>
+        <f>'data'!$B$82</f>
       </c>
       <c r="B68" s="22"/>
       <c r="C68" s="22"/>
@@ -6068,7 +6068,7 @@
       <c r="M68" s="22"/>
       <c r="N68" s="22"/>
       <c r="O68" s="19" t="str">
-        <f>'data'!$B$88</f>
+        <f>'data'!$B$71</f>
       </c>
     </row>
     <row r="70">
@@ -6133,7 +6133,7 @@
     </row>
     <row r="76">
       <c r="A76" s="19" t="str">
-        <f>'data'!$B$29</f>
+        <f>'data'!$B$56</f>
       </c>
       <c r="B76" s="22"/>
       <c r="C76" s="22"/>
@@ -6141,10 +6141,10 @@
       <c r="E76" s="22"/>
       <c r="F76" s="22"/>
       <c r="G76" s="19" t="str">
-        <f>'data'!$B$28</f>
+        <f>'data'!$B$81</f>
       </c>
       <c r="I76" s="19" t="str">
-        <f>'data'!$B$68</f>
+        <f>'data'!$B$75</f>
       </c>
       <c r="J76" s="22"/>
       <c r="K76" s="22"/>
@@ -6152,7 +6152,7 @@
       <c r="M76" s="22"/>
       <c r="N76" s="22"/>
       <c r="O76" s="19" t="str">
-        <f>'data'!$B$74</f>
+        <f>'data'!$B$4</f>
       </c>
     </row>
     <row r="78">
@@ -6301,7 +6301,7 @@
     </row>
     <row r="92">
       <c r="A92" s="19" t="str">
-        <f>'data'!$B$55</f>
+        <f>'data'!$B$18</f>
       </c>
       <c r="B92" s="22"/>
       <c r="C92" s="22"/>
@@ -6312,7 +6312,7 @@
         <f>'data'!$B$5</f>
       </c>
       <c r="I92" s="19" t="str">
-        <f>'data'!$B$9</f>
+        <f>'data'!$B$81</f>
       </c>
       <c r="J92" s="22"/>
       <c r="K92" s="22"/>
@@ -6320,7 +6320,7 @@
       <c r="M92" s="22"/>
       <c r="N92" s="22"/>
       <c r="O92" s="19" t="str">
-        <f>'data'!$B$7</f>
+        <f>'data'!$B$80</f>
       </c>
     </row>
     <row r="94">
@@ -6385,7 +6385,7 @@
     </row>
     <row r="100">
       <c r="A100" s="19" t="str">
-        <f>'data'!$B$10</f>
+        <f>'data'!$B$38</f>
       </c>
       <c r="B100" s="22"/>
       <c r="C100" s="22"/>
@@ -6393,10 +6393,10 @@
       <c r="E100" s="22"/>
       <c r="F100" s="22"/>
       <c r="G100" s="19" t="str">
-        <f>'data'!$B$9</f>
+        <f>'data'!$B$37</f>
       </c>
       <c r="I100" s="19" t="str">
-        <f>'data'!$B$5</f>
+        <f>'data'!$B$84</f>
       </c>
       <c r="J100" s="22"/>
       <c r="K100" s="22"/>
@@ -6404,7 +6404,7 @@
       <c r="M100" s="22"/>
       <c r="N100" s="22"/>
       <c r="O100" s="19" t="str">
-        <f>'data'!$B$3</f>
+        <f>'data'!$B$83</f>
       </c>
     </row>
     <row r="102">
@@ -6469,7 +6469,7 @@
     </row>
     <row r="108">
       <c r="A108" s="19" t="str">
-        <f>'data'!$B$13</f>
+        <f>'data'!$B$91</f>
       </c>
       <c r="B108" s="22"/>
       <c r="C108" s="22"/>
@@ -6477,7 +6477,7 @@
       <c r="E108" s="22"/>
       <c r="F108" s="22"/>
       <c r="G108" s="19" t="str">
-        <f>'data'!$B$12</f>
+        <f>'data'!$B$90</f>
       </c>
       <c r="I108" s="19" t="str">
         <f>'data'!$B$87</f>
@@ -6488,7 +6488,7 @@
       <c r="M108" s="22"/>
       <c r="N108" s="22"/>
       <c r="O108" s="19" t="str">
-        <f>'data'!$B$12</f>
+        <f>'data'!$B$86</f>
       </c>
     </row>
     <row r="110">
@@ -6561,10 +6561,10 @@
       <c r="E116" s="22"/>
       <c r="F116" s="22"/>
       <c r="G116" s="19" t="str">
-        <f>'data'!$B$54</f>
+        <f>'data'!$B$15</f>
       </c>
       <c r="I116" s="19" t="str">
-        <f>'data'!$B$90</f>
+        <f>'data'!$B$40</f>
       </c>
       <c r="J116" s="22"/>
       <c r="K116" s="22"/>
@@ -6656,7 +6656,7 @@
       <c r="M124" s="22"/>
       <c r="N124" s="22"/>
       <c r="O124" s="19" t="str">
-        <f>'data'!$B$4</f>
+        <f>'data'!$B$92</f>
       </c>
     </row>
     <row r="126">
@@ -6729,7 +6729,7 @@
       <c r="E137" s="22"/>
       <c r="F137" s="22"/>
       <c r="G137" s="19" t="str">
-        <f>'data'!$B$84</f>
+        <f>'data'!$B$27</f>
       </c>
       <c r="I137" s="19" t="str">
         <f>CONCATENATE("M 18 ",O14)</f>
@@ -6813,7 +6813,7 @@
       <c r="E145" s="22"/>
       <c r="F145" s="22"/>
       <c r="G145" s="19" t="str">
-        <f>'data'!$B$36</f>
+        <f>'data'!$B$79</f>
       </c>
       <c r="I145" s="19" t="str">
         <f>CONCATENATE("M 19 ",O22)</f>
@@ -6897,7 +6897,7 @@
       <c r="E153" s="22"/>
       <c r="F153" s="22"/>
       <c r="G153" s="19" t="str">
-        <f>'data'!$B$85</f>
+        <f>'data'!$B$39</f>
       </c>
       <c r="I153" s="19" t="str">
         <f>CONCATENATE("M 20 ",O30)</f>
@@ -6908,7 +6908,7 @@
       <c r="M153" s="22"/>
       <c r="N153" s="22"/>
       <c r="O153" s="19" t="str">
-        <f>'data'!$B$56</f>
+        <f>'data'!$B$3</f>
       </c>
     </row>
     <row r="155">
@@ -6981,7 +6981,7 @@
       <c r="E161" s="22"/>
       <c r="F161" s="22"/>
       <c r="G161" s="19" t="str">
-        <f>'data'!$B$16</f>
+        <f>'data'!$B$71</f>
       </c>
       <c r="I161" s="19" t="str">
         <f>CONCATENATE("M 21 ",O38)</f>
@@ -6992,7 +6992,7 @@
       <c r="M161" s="22"/>
       <c r="N161" s="22"/>
       <c r="O161" s="19" t="str">
-        <f>'data'!$B$59</f>
+        <f>'data'!$B$6</f>
       </c>
     </row>
     <row r="163">
@@ -7076,7 +7076,7 @@
       <c r="M169" s="22"/>
       <c r="N169" s="22"/>
       <c r="O169" s="19" t="str">
-        <f>'data'!$B$20</f>
+        <f>'data'!$B$15</f>
       </c>
     </row>
     <row r="171">
@@ -7149,7 +7149,7 @@
       <c r="E177" s="22"/>
       <c r="F177" s="22"/>
       <c r="G177" s="19" t="str">
-        <f>'data'!$B$64</f>
+        <f>'data'!$B$22</f>
       </c>
       <c r="I177" s="19" t="str">
         <f>CONCATENATE("M 23 ",O54)</f>
@@ -7233,7 +7233,7 @@
       <c r="E185" s="22"/>
       <c r="F185" s="22"/>
       <c r="G185" s="19" t="str">
-        <f>'data'!$B$27</f>
+        <f>'data'!$B$58</f>
       </c>
       <c r="I185" s="19" t="str">
         <f>CONCATENATE("M 24 ",O62)</f>
@@ -7244,7 +7244,7 @@
       <c r="M185" s="22"/>
       <c r="N185" s="22"/>
       <c r="O185" s="19" t="str">
-        <f>'data'!$B$75</f>
+        <f>'data'!$B$48</f>
       </c>
     </row>
     <row r="187">
@@ -7485,7 +7485,7 @@
       <c r="E209" s="22"/>
       <c r="F209" s="22"/>
       <c r="G209" s="19" t="str">
-        <f>'data'!$B$36</f>
+        <f>'data'!$B$8</f>
       </c>
       <c r="I209" s="19" t="str">
         <f>CONCATENATE("M 28 ",O94)</f>
@@ -7496,7 +7496,7 @@
       <c r="M209" s="22"/>
       <c r="N209" s="22"/>
       <c r="O209" s="19" t="str">
-        <f>'data'!$B$6</f>
+        <f>'data'!$B$8</f>
       </c>
     </row>
     <row r="211">
@@ -7569,7 +7569,7 @@
       <c r="E217" s="22"/>
       <c r="F217" s="22"/>
       <c r="G217" s="19" t="str">
-        <f>'data'!$B$11</f>
+        <f>'data'!$B$39</f>
       </c>
       <c r="I217" s="19" t="str">
         <f>CONCATENATE("M 29 ",O102)</f>
@@ -7580,7 +7580,7 @@
       <c r="M217" s="22"/>
       <c r="N217" s="22"/>
       <c r="O217" s="19" t="str">
-        <f>'data'!$B$10</f>
+        <f>'data'!$B$74</f>
       </c>
     </row>
     <row r="219">
@@ -7653,7 +7653,7 @@
       <c r="E225" s="22"/>
       <c r="F225" s="22"/>
       <c r="G225" s="19" t="str">
-        <f>'data'!$B$42</f>
+        <f>'data'!$B$55</f>
       </c>
       <c r="I225" s="19" t="str">
         <f>CONCATENATE("M 30 ",O110)</f>
@@ -7664,7 +7664,7 @@
       <c r="M225" s="22"/>
       <c r="N225" s="22"/>
       <c r="O225" s="19" t="str">
-        <f>'data'!$B$11</f>
+        <f>'data'!$B$7</f>
       </c>
     </row>
     <row r="227">
@@ -7748,7 +7748,7 @@
       <c r="M233" s="22"/>
       <c r="N233" s="22"/>
       <c r="O233" s="19" t="str">
-        <f>'data'!$B$88</f>
+        <f>'data'!$B$16</f>
       </c>
     </row>
     <row r="235">
@@ -7803,7 +7803,7 @@
       <c r="M241" s="22"/>
       <c r="N241" s="22"/>
       <c r="O241" s="19" t="str">
-        <f>'data'!$B$91</f>
+        <f>'data'!$B$41</f>
       </c>
     </row>
     <row r="243">
@@ -9271,7 +9271,7 @@
     </row>
     <row r="5">
       <c r="C5" s="16" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6">
@@ -9282,7 +9282,7 @@
     </row>
     <row r="7">
       <c r="C7" s="16" t="s">
-        <v>186</v>
+        <v>71</v>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="12"/>
@@ -9311,7 +9311,7 @@
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
-        <v>188</v>
+        <v>74</v>
       </c>
       <c r="I14" s="12"/>
       <c r="K14" s="12"/>
@@ -9332,7 +9332,7 @@
     </row>
     <row r="17">
       <c r="C17" s="16" t="s">
-        <v>179</v>
+        <v>77</v>
       </c>
       <c r="G17" s="12"/>
       <c r="K17" s="12"/>
@@ -9348,7 +9348,7 @@
     </row>
     <row r="19">
       <c r="C19" s="16" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="12"/>
@@ -9366,7 +9366,7 @@
       <c r="C22" s="16"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16" t="s">
-        <v>32</v>
+        <v>179</v>
       </c>
       <c r="K22" s="12"/>
     </row>
@@ -9383,7 +9383,7 @@
     </row>
     <row r="25">
       <c r="C25" s="16" t="s">
-        <v>132</v>
+        <v>34</v>
       </c>
       <c r="G25" s="12"/>
       <c r="H25" s="14"/>
@@ -9402,7 +9402,7 @@
     </row>
     <row r="27">
       <c r="C27" s="16" t="s">
-        <v>184</v>
+        <v>36</v>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="12"/>
@@ -9423,7 +9423,7 @@
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
-        <v>190</v>
+        <v>38</v>
       </c>
       <c r="I30" s="12"/>
     </row>
@@ -9441,7 +9441,7 @@
     </row>
     <row r="33">
       <c r="C33" s="16" t="s">
-        <v>192</v>
+        <v>40</v>
       </c>
       <c r="G33" s="12"/>
     </row>
@@ -9455,7 +9455,7 @@
     </row>
     <row r="35">
       <c r="C35" s="16" t="s">
-        <v>110</v>
+        <v>42</v>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="12"/>
@@ -9501,7 +9501,7 @@
     </row>
     <row r="5">
       <c r="C5" s="16" t="s">
-        <v>44</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6">
@@ -9512,7 +9512,7 @@
     </row>
     <row r="7">
       <c r="C7" s="16" t="s">
-        <v>46</v>
+        <v>141</v>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="12"/>
@@ -9541,7 +9541,7 @@
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
-        <v>48</v>
+        <v>164</v>
       </c>
       <c r="I14" s="12"/>
       <c r="K14" s="12"/>
@@ -9562,7 +9562,7 @@
     </row>
     <row r="17">
       <c r="C17" s="16" t="s">
-        <v>50</v>
+        <v>147</v>
       </c>
       <c r="G17" s="12"/>
       <c r="K17" s="12"/>
@@ -9578,7 +9578,7 @@
     </row>
     <row r="19">
       <c r="C19" s="16" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="12"/>
@@ -9613,7 +9613,7 @@
     </row>
     <row r="25">
       <c r="C25" s="16" t="s">
-        <v>141</v>
+        <v>56</v>
       </c>
       <c r="G25" s="12"/>
       <c r="H25" s="14"/>
@@ -9632,7 +9632,7 @@
     </row>
     <row r="27">
       <c r="C27" s="16" t="s">
-        <v>144</v>
+        <v>58</v>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="12"/>
@@ -9653,7 +9653,7 @@
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
-        <v>147</v>
+        <v>60</v>
       </c>
       <c r="I30" s="12"/>
     </row>
@@ -9685,7 +9685,7 @@
     </row>
     <row r="35">
       <c r="C35" s="16" t="s">
-        <v>203</v>
+        <v>65</v>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="12"/>

--- a/playoffs-example-large.xlsx
+++ b/playoffs-example-large.xlsx
@@ -1472,7 +1472,7 @@
       <alignment horizontal="center" shrinkToFit="true" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" shrinkToFit="true" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
@@ -4782,8 +4782,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="30"/>
-    <col customWidth="true" max="2" min="2" width="160"/>
+    <col customWidth="true" max="1" min="1" width="40"/>
+    <col customWidth="true" max="2" min="2" width="140"/>
   </cols>
   <sheetData>
     <row r="1" ht="270" customHeight="true">
@@ -5183,8 +5183,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="30"/>
-    <col customWidth="true" max="2" min="2" width="160"/>
+    <col customWidth="true" max="1" min="1" width="40"/>
+    <col customWidth="true" max="2" min="2" width="140"/>
   </cols>
   <sheetData>
     <row r="1" ht="270" customHeight="true">

--- a/playoffs-example-large.xlsx
+++ b/playoffs-example-large.xlsx
@@ -74,7 +74,7 @@
     <t/>
   </si>
   <si>
-    <t>Draw order</t>
+    <t>Entry order</t>
   </si>
   <si>
     <t>Player Name</t>

--- a/playoffs-example-large.xlsx
+++ b/playoffs-example-large.xlsx
@@ -92,136 +92,799 @@
     <t>Metadata</t>
   </si>
   <si>
+    <t>Kaden Martin</t>
+  </si>
+  <si>
+    <t>Team Alpha</t>
+  </si>
+  <si>
+    <t>MARTIN</t>
+  </si>
+  <si>
+    <t>K1</t>
+  </si>
+  <si>
+    <t>Hudson Jackson</t>
+  </si>
+  <si>
+    <t>Team Theta</t>
+  </si>
+  <si>
+    <t>JACKSON</t>
+  </si>
+  <si>
+    <t>K2</t>
+  </si>
+  <si>
+    <t>Isaac White</t>
+  </si>
+  <si>
+    <t>Team Iota</t>
+  </si>
+  <si>
+    <t>WHITE</t>
+  </si>
+  <si>
+    <t>K3</t>
+  </si>
+  <si>
+    <t>Jackson Harris</t>
+  </si>
+  <si>
+    <t>Team Kappa</t>
+  </si>
+  <si>
+    <t>HARRIS</t>
+  </si>
+  <si>
+    <t>K4</t>
+  </si>
+  <si>
+    <t>Quirinus Quirrell</t>
+  </si>
+  <si>
+    <t>Team Rho</t>
+  </si>
+  <si>
+    <t>QUIRRELL</t>
+  </si>
+  <si>
+    <t>K5</t>
+  </si>
+  <si>
+    <t>Katniss Everdeen</t>
+  </si>
+  <si>
+    <t>Team Lambda</t>
+  </si>
+  <si>
+    <t>EVERDEEN</t>
+  </si>
+  <si>
+    <t>K6</t>
+  </si>
+  <si>
+    <t>Quentin Allen</t>
+  </si>
+  <si>
+    <t>Team Beta</t>
+  </si>
+  <si>
+    <t>ALLEN</t>
+  </si>
+  <si>
+    <t>K7</t>
+  </si>
+  <si>
+    <t>Robert Young</t>
+  </si>
+  <si>
+    <t>Team Gamma</t>
+  </si>
+  <si>
+    <t>YOUNG</t>
+  </si>
+  <si>
+    <t>K8</t>
+  </si>
+  <si>
+    <t>Steven Hernandez</t>
+  </si>
+  <si>
+    <t>Team Delta</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>K9</t>
+  </si>
+  <si>
+    <t>Thomas King</t>
+  </si>
+  <si>
+    <t>Team Epsilon</t>
+  </si>
+  <si>
+    <t>KING</t>
+  </si>
+  <si>
+    <t>K10</t>
+  </si>
+  <si>
+    <t>Uriel Wright</t>
+  </si>
+  <si>
+    <t>WRIGHT</t>
+  </si>
+  <si>
+    <t>K11</t>
+  </si>
+  <si>
+    <t>Ray Bradbury</t>
+  </si>
+  <si>
+    <t>Team Sigma</t>
+  </si>
+  <si>
+    <t>BRADBURY</t>
+  </si>
+  <si>
+    <t>K12</t>
+  </si>
+  <si>
+    <t>Sylvia Plath</t>
+  </si>
+  <si>
+    <t>Team Tau</t>
+  </si>
+  <si>
+    <t>PLATH</t>
+  </si>
+  <si>
+    <t>K13</t>
+  </si>
+  <si>
+    <t>Tyrion Lannister</t>
+  </si>
+  <si>
+    <t>Team Upsilon</t>
+  </si>
+  <si>
+    <t>LANNISTER</t>
+  </si>
+  <si>
+    <t>K14</t>
+  </si>
+  <si>
+    <t>Ursula K Le Guin</t>
+  </si>
+  <si>
+    <t>Team Phi</t>
+  </si>
+  <si>
+    <t>LE GUIN</t>
+  </si>
+  <si>
+    <t>K15</t>
+  </si>
+  <si>
+    <t>Quinn Walker</t>
+  </si>
+  <si>
+    <t>Team Eta</t>
+  </si>
+  <si>
+    <t>WALKER</t>
+  </si>
+  <si>
+    <t>K16</t>
+  </si>
+  <si>
+    <t>Aaron Thompson</t>
+  </si>
+  <si>
+    <t>THOMPSON</t>
+  </si>
+  <si>
+    <t>K17</t>
+  </si>
+  <si>
+    <t>Benjamin Evans</t>
+  </si>
+  <si>
+    <t>EVANS</t>
+  </si>
+  <si>
+    <t>K18</t>
+  </si>
+  <si>
+    <t>Caleb Wilson</t>
+  </si>
+  <si>
+    <t>WILSON</t>
+  </si>
+  <si>
+    <t>K19</t>
+  </si>
+  <si>
+    <t>Dylan Moore</t>
+  </si>
+  <si>
+    <t>MOORE</t>
+  </si>
+  <si>
+    <t>K20</t>
+  </si>
+  <si>
+    <t>Elijah Taylor</t>
+  </si>
+  <si>
+    <t>TAYLOR</t>
+  </si>
+  <si>
+    <t>K21</t>
+  </si>
+  <si>
+    <t>Finn Anderson</t>
+  </si>
+  <si>
+    <t>Team Zeta</t>
+  </si>
+  <si>
+    <t>ANDERSON</t>
+  </si>
+  <si>
+    <t>K22</t>
+  </si>
+  <si>
+    <t>Gabriel Thomas</t>
+  </si>
+  <si>
+    <t>THOMAS</t>
+  </si>
+  <si>
+    <t>K23</t>
+  </si>
+  <si>
+    <t>Neville Longbottom</t>
+  </si>
+  <si>
+    <t>Team Xi</t>
+  </si>
+  <si>
+    <t>LONGBOTTOM</t>
+  </si>
+  <si>
+    <t>K24</t>
+  </si>
+  <si>
+    <t>Oscar Wilde</t>
+  </si>
+  <si>
+    <t>Team Omicron</t>
+  </si>
+  <si>
+    <t>WILDE</t>
+  </si>
+  <si>
+    <t>K25</t>
+  </si>
+  <si>
+    <t>Philip K Dick</t>
+  </si>
+  <si>
+    <t>Team Pi</t>
+  </si>
+  <si>
+    <t>DICK</t>
+  </si>
+  <si>
+    <t>K26</t>
+  </si>
+  <si>
+    <t>Mary Shelley</t>
+  </si>
+  <si>
+    <t>Team Nu</t>
+  </si>
+  <si>
+    <t>SHELLEY</t>
+  </si>
+  <si>
+    <t>K27</t>
+  </si>
+  <si>
+    <t>Liam Thompson</t>
+  </si>
+  <si>
+    <t>K28</t>
+  </si>
+  <si>
+    <t>Mason Martinez</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>K29</t>
+  </si>
+  <si>
+    <t>Nolan Clark</t>
+  </si>
+  <si>
+    <t>CLARK</t>
+  </si>
+  <si>
+    <t>K30</t>
+  </si>
+  <si>
+    <t>Owen Rodriguez</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>K31</t>
+  </si>
+  <si>
+    <t>Parker Lewis</t>
+  </si>
+  <si>
+    <t>LEWIS</t>
+  </si>
+  <si>
+    <t>K32</t>
+  </si>
+  <si>
+    <t>Zachary Adams</t>
+  </si>
+  <si>
+    <t>ADAMS</t>
+  </si>
+  <si>
+    <t>K33</t>
+  </si>
+  <si>
+    <t>Ryan Hall</t>
+  </si>
+  <si>
+    <t>HALL</t>
+  </si>
+  <si>
+    <t>K34</t>
+  </si>
+  <si>
+    <t>Sebastian Allen</t>
+  </si>
+  <si>
+    <t>K35</t>
+  </si>
+  <si>
+    <t>Tristan Young</t>
+  </si>
+  <si>
+    <t>K36</t>
+  </si>
+  <si>
+    <t>Ulysses Hernandez</t>
+  </si>
+  <si>
+    <t>K37</t>
+  </si>
+  <si>
+    <t>Voldemort</t>
+  </si>
+  <si>
+    <t>Team Chi</t>
+  </si>
+  <si>
+    <t>VOLDEMORT</t>
+  </si>
+  <si>
+    <t>K38</t>
+  </si>
+  <si>
+    <t>Willy Wonka</t>
+  </si>
+  <si>
+    <t>Team Psi</t>
+  </si>
+  <si>
+    <t>WONKA</t>
+  </si>
+  <si>
+    <t>K39</t>
+  </si>
+  <si>
+    <t>Lewis Carroll</t>
+  </si>
+  <si>
+    <t>Team Mu</t>
+  </si>
+  <si>
+    <t>CARROLL</t>
+  </si>
+  <si>
+    <t>K40</t>
+  </si>
+  <si>
+    <t>Yosef Hill</t>
+  </si>
+  <si>
+    <t>HILL</t>
+  </si>
+  <si>
+    <t>K41</t>
+  </si>
+  <si>
+    <t>Arthur Conan</t>
+  </si>
+  <si>
+    <t>CONAN</t>
+  </si>
+  <si>
+    <t>K42</t>
+  </si>
+  <si>
+    <t>Bram Stoker</t>
+  </si>
+  <si>
+    <t>STOKER</t>
+  </si>
+  <si>
+    <t>K43</t>
+  </si>
+  <si>
+    <t>Charles Dickens</t>
+  </si>
+  <si>
+    <t>DICKENS</t>
+  </si>
+  <si>
+    <t>K44</t>
+  </si>
+  <si>
+    <t>Daniel Defoe</t>
+  </si>
+  <si>
+    <t>DEFOE</t>
+  </si>
+  <si>
+    <t>K45</t>
+  </si>
+  <si>
+    <t>Victor Lopez</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>K46</t>
+  </si>
+  <si>
+    <t>Yosef Green</t>
+  </si>
+  <si>
+    <t>GREEN</t>
+  </si>
+  <si>
+    <t>K47</t>
+  </si>
+  <si>
+    <t>George Orwell</t>
+  </si>
+  <si>
+    <t>ORWELL</t>
+  </si>
+  <si>
+    <t>K48</t>
+  </si>
+  <si>
+    <t>Herman Melville</t>
+  </si>
+  <si>
+    <t>MELVILLE</t>
+  </si>
+  <si>
+    <t>K49</t>
+  </si>
+  <si>
+    <t>Isaac Asimov</t>
+  </si>
+  <si>
+    <t>ASIMOV</t>
+  </si>
+  <si>
+    <t>K50</t>
+  </si>
+  <si>
+    <t>Jane Austen</t>
+  </si>
+  <si>
+    <t>AUSTEN</t>
+  </si>
+  <si>
+    <t>K51</t>
+  </si>
+  <si>
+    <t>Kurt Vonnegut</t>
+  </si>
+  <si>
+    <t>VONNEGUT</t>
+  </si>
+  <si>
+    <t>K52</t>
+  </si>
+  <si>
+    <t>Xavier Lopez</t>
+  </si>
+  <si>
+    <t>K53</t>
+  </si>
+  <si>
     <t>Kevin Clark</t>
   </si>
   <si>
-    <t>Team Alpha</t>
-  </si>
-  <si>
-    <t>CLARK</t>
-  </si>
-  <si>
-    <t>K1</t>
+    <t>K54</t>
+  </si>
+  <si>
+    <t>Nathaniel Hawthorne</t>
+  </si>
+  <si>
+    <t>HAWTHORNE</t>
+  </si>
+  <si>
+    <t>K55</t>
+  </si>
+  <si>
+    <t>Michael Lewis</t>
+  </si>
+  <si>
+    <t>K56</t>
+  </si>
+  <si>
+    <t>Nathan Lee</t>
+  </si>
+  <si>
+    <t>LEE</t>
+  </si>
+  <si>
+    <t>K57</t>
+  </si>
+  <si>
+    <t>Quentin Blake</t>
+  </si>
+  <si>
+    <t>BLAKE</t>
+  </si>
+  <si>
+    <t>K58</t>
+  </si>
+  <si>
+    <t>Yann Martel</t>
+  </si>
+  <si>
+    <t>MARTEL</t>
+  </si>
+  <si>
+    <t>K59</t>
+  </si>
+  <si>
+    <t>William Hill</t>
+  </si>
+  <si>
+    <t>K60</t>
+  </si>
+  <si>
+    <t>Thomas Hardy</t>
+  </si>
+  <si>
+    <t>HARDY</t>
+  </si>
+  <si>
+    <t>K61</t>
+  </si>
+  <si>
+    <t>Fyodor Dostoevsky</t>
+  </si>
+  <si>
+    <t>DOSTOEVSKY</t>
+  </si>
+  <si>
+    <t>K62</t>
+  </si>
+  <si>
+    <t>Virginia Woolf</t>
+  </si>
+  <si>
+    <t>WOOLF</t>
+  </si>
+  <si>
+    <t>K63</t>
+  </si>
+  <si>
+    <t>William Shakespeare</t>
+  </si>
+  <si>
+    <t>SHAKESPEARE</t>
+  </si>
+  <si>
+    <t>K64</t>
+  </si>
+  <si>
+    <t>Xavier Herbert</t>
+  </si>
+  <si>
+    <t>Team Omega</t>
+  </si>
+  <si>
+    <t>HERBERT</t>
+  </si>
+  <si>
+    <t>K65</t>
+  </si>
+  <si>
+    <t>Emily Bronte</t>
+  </si>
+  <si>
+    <t>BRONTE</t>
+  </si>
+  <si>
+    <t>K66</t>
+  </si>
+  <si>
+    <t>Albus Dumbledore</t>
+  </si>
+  <si>
+    <t>DUMBLEDORE</t>
+  </si>
+  <si>
+    <t>K67</t>
+  </si>
+  <si>
+    <t>Bilbo Baggins</t>
+  </si>
+  <si>
+    <t>BAGGINS</t>
+  </si>
+  <si>
+    <t>K68</t>
+  </si>
+  <si>
+    <t>Cersei Lannister</t>
+  </si>
+  <si>
+    <t>K69</t>
+  </si>
+  <si>
+    <t>Daenerys Targaryen</t>
+  </si>
+  <si>
+    <t>TARGARYEN</t>
+  </si>
+  <si>
+    <t>K70</t>
+  </si>
+  <si>
+    <t>Eddard Stark</t>
+  </si>
+  <si>
+    <t>STARK</t>
+  </si>
+  <si>
+    <t>K71</t>
   </si>
   <si>
     <t>Luke Rodriguez</t>
   </si>
   <si>
-    <t>Team Beta</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>K2</t>
-  </si>
-  <si>
-    <t>Michael Lewis</t>
-  </si>
-  <si>
-    <t>Team Gamma</t>
-  </si>
-  <si>
-    <t>LEWIS</t>
-  </si>
-  <si>
-    <t>K3</t>
-  </si>
-  <si>
-    <t>Nathan Lee</t>
-  </si>
-  <si>
-    <t>Team Delta</t>
-  </si>
-  <si>
-    <t>LEE</t>
-  </si>
-  <si>
-    <t>K4</t>
+    <t>K72</t>
+  </si>
+  <si>
+    <t>Gandalf The Grey</t>
+  </si>
+  <si>
+    <t>GANDALF</t>
+  </si>
+  <si>
+    <t>K73</t>
+  </si>
+  <si>
+    <t>Hermione Granger</t>
+  </si>
+  <si>
+    <t>GRANGER</t>
+  </si>
+  <si>
+    <t>K74</t>
+  </si>
+  <si>
+    <t>Inigo Montoya</t>
+  </si>
+  <si>
+    <t>MONTOYA</t>
+  </si>
+  <si>
+    <t>K75</t>
+  </si>
+  <si>
+    <t>Jon Snow</t>
+  </si>
+  <si>
+    <t>SNOW</t>
+  </si>
+  <si>
+    <t>K76</t>
+  </si>
+  <si>
+    <t>Paul Hall</t>
+  </si>
+  <si>
+    <t>K77</t>
+  </si>
+  <si>
+    <t>Legolas Greenleaf</t>
+  </si>
+  <si>
+    <t>GREENLEAF</t>
+  </si>
+  <si>
+    <t>K78</t>
+  </si>
+  <si>
+    <t>Moby Dick</t>
+  </si>
+  <si>
+    <t>K79</t>
+  </si>
+  <si>
+    <t>Frodo Baggins</t>
+  </si>
+  <si>
+    <t>K80</t>
+  </si>
+  <si>
+    <t>Othello</t>
+  </si>
+  <si>
+    <t>OTHELLO</t>
+  </si>
+  <si>
+    <t>K81</t>
+  </si>
+  <si>
+    <t>Petyr Baelish</t>
+  </si>
+  <si>
+    <t>BAELISH</t>
+  </si>
+  <si>
+    <t>K82</t>
   </si>
   <si>
     <t>Oliver Walker</t>
   </si>
   <si>
-    <t>Team Epsilon</t>
-  </si>
-  <si>
-    <t>WALKER</t>
-  </si>
-  <si>
-    <t>K5</t>
-  </si>
-  <si>
-    <t>Paul Hall</t>
-  </si>
-  <si>
-    <t>HALL</t>
-  </si>
-  <si>
-    <t>K6</t>
-  </si>
-  <si>
-    <t>Quentin Allen</t>
-  </si>
-  <si>
-    <t>ALLEN</t>
-  </si>
-  <si>
-    <t>K7</t>
-  </si>
-  <si>
-    <t>Robert Young</t>
-  </si>
-  <si>
-    <t>YOUNG</t>
-  </si>
-  <si>
-    <t>K8</t>
-  </si>
-  <si>
-    <t>Steven Hernandez</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>K9</t>
-  </si>
-  <si>
-    <t>Thomas King</t>
-  </si>
-  <si>
-    <t>KING</t>
-  </si>
-  <si>
-    <t>K10</t>
-  </si>
-  <si>
-    <t>Uriel Wright</t>
-  </si>
-  <si>
-    <t>WRIGHT</t>
-  </si>
-  <si>
-    <t>K11</t>
-  </si>
-  <si>
-    <t>Victor Lopez</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>K12</t>
-  </si>
-  <si>
-    <t>William Hill</t>
-  </si>
-  <si>
-    <t>HILL</t>
-  </si>
-  <si>
-    <t>K13</t>
+    <t>K83</t>
+  </si>
+  <si>
+    <t>Ron Weasley</t>
+  </si>
+  <si>
+    <t>WEASLEY</t>
+  </si>
+  <si>
+    <t>K84</t>
+  </si>
+  <si>
+    <t>Samwise Gamgee</t>
+  </si>
+  <si>
+    <t>GAMGEE</t>
+  </si>
+  <si>
+    <t>K85</t>
   </si>
   <si>
     <t>Xavier Scott</t>
@@ -230,688 +893,25 @@
     <t>SCOTT</t>
   </si>
   <si>
-    <t>K14</t>
-  </si>
-  <si>
-    <t>Yosef Green</t>
-  </si>
-  <si>
-    <t>GREEN</t>
-  </si>
-  <si>
-    <t>K15</t>
-  </si>
-  <si>
-    <t>Zachary Adams</t>
-  </si>
-  <si>
-    <t>ADAMS</t>
-  </si>
-  <si>
-    <t>K16</t>
-  </si>
-  <si>
-    <t>Aaron Thompson</t>
-  </si>
-  <si>
-    <t>THOMPSON</t>
-  </si>
-  <si>
-    <t>K17</t>
-  </si>
-  <si>
-    <t>Benjamin Evans</t>
-  </si>
-  <si>
-    <t>EVANS</t>
-  </si>
-  <si>
-    <t>K18</t>
-  </si>
-  <si>
-    <t>Caleb Wilson</t>
-  </si>
-  <si>
-    <t>WILSON</t>
-  </si>
-  <si>
-    <t>K19</t>
-  </si>
-  <si>
-    <t>Dylan Moore</t>
-  </si>
-  <si>
-    <t>MOORE</t>
-  </si>
-  <si>
-    <t>K20</t>
-  </si>
-  <si>
-    <t>Elijah Taylor</t>
-  </si>
-  <si>
-    <t>TAYLOR</t>
-  </si>
-  <si>
-    <t>K21</t>
-  </si>
-  <si>
-    <t>Finn Anderson</t>
-  </si>
-  <si>
-    <t>Team Zeta</t>
-  </si>
-  <si>
-    <t>ANDERSON</t>
-  </si>
-  <si>
-    <t>K22</t>
-  </si>
-  <si>
-    <t>Gabriel Thomas</t>
-  </si>
-  <si>
-    <t>Team Eta</t>
-  </si>
-  <si>
-    <t>THOMAS</t>
-  </si>
-  <si>
-    <t>K23</t>
-  </si>
-  <si>
-    <t>Hudson Jackson</t>
-  </si>
-  <si>
-    <t>Team Theta</t>
-  </si>
-  <si>
-    <t>JACKSON</t>
-  </si>
-  <si>
-    <t>K24</t>
-  </si>
-  <si>
-    <t>Isaac White</t>
-  </si>
-  <si>
-    <t>Team Iota</t>
-  </si>
-  <si>
-    <t>WHITE</t>
-  </si>
-  <si>
-    <t>K25</t>
-  </si>
-  <si>
-    <t>Jackson Harris</t>
-  </si>
-  <si>
-    <t>Team Kappa</t>
-  </si>
-  <si>
-    <t>HARRIS</t>
-  </si>
-  <si>
-    <t>K26</t>
-  </si>
-  <si>
-    <t>Kaden Martin</t>
-  </si>
-  <si>
-    <t>MARTIN</t>
-  </si>
-  <si>
-    <t>K27</t>
-  </si>
-  <si>
-    <t>Liam Thompson</t>
-  </si>
-  <si>
-    <t>K28</t>
-  </si>
-  <si>
-    <t>Mason Martinez</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>K29</t>
-  </si>
-  <si>
-    <t>Nolan Clark</t>
-  </si>
-  <si>
-    <t>K30</t>
-  </si>
-  <si>
-    <t>Owen Rodriguez</t>
-  </si>
-  <si>
-    <t>K31</t>
-  </si>
-  <si>
-    <t>Parker Lewis</t>
-  </si>
-  <si>
-    <t>K32</t>
-  </si>
-  <si>
-    <t>Quinn Walker</t>
-  </si>
-  <si>
-    <t>K33</t>
-  </si>
-  <si>
-    <t>Ryan Hall</t>
-  </si>
-  <si>
-    <t>K34</t>
-  </si>
-  <si>
-    <t>Sebastian Allen</t>
-  </si>
-  <si>
-    <t>K35</t>
-  </si>
-  <si>
-    <t>Tristan Young</t>
-  </si>
-  <si>
-    <t>K36</t>
-  </si>
-  <si>
-    <t>Ulysses Hernandez</t>
-  </si>
-  <si>
-    <t>K37</t>
+    <t>K86</t>
+  </si>
+  <si>
+    <t>Ulysses</t>
+  </si>
+  <si>
+    <t>ULYSSES</t>
+  </si>
+  <si>
+    <t>K87</t>
   </si>
   <si>
     <t>Vincent King</t>
   </si>
   <si>
-    <t>K38</t>
+    <t>K88</t>
   </si>
   <si>
     <t>William Wright</t>
-  </si>
-  <si>
-    <t>K39</t>
-  </si>
-  <si>
-    <t>Xavier Lopez</t>
-  </si>
-  <si>
-    <t>K40</t>
-  </si>
-  <si>
-    <t>Yosef Hill</t>
-  </si>
-  <si>
-    <t>K41</t>
-  </si>
-  <si>
-    <t>Arthur Conan</t>
-  </si>
-  <si>
-    <t>CONAN</t>
-  </si>
-  <si>
-    <t>K42</t>
-  </si>
-  <si>
-    <t>Bram Stoker</t>
-  </si>
-  <si>
-    <t>STOKER</t>
-  </si>
-  <si>
-    <t>K43</t>
-  </si>
-  <si>
-    <t>Charles Dickens</t>
-  </si>
-  <si>
-    <t>DICKENS</t>
-  </si>
-  <si>
-    <t>K44</t>
-  </si>
-  <si>
-    <t>Daniel Defoe</t>
-  </si>
-  <si>
-    <t>DEFOE</t>
-  </si>
-  <si>
-    <t>K45</t>
-  </si>
-  <si>
-    <t>Emily Bronte</t>
-  </si>
-  <si>
-    <t>BRONTE</t>
-  </si>
-  <si>
-    <t>K46</t>
-  </si>
-  <si>
-    <t>Fyodor Dostoevsky</t>
-  </si>
-  <si>
-    <t>DOSTOEVSKY</t>
-  </si>
-  <si>
-    <t>K47</t>
-  </si>
-  <si>
-    <t>George Orwell</t>
-  </si>
-  <si>
-    <t>ORWELL</t>
-  </si>
-  <si>
-    <t>K48</t>
-  </si>
-  <si>
-    <t>Herman Melville</t>
-  </si>
-  <si>
-    <t>MELVILLE</t>
-  </si>
-  <si>
-    <t>K49</t>
-  </si>
-  <si>
-    <t>Isaac Asimov</t>
-  </si>
-  <si>
-    <t>ASIMOV</t>
-  </si>
-  <si>
-    <t>K50</t>
-  </si>
-  <si>
-    <t>Jane Austen</t>
-  </si>
-  <si>
-    <t>AUSTEN</t>
-  </si>
-  <si>
-    <t>K51</t>
-  </si>
-  <si>
-    <t>Kurt Vonnegut</t>
-  </si>
-  <si>
-    <t>Team Lambda</t>
-  </si>
-  <si>
-    <t>VONNEGUT</t>
-  </si>
-  <si>
-    <t>K52</t>
-  </si>
-  <si>
-    <t>Lewis Carroll</t>
-  </si>
-  <si>
-    <t>Team Mu</t>
-  </si>
-  <si>
-    <t>CARROLL</t>
-  </si>
-  <si>
-    <t>K53</t>
-  </si>
-  <si>
-    <t>Mary Shelley</t>
-  </si>
-  <si>
-    <t>Team Nu</t>
-  </si>
-  <si>
-    <t>SHELLEY</t>
-  </si>
-  <si>
-    <t>K54</t>
-  </si>
-  <si>
-    <t>Nathaniel Hawthorne</t>
-  </si>
-  <si>
-    <t>Team Xi</t>
-  </si>
-  <si>
-    <t>HAWTHORNE</t>
-  </si>
-  <si>
-    <t>K55</t>
-  </si>
-  <si>
-    <t>Oscar Wilde</t>
-  </si>
-  <si>
-    <t>Team Omicron</t>
-  </si>
-  <si>
-    <t>WILDE</t>
-  </si>
-  <si>
-    <t>K56</t>
-  </si>
-  <si>
-    <t>Philip K Dick</t>
-  </si>
-  <si>
-    <t>Team Pi</t>
-  </si>
-  <si>
-    <t>DICK</t>
-  </si>
-  <si>
-    <t>K57</t>
-  </si>
-  <si>
-    <t>Quentin Blake</t>
-  </si>
-  <si>
-    <t>Team Rho</t>
-  </si>
-  <si>
-    <t>BLAKE</t>
-  </si>
-  <si>
-    <t>K58</t>
-  </si>
-  <si>
-    <t>Ray Bradbury</t>
-  </si>
-  <si>
-    <t>Team Sigma</t>
-  </si>
-  <si>
-    <t>BRADBURY</t>
-  </si>
-  <si>
-    <t>K59</t>
-  </si>
-  <si>
-    <t>Sylvia Plath</t>
-  </si>
-  <si>
-    <t>Team Tau</t>
-  </si>
-  <si>
-    <t>PLATH</t>
-  </si>
-  <si>
-    <t>K60</t>
-  </si>
-  <si>
-    <t>Thomas Hardy</t>
-  </si>
-  <si>
-    <t>Team Upsilon</t>
-  </si>
-  <si>
-    <t>HARDY</t>
-  </si>
-  <si>
-    <t>K61</t>
-  </si>
-  <si>
-    <t>Ursula K Le Guin</t>
-  </si>
-  <si>
-    <t>Team Phi</t>
-  </si>
-  <si>
-    <t>LE GUIN</t>
-  </si>
-  <si>
-    <t>K62</t>
-  </si>
-  <si>
-    <t>Virginia Woolf</t>
-  </si>
-  <si>
-    <t>Team Chi</t>
-  </si>
-  <si>
-    <t>WOOLF</t>
-  </si>
-  <si>
-    <t>K63</t>
-  </si>
-  <si>
-    <t>William Shakespeare</t>
-  </si>
-  <si>
-    <t>Team Psi</t>
-  </si>
-  <si>
-    <t>SHAKESPEARE</t>
-  </si>
-  <si>
-    <t>K64</t>
-  </si>
-  <si>
-    <t>Xavier Herbert</t>
-  </si>
-  <si>
-    <t>Team Omega</t>
-  </si>
-  <si>
-    <t>HERBERT</t>
-  </si>
-  <si>
-    <t>K65</t>
-  </si>
-  <si>
-    <t>Yann Martel</t>
-  </si>
-  <si>
-    <t>MARTEL</t>
-  </si>
-  <si>
-    <t>K66</t>
-  </si>
-  <si>
-    <t>Albus Dumbledore</t>
-  </si>
-  <si>
-    <t>DUMBLEDORE</t>
-  </si>
-  <si>
-    <t>K67</t>
-  </si>
-  <si>
-    <t>Bilbo Baggins</t>
-  </si>
-  <si>
-    <t>BAGGINS</t>
-  </si>
-  <si>
-    <t>K68</t>
-  </si>
-  <si>
-    <t>Cersei Lannister</t>
-  </si>
-  <si>
-    <t>LANNISTER</t>
-  </si>
-  <si>
-    <t>K69</t>
-  </si>
-  <si>
-    <t>Daenerys Targaryen</t>
-  </si>
-  <si>
-    <t>TARGARYEN</t>
-  </si>
-  <si>
-    <t>K70</t>
-  </si>
-  <si>
-    <t>Eddard Stark</t>
-  </si>
-  <si>
-    <t>STARK</t>
-  </si>
-  <si>
-    <t>K71</t>
-  </si>
-  <si>
-    <t>Frodo Baggins</t>
-  </si>
-  <si>
-    <t>K72</t>
-  </si>
-  <si>
-    <t>Gandalf The Grey</t>
-  </si>
-  <si>
-    <t>GANDALF</t>
-  </si>
-  <si>
-    <t>K73</t>
-  </si>
-  <si>
-    <t>Hermione Granger</t>
-  </si>
-  <si>
-    <t>GRANGER</t>
-  </si>
-  <si>
-    <t>K74</t>
-  </si>
-  <si>
-    <t>Inigo Montoya</t>
-  </si>
-  <si>
-    <t>MONTOYA</t>
-  </si>
-  <si>
-    <t>K75</t>
-  </si>
-  <si>
-    <t>Jon Snow</t>
-  </si>
-  <si>
-    <t>SNOW</t>
-  </si>
-  <si>
-    <t>K76</t>
-  </si>
-  <si>
-    <t>Katniss Everdeen</t>
-  </si>
-  <si>
-    <t>EVERDEEN</t>
-  </si>
-  <si>
-    <t>K77</t>
-  </si>
-  <si>
-    <t>Legolas Greenleaf</t>
-  </si>
-  <si>
-    <t>GREENLEAF</t>
-  </si>
-  <si>
-    <t>K78</t>
-  </si>
-  <si>
-    <t>Moby Dick</t>
-  </si>
-  <si>
-    <t>K79</t>
-  </si>
-  <si>
-    <t>Neville Longbottom</t>
-  </si>
-  <si>
-    <t>LONGBOTTOM</t>
-  </si>
-  <si>
-    <t>K80</t>
-  </si>
-  <si>
-    <t>Othello</t>
-  </si>
-  <si>
-    <t>OTHELLO</t>
-  </si>
-  <si>
-    <t>K81</t>
-  </si>
-  <si>
-    <t>Petyr Baelish</t>
-  </si>
-  <si>
-    <t>BAELISH</t>
-  </si>
-  <si>
-    <t>K82</t>
-  </si>
-  <si>
-    <t>Quirinus Quirrell</t>
-  </si>
-  <si>
-    <t>QUIRRELL</t>
-  </si>
-  <si>
-    <t>K83</t>
-  </si>
-  <si>
-    <t>Ron Weasley</t>
-  </si>
-  <si>
-    <t>WEASLEY</t>
-  </si>
-  <si>
-    <t>K84</t>
-  </si>
-  <si>
-    <t>Samwise Gamgee</t>
-  </si>
-  <si>
-    <t>GAMGEE</t>
-  </si>
-  <si>
-    <t>K85</t>
-  </si>
-  <si>
-    <t>Tyrion Lannister</t>
-  </si>
-  <si>
-    <t>K86</t>
-  </si>
-  <si>
-    <t>Ulysses</t>
-  </si>
-  <si>
-    <t>ULYSSES</t>
-  </si>
-  <si>
-    <t>K87</t>
-  </si>
-  <si>
-    <t>Voldemort</t>
-  </si>
-  <si>
-    <t>VOLDEMORT</t>
-  </si>
-  <si>
-    <t>K88</t>
-  </si>
-  <si>
-    <t>Willy Wonka</t>
-  </si>
-  <si>
-    <t>WONKA</t>
   </si>
   <si>
     <t>K89</t>
@@ -1808,7 +1808,7 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="B3" t="s">
         <v>17</v>
@@ -1825,7 +1825,7 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
@@ -1842,7 +1842,7 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
@@ -1859,7 +1859,7 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="B6" t="s">
         <v>29</v>
@@ -1876,7 +1876,7 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="B7" t="s">
         <v>33</v>
@@ -1893,19 +1893,19 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="B8" t="s">
         <v>37</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="D8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9">
@@ -1913,16 +1913,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="D9" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E9" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10">
@@ -1930,16 +1930,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="D10" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E10" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11">
@@ -1947,16 +1947,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D11" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E11" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12">
@@ -1964,16 +1964,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C12" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="D12" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E12" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13">
@@ -1981,101 +1981,101 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C13" t="s">
         <v>18</v>
       </c>
       <c r="D13" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E13" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>12</v>
+        <v>59</v>
       </c>
       <c r="B14" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C14" t="s">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="D14" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="E14" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="B15" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="C15" t="s">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="D15" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="E15" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>14</v>
+        <v>86</v>
       </c>
       <c r="B16" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>69</v>
       </c>
       <c r="D16" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="E16" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>15</v>
+        <v>62</v>
       </c>
       <c r="B17" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="C17" t="s">
-        <v>34</v>
+        <v>73</v>
       </c>
       <c r="D17" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="E17" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="B18" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="C18" t="s">
-        <v>18</v>
+        <v>77</v>
       </c>
       <c r="D18" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="E18" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19">
@@ -2083,16 +2083,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C19" t="s">
         <v>18</v>
       </c>
       <c r="D19" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="E19" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="20">
@@ -2100,16 +2100,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="C20" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="D20" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="E20" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
     </row>
     <row r="21">
@@ -2117,16 +2117,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="C21" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="D21" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="E21" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
     </row>
     <row r="22">
@@ -2134,16 +2134,16 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="C22" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D22" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="E22" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23">
@@ -2151,16 +2151,16 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="C23" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="D23" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="E23" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
     </row>
     <row r="24">
@@ -2168,16 +2168,16 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="C24" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="D24" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="E24" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
     </row>
     <row r="25">
@@ -2185,84 +2185,84 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="C25" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="D25" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="E25" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="B26" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="C26" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="D26" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="E26" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="B27" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="C27" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="D27" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="E27" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="B28" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="C28" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="D28" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="E28" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="B29" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="C29" t="s">
-        <v>18</v>
+        <v>115</v>
       </c>
       <c r="D29" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="E29" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
     </row>
     <row r="30">
@@ -2270,16 +2270,16 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="C30" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="D30" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="E30" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
     </row>
     <row r="31">
@@ -2287,16 +2287,16 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="C31" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="D31" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="E31" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
     </row>
     <row r="32">
@@ -2304,16 +2304,16 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="C32" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D32" t="s">
-        <v>19</v>
+        <v>124</v>
       </c>
       <c r="E32" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
     </row>
     <row r="33">
@@ -2321,16 +2321,16 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="C33" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="D33" t="s">
-        <v>23</v>
+        <v>127</v>
       </c>
       <c r="E33" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
     </row>
     <row r="34">
@@ -2338,33 +2338,33 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="C34" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="D34" t="s">
-        <v>27</v>
+        <v>130</v>
       </c>
       <c r="E34" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="B35" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="C35" t="s">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="D35" t="s">
-        <v>35</v>
+        <v>133</v>
       </c>
       <c r="E35" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
     </row>
     <row r="36">
@@ -2372,16 +2372,16 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="C36" t="s">
-        <v>94</v>
+        <v>22</v>
       </c>
       <c r="D36" t="s">
-        <v>38</v>
+        <v>136</v>
       </c>
       <c r="E36" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
     </row>
     <row r="37">
@@ -2389,16 +2389,16 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="C37" t="s">
-        <v>98</v>
+        <v>26</v>
       </c>
       <c r="D37" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E37" t="s">
-        <v>124</v>
+        <v>139</v>
       </c>
     </row>
     <row r="38">
@@ -2406,16 +2406,16 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="C38" t="s">
-        <v>102</v>
+        <v>30</v>
       </c>
       <c r="D38" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E38" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
     </row>
     <row r="39">
@@ -2423,67 +2423,67 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="C39" t="s">
         <v>18</v>
       </c>
       <c r="D39" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E39" t="s">
-        <v>128</v>
+        <v>143</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="B40" t="s">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="C40" t="s">
-        <v>22</v>
+        <v>145</v>
       </c>
       <c r="D40" t="s">
-        <v>50</v>
+        <v>146</v>
       </c>
       <c r="E40" t="s">
-        <v>130</v>
+        <v>147</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="B41" t="s">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="C41" t="s">
-        <v>26</v>
+        <v>149</v>
       </c>
       <c r="D41" t="s">
-        <v>53</v>
+        <v>150</v>
       </c>
       <c r="E41" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="B42" t="s">
-        <v>133</v>
+        <v>152</v>
       </c>
       <c r="C42" t="s">
-        <v>30</v>
+        <v>153</v>
       </c>
       <c r="D42" t="s">
-        <v>56</v>
+        <v>154</v>
       </c>
       <c r="E42" t="s">
-        <v>134</v>
+        <v>155</v>
       </c>
     </row>
     <row r="43">
@@ -2491,16 +2491,16 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="C43" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="D43" t="s">
-        <v>59</v>
+        <v>157</v>
       </c>
       <c r="E43" t="s">
-        <v>136</v>
+        <v>158</v>
       </c>
     </row>
     <row r="44">
@@ -2508,16 +2508,16 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>137</v>
+        <v>159</v>
       </c>
       <c r="C44" t="s">
         <v>18</v>
       </c>
       <c r="D44" t="s">
-        <v>138</v>
+        <v>160</v>
       </c>
       <c r="E44" t="s">
-        <v>139</v>
+        <v>161</v>
       </c>
     </row>
     <row r="45">
@@ -2525,16 +2525,16 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
       <c r="C45" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="D45" t="s">
-        <v>141</v>
+        <v>163</v>
       </c>
       <c r="E45" t="s">
-        <v>142</v>
+        <v>164</v>
       </c>
     </row>
     <row r="46">
@@ -2542,16 +2542,16 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>143</v>
+        <v>165</v>
       </c>
       <c r="C46" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="D46" t="s">
-        <v>144</v>
+        <v>166</v>
       </c>
       <c r="E46" t="s">
-        <v>145</v>
+        <v>167</v>
       </c>
     </row>
     <row r="47">
@@ -2559,50 +2559,50 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>146</v>
+        <v>168</v>
       </c>
       <c r="C47" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D47" t="s">
-        <v>147</v>
+        <v>169</v>
       </c>
       <c r="E47" t="s">
-        <v>148</v>
+        <v>170</v>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="B48" t="s">
-        <v>149</v>
+        <v>171</v>
       </c>
       <c r="C48" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D48" t="s">
-        <v>150</v>
+        <v>172</v>
       </c>
       <c r="E48" t="s">
-        <v>151</v>
+        <v>173</v>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="B49" t="s">
-        <v>152</v>
+        <v>174</v>
       </c>
       <c r="C49" t="s">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="D49" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="E49" t="s">
-        <v>154</v>
+        <v>176</v>
       </c>
     </row>
     <row r="50">
@@ -2610,16 +2610,16 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>155</v>
+        <v>177</v>
       </c>
       <c r="C50" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="D50" t="s">
-        <v>156</v>
+        <v>178</v>
       </c>
       <c r="E50" t="s">
-        <v>157</v>
+        <v>179</v>
       </c>
     </row>
     <row r="51">
@@ -2627,16 +2627,16 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>158</v>
+        <v>180</v>
       </c>
       <c r="C51" t="s">
-        <v>94</v>
+        <v>22</v>
       </c>
       <c r="D51" t="s">
-        <v>159</v>
+        <v>181</v>
       </c>
       <c r="E51" t="s">
-        <v>160</v>
+        <v>182</v>
       </c>
     </row>
     <row r="52">
@@ -2644,16 +2644,16 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="C52" t="s">
-        <v>98</v>
+        <v>26</v>
       </c>
       <c r="D52" t="s">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="E52" t="s">
-        <v>163</v>
+        <v>185</v>
       </c>
     </row>
     <row r="53">
@@ -2661,16 +2661,16 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>164</v>
+        <v>186</v>
       </c>
       <c r="C53" t="s">
-        <v>102</v>
+        <v>30</v>
       </c>
       <c r="D53" t="s">
-        <v>165</v>
+        <v>187</v>
       </c>
       <c r="E53" t="s">
-        <v>166</v>
+        <v>188</v>
       </c>
     </row>
     <row r="54">
@@ -2678,50 +2678,50 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>167</v>
+        <v>189</v>
       </c>
       <c r="C54" t="s">
-        <v>168</v>
+        <v>38</v>
       </c>
       <c r="D54" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="E54" t="s">
-        <v>170</v>
+        <v>191</v>
       </c>
     </row>
     <row r="55">
       <c r="A55">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="B55" t="s">
-        <v>171</v>
+        <v>192</v>
       </c>
       <c r="C55" t="s">
+        <v>50</v>
+      </c>
+      <c r="D55" t="s">
         <v>172</v>
       </c>
-      <c r="D55" t="s">
-        <v>173</v>
-      </c>
       <c r="E55" t="s">
-        <v>174</v>
+        <v>193</v>
       </c>
     </row>
     <row r="56">
       <c r="A56">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="B56" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="C56" t="s">
-        <v>176</v>
+        <v>18</v>
       </c>
       <c r="D56" t="s">
-        <v>177</v>
+        <v>124</v>
       </c>
       <c r="E56" t="s">
-        <v>178</v>
+        <v>195</v>
       </c>
     </row>
     <row r="57">
@@ -2729,50 +2729,50 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="C57" t="s">
-        <v>180</v>
+        <v>103</v>
       </c>
       <c r="D57" t="s">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="E57" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
     </row>
     <row r="58">
       <c r="A58">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="B58" t="s">
-        <v>183</v>
+        <v>199</v>
       </c>
       <c r="C58" t="s">
-        <v>184</v>
+        <v>46</v>
       </c>
       <c r="D58" t="s">
-        <v>185</v>
+        <v>130</v>
       </c>
       <c r="E58" t="s">
-        <v>186</v>
+        <v>200</v>
       </c>
     </row>
     <row r="59">
       <c r="A59">
-        <v>57</v>
+        <v>4</v>
       </c>
       <c r="B59" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="C59" t="s">
-        <v>188</v>
+        <v>50</v>
       </c>
       <c r="D59" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="E59" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
     </row>
     <row r="60">
@@ -2780,50 +2780,50 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="C60" t="s">
-        <v>192</v>
+        <v>34</v>
       </c>
       <c r="D60" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="E60" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
     </row>
     <row r="61">
       <c r="A61">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="B61" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="C61" t="s">
-        <v>196</v>
+        <v>18</v>
       </c>
       <c r="D61" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="E61" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
     </row>
     <row r="62">
       <c r="A62">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="B62" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="C62" t="s">
-        <v>200</v>
+        <v>46</v>
       </c>
       <c r="D62" t="s">
-        <v>201</v>
+        <v>157</v>
       </c>
       <c r="E62" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
     </row>
     <row r="63">
@@ -2831,33 +2831,33 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="C63" t="s">
-        <v>204</v>
+        <v>69</v>
       </c>
       <c r="D63" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="E63" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
     </row>
     <row r="64">
       <c r="A64">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="B64" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="C64" t="s">
-        <v>208</v>
+        <v>96</v>
       </c>
       <c r="D64" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="E64" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
     </row>
     <row r="65">
@@ -2865,16 +2865,16 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="C65" t="s">
-        <v>212</v>
+        <v>145</v>
       </c>
       <c r="D65" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="E65" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
     </row>
     <row r="66">
@@ -2882,16 +2882,16 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="C66" t="s">
-        <v>216</v>
+        <v>149</v>
       </c>
       <c r="D66" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="E66" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
     </row>
     <row r="67">
@@ -2899,33 +2899,33 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="C67" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="D67" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="E67" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
     </row>
     <row r="68">
       <c r="A68">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="B68" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="C68" t="s">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="D68" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="E68" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
     </row>
     <row r="69">
@@ -2933,16 +2933,16 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="C69" t="s">
         <v>18</v>
       </c>
       <c r="D69" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="E69" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
     </row>
     <row r="70">
@@ -2950,16 +2950,16 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="C70" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="D70" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="E70" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
     </row>
     <row r="71">
@@ -2967,16 +2967,16 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="C71" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="D71" t="s">
-        <v>233</v>
+        <v>70</v>
       </c>
       <c r="E71" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="72">
@@ -2984,16 +2984,16 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="C72" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D72" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="E72" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
     </row>
     <row r="73">
@@ -3001,33 +3001,33 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="C73" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="D73" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="E73" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
     </row>
     <row r="74">
       <c r="A74">
-        <v>72</v>
+        <v>2</v>
       </c>
       <c r="B74" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="C74" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="D74" t="s">
-        <v>230</v>
+        <v>127</v>
       </c>
       <c r="E74" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
     </row>
     <row r="75">
@@ -3035,16 +3035,16 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C75" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="D75" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="E75" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
     </row>
     <row r="76">
@@ -3052,16 +3052,16 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="C76" t="s">
-        <v>94</v>
+        <v>22</v>
       </c>
       <c r="D76" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="E76" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
     </row>
     <row r="77">
@@ -3069,16 +3069,16 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="C77" t="s">
-        <v>98</v>
+        <v>26</v>
       </c>
       <c r="D77" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="E77" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
     </row>
     <row r="78">
@@ -3086,33 +3086,33 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="C78" t="s">
-        <v>102</v>
+        <v>30</v>
       </c>
       <c r="D78" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="E78" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
     </row>
     <row r="79">
       <c r="A79">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="B79" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="C79" t="s">
-        <v>168</v>
+        <v>18</v>
       </c>
       <c r="D79" t="s">
-        <v>256</v>
+        <v>136</v>
       </c>
       <c r="E79" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
     </row>
     <row r="80">
@@ -3120,16 +3120,16 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C80" t="s">
-        <v>172</v>
+        <v>153</v>
       </c>
       <c r="D80" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="E80" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
     </row>
     <row r="81">
@@ -3137,33 +3137,33 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C81" t="s">
-        <v>176</v>
+        <v>115</v>
       </c>
       <c r="D81" t="s">
-        <v>189</v>
+        <v>112</v>
       </c>
       <c r="E81" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
     </row>
     <row r="82">
       <c r="A82">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="B82" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C82" t="s">
-        <v>180</v>
+        <v>96</v>
       </c>
       <c r="D82" t="s">
-        <v>264</v>
+        <v>235</v>
       </c>
       <c r="E82" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="83">
@@ -3171,16 +3171,16 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C83" t="s">
-        <v>184</v>
+        <v>107</v>
       </c>
       <c r="D83" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E83" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="84">
@@ -3188,33 +3188,33 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C84" t="s">
-        <v>188</v>
+        <v>111</v>
       </c>
       <c r="D84" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E84" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="85">
       <c r="A85">
-        <v>83</v>
+        <v>5</v>
       </c>
       <c r="B85" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C85" t="s">
-        <v>192</v>
+        <v>54</v>
       </c>
       <c r="D85" t="s">
-        <v>273</v>
+        <v>78</v>
       </c>
       <c r="E85" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="86">
@@ -3222,16 +3222,16 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C86" t="s">
-        <v>196</v>
+        <v>61</v>
       </c>
       <c r="D86" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E86" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="87">
@@ -3239,33 +3239,33 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C87" t="s">
-        <v>200</v>
+        <v>65</v>
       </c>
       <c r="D87" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E87" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="88">
       <c r="A88">
-        <v>86</v>
+        <v>14</v>
       </c>
       <c r="B88" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C88" t="s">
-        <v>204</v>
+        <v>50</v>
       </c>
       <c r="D88" t="s">
-        <v>233</v>
+        <v>283</v>
       </c>
       <c r="E88" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="89">
@@ -3273,47 +3273,47 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C89" t="s">
-        <v>208</v>
+        <v>73</v>
       </c>
       <c r="D89" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E89" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="90">
       <c r="A90">
-        <v>88</v>
+        <v>38</v>
       </c>
       <c r="B90" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C90" t="s">
-        <v>212</v>
+        <v>42</v>
       </c>
       <c r="D90" t="s">
-        <v>287</v>
+        <v>55</v>
       </c>
       <c r="E90" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="91">
       <c r="A91">
-        <v>89</v>
+        <v>39</v>
       </c>
       <c r="B91" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C91" t="s">
-        <v>216</v>
+        <v>46</v>
       </c>
       <c r="D91" t="s">
-        <v>290</v>
+        <v>58</v>
       </c>
       <c r="E91" t="s">
         <v>291</v>
@@ -3327,7 +3327,7 @@
         <v>292</v>
       </c>
       <c r="C92" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="D92" t="s">
         <v>293</v>
@@ -3390,7 +3390,7 @@
     </row>
     <row r="5">
       <c r="C5" s="16" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6">
@@ -3401,7 +3401,7 @@
     </row>
     <row r="7">
       <c r="C7" s="16" t="s">
-        <v>264</v>
+        <v>104</v>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="12"/>
@@ -3430,7 +3430,7 @@
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
-        <v>185</v>
+        <v>108</v>
       </c>
       <c r="I14" s="12"/>
       <c r="K14" s="12"/>
@@ -3451,7 +3451,7 @@
     </row>
     <row r="17">
       <c r="C17" s="16" t="s">
-        <v>189</v>
+        <v>112</v>
       </c>
       <c r="G17" s="12"/>
       <c r="K17" s="12"/>
@@ -3467,7 +3467,7 @@
     </row>
     <row r="19">
       <c r="C19" s="16" t="s">
-        <v>177</v>
+        <v>116</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="12"/>
@@ -3485,7 +3485,7 @@
       <c r="C22" s="16"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="K22" s="12"/>
     </row>
@@ -3502,7 +3502,7 @@
     </row>
     <row r="25">
       <c r="C25" s="16" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="G25" s="12"/>
       <c r="H25" s="14"/>
@@ -3521,7 +3521,7 @@
     </row>
     <row r="27">
       <c r="C27" s="16" t="s">
-        <v>19</v>
+        <v>124</v>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="12"/>
@@ -3542,7 +3542,7 @@
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
-        <v>23</v>
+        <v>127</v>
       </c>
       <c r="I30" s="12"/>
     </row>
@@ -3560,7 +3560,7 @@
     </row>
     <row r="33">
       <c r="C33" s="16" t="s">
-        <v>27</v>
+        <v>130</v>
       </c>
       <c r="G33" s="12"/>
     </row>
@@ -3574,7 +3574,7 @@
     </row>
     <row r="35">
       <c r="C35" s="16" t="s">
-        <v>68</v>
+        <v>133</v>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="12"/>
@@ -3622,7 +3622,7 @@
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
       <c r="E6" s="16" t="s">
-        <v>38</v>
+        <v>136</v>
       </c>
     </row>
     <row r="7">
@@ -3636,7 +3636,7 @@
     </row>
     <row r="9">
       <c r="C9" s="16" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G9" s="12"/>
       <c r="H9" s="14"/>
@@ -3653,7 +3653,7 @@
     </row>
     <row r="11">
       <c r="C11" s="16" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="12"/>
@@ -3673,7 +3673,7 @@
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I14" s="12"/>
       <c r="K14" s="12"/>
@@ -3694,7 +3694,7 @@
     </row>
     <row r="17">
       <c r="C17" s="16" t="s">
-        <v>287</v>
+        <v>146</v>
       </c>
       <c r="G17" s="12"/>
       <c r="K17" s="12"/>
@@ -3710,7 +3710,7 @@
     </row>
     <row r="19">
       <c r="C19" s="16" t="s">
-        <v>290</v>
+        <v>150</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="12"/>
@@ -3728,7 +3728,7 @@
       <c r="C22" s="16"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16" t="s">
-        <v>173</v>
+        <v>154</v>
       </c>
       <c r="K22" s="12"/>
     </row>
@@ -3745,7 +3745,7 @@
     </row>
     <row r="25">
       <c r="C25" s="16" t="s">
-        <v>59</v>
+        <v>157</v>
       </c>
       <c r="G25" s="12"/>
       <c r="H25" s="14"/>
@@ -3764,7 +3764,7 @@
     </row>
     <row r="27">
       <c r="C27" s="16" t="s">
-        <v>138</v>
+        <v>160</v>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="12"/>
@@ -3785,7 +3785,7 @@
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
-        <v>141</v>
+        <v>163</v>
       </c>
       <c r="I30" s="12"/>
     </row>
@@ -3803,7 +3803,7 @@
     </row>
     <row r="33">
       <c r="C33" s="16" t="s">
-        <v>144</v>
+        <v>166</v>
       </c>
       <c r="G33" s="12"/>
     </row>
@@ -3817,7 +3817,7 @@
     </row>
     <row r="35">
       <c r="C35" s="16" t="s">
-        <v>147</v>
+        <v>169</v>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="12"/>
@@ -3863,7 +3863,7 @@
     </row>
     <row r="5">
       <c r="C5" s="16" t="s">
-        <v>56</v>
+        <v>172</v>
       </c>
     </row>
     <row r="6">
@@ -3874,7 +3874,7 @@
     </row>
     <row r="7">
       <c r="C7" s="16" t="s">
-        <v>65</v>
+        <v>175</v>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="12"/>
@@ -3903,7 +3903,7 @@
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
-        <v>156</v>
+        <v>178</v>
       </c>
       <c r="I14" s="12"/>
       <c r="K14" s="12"/>
@@ -3924,7 +3924,7 @@
     </row>
     <row r="17">
       <c r="C17" s="16" t="s">
-        <v>159</v>
+        <v>181</v>
       </c>
       <c r="G17" s="12"/>
       <c r="K17" s="12"/>
@@ -3940,7 +3940,7 @@
     </row>
     <row r="19">
       <c r="C19" s="16" t="s">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="12"/>
@@ -3958,7 +3958,7 @@
       <c r="C22" s="16"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16" t="s">
-        <v>165</v>
+        <v>187</v>
       </c>
       <c r="K22" s="12"/>
     </row>
@@ -3975,7 +3975,7 @@
     </row>
     <row r="25">
       <c r="C25" s="16" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="G25" s="12"/>
       <c r="H25" s="14"/>
@@ -3994,7 +3994,7 @@
     </row>
     <row r="27">
       <c r="C27" s="16" t="s">
-        <v>56</v>
+        <v>172</v>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="12"/>
@@ -4015,7 +4015,7 @@
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
-        <v>19</v>
+        <v>124</v>
       </c>
       <c r="I30" s="12"/>
     </row>
@@ -4033,7 +4033,7 @@
     </row>
     <row r="33">
       <c r="C33" s="16" t="s">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="G33" s="12"/>
     </row>
@@ -4047,7 +4047,7 @@
     </row>
     <row r="35">
       <c r="C35" s="16" t="s">
-        <v>27</v>
+        <v>130</v>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="12"/>
@@ -4095,7 +4095,7 @@
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
       <c r="E6" s="16" t="s">
-        <v>31</v>
+        <v>202</v>
       </c>
     </row>
     <row r="7">
@@ -4109,7 +4109,7 @@
     </row>
     <row r="9">
       <c r="C9" s="16" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="G9" s="12"/>
       <c r="H9" s="14"/>
@@ -4126,7 +4126,7 @@
     </row>
     <row r="11">
       <c r="C11" s="16" t="s">
-        <v>224</v>
+        <v>208</v>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="12"/>
@@ -4146,7 +4146,7 @@
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
-        <v>59</v>
+        <v>157</v>
       </c>
       <c r="I14" s="12"/>
       <c r="K14" s="12"/>
@@ -4167,7 +4167,7 @@
     </row>
     <row r="17">
       <c r="C17" s="16" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="G17" s="12"/>
       <c r="K17" s="12"/>
@@ -4183,7 +4183,7 @@
     </row>
     <row r="19">
       <c r="C19" s="16" t="s">
-        <v>153</v>
+        <v>216</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="12"/>
@@ -4201,7 +4201,7 @@
       <c r="C22" s="16"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="K22" s="12"/>
     </row>
@@ -4218,7 +4218,7 @@
     </row>
     <row r="25">
       <c r="C25" s="16" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="G25" s="12"/>
       <c r="H25" s="14"/>
@@ -4237,7 +4237,7 @@
     </row>
     <row r="27">
       <c r="C27" s="16" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="12"/>
@@ -4258,7 +4258,7 @@
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
-        <v>150</v>
+        <v>229</v>
       </c>
       <c r="I30" s="12"/>
     </row>
@@ -4276,7 +4276,7 @@
     </row>
     <row r="33">
       <c r="C33" s="16" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="G33" s="12"/>
     </row>
@@ -4290,7 +4290,7 @@
     </row>
     <row r="35">
       <c r="C35" s="16" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="12"/>
@@ -4336,7 +4336,7 @@
     </row>
     <row r="5">
       <c r="C5" s="16" t="s">
-        <v>233</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6">
@@ -4347,7 +4347,7 @@
     </row>
     <row r="7">
       <c r="C7" s="16" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="12"/>
@@ -4376,7 +4376,7 @@
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="I14" s="12"/>
       <c r="K14" s="12"/>
@@ -4397,7 +4397,7 @@
     </row>
     <row r="17">
       <c r="C17" s="16" t="s">
-        <v>23</v>
+        <v>127</v>
       </c>
       <c r="G17" s="12"/>
       <c r="K17" s="12"/>
@@ -4413,7 +4413,7 @@
     </row>
     <row r="19">
       <c r="C19" s="16" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="12"/>
@@ -4431,7 +4431,7 @@
       <c r="C22" s="16"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="K22" s="12"/>
     </row>
@@ -4448,7 +4448,7 @@
     </row>
     <row r="25">
       <c r="C25" s="16" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="G25" s="12"/>
       <c r="H25" s="14"/>
@@ -4467,7 +4467,7 @@
     </row>
     <row r="27">
       <c r="C27" s="16" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="12"/>
@@ -4488,7 +4488,7 @@
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
-        <v>38</v>
+        <v>136</v>
       </c>
       <c r="I30" s="12"/>
     </row>
@@ -4506,7 +4506,7 @@
     </row>
     <row r="33">
       <c r="C33" s="16" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="G33" s="12"/>
     </row>
@@ -4520,7 +4520,7 @@
     </row>
     <row r="35">
       <c r="C35" s="16" t="s">
-        <v>189</v>
+        <v>112</v>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="12"/>
@@ -4568,7 +4568,7 @@
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
       <c r="E6" s="16" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
     </row>
     <row r="7">
@@ -4582,7 +4582,7 @@
     </row>
     <row r="9">
       <c r="C9" s="16" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="G9" s="12"/>
       <c r="H9" s="14"/>
@@ -4599,7 +4599,7 @@
     </row>
     <row r="11">
       <c r="C11" s="16" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="12"/>
@@ -4619,7 +4619,7 @@
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="I14" s="12"/>
       <c r="K14" s="12"/>
@@ -4640,7 +4640,7 @@
     </row>
     <row r="17">
       <c r="C17" s="16" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="G17" s="12"/>
       <c r="K17" s="12"/>
@@ -4656,7 +4656,7 @@
     </row>
     <row r="19">
       <c r="C19" s="16" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="12"/>
@@ -4674,7 +4674,7 @@
       <c r="C22" s="16"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16" t="s">
-        <v>62</v>
+        <v>283</v>
       </c>
       <c r="K22" s="12"/>
     </row>
@@ -4691,7 +4691,7 @@
     </row>
     <row r="25">
       <c r="C25" s="16" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="G25" s="12"/>
       <c r="H25" s="14"/>
@@ -4710,7 +4710,7 @@
     </row>
     <row r="27">
       <c r="C27" s="16" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="12"/>
@@ -4731,7 +4731,7 @@
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="I30" s="12"/>
     </row>
@@ -4788,50 +4788,50 @@
   <sheetData>
     <row r="1" ht="270" customHeight="true">
       <c r="A1" s="17" t="str">
-        <f>'data'!$E$29</f>
+        <f>'data'!$E$3</f>
       </c>
       <c r="B1" s="18" t="str">
-        <f>'data'!D29</f>
+        <f>'data'!D3</f>
       </c>
     </row>
     <row r="2" ht="270" customHeight="true">
       <c r="A2" s="17" t="str">
-        <f>'data'!$E$26</f>
+        <f>'data'!$E$4</f>
       </c>
       <c r="B2" s="18" t="str">
-        <f>'data'!D26</f>
+        <f>'data'!D4</f>
       </c>
     </row>
     <row r="3" ht="270" customHeight="true">
       <c r="A3" s="17" t="str">
-        <f>'data'!$E$27</f>
+        <f>'data'!$E$5</f>
       </c>
       <c r="B3" s="18" t="str">
-        <f>'data'!D27</f>
+        <f>'data'!D5</f>
       </c>
     </row>
     <row r="4" ht="270" customHeight="true">
       <c r="A4" s="17" t="str">
-        <f>'data'!$E$28</f>
+        <f>'data'!$E$6</f>
       </c>
       <c r="B4" s="18" t="str">
-        <f>'data'!D28</f>
+        <f>'data'!D6</f>
       </c>
     </row>
     <row r="5" ht="270" customHeight="true">
       <c r="A5" s="17" t="str">
-        <f>'data'!$E$85</f>
+        <f>'data'!$E$7</f>
       </c>
       <c r="B5" s="18" t="str">
-        <f>'data'!D85</f>
+        <f>'data'!D7</f>
       </c>
     </row>
     <row r="6" ht="270" customHeight="true">
       <c r="A6" s="17" t="str">
-        <f>'data'!$E$79</f>
+        <f>'data'!$E$8</f>
       </c>
       <c r="B6" s="18" t="str">
-        <f>'data'!D79</f>
+        <f>'data'!D8</f>
       </c>
     </row>
     <row r="7" ht="270" customHeight="true">
@@ -4876,42 +4876,42 @@
     </row>
     <row r="12" ht="270" customHeight="true">
       <c r="A12" s="17" t="str">
-        <f>'data'!$E$61</f>
+        <f>'data'!$E$14</f>
       </c>
       <c r="B12" s="18" t="str">
-        <f>'data'!D61</f>
+        <f>'data'!D14</f>
       </c>
     </row>
     <row r="13" ht="270" customHeight="true">
       <c r="A13" s="17" t="str">
-        <f>'data'!$E$62</f>
+        <f>'data'!$E$15</f>
       </c>
       <c r="B13" s="18" t="str">
-        <f>'data'!D62</f>
+        <f>'data'!D15</f>
       </c>
     </row>
     <row r="14" ht="270" customHeight="true">
       <c r="A14" s="17" t="str">
-        <f>'data'!$E$88</f>
+        <f>'data'!$E$16</f>
       </c>
       <c r="B14" s="18" t="str">
-        <f>'data'!D88</f>
+        <f>'data'!D16</f>
       </c>
     </row>
     <row r="15" ht="270" customHeight="true">
       <c r="A15" s="17" t="str">
-        <f>'data'!$E$64</f>
+        <f>'data'!$E$17</f>
       </c>
       <c r="B15" s="18" t="str">
-        <f>'data'!D64</f>
+        <f>'data'!D17</f>
       </c>
     </row>
     <row r="16" ht="270" customHeight="true">
       <c r="A16" s="17" t="str">
-        <f>'data'!$E$35</f>
+        <f>'data'!$E$18</f>
       </c>
       <c r="B16" s="18" t="str">
-        <f>'data'!D35</f>
+        <f>'data'!D18</f>
       </c>
     </row>
     <row r="17" ht="270" customHeight="true">
@@ -4972,34 +4972,34 @@
     </row>
     <row r="24" ht="270" customHeight="true">
       <c r="A24" s="17" t="str">
-        <f>'data'!$E$82</f>
+        <f>'data'!$E$26</f>
       </c>
       <c r="B24" s="18" t="str">
-        <f>'data'!D82</f>
+        <f>'data'!D26</f>
       </c>
     </row>
     <row r="25" ht="270" customHeight="true">
       <c r="A25" s="17" t="str">
-        <f>'data'!$E$58</f>
+        <f>'data'!$E$27</f>
       </c>
       <c r="B25" s="18" t="str">
-        <f>'data'!D58</f>
+        <f>'data'!D27</f>
       </c>
     </row>
     <row r="26" ht="270" customHeight="true">
       <c r="A26" s="17" t="str">
-        <f>'data'!$E$59</f>
+        <f>'data'!$E$28</f>
       </c>
       <c r="B26" s="18" t="str">
-        <f>'data'!D59</f>
+        <f>'data'!D28</f>
       </c>
     </row>
     <row r="27" ht="270" customHeight="true">
       <c r="A27" s="17" t="str">
-        <f>'data'!$E$56</f>
+        <f>'data'!$E$29</f>
       </c>
       <c r="B27" s="18" t="str">
-        <f>'data'!D56</f>
+        <f>'data'!D29</f>
       </c>
     </row>
     <row r="28" ht="270" customHeight="true">
@@ -5044,10 +5044,10 @@
     </row>
     <row r="33" ht="270" customHeight="true">
       <c r="A33" s="17" t="str">
-        <f>'data'!$E$18</f>
+        <f>'data'!$E$35</f>
       </c>
       <c r="B33" s="18" t="str">
-        <f>'data'!D18</f>
+        <f>'data'!D35</f>
       </c>
     </row>
     <row r="34" ht="270" customHeight="true">
@@ -5084,26 +5084,26 @@
     </row>
     <row r="38" ht="270" customHeight="true">
       <c r="A38" s="17" t="str">
-        <f>'data'!$E$90</f>
+        <f>'data'!$E$40</f>
       </c>
       <c r="B38" s="18" t="str">
-        <f>'data'!D90</f>
+        <f>'data'!D40</f>
       </c>
     </row>
     <row r="39" ht="270" customHeight="true">
       <c r="A39" s="17" t="str">
-        <f>'data'!$E$91</f>
+        <f>'data'!$E$41</f>
       </c>
       <c r="B39" s="18" t="str">
-        <f>'data'!D91</f>
+        <f>'data'!D41</f>
       </c>
     </row>
     <row r="40" ht="270" customHeight="true">
       <c r="A40" s="17" t="str">
-        <f>'data'!$E$55</f>
+        <f>'data'!$E$42</f>
       </c>
       <c r="B40" s="18" t="str">
-        <f>'data'!D55</f>
+        <f>'data'!D42</f>
       </c>
     </row>
     <row r="41" ht="270" customHeight="true">
@@ -5148,10 +5148,10 @@
     </row>
     <row r="46" ht="270" customHeight="true">
       <c r="A46" s="17" t="str">
-        <f>'data'!$E$14</f>
+        <f>'data'!$E$48</f>
       </c>
       <c r="B46" s="18" t="str">
-        <f>'data'!D14</f>
+        <f>'data'!D48</f>
       </c>
     </row>
   </sheetData>
@@ -5189,10 +5189,10 @@
   <sheetData>
     <row r="1" ht="270" customHeight="true">
       <c r="A1" s="17" t="str">
-        <f>'data'!$E$17</f>
+        <f>'data'!$E$49</f>
       </c>
       <c r="B1" s="18" t="str">
-        <f>'data'!D17</f>
+        <f>'data'!D49</f>
       </c>
     </row>
     <row r="2" ht="270" customHeight="true">
@@ -5237,18 +5237,18 @@
     </row>
     <row r="7" ht="270" customHeight="true">
       <c r="A7" s="17" t="str">
-        <f>'data'!$E$42</f>
+        <f>'data'!$E$55</f>
       </c>
       <c r="B7" s="18" t="str">
-        <f>'data'!D42</f>
+        <f>'data'!D55</f>
       </c>
     </row>
     <row r="8" ht="270" customHeight="true">
       <c r="A8" s="17" t="str">
-        <f>'data'!$E$3</f>
+        <f>'data'!$E$56</f>
       </c>
       <c r="B8" s="18" t="str">
-        <f>'data'!D3</f>
+        <f>'data'!D56</f>
       </c>
     </row>
     <row r="9" ht="270" customHeight="true">
@@ -5261,18 +5261,18 @@
     </row>
     <row r="10" ht="270" customHeight="true">
       <c r="A10" s="17" t="str">
-        <f>'data'!$E$5</f>
+        <f>'data'!$E$58</f>
       </c>
       <c r="B10" s="18" t="str">
-        <f>'data'!D5</f>
+        <f>'data'!D58</f>
       </c>
     </row>
     <row r="11" ht="270" customHeight="true">
       <c r="A11" s="17" t="str">
-        <f>'data'!$E$6</f>
+        <f>'data'!$E$59</f>
       </c>
       <c r="B11" s="18" t="str">
-        <f>'data'!D6</f>
+        <f>'data'!D59</f>
       </c>
     </row>
     <row r="12" ht="270" customHeight="true">
@@ -5285,18 +5285,18 @@
     </row>
     <row r="13" ht="270" customHeight="true">
       <c r="A13" s="17" t="str">
-        <f>'data'!$E$68</f>
+        <f>'data'!$E$61</f>
       </c>
       <c r="B13" s="18" t="str">
-        <f>'data'!D68</f>
+        <f>'data'!D61</f>
       </c>
     </row>
     <row r="14" ht="270" customHeight="true">
       <c r="A14" s="17" t="str">
-        <f>'data'!$E$15</f>
+        <f>'data'!$E$62</f>
       </c>
       <c r="B14" s="18" t="str">
-        <f>'data'!D15</f>
+        <f>'data'!D62</f>
       </c>
     </row>
     <row r="15" ht="270" customHeight="true">
@@ -5309,10 +5309,10 @@
     </row>
     <row r="16" ht="270" customHeight="true">
       <c r="A16" s="17" t="str">
-        <f>'data'!$E$49</f>
+        <f>'data'!$E$64</f>
       </c>
       <c r="B16" s="18" t="str">
-        <f>'data'!D49</f>
+        <f>'data'!D64</f>
       </c>
     </row>
     <row r="17" ht="270" customHeight="true">
@@ -5341,10 +5341,10 @@
     </row>
     <row r="20" ht="270" customHeight="true">
       <c r="A20" s="17" t="str">
-        <f>'data'!$E$48</f>
+        <f>'data'!$E$68</f>
       </c>
       <c r="B20" s="18" t="str">
-        <f>'data'!D48</f>
+        <f>'data'!D68</f>
       </c>
     </row>
     <row r="21" ht="270" customHeight="true">
@@ -5389,10 +5389,10 @@
     </row>
     <row r="26" ht="270" customHeight="true">
       <c r="A26" s="17" t="str">
-        <f>'data'!$E$4</f>
+        <f>'data'!$E$74</f>
       </c>
       <c r="B26" s="18" t="str">
-        <f>'data'!D4</f>
+        <f>'data'!D74</f>
       </c>
     </row>
     <row r="27" ht="270" customHeight="true">
@@ -5429,10 +5429,10 @@
     </row>
     <row r="31" ht="270" customHeight="true">
       <c r="A31" s="17" t="str">
-        <f>'data'!$E$8</f>
+        <f>'data'!$E$79</f>
       </c>
       <c r="B31" s="18" t="str">
-        <f>'data'!D8</f>
+        <f>'data'!D79</f>
       </c>
     </row>
     <row r="32" ht="270" customHeight="true">
@@ -5453,10 +5453,10 @@
     </row>
     <row r="34" ht="270" customHeight="true">
       <c r="A34" s="17" t="str">
-        <f>'data'!$E$74</f>
+        <f>'data'!$E$82</f>
       </c>
       <c r="B34" s="18" t="str">
-        <f>'data'!D74</f>
+        <f>'data'!D82</f>
       </c>
     </row>
     <row r="35" ht="270" customHeight="true">
@@ -5477,10 +5477,10 @@
     </row>
     <row r="37" ht="270" customHeight="true">
       <c r="A37" s="17" t="str">
-        <f>'data'!$E$7</f>
+        <f>'data'!$E$85</f>
       </c>
       <c r="B37" s="18" t="str">
-        <f>'data'!D7</f>
+        <f>'data'!D85</f>
       </c>
     </row>
     <row r="38" ht="270" customHeight="true">
@@ -5501,10 +5501,10 @@
     </row>
     <row r="40" ht="270" customHeight="true">
       <c r="A40" s="17" t="str">
-        <f>'data'!$E$16</f>
+        <f>'data'!$E$88</f>
       </c>
       <c r="B40" s="18" t="str">
-        <f>'data'!D16</f>
+        <f>'data'!D88</f>
       </c>
     </row>
     <row r="41" ht="270" customHeight="true">
@@ -5517,18 +5517,18 @@
     </row>
     <row r="42" ht="270" customHeight="true">
       <c r="A42" s="17" t="str">
-        <f>'data'!$E$40</f>
+        <f>'data'!$E$90</f>
       </c>
       <c r="B42" s="18" t="str">
-        <f>'data'!D40</f>
+        <f>'data'!D90</f>
       </c>
     </row>
     <row r="43" ht="270" customHeight="true">
       <c r="A43" s="17" t="str">
-        <f>'data'!$E$41</f>
+        <f>'data'!$E$91</f>
       </c>
       <c r="B43" s="18" t="str">
-        <f>'data'!D41</f>
+        <f>'data'!D91</f>
       </c>
     </row>
     <row r="44" ht="270" customHeight="true">
@@ -5929,7 +5929,7 @@
     </row>
     <row r="4">
       <c r="A4" s="19" t="str">
-        <f>'data'!$B$26</f>
+        <f>'data'!$B$4</f>
       </c>
       <c r="B4" s="22"/>
       <c r="C4" s="22"/>
@@ -5937,10 +5937,10 @@
       <c r="E4" s="22"/>
       <c r="F4" s="22"/>
       <c r="G4" s="19" t="str">
-        <f>'data'!$B$29</f>
+        <f>'data'!$B$3</f>
       </c>
       <c r="I4" s="19" t="str">
-        <f>'data'!$B$17</f>
+        <f>'data'!$B$49</f>
       </c>
       <c r="J4" s="22"/>
       <c r="K4" s="22"/>
@@ -5948,7 +5948,7 @@
       <c r="M4" s="22"/>
       <c r="N4" s="22"/>
       <c r="O4" s="19" t="str">
-        <f>'data'!$B$42</f>
+        <f>'data'!$B$55</f>
       </c>
     </row>
     <row r="6">
@@ -6013,7 +6013,7 @@
     </row>
     <row r="12">
       <c r="A12" s="19" t="str">
-        <f>'data'!$B$85</f>
+        <f>'data'!$B$7</f>
       </c>
       <c r="B12" s="22"/>
       <c r="C12" s="22"/>
@@ -6021,7 +6021,7 @@
       <c r="E12" s="22"/>
       <c r="F12" s="22"/>
       <c r="G12" s="19" t="str">
-        <f>'data'!$B$28</f>
+        <f>'data'!$B$6</f>
       </c>
       <c r="I12" s="19" t="str">
         <f>'data'!$B$52</f>
@@ -6108,7 +6108,7 @@
         <f>'data'!$B$37</f>
       </c>
       <c r="I20" s="19" t="str">
-        <f>'data'!$B$42</f>
+        <f>'data'!$B$55</f>
       </c>
       <c r="J20" s="22"/>
       <c r="K20" s="22"/>
@@ -6181,7 +6181,7 @@
     </row>
     <row r="28">
       <c r="A28" s="19" t="str">
-        <f>'data'!$B$41</f>
+        <f>'data'!$B$91</f>
       </c>
       <c r="B28" s="22"/>
       <c r="C28" s="22"/>
@@ -6189,10 +6189,10 @@
       <c r="E28" s="22"/>
       <c r="F28" s="22"/>
       <c r="G28" s="19" t="str">
-        <f>'data'!$B$40</f>
+        <f>'data'!$B$90</f>
       </c>
       <c r="I28" s="19" t="str">
-        <f>'data'!$B$5</f>
+        <f>'data'!$B$58</f>
       </c>
       <c r="J28" s="22"/>
       <c r="K28" s="22"/>
@@ -6265,7 +6265,7 @@
     </row>
     <row r="36">
       <c r="A36" s="19" t="str">
-        <f>'data'!$B$62</f>
+        <f>'data'!$B$15</f>
       </c>
       <c r="B36" s="22"/>
       <c r="C36" s="22"/>
@@ -6273,10 +6273,10 @@
       <c r="E36" s="22"/>
       <c r="F36" s="22"/>
       <c r="G36" s="19" t="str">
+        <f>'data'!$B$14</f>
+      </c>
+      <c r="I36" s="19" t="str">
         <f>'data'!$B$61</f>
-      </c>
-      <c r="I36" s="19" t="str">
-        <f>'data'!$B$68</f>
       </c>
       <c r="J36" s="22"/>
       <c r="K36" s="22"/>
@@ -6349,7 +6349,7 @@
     </row>
     <row r="44">
       <c r="A44" s="19" t="str">
-        <f>'data'!$B$7</f>
+        <f>'data'!$B$85</f>
       </c>
       <c r="B44" s="22"/>
       <c r="C44" s="22"/>
@@ -6357,10 +6357,10 @@
       <c r="E44" s="22"/>
       <c r="F44" s="22"/>
       <c r="G44" s="19" t="str">
+        <f>'data'!$B$17</f>
+      </c>
+      <c r="I44" s="19" t="str">
         <f>'data'!$B$64</f>
-      </c>
-      <c r="I44" s="19" t="str">
-        <f>'data'!$B$49</f>
       </c>
       <c r="J44" s="22"/>
       <c r="K44" s="22"/>
@@ -6528,7 +6528,7 @@
         <f>'data'!$B$23</f>
       </c>
       <c r="I60" s="19" t="str">
-        <f>'data'!$B$74</f>
+        <f>'data'!$B$82</f>
       </c>
       <c r="J60" s="22"/>
       <c r="K60" s="22"/>
@@ -6601,7 +6601,7 @@
     </row>
     <row r="68">
       <c r="A68" s="19" t="str">
-        <f>'data'!$B$82</f>
+        <f>'data'!$B$26</f>
       </c>
       <c r="B68" s="22"/>
       <c r="C68" s="22"/>
@@ -6685,7 +6685,7 @@
     </row>
     <row r="76">
       <c r="A76" s="19" t="str">
-        <f>'data'!$B$56</f>
+        <f>'data'!$B$29</f>
       </c>
       <c r="B76" s="22"/>
       <c r="C76" s="22"/>
@@ -6704,7 +6704,7 @@
       <c r="M76" s="22"/>
       <c r="N76" s="22"/>
       <c r="O76" s="19" t="str">
-        <f>'data'!$B$4</f>
+        <f>'data'!$B$74</f>
       </c>
     </row>
     <row r="78">
@@ -6769,7 +6769,7 @@
     </row>
     <row r="84">
       <c r="A84" s="19" t="str">
-        <f>'data'!$B$3</f>
+        <f>'data'!$B$56</f>
       </c>
       <c r="B84" s="22"/>
       <c r="C84" s="22"/>
@@ -6853,7 +6853,7 @@
     </row>
     <row r="92">
       <c r="A92" s="19" t="str">
-        <f>'data'!$B$18</f>
+        <f>'data'!$B$35</f>
       </c>
       <c r="B92" s="22"/>
       <c r="C92" s="22"/>
@@ -6861,7 +6861,7 @@
       <c r="E92" s="22"/>
       <c r="F92" s="22"/>
       <c r="G92" s="19" t="str">
-        <f>'data'!$B$5</f>
+        <f>'data'!$B$58</f>
       </c>
       <c r="I92" s="19" t="str">
         <f>'data'!$B$81</f>
@@ -7021,7 +7021,7 @@
     </row>
     <row r="108">
       <c r="A108" s="19" t="str">
-        <f>'data'!$B$91</f>
+        <f>'data'!$B$41</f>
       </c>
       <c r="B108" s="22"/>
       <c r="C108" s="22"/>
@@ -7029,7 +7029,7 @@
       <c r="E108" s="22"/>
       <c r="F108" s="22"/>
       <c r="G108" s="19" t="str">
-        <f>'data'!$B$90</f>
+        <f>'data'!$B$40</f>
       </c>
       <c r="I108" s="19" t="str">
         <f>'data'!$B$87</f>
@@ -7113,10 +7113,10 @@
       <c r="E116" s="22"/>
       <c r="F116" s="22"/>
       <c r="G116" s="19" t="str">
-        <f>'data'!$B$15</f>
+        <f>'data'!$B$62</f>
       </c>
       <c r="I116" s="19" t="str">
-        <f>'data'!$B$40</f>
+        <f>'data'!$B$90</f>
       </c>
       <c r="J116" s="22"/>
       <c r="K116" s="22"/>
@@ -7281,7 +7281,7 @@
       <c r="E137" s="22"/>
       <c r="F137" s="22"/>
       <c r="G137" s="19" t="str">
-        <f>'data'!$B$27</f>
+        <f>'data'!$B$5</f>
       </c>
       <c r="I137" s="19" t="str">
         <f>CONCATENATE("M 18 ",O14)</f>
@@ -7365,7 +7365,7 @@
       <c r="E145" s="22"/>
       <c r="F145" s="22"/>
       <c r="G145" s="19" t="str">
-        <f>'data'!$B$79</f>
+        <f>'data'!$B$8</f>
       </c>
       <c r="I145" s="19" t="str">
         <f>CONCATENATE("M 19 ",O22)</f>
@@ -7460,7 +7460,7 @@
       <c r="M153" s="22"/>
       <c r="N153" s="22"/>
       <c r="O153" s="19" t="str">
-        <f>'data'!$B$3</f>
+        <f>'data'!$B$56</f>
       </c>
     </row>
     <row r="155">
@@ -7544,7 +7544,7 @@
       <c r="M161" s="22"/>
       <c r="N161" s="22"/>
       <c r="O161" s="19" t="str">
-        <f>'data'!$B$6</f>
+        <f>'data'!$B$59</f>
       </c>
     </row>
     <row r="163">
@@ -7628,7 +7628,7 @@
       <c r="M169" s="22"/>
       <c r="N169" s="22"/>
       <c r="O169" s="19" t="str">
-        <f>'data'!$B$15</f>
+        <f>'data'!$B$62</f>
       </c>
     </row>
     <row r="171">
@@ -7785,7 +7785,7 @@
       <c r="E185" s="22"/>
       <c r="F185" s="22"/>
       <c r="G185" s="19" t="str">
-        <f>'data'!$B$58</f>
+        <f>'data'!$B$27</f>
       </c>
       <c r="I185" s="19" t="str">
         <f>CONCATENATE("M 24 ",O62)</f>
@@ -7796,7 +7796,7 @@
       <c r="M185" s="22"/>
       <c r="N185" s="22"/>
       <c r="O185" s="19" t="str">
-        <f>'data'!$B$48</f>
+        <f>'data'!$B$68</f>
       </c>
     </row>
     <row r="187">
@@ -7953,7 +7953,7 @@
       <c r="E201" s="22"/>
       <c r="F201" s="22"/>
       <c r="G201" s="19" t="str">
-        <f>'data'!$B$4</f>
+        <f>'data'!$B$74</f>
       </c>
       <c r="I201" s="19" t="str">
         <f>CONCATENATE("M 27 ",O86)</f>
@@ -8037,7 +8037,7 @@
       <c r="E209" s="22"/>
       <c r="F209" s="22"/>
       <c r="G209" s="19" t="str">
-        <f>'data'!$B$8</f>
+        <f>'data'!$B$79</f>
       </c>
       <c r="I209" s="19" t="str">
         <f>CONCATENATE("M 28 ",O94)</f>
@@ -8048,7 +8048,7 @@
       <c r="M209" s="22"/>
       <c r="N209" s="22"/>
       <c r="O209" s="19" t="str">
-        <f>'data'!$B$8</f>
+        <f>'data'!$B$79</f>
       </c>
     </row>
     <row r="211">
@@ -8132,7 +8132,7 @@
       <c r="M217" s="22"/>
       <c r="N217" s="22"/>
       <c r="O217" s="19" t="str">
-        <f>'data'!$B$74</f>
+        <f>'data'!$B$82</f>
       </c>
     </row>
     <row r="219">
@@ -8205,7 +8205,7 @@
       <c r="E225" s="22"/>
       <c r="F225" s="22"/>
       <c r="G225" s="19" t="str">
-        <f>'data'!$B$55</f>
+        <f>'data'!$B$42</f>
       </c>
       <c r="I225" s="19" t="str">
         <f>CONCATENATE("M 30 ",O110)</f>
@@ -8216,7 +8216,7 @@
       <c r="M225" s="22"/>
       <c r="N225" s="22"/>
       <c r="O225" s="19" t="str">
-        <f>'data'!$B$7</f>
+        <f>'data'!$B$85</f>
       </c>
     </row>
     <row r="227">
@@ -8300,7 +8300,7 @@
       <c r="M233" s="22"/>
       <c r="N233" s="22"/>
       <c r="O233" s="19" t="str">
-        <f>'data'!$B$16</f>
+        <f>'data'!$B$88</f>
       </c>
     </row>
     <row r="235">
@@ -8355,7 +8355,7 @@
       <c r="M241" s="22"/>
       <c r="N241" s="22"/>
       <c r="O241" s="19" t="str">
-        <f>'data'!$B$41</f>
+        <f>'data'!$B$91</f>
       </c>
     </row>
     <row r="243">
@@ -9823,7 +9823,7 @@
     </row>
     <row r="5">
       <c r="C5" s="16" t="s">
-        <v>106</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
@@ -9834,7 +9834,7 @@
     </row>
     <row r="7">
       <c r="C7" s="16" t="s">
-        <v>95</v>
+        <v>23</v>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="12"/>
@@ -9863,7 +9863,7 @@
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
-        <v>99</v>
+        <v>27</v>
       </c>
       <c r="I14" s="12"/>
       <c r="K14" s="12"/>
@@ -9884,7 +9884,7 @@
     </row>
     <row r="17">
       <c r="C17" s="16" t="s">
-        <v>103</v>
+        <v>31</v>
       </c>
       <c r="G17" s="12"/>
       <c r="K17" s="12"/>
@@ -9900,7 +9900,7 @@
     </row>
     <row r="19">
       <c r="C19" s="16" t="s">
-        <v>273</v>
+        <v>35</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="12"/>
@@ -9918,7 +9918,7 @@
       <c r="C22" s="16"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16" t="s">
-        <v>256</v>
+        <v>39</v>
       </c>
       <c r="K22" s="12"/>
     </row>
@@ -9935,7 +9935,7 @@
     </row>
     <row r="25">
       <c r="C25" s="16" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G25" s="12"/>
       <c r="H25" s="14"/>
@@ -9954,7 +9954,7 @@
     </row>
     <row r="27">
       <c r="C27" s="16" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="12"/>
@@ -9975,7 +9975,7 @@
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I30" s="12"/>
     </row>
@@ -9993,7 +9993,7 @@
     </row>
     <row r="33">
       <c r="C33" s="16" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="G33" s="12"/>
     </row>
@@ -10007,7 +10007,7 @@
     </row>
     <row r="35">
       <c r="C35" s="16" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="12"/>
@@ -10053,7 +10053,7 @@
     </row>
     <row r="5">
       <c r="C5" s="16" t="s">
-        <v>197</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6">
@@ -10064,7 +10064,7 @@
     </row>
     <row r="7">
       <c r="C7" s="16" t="s">
-        <v>201</v>
+        <v>66</v>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="12"/>
@@ -10093,7 +10093,7 @@
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
-        <v>233</v>
+        <v>70</v>
       </c>
       <c r="I14" s="12"/>
       <c r="K14" s="12"/>
@@ -10114,7 +10114,7 @@
     </row>
     <row r="17">
       <c r="C17" s="16" t="s">
-        <v>209</v>
+        <v>74</v>
       </c>
       <c r="G17" s="12"/>
       <c r="K17" s="12"/>
@@ -10130,7 +10130,7 @@
     </row>
     <row r="19">
       <c r="C19" s="16" t="s">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="12"/>
@@ -10148,7 +10148,7 @@
       <c r="C22" s="16"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="K22" s="12"/>
     </row>
@@ -10165,7 +10165,7 @@
     </row>
     <row r="25">
       <c r="C25" s="16" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="G25" s="12"/>
       <c r="H25" s="14"/>
@@ -10184,7 +10184,7 @@
     </row>
     <row r="27">
       <c r="C27" s="16" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="12"/>
@@ -10205,7 +10205,7 @@
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I30" s="12"/>
     </row>
@@ -10223,7 +10223,7 @@
     </row>
     <row r="33">
       <c r="C33" s="16" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="G33" s="12"/>
     </row>
@@ -10237,7 +10237,7 @@
     </row>
     <row r="35">
       <c r="C35" s="16" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="12"/>
